--- a/output.xlsx
+++ b/output.xlsx
@@ -17,12 +17,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -43,14 +50,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,28 +423,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Designator</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Footprint</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Total Price</t>
         </is>
       </c>
     </row>
@@ -442,93 +487,30 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://lionelectronic.ir/products/2867-SMBJ16A</t>
-        </is>
+      <c r="B2" t="n">
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>لیون الکترونیک | SMBJ16A خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products Discrete Semiconductors Diodes And Rectifiers TVS Diodes - ESD Suppressors SMBJ16A 3,069 موجودی محصول تعداد قیمت 2 128,128 ریال 25 124,467 ریال 250 121,722 ریال 1000 119,891 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام SMBJ16A SMBJ16A Part Number 2867 Lion Part Download Datasheet Littelfuse Manufacture دیود TVS یک جهته 16 ولت با بیشنه پالس جریان 23.1 آمپر با پکیج SMB TVS Diode Uni-directional 16V SMB مشخصات دیود تی‌وی‌اس SMBJ16A دیود تی‌وی‌اس SMBJ16A Part Number 1 Number of Channels -65C Minimum Operating Temperature 30kV Vesd - Voltage ESD Air Gap Reel Packaging 30kV Vesd - Voltage ESD Contact SMD/SMT Termination style Unidirectional Polarity 600W Pppm - Peak Pulse Power Dissipation +150C Maximum Operating Temperature 16V Working Voltage 26V Clamping Voltage N/A Cd - Diode Capacitance 17.8V Breakdown Voltage 23.1A Ipp - Peak Pulse Current TVS Diodes Product Type DO-214AA (SMB) Package-Case نظرات کاربران ارسال نظر محصولات مرتبط SD03C SD03 SMF26A SMBJ350CA SMBJ400CA PESD12VS1UA PESD12VL1BA D5V0P4UR6SO-7 NUF8410MNT4G SMAJ58CA × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 3,069 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
+          <t>LED_TH-R_5mm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://eshop.eca.ir/سون-سگمنت/4726-سگمنت-نمایشگر-مدل-باتری-چهار-رنگ.html</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>سگمنت نمایشگر مدل باتری چهار رنگ دسته بندی ها search جستجو علاقه‌مندی ورود | ثبت‌نام 0 0 سبد خرید سبد خرید سبد خرید شما خالی است view_headline دسته‌بندی home خانه قطعات و تجهیزات الکترونیکی ابزارآلات و تجهیزات تجهیزات رباتیک ماژول ها منابع تغذیه و باتری مینی‌کامپیوترها نمایشگرها هوشمند سازی فروش ویژه خانه chevron_right قطعات و تجهیزات الکترونیکی chevron_right سگمنت و ماتریس chevron_right سون سگمنت chevron_right سگمنت نمایشگر مدل باتری چهار رنگ zoom_out_map chevron_left chevron_right سگمنت نمایشگر مدل باتری چهار رنگ کد کالا: 2061003031 نمایشگر بارگراف LED چهار رنگ برای نمایش میزان شارژ، سطح صدا یا داده‌های آنالوگ به‌صورت بصری و خطی 4.1 (13 رأی‌دهنده) دیدگاه کاربران 21 دیدگاه × اشتراک گذاری این کالا را با دوستان خود به اشتراک بگذارید کپی لینک ارسال سریع به سراسر کشور ارسال روزانه سفارش‌ها به تمامی نقاط ایران با امکان ارسال رایگان و روش‌های متنوع حمل بسته‌بندی حرفه‌ای و ایمن بسته‌بندی مناسب برای محافظت از قطعات الکترونیکی حساس در فرآیند حمل و جابه‌جایی خرید مطمئن از ECA ارائه کالاها با تضمین اصالت و پشتیبانی پس از فروش مقدار تخفیف تعداد درصد قیمت با تخفیف 10 3% 91,277‎ تومان 50 5% 89,395‎ تومان 100 7% 87,513‎ تومان 941,000 ریال موجود در انبار موجود در انبار shopping_cart افزودن به سبد خرید توضیحات این نمایشگر سگمنت رنگی از نوع بارگراف (Bar Graph LED) با 10 بخش مجزا و رنگ‌های متنوع آبی، سبز، زرد و قرمز طراحی شده است که با ولتاژ و جریان پایین راه‌اندازی می‌شود. طراحی آن به‌صورت فشرده و مستحکم بوده و به‌دلیل استفاده از بسته‌بندی جامد پلاستیکی، از دوام و پایداری بالایی برخوردار است. ویژگی‌هایی مانند زمان پاسخ‌دهی بسیار سریع کمتر از 0.1 میکروثانیه، زاویه دید گسترده، رنگ‌های شفاف و روشنایی بالا، این قطعه را به انتخابی مناسب برای نمایش‌های دینامیک در مدارهای مختلف تبدیل کرده است. این ماژول با درایو پیوسته و اسکن هر بایت، نمایش روان و یکنواختی فراهم می‌کند. استفاده از این ماژول به‌صورت جریان ثابت توصیه می‌شود تا از یکنواختی نوردهی اطمینان حاصل گردد. ابعاد کوچک و وزن سبک آن، امکان نصب آسان در فضای محدود را فراهم کرده و قابلیت اطمینان آن را در پروژه‌های صنعتی و آموزشی افزایش داده است. مشخصات نوع نمایش: بارگراف LED چندرنگ (چهار رنگ) تعداد سگمنت: 10 عدد رنگ سگمنت‌ها: آبی، سبز، زرد، قرمز زمان پاسخ‌دهی: کمتر از 0.1 میکروثانیه دمای کاری: -20~60°C دمای لحیم‌کاری: 260°C ابعاد: 26mm × 10mm ارتفاع ماژول: 8mm طول عمر مفید: بیش از 50000 ساعت نوع نصب: DIP کاربردهای رایج این نمایشگر برای نمایش تصویری مقادیر آنالوگ یا دیجیتال در سیستم‌های اندازه‌گیری یا هشدار به‌کار می‌رود. معمولاً در مدارهایی مانند نشانگر سطح باتری، نمایشگر شدت سیگنال صوتی (VU Meter)، سطح ولتاژ، شارژ کنترلرها و تجهیزات قابل‌حمل استفاده می‌شود. همچنین به‌دلیل زیبایی بصری بالا، در پروژه‌های DIY و آموزشی نیز محبوب است. نمایشگر سطح باتری در مدارهای شارژ نمایشگر شدت صوتی در آمپلی‌فایرها و میکسرهای صوتی نمایشگر دما در پروژه‌های سنسور نمایشگر ولتاژ در منبع تغذیه نشانگر سطح مایع یا فشار در سیستم‌های صنعتی نمایشگر شدت نور در سیستم‌های نورپردازی نمایشگر گرافیکی در بردهای آموزشی استفاده در پروژه‌های آردوینو و میکروکنترلری کاربرد تزئینی در گجت‌های الکترونیکی نشانگر وضعیت سیگنال در سیستم‌های مخابراتی Specification can drive the light emitting at a low voltage , low current condition emitting very short response time (&lt;0.1μs), good high-frequency characteristics , good color , high brightness small size, light weight, good impact resistance. Solid package , packages of plastic irrigation , high stability Long life , service life of 50,000 hours continuous scanning drive each byte good display , a wide viewing angle Recommended constant use , constant brightness appears uneven surface protective film products , can be peeled off before use temperature: -20-60 degrees Celsius soldering temperature : 260 ℃ to stay the longest five seconds Size: 26mm x 10mm height: 8mm 10 کالای مشابه local_mall سون سگمنت تکی 0.56 اینچ سبز آند مشترک 216,000 ریال local_mall نمایشگر سگمنتی چند منظوره PT6961 سایز 135x40mm 3,710,000 ریال local_mall سون سگمنت 2 دیجیت 0.3 اینچ قرمز کاتد مشترک کد LTD333P 258,000 ریال local_mall سون سگمنت مالتی پلکس 2 دیجیت 0.4 اینچ قرمز آند مشترک کد 482H 310,000 ریال local_mall سون سگمنت 2.5 دیجیت 0.40 اینچ قرمز آند مشترک 347,000 ریال local_mall سون سگمنت 4 دیجیت 0.4 اینچ قرمز آند مشترک کد 4N4H 545,000 ریال local_mall سون سگمنت تکی 0.4 اینچ سبز کاتد مشترک مارک LITE-ON کد LTS-4301G 150,000 ریال local_mall سون سگمنت 2 دیجیت 0.3 اینچ سبز کاتد مشترک کد BD-F30 238,000 ریال local_mall سون سگمنت 2 دیجیت 0.5 اینچ سبز کاتد مشترک 284,000 ریال local_mall سون سگمنت 2 دیجیت 0.56 اینچ قرمز کاتد مشترک کد 6740R 266,000 ریال کالاهای بازدید شده اخیر local_mall کابل فلت طوسی 30 رشته یک متر 966,000 ریال local_mall سیم افشان سایز 0.25 طوسی 15cm دو سر لخت بسته50 تایی 986,000 ریال 15% local_mall میکروکنترلر PIC16C72A-04/SP پکیج DIP 845,750 ریال 995,000 ریال local_mall ماسفت K10A60DR نوع N-Channel تایوانی مارک TOSHIBA پکیج TO-220FP 1,020,000 ریال local_mall مایع فلاکس عمومی 120cc تکنوشیمی 1,040,000 ریال local_mall ماژول رگولاتور کاهنده 12 ولت 3A 1,060,000 ریال local_mall پیچ گوشتی دوسر دوکاره مشتی 6X60mm 1,080,000 ریال local_mall LED COB سفید مهتابی 12W مدل LUSTROUS L112NW 1,100,000 ریال نظرات امتیاز شما 4.1 (امتیاز 13 رأی‌دهنده) دیدگاه کاربران 21 دیدگاه محمدرضا ماهرانی | 9 ماه پیش لطفا موجود کنید. 0 0 پاسخ | گزارش مشاهده پاسخ ها (1) محمدرضا ماهرانی | 11 ماه پیش این قطعه دیتاشیتی نداره و هیچ راهی نیست که قبل از خرید قطعه بشه آند و کاتدش را تشخیص داد و من هم باید الان طراحی را انجام بدم. لطفا مشخص کنید که در زمانی که مثلا رنگ آبی بالاست و رنگ قرمز پایین هست سمت چپ آند هست و راست کاتد و یا بالعکس؟ 0 0 پاسخ | گزارش پشتیبانی | 11 ماه پیش محمدرضا ماهرانی سلام می توانید از تصاویر شماتیک کلی و مشخصات موجود در انتهای توضیحات استفاده نمایید . 0 0 پاسخ | گزارش امیر حسین زاهدی پویا | 11 ماه پیش خریدار سلام من میخواهم برای نمایش میزان شارژ باتری ازش استفاده کنم میشه بگید چتور باهاش کار کنم 0 0 پاسخ | گزارش پشتیبانی | 11 ماه پیش امیر حسین زاهدی پویا سلام قابلیتی برای استفاده به صورت مستقیم ندارد و نیاز به طراحی یک مدار دارید پیشنهاد می شود از مدل های زیر استفاده نمایید . ماژول نمایشگر سطح شارژ باترى 12V روپنلی کد کالا: 3011015040 ماژول نمایشگر سطح شارژ باترى 60-12 ولت روپنلی کد کالا: 3011015142 ماژول نمایشگر سطح شارژ باترى اسیدی روپنلی 12V دارای 2 خروجی USB کد کالا: 3011015226 0 0 پاسخ | گزارش وحید زارعی | 4 سال پیش خریدار مثل اینکه باید از درایوری مانند LM391X - نوع مقیاس خطی آن - استفاده شود . ومثل هر LED بار گراف باید بشود با آن کار کرد.مثلا محدوده حد اکثر و حد اقل ولتاژ را ( بنا بر نوع باتری و تعداد آن ) برای آیسی فوق بایاس کرد . بعد از آن در محدوده ای که تعریف کرده اید - با حداقل ولتاژ باتری - اولین ال یی دی و با بیشترین ولتاژ - آن ال یی دی که باید آن باشد که وصل به سیم مربوط به نشانگر سر باتری (روی سطح نمایشگر) است - روشن شود. برتری این نمایشگر بر یک نمایشگر بار گراف معمولی - طبق آنچه در متن توضیح محصول نوشته شده - توان مصرفی کم آن و درخشندگی آن با جریان کم است. 0 0 پاسخ | گزارش بهروز کشکر | 5 سال پیش خریدار سلام اینطور که این عزیزان سایت راهنمایی میکنند نیست درسته که نه کاتد و نه اند مشترک نیست اما شما باید حتما براش بورد درست کنید و میتونید خودتون اند یا کاتد رو مشترک کنید نسبت به بوردی که میسازید و از ترانزیستور استفاده کنید چون مسلما قرار نیست همیشه روشن بمونه وگرنه خوردش از باتری مصرف میکنه باید یه دکمه کوچیک کنارش باشه وقتی زده میشه اطلاعات باتری رو به مدار بفرسته و از اون سمت مدار به نسبت بیاد ال ای دی های مجاز رو روشن کنه 0 0 پاسخ | گزارش فرهاد نوبخت | 5 سال پیش خریدار سلام . مقاومت چند اوهم باید باشه مثلا با باطری 12ولت .یا 6. 0 0 پاسخ | گزارش پشتیبانی | 5 سال پیش فرهاد نوبخت سلام، در ولتاژهای پایینتر کار می کند و برای ولتاژ های بالاتر باید مقاومت موردنیاز را خودتان حساب کنید. 0 0 پاسخ | گزارش مسعود پناهی | 6 سال پیش خریدار سلام این به مدار نیاز دارد اگر نیاز دارد مدار ای را دارید 0 0 پاسخ | گزارش پشتیبانی | 6 سال پیش مسعود پناهی سلام، نیاز به مدار خاصی ندارد با اعمال ولتاژ مناسب به پایه های متناظر سگمنت روشن می شود. 0 0 پاسخ | گزارش سید عباس حسینی | 6 سال پیش سلام آند مشترکه یا کاتد مشترک؟ ولتاژ مجازش هم همون 2 تا 2.2 ولته؟ ممنون 0 0 پاسخ | گزارش پشتیبانی | 6 سال پیش سید عباس حسینی سلام، این قطعه پایه مشترک ندارد. ولتاژ مجاز در محدوده مورد نظر می باشد. 0 0 پاسخ | گزارش حسین کیانی | 6 سال پیش سلام، خسته نباشید ماژول Goode GD-Y30 هم وارد کنین 0 0 پاسخ | گزارش Saleh  jaberi | 6 سال پیش سلام ابعاد سگمنت نمایشگر مدل باتری چهار رنگ چقدر هست 0 0 پاسخ | گزارش پشتیبانی | 6 سال پیش Saleh  jaberi سلام، اطلاعات مورد نیاز در توضیحات کالا آمده است. 0 0 پاسخ | گزارش 1 2 بعدی سگمنت نمایشگر مدل باتری چهار رنگ 941,000 ریال موجود در انبار موجود در انبار shopping_cart افزودن به سبد خرید × کامنت شما با موفقیت ثبت شد و پس از تایید نمایش داده خواهد شد. باشه × - گزارش نظر اگر این نظر نامناسب است، لطفاً دلیل خود را بنویسید تا بررسی شود. گزارش شما با موفقیت ثبت شد و به زودی بررسی می‌شود. ثبت گزارش نحوه خرید از فروشگاه ارسال رایگان تماس با ما پشتیبانی و مشاوره فنی نحوه خرید از فروشگاه × خرید سریع، ساده و مطمئن از ECA خرید از فروشگاه ECA سریع و ساده طراحی شده است. کافی است حساب کاربری ایجاد کنید، کالای مورد نظر را به سبد خرید اضافه کرده و با انتخاب روش پرداخت و ارسال، سفارش خود را نهایی کنید. پس از ثبت سفارش، تیم فروشگاه در کوتاه‌ترین زمان سفارش شما را آماده و ارسال می‌کند و شما می‌توانید از طریق پنل کاربری، وضعیت سفارش خود را به‌صورت لحظه‌ای مشاهده کنید. قیمت کالاها به‌صورت به‌روز بوده و می توانید سریع و مطمئن، خرید خود را انجام دهید. اگر در هر مرحله از انتخاب یا ثبت سفارش نیاز به راهنمایی داشتید، تیم فروش آماده پاسخگویی و راهنمایی شما است. ساخت / ورود به حساب پیگیری سفارش‌ها مشاهده راهنمای کامل خرید ارسال رایگان × ارسال رایگان برای خریدهای بالای ۱۰ میلیون تومان برای سفارش‌های بیش از ۱۰ ,۰۰۰,۰۰۰ تومان ، ارسال پستی رایگان به سراسر کشور فعال است تا هزینه‌های جانبی خرید کمتر شود و تهیه قطعات تخصصی راحت‌تر انجام شود. پیگیری سفارش‌ها تماس با بخش فروش راهنمای خرید شرایط و زمان ارسال تماس با ما × دفتر مرکزی تبریز شماره تماس: 041-51388888 ایمیل: eshop.eca@gmail.com آدرس: تبریز، مابین باغ گلستان و چهارراه شریعتی، مجتمع تجاری گلستان، واحد ۷ * برای پیگیری سفارش‌های اینترنتی، استعلام موجودی و پشتیبانی وب‌سایت فقط با دفتر مرکزی تبریز تماس بگیرید. دفتر فروش تهران آدرس: تهران، خیابان جمهوری، نرسیده به پل حافظ، پاساژ توکل، طبقه زیرهمکف، واحد B6 (تاپ‌ترونیک) شماره تماس فروش: 021-66741971 * دفتر تهران ویژه فروش حضوری و مشتریان عمده است و امور پشتیبانی سفارش‌های آنلاین از این دفتر انجام نمی‌شود. پشتیبانی و مشاوره فنی × با پشتیبانی فنی و تخصصی، قبل و بعد از خرید کنار شما هستیم در صورت وجود هرگونه سوال فنی درباره کالاها، می‌توانید سوال خود را در بخش نظرات همان کالا ثبت کنید تا توسط کارشناسان فنی بررسی و پاسخ داده شود. پس از خرید نیز تیم پشتیبانی ECA در کنار شما خواهد بود. در صورت بروز هرگونه مشکل یا نیاز به راهنمایی، می‌توانید با در دست داشتن شماره سفارش، با امور مشتریان ECA به شماره 51388888-041 تماس بگیرید. همچنین می‌توانید از طریق سامانه خدمات پس از فروش ECA درخواست خود را ثبت کنید تا کارشناسان فنی در سریع‌ترین زمان ممکن رسیدگی کنند. برای آموزش و راه‌اندازی تجهیزات نیز می‌توانید از انجمن تخصصی برق و الکترونیک ECA استفاده کنید. تماس با پشتیبانی انجمن های تخصصی خدمات پس از فروش اطلاع از موجودی × باید برای اطلاع از موجودی وارد
-                        حساب کاربری خود شوید اطلاعات امور مشتریان: 041-51388888 آدرس دفتر مرکزی تبریز: تبریز، چهارراه شریعتی، مجتمع تجاری گلستان، واحد ۷ آدرس فروشگاه تهران: تهران، خیابان جمهوری، نرسیده به پل حافظ، پاساژ توکل، طبقه زیرهمکف، واحد B6 (تاپ ترونیک) بخش‌های فروشگاه شرايط و قوانین فروشگاه راهنمای خرید درباره‌ی ما حریم خصوصی بخش‌های سایت صفحه اصلی انجمن‌های تخصصی ECA بلاگ ECA سفارش و ساخت برد مدار چاپی جدید سامانه خدمات پس از فروش اینستاگرام تلگرام بله اضافه کردن به علاقه‌مندی × add_circle_outline ایجاد لیست جدید ایجاد لیست جدید × نام لیست نباید خالی باشد. ((label)) توضیحات لیست ((cancelText)) ((createText)) Sign in × برای ذخیره کالا در لیست علاقمندی‌ها باید وارد حساب کاربری خود شوید. ((cancelText)) ((loginText)) تمامی کالاها و خدمات این فروشگاه دارای مجوز‌های لازم از مراجع مربوطه می‌باشند و فعالیت های این سایت تابع قوانین و مقررات جمهوری اسلامی ایران است. خانه دسته بندی فروش ویژه 0 0 سبد خرید سبد خرید سبد خرید شما خالی است جستجو علاقه‌مندی ورود | ثبت‌نام search جستجوهای پرطرفدار close × error_outline ×</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://shop.ideaelec.com/product/behinex100gr4/</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ERROR: 403 Client Error: Forbidden for url: https://shop.ideaelec.com/product/behinex100gr4/</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.javanelec.com/shop/category/4/electromechanical/الکترومکانیکی#dtl/1943</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>الکترومکانیکی خانه دسته‌بندی‌ها الکترومکانیکی قطعات الکترومکانیکی فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش برند 180 Advanced Acoustic Technology Corp. Advantech Corp Agilent Technologies Albright International Ltd Alps Electric Co American Zettler, Inc. APEM Inc Audiowell Electronics Co Autonics Corporation Avago Technologies BAFO Technologies Corp Bivar, Inc Bosch Semiconductors Bosch Sensortec Bourns Inc Broadcom Limited C&amp;K Components California Eastern Laboratories Celduc relais Central Georgia Generator Changzhou Cre-sound Electronics Changzhou Esuntech Co Changzhou TDA Electronic Changzhou Yuanwang Fluid Technology CiXi KaiFeng Electronics Co Clare, Inc Cliff Electronic Components Limited Coto Technology Crydom Inc CTS Corporation CUI Inc Daier Electron Co Davies Molding, LLC DB Unlimited Deep Sea Electronics Delta Electronics Deva Electronic Controls Limited. Diptronics Manufacturing Inc Dualsky Models Co Duoxing Electronics Co Eledis ELESTA GmbH Emerson Enrwey Co Ltd E-Switch, Inc E-T-A Circuit Breakers Excel Cell Electronic Faulhaber GmbH Finder Relays, Inc Formosa MS FOTEK Controls Fujitsu Semiconductor Fujitsu-Takamisawa Fulihua Printer Ribbon Co General Monitors Global Mixed-mode Technology Grayhill Inc GRUNER AG Hangzhou Prosper Hanyoung Nux Co Harwin Hewlett-Packard Highly Electric HITPOINT Inc Honeywell International Hongfa Electroacoustic Co Huaqi Microelectronics Co ICP DAS CO IDEC Corporation Infineon Technologies International Rectifier IRAN ITT Cannon, LLC IXYS Integrated Circuits JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Johnson Electric Kai Suh Suh Enterprise KSS Kaihua Electronics Co Kelly Controls, LLC KEMET Corporation Key Technology Keystone Electronic Kingstate Electronics Knowles Electronics KUOYUH W.L. Enterprise Co L-com, Inc Littelfuse Inc Lixin Electromagnetic Clutch Longview Technologies Co MACOM Technology Manorshi Electronics Marquardt Switches, Inc Matsushita Electric Maxim Integrated Maxon motor MEAN WELL Enterprises Co MikroElektronika Mill-Max Mfg Monitor Enterprises Inc Monolithic Power Systems MORNSUN Science &amp; Technology Multicomp NEC Electronics Nidec Copal Electronics Ningbo East Electronics Ningbo ForwardRelayCorporationLTD Ningbo Huaguan Electronics Ningbo Songle Relay Ningbo Tianbo Ganglian Electronics Ninigi NKK Switches Non-Brand Novatek Microelectronics OKI Semiconductor Omron Electronics Omten Electronics Opticon Inc Opto 22 OTAX Corporation Other Panasonic Corporation PEAK-System Technik Penny &amp; Giles Phoenix Contact Pickering Electronics Ltd Pro-Wave Electronic PUI Audio RAFI GmbH &amp; Co Ready Made RC LLC Reichelt elektronik GmbH &amp; Co. KG RELPOL S.A Saia-Burgess Switches Salecom Electronics SANCO Electronics Co Sanjiaozhou Electrical Technology Sanyo Denki Sanyo Electric Schrack Technik GmbH Seaparks Machinery-Electronics Seeed Technology Seiko Instruments Inc Sensirion Servotecnica SpA SERVO-TEK PRODUCTS COMPANY, INC. Shanghai Houde Photo-electric SHARP Corporation Shenzhen Baishan Mechatronics Siemens Semiconductor Group Sinomags Technologies Co Sizto Tech Corp SMSC Corporation Soberton Inc Softing Automotive Electronics Sola/Hevi-Duty Song Chuan Soundwell Electronic SparkFun Electronics SPX Flow Technology STMicroelectronics Taiwan Alpha Electronic Co Tamagawa seiki Co TDK Corporation (EPCOS) TE Connectivity Telechips Inc Teledyne Technologies Texas Instruments THORLABS Toshiba Corporation Ultisensor Electronics Unictron Technologies Corporation. US Digital Vishay Waveshare Electronics Woosim Systems Xiamen Cashino Electronic YAKO Automation Technology Yueqing Winston Electric ZETTLER electronics GmbH Zhejiang HKE Co = پکیج 56 3590S Axial Axial Surface Mount Board Cable Circular Connector Cylindrical DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 ISOPLUS-264 Module Motor Nut Other Package U Panel Mount Programmer Radial Screw SDIP-10 SIP-4 SMD 5x5x2 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Square SSOP-4 Surface Mount Switch Switch Cap Through-hole TO-5 Tool = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز برند پکیج مرتب کردن مرتب سازی All Products Electromechanical اوریجینال HEAD PHILLIPS SELF TAPPING SCREW 3*10MM IRAN Screw 3,240 ریال اضافه به سبد خرید اوریجینال CAP SCREW M3*6 IRAN Screw 3,240 ریال اضافه به سبد خرید اوریجینال HEXAGON NUT 3MM IRAN Nut 3,870 ریال اضافه به سبد خرید اوریجینال THIN HEX NUT 6MM Non-Brand Nut 4,500 ریال اضافه به سبد خرید اوریجینال LED SPACER 5*7MM Non-Brand Connector 7,120 ریال اضافه به سبد خرید اوریجینال LED SPACER 5*10MM Non-Brand Connector 8,060 ریال اضافه به سبد خرید اوریجینال HEXAGON NUT INCH Non-Brand Nut 8,640 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال CAP SCREW M2.5*5 Non-Brand Screw 16,900 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال PLASTIC HEX SPACER 7MM Non-Brand Cylindrical 26,600 ریال اضافه به سبد خرید اوریجینال HEX JACK SCREW 5MM H IRAN Cylindrical 26,800 ریال اضافه به سبد خرید اوریجینال PLASTIC HEX SPACER 10MM H Non-Brand Cylindrical 30,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال PLASTIC HEX SPACER 10MM Non-Brand Cylindrical 33,400 ریال اضافه به سبد خرید اوریجینال PLASTIC HEX SPACER 15MM Non-Brand Cylindrical 44,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال HEX JACK SCREW 5MM IRAN Cylindrical 50,000 ریال اضافه به سبد خرید اوریجینال HEX JACK SCREW 5 INCH IRAN Cylindrical 50,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
+          <t>+3V3,+5V,+12V</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LED-TH_BD5.8-P2.54-FD</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>https://www.javanelec.com/shop/product/11930/non-brand/led-smd-1206-red/%d8%a7%d9%84-%d8%a7%db%8c-%d8%af%db%8c-%d8%a7%d8%b3-%d8%a7%d9%85-%d8%af%db%8c-1206-%d9%82%d8%b1%d9%85%d8%b2</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>LED SMD 1206 RED | ال ای دی  اس ام دی 1206 قرمز خانه دسته‌بندی‌ها All Products LED Lighting LED Emitters Standard LEDs-SMD اوریجینال ال ای دی  اس ام دی 1206 قرمز نام کارخانه‌ای: LED SMD 1206 RED برند: Non-Brand کشور سازنده: چین پکیج: 1206 3216 بسته‌بندی: Tape &amp; Reel - 3,000 عدد حداقل: 15 عدد عنوان گروه: Standard LEDs-SMD دیتاشیت: LED SMD 1206 RED Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات ال ای دی  اس ام دی 1206 قرمز ال ای دی  اس ام دی 1206 قرمز از خانواده ال ای دی اس ام دی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج 1206 جریان 25 میلی آمپر ولتاژ مستقیم 2 ولت توان (وات) 75 میلی وات حداقل دمای عملیاتی -30 درجه سانتیگراد حداکثر دمای عملیاتی +85 درجه سانتیگراد نوع LED رنگ روشنایی Red طول موج 635 نانو متر شدت نور 180 ام سی دی زاویه دید 130 درجه اندازه ال ای دی 3.2 میلیمتر رنگ لنز Colorless LED SMD 1206 RED یک دیود نورافشان نصب سطحی (SMD LED) با پکیج 1206 و نور قرمز (Red) است که برای کاربردهایی مانند نشانگرهای وضعیت (Status Indicator)، بردهای الکترونیکی، تجهیزات صنعتی، پنل‌های کنترلی، تابلوهای LED، تجهیزات مخابراتی و پروژه‌های مبتنی بر فناوری SMD طراحی شده است. این LED به دلیل ابعاد استاندارد، مصرف توان پایین، روشنایی مناسب، زاویه دید گسترده و طول عمر بالا در انواع تجهیزات الکترونیکی و صنعتی کاربرد فراوانی دارد. 💡 کاربردهای اصلی: نشانگرهای وضعیت (Status Indicators) بردهای الکترونیکی SMD پنل‌های کنترل صنعتی تجهیزات مخابراتی تجهیزات پزشکی تابلوهای LED تجهیزات اندازه‌گیری لوازم الکترونیکی مصرفی پروژه‌های مبتنی بر Arduino، STM32، AVR و PIC سیستم‌های هشدار و اعلان ✅ مزایا: ابعاد استاندارد 1206: پکیج 1206 نسبت به پکیج‌های کوچک‌تر مانند 0603 و 0805 ابعاد بزرگ‌تری دارد و علاوه بر مونتاژ خودکار، برای مونتاژ دستی نیز مناسب است. مصرف انرژی پایین: با توان 75 میلی‌وات و جریان کاری 25 میلی‌آمپر ، مصرف انرژی کمی داشته و برای تجهیزات کم‌مصرف مناسب است. نور قرمز واضح: طول موج 635 نانومتر باعث ایجاد نور قرمز شفاف و قابل مشاهده برای کاربردهای نمایشی و نشانگر می‌شود. شدت نور مناسب: شدت نور 180 میلی‌کندلا برای استفاده در نشانگرها، پنل‌های کنترلی و تجهیزات الکترونیکی کاملاً مناسب است. زاویه دید گسترده: زاویه تابش 130 درجه موجب توزیع یکنواخت نور و مشاهده مناسب از زوایای مختلف می‌شود. لنز شفاف: وجود لنز Colorless باعث افزایش کیفیت انتشار نور و ظاهر مناسب LED در زمان خاموش و روشن بودن می‌شود. طول عمر بالا: ساختار LED موجب کاهش مصرف انرژی، تولید حرارت کمتر و افزایش دوام و قابلیت اطمینان قطعه می‌شود. محدوده دمای کاری مناسب: قابلیت عملکرد در دمای 30- تا 85+ درجه سانتی‌گراد امکان استفاده از این LED را در محیط‌های صنعتی و تجاری فراهم می‌کند. 🎯 جمع‌بندی: LED SMD 1206 RED یک دیود نورافشان SMD با پکیج 1206 است که دارای نور قرمز، توان 75 میلی‌وات، ولتاژ مستقیم 2 ولت، جریان کاری 25 میلی‌آمپر، طول موج 635 نانومتر، شدت نور 180 میلی‌کندلا، زاویه دید 130 درجه و لنز شفاف می‌باشد. به دلیل ابعاد استاندارد، مصرف انرژی پایین، روشنایی مناسب، لنز شفاف، زاویه دید گسترده، نصب آسان، طول عمر بالا و عملکرد پایدار ، این LED گزینه‌ای مناسب برای نشانگرهای وضعیت، بردهای الکترونیکی، تجهیزات صنعتی، مخابراتی، پزشکی، تابلوهای LED و انواع پروژه‌های الکترونیکی SMD محسوب می‌شود. Features انتخاب ویژگی Power Rating 75 mW ≤ = ≥ Forward Current (If) 25 mA ≤ = ≥ Illumination Color Red Wavelength 635 nm ≤ = ≥ Forward Voltage (Vf) 2 V ≤ = ≥ Luminous Intensity 180 mcd ≤ = ≥ Viewing Angle 130 deg ≤ = ≥ Lens Color Colorless LED Size 3.2 mm ≤ = ≥ Type LED Minimum Operating Temperature -30 °C ≤ = ≥ Maximum Operating Temperature +85 °C ≤ = ≥ Brand Non-Brand Package 1206 جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 85 4,610 ریال 4,560 ریال 500
                                                         عدد 4,510 ریال 1,000
@@ -536,73 +518,2497 @@
                                                         عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4610</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>13830</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/product/11932/non-brand/led-smd-1206-yellow/%d8%a7%d9%84-%d8%a7%db%8c-%d8%af%db%8c-%d8%a7%d8%b3-%d8%a7%d9%85-%d8%af%db%8c-1206-%d8%b2%d8%b1%d8%af</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>LED SMD 1206 YELLOW | ال ای دی  اس ام دی 1206 زرد خانه دسته‌بندی‌ها All Products LED Lighting LED Emitters Standard LEDs-SMD اوریجینال ال ای دی  اس ام دی 1206 زرد نام کارخانه‌ای: LED SMD 1206 YELLOW برند: Non-Brand کشور سازنده: چین پکیج: 1206 3216 بسته‌بندی: Tape &amp; Reel - 3,000 عدد حداقل: 10 عدد عنوان گروه: Standard LEDs-SMD دیتاشیت: LED SMD 1206 YELLOW Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات ال ای دی  اس ام دی 1206 زرد ال ای دی  اس ام دی 1206 زرد از خانواده ال ای دی اس ام دی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج 1206 توان (وات) 75 میلی وات جریان 25 میلی آمپر ولتاژ مستقیم 2.4 ولت حداقل دمای عملیاتی -30 درجه سانتیگراد حداکثر دمای عملیاتی +85 درجه سانتیگراد نوع LED رنگ روشنایی Yellow طول موج 596 نانو متر زاویه دید 130 درجه اندازه ال ای دی 3.2 میلیمتر شدت نور 180 ام سی دی رنگ لنز Colorless LED SMD 1206 YELLOW یک دیود نورافشان نصب سطحی (SMD LED) با پکیج 1206 و نور زرد (Yellow) است که برای کاربردهایی مانند نشانگرهای وضعیت (Status Indicator)، بردهای الکترونیکی، پنل‌های کنترلی، تجهیزات صنعتی، نمایشگرها، سیستم‌های هشدار و پروژه‌های مبتنی بر فناوری SMD طراحی شده است. این LED به دلیل ابعاد استاندارد، مصرف توان پایین، روشنایی مناسب، زاویه دید گسترده و طول عمر بالا در انواع تجهیزات الکترونیکی و صنعتی کاربرد گسترده‌ای دارد. 💡 کاربردهای اصلی: نشانگرهای وضعیت (Status Indicators) چراغ‌های هشدار و اعلان بردهای الکترونیکی SMD پنل‌های کنترل صنعتی تجهیزات مخابراتی تجهیزات پزشکی نمایشگرها و ماژول‌های LED تجهیزات اندازه‌گیری لوازم الکترونیکی مصرفی پروژه‌های مبتنی بر Arduino، STM32، AVR و PIC سیستم‌های روشنایی و علائم هشدار ✅ مزایا: ابعاد استاندارد 1206: پکیج 1206 نسبت به پکیج‌های 0603 و 0805 بزرگ‌تر بوده و برای مونتاژ خودکار و همچنین مونتاژ دستی مناسب است. مصرف انرژی پایین: با توان 75 میلی‌وات و جریان کاری 25 میلی‌آمپر ، مصرف انرژی کمی داشته و برای مدارهای کم‌مصرف مناسب است. نور زرد واضح: طول موج 596 نانومتر باعث ایجاد نور زرد شفاف و مناسب برای کاربردهای نمایشی، هشدار و نشانگر می‌شود. شدت نور مناسب: شدت نور 180 میلی‌کندلا برای استفاده در نشانگرهای وضعیت و پنل‌های کنترلی کاملاً مناسب است. زاویه دید گسترده: زاویه تابش 130 درجه موجب توزیع یکنواخت نور و مشاهده مناسب از زوایای مختلف می‌شود. لنز شفاف: وجود لنز Colorless باعث افزایش کیفیت انتشار نور و ظاهر مناسب LED در زمان خاموش و روشن بودن می‌شود. طول عمر بالا: فناوری LED موجب کاهش مصرف انرژی، تولید حرارت کمتر و افزایش دوام و قابلیت اطمینان قطعه می‌شود. محدوده دمای کاری مناسب: قابلیت عملکرد در دمای 30- تا 85+ درجه سانتی‌گراد استفاده از این LED را در محیط‌های صنعتی و تجاری امکان‌پذیر می‌کند. 🎯 جمع‌بندی: LED SMD 1206 YELLOW یک دیود نورافشان SMD با پکیج 1206 است که دارای نور زرد، توان 75 میلی‌وات، ولتاژ مستقیم 2.4 ولت، جریان کاری 25 میلی‌آمپر، طول موج 596 نانومتر، شدت نور 180 میلی‌کندلا، زاویه دید 130 درجه و لنز شفاف می‌باشد. به دلیل ابعاد استاندارد، مصرف انرژی پایین، روشنایی مناسب، لنز شفاف، زاویه دید گسترده، نصب آسان، طول عمر بالا و عملکرد پایدار ، این LED گزینه‌ای مناسب برای نشانگرهای وضعیت، بردهای الکترونیکی، تجهیزات صنعتی، مخابراتی، پزشکی، سیستم‌های هشدار و انواع پروژه‌های الکترونیکی SMD محسوب می‌شود. Features انتخاب ویژگی Power Rating 75 mW ≤ = ≥ Forward Current (If) 25 mA ≤ = ≥ Illumination Color Yellow Wavelength 596 nm ≤ = ≥ Forward Voltage (Vf) 2.4 V ≤ = ≥ Luminous Intensity 180 mcd ≤ = ≥ Viewing Angle 130 deg ≤ = ≥ Lens Color Colorless LED Size 3.2 mm ≤ = ≥ Type LED Minimum Operating Temperature -30 °C ≤ = ≥ Maximum Operating Temperature +85 °C ≤ = ≥ Brand Non-Brand Package 1206 جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 85 5,310 ریال 5,250 ریال 500
+                                                        عدد 5,200 ریال 1,000
+                                                        عدد 4,670 ریال 3,000
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5310</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>5310</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>https://lionelectronic.ir/products/2221-XL-3216UBC</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>لیون الکترونیک | XL-3216UBC خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products LED Lighting LED Color LEDs XL-3216UBC 9,900 موجودی محصول تعداد قیمت 100 9,456 ریال 500 9,141 ریال 1500 8,952 ریال 3000 8,826 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام XL-3216UBC XL-3216UBC Part Number 2221 Lion Part Download Datasheet XINGLIGHT Manufacture ال ای دی آبی پکیچ 1206 LED Blue 455-475nm 1206 25mA 75mW مشخصات ال‌ای‌دی آبی XL-3216UBC ال‌ای‌دی آبی XL-3216UBC Part Number Blue Illumination Color 120° Viewing Angle Reel Packaging SMD/SMT Mounting Style 75mW Power Rating -30C Minimum Operating Temperature 42-86mcd Luminous Intensity +85C Maximum Operating Temperature 25mA If - Forward Current 455-475nm Wavelength-Color Temperature 1206 (3216 metric) Package-Case 2.6-3.2V Vf - Forward Voltage نظرات کاربران ارسال نظر محصولات مرتبط XL-1005UYC XL-1005UWC XL-1005SURC XL-1005UBC XL-1005UGC SK6812MINI-E XL-3215UYC XL-3215UGC XL-3215SURC WS2812D-F8 × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 9,900 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9456</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>9456</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TSB008A2518A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BOOT,RST</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SW-SMD_L6.0-W3.5-LS8.2</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/category/202/switches/%d8%b3%d9%88%d8%a6%db%8c%da%86-%d9%88-%da%a9%d9%84%db%8c%d8%af#dtl/35210</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10900</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>21800</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1u</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/category/202/switches/%d8%b3%d9%88%d8%a6%db%8c%da%86-%d9%88-%da%a9%d9%84%db%8c%d8%af#dtl/7605</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>10900</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>10900</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.javanelec.com/shop?searchfilter=100nf%201206#dtl/7589</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>محصولات خانه دسته‌بندی‌ها فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه عبارت 100nf 1206 جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش برند 1666 3M Dynapro 3M Interconnect 3PEAK Incorporated 4D Systems Pty Ltd A Power microelectronics AAEON Technology Aavid Thermalloy ABC Taiwan Electronics ABLIC Inc Abracon Corporation Acam-Messelectronic Acrian, Inc Actel Corporation Active-Semi, Inc Actox Corporation. AD Semiconductor Confidential Adafruit Industries LLC Adam Technologies, Inc ADDA Corp ADDtek Corp Adesto Technologies ADMtek Inc Advanced Acoustic Technology Corp. Advanced Analog Technology Advanced Analogic Technologies Advanced Card Systems Advanced Ceramic X Corp Advanced Linear Devices Inc Advanced Monolithic Systems Advanced Photonix, Inc Advanced Power Electronics Corp Advanced Power Technology Advanced Semiconductor Advantech Corp Advantech Equipment Corporation Aegis Electronic Group AEL Crystals Limited AEM, Inc Aerosemi Technology Co Afa Technologies Inc AG Electrical Technology Agere Systems Agilent Technologies AGM Semiconductor AIC tech Inc. Aimtec Aimtron Corporation Airoha Technology Corp AIRWAVE Technologies Inc AiSHi Capacitors Aixin Opto-Electrical Technology Albright International Ltd Alcatel Microelectronics Alcor Micro Corp Alex Connector Co Ltd Alfa Electronics Algocraft Srl. ALi Corporation Alinx Electronic Technology All Sensors Corporation Allegro Microsystems Alliance Memory Allied Vision, Inc. Allwinner Technology Almita Co. Ltd Alpha &amp; Omega Semiconductor Alpha Micro Components Alpha Semiconductor Alpha Wire Alphasense Ltd, Sensor Technology Alps Electric Co Altera Corporation Amazing Electronic Co Amazing Microelectronic Corp AMD American Microsemiconductors American Microsystems Inc American Power Management American Technical Ceramics Corp American Zettler, Inc. Ametherm, Inc AMI Semiconductor AMIC Technology Corp Amidon Associates, Inc Amlogic Inc. Amotech Corp AMPAK Technology Inc Amphenol Advanced Sensors Amphenol Corporation Amphenol FCI Amphenol RF Ampleon USA Inc ams AG Anachip Corp ANADIGICS Anadigm, Inc Analog Devices Analog Integrations Corporation Analog Microelectronics Analog Power Analogix Semiconductor Inc Anaren, Inc Ancol Electronics Co Andigilog, Inc ANENG Anhui FOSAN Semiconductor Anhui Vico Technologes Co Anovay Technologies Limited ANPEC Electronics Corp Ante Intelligent Company Limited AP Memory Technology. APC Propellers APEM Inc Apex Material Technology Apex Precision Power API Delevan Inc API Technologies Aplus Integrated Circuits Inc APMKorea Apogee Technology, Inc Applent Instruments Applied Micro Circuits Co AppoTech Ltd APT Electronics Co., Ltd. Aptek Technologies ArchNet Technology Arcol UK Ltd Arduino Arduino Nicla Voice. Arima Lasers Corporation Aristotle Enterprises Inc ARTCHIP Semiconductor Artesyn Embedded Technologies AS ENERGI Asahi Kasei Microdevices ASAHI Solder Asia Vital Components Asiliant Technologies ASIX Electronics Corp AsLic Microelectronics Corporation ASMedia Technology Inc. Associated Opto-Electronics Astec Semiconductor. Astrodyne TDI Corporation. ATE Electronics s.r.l Atech Technology Co ATEN International Co Atheros Communications, Inc ATI Technologies Inc Atlas Scientific LLC. Attend Technology Inc AU Optronics Corp Audiowell Electronics Co Auk Contractors Co AUK Semiconductor AUO Corporation AUREL S.P.A Austar Technology AuthenTec, Inc Autonics Corporation Avago Technologies AVANTEK INC. AverLogic Technologies, Inc AVerMedia Technologies Avia Semiconductor Avnet, Inc AVX Corporation AXElite Technology Co Axiomtek Axis Communications AZ Displays, Inc Azoteq Ltd BAFO Technologies Corp Bahar Enclosure Baumer International BBT-China Inc BCD Semiconductor Beckhoff Automation Beijing Boshida Beijing HRH Information Co Beijing Ultrasonic Beijing Yihongtai Technology Beijing Zhongxun Sifang Science &amp; Technology Beken Corporation Bel Fuse Inc Bel Power Solutions Inc Belden Inc Bellnix Bencent Tzeng Ind. Co. Ltd Betlux Beyond Innovation Technology BI Technologies Bicker Elektronik GmbH Billionton Systems Inc Bird Technologies Bi-Sonic Technology Bivar, Inc Blackhawk BLOCK Inc Bluegiga Technologies BOLYMIN,INC BONGSHIN LOADCELL CO. Bookly Micro Electronic Bosch Security Systems Inc Bosch Semiconductors Bosch Sensortec Bothhand USA Boundary Devices Bourns Inc Bowin Microelectronics Brainboxes Limited BRIGHT LED ELECTRONICS CORP. Bright Power Semiconductor BrightKing Inc Brilliance Semiconductor, Inc Broadchip Technology Broadcom Limited BroadLight Inc Brooktree Corporation Burr-Brown Corporation BYD Microelectronics Co., Ltd. C&amp;D Technologies C&amp;K Components Caddock Electronics Inc California Eastern Laboratories California Micro Devices Calogic LLC Cambridge Integrated Circuits Cambridge Silicon Ra dio Limited Camille Bauer Ltd Catalyst Semiconductor Celduc relais CellWise Microelectronics Co Cenker Enterprise Ltd Centenary Materials Co CeNtRa Science Corp Central Components Manufacturing Central Georgia Generator Central Semiconductor CEVA Technologies CFSensor Challenge Electronics Champion Microelectronic Changzhou changjie Technology Co Changzhou Cre-sound Electronics Changzhou DRM Changzhou Esuntech Co Changzhou Kennon ELectronics Changzhou TDA Electronic Changzhou Yuanwang Fluid Technology Chaozhou Three-circle (Group) Co chargebyte GmbH. Chengdu Ebyte Electronic Technology Chengdu Guosheng Technology Chengdu Xincheng Huachuang Electronic ChenMoun Electronic ChenYang Technologies Cheuk Yui Innovation Co Chi Mei Optoelectronics Chieful Science ＆ Technology Chilisin Electronics Co China Base Electronic Technology China ECU Tools Centre China Resources Microelectronics China Software Industry Association Chinfa Electronics Chingis Technology Corp Chino-Excel Technology Chipanalog Incorporated ChipLink Tech Chiplus Semiconductor ChipON Chipower Electronics CHIPS Technology Chipstar Microelectronics CHK Electronics Ltd Chogori USA Chongqing Shengpu Electronics Chrontel, Inc Chunghwa Picture Tubes Churod Electronics Chyao Shiunn Electronic Cincon Electronics Cinetech Ind Cirrus Logic Inc Cisco Systems CIT Relay &amp; Switch Citizen Finedevice Co Cixi AnXon Electronic Cixi Dafa precise Linker Co CiXi KaiFeng Electronics Co Cixi Kefa Electronics Cixi Max Electronics Co.,Ltd Clare, Inc Cliff Electronic Components Limited Cmedia Electronics Inc CML Microsystems Coil Master Co Coil Winding Coilcraft Inc Coiltronics (Eaton) Comchip Technology Commodore Semiconductor Comtec Crystals comtech aha corporation CONEC Elektronische Bauelemente GmbH Conesys,Inc. Conexant Systems, Inc Connfly Electronic Co Connor-Winfield Conquer Electronic Continental Device India Controlair Inc Conversion Devices, Inc Cooper Bussmann Coretek Opto Corporation. Cornell Dubilier Electronics Cortina Systems, Inc Cosel Co Ltd COSINE Nanoelectronics Coto Technology CR Powtech Co Cree, Inc Crydom Inc Crystal Semiconductor Corporation Crystalfontz Crystek Corporation CSCONN PRECISE ELECTRONICS CO.,LTD CT Micro International Co CTS Corporation CUI Inc CVI Laser, LLC CW Industries Cyntec Co Cypress Semiconductor Cyrustek Corporation CYStech Electronics Corp. CYT Opto-Electronic Technology Dachang Electronics Daewoo Semiconductor Daier Electron Co Dailywell Electronics Daishinku Corp Daito Communication Apparatus Daiyo Electronics Dallas Semiconductor DANFOSS Daniels Manufacturing Co Data Device Corporation Davicom Semiconductor Davies Molding, LLC DB Lectro Inc DB Unlimited DC Components Co Dean Technology DECA SwitchLab Inc Decawave Ltd Dechang Electronic Deep Sea Electronics DEGSON Electronics Co Dell Inspiron Delta Electronics DeMint Electronics DENSO Destiny Technology Corp Detaik Technology Co Deva Electronic Controls Limited. Devantech Device Engineering Inc Dexter Magnetic Technologies DFRobot. Dialight Electronics Company Dialog Semiconductor Dielectric Laboratories Digi International Digilent, Inc Digital Voice Systems Digitrax, Inc Digitron Semiconductors Dinkle International Co. Ltd DIN-TEK Microelectronics Diodes Incorporated Diotec Semiconductor Diptronics Manufacturing Inc Display Solution AG DISPLAY VISIONS GmbH 2022. DMB Technology DOESTEK Co DOINGTER Semiconductor Domintech Co Don Connex Electronics DONG IL TECHNOLOGY LTD. Dongguan CHENGXING Electronic Co Dongguan City Wasi Electronic Technology Dongguan Cosson DongGuan HeLing Electronics Dongguan Lanbo Electronics Technology CO Dongguan Yuandi Electronics Dongguan Yuanze Electric Co.,Ltd Dongguan Yuxi Precise Connector Co., Ltd Dongke semiconductor Anhui Co., Ltd Donguan Keyouda Electronic Dosilicon Co DTK electronics Dualsky Models Co Duoxing Electronics Co Duty-Cycle Semiconductor Dynamic Technologies (DTCC) Dynex Semiconductor Ltd, E &amp; E Magnetic Products Limited EAST Semiconductor East Texas Integrated Circuits Eastrising Technology Co Eastsensor Technology Easy IoT Eaton’s Bussmann Ebm-papst inc Echelon Corporation Ecliptek Corporation ECOFIT &amp; ETRI ECS, Inc International EDAC EECO Switch E-Elements Technology Co Efficient Power Conversion Co EG Microelectronics Corp EIC Semiconductor Elan Microelectronics Co Elantec, Inc Electrolube Electronic Alliance Electronic Assembly Electronic Devices Inc Electroustic Ltd Eledis Element14 ELESTA GmbH Elite Semiconductor Memory Eljen Technology Elm Electronics ELM Technology Co Elmos Semiconductor AG ELNA Company Elpida Memory, Inc EM Microelectronic-Marin EMAD Embedded Artists Embest Technology Emerson Encitech Endress+Hauser Management ENE Technology Enplas Corporation Enrwey Co Ltd Eon Silicon Solution E-peas Semiconductors Epitex Inc Epoxy Technology Inc EPSON Electronics Ept Inc Ericsson Microelectronics ERNI Electronics ERSA UK LTD Espressif Systems ESS Technologies E-Switch, Inc ET Enterprises Limited E-T-A Circuit Breakers ETA Solutions E-tec Interconnect Ethertronics Inc Etron Technology, Inc EUCHNER GmbH Eupec semiconductor Euroquartz Ltd Eutech Microelectronics Everanalog Everest Semiconductor Everlight Electronics Everspin Technologies Exar Corporation Excel Cell Electronic Excelitas Technologies Excellence Opto, Inc Excelliance MOS Corporation Fagor Electronica Fairchild Semiconductor Fair-Rite Products Corp FANUC Corporation Faraday Technology Fastline Fastrax Ltd FASTRON Faulhaber GmbH FDK Corporation Feature Integration Technology Feei Cherng Enterprise Feeling Technology Feiyi Technology FEMA Electronics Corporation Fenghua Advanced Technology Ferroxcube International FERYSTER Sp. z.o.o Figaro Engineering Inc Finder Relays, Inc Fingerprint Cards First Semiconductor First Sensor FIS Inc Fischer Connectors Fischer Elektronik Fitipower Integrated Technology Force MOS Technology Co Formosa MS Formox Semiconductor Forsentrk Fortior Technology Co Fortune Semiconductor Forward International Electronics FOTEK Controls Fox Electronics Foxconn Technology Fractus S.A Franz Binder GmbH &amp; Co. Free2Move Holding AB. Freescale Semiconductor Fremont Micro Devices Friendcom Technology Develop FriendlyARM Computer Tech FTDI Chip Fuda Hisi Microelectronics Fuji Electric Fujikura Fujitsu Semiconductor Fujitsu-Takamisawa Fulihua Printer Ribbon Co Futaba Corporation Fu-Yao Technology Co Fuzetec Technology Co Fuzhou Rockchip Electronics Co., Ltd GainSpan Corporation GalaxyCore Inc GaNPower International Inc G-Antetech Industrial Garmin Ltd. Gas Sensing Solutions Ltd. Gaston Electronics GC GE Fanuc GEC Plessey Geehy Semiconductor Co General Electronic Devices General Monitors General Semiconductor Generalplus Technology GeneSiC Semiconductor Genesis Microchip Inc Genesys Logic, Inc Genicom Co., Ltd. Gennum Corporation GETE Electronics GigaDevice Semiconductor Global Connector Technology (GCT) Global Mixed-mode Technology GlobespanVirata, Inc GMC Instruments GME Technology, LLC GoChip Electronic Technology GoldStar Semiconductor Gonbes Technology Co Good Display Good Will Instrument Good-Ark Semiconductor Goodix Technology Governors America Co Gpixel Microelectronics Inc Grayhill Inc GreatLEDs Co Greenliant Systems GRUNER AG GSI Technology, Inc Guangdong Hottech Co Guangdong Huaguan Semiconductor Guangdong TIANQIU Electronics Technology Guangzhou Aosong Electronics Guangzhou Xinyue Electronic Guerrilla RF, Inc H&amp;M Semiconductor HABEY Halbleiter aus Frankfurt HALO Electronics Hamamatsu Photonics Hangzhou Grow Technology Co Hangzhou Nationalchip Science Hangzhou Prosper Hangzhou Silan Microelectronics Hannstar Display Corp HanRun Electronics Hanwei Electronics Co Hanyoung Nux Co HAOHAI ELECTRONICS HAOYU Electronics Harris Semiconductor HARTING Technology Harvatek Corporation Harwin Hawyang Semiconductor Hebei International Trading Co HEITEC AG. Hemingruizhi Electronic Henan Hanwei Electronics Co Hengda New Materials Technology HengJiaXing Electronics Co Henkel Corporation HenLv Power Technology Heter Electronics Hewlett-Packard Hexin Technology Highly Electric Hi-Link Electronic Technology Hi-Optel Technology Hirose Electric Hi-Sincerity Microelectronics Hitachi Maxell, Ltd Hitachi Semiconductor HITPOINT Inc Hittite Microwave Hivolt Capacitors Ltd H-JTAG Technology Hokuriku Electric Industry Co Ltd Hokuyo Automatic Co Holt Integrated Circuits Holtek Semiconductor Honeywell International Hong Kong Resistors Manufactory Hongfa Electroacoustic Co HONGHUA ELECTRONIC Hope Microelectronics HORIBA, Ltd. Hosiden Corporation Hosonic Electronic Co Hotchip Technology HTC Korea TAEJIN Technology Huada Connectors Huanor International Huaqi Microelectronics Co Huawei Technologies Huayu Technology HuaYuan Micro Electronic Huayue Microelectronics Co HUBER+SUHNER Huibei KENTO Electronic Huidu Technology Hukx Sensor Technology Humirel Hurricane Tech. Co HW group s.r.o HYCON Technology Corp. Hynix Semiconductor Hyundai Semiconductor IC Plus Corp ICE Components, Inc. iC-Haus GmbH Icom Inc ICP DAS CO ID Innovations ID TECH IDEC Corporation IEI Integration Ignion Iintelligent Motion Systems IK Semiconductor ILSI America LLC IMP, Inc Inchange Semiconductor Industrial Fiber Optics, Inc Industrial Technology Research Institute Infineon Technologies Initio Corporation INJOINIC TECHNOLOGY Innolux Corporation InnoSenT-Innovative Radar Sensor Technology Innovative Sensor Technology IST Innuovo Magnetics Co Inova Semiconductors InPlay Inc. InPower Semiconductor INTEGRAL JSC Integrated Circuit Solution Integrated Circuit Systems Integrated Crystal Technology Integrated Device Technology Integrated Sensor Technologies Integrated Silicon Solution Intel Corporation InterFET Corp Interlink Electronics International CMOS Technology International Rectifier Intersil Corporation Intronic Semiconductor Intronics Power, Inc InvenSense Inc IQD Frequency Products Ltd IRAN Ironwood Electronics IRXON Electronic Isabellenhütte Heusler GmbH &amp; Co KG Isahaya Electronics Co iSentek Technology Isocom Components Isotek Corp ITE Tech ITT Cannon, LLC ITT Semiconductors Ituner Networks Corp iWatt Inc IXYS Integrated Circuits J.S.T. Mfg. Co JACKSON ELECTRONICS IND. CROP. JAE Electronics JAI Ltd Jamicon Electronics JAVAN JCET Group Co JCI Jewel Hill Electronic Co JHDLCM Electronics Jiangsu Changjiang Electronics Jiangsu Donghai Semiconductor Jiangsu Juguang Jiangsu Runic Technology Co Jiangsu Szdhdtgd Electronics Jiangxi Jia Wei Cheng Electronic Jilin Sino-Microelectronics Co Jinan USR IOT Technology JING LI Power Electronics Jingcheng Electronics Co Jinghan Switch Electronic JMicron Technology Corp JNHuaMao Technology JODO International Johanson Dielectrics Johanson Technology Johnson Electric JPC Company JYE Tech Ltd JYH HSU(JEC) ELECTRONICS Kai Suh Suh Enterprise KSS Kaida Holding Kaihua Electronics Co Kangmu Sheng Electronics Ka-Ro electronics GmbH. KEC Semiconductor Keil Elektronik Keithley Instruments Kelly Controls, LLC KEMET Corporation Key Technology Keysight Technologies Keystone Electronic King Core Electronics Kingbor Technology Kingbright Electronic KingCCTV Technology Kingdatron Electronic Industrial Co Kingsignal Technology Kingstate Electronics Kingston KIOXIA America, Inc Kiwi Instruments Corp Knowles Electronics KOA Speer Electronics Kobiconn Kodenshi Corp Kohshin Electric Corporation KONE Elevator Kontron S&amp;T KT Micro Inc Kunshan Sino Silicon Technology KUOYUH W.L. Enterprise Co Kutai Electronics Kycon, Inc Kyocera Corporation Ladder Electronics Co Laird Performance Materials. Laird Technologies Laser Components Lattice Semiconductor LawMate International L-com, Inc LD-PD Inc. Leadtrend Technology Corp LEAP Electronic Legerity, Inc Lelon Electronics Corp LEM Components LEMO Lenovo LENZE Lesfuse Electric Co Leshan Radio Co LG Semiconductor LG.Philips Displays Lianchao Future Technology Lighting Integration System Ligitek Electronics Co Lime Microsystems Lineage Power Private Limited Linear Systems Linear Technology Linfinity Microelectronics Link-PP Int'l Technology LinkSmart LINP OMTER International Linx Technologies Lision Technology LITE-ON Semiconductor Littelfuse Inc Lixin Electromagnetic Clutch LIZE Electronic Technology LND, INC LOETRONIC LOGIC Devices Incorporated Longtech Optics Co Longview Technologies Co Lovid International Electronic Low Power Radio Solutions Ltd LOZEN TECHNOLOGY LS ELECTRIC LS Mtron Ltd LSI Computer Systems LTKCHIP LTN Servotechnik GmbH Lucent Technologies LUCKFOX Technology Lucky Light Electronic Luguang Electronic Technology Lumberg Holding Lumentum Operations LLC. Lumex Inc Lumileds Luminus, Inc. Lumissil Microsystems Luna Optoelectronics Lutron Electronic Enterprise Co Lyontek Inc M.S. Kennedy Corp M+R Multitronik GmbH MACOM Technology Macroblock, Inc Macronix International MacTek Corp MagnaChip Semiconductor Magnetics MagnTek Microelectronics Magtek Technology Inc Manorshi Electronics Marktech Optoelectronics, Inc Marlow Industries, Inc Marquardt Switches, Inc Marvell International Matsushita Electric Max Echo Technology Corp MaxBotix Inc Maxic Technology Corporation Maxim Integrated MaxLinear Inc Maxon motor Maxwell Technologies Mayloon Electronic Company MCS Logic Inc Mcuzone International MEAN WELL Enterprises Co Measurement Specialties Mechanic MediaTek Inc Megatek Melexis Technologies Memory Protection Devices MEMSIC, Inc Mentor GmbH Mercury Electronic Meritek Electronics Corporation Mersen EP Metalink Broadband Meticom GmbH. METRODYNE MICROSYSTEM CORP. MIC Electronic Micrel, Inc Micro Commercial Components Micro Crystal AG Micro Electronics Micro Linear Micro One Electronics Micro Power Systems MICRO SENSOR CO;LTD Microchip Technology Microdiode Semiconductor Micrometals, Inc Micron Technology Micronet Communication Microsemi Corporation Microtech Technology Co Ltd Microtherm Sentronic GmbH Microtips Technology Midori Precisions MikroElektronika MikroElektronika d.o.o MikroTik Mill-Max Mfg Milnec Interconnect Systems MindMotion Microelectronics Co. Mingtek Electronics Ltd Mini-Circuits Minilogic Device Corporation Ltd Minmax Technology Minsoo Electronic Co MiTAC Computing Technology Mitel Semiconductor Mitsubishi Electric Mitsubishi Rayon Co Mitsumi Electric Co Mixed Signal Integration Mixic Electronics MKMX America LLC MMI Semiconductors MOAI electronics co Mobicon Electronic Component Modulestek Inc MOKO TECHNOLOGY LTD. Molex Electronic Monitor Enterprises Inc Monolithic Power Systems Morethanall Co Morningstar Corporation MORNSUN Science &amp; Technology Mosdesign Semiconductor Corp Mosel Vitelic Co MOSPEC Semiconductor MOS-TECH Semiconductor Mostek MOTIEN Technology Motorola Mstar Semiconductor M-Systems Inc Multicomp Multi-Inno Technology Multi-Tech Systems Inc Murata Manufacturing Co MVSILICON MYIR Tech Myrra SAS Naina Semiconductor Limited. Nanjing Haichuan Electronic Nanjing Ouzhuo Tech Nanjing Qinheng Microelectronics Nanjing Shiheng Elec NanJing Top Power ASIC Nanjing Up Electronic Technology Nanjing Wotian Technology Co Nanjing Zeming Electronic Co Nanya Technology Co National Instruments National Semiconductor NDK America Inc NEC Electronics Nell Semiconductor Neltron Industrial Nemoto Sensor Engineering NeuroSky, Inc. Neutrik New Jersey Semiconductor NewAE Technology Inc. Newava Technology Inc. Newhaven Display Newport Corporation NewTec Display Co NexFlash Technologies, Inc Nexperia USA Inc Nextchip Nextion NIC Components Corp. Nichia Corporation Nichicon Corporation Nidec Copal Electronics NIDEC SERVO CORPORATION. Nihon Dempa Kogyo Nihon Inter Electronics NIKO Semiconductor Ningbo East Electronics Ningbo ForwardRelayCorporationLTD Ningbo Gosun Technology Co Ningbo Huaguan Electronics Ningbo KLS Electronic Co Ningbo MAX Electronic Technology Co., Ltd Ningbo MKX Electronic Technology Ningbo Rel Electric Co., Ltd. Ningbo Songle Relay Ningbo Tianbo Ganglian Electronics Ninigi Nippon Chemi-Con Nippon Pulse America, Inc Nisshinbo Micro Devices Inc NJR Corporation NKK Switches NMB Technologies Non-Brand Norcomp Inc Nordic Semiconductor Noritake Itron Co Novacap Novatek Microelectronics NTE Electronics NUAND LLC. Nuvoton Technology NVE Corporation Nvidia NVS Navigation Technologies NXP Semiconductors NYS Resistor O2Micro OCIC co Octavo Systems LLC Ogemray Technology Co Ohmite OKI Semiconductor Ole Wolff Electronics Inc Olimex OmniVision Technologies Omron Electronics Omten Electronics ON Semiconductor ON Semiconductor CHINA On Shore Technology On-Bright Electronics OPTEK Technology Inc OPTi Inc Opticon Inc Opto 22 Opto Diode Corp Opto Electronics Co,. LTD OPTOLAB Microsystems Orient Display Oriental Semiconductor Orion Orion Display Technology Co OSI Optoelectronics OSRAM Opto Semiconductors OTAX Corporation Other Oupiin Enterprise Co OWON Technology Inc P&amp;E Microcomputer Systems Pacific Silicon Sensor Panasonic Corporation Panavision Imaging LLC Pancon Corporation PandaBoard PANJIT International Inc Para Light Electronics P-DUKE Technology Co PEAK Electronics GmbH PEAK-System Technik Penny &amp; Giles Peregrine Semiconductor Pericom Semiconductor Corp PerkinElmer Inc Phidgets, Inc Philips Semiconductor Phison Electronics Phoenix Contact Pickering Electronics Ltd PICO Electronics Pico Technology Piher Sensors &amp; Controls SA Pingjing Semi Technology PIR Sensor Co PixArt Imaging Inc Planar Systems, Inc PLX Technology PMC-Sierra, Inc PNI Sensor Corporation POCO Magnetic Polyfet RF Devices Polytronics Technology Pomona Electronics Power Integrations Power Mate Technology Power Systems GmbH Power-Changer Electronic Co Powerex Inc PowerPlaza Powersem GmbH Powertip Technology Preci-Dip SA Precision Monolithics, Inc PREMA Semiconductor GmbH Premier Magnetics PRETEC/C-One Technology Corp. Princeton Technology Proant AB Profichip GmbH Prokit's Industries Prolific Technology Inc Promax-Johnton Semiconductor Pro-Signal ProTek Devices Pro-Wave Electronic PRT PUI Audio Pulse Electronics Qimei Optical &amp; Electric Qingdao Mefine Electronics Qingxian Zeming Langxi Electronic Devices Co Qingyuan Tesla Electronic Technology Qorvo QT Brightek (QTB) QT Optoelectronics Qualcomm Atheros, Inc Quality Semiconductor Qualtek Electronics Quarton inc Quasar Electronics Limited Quectel Wireless Solutions QuickLogic Corporation QX Micro Devices Radiall Radxa Computer Rafael Microelectronics RAFI GmbH &amp; Co RAiO TECHNOLOGY INC RAKwireless Technology Limited. RALEC Ltd Ralink Technology Raltron Electronics Corporation Ramtron International Rapid Electronics Ltd Raspberry Pi Raycom Co Raytac Corporation. Raytheon RCA Corporation Ready Made RC LLC Realtek Semiconductor RECOM Power GmbH Rectron Semiconductor Reichelt elektronik GmbH &amp; Co. KG RELPOL S.A Renata SA Renesas Technology Renhotec Group Ltd Reomax Electronics Reyed Electronics Co RF Digital Corporation. RF Micro Devices RF Solutions Ltd RFaxis, Inc RFHIC Corporation RFM Integrated Device, Inc. RFT Mikroelektronik Rhombus Industries Inc Richtek Technology Co RichWave Technology Ricoh Electronic Devices Riedon RIGOL Ring&amp;tone Electronic Technology Riverdi RLS Merilna tehnika d.o.o ROBOTIS Co Rockwell Rogers Corporation ROHM Semiconductor Roithner Lasertechnik GmbH Rongtech Industry Royal Electronic Factory Co RS Components Ltd RTD Embedded Technologies Rubycon RYCHIP Semiconductor s.m.a.e. GmbH Saft Groupe S.A Sagami Electronics Saia-Burgess Switches Sakae Tsushin Kogyo Saleae, Inc Salecom Electronics Same Sky SamHop Microelectronics Samsung Electronics Samtec Samwha Capacitor Samwin Electronic Technology Samyoung S &amp; C Co SANCO Electronics Co SanDisk Sanhe Enclosure Sanjiaozhou Electrical Technology Sanken Electric SanRex Corporation Sanyo Denki Sanyo Electric Savantic Electronic Sawnics Inc Schaffner Group Schott AG Schrack Technik GmbH Schurter Inc Sciosense B.V. SCTF Electronics Seagate Technology LLC Seaparks Machinery-Electronics Seaward Electronics SeCoS Corporation SEED International Ltd Seeed Technology SEEQ Technology Segger Microcontroller Systems Seiko Instruments Inc Seiko NPC Corporation Semiconductor Circuits, Inc SemiHow Semikron Semiment Technologies Semi-Powerex Corp. SEMITEC Corporation SemiWell Semiconductor Semtech Corporation Semtech Electronics Senba Sensing Technology Co Sendo Sensor Sensata Technologies Sensirion Sentry Manufacturing Inc SEP Electronic Corp Servotecnica SpA SERVO-TEK PRODUCTS COMPANY, INC. SG Micro Corp SGX Sensortech Shaanxi Fullstar Electronics Co Shaanxi Qunli Electric Shaanxi Reactor Microelectronics Shandong Jingdao Microelectronics Shanghai AVIC Optoelectronics Shanghai Belling Co,Ltd Shanghai Consonance Electronics Shanghai Fengxin Electronic Technology Shanghai Fudan Microelectronics Shanghai Gotop Technology Shanghai High-Flying Electronics Shanghai Houde Photo-electric Shanghai Mixinno Microelectronics Co Shanghai Natlinear Electronics Shanghai Xinlong Semiconductor Shanghai Zhichuan Electronic Tech SHARP Corporation Sheng Jay Automation Techno Shenyang Guangcheng Technology Co., Ltd Shenyang KingStar Automation ShenZhen AI-thinker CO Shenzhen AnBoShi Electronic Shenzhen Asenware Test Shenzhen Baishan Mechatronics Shenzhen Biosled Technology Shenzhen Bolutek Technology Shenzhen Chipsea Technologies ShenZhen ChipSourceTek Technology Shenzhen ExSAF Electronics Co Shenzhen Genesis-Systech ShenZhen Gerbole Shenzhen Getech Co Shenzhen GUANGSHIMEI Electronic Shenzhen Hanxia Electronics Shenzhen Haolin Electronics Shenzhen Heliwei Technology Shenzhen honglifa Electronics Co Shenzhen HongyeX Electronics Co ShenZhen HuaXinAn Electronics Co.,Ltd Shenzhen Injoinic Technology Co. Shenzhen Jin Yu Semiconductor Co ShenZhen JINCI Technology Shenzhen Jinrui Electronic Material Co Shenzhen JMRTH Co Shenzhen Kaiyuexiang Electronics Co Shenzhen LFN Technology Co Shenzhen Lodestar S.T Co Shenzhen Lumen Electronics Shenzhen Magnetic Technology Shenzhen MilkV Technology Shenzhen Milliohm Electronics Shenzhen Minewsemi Co., Ltd Shenzhen Nsiway Tech Shenzhen Ou Chuangxin Semiconductor ShenZhen Qi Dian Shi Dai Technology Shenzhen Ruichips Semiconductor Shenzhen Ruilongyuan Electronics Shenzhen Shiji Lighting Shenzhen SI Semiconductors Shenzhen SLKOR Micro Semicon Co Shenzhen Sunmoon Microelectronics Shenzhen Suosemi Tech Shenzhen TongYiFang Optoelectronic Technology CO,Ltd Shenzhen Topmay Electronic Shenzhen TPOWER Semiconductor Shenzhen Universal Micro-Electronics Shenzhen USBR Precision Hardware Electronics Shenzhen Weidy Industrial Development Co., Ltd. Shenzhen Xinbole Electronics Co. Shenzhen Xptek Technology Shenzhen Xunlong Shenzhen Yangxing Technology Co. SHENZHEN YeZhan Electronics Shenzhen Yiwei Technology Shenzhen ZVELL Electronics Shindengen Electric Shin-Etsu Chemical Co SHINYEI Technology SHOEI SIBA GmbH Sichuan huafeng enterprise group SICK, Inc. Siemens Semiconductor Group Si-En Technology SiFirst Technology SiGe Semiconductor Sigma Microelectronics Signetics Silego Technology Silergy Corp Silicon Image Silicon Integrated Systems Silicon Laboratories Silicon Microstructures, Inc. Silicon Motion, Inc Silicon Sensing Systems Limited Silicon Standard Corp Silicon Storage Technology Silicon Systems Inc Silicon Touch Technology Silvan Chip Electronics Silver Telecom Ltd SilverStone Technology SIMCom Wireless Solutions SIMTEK Electronic Components Sinda Photoelectricity Technology SINGULAR TECHNOLOGY CO., LTD. Sinomags Technologies Co Sinopower Semiconductor Sipex Corporation Sirectifier Semiconductors SiTime Corporation Sivago Semiconductor Co SIWARD Crystal Technology Siyang Microelectronics Sizto Tech Corp SKYLAB M&amp;C Technology Skyworks Solutions, Inc SL Power Electronics Corp. SMAR Smartec BV SMC Diode Solutions Co. Smiths Interconnect. SMSC Corporation Soberton Inc Softing Automotive Electronics Sola/Hevi-Duty Sola-IC Solarflex SA Soldex Solid State Scientific SOLIDIC Solitronics Engineering Limited SOL-LED Lighting Co Solomon Systech Song Chuan Song Huei Electric Sonix Technology Sony Corporation Soundwell Electronic South African Micro-Electronic Systems Spansion inc SparkFun Electronics SPEC Sensors LLC Spectra Symbol Corp. Spectrum Digital Incorporated Speed Tech Corp Spin Semiconductor Sprague Semiconductors SPX Flow Technology ST Engineering Stackpole Electronics Standex-Meder Electronics Stannol GmbH Stanson Technology StarChips Technology StarPower Semiconductor Ltd. Startek Electronic Technology STATEK CORPORATION Stäubli International AG. STCmicro Technology Co Stewart Connector STMicroelectronics Stocko Stork Solutions Ltd. Sullins Connector Solutions SUMIDA Corporation Sun Hydraulics Corporation Sun Microelectronics SunLED SUNLORD Sunltech Tech SUNMATE Electronic Sunonwealth Electric Machine Sunplus Technology Sunrise Electronics Suntan Technology Company Suntsu Electronics, Inc. SUNYUAN Technology Supertex Inc Susumu International Suzhou Innoson Technology Suzhou NOVOSENSE Microelectronics Co., Ltd Suzhou Silikron Semiconductor Corp Switchcraft Inc. Switec SYNC Power Crop SyncMOS Technologies Synoxo International System General Corp Tadiran Batteries TAG Semiconductors TA-I Technology TAIKO-NET Tai-Saw Technology Tai-Tech Advanced Electronics Taitien Electronics Taitron Components, Inc Taiwan Alpha Electronic Co Taiwan Semiconductor Taiyo Electric Co Taiyo Yuden Tak Cheong Electronics Talema Group, LLC Tamagawa seiki Co Tamron Tamura Corporation TANCAP Technology Taoglas Limited TDK Corporation (EPCOS) TDK-Lambda Corporation TDK-Micronas GmbH TE Connectivity Team Source Display tech.co,ltd. Techcode Semiconductor Techpoint Inc Techspray/Plato-EMX Enterprises Limited Techstar Electronics TechToys Company TelCom Semiconductor Telcon Ltd Telechips Inc Teledyne Technologies TELEFUNKEN Elektroakustik Telegesis Ltd Telit TEMIC Semiconductor Terawins, Inc Teridian Semiconductor TESLA Testo SE &amp; Co Texas Advanced Optoelectronic Solutions Texas Instruments THAT Corporation Thegioiic Corporation Thermonamic Electronics(Jiangxi) Corp THine Electronics, Inc Thinki Semiconductor Thinking Electronic THOMSON Inc THORLABS Thousand Hundred Industrial Thunder Precision Resistor TIANMA Titan Micro TLC Electronics TNI-U TOOL Token Electronics Industry Tokmas Semiconductor TOKO, Inc Tontek Design Technology Top-arm Topro Technology Topway Technology Torex Semiconductor Toshiba Corporation touchSEMI TOYO LED ELECTRONICS LIMITED. TOYODA TR Electronic Nordic AB. Traco Electronic AG Transcom, Inc Transko Electronics, Inc. TRENDnet, Inc Trenz Electronic Triad Magnetics Trident Microsystems Trimble Inc TRINAMIC Motion Control TRinno Technology Co Tripath Technology TriQuint Semiconductor Truly Semiconductors TRW Inc TT Electronics TTM Technologies, Inc. TXC Corporation UBIQ Semiconductor Ubiquiti Inc u-blox UCE Ultrasonic Co UDF Semiconductor Ultisensor Electronics UNI SEMICONDUCTOR LIMITED Unicorn Microelectronics Corporation Unictron Technologies Corporation. Union Semiconductor Uniroyal Electronics Industry Co Unisonic Technologies Unitra Cemi Uni-Trend Technology Co Unitrode Corporation Universal Microelectronics UPI Semiconductor Corp US Digital US Micro Products. Usha India Ltd Ushio Opto Semiconductors UTRON Technology, Inc Vacuumschmelze GmbH VADEM LTD Vango Technologies, Inc Varitronix Limited VARTA AG Vatronics Technologies Ltd VBsemi Electronics Co. Ltd V-Chip Microsystems VectorNav Vectron International Vehicles instrumentation Device Venkel Ltd VIA Technologies Vicor Corporation Vigortronix Ltd. Vincotech Vishay Visual communication company Vitesse Semiconductor Vivesea VLSI Solution Vweb Corporation W. L. Gore &amp; Associates, Inc WAGO Kontakttechnik GmbH Wakefield Thermal, Inc. Walsin Technology Corporation Walter Electronic Co WanTcom, Inc Wavecom Waveshare Electronics Wavespectrum Laser Inc Wavetronics Technologies WAYTRONIC ELECTRONIC CO.LTD WeEn Semiconductors Weidmüller Interface GmbH Weipu connector Weltrend Semiconductor WENSHING Electronics Western Digital Corporation Willas Electronic Corp WIMA Winbond Elect</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
+          <t>C2,C5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop?filters=[-2,"622","","=",""]#dtl/7605</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محصولات خانه دسته‌بندی‌ها فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه پکیج 1206 جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش برند 1666 3M Dynapro 3M Interconnect 3PEAK Incorporated 4D Systems Pty Ltd A Power microelectronics AAEON Technology Aavid Thermalloy ABC Taiwan Electronics ABLIC Inc Abracon Corporation Acam-Messelectronic Acrian, Inc Actel Corporation Active-Semi, Inc Actox Corporation. AD Semiconductor Confidential Adafruit Industries LLC Adam Technologies, Inc ADDA Corp ADDtek Corp Adesto Technologies ADMtek Inc Advanced Acoustic Technology Corp. Advanced Analog Technology Advanced Analogic Technologies Advanced Card Systems Advanced Ceramic X Corp Advanced Linear Devices Inc Advanced Monolithic Systems Advanced Photonix, Inc Advanced Power Electronics Corp Advanced Power Technology Advanced Semiconductor Advantech Corp Advantech Equipment Corporation Aegis Electronic Group AEL Crystals Limited AEM, Inc Aerosemi Technology Co Afa Technologies Inc AG Electrical Technology Agere Systems Agilent Technologies AGM Semiconductor AIC tech Inc. Aimtec Aimtron Corporation Airoha Technology Corp AIRWAVE Technologies Inc AiSHi Capacitors Aixin Opto-Electrical Technology Albright International Ltd Alcatel Microelectronics Alcor Micro Corp Alex Connector Co Ltd Alfa Electronics Algocraft Srl. ALi Corporation Alinx Electronic Technology All Sensors Corporation Allegro Microsystems Alliance Memory Allied Vision, Inc. Allwinner Technology Almita Co. Ltd Alpha &amp; Omega Semiconductor Alpha Micro Components Alpha Semiconductor Alpha Wire Alphasense Ltd, Sensor Technology Alps Electric Co Altera Corporation Amazing Electronic Co Amazing Microelectronic Corp AMD American Microsemiconductors American Microsystems Inc American Power Management American Technical Ceramics Corp American Zettler, Inc. Ametherm, Inc AMI Semiconductor AMIC Technology Corp Amidon Associates, Inc Amlogic Inc. Amotech Corp AMPAK Technology Inc Amphenol Advanced Sensors Amphenol Corporation Amphenol FCI Amphenol RF Ampleon USA Inc ams AG Anachip Corp ANADIGICS Anadigm, Inc Analog Devices Analog Integrations Corporation Analog Microelectronics Analog Power Analogix Semiconductor Inc Anaren, Inc Ancol Electronics Co Andigilog, Inc ANENG Anhui FOSAN Semiconductor Anhui Vico Technologes Co Anovay Technologies Limited ANPEC Electronics Corp Ante Intelligent Company Limited AP Memory Technology. APC Propellers APEM Inc Apex Material Technology Apex Precision Power API Delevan Inc API Technologies Aplus Integrated Circuits Inc APMKorea Apogee Technology, Inc Applent Instruments Applied Micro Circuits Co AppoTech Ltd APT Electronics Co., Ltd. Aptek Technologies ArchNet Technology Arcol UK Ltd Arduino Arduino Nicla Voice. Arima Lasers Corporation Aristotle Enterprises Inc ARTCHIP Semiconductor Artesyn Embedded Technologies AS ENERGI Asahi Kasei Microdevices ASAHI Solder Asia Vital Components Asiliant Technologies ASIX Electronics Corp AsLic Microelectronics Corporation ASMedia Technology Inc. Associated Opto-Electronics Astec Semiconductor. Astrodyne TDI Corporation. ATE Electronics s.r.l Atech Technology Co ATEN International Co Atheros Communications, Inc ATI Technologies Inc Atlas Scientific LLC. Attend Technology Inc AU Optronics Corp Audiowell Electronics Co Auk Contractors Co AUK Semiconductor AUO Corporation AUREL S.P.A Austar Technology AuthenTec, Inc Autonics Corporation Avago Technologies AVANTEK INC. AverLogic Technologies, Inc AVerMedia Technologies Avia Semiconductor Avnet, Inc AVX Corporation AXElite Technology Co Axiomtek Axis Communications AZ Displays, Inc Azoteq Ltd BAFO Technologies Corp Bahar Enclosure Baumer International BBT-China Inc BCD Semiconductor Beckhoff Automation Beijing Boshida Beijing HRH Information Co Beijing Ultrasonic Beijing Yihongtai Technology Beijing Zhongxun Sifang Science &amp; Technology Beken Corporation Bel Fuse Inc Bel Power Solutions Inc Belden Inc Bellnix Bencent Tzeng Ind. Co. Ltd Betlux Beyond Innovation Technology BI Technologies Bicker Elektronik GmbH Billionton Systems Inc Bird Technologies Bi-Sonic Technology Bivar, Inc Blackhawk BLOCK Inc Bluegiga Technologies BOLYMIN,INC BONGSHIN LOADCELL CO. Bookly Micro Electronic Bosch Security Systems Inc Bosch Semiconductors Bosch Sensortec Bothhand USA Boundary Devices Bourns Inc Bowin Microelectronics Brainboxes Limited BRIGHT LED ELECTRONICS CORP. Bright Power Semiconductor BrightKing Inc Brilliance Semiconductor, Inc Broadchip Technology Broadcom Limited BroadLight Inc Brooktree Corporation Burr-Brown Corporation BYD Microelectronics Co., Ltd. C&amp;D Technologies C&amp;K Components Caddock Electronics Inc California Eastern Laboratories California Micro Devices Calogic LLC Cambridge Integrated Circuits Cambridge Silicon Ra dio Limited Camille Bauer Ltd Catalyst Semiconductor Celduc relais CellWise Microelectronics Co Cenker Enterprise Ltd Centenary Materials Co CeNtRa Science Corp Central Components Manufacturing Central Georgia Generator Central Semiconductor CEVA Technologies CFSensor Challenge Electronics Champion Microelectronic Changzhou changjie Technology Co Changzhou Cre-sound Electronics Changzhou DRM Changzhou Esuntech Co Changzhou Kennon ELectronics Changzhou TDA Electronic Changzhou Yuanwang Fluid Technology Chaozhou Three-circle (Group) Co chargebyte GmbH. Chengdu Ebyte Electronic Technology Chengdu Guosheng Technology Chengdu Xincheng Huachuang Electronic ChenMoun Electronic ChenYang Technologies Cheuk Yui Innovation Co Chi Mei Optoelectronics Chieful Science ＆ Technology Chilisin Electronics Co China Base Electronic Technology China ECU Tools Centre China Resources Microelectronics China Software Industry Association Chinfa Electronics Chingis Technology Corp Chino-Excel Technology Chipanalog Incorporated ChipLink Tech Chiplus Semiconductor ChipON Chipower Electronics CHIPS Technology Chipstar Microelectronics CHK Electronics Ltd Chogori USA Chongqing Shengpu Electronics Chrontel, Inc Chunghwa Picture Tubes Churod Electronics Chyao Shiunn Electronic Cincon Electronics Cinetech Ind Cirrus Logic Inc Cisco Systems CIT Relay &amp; Switch Citizen Finedevice Co Cixi AnXon Electronic Cixi Dafa precise Linker Co CiXi KaiFeng Electronics Co Cixi Kefa Electronics Cixi Max Electronics Co.,Ltd Clare, Inc Cliff Electronic Components Limited Cmedia Electronics Inc CML Microsystems Coil Master Co Coil Winding Coilcraft Inc Coiltronics (Eaton) Comchip Technology Commodore Semiconductor Comtec Crystals comtech aha corporation CONEC Elektronische Bauelemente GmbH Conesys,Inc. Conexant Systems, Inc Connfly Electronic Co Connor-Winfield Conquer Electronic Continental Device India Controlair Inc Conversion Devices, Inc Cooper Bussmann Coretek Opto Corporation. Cornell Dubilier Electronics Cortina Systems, Inc Cosel Co Ltd COSINE Nanoelectronics Coto Technology CR Powtech Co Cree, Inc Crydom Inc Crystal Semiconductor Corporation Crystalfontz Crystek Corporation CSCONN PRECISE ELECTRONICS CO.,LTD CT Micro International Co CTS Corporation CUI Inc CVI Laser, LLC CW Industries Cyntec Co Cypress Semiconductor Cyrustek Corporation CYStech Electronics Corp. CYT Opto-Electronic Technology Dachang Electronics Daewoo Semiconductor Daier Electron Co Dailywell Electronics Daishinku Corp Daito Communication Apparatus Daiyo Electronics Dallas Semiconductor DANFOSS Daniels Manufacturing Co Data Device Corporation Davicom Semiconductor Davies Molding, LLC DB Lectro Inc DB Unlimited DC Components Co Dean Technology DECA SwitchLab Inc Decawave Ltd Dechang Electronic Deep Sea Electronics DEGSON Electronics Co Dell Inspiron Delta Electronics DeMint Electronics DENSO Destiny Technology Corp Detaik Technology Co Deva Electronic Controls Limited. Devantech Device Engineering Inc Dexter Magnetic Technologies DFRobot. Dialight Electronics Company Dialog Semiconductor Dielectric Laboratories Digi International Digilent, Inc Digital Voice Systems Digitrax, Inc Digitron Semiconductors Dinkle International Co. Ltd DIN-TEK Microelectronics Diodes Incorporated Diotec Semiconductor Diptronics Manufacturing Inc Display Solution AG DISPLAY VISIONS GmbH 2022. DMB Technology DOESTEK Co DOINGTER Semiconductor Domintech Co Don Connex Electronics DONG IL TECHNOLOGY LTD. Dongguan CHENGXING Electronic Co Dongguan City Wasi Electronic Technology Dongguan Cosson DongGuan HeLing Electronics Dongguan Lanbo Electronics Technology CO Dongguan Yuandi Electronics Dongguan Yuanze Electric Co.,Ltd Dongguan Yuxi Precise Connector Co., Ltd Dongke semiconductor Anhui Co., Ltd Donguan Keyouda Electronic Dosilicon Co DTK electronics Dualsky Models Co Duoxing Electronics Co Duty-Cycle Semiconductor Dynamic Technologies (DTCC) Dynex Semiconductor Ltd, E &amp; E Magnetic Products Limited EAST Semiconductor East Texas Integrated Circuits Eastrising Technology Co Eastsensor Technology Easy IoT Eaton’s Bussmann Ebm-papst inc Echelon Corporation Ecliptek Corporation ECOFIT &amp; ETRI ECS, Inc International EDAC EECO Switch E-Elements Technology Co Efficient Power Conversion Co EG Microelectronics Corp EIC Semiconductor Elan Microelectronics Co Elantec, Inc Electrolube Electronic Alliance Electronic Assembly Electronic Devices Inc Electroustic Ltd Eledis Element14 ELESTA GmbH Elite Semiconductor Memory Eljen Technology Elm Electronics ELM Technology Co Elmos Semiconductor AG ELNA Company Elpida Memory, Inc EM Microelectronic-Marin EMAD Embedded Artists Embest Technology Emerson Encitech Endress+Hauser Management ENE Technology Enplas Corporation Enrwey Co Ltd Eon Silicon Solution E-peas Semiconductors Epitex Inc Epoxy Technology Inc EPSON Electronics Ept Inc Ericsson Microelectronics ERNI Electronics ERSA UK LTD Espressif Systems ESS Technologies E-Switch, Inc ET Enterprises Limited E-T-A Circuit Breakers ETA Solutions E-tec Interconnect Ethertronics Inc Etron Technology, Inc EUCHNER GmbH Eupec semiconductor Euroquartz Ltd Eutech Microelectronics Everanalog Everest Semiconductor Everlight Electronics Everspin Technologies Exar Corporation Excel Cell Electronic Excelitas Technologies Excellence Opto, Inc Excelliance MOS Corporation Fagor Electronica Fairchild Semiconductor Fair-Rite Products Corp FANUC Corporation Faraday Technology Fastline Fastrax Ltd FASTRON Faulhaber GmbH FDK Corporation Feature Integration Technology Feei Cherng Enterprise Feeling Technology Feiyi Technology FEMA Electronics Corporation Fenghua Advanced Technology Ferroxcube International FERYSTER Sp. z.o.o Figaro Engineering Inc Finder Relays, Inc Fingerprint Cards First Semiconductor First Sensor FIS Inc Fischer Connectors Fischer Elektronik Fitipower Integrated Technology Force MOS Technology Co Formosa MS Formox Semiconductor Forsentrk Fortior Technology Co Fortune Semiconductor Forward International Electronics FOTEK Controls Fox Electronics Foxconn Technology Fractus S.A Franz Binder GmbH &amp; Co. Free2Move Holding AB. Freescale Semiconductor Fremont Micro Devices Friendcom Technology Develop FriendlyARM Computer Tech FTDI Chip Fuda Hisi Microelectronics Fuji Electric Fujikura Fujitsu Semiconductor Fujitsu-Takamisawa Fulihua Printer Ribbon Co Futaba Corporation Fu-Yao Technology Co Fuzetec Technology Co Fuzhou Rockchip Electronics Co., Ltd GainSpan Corporation GalaxyCore Inc GaNPower International Inc G-Antetech Industrial Garmin Ltd. Gas Sensing Solutions Ltd. Gaston Electronics GC GE Fanuc GEC Plessey Geehy Semiconductor Co General Electronic Devices General Monitors General Semiconductor Generalplus Technology GeneSiC Semiconductor Genesis Microchip Inc Genesys Logic, Inc Genicom Co., Ltd. Gennum Corporation GETE Electronics GigaDevice Semiconductor Global Connector Technology (GCT) Global Mixed-mode Technology GlobespanVirata, Inc GMC Instruments GME Technology, LLC GoChip Electronic Technology GoldStar Semiconductor Gonbes Technology Co Good Display Good Will Instrument Good-Ark Semiconductor Goodix Technology Governors America Co Gpixel Microelectronics Inc Grayhill Inc GreatLEDs Co Greenliant Systems GRUNER AG GSI Technology, Inc Guangdong Hottech Co Guangdong Huaguan Semiconductor Guangdong TIANQIU Electronics Technology Guangzhou Aosong Electronics Guangzhou Xinyue Electronic Guerrilla RF, Inc H&amp;M Semiconductor HABEY Halbleiter aus Frankfurt HALO Electronics Hamamatsu Photonics Hangzhou Grow Technology Co Hangzhou Nationalchip Science Hangzhou Prosper Hangzhou Silan Microelectronics Hannstar Display Corp HanRun Electronics Hanwei Electronics Co Hanyoung Nux Co HAOHAI ELECTRONICS HAOYU Electronics Harris Semiconductor HARTING Technology Harvatek Corporation Harwin Hawyang Semiconductor Hebei International Trading Co HEITEC AG. Hemingruizhi Electronic Henan Hanwei Electronics Co Hengda New Materials Technology HengJiaXing Electronics Co Henkel Corporation HenLv Power Technology Heter Electronics Hewlett-Packard Hexin Technology Highly Electric Hi-Link Electronic Technology Hi-Optel Technology Hirose Electric Hi-Sincerity Microelectronics Hitachi Maxell, Ltd Hitachi Semiconductor HITPOINT Inc Hittite Microwave Hivolt Capacitors Ltd H-JTAG Technology Hokuriku Electric Industry Co Ltd Hokuyo Automatic Co Holt Integrated Circuits Holtek Semiconductor Honeywell International Hong Kong Resistors Manufactory Hongfa Electroacoustic Co HONGHUA ELECTRONIC Hope Microelectronics HORIBA, Ltd. Hosiden Corporation Hosonic Electronic Co Hotchip Technology HTC Korea TAEJIN Technology Huada Connectors Huanor International Huaqi Microelectronics Co Huawei Technologies Huayu Technology HuaYuan Micro Electronic Huayue Microelectronics Co HUBER+SUHNER Huibei KENTO Electronic Huidu Technology Hukx Sensor Technology Humirel Hurricane Tech. Co HW group s.r.o HYCON Technology Corp. Hynix Semiconductor Hyundai Semiconductor IC Plus Corp ICE Components, Inc. iC-Haus GmbH Icom Inc ICP DAS CO ID Innovations ID TECH IDEC Corporation IEI Integration Ignion Iintelligent Motion Systems IK Semiconductor ILSI America LLC IMP, Inc Inchange Semiconductor Industrial Fiber Optics, Inc Industrial Technology Research Institute Infineon Technologies Initio Corporation INJOINIC TECHNOLOGY Innolux Corporation InnoSenT-Innovative Radar Sensor Technology Innovative Sensor Technology IST Innuovo Magnetics Co Inova Semiconductors InPlay Inc. InPower Semiconductor INTEGRAL JSC Integrated Circuit Solution Integrated Circuit Systems Integrated Crystal Technology Integrated Device Technology Integrated Sensor Technologies Integrated Silicon Solution Intel Corporation InterFET Corp Interlink Electronics International CMOS Technology International Rectifier Intersil Corporation Intronic Semiconductor Intronics Power, Inc InvenSense Inc IQD Frequency Products Ltd IRAN Ironwood Electronics IRXON Electronic Isabellenhütte Heusler GmbH &amp; Co KG Isahaya Electronics Co iSentek Technology Isocom Components Isotek Corp ITE Tech ITT Cannon, LLC ITT Semiconductors Ituner Networks Corp iWatt Inc IXYS Integrated Circuits J.S.T. Mfg. Co JACKSON ELECTRONICS IND. CROP. JAE Electronics JAI Ltd Jamicon Electronics JAVAN JCET Group Co JCI Jewel Hill Electronic Co JHDLCM Electronics Jiangsu Changjiang Electronics Jiangsu Donghai Semiconductor Jiangsu Juguang Jiangsu Runic Technology Co Jiangsu Szdhdtgd Electronics Jiangxi Jia Wei Cheng Electronic Jilin Sino-Microelectronics Co Jinan USR IOT Technology JING LI Power Electronics Jingcheng Electronics Co Jinghan Switch Electronic JMicron Technology Corp JNHuaMao Technology JODO International Johanson Dielectrics Johanson Technology Johnson Electric JPC Company JYE Tech Ltd JYH HSU(JEC) ELECTRONICS Kai Suh Suh Enterprise KSS Kaida Holding Kaihua Electronics Co Kangmu Sheng Electronics Ka-Ro electronics GmbH. KEC Semiconductor Keil Elektronik Keithley Instruments Kelly Controls, LLC KEMET Corporation Key Technology Keysight Technologies Keystone Electronic King Core Electronics Kingbor Technology Kingbright Electronic KingCCTV Technology Kingdatron Electronic Industrial Co Kingsignal Technology Kingstate Electronics Kingston KIOXIA America, Inc Kiwi Instruments Corp Knowles Electronics KOA Speer Electronics Kobiconn Kodenshi Corp Kohshin Electric Corporation KONE Elevator Kontron S&amp;T KT Micro Inc Kunshan Sino Silicon Technology KUOYUH W.L. Enterprise Co Kutai Electronics Kycon, Inc Kyocera Corporation Ladder Electronics Co Laird Performance Materials. Laird Technologies Laser Components Lattice Semiconductor LawMate International L-com, Inc LD-PD Inc. Leadtrend Technology Corp LEAP Electronic Legerity, Inc Lelon Electronics Corp LEM Components LEMO Lenovo LENZE Lesfuse Electric Co Leshan Radio Co LG Semiconductor LG.Philips Displays Lianchao Future Technology Lighting Integration System Ligitek Electronics Co Lime Microsystems Lineage Power Private Limited Linear Systems Linear Technology Linfinity Microelectronics Link-PP Int'l Technology LinkSmart LINP OMTER International Linx Technologies Lision Technology LITE-ON Semiconductor Littelfuse Inc Lixin Electromagnetic Clutch LIZE Electronic Technology LND, INC LOETRONIC LOGIC Devices Incorporated Longtech Optics Co Longview Technologies Co Lovid International Electronic Low Power Radio Solutions Ltd LOZEN TECHNOLOGY LS ELECTRIC LS Mtron Ltd LSI Computer Systems LTKCHIP LTN Servotechnik GmbH Lucent Technologies LUCKFOX Technology Lucky Light Electronic Luguang Electronic Technology Lumberg Holding Lumentum Operations LLC. Lumex Inc Lumileds Luminus, Inc. Lumissil Microsystems Luna Optoelectronics Lutron Electronic Enterprise Co Lyontek Inc M.S. Kennedy Corp M+R Multitronik GmbH MACOM Technology Macroblock, Inc Macronix International MacTek Corp MagnaChip Semiconductor Magnetics MagnTek Microelectronics Magtek Technology Inc Manorshi Electronics Marktech Optoelectronics, Inc Marlow Industries, Inc Marquardt Switches, Inc Marvell International Matsushita Electric Max Echo Technology Corp MaxBotix Inc Maxic Technology Corporation Maxim Integrated MaxLinear Inc Maxon motor Maxwell Technologies Mayloon Electronic Company MCS Logic Inc Mcuzone International MEAN WELL Enterprises Co Measurement Specialties Mechanic MediaTek Inc Megatek Melexis Technologies Memory Protection Devices MEMSIC, Inc Mentor GmbH Mercury Electronic Meritek Electronics Corporation Mersen EP Metalink Broadband Meticom GmbH. METRODYNE MICROSYSTEM CORP. MIC Electronic Micrel, Inc Micro Commercial Components Micro Crystal AG Micro Electronics Micro Linear Micro One Electronics Micro Power Systems MICRO SENSOR CO;LTD Microchip Technology Microdiode Semiconductor Micrometals, Inc Micron Technology Micronet Communication Microsemi Corporation Microtech Technology Co Ltd Microtherm Sentronic GmbH Microtips Technology Midori Precisions MikroElektronika MikroElektronika d.o.o MikroTik Mill-Max Mfg Milnec Interconnect Systems MindMotion Microelectronics Co. Mingtek Electronics Ltd Mini-Circuits Minilogic Device Corporation Ltd Minmax Technology Minsoo Electronic Co MiTAC Computing Technology Mitel Semiconductor Mitsubishi Electric Mitsubishi Rayon Co Mitsumi Electric Co Mixed Signal Integration Mixic Electronics MKMX America LLC MMI Semiconductors MOAI electronics co Mobicon Electronic Component Modulestek Inc MOKO TECHNOLOGY LTD. Molex Electronic Monitor Enterprises Inc Monolithic Power Systems Morethanall Co Morningstar Corporation MORNSUN Science &amp; Technology Mosdesign Semiconductor Corp Mosel Vitelic Co MOSPEC Semiconductor MOS-TECH Semiconductor Mostek MOTIEN Technology Motorola Mstar Semiconductor M-Systems Inc Multicomp Multi-Inno Technology Multi-Tech Systems Inc Murata Manufacturing Co MVSILICON MYIR Tech Myrra SAS Naina Semiconductor Limited. Nanjing Haichuan Electronic Nanjing Ouzhuo Tech Nanjing Qinheng Microelectronics Nanjing Shiheng Elec NanJing Top Power ASIC Nanjing Up Electronic Technology Nanjing Wotian Technology Co Nanjing Zeming Electronic Co Nanya Technology Co National Instruments National Semiconductor NDK America Inc NEC Electronics Nell Semiconductor Neltron Industrial Nemoto Sensor Engineering NeuroSky, Inc. Neutrik New Jersey Semiconductor NewAE Technology Inc. Newava Technology Inc. Newhaven Display Newport Corporation NewTec Display Co NexFlash Technologies, Inc Nexperia USA Inc Nextchip Nextion NIC Components Corp. Nichia Corporation Nichicon Corporation Nidec Copal Electronics NIDEC SERVO CORPORATION. Nihon Dempa Kogyo Nihon Inter Electronics NIKO Semiconductor Ningbo East Electronics Ningbo ForwardRelayCorporationLTD Ningbo Gosun Technology Co Ningbo Huaguan Electronics Ningbo KLS Electronic Co Ningbo MAX Electronic Technology Co., Ltd Ningbo MKX Electronic Technology Ningbo Rel Electric Co., Ltd. Ningbo Songle Relay Ningbo Tianbo Ganglian Electronics Ninigi Nippon Chemi-Con Nippon Pulse America, Inc Nisshinbo Micro Devices Inc NJR Corporation NKK Switches NMB Technologies Non-Brand Norcomp Inc Nordic Semiconductor Noritake Itron Co Novacap Novatek Microelectronics NTE Electronics NUAND LLC. Nuvoton Technology NVE Corporation Nvidia NVS Navigation Technologies NXP Semiconductors NYS Resistor O2Micro OCIC co Octavo Systems LLC Ogemray Technology Co Ohmite OKI Semiconductor Ole Wolff Electronics Inc Olimex OmniVision Technologies Omron Electronics Omten Electronics ON Semiconductor ON Semiconductor CHINA On Shore Technology On-Bright Electronics OPTEK Technology Inc OPTi Inc Opticon Inc Opto 22 Opto Diode Corp Opto Electronics Co,. LTD OPTOLAB Microsystems Orient Display Oriental Semiconductor Orion Orion Display Technology Co OSI Optoelectronics OSRAM Opto Semiconductors OTAX Corporation Other Oupiin Enterprise Co OWON Technology Inc P&amp;E Microcomputer Systems Pacific Silicon Sensor Panasonic Corporation Panavision Imaging LLC Pancon Corporation PandaBoard PANJIT International Inc Para Light Electronics P-DUKE Technology Co PEAK Electronics GmbH PEAK-System Technik Penny &amp; Giles Peregrine Semiconductor Pericom Semiconductor Corp PerkinElmer Inc Phidgets, Inc Philips Semiconductor Phison Electronics Phoenix Contact Pickering Electronics Ltd PICO Electronics Pico Technology Piher Sensors &amp; Controls SA Pingjing Semi Technology PIR Sensor Co PixArt Imaging Inc Planar Systems, Inc PLX Technology PMC-Sierra, Inc PNI Sensor Corporation POCO Magnetic Polyfet RF Devices Polytronics Technology Pomona Electronics Power Integrations Power Mate Technology Power Systems GmbH Power-Changer Electronic Co Powerex Inc PowerPlaza Powersem GmbH Powertip Technology Preci-Dip SA Precision Monolithics, Inc PREMA Semiconductor GmbH Premier Magnetics PRETEC/C-One Technology Corp. Princeton Technology Proant AB Profichip GmbH Prokit's Industries Prolific Technology Inc Promax-Johnton Semiconductor Pro-Signal ProTek Devices Pro-Wave Electronic PRT PUI Audio Pulse Electronics Qimei Optical &amp; Electric Qingdao Mefine Electronics Qingxian Zeming Langxi Electronic Devices Co Qingyuan Tesla Electronic Technology Qorvo QT Brightek (QTB) QT Optoelectronics Qualcomm Atheros, Inc Quality Semiconductor Qualtek Electronics Quarton inc Quasar Electronics Limited Quectel Wireless Solutions QuickLogic Corporation QX Micro Devices Radiall Radxa Computer Rafael Microelectronics RAFI GmbH &amp; Co RAiO TECHNOLOGY INC RAKwireless Technology Limited. RALEC Ltd Ralink Technology Raltron Electronics Corporation Ramtron International Rapid Electronics Ltd Raspberry Pi Raycom Co Raytac Corporation. Raytheon RCA Corporation Ready Made RC LLC Realtek Semiconductor RECOM Power GmbH Rectron Semiconductor Reichelt elektronik GmbH &amp; Co. KG RELPOL S.A Renata SA Renesas Technology Renhotec Group Ltd Reomax Electronics Reyed Electronics Co RF Digital Corporation. RF Micro Devices RF Solutions Ltd RFaxis, Inc RFHIC Corporation RFM Integrated Device, Inc. RFT Mikroelektronik Rhombus Industries Inc Richtek Technology Co RichWave Technology Ricoh Electronic Devices Riedon RIGOL Ring&amp;tone Electronic Technology Riverdi RLS Merilna tehnika d.o.o ROBOTIS Co Rockwell Rogers Corporation ROHM Semiconductor Roithner Lasertechnik GmbH Rongtech Industry Royal Electronic Factory Co RS Components Ltd RTD Embedded Technologies Rubycon RYCHIP Semiconductor s.m.a.e. GmbH Saft Groupe S.A Sagami Electronics Saia-Burgess Switches Sakae Tsushin Kogyo Saleae, Inc Salecom Electronics Same Sky SamHop Microelectronics Samsung Electronics Samtec Samwha Capacitor Samwin Electronic Technology Samyoung S &amp; C Co SANCO Electronics Co SanDisk Sanhe Enclosure Sanjiaozhou Electrical Technology Sanken Electric SanRex Corporation Sanyo Denki Sanyo Electric Savantic Electronic Sawnics Inc Schaffner Group Schott AG Schrack Technik GmbH Schurter Inc Sciosense B.V. SCTF Electronics Seagate Technology LLC Seaparks Machinery-Electronics Seaward Electronics SeCoS Corporation SEED International Ltd Seeed Technology SEEQ Technology Segger Microcontroller Systems Seiko Instruments Inc Seiko NPC Corporation Semiconductor Circuits, Inc SemiHow Semikron Semiment Technologies Semi-Powerex Corp. SEMITEC Corporation SemiWell Semiconductor Semtech Corporation Semtech Electronics Senba Sensing Technology Co Sendo Sensor Sensata Technologies Sensirion Sentry Manufacturing Inc SEP Electronic Corp Servotecnica SpA SERVO-TEK PRODUCTS COMPANY, INC. SG Micro Corp SGX Sensortech Shaanxi Fullstar Electronics Co Shaanxi Qunli Electric Shaanxi Reactor Microelectronics Shandong Jingdao Microelectronics Shanghai AVIC Optoelectronics Shanghai Belling Co,Ltd Shanghai Consonance Electronics Shanghai Fengxin Electronic Technology Shanghai Fudan Microelectronics Shanghai Gotop Technology Shanghai High-Flying Electronics Shanghai Houde Photo-electric Shanghai Mixinno Microelectronics Co Shanghai Natlinear Electronics Shanghai Xinlong Semiconductor Shanghai Zhichuan Electronic Tech SHARP Corporation Sheng Jay Automation Techno Shenyang Guangcheng Technology Co., Ltd Shenyang KingStar Automation ShenZhen AI-thinker CO Shenzhen AnBoShi Electronic Shenzhen Asenware Test Shenzhen Baishan Mechatronics Shenzhen Biosled Technology Shenzhen Bolutek Technology Shenzhen Chipsea Technologies ShenZhen ChipSourceTek Technology Shenzhen ExSAF Electronics Co Shenzhen Genesis-Systech ShenZhen Gerbole Shenzhen Getech Co Shenzhen GUANGSHIMEI Electronic Shenzhen Hanxia Electronics Shenzhen Haolin Electronics Shenzhen Heliwei Technology Shenzhen honglifa Electronics Co Shenzhen HongyeX Electronics Co ShenZhen HuaXinAn Electronics Co.,Ltd Shenzhen Injoinic Technology Co. Shenzhen Jin Yu Semiconductor Co ShenZhen JINCI Technology Shenzhen Jinrui Electronic Material Co Shenzhen JMRTH Co Shenzhen Kaiyuexiang Electronics Co Shenzhen LFN Technology Co Shenzhen Lodestar S.T Co Shenzhen Lumen Electronics Shenzhen Magnetic Technology Shenzhen MilkV Technology Shenzhen Milliohm Electronics Shenzhen Minewsemi Co., Ltd Shenzhen Nsiway Tech Shenzhen Ou Chuangxin Semiconductor ShenZhen Qi Dian Shi Dai Technology Shenzhen Ruichips Semiconductor Shenzhen Ruilongyuan Electronics Shenzhen Shiji Lighting Shenzhen SI Semiconductors Shenzhen SLKOR Micro Semicon Co Shenzhen Sunmoon Microelectronics Shenzhen Suosemi Tech Shenzhen TongYiFang Optoelectronic Technology CO,Ltd Shenzhen Topmay Electronic Shenzhen TPOWER Semiconductor Shenzhen Universal Micro-Electronics Shenzhen USBR Precision Hardware Electronics Shenzhen Weidy Industrial Development Co., Ltd. Shenzhen Xinbole Electronics Co. Shenzhen Xptek Technology Shenzhen Xunlong Shenzhen Yangxing Technology Co. SHENZHEN YeZhan Electronics Shenzhen Yiwei Technology Shenzhen ZVELL Electronics Shindengen Electric Shin-Etsu Chemical Co SHINYEI Technology SHOEI SIBA GmbH Sichuan huafeng enterprise group SICK, Inc. Siemens Semiconductor Group Si-En Technology SiFirst Technology SiGe Semiconductor Sigma Microelectronics Signetics Silego Technology Silergy Corp Silicon Image Silicon Integrated Systems Silicon Laboratories Silicon Microstructures, Inc. Silicon Motion, Inc Silicon Sensing Systems Limited Silicon Standard Corp Silicon Storage Technology Silicon Systems Inc Silicon Touch Technology Silvan Chip Electronics Silver Telecom Ltd SilverStone Technology SIMCom Wireless Solutions SIMTEK Electronic Components Sinda Photoelectricity Technology SINGULAR TECHNOLOGY CO., LTD. Sinomags Technologies Co Sinopower Semiconductor Sipex Corporation Sirectifier Semiconductors SiTime Corporation Sivago Semiconductor Co SIWARD Crystal Technology Siyang Microelectronics Sizto Tech Corp SKYLAB M&amp;C Technology Skyworks Solutions, Inc SL Power Electronics Corp. SMAR Smartec BV SMC Diode Solutions Co. Smiths Interconnect. SMSC Corporation Soberton Inc Softing Automotive Electronics Sola/Hevi-Duty Sola-IC Solarflex SA Soldex Solid State Scientific SOLIDIC Solitronics Engineering Limited SOL-LED Lighting Co Solomon Systech Song Chuan Song Huei Electric Sonix Technology Sony Corporation Soundwell Electronic South African Micro-Electronic Systems Spansion inc SparkFun Electronics SPEC Sensors LLC Spectra Symbol Corp. Spectrum Digital Incorporated Speed Tech Corp Spin Semiconductor Sprague Semiconductors SPX Flow Technology ST Engineering Stackpole Electronics Standex-Meder Electronics Stannol GmbH Stanson Technology StarChips Technology StarPower Semiconductor Ltd. Startek Electronic Technology STATEK CORPORATION Stäubli International AG. STCmicro Technology Co Stewart Connector STMicroelectronics Stocko Stork Solutions Ltd. Sullins Connector Solutions SUMIDA Corporation Sun Hydraulics Corporation Sun Microelectronics SunLED SUNLORD Sunltech Tech SUNMATE Electronic Sunonwealth Electric Machine Sunplus Technology Sunrise Electronics Suntan Technology Company Suntsu Electronics, Inc. SUNYUAN Technology Supertex Inc Susumu International Suzhou Innoson Technology Suzhou NOVOSENSE Microelectronics Co., Ltd Suzhou Silikron Semiconductor Corp Switchcraft Inc. Switec SYNC Power Crop SyncMOS Technologies Synoxo International System General Corp Tadiran Batteries TAG Semiconductors TA-I Technology TAIKO-NET Tai-Saw Technology Tai-Tech Advanced Electronics Taitien Electronics Taitron Components, Inc Taiwan Alpha Electronic Co Taiwan Semiconductor Taiyo Electric Co Taiyo Yuden Tak Cheong Electronics Talema Group, LLC Tamagawa seiki Co Tamron Tamura Corporation TANCAP Technology Taoglas Limited TDK Corporation (EPCOS) TDK-Lambda Corporation TDK-Micronas GmbH TE Connectivity Team Source Display tech.co,ltd. Techcode Semiconductor Techpoint Inc Techspray/Plato-EMX Enterprises Limited Techstar Electronics TechToys Company TelCom Semiconductor Telcon Ltd Telechips Inc Teledyne Technologies TELEFUNKEN Elektroakustik Telegesis Ltd Telit TEMIC Semiconductor Terawins, Inc Teridian Semiconductor TESLA Testo SE &amp; Co Texas Advanced Optoelectronic Solutions Texas Instruments THAT Corporation Thegioiic Corporation Thermonamic Electronics(Jiangxi) Corp THine Electronics, Inc Thinki Semiconductor Thinking Electronic THOMSON Inc THORLABS Thousand Hundred Industrial Thunder Precision Resistor TIANMA Titan Micro TLC Electronics TNI-U TOOL Token Electronics Industry Tokmas Semiconductor TOKO, Inc Tontek Design Technology Top-arm Topro Technology Topway Technology Torex Semiconductor Toshiba Corporation touchSEMI TOYO LED ELECTRONICS LIMITED. TOYODA TR Electronic Nordic AB. Traco Electronic AG Transcom, Inc Transko Electronics, Inc. TRENDnet, Inc Trenz Electronic Triad Magnetics Trident Microsystems Trimble Inc TRINAMIC Motion Control TRinno Technology Co Tripath Technology TriQuint Semiconductor Truly Semiconductors TRW Inc TT Electronics TTM Technologies, Inc. TXC Corporation UBIQ Semiconductor Ubiquiti Inc u-blox UCE Ultrasonic Co UDF Semiconductor Ultisensor Electronics UNI SEMICONDUCTOR LIMITED Unicorn Microelectronics Corporation Unictron Technologies Corporation. Union Semiconductor Uniroyal Electronics Industry Co Unisonic Technologies Unitra Cemi Uni-Trend Technology Co Unitrode Corporation Universal Microelectronics UPI Semiconductor Corp US Digital US Micro Products. Usha India Ltd Ushio Opto Semiconductors UTRON Technology, Inc Vacuumschmelze GmbH VADEM LTD Vango Technologies, Inc Varitronix Limited VARTA AG Vatronics Technologies Ltd VBsemi Electronics Co. Ltd V-Chip Microsystems VectorNav Vectron International Vehicles instrumentation Device Venkel Ltd VIA Technologies Vicor Corporation Vigortronix Ltd. Vincotech Vishay Visual communication company Vitesse Semiconductor Vivesea VLSI Solution Vweb Corporation W. L. Gore &amp; Associates, Inc WAGO Kontakttechnik GmbH Wakefield Thermal, Inc. Walsin Technology Corporation Walter Electronic Co WanTcom, Inc Wavecom Waveshare Electronics Wavespectrum Laser Inc Wavetronics Technologies WAYTRONIC ELECTRONIC CO.LTD WeEn Semiconductors Weidmüller Interface GmbH Weipu connector Weltrend Semiconductor WENSHING Electronics Western Digital Corporation Willas Electronic Corp WIMA Winbond Electronics </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4610</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>9220</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://lionelectronic.ir/products/2221-XL-3216UBC</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>لیون الکترونیک | XL-3216UBC خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products LED Lighting LED Color LEDs XL-3216UBC 9,900 موجودی محصول تعداد قیمت 100 9,456 ریال 500 9,141 ریال 1500 8,952 ریال 3000 8,826 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام XL-3216UBC XL-3216UBC Part Number 2221 Lion Part Download Datasheet XINGLIGHT Manufacture ال ای دی آبی پکیچ 1206 LED Blue 455-475nm 1206 25mA 75mW مشخصات ال‌ای‌دی آبی XL-3216UBC ال‌ای‌دی آبی XL-3216UBC Part Number Blue Illumination Color 120° Viewing Angle Reel Packaging 75mW Power Rating SMD/SMT Mounting Style -30C Minimum Operating Temperature 42-86mcd Luminous Intensity +85C Maximum Operating Temperature 25mA If - Forward Current 455-475nm Wavelength-Color Temperature 1206 (3216 metric) Package-Case 2.6-3.2V Vf - Forward Voltage نظرات کاربران ارسال نظر محصولات مرتبط XL-1005UYC XL-1005UWC XL-1005SURC XL-1005UBC XL-1005UGC SK6812MINI-E XL-3215UYC XL-3215UGC XL-3215SURC WS2812D-F8 × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 9,900 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
+          <t>220u</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
+          <t>C3,C4</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CAP-D10.0XH12.5</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop?searchfilter=220uf#dtl/4339</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>محصولات خانه دسته‌بندی‌ها فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه عبارت 220uf جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش برند 1666 3M Dynapro 3M Interconnect 3PEAK Incorporated 4D Systems Pty Ltd A Power microelectronics AAEON Technology Aavid Thermalloy ABC Taiwan Electronics ABLIC Inc Abracon Corporation Acam-Messelectronic Acrian, Inc Actel Corporation Active-Semi, Inc Actox Corporation. AD Semiconductor Confidential Adafruit Industries LLC Adam Technologies, Inc ADDA Corp ADDtek Corp Adesto Technologies ADMtek Inc Advanced Acoustic Technology Corp. Advanced Analog Technology Advanced Analogic Technologies Advanced Card Systems Advanced Ceramic X Corp Advanced Linear Devices Inc Advanced Monolithic Systems Advanced Photonix, Inc Advanced Power Electronics Corp Advanced Power Technology Advanced Semiconductor Advantech Corp Advantech Equipment Corporation Aegis Electronic Group AEL Crystals Limited AEM, Inc Aerosemi Technology Co Afa Technologies Inc AG Electrical Technology Agere Systems Agilent Technologies AGM Semiconductor AIC tech Inc. Aimtec Aimtron Corporation Airoha Technology Corp AIRWAVE Technologies Inc AiSHi Capacitors Aixin Opto-Electrical Technology Albright International Ltd Alcatel Microelectronics Alcor Micro Corp Alex Connector Co Ltd Alfa Electronics Algocraft Srl. ALi Corporation Alinx Electronic Technology All Sensors Corporation Allegro Microsystems Alliance Memory Allied Vision, Inc. Allwinner Technology Almita Co. Ltd Alpha &amp; Omega Semiconductor Alpha Micro Components Alpha Semiconductor Alpha Wire Alphasense Ltd, Sensor Technology Alps Electric Co Altera Corporation Amazing Electronic Co Amazing Microelectronic Corp AMD American Microsemiconductors American Microsystems Inc American Power Management American Technical Ceramics Corp American Zettler, Inc. Ametherm, Inc AMI Semiconductor AMIC Technology Corp Amidon Associates, Inc Amlogic Inc. Amotech Corp AMPAK Technology Inc Amphenol Advanced Sensors Amphenol Corporation Amphenol FCI Amphenol RF Ampleon USA Inc ams AG Anachip Corp ANADIGICS Anadigm, Inc Analog Devices Analog Integrations Corporation Analog Microelectronics Analog Power Analogix Semiconductor Inc Anaren, Inc Ancol Electronics Co Andigilog, Inc ANENG Anhui FOSAN Semiconductor Anhui Vico Technologes Co Anovay Technologies Limited ANPEC Electronics Corp Ante Intelligent Company Limited AP Memory Technology. APC Propellers APEM Inc Apex Material Technology Apex Precision Power API Delevan Inc API Technologies Aplus Integrated Circuits Inc APMKorea Apogee Technology, Inc Applent Instruments Applied Micro Circuits Co AppoTech Ltd APT Electronics Co., Ltd. Aptek Technologies ArchNet Technology Arcol UK Ltd Arduino Arduino Nicla Voice. Arima Lasers Corporation Aristotle Enterprises Inc ARTCHIP Semiconductor Artesyn Embedded Technologies AS ENERGI Asahi Kasei Microdevices ASAHI Solder Asia Vital Components Asiliant Technologies ASIX Electronics Corp AsLic Microelectronics Corporation ASMedia Technology Inc. Associated Opto-Electronics Astec Semiconductor. Astrodyne TDI Corporation. ATE Electronics s.r.l Atech Technology Co ATEN International Co Atheros Communications, Inc ATI Technologies Inc Atlas Scientific LLC. Attend Technology Inc AU Optronics Corp Audiowell Electronics Co Auk Contractors Co AUK Semiconductor AUO Corporation AUREL S.P.A Austar Technology AuthenTec, Inc Autonics Corporation Avago Technologies AVANTEK INC. AverLogic Technologies, Inc AVerMedia Technologies Avia Semiconductor Avnet, Inc AVX Corporation AXElite Technology Co Axiomtek Axis Communications AZ Displays, Inc Azoteq Ltd BAFO Technologies Corp Bahar Enclosure Baumer International BBT-China Inc BCD Semiconductor Beckhoff Automation Beijing Boshida Beijing HRH Information Co Beijing Ultrasonic Beijing Yihongtai Technology Beijing Zhongxun Sifang Science &amp; Technology Beken Corporation Bel Fuse Inc Bel Power Solutions Inc Belden Inc Bellnix Bencent Tzeng Ind. Co. Ltd Betlux Beyond Innovation Technology BI Technologies Bicker Elektronik GmbH Billionton Systems Inc Bird Technologies Bi-Sonic Technology Bivar, Inc Blackhawk BLOCK Inc Bluegiga Technologies BOLYMIN,INC BONGSHIN LOADCELL CO. Bookly Micro Electronic Bosch Security Systems Inc Bosch Semiconductors Bosch Sensortec Bothhand USA Boundary Devices Bourns Inc Bowin Microelectronics Brainboxes Limited BRIGHT LED ELECTRONICS CORP. Bright Power Semiconductor BrightKing Inc Brilliance Semiconductor, Inc Broadchip Technology Broadcom Limited BroadLight Inc Brooktree Corporation Burr-Brown Corporation BYD Microelectronics Co., Ltd. C&amp;D Technologies C&amp;K Components Caddock Electronics Inc California Eastern Laboratories California Micro Devices Calogic LLC Cambridge Integrated Circuits Cambridge Silicon Ra dio Limited Camille Bauer Ltd Catalyst Semiconductor Celduc relais CellWise Microelectronics Co Cenker Enterprise Ltd Centenary Materials Co CeNtRa Science Corp Central Components Manufacturing Central Georgia Generator Central Semiconductor CEVA Technologies CFSensor Challenge Electronics Champion Microelectronic Changzhou changjie Technology Co Changzhou Cre-sound Electronics Changzhou DRM Changzhou Esuntech Co Changzhou Kennon ELectronics Changzhou TDA Electronic Changzhou Yuanwang Fluid Technology Chaozhou Three-circle (Group) Co chargebyte GmbH. Chengdu Ebyte Electronic Technology Chengdu Guosheng Technology Chengdu Xincheng Huachuang Electronic ChenMoun Electronic ChenYang Technologies Cheuk Yui Innovation Co Chi Mei Optoelectronics Chieful Science ＆ Technology Chilisin Electronics Co China Base Electronic Technology China ECU Tools Centre China Resources Microelectronics China Software Industry Association Chinfa Electronics Chingis Technology Corp Chino-Excel Technology Chipanalog Incorporated ChipLink Tech Chiplus Semiconductor ChipON Chipower Electronics CHIPS Technology Chipstar Microelectronics CHK Electronics Ltd Chogori USA Chongqing Shengpu Electronics Chrontel, Inc Chunghwa Picture Tubes Churod Electronics Chyao Shiunn Electronic Cincon Electronics Cinetech Ind Cirrus Logic Inc Cisco Systems CIT Relay &amp; Switch Citizen Finedevice Co Cixi AnXon Electronic Cixi Dafa precise Linker Co CiXi KaiFeng Electronics Co Cixi Kefa Electronics Cixi Max Electronics Co.,Ltd Clare, Inc Cliff Electronic Components Limited Cmedia Electronics Inc CML Microsystems Coil Master Co Coil Winding Coilcraft Inc Coiltronics (Eaton) Comchip Technology Commodore Semiconductor Comtec Crystals comtech aha corporation CONEC Elektronische Bauelemente GmbH Conesys,Inc. Conexant Systems, Inc Connfly Electronic Co Connor-Winfield Conquer Electronic Continental Device India Controlair Inc Conversion Devices, Inc Cooper Bussmann Coretek Opto Corporation. Cornell Dubilier Electronics Cortina Systems, Inc Cosel Co Ltd COSINE Nanoelectronics Coto Technology CR Powtech Co Cree, Inc Crydom Inc Crystal Semiconductor Corporation Crystalfontz Crystek Corporation CSCONN PRECISE ELECTRONICS CO.,LTD CT Micro International Co CTS Corporation CUI Inc CVI Laser, LLC CW Industries Cyntec Co Cypress Semiconductor Cyrustek Corporation CYStech Electronics Corp. CYT Opto-Electronic Technology Dachang Electronics Daewoo Semiconductor Daier Electron Co Dailywell Electronics Daishinku Corp Daito Communication Apparatus Daiyo Electronics Dallas Semiconductor DANFOSS Daniels Manufacturing Co Data Device Corporation Davicom Semiconductor Davies Molding, LLC DB Lectro Inc DB Unlimited DC Components Co Dean Technology DECA SwitchLab Inc Decawave Ltd Dechang Electronic Deep Sea Electronics DEGSON Electronics Co Dell Inspiron Delta Electronics DeMint Electronics DENSO Destiny Technology Corp Detaik Technology Co Deva Electronic Controls Limited. Devantech Device Engineering Inc Dexter Magnetic Technologies DFRobot. Dialight Electronics Company Dialog Semiconductor Dielectric Laboratories Digi International Digilent, Inc Digital Voice Systems Digitrax, Inc Digitron Semiconductors Dinkle International Co. Ltd DIN-TEK Microelectronics Diodes Incorporated Diotec Semiconductor Diptronics Manufacturing Inc Display Solution AG DISPLAY VISIONS GmbH 2022. DMB Technology DOESTEK Co DOINGTER Semiconductor Domintech Co Don Connex Electronics DONG IL TECHNOLOGY LTD. Dongguan CHENGXING Electronic Co Dongguan City Wasi Electronic Technology Dongguan Cosson DongGuan HeLing Electronics Dongguan Lanbo Electronics Technology CO Dongguan Yuandi Electronics Dongguan Yuanze Electric Co.,Ltd Dongguan Yuxi Precise Connector Co., Ltd Dongke semiconductor Anhui Co., Ltd Donguan Keyouda Electronic Dosilicon Co DTK electronics Dualsky Models Co Duoxing Electronics Co Duty-Cycle Semiconductor Dynamic Technologies (DTCC) Dynex Semiconductor Ltd, E &amp; E Magnetic Products Limited EAST Semiconductor East Texas Integrated Circuits Eastrising Technology Co Eastsensor Technology Easy IoT Eaton’s Bussmann Ebm-papst inc Echelon Corporation Ecliptek Corporation ECOFIT &amp; ETRI ECS, Inc International EDAC EECO Switch E-Elements Technology Co Efficient Power Conversion Co EG Microelectronics Corp EIC Semiconductor Elan Microelectronics Co Elantec, Inc Electrolube Electronic Alliance Electronic Assembly Electronic Devices Inc Electroustic Ltd Eledis Element14 ELESTA GmbH Elite Semiconductor Memory Eljen Technology Elm Electronics ELM Technology Co Elmos Semiconductor AG ELNA Company Elpida Memory, Inc EM Microelectronic-Marin EMAD Embedded Artists Embest Technology Emerson Encitech Endress+Hauser Management ENE Technology Enplas Corporation Enrwey Co Ltd Eon Silicon Solution E-peas Semiconductors Epitex Inc Epoxy Technology Inc EPSON Electronics Ept Inc Ericsson Microelectronics ERNI Electronics ERSA UK LTD Espressif Systems ESS Technologies E-Switch, Inc ET Enterprises Limited E-T-A Circuit Breakers ETA Solutions E-tec Interconnect Ethertronics Inc Etron Technology, Inc EUCHNER GmbH Eupec semiconductor Euroquartz Ltd Eutech Microelectronics Everanalog Everest Semiconductor Everlight Electronics Everspin Technologies Exar Corporation Excel Cell Electronic Excelitas Technologies Excellence Opto, Inc Excelliance MOS Corporation Fagor Electronica Fairchild Semiconductor Fair-Rite Products Corp FANUC Corporation Faraday Technology Fastline Fastrax Ltd FASTRON Faulhaber GmbH FDK Corporation Feature Integration Technology Feei Cherng Enterprise Feeling Technology Feiyi Technology FEMA Electronics Corporation Fenghua Advanced Technology Ferroxcube International FERYSTER Sp. z.o.o Figaro Engineering Inc Finder Relays, Inc Fingerprint Cards First Semiconductor First Sensor FIS Inc Fischer Connectors Fischer Elektronik Fitipower Integrated Technology Force MOS Technology Co Formosa MS Formox Semiconductor Forsentrk Fortior Technology Co Fortune Semiconductor Forward International Electronics FOTEK Controls Fox Electronics Foxconn Technology Fractus S.A Franz Binder GmbH &amp; Co. Free2Move Holding AB. Freescale Semiconductor Fremont Micro Devices Friendcom Technology Develop FriendlyARM Computer Tech FTDI Chip Fuda Hisi Microelectronics Fuji Electric Fujikura Fujitsu Semiconductor Fujitsu-Takamisawa Fulihua Printer Ribbon Co Futaba Corporation Fu-Yao Technology Co Fuzetec Technology Co Fuzhou Rockchip Electronics Co., Ltd GainSpan Corporation GalaxyCore Inc GaNPower International Inc G-Antetech Industrial Garmin Ltd. Gas Sensing Solutions Ltd. Gaston Electronics GC GE Fanuc GEC Plessey Geehy Semiconductor Co General Electronic Devices General Monitors General Semiconductor Generalplus Technology GeneSiC Semiconductor Genesis Microchip Inc Genesys Logic, Inc Genicom Co., Ltd. Gennum Corporation GETE Electronics GigaDevice Semiconductor Global Connector Technology (GCT) Global Mixed-mode Technology GlobespanVirata, Inc GMC Instruments GME Technology, LLC GoChip Electronic Technology GoldStar Semiconductor Gonbes Technology Co Good Display Good Will Instrument Good-Ark Semiconductor Goodix Technology Governors America Co Gpixel Microelectronics Inc Grayhill Inc GreatLEDs Co Greenliant Systems GRUNER AG GSI Technology, Inc Guangdong Hottech Co Guangdong Huaguan Semiconductor Guangdong TIANQIU Electronics Technology Guangzhou Aosong Electronics Guangzhou Xinyue Electronic Guerrilla RF, Inc H&amp;M Semiconductor HABEY Halbleiter aus Frankfurt HALO Electronics Hamamatsu Photonics Hangzhou Grow Technology Co Hangzhou Nationalchip Science Hangzhou Prosper Hangzhou Silan Microelectronics Hannstar Display Corp HanRun Electronics Hanwei Electronics Co Hanyoung Nux Co HAOHAI ELECTRONICS HAOYU Electronics Harris Semiconductor HARTING Technology Harvatek Corporation Harwin Hawyang Semiconductor Hebei International Trading Co HEITEC AG. Hemingruizhi Electronic Henan Hanwei Electronics Co Hengda New Materials Technology HengJiaXing Electronics Co Henkel Corporation HenLv Power Technology Heter Electronics Hewlett-Packard Hexin Technology Highly Electric Hi-Link Electronic Technology Hi-Optel Technology Hirose Electric Hi-Sincerity Microelectronics Hitachi Maxell, Ltd Hitachi Semiconductor HITPOINT Inc Hittite Microwave Hivolt Capacitors Ltd H-JTAG Technology Hokuriku Electric Industry Co Ltd Hokuyo Automatic Co Holt Integrated Circuits Holtek Semiconductor Honeywell International Hong Kong Resistors Manufactory Hongfa Electroacoustic Co HONGHUA ELECTRONIC Hope Microelectronics HORIBA, Ltd. Hosiden Corporation Hosonic Electronic Co Hotchip Technology HTC Korea TAEJIN Technology Huada Connectors Huanor International Huaqi Microelectronics Co Huawei Technologies Huayu Technology HuaYuan Micro Electronic Huayue Microelectronics Co HUBER+SUHNER Huibei KENTO Electronic Huidu Technology Hukx Sensor Technology Humirel Hurricane Tech. Co HW group s.r.o HYCON Technology Corp. Hynix Semiconductor Hyundai Semiconductor IC Plus Corp ICE Components, Inc. iC-Haus GmbH Icom Inc ICP DAS CO ID Innovations ID TECH IDEC Corporation IEI Integration Ignion Iintelligent Motion Systems IK Semiconductor ILSI America LLC IMP, Inc Inchange Semiconductor Industrial Fiber Optics, Inc Industrial Technology Research Institute Infineon Technologies Initio Corporation INJOINIC TECHNOLOGY Innolux Corporation InnoSenT-Innovative Radar Sensor Technology Innovative Sensor Technology IST Innuovo Magnetics Co Inova Semiconductors InPlay Inc. InPower Semiconductor INTEGRAL JSC Integrated Circuit Solution Integrated Circuit Systems Integrated Crystal Technology Integrated Device Technology Integrated Sensor Technologies Integrated Silicon Solution Intel Corporation InterFET Corp Interlink Electronics International CMOS Technology International Rectifier Intersil Corporation Intronic Semiconductor Intronics Power, Inc InvenSense Inc IQD Frequency Products Ltd IRAN Ironwood Electronics IRXON Electronic Isabellenhütte Heusler GmbH &amp; Co KG Isahaya Electronics Co iSentek Technology Isocom Components Isotek Corp ITE Tech ITT Cannon, LLC ITT Semiconductors Ituner Networks Corp iWatt Inc IXYS Integrated Circuits J.S.T. Mfg. Co JACKSON ELECTRONICS IND. CROP. JAE Electronics JAI Ltd Jamicon Electronics JAVAN JCET Group Co JCI Jewel Hill Electronic Co JHDLCM Electronics Jiangsu Changjiang Electronics Jiangsu Donghai Semiconductor Jiangsu Juguang Jiangsu Runic Technology Co Jiangsu Szdhdtgd Electronics Jiangxi Jia Wei Cheng Electronic Jilin Sino-Microelectronics Co Jinan USR IOT Technology JING LI Power Electronics Jingcheng Electronics Co Jinghan Switch Electronic JMicron Technology Corp JNHuaMao Technology JODO International Johanson Dielectrics Johanson Technology Johnson Electric JPC Company JYE Tech Ltd JYH HSU(JEC) ELECTRONICS Kai Suh Suh Enterprise KSS Kaida Holding Kaihua Electronics Co Kangmu Sheng Electronics Ka-Ro electronics GmbH. KEC Semiconductor Keil Elektronik Keithley Instruments Kelly Controls, LLC KEMET Corporation Key Technology Keysight Technologies Keystone Electronic King Core Electronics Kingbor Technology Kingbright Electronic KingCCTV Technology Kingdatron Electronic Industrial Co Kingsignal Technology Kingstate Electronics Kingston KIOXIA America, Inc Kiwi Instruments Corp Knowles Electronics KOA Speer Electronics Kobiconn Kodenshi Corp Kohshin Electric Corporation KONE Elevator Kontron S&amp;T KT Micro Inc Kunshan Sino Silicon Technology KUOYUH W.L. Enterprise Co Kutai Electronics Kycon, Inc Kyocera Corporation Ladder Electronics Co Laird Performance Materials. Laird Technologies Laser Components Lattice Semiconductor LawMate International L-com, Inc LD-PD Inc. Leadtrend Technology Corp LEAP Electronic Legerity, Inc Lelon Electronics Corp LEM Components LEMO Lenovo LENZE Lesfuse Electric Co Leshan Radio Co LG Semiconductor LG.Philips Displays Lianchao Future Technology Lighting Integration System Ligitek Electronics Co Lime Microsystems Lineage Power Private Limited Linear Systems Linear Technology Linfinity Microelectronics Link-PP Int'l Technology LinkSmart LINP OMTER International Linx Technologies Lision Technology LITE-ON Semiconductor Littelfuse Inc Lixin Electromagnetic Clutch LIZE Electronic Technology LND, INC LOETRONIC LOGIC Devices Incorporated Longtech Optics Co Longview Technologies Co Lovid International Electronic Low Power Radio Solutions Ltd LOZEN TECHNOLOGY LS ELECTRIC LS Mtron Ltd LSI Computer Systems LTKCHIP LTN Servotechnik GmbH Lucent Technologies LUCKFOX Technology Lucky Light Electronic Luguang Electronic Technology Lumberg Holding Lumentum Operations LLC. Lumex Inc Lumileds Luminus, Inc. Lumissil Microsystems Luna Optoelectronics Lutron Electronic Enterprise Co Lyontek Inc M.S. Kennedy Corp M+R Multitronik GmbH MACOM Technology Macroblock, Inc Macronix International MacTek Corp MagnaChip Semiconductor Magnetics MagnTek Microelectronics Magtek Technology Inc Manorshi Electronics Marktech Optoelectronics, Inc Marlow Industries, Inc Marquardt Switches, Inc Marvell International Matsushita Electric Max Echo Technology Corp MaxBotix Inc Maxic Technology Corporation Maxim Integrated MaxLinear Inc Maxon motor Maxwell Technologies Mayloon Electronic Company MCS Logic Inc Mcuzone International MEAN WELL Enterprises Co Measurement Specialties Mechanic MediaTek Inc Megatek Melexis Technologies Memory Protection Devices MEMSIC, Inc Mentor GmbH Mercury Electronic Meritek Electronics Corporation Mersen EP Metalink Broadband Meticom GmbH. METRODYNE MICROSYSTEM CORP. MIC Electronic Micrel, Inc Micro Commercial Components Micro Crystal AG Micro Electronics Micro Linear Micro One Electronics Micro Power Systems MICRO SENSOR CO;LTD Microchip Technology Microdiode Semiconductor Micrometals, Inc Micron Technology Micronet Communication Microsemi Corporation Microtech Technology Co Ltd Microtherm Sentronic GmbH Microtips Technology Midori Precisions MikroElektronika MikroElektronika d.o.o MikroTik Mill-Max Mfg Milnec Interconnect Systems MindMotion Microelectronics Co. Mingtek Electronics Ltd Mini-Circuits Minilogic Device Corporation Ltd Minmax Technology Minsoo Electronic Co MiTAC Computing Technology Mitel Semiconductor Mitsubishi Electric Mitsubishi Rayon Co Mitsumi Electric Co Mixed Signal Integration Mixic Electronics MKMX America LLC MMI Semiconductors MOAI electronics co Mobicon Electronic Component Modulestek Inc MOKO TECHNOLOGY LTD. Molex Electronic Monitor Enterprises Inc Monolithic Power Systems Morethanall Co Morningstar Corporation MORNSUN Science &amp; Technology Mosdesign Semiconductor Corp Mosel Vitelic Co MOSPEC Semiconductor MOS-TECH Semiconductor Mostek MOTIEN Technology Motorola Mstar Semiconductor M-Systems Inc Multicomp Multi-Inno Technology Multi-Tech Systems Inc Murata Manufacturing Co MVSILICON MYIR Tech Myrra SAS Naina Semiconductor Limited. Nanjing Haichuan Electronic Nanjing Ouzhuo Tech Nanjing Qinheng Microelectronics Nanjing Shiheng Elec NanJing Top Power ASIC Nanjing Up Electronic Technology Nanjing Wotian Technology Co Nanjing Zeming Electronic Co Nanya Technology Co National Instruments National Semiconductor NDK America Inc NEC Electronics Nell Semiconductor Neltron Industrial Nemoto Sensor Engineering NeuroSky, Inc. Neutrik New Jersey Semiconductor NewAE Technology Inc. Newava Technology Inc. Newhaven Display Newport Corporation NewTec Display Co NexFlash Technologies, Inc Nexperia USA Inc Nextchip Nextion NIC Components Corp. Nichia Corporation Nichicon Corporation Nidec Copal Electronics NIDEC SERVO CORPORATION. Nihon Dempa Kogyo Nihon Inter Electronics NIKO Semiconductor Ningbo East Electronics Ningbo ForwardRelayCorporationLTD Ningbo Gosun Technology Co Ningbo Huaguan Electronics Ningbo KLS Electronic Co Ningbo MAX Electronic Technology Co., Ltd Ningbo MKX Electronic Technology Ningbo Rel Electric Co., Ltd. Ningbo Songle Relay Ningbo Tianbo Ganglian Electronics Ninigi Nippon Chemi-Con Nippon Pulse America, Inc Nisshinbo Micro Devices Inc NJR Corporation NKK Switches NMB Technologies Non-Brand Norcomp Inc Nordic Semiconductor Noritake Itron Co Novacap Novatek Microelectronics NTE Electronics NUAND LLC. Nuvoton Technology NVE Corporation Nvidia NVS Navigation Technologies NXP Semiconductors NYS Resistor O2Micro OCIC co Octavo Systems LLC Ogemray Technology Co Ohmite OKI Semiconductor Ole Wolff Electronics Inc Olimex OmniVision Technologies Omron Electronics Omten Electronics ON Semiconductor ON Semiconductor CHINA On Shore Technology On-Bright Electronics OPTEK Technology Inc OPTi Inc Opticon Inc Opto 22 Opto Diode Corp Opto Electronics Co,. LTD OPTOLAB Microsystems Orient Display Oriental Semiconductor Orion Orion Display Technology Co OSI Optoelectronics OSRAM Opto Semiconductors OTAX Corporation Other Oupiin Enterprise Co OWON Technology Inc P&amp;E Microcomputer Systems Pacific Silicon Sensor Panasonic Corporation Panavision Imaging LLC Pancon Corporation PandaBoard PANJIT International Inc Para Light Electronics P-DUKE Technology Co PEAK Electronics GmbH PEAK-System Technik Penny &amp; Giles Peregrine Semiconductor Pericom Semiconductor Corp PerkinElmer Inc Phidgets, Inc Philips Semiconductor Phison Electronics Phoenix Contact Pickering Electronics Ltd PICO Electronics Pico Technology Piher Sensors &amp; Controls SA Pingjing Semi Technology PIR Sensor Co PixArt Imaging Inc Planar Systems, Inc PLX Technology PMC-Sierra, Inc PNI Sensor Corporation POCO Magnetic Polyfet RF Devices Polytronics Technology Pomona Electronics Power Integrations Power Mate Technology Power Systems GmbH Power-Changer Electronic Co Powerex Inc PowerPlaza Powersem GmbH Powertip Technology Preci-Dip SA Precision Monolithics, Inc PREMA Semiconductor GmbH Premier Magnetics PRETEC/C-One Technology Corp. Princeton Technology Proant AB Profichip GmbH Prokit's Industries Prolific Technology Inc Promax-Johnton Semiconductor Pro-Signal ProTek Devices Pro-Wave Electronic PRT PUI Audio Pulse Electronics Qimei Optical &amp; Electric Qingdao Mefine Electronics Qingxian Zeming Langxi Electronic Devices Co Qingyuan Tesla Electronic Technology Qorvo QT Brightek (QTB) QT Optoelectronics Qualcomm Atheros, Inc Quality Semiconductor Qualtek Electronics Quarton inc Quasar Electronics Limited Quectel Wireless Solutions QuickLogic Corporation QX Micro Devices Radiall Radxa Computer Rafael Microelectronics RAFI GmbH &amp; Co RAiO TECHNOLOGY INC RAKwireless Technology Limited. RALEC Ltd Ralink Technology Raltron Electronics Corporation Ramtron International Rapid Electronics Ltd Raspberry Pi Raycom Co Raytac Corporation. Raytheon RCA Corporation Ready Made RC LLC Realtek Semiconductor RECOM Power GmbH Rectron Semiconductor Reichelt elektronik GmbH &amp; Co. KG RELPOL S.A Renata SA Renesas Technology Renhotec Group Ltd Reomax Electronics Reyed Electronics Co RF Digital Corporation. RF Micro Devices RF Solutions Ltd RFaxis, Inc RFHIC Corporation RFM Integrated Device, Inc. RFT Mikroelektronik Rhombus Industries Inc Richtek Technology Co RichWave Technology Ricoh Electronic Devices Riedon RIGOL Ring&amp;tone Electronic Technology Riverdi RLS Merilna tehnika d.o.o ROBOTIS Co Rockwell Rogers Corporation ROHM Semiconductor Roithner Lasertechnik GmbH Rongtech Industry Royal Electronic Factory Co RS Components Ltd RTD Embedded Technologies Rubycon RYCHIP Semiconductor s.m.a.e. GmbH Saft Groupe S.A Sagami Electronics Saia-Burgess Switches Sakae Tsushin Kogyo Saleae, Inc Salecom Electronics Same Sky SamHop Microelectronics Samsung Electronics Samtec Samwha Capacitor Samwin Electronic Technology Samyoung S &amp; C Co SANCO Electronics Co SanDisk Sanhe Enclosure Sanjiaozhou Electrical Technology Sanken Electric SanRex Corporation Sanyo Denki Sanyo Electric Savantic Electronic Sawnics Inc Schaffner Group Schott AG Schrack Technik GmbH Schurter Inc Sciosense B.V. SCTF Electronics Seagate Technology LLC Seaparks Machinery-Electronics Seaward Electronics SeCoS Corporation SEED International Ltd Seeed Technology SEEQ Technology Segger Microcontroller Systems Seiko Instruments Inc Seiko NPC Corporation Semiconductor Circuits, Inc SemiHow Semikron Semiment Technologies Semi-Powerex Corp. SEMITEC Corporation SemiWell Semiconductor Semtech Corporation Semtech Electronics Senba Sensing Technology Co Sendo Sensor Sensata Technologies Sensirion Sentry Manufacturing Inc SEP Electronic Corp Servotecnica SpA SERVO-TEK PRODUCTS COMPANY, INC. SG Micro Corp SGX Sensortech Shaanxi Fullstar Electronics Co Shaanxi Qunli Electric Shaanxi Reactor Microelectronics Shandong Jingdao Microelectronics Shanghai AVIC Optoelectronics Shanghai Belling Co,Ltd Shanghai Consonance Electronics Shanghai Fengxin Electronic Technology Shanghai Fudan Microelectronics Shanghai Gotop Technology Shanghai High-Flying Electronics Shanghai Houde Photo-electric Shanghai Mixinno Microelectronics Co Shanghai Natlinear Electronics Shanghai Xinlong Semiconductor Shanghai Zhichuan Electronic Tech SHARP Corporation Sheng Jay Automation Techno Shenyang Guangcheng Technology Co., Ltd Shenyang KingStar Automation ShenZhen AI-thinker CO Shenzhen AnBoShi Electronic Shenzhen Asenware Test Shenzhen Baishan Mechatronics Shenzhen Biosled Technology Shenzhen Bolutek Technology Shenzhen Chipsea Technologies ShenZhen ChipSourceTek Technology Shenzhen ExSAF Electronics Co Shenzhen Genesis-Systech ShenZhen Gerbole Shenzhen Getech Co Shenzhen GUANGSHIMEI Electronic Shenzhen Hanxia Electronics Shenzhen Haolin Electronics Shenzhen Heliwei Technology Shenzhen honglifa Electronics Co Shenzhen HongyeX Electronics Co ShenZhen HuaXinAn Electronics Co.,Ltd Shenzhen Injoinic Technology Co. Shenzhen Jin Yu Semiconductor Co ShenZhen JINCI Technology Shenzhen Jinrui Electronic Material Co Shenzhen JMRTH Co Shenzhen Kaiyuexiang Electronics Co Shenzhen LFN Technology Co Shenzhen Lodestar S.T Co Shenzhen Lumen Electronics Shenzhen Magnetic Technology Shenzhen MilkV Technology Shenzhen Milliohm Electronics Shenzhen Minewsemi Co., Ltd Shenzhen Nsiway Tech Shenzhen Ou Chuangxin Semiconductor ShenZhen Qi Dian Shi Dai Technology Shenzhen Ruichips Semiconductor Shenzhen Ruilongyuan Electronics Shenzhen Shiji Lighting Shenzhen SI Semiconductors Shenzhen SLKOR Micro Semicon Co Shenzhen Sunmoon Microelectronics Shenzhen Suosemi Tech Shenzhen TongYiFang Optoelectronic Technology CO,Ltd Shenzhen Topmay Electronic Shenzhen TPOWER Semiconductor Shenzhen Universal Micro-Electronics Shenzhen USBR Precision Hardware Electronics Shenzhen Weidy Industrial Development Co., Ltd. Shenzhen Xinbole Electronics Co. Shenzhen Xptek Technology Shenzhen Xunlong Shenzhen Yangxing Technology Co. SHENZHEN YeZhan Electronics Shenzhen Yiwei Technology Shenzhen ZVELL Electronics Shindengen Electric Shin-Etsu Chemical Co SHINYEI Technology SHOEI SIBA GmbH Sichuan huafeng enterprise group SICK, Inc. Siemens Semiconductor Group Si-En Technology SiFirst Technology SiGe Semiconductor Sigma Microelectronics Signetics Silego Technology Silergy Corp Silicon Image Silicon Integrated Systems Silicon Laboratories Silicon Microstructures, Inc. Silicon Motion, Inc Silicon Sensing Systems Limited Silicon Standard Corp Silicon Storage Technology Silicon Systems Inc Silicon Touch Technology Silvan Chip Electronics Silver Telecom Ltd SilverStone Technology SIMCom Wireless Solutions SIMTEK Electronic Components Sinda Photoelectricity Technology SINGULAR TECHNOLOGY CO., LTD. Sinomags Technologies Co Sinopower Semiconductor Sipex Corporation Sirectifier Semiconductors SiTime Corporation Sivago Semiconductor Co SIWARD Crystal Technology Siyang Microelectronics Sizto Tech Corp SKYLAB M&amp;C Technology Skyworks Solutions, Inc SL Power Electronics Corp. SMAR Smartec BV SMC Diode Solutions Co. Smiths Interconnect. SMSC Corporation Soberton Inc Softing Automotive Electronics Sola/Hevi-Duty Sola-IC Solarflex SA Soldex Solid State Scientific SOLIDIC Solitronics Engineering Limited SOL-LED Lighting Co Solomon Systech Song Chuan Song Huei Electric Sonix Technology Sony Corporation Soundwell Electronic South African Micro-Electronic Systems Spansion inc SparkFun Electronics SPEC Sensors LLC Spectra Symbol Corp. Spectrum Digital Incorporated Speed Tech Corp Spin Semiconductor Sprague Semiconductors SPX Flow Technology ST Engineering Stackpole Electronics Standex-Meder Electronics Stannol GmbH Stanson Technology StarChips Technology StarPower Semiconductor Ltd. Startek Electronic Technology STATEK CORPORATION Stäubli International AG. STCmicro Technology Co Stewart Connector STMicroelectronics Stocko Stork Solutions Ltd. Sullins Connector Solutions SUMIDA Corporation Sun Hydraulics Corporation Sun Microelectronics SunLED SUNLORD Sunltech Tech SUNMATE Electronic Sunonwealth Electric Machine Sunplus Technology Sunrise Electronics Suntan Technology Company Suntsu Electronics, Inc. SUNYUAN Technology Supertex Inc Susumu International Suzhou Innoson Technology Suzhou NOVOSENSE Microelectronics Co., Ltd Suzhou Silikron Semiconductor Corp Switchcraft Inc. Switec SYNC Power Crop SyncMOS Technologies Synoxo International System General Corp Tadiran Batteries TAG Semiconductors TA-I Technology TAIKO-NET Tai-Saw Technology Tai-Tech Advanced Electronics Taitien Electronics Taitron Components, Inc Taiwan Alpha Electronic Co Taiwan Semiconductor Taiyo Electric Co Taiyo Yuden Tak Cheong Electronics Talema Group, LLC Tamagawa seiki Co Tamron Tamura Corporation TANCAP Technology Taoglas Limited TDK Corporation (EPCOS) TDK-Lambda Corporation TDK-Micronas GmbH TE Connectivity Team Source Display tech.co,ltd. Techcode Semiconductor Techpoint Inc Techspray/Plato-EMX Enterprises Limited Techstar Electronics TechToys Company TelCom Semiconductor Telcon Ltd Telechips Inc Teledyne Technologies TELEFUNKEN Elektroakustik Telegesis Ltd Telit TEMIC Semiconductor Terawins, Inc Teridian Semiconductor TESLA Testo SE &amp; Co Texas Advanced Optoelectronic Solutions Texas Instruments THAT Corporation Thegioiic Corporation Thermonamic Electronics(Jiangxi) Corp THine Electronics, Inc Thinki Semiconductor Thinking Electronic THOMSON Inc THORLABS Thousand Hundred Industrial Thunder Precision Resistor TIANMA Titan Micro TLC Electronics TNI-U TOOL Token Electronics Industry Tokmas Semiconductor TOKO, Inc Tontek Design Technology Top-arm Topro Technology Topway Technology Torex Semiconductor Toshiba Corporation touchSEMI TOYO LED ELECTRONICS LIMITED. TOYODA TR Electronic Nordic AB. Traco Electronic AG Transcom, Inc Transko Electronics, Inc. TRENDnet, Inc Trenz Electronic Triad Magnetics Trident Microsystems Trimble Inc TRINAMIC Motion Control TRinno Technology Co Tripath Technology TriQuint Semiconductor Truly Semiconductors TRW Inc TT Electronics TTM Technologies, Inc. TXC Corporation UBIQ Semiconductor Ubiquiti Inc u-blox UCE Ultrasonic Co UDF Semiconductor Ultisensor Electronics UNI SEMICONDUCTOR LIMITED Unicorn Microelectronics Corporation Unictron Technologies Corporation. Union Semiconductor Uniroyal Electronics Industry Co Unisonic Technologies Unitra Cemi Uni-Trend Technology Co Unitrode Corporation Universal Microelectronics UPI Semiconductor Corp US Digital US Micro Products. Usha India Ltd Ushio Opto Semiconductors UTRON Technology, Inc Vacuumschmelze GmbH VADEM LTD Vango Technologies, Inc Varitronix Limited VARTA AG Vatronics Technologies Ltd VBsemi Electronics Co. Ltd V-Chip Microsystems VectorNav Vectron International Vehicles instrumentation Device Venkel Ltd VIA Technologies Vicor Corporation Vigortronix Ltd. Vincotech Vishay Visual communication company Vitesse Semiconductor Vivesea VLSI Solution Vweb Corporation W. L. Gore &amp; Associates, Inc WAGO Kontakttechnik GmbH Wakefield Thermal, Inc. Walsin Technology Corporation Walter Electronic Co WanTcom, Inc Wavecom Waveshare Electronics Wavespectrum Laser Inc Wavetronics Technologies WAYTRONIC ELECTRONIC CO.LTD WeEn Semiconductors Weidmüller Interface GmbH Weipu connector Weltrend Semiconductor WENSHING Electronics Western Digital Corporation Willas Electronic Corp WIMA Winbond Electronic</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>27700</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>55400</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>100nF</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C6,C7,C8,C9,C10,C15,C16</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>100nF</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop?searchfilter=4184#dtl/7589</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>محصولات خانه دسته‌بندی‌ها فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه عبارت 4184 جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش برند 1666 3M Dynapro 3M Interconnect 3PEAK Incorporated 4D Systems Pty Ltd A Power microelectronics AAEON Technology Aavid Thermalloy ABC Taiwan Electronics ABLIC Inc Abracon Corporation Acam-Messelectronic Acrian, Inc Actel Corporation Active-Semi, Inc Actox Corporation. AD Semiconductor Confidential Adafruit Industries LLC Adam Technologies, Inc ADDA Corp ADDtek Corp Adesto Technologies ADMtek Inc Advanced Acoustic Technology Corp. Advanced Analog Technology Advanced Analogic Technologies Advanced Card Systems Advanced Ceramic X Corp Advanced Linear Devices Inc Advanced Monolithic Systems Advanced Photonix, Inc Advanced Power Electronics Corp Advanced Power Technology Advanced Semiconductor Advantech Corp Advantech Equipment Corporation Aegis Electronic Group AEL Crystals Limited AEM, Inc Aerosemi Technology Co Afa Technologies Inc AG Electrical Technology Agere Systems Agilent Technologies AGM Semiconductor AIC tech Inc. Aimtec Aimtron Corporation Airoha Technology Corp AIRWAVE Technologies Inc AiSHi Capacitors Aixin Opto-Electrical Technology Albright International Ltd Alcatel Microelectronics Alcor Micro Corp Alex Connector Co Ltd Alfa Electronics Algocraft Srl. ALi Corporation Alinx Electronic Technology All Sensors Corporation Allegro Microsystems Alliance Memory Allied Vision, Inc. Allwinner Technology Almita Co. Ltd Alpha &amp; Omega Semiconductor Alpha Micro Components Alpha Semiconductor Alpha Wire Alphasense Ltd, Sensor Technology Alps Electric Co Altera Corporation Amazing Electronic Co Amazing Microelectronic Corp AMD American Microsemiconductors American Microsystems Inc American Power Management American Technical Ceramics Corp American Zettler, Inc. Ametherm, Inc AMI Semiconductor AMIC Technology Corp Amidon Associates, Inc Amlogic Inc. Amotech Corp AMPAK Technology Inc Amphenol Advanced Sensors Amphenol Corporation Amphenol FCI Amphenol RF Ampleon USA Inc ams AG Anachip Corp ANADIGICS Anadigm, Inc Analog Devices Analog Integrations Corporation Analog Microelectronics Analog Power Analogix Semiconductor Inc Anaren, Inc Ancol Electronics Co Andigilog, Inc ANENG Anhui FOSAN Semiconductor Anhui Vico Technologes Co Anovay Technologies Limited ANPEC Electronics Corp Ante Intelligent Company Limited AP Memory Technology. APC Propellers APEM Inc Apex Material Technology Apex Precision Power API Delevan Inc API Technologies Aplus Integrated Circuits Inc APMKorea Apogee Technology, Inc Applent Instruments Applied Micro Circuits Co AppoTech Ltd APT Electronics Co., Ltd. Aptek Technologies ArchNet Technology Arcol UK Ltd Arduino Arduino Nicla Voice. Arima Lasers Corporation Aristotle Enterprises Inc ARTCHIP Semiconductor Artesyn Embedded Technologies AS ENERGI Asahi Kasei Microdevices ASAHI Solder Asia Vital Components Asiliant Technologies ASIX Electronics Corp AsLic Microelectronics Corporation ASMedia Technology Inc. Associated Opto-Electronics Astec Semiconductor. Astrodyne TDI Corporation. ATE Electronics s.r.l Atech Technology Co ATEN International Co Atheros Communications, Inc ATI Technologies Inc Atlas Scientific LLC. Attend Technology Inc AU Optronics Corp Audiowell Electronics Co Auk Contractors Co AUK Semiconductor AUO Corporation AUREL S.P.A Austar Technology AuthenTec, Inc Autonics Corporation Avago Technologies AVANTEK INC. AverLogic Technologies, Inc AVerMedia Technologies Avia Semiconductor Avnet, Inc AVX Corporation AXElite Technology Co Axiomtek Axis Communications AZ Displays, Inc Azoteq Ltd BAFO Technologies Corp Bahar Enclosure Baumer International BBT-China Inc BCD Semiconductor Beckhoff Automation Beijing Boshida Beijing HRH Information Co Beijing Ultrasonic Beijing Yihongtai Technology Beijing Zhongxun Sifang Science &amp; Technology Beken Corporation Bel Fuse Inc Bel Power Solutions Inc Belden Inc Bellnix Bencent Tzeng Ind. Co. Ltd Betlux Beyond Innovation Technology BI Technologies Bicker Elektronik GmbH Billionton Systems Inc Bird Technologies Bi-Sonic Technology Bivar, Inc Blackhawk BLOCK Inc Bluegiga Technologies BOLYMIN,INC BONGSHIN LOADCELL CO. Bookly Micro Electronic Bosch Security Systems Inc Bosch Semiconductors Bosch Sensortec Bothhand USA Boundary Devices Bourns Inc Bowin Microelectronics Brainboxes Limited BRIGHT LED ELECTRONICS CORP. Bright Power Semiconductor BrightKing Inc Brilliance Semiconductor, Inc Broadchip Technology Broadcom Limited BroadLight Inc Brooktree Corporation Burr-Brown Corporation BYD Microelectronics Co., Ltd. C&amp;D Technologies C&amp;K Components Caddock Electronics Inc California Eastern Laboratories California Micro Devices Calogic LLC Cambridge Integrated Circuits Cambridge Silicon Ra dio Limited Camille Bauer Ltd Catalyst Semiconductor Celduc relais CellWise Microelectronics Co Cenker Enterprise Ltd Centenary Materials Co CeNtRa Science Corp Central Components Manufacturing Central Georgia Generator Central Semiconductor CEVA Technologies CFSensor Challenge Electronics Champion Microelectronic Changzhou changjie Technology Co Changzhou Cre-sound Electronics Changzhou DRM Changzhou Esuntech Co Changzhou Kennon ELectronics Changzhou TDA Electronic Changzhou Yuanwang Fluid Technology Chaozhou Three-circle (Group) Co chargebyte GmbH. Chengdu Ebyte Electronic Technology Chengdu Guosheng Technology Chengdu Xincheng Huachuang Electronic ChenMoun Electronic ChenYang Technologies Cheuk Yui Innovation Co Chi Mei Optoelectronics Chieful Science ＆ Technology Chilisin Electronics Co China Base Electronic Technology China ECU Tools Centre China Resources Microelectronics China Software Industry Association Chinfa Electronics Chingis Technology Corp Chino-Excel Technology Chipanalog Incorporated ChipLink Tech Chiplus Semiconductor ChipON Chipower Electronics CHIPS Technology Chipstar Microelectronics CHK Electronics Ltd Chogori USA Chongqing Shengpu Electronics Chrontel, Inc Chunghwa Picture Tubes Churod Electronics Chyao Shiunn Electronic Cincon Electronics Cinetech Ind Cirrus Logic Inc Cisco Systems CIT Relay &amp; Switch Citizen Finedevice Co Cixi AnXon Electronic Cixi Dafa precise Linker Co CiXi KaiFeng Electronics Co Cixi Kefa Electronics Cixi Max Electronics Co.,Ltd Clare, Inc Cliff Electronic Components Limited Cmedia Electronics Inc CML Microsystems Coil Master Co Coil Winding Coilcraft Inc Coiltronics (Eaton) Comchip Technology Commodore Semiconductor Comtec Crystals comtech aha corporation CONEC Elektronische Bauelemente GmbH Conesys,Inc. Conexant Systems, Inc Connfly Electronic Co Connor-Winfield Conquer Electronic Continental Device India Controlair Inc Conversion Devices, Inc Cooper Bussmann Coretek Opto Corporation. Cornell Dubilier Electronics Cortina Systems, Inc Cosel Co Ltd COSINE Nanoelectronics Coto Technology CR Powtech Co Cree, Inc Crydom Inc Crystal Semiconductor Corporation Crystalfontz Crystek Corporation CSCONN PRECISE ELECTRONICS CO.,LTD CT Micro International Co CTS Corporation CUI Inc CVI Laser, LLC CW Industries Cyntec Co Cypress Semiconductor Cyrustek Corporation CYStech Electronics Corp. CYT Opto-Electronic Technology Dachang Electronics Daewoo Semiconductor Daier Electron Co Dailywell Electronics Daishinku Corp Daito Communication Apparatus Daiyo Electronics Dallas Semiconductor DANFOSS Daniels Manufacturing Co Data Device Corporation Davicom Semiconductor Davies Molding, LLC DB Lectro Inc DB Unlimited DC Components Co Dean Technology DECA SwitchLab Inc Decawave Ltd Dechang Electronic Deep Sea Electronics DEGSON Electronics Co Dell Inspiron Delta Electronics DeMint Electronics DENSO Destiny Technology Corp Detaik Technology Co Deva Electronic Controls Limited. Devantech Device Engineering Inc Dexter Magnetic Technologies DFRobot. Dialight Electronics Company Dialog Semiconductor Dielectric Laboratories Digi International Digilent, Inc Digital Voice Systems Digitrax, Inc Digitron Semiconductors Dinkle International Co. Ltd DIN-TEK Microelectronics Diodes Incorporated Diotec Semiconductor Diptronics Manufacturing Inc Display Solution AG DISPLAY VISIONS GmbH 2022. DMB Technology DOESTEK Co DOINGTER Semiconductor Domintech Co Don Connex Electronics DONG IL TECHNOLOGY LTD. Dongguan CHENGXING Electronic Co Dongguan City Wasi Electronic Technology Dongguan Cosson DongGuan HeLing Electronics Dongguan Lanbo Electronics Technology CO Dongguan Yuandi Electronics Dongguan Yuanze Electric Co.,Ltd Dongguan Yuxi Precise Connector Co., Ltd Dongke semiconductor Anhui Co., Ltd Donguan Keyouda Electronic Dosilicon Co DTK electronics Dualsky Models Co Duoxing Electronics Co Duty-Cycle Semiconductor Dynamic Technologies (DTCC) Dynex Semiconductor Ltd, E &amp; E Magnetic Products Limited EAST Semiconductor East Texas Integrated Circuits Eastrising Technology Co Eastsensor Technology Easy IoT Eaton’s Bussmann Ebm-papst inc Echelon Corporation Ecliptek Corporation ECOFIT &amp; ETRI ECS, Inc International EDAC EECO Switch E-Elements Technology Co Efficient Power Conversion Co EG Microelectronics Corp EIC Semiconductor Elan Microelectronics Co Elantec, Inc Electrolube Electronic Alliance Electronic Assembly Electronic Devices Inc Electroustic Ltd Eledis Element14 ELESTA GmbH Elite Semiconductor Memory Eljen Technology Elm Electronics ELM Technology Co Elmos Semiconductor AG ELNA Company Elpida Memory, Inc EM Microelectronic-Marin EMAD Embedded Artists Embest Technology Emerson Encitech Endress+Hauser Management ENE Technology Enplas Corporation Enrwey Co Ltd Eon Silicon Solution E-peas Semiconductors Epitex Inc Epoxy Technology Inc EPSON Electronics Ept Inc Ericsson Microelectronics ERNI Electronics ERSA UK LTD Espressif Systems ESS Technologies E-Switch, Inc ET Enterprises Limited E-T-A Circuit Breakers ETA Solutions E-tec Interconnect Ethertronics Inc Etron Technology, Inc EUCHNER GmbH Eupec semiconductor Euroquartz Ltd Eutech Microelectronics Everanalog Everest Semiconductor Everlight Electronics Everspin Technologies Exar Corporation Excel Cell Electronic Excelitas Technologies Excellence Opto, Inc Excelliance MOS Corporation Fagor Electronica Fairchild Semiconductor Fair-Rite Products Corp FANUC Corporation Faraday Technology Fastline Fastrax Ltd FASTRON Faulhaber GmbH FDK Corporation Feature Integration Technology Feei Cherng Enterprise Feeling Technology Feiyi Technology FEMA Electronics Corporation Fenghua Advanced Technology Ferroxcube International FERYSTER Sp. z.o.o Figaro Engineering Inc Finder Relays, Inc Fingerprint Cards First Semiconductor First Sensor FIS Inc Fischer Connectors Fischer Elektronik Fitipower Integrated Technology Force MOS Technology Co Formosa MS Formox Semiconductor Forsentrk Fortior Technology Co Fortune Semiconductor Forward International Electronics FOTEK Controls Fox Electronics Foxconn Technology Fractus S.A Franz Binder GmbH &amp; Co. Free2Move Holding AB. Freescale Semiconductor Fremont Micro Devices Friendcom Technology Develop FriendlyARM Computer Tech FTDI Chip Fuda Hisi Microelectronics Fuji Electric Fujikura Fujitsu Semiconductor Fujitsu-Takamisawa Fulihua Printer Ribbon Co Futaba Corporation Fu-Yao Technology Co Fuzetec Technology Co Fuzhou Rockchip Electronics Co., Ltd GainSpan Corporation GalaxyCore Inc GaNPower International Inc G-Antetech Industrial Garmin Ltd. Gas Sensing Solutions Ltd. Gaston Electronics GC GE Fanuc GEC Plessey Geehy Semiconductor Co General Electronic Devices General Monitors General Semiconductor Generalplus Technology GeneSiC Semiconductor Genesis Microchip Inc Genesys Logic, Inc Genicom Co., Ltd. Gennum Corporation GETE Electronics GigaDevice Semiconductor Global Connector Technology (GCT) Global Mixed-mode Technology GlobespanVirata, Inc GMC Instruments GME Technology, LLC GoChip Electronic Technology GoldStar Semiconductor Gonbes Technology Co Good Display Good Will Instrument Good-Ark Semiconductor Goodix Technology Governors America Co Gpixel Microelectronics Inc Grayhill Inc GreatLEDs Co Greenliant Systems GRUNER AG GSI Technology, Inc Guangdong Hottech Co Guangdong Huaguan Semiconductor Guangdong TIANQIU Electronics Technology Guangzhou Aosong Electronics Guangzhou Xinyue Electronic Guerrilla RF, Inc H&amp;M Semiconductor HABEY Halbleiter aus Frankfurt HALO Electronics Hamamatsu Photonics Hangzhou Grow Technology Co Hangzhou Nationalchip Science Hangzhou Prosper Hangzhou Silan Microelectronics Hannstar Display Corp HanRun Electronics Hanwei Electronics Co Hanyoung Nux Co HAOHAI ELECTRONICS HAOYU Electronics Harris Semiconductor HARTING Technology Harvatek Corporation Harwin Hawyang Semiconductor Hebei International Trading Co HEITEC AG. Hemingruizhi Electronic Henan Hanwei Electronics Co Hengda New Materials Technology HengJiaXing Electronics Co Henkel Corporation HenLv Power Technology Heter Electronics Hewlett-Packard Hexin Technology Highly Electric Hi-Link Electronic Technology Hi-Optel Technology Hirose Electric Hi-Sincerity Microelectronics Hitachi Maxell, Ltd Hitachi Semiconductor HITPOINT Inc Hittite Microwave Hivolt Capacitors Ltd H-JTAG Technology Hokuriku Electric Industry Co Ltd Hokuyo Automatic Co Holt Integrated Circuits Holtek Semiconductor Honeywell International Hong Kong Resistors Manufactory Hongfa Electroacoustic Co HONGHUA ELECTRONIC Hope Microelectronics HORIBA, Ltd. Hosiden Corporation Hosonic Electronic Co Hotchip Technology HTC Korea TAEJIN Technology Huada Connectors Huanor International Huaqi Microelectronics Co Huawei Technologies Huayu Technology HuaYuan Micro Electronic Huayue Microelectronics Co HUBER+SUHNER Huibei KENTO Electronic Huidu Technology Hukx Sensor Technology Humirel Hurricane Tech. Co HW group s.r.o HYCON Technology Corp. Hynix Semiconductor Hyundai Semiconductor IC Plus Corp ICE Components, Inc. iC-Haus GmbH Icom Inc ICP DAS CO ID Innovations ID TECH IDEC Corporation IEI Integration Ignion Iintelligent Motion Systems IK Semiconductor ILSI America LLC IMP, Inc Inchange Semiconductor Industrial Fiber Optics, Inc Industrial Technology Research Institute Infineon Technologies Initio Corporation INJOINIC TECHNOLOGY Innolux Corporation InnoSenT-Innovative Radar Sensor Technology Innovative Sensor Technology IST Innuovo Magnetics Co Inova Semiconductors InPlay Inc. InPower Semiconductor INTEGRAL JSC Integrated Circuit Solution Integrated Circuit Systems Integrated Crystal Technology Integrated Device Technology Integrated Sensor Technologies Integrated Silicon Solution Intel Corporation InterFET Corp Interlink Electronics International CMOS Technology International Rectifier Intersil Corporation Intronic Semiconductor Intronics Power, Inc InvenSense Inc IQD Frequency Products Ltd IRAN Ironwood Electronics IRXON Electronic Isabellenhütte Heusler GmbH &amp; Co KG Isahaya Electronics Co iSentek Technology Isocom Components Isotek Corp ITE Tech ITT Cannon, LLC ITT Semiconductors Ituner Networks Corp iWatt Inc IXYS Integrated Circuits J.S.T. Mfg. Co JACKSON ELECTRONICS IND. CROP. JAE Electronics JAI Ltd Jamicon Electronics JAVAN JCET Group Co JCI Jewel Hill Electronic Co JHDLCM Electronics Jiangsu Changjiang Electronics Jiangsu Donghai Semiconductor Jiangsu Juguang Jiangsu Runic Technology Co Jiangsu Szdhdtgd Electronics Jiangxi Jia Wei Cheng Electronic Jilin Sino-Microelectronics Co Jinan USR IOT Technology JING LI Power Electronics Jingcheng Electronics Co Jinghan Switch Electronic JMicron Technology Corp JNHuaMao Technology JODO International Johanson Dielectrics Johanson Technology Johnson Electric JPC Company JYE Tech Ltd JYH HSU(JEC) ELECTRONICS Kai Suh Suh Enterprise KSS Kaida Holding Kaihua Electronics Co Kangmu Sheng Electronics Ka-Ro electronics GmbH. KEC Semiconductor Keil Elektronik Keithley Instruments Kelly Controls, LLC KEMET Corporation Key Technology Keysight Technologies Keystone Electronic King Core Electronics Kingbor Technology Kingbright Electronic KingCCTV Technology Kingdatron Electronic Industrial Co Kingsignal Technology Kingstate Electronics Kingston KIOXIA America, Inc Kiwi Instruments Corp Knowles Electronics KOA Speer Electronics Kobiconn Kodenshi Corp Kohshin Electric Corporation KONE Elevator Kontron S&amp;T KT Micro Inc Kunshan Sino Silicon Technology KUOYUH W.L. Enterprise Co Kutai Electronics Kycon, Inc Kyocera Corporation Ladder Electronics Co Laird Performance Materials. Laird Technologies Laser Components Lattice Semiconductor LawMate International L-com, Inc LD-PD Inc. Leadtrend Technology Corp LEAP Electronic Legerity, Inc Lelon Electronics Corp LEM Components LEMO Lenovo LENZE Lesfuse Electric Co Leshan Radio Co LG Semiconductor LG.Philips Displays Lianchao Future Technology Lighting Integration System Ligitek Electronics Co Lime Microsystems Lineage Power Private Limited Linear Systems Linear Technology Linfinity Microelectronics Link-PP Int'l Technology LinkSmart LINP OMTER International Linx Technologies Lision Technology LITE-ON Semiconductor Littelfuse Inc Lixin Electromagnetic Clutch LIZE Electronic Technology LND, INC LOETRONIC LOGIC Devices Incorporated Longtech Optics Co Longview Technologies Co Lovid International Electronic Low Power Radio Solutions Ltd LOZEN TECHNOLOGY LS ELECTRIC LS Mtron Ltd LSI Computer Systems LTKCHIP LTN Servotechnik GmbH Lucent Technologies LUCKFOX Technology Lucky Light Electronic Luguang Electronic Technology Lumberg Holding Lumentum Operations LLC. Lumex Inc Lumileds Luminus, Inc. Lumissil Microsystems Luna Optoelectronics Lutron Electronic Enterprise Co Lyontek Inc M.S. Kennedy Corp M+R Multitronik GmbH MACOM Technology Macroblock, Inc Macronix International MacTek Corp MagnaChip Semiconductor Magnetics MagnTek Microelectronics Magtek Technology Inc Manorshi Electronics Marktech Optoelectronics, Inc Marlow Industries, Inc Marquardt Switches, Inc Marvell International Matsushita Electric Max Echo Technology Corp MaxBotix Inc Maxic Technology Corporation Maxim Integrated MaxLinear Inc Maxon motor Maxwell Technologies Mayloon Electronic Company MCS Logic Inc Mcuzone International MEAN WELL Enterprises Co Measurement Specialties Mechanic MediaTek Inc Megatek Melexis Technologies Memory Protection Devices MEMSIC, Inc Mentor GmbH Mercury Electronic Meritek Electronics Corporation Mersen EP Metalink Broadband Meticom GmbH. METRODYNE MICROSYSTEM CORP. MIC Electronic Micrel, Inc Micro Commercial Components Micro Crystal AG Micro Electronics Micro Linear Micro One Electronics Micro Power Systems MICRO SENSOR CO;LTD Microchip Technology Microdiode Semiconductor Micrometals, Inc Micron Technology Micronet Communication Microsemi Corporation Microtech Technology Co Ltd Microtherm Sentronic GmbH Microtips Technology Midori Precisions MikroElektronika MikroElektronika d.o.o MikroTik Mill-Max Mfg Milnec Interconnect Systems MindMotion Microelectronics Co. Mingtek Electronics Ltd Mini-Circuits Minilogic Device Corporation Ltd Minmax Technology Minsoo Electronic Co MiTAC Computing Technology Mitel Semiconductor Mitsubishi Electric Mitsubishi Rayon Co Mitsumi Electric Co Mixed Signal Integration Mixic Electronics MKMX America LLC MMI Semiconductors MOAI electronics co Mobicon Electronic Component Modulestek Inc MOKO TECHNOLOGY LTD. Molex Electronic Monitor Enterprises Inc Monolithic Power Systems Morethanall Co Morningstar Corporation MORNSUN Science &amp; Technology Mosdesign Semiconductor Corp Mosel Vitelic Co MOSPEC Semiconductor MOS-TECH Semiconductor Mostek MOTIEN Technology Motorola Mstar Semiconductor M-Systems Inc Multicomp Multi-Inno Technology Multi-Tech Systems Inc Murata Manufacturing Co MVSILICON MYIR Tech Myrra SAS Naina Semiconductor Limited. Nanjing Haichuan Electronic Nanjing Ouzhuo Tech Nanjing Qinheng Microelectronics Nanjing Shiheng Elec NanJing Top Power ASIC Nanjing Up Electronic Technology Nanjing Wotian Technology Co Nanjing Zeming Electronic Co Nanya Technology Co National Instruments National Semiconductor NDK America Inc NEC Electronics Nell Semiconductor Neltron Industrial Nemoto Sensor Engineering NeuroSky, Inc. Neutrik New Jersey Semiconductor NewAE Technology Inc. Newava Technology Inc. Newhaven Display Newport Corporation NewTec Display Co NexFlash Technologies, Inc Nexperia USA Inc Nextchip Nextion NIC Components Corp. Nichia Corporation Nichicon Corporation Nidec Copal Electronics NIDEC SERVO CORPORATION. Nihon Dempa Kogyo Nihon Inter Electronics NIKO Semiconductor Ningbo East Electronics Ningbo ForwardRelayCorporationLTD Ningbo Gosun Technology Co Ningbo Huaguan Electronics Ningbo KLS Electronic Co Ningbo MAX Electronic Technology Co., Ltd Ningbo MKX Electronic Technology Ningbo Rel Electric Co., Ltd. Ningbo Songle Relay Ningbo Tianbo Ganglian Electronics Ninigi Nippon Chemi-Con Nippon Pulse America, Inc Nisshinbo Micro Devices Inc NJR Corporation NKK Switches NMB Technologies Non-Brand Norcomp Inc Nordic Semiconductor Noritake Itron Co Novacap Novatek Microelectronics NTE Electronics NUAND LLC. Nuvoton Technology NVE Corporation Nvidia NVS Navigation Technologies NXP Semiconductors NYS Resistor O2Micro OCIC co Octavo Systems LLC Ogemray Technology Co Ohmite OKI Semiconductor Ole Wolff Electronics Inc Olimex OmniVision Technologies Omron Electronics Omten Electronics ON Semiconductor ON Semiconductor CHINA On Shore Technology On-Bright Electronics OPTEK Technology Inc OPTi Inc Opticon Inc Opto 22 Opto Diode Corp Opto Electronics Co,. LTD OPTOLAB Microsystems Orient Display Oriental Semiconductor Orion Orion Display Technology Co OSI Optoelectronics OSRAM Opto Semiconductors OTAX Corporation Other Oupiin Enterprise Co OWON Technology Inc P&amp;E Microcomputer Systems Pacific Silicon Sensor Panasonic Corporation Panavision Imaging LLC Pancon Corporation PandaBoard PANJIT International Inc Para Light Electronics P-DUKE Technology Co PEAK Electronics GmbH PEAK-System Technik Penny &amp; Giles Peregrine Semiconductor Pericom Semiconductor Corp PerkinElmer Inc Phidgets, Inc Philips Semiconductor Phison Electronics Phoenix Contact Pickering Electronics Ltd PICO Electronics Pico Technology Piher Sensors &amp; Controls SA Pingjing Semi Technology PIR Sensor Co PixArt Imaging Inc Planar Systems, Inc PLX Technology PMC-Sierra, Inc PNI Sensor Corporation POCO Magnetic Polyfet RF Devices Polytronics Technology Pomona Electronics Power Integrations Power Mate Technology Power Systems GmbH Power-Changer Electronic Co Powerex Inc PowerPlaza Powersem GmbH Powertip Technology Preci-Dip SA Precision Monolithics, Inc PREMA Semiconductor GmbH Premier Magnetics PRETEC/C-One Technology Corp. Princeton Technology Proant AB Profichip GmbH Prokit's Industries Prolific Technology Inc Promax-Johnton Semiconductor Pro-Signal ProTek Devices Pro-Wave Electronic PRT PUI Audio Pulse Electronics Qimei Optical &amp; Electric Qingdao Mefine Electronics Qingxian Zeming Langxi Electronic Devices Co Qingyuan Tesla Electronic Technology Qorvo QT Brightek (QTB) QT Optoelectronics Qualcomm Atheros, Inc Quality Semiconductor Qualtek Electronics Quarton inc Quasar Electronics Limited Quectel Wireless Solutions QuickLogic Corporation QX Micro Devices Radiall Radxa Computer Rafael Microelectronics RAFI GmbH &amp; Co RAiO TECHNOLOGY INC RAKwireless Technology Limited. RALEC Ltd Ralink Technology Raltron Electronics Corporation Ramtron International Rapid Electronics Ltd Raspberry Pi Raycom Co Raytac Corporation. Raytheon RCA Corporation Ready Made RC LLC Realtek Semiconductor RECOM Power GmbH Rectron Semiconductor Reichelt elektronik GmbH &amp; Co. KG RELPOL S.A Renata SA Renesas Technology Renhotec Group Ltd Reomax Electronics Reyed Electronics Co RF Digital Corporation. RF Micro Devices RF Solutions Ltd RFaxis, Inc RFHIC Corporation RFM Integrated Device, Inc. RFT Mikroelektronik Rhombus Industries Inc Richtek Technology Co RichWave Technology Ricoh Electronic Devices Riedon RIGOL Ring&amp;tone Electronic Technology Riverdi RLS Merilna tehnika d.o.o ROBOTIS Co Rockwell Rogers Corporation ROHM Semiconductor Roithner Lasertechnik GmbH Rongtech Industry Royal Electronic Factory Co RS Components Ltd RTD Embedded Technologies Rubycon RYCHIP Semiconductor s.m.a.e. GmbH Saft Groupe S.A Sagami Electronics Saia-Burgess Switches Sakae Tsushin Kogyo Saleae, Inc Salecom Electronics Same Sky SamHop Microelectronics Samsung Electronics Samtec Samwha Capacitor Samwin Electronic Technology Samyoung S &amp; C Co SANCO Electronics Co SanDisk Sanhe Enclosure Sanjiaozhou Electrical Technology Sanken Electric SanRex Corporation Sanyo Denki Sanyo Electric Savantic Electronic Sawnics Inc Schaffner Group Schott AG Schrack Technik GmbH Schurter Inc Sciosense B.V. SCTF Electronics Seagate Technology LLC Seaparks Machinery-Electronics Seaward Electronics SeCoS Corporation SEED International Ltd Seeed Technology SEEQ Technology Segger Microcontroller Systems Seiko Instruments Inc Seiko NPC Corporation Semiconductor Circuits, Inc SemiHow Semikron Semiment Technologies Semi-Powerex Corp. SEMITEC Corporation SemiWell Semiconductor Semtech Corporation Semtech Electronics Senba Sensing Technology Co Sendo Sensor Sensata Technologies Sensirion Sentry Manufacturing Inc SEP Electronic Corp Servotecnica SpA SERVO-TEK PRODUCTS COMPANY, INC. SG Micro Corp SGX Sensortech Shaanxi Fullstar Electronics Co Shaanxi Qunli Electric Shaanxi Reactor Microelectronics Shandong Jingdao Microelectronics Shanghai AVIC Optoelectronics Shanghai Belling Co,Ltd Shanghai Consonance Electronics Shanghai Fengxin Electronic Technology Shanghai Fudan Microelectronics Shanghai Gotop Technology Shanghai High-Flying Electronics Shanghai Houde Photo-electric Shanghai Mixinno Microelectronics Co Shanghai Natlinear Electronics Shanghai Xinlong Semiconductor Shanghai Zhichuan Electronic Tech SHARP Corporation Sheng Jay Automation Techno Shenyang Guangcheng Technology Co., Ltd Shenyang KingStar Automation ShenZhen AI-thinker CO Shenzhen AnBoShi Electronic Shenzhen Asenware Test Shenzhen Baishan Mechatronics Shenzhen Biosled Technology Shenzhen Bolutek Technology Shenzhen Chipsea Technologies ShenZhen ChipSourceTek Technology Shenzhen ExSAF Electronics Co Shenzhen Genesis-Systech ShenZhen Gerbole Shenzhen Getech Co Shenzhen GUANGSHIMEI Electronic Shenzhen Hanxia Electronics Shenzhen Haolin Electronics Shenzhen Heliwei Technology Shenzhen honglifa Electronics Co Shenzhen HongyeX Electronics Co ShenZhen HuaXinAn Electronics Co.,Ltd Shenzhen Injoinic Technology Co. Shenzhen Jin Yu Semiconductor Co ShenZhen JINCI Technology Shenzhen Jinrui Electronic Material Co Shenzhen JMRTH Co Shenzhen Kaiyuexiang Electronics Co Shenzhen LFN Technology Co Shenzhen Lodestar S.T Co Shenzhen Lumen Electronics Shenzhen Magnetic Technology Shenzhen MilkV Technology Shenzhen Milliohm Electronics Shenzhen Minewsemi Co., Ltd Shenzhen Nsiway Tech Shenzhen Ou Chuangxin Semiconductor ShenZhen Qi Dian Shi Dai Technology Shenzhen Ruichips Semiconductor Shenzhen Ruilongyuan Electronics Shenzhen Shiji Lighting Shenzhen SI Semiconductors Shenzhen SLKOR Micro Semicon Co Shenzhen Sunmoon Microelectronics Shenzhen Suosemi Tech Shenzhen TongYiFang Optoelectronic Technology CO,Ltd Shenzhen Topmay Electronic Shenzhen TPOWER Semiconductor Shenzhen Universal Micro-Electronics Shenzhen USBR Precision Hardware Electronics Shenzhen Weidy Industrial Development Co., Ltd. Shenzhen Xinbole Electronics Co. Shenzhen Xptek Technology Shenzhen Xunlong Shenzhen Yangxing Technology Co. SHENZHEN YeZhan Electronics Shenzhen Yiwei Technology Shenzhen ZVELL Electronics Shindengen Electric Shin-Etsu Chemical Co SHINYEI Technology SHOEI SIBA GmbH Sichuan huafeng enterprise group SICK, Inc. Siemens Semiconductor Group Si-En Technology SiFirst Technology SiGe Semiconductor Sigma Microelectronics Signetics Silego Technology Silergy Corp Silicon Image Silicon Integrated Systems Silicon Laboratories Silicon Microstructures, Inc. Silicon Motion, Inc Silicon Sensing Systems Limited Silicon Standard Corp Silicon Storage Technology Silicon Systems Inc Silicon Touch Technology Silvan Chip Electronics Silver Telecom Ltd SilverStone Technology SIMCom Wireless Solutions SIMTEK Electronic Components Sinda Photoelectricity Technology SINGULAR TECHNOLOGY CO., LTD. Sinomags Technologies Co Sinopower Semiconductor Sipex Corporation Sirectifier Semiconductors SiTime Corporation Sivago Semiconductor Co SIWARD Crystal Technology Siyang Microelectronics Sizto Tech Corp SKYLAB M&amp;C Technology Skyworks Solutions, Inc SL Power Electronics Corp. SMAR Smartec BV SMC Diode Solutions Co. Smiths Interconnect. SMSC Corporation Soberton Inc Softing Automotive Electronics Sola/Hevi-Duty Sola-IC Solarflex SA Soldex Solid State Scientific SOLIDIC Solitronics Engineering Limited SOL-LED Lighting Co Solomon Systech Song Chuan Song Huei Electric Sonix Technology Sony Corporation Soundwell Electronic South African Micro-Electronic Systems Spansion inc SparkFun Electronics SPEC Sensors LLC Spectra Symbol Corp. Spectrum Digital Incorporated Speed Tech Corp Spin Semiconductor Sprague Semiconductors SPX Flow Technology ST Engineering Stackpole Electronics Standex-Meder Electronics Stannol GmbH Stanson Technology StarChips Technology StarPower Semiconductor Ltd. Startek Electronic Technology STATEK CORPORATION Stäubli International AG. STCmicro Technology Co Stewart Connector STMicroelectronics Stocko Stork Solutions Ltd. Sullins Connector Solutions SUMIDA Corporation Sun Hydraulics Corporation Sun Microelectronics SunLED SUNLORD Sunltech Tech SUNMATE Electronic Sunonwealth Electric Machine Sunplus Technology Sunrise Electronics Suntan Technology Company Suntsu Electronics, Inc. SUNYUAN Technology Supertex Inc Susumu International Suzhou Innoson Technology Suzhou NOVOSENSE Microelectronics Co., Ltd Suzhou Silikron Semiconductor Corp Switchcraft Inc. Switec SYNC Power Crop SyncMOS Technologies Synoxo International System General Corp Tadiran Batteries TAG Semiconductors TA-I Technology TAIKO-NET Tai-Saw Technology Tai-Tech Advanced Electronics Taitien Electronics Taitron Components, Inc Taiwan Alpha Electronic Co Taiwan Semiconductor Taiyo Electric Co Taiyo Yuden Tak Cheong Electronics Talema Group, LLC Tamagawa seiki Co Tamron Tamura Corporation TANCAP Technology Taoglas Limited TDK Corporation (EPCOS) TDK-Lambda Corporation TDK-Micronas GmbH TE Connectivity Team Source Display tech.co,ltd. Techcode Semiconductor Techpoint Inc Techspray/Plato-EMX Enterprises Limited Techstar Electronics TechToys Company TelCom Semiconductor Telcon Ltd Telechips Inc Teledyne Technologies TELEFUNKEN Elektroakustik Telegesis Ltd Telit TEMIC Semiconductor Terawins, Inc Teridian Semiconductor TESLA Testo SE &amp; Co Texas Advanced Optoelectronic Solutions Texas Instruments THAT Corporation Thegioiic Corporation Thermonamic Electronics(Jiangxi) Corp THine Electronics, Inc Thinki Semiconductor Thinking Electronic THOMSON Inc THORLABS Thousand Hundred Industrial Thunder Precision Resistor TIANMA Titan Micro TLC Electronics TNI-U TOOL Token Electronics Industry Tokmas Semiconductor TOKO, Inc Tontek Design Technology Top-arm Topro Technology Topway Technology Torex Semiconductor Toshiba Corporation touchSEMI TOYO LED ELECTRONICS LIMITED. TOYODA TR Electronic Nordic AB. Traco Electronic AG Transcom, Inc Transko Electronics, Inc. TRENDnet, Inc Trenz Electronic Triad Magnetics Trident Microsystems Trimble Inc TRINAMIC Motion Control TRinno Technology Co Tripath Technology TriQuint Semiconductor Truly Semiconductors TRW Inc TT Electronics TTM Technologies, Inc. TXC Corporation UBIQ Semiconductor Ubiquiti Inc u-blox UCE Ultrasonic Co UDF Semiconductor Ultisensor Electronics UNI SEMICONDUCTOR LIMITED Unicorn Microelectronics Corporation Unictron Technologies Corporation. Union Semiconductor Uniroyal Electronics Industry Co Unisonic Technologies Unitra Cemi Uni-Trend Technology Co Unitrode Corporation Universal Microelectronics UPI Semiconductor Corp US Digital US Micro Products. Usha India Ltd Ushio Opto Semiconductors UTRON Technology, Inc Vacuumschmelze GmbH VADEM LTD Vango Technologies, Inc Varitronix Limited VARTA AG Vatronics Technologies Ltd VBsemi Electronics Co. Ltd V-Chip Microsystems VectorNav Vectron International Vehicles instrumentation Device Venkel Ltd VIA Technologies Vicor Corporation Vigortronix Ltd. Vincotech Vishay Visual communication company Vitesse Semiconductor Vivesea VLSI Solution Vweb Corporation W. L. Gore &amp; Associates, Inc WAGO Kontakttechnik GmbH Wakefield Thermal, Inc. Walsin Technology Corporation Walter Electronic Co WanTcom, Inc Wavecom Waveshare Electronics Wavespectrum Laser Inc Wavetronics Technologies WAYTRONIC ELECTRONIC CO.LTD WeEn Semiconductors Weidmüller Interface GmbH Weipu connector Weltrend Semiconductor WENSHING Electronics Western Digital Corporation Willas Electronic Corp WIMA Winbond Electronics</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.1u</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C11,C13</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop?searchfilter=4184#dtl/7589</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>محصولات خانه دسته‌بندی‌ها فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه عبارت 4184 جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش برند 1666 3M Dynapro 3M Interconnect 3PEAK Incorporated 4D Systems Pty Ltd A Power microelectronics AAEON Technology Aavid Thermalloy ABC Taiwan Electronics ABLIC Inc Abracon Corporation Acam-Messelectronic Acrian, Inc Actel Corporation Active-Semi, Inc Actox Corporation. AD Semiconductor Confidential Adafruit Industries LLC Adam Technologies, Inc ADDA Corp ADDtek Corp Adesto Technologies ADMtek Inc Advanced Acoustic Technology Corp. Advanced Analog Technology Advanced Analogic Technologies Advanced Card Systems Advanced Ceramic X Corp Advanced Linear Devices Inc Advanced Monolithic Systems Advanced Photonix, Inc Advanced Power Electronics Corp Advanced Power Technology Advanced Semiconductor Advantech Corp Advantech Equipment Corporation Aegis Electronic Group AEL Crystals Limited AEM, Inc Aerosemi Technology Co Afa Technologies Inc AG Electrical Technology Agere Systems Agilent Technologies AGM Semiconductor AIC tech Inc. Aimtec Aimtron Corporation Airoha Technology Corp AIRWAVE Technologies Inc AiSHi Capacitors Aixin Opto-Electrical Technology Albright International Ltd Alcatel Microelectronics Alcor Micro Corp Alex Connector Co Ltd Alfa Electronics Algocraft Srl. ALi Corporation Alinx Electronic Technology All Sensors Corporation Allegro Microsystems Alliance Memory Allied Vision, Inc. Allwinner Technology Almita Co. Ltd Alpha &amp; Omega Semiconductor Alpha Micro Components Alpha Semiconductor Alpha Wire Alphasense Ltd, Sensor Technology Alps Electric Co Altera Corporation Amazing Electronic Co Amazing Microelectronic Corp AMD American Microsemiconductors American Microsystems Inc American Power Management American Technical Ceramics Corp American Zettler, Inc. Ametherm, Inc AMI Semiconductor AMIC Technology Corp Amidon Associates, Inc Amlogic Inc. Amotech Corp AMPAK Technology Inc Amphenol Advanced Sensors Amphenol Corporation Amphenol FCI Amphenol RF Ampleon USA Inc ams AG Anachip Corp ANADIGICS Anadigm, Inc Analog Devices Analog Integrations Corporation Analog Microelectronics Analog Power Analogix Semiconductor Inc Anaren, Inc Ancol Electronics Co Andigilog, Inc ANENG Anhui FOSAN Semiconductor Anhui Vico Technologes Co Anovay Technologies Limited ANPEC Electronics Corp Ante Intelligent Company Limited AP Memory Technology. APC Propellers APEM Inc Apex Material Technology Apex Precision Power API Delevan Inc API Technologies Aplus Integrated Circuits Inc APMKorea Apogee Technology, Inc Applent Instruments Applied Micro Circuits Co AppoTech Ltd APT Electronics Co., Ltd. Aptek Technologies ArchNet Technology Arcol UK Ltd Arduino Arduino Nicla Voice. Arima Lasers Corporation Aristotle Enterprises Inc ARTCHIP Semiconductor Artesyn Embedded Technologies AS ENERGI Asahi Kasei Microdevices ASAHI Solder Asia Vital Components Asiliant Technologies ASIX Electronics Corp AsLic Microelectronics Corporation ASMedia Technology Inc. Associated Opto-Electronics Astec Semiconductor. Astrodyne TDI Corporation. ATE Electronics s.r.l Atech Technology Co ATEN International Co Atheros Communications, Inc ATI Technologies Inc Atlas Scientific LLC. Attend Technology Inc AU Optronics Corp Audiowell Electronics Co Auk Contractors Co AUK Semiconductor AUO Corporation AUREL S.P.A Austar Technology AuthenTec, Inc Autonics Corporation Avago Technologies AVANTEK INC. AverLogic Technologies, Inc AVerMedia Technologies Avia Semiconductor Avnet, Inc AVX Corporation AXElite Technology Co Axiomtek Axis Communications AZ Displays, Inc Azoteq Ltd BAFO Technologies Corp Bahar Enclosure Baumer International BBT-China Inc BCD Semiconductor Beckhoff Automation Beijing Boshida Beijing HRH Information Co Beijing Ultrasonic Beijing Yihongtai Technology Beijing Zhongxun Sifang Science &amp; Technology Beken Corporation Bel Fuse Inc Bel Power Solutions Inc Belden Inc Bellnix Bencent Tzeng Ind. Co. Ltd Betlux Beyond Innovation Technology BI Technologies Bicker Elektronik GmbH Billionton Systems Inc Bird Technologies Bi-Sonic Technology Bivar, Inc Blackhawk BLOCK Inc Bluegiga Technologies BOLYMIN,INC BONGSHIN LOADCELL CO. Bookly Micro Electronic Bosch Security Systems Inc Bosch Semiconductors Bosch Sensortec Bothhand USA Boundary Devices Bourns Inc Bowin Microelectronics Brainboxes Limited BRIGHT LED ELECTRONICS CORP. Bright Power Semiconductor BrightKing Inc Brilliance Semiconductor, Inc Broadchip Technology Broadcom Limited BroadLight Inc Brooktree Corporation Burr-Brown Corporation BYD Microelectronics Co., Ltd. C&amp;D Technologies C&amp;K Components Caddock Electronics Inc California Eastern Laboratories California Micro Devices Calogic LLC Cambridge Integrated Circuits Cambridge Silicon Ra dio Limited Camille Bauer Ltd Catalyst Semiconductor Celduc relais CellWise Microelectronics Co Cenker Enterprise Ltd Centenary Materials Co CeNtRa Science Corp Central Components Manufacturing Central Georgia Generator Central Semiconductor CEVA Technologies CFSensor Challenge Electronics Champion Microelectronic Changzhou changjie Technology Co Changzhou Cre-sound Electronics Changzhou DRM Changzhou Esuntech Co Changzhou Kennon ELectronics Changzhou TDA Electronic Changzhou Yuanwang Fluid Technology Chaozhou Three-circle (Group) Co chargebyte GmbH. Chengdu Ebyte Electronic Technology Chengdu Guosheng Technology Chengdu Xincheng Huachuang Electronic ChenMoun Electronic ChenYang Technologies Cheuk Yui Innovation Co Chi Mei Optoelectronics Chieful Science ＆ Technology Chilisin Electronics Co China Base Electronic Technology China ECU Tools Centre China Resources Microelectronics China Software Industry Association Chinfa Electronics Chingis Technology Corp Chino-Excel Technology Chipanalog Incorporated ChipLink Tech Chiplus Semiconductor ChipON Chipower Electronics CHIPS Technology Chipstar Microelectronics CHK Electronics Ltd Chogori USA Chongqing Shengpu Electronics Chrontel, Inc Chunghwa Picture Tubes Churod Electronics Chyao Shiunn Electronic Cincon Electronics Cinetech Ind Cirrus Logic Inc Cisco Systems CIT Relay &amp; Switch Citizen Finedevice Co Cixi AnXon Electronic Cixi Dafa precise Linker Co CiXi KaiFeng Electronics Co Cixi Kefa Electronics Cixi Max Electronics Co.,Ltd Clare, Inc Cliff Electronic Components Limited Cmedia Electronics Inc CML Microsystems Coil Master Co Coil Winding Coilcraft Inc Coiltronics (Eaton) Comchip Technology Commodore Semiconductor Comtec Crystals comtech aha corporation CONEC Elektronische Bauelemente GmbH Conesys,Inc. Conexant Systems, Inc Connfly Electronic Co Connor-Winfield Conquer Electronic Continental Device India Controlair Inc Conversion Devices, Inc Cooper Bussmann Coretek Opto Corporation. Cornell Dubilier Electronics Cortina Systems, Inc Cosel Co Ltd COSINE Nanoelectronics Coto Technology CR Powtech Co Cree, Inc Crydom Inc Crystal Semiconductor Corporation Crystalfontz Crystek Corporation CSCONN PRECISE ELECTRONICS CO.,LTD CT Micro International Co CTS Corporation CUI Inc CVI Laser, LLC CW Industries Cyntec Co Cypress Semiconductor Cyrustek Corporation CYStech Electronics Corp. CYT Opto-Electronic Technology Dachang Electronics Daewoo Semiconductor Daier Electron Co Dailywell Electronics Daishinku Corp Daito Communication Apparatus Daiyo Electronics Dallas Semiconductor DANFOSS Daniels Manufacturing Co Data Device Corporation Davicom Semiconductor Davies Molding, LLC DB Lectro Inc DB Unlimited DC Components Co Dean Technology DECA SwitchLab Inc Decawave Ltd Dechang Electronic Deep Sea Electronics DEGSON Electronics Co Dell Inspiron Delta Electronics DeMint Electronics DENSO Destiny Technology Corp Detaik Technology Co Deva Electronic Controls Limited. Devantech Device Engineering Inc Dexter Magnetic Technologies DFRobot. Dialight Electronics Company Dialog Semiconductor Dielectric Laboratories Digi International Digilent, Inc Digital Voice Systems Digitrax, Inc Digitron Semiconductors Dinkle International Co. Ltd DIN-TEK Microelectronics Diodes Incorporated Diotec Semiconductor Diptronics Manufacturing Inc Display Solution AG DISPLAY VISIONS GmbH 2022. DMB Technology DOESTEK Co DOINGTER Semiconductor Domintech Co Don Connex Electronics DONG IL TECHNOLOGY LTD. Dongguan CHENGXING Electronic Co Dongguan City Wasi Electronic Technology Dongguan Cosson DongGuan HeLing Electronics Dongguan Lanbo Electronics Technology CO Dongguan Yuandi Electronics Dongguan Yuanze Electric Co.,Ltd Dongguan Yuxi Precise Connector Co., Ltd Dongke semiconductor Anhui Co., Ltd Donguan Keyouda Electronic Dosilicon Co DTK electronics Dualsky Models Co Duoxing Electronics Co Duty-Cycle Semiconductor Dynamic Technologies (DTCC) Dynex Semiconductor Ltd, E &amp; E Magnetic Products Limited EAST Semiconductor East Texas Integrated Circuits Eastrising Technology Co Eastsensor Technology Easy IoT Eaton’s Bussmann Ebm-papst inc Echelon Corporation Ecliptek Corporation ECOFIT &amp; ETRI ECS, Inc International EDAC EECO Switch E-Elements Technology Co Efficient Power Conversion Co EG Microelectronics Corp EIC Semiconductor Elan Microelectronics Co Elantec, Inc Electrolube Electronic Alliance Electronic Assembly Electronic Devices Inc Electroustic Ltd Eledis Element14 ELESTA GmbH Elite Semiconductor Memory Eljen Technology Elm Electronics ELM Technology Co Elmos Semiconductor AG ELNA Company Elpida Memory, Inc EM Microelectronic-Marin EMAD Embedded Artists Embest Technology Emerson Encitech Endress+Hauser Management ENE Technology Enplas Corporation Enrwey Co Ltd Eon Silicon Solution E-peas Semiconductors Epitex Inc Epoxy Technology Inc EPSON Electronics Ept Inc Ericsson Microelectronics ERNI Electronics ERSA UK LTD Espressif Systems ESS Technologies E-Switch, Inc ET Enterprises Limited E-T-A Circuit Breakers ETA Solutions E-tec Interconnect Ethertronics Inc Etron Technology, Inc EUCHNER GmbH Eupec semiconductor Euroquartz Ltd Eutech Microelectronics Everanalog Everest Semiconductor Everlight Electronics Everspin Technologies Exar Corporation Excel Cell Electronic Excelitas Technologies Excellence Opto, Inc Excelliance MOS Corporation Fagor Electronica Fairchild Semiconductor Fair-Rite Products Corp FANUC Corporation Faraday Technology Fastline Fastrax Ltd FASTRON Faulhaber GmbH FDK Corporation Feature Integration Technology Feei Cherng Enterprise Feeling Technology Feiyi Technology FEMA Electronics Corporation Fenghua Advanced Technology Ferroxcube International FERYSTER Sp. z.o.o Figaro Engineering Inc Finder Relays, Inc Fingerprint Cards First Semiconductor First Sensor FIS Inc Fischer Connectors Fischer Elektronik Fitipower Integrated Technology Force MOS Technology Co Formosa MS Formox Semiconductor Forsentrk Fortior Technology Co Fortune Semiconductor Forward International Electronics FOTEK Controls Fox Electronics Foxconn Technology Fractus S.A Franz Binder GmbH &amp; Co. Free2Move Holding AB. Freescale Semiconductor Fremont Micro Devices Friendcom Technology Develop FriendlyARM Computer Tech FTDI Chip Fuda Hisi Microelectronics Fuji Electric Fujikura Fujitsu Semiconductor Fujitsu-Takamisawa Fulihua Printer Ribbon Co Futaba Corporation Fu-Yao Technology Co Fuzetec Technology Co Fuzhou Rockchip Electronics Co., Ltd GainSpan Corporation GalaxyCore Inc GaNPower International Inc G-Antetech Industrial Garmin Ltd. Gas Sensing Solutions Ltd. Gaston Electronics GC GE Fanuc GEC Plessey Geehy Semiconductor Co General Electronic Devices General Monitors General Semiconductor Generalplus Technology GeneSiC Semiconductor Genesis Microchip Inc Genesys Logic, Inc Genicom Co., Ltd. Gennum Corporation GETE Electronics GigaDevice Semiconductor Global Connector Technology (GCT) Global Mixed-mode Technology GlobespanVirata, Inc GMC Instruments GME Technology, LLC GoChip Electronic Technology GoldStar Semiconductor Gonbes Technology Co Good Display Good Will Instrument Good-Ark Semiconductor Goodix Technology Governors America Co Gpixel Microelectronics Inc Grayhill Inc GreatLEDs Co Greenliant Systems GRUNER AG GSI Technology, Inc Guangdong Hottech Co Guangdong Huaguan Semiconductor Guangdong TIANQIU Electronics Technology Guangzhou Aosong Electronics Guangzhou Xinyue Electronic Guerrilla RF, Inc H&amp;M Semiconductor HABEY Halbleiter aus Frankfurt HALO Electronics Hamamatsu Photonics Hangzhou Grow Technology Co Hangzhou Nationalchip Science Hangzhou Prosper Hangzhou Silan Microelectronics Hannstar Display Corp HanRun Electronics Hanwei Electronics Co Hanyoung Nux Co HAOHAI ELECTRONICS HAOYU Electronics Harris Semiconductor HARTING Technology Harvatek Corporation Harwin Hawyang Semiconductor Hebei International Trading Co HEITEC AG. Hemingruizhi Electronic Henan Hanwei Electronics Co Hengda New Materials Technology HengJiaXing Electronics Co Henkel Corporation HenLv Power Technology Heter Electronics Hewlett-Packard Hexin Technology Highly Electric Hi-Link Electronic Technology Hi-Optel Technology Hirose Electric Hi-Sincerity Microelectronics Hitachi Maxell, Ltd Hitachi Semiconductor HITPOINT Inc Hittite Microwave Hivolt Capacitors Ltd H-JTAG Technology Hokuriku Electric Industry Co Ltd Hokuyo Automatic Co Holt Integrated Circuits Holtek Semiconductor Honeywell International Hong Kong Resistors Manufactory Hongfa Electroacoustic Co HONGHUA ELECTRONIC Hope Microelectronics HORIBA, Ltd. Hosiden Corporation Hosonic Electronic Co Hotchip Technology HTC Korea TAEJIN Technology Huada Connectors Huanor International Huaqi Microelectronics Co Huawei Technologies Huayu Technology HuaYuan Micro Electronic Huayue Microelectronics Co HUBER+SUHNER Huibei KENTO Electronic Huidu Technology Hukx Sensor Technology Humirel Hurricane Tech. Co HW group s.r.o HYCON Technology Corp. Hynix Semiconductor Hyundai Semiconductor IC Plus Corp ICE Components, Inc. iC-Haus GmbH Icom Inc ICP DAS CO ID Innovations ID TECH IDEC Corporation IEI Integration Ignion Iintelligent Motion Systems IK Semiconductor ILSI America LLC IMP, Inc Inchange Semiconductor Industrial Fiber Optics, Inc Industrial Technology Research Institute Infineon Technologies Initio Corporation INJOINIC TECHNOLOGY Innolux Corporation InnoSenT-Innovative Radar Sensor Technology Innovative Sensor Technology IST Innuovo Magnetics Co Inova Semiconductors InPlay Inc. InPower Semiconductor INTEGRAL JSC Integrated Circuit Solution Integrated Circuit Systems Integrated Crystal Technology Integrated Device Technology Integrated Sensor Technologies Integrated Silicon Solution Intel Corporation InterFET Corp Interlink Electronics International CMOS Technology International Rectifier Intersil Corporation Intronic Semiconductor Intronics Power, Inc InvenSense Inc IQD Frequency Products Ltd IRAN Ironwood Electronics IRXON Electronic Isabellenhütte Heusler GmbH &amp; Co KG Isahaya Electronics Co iSentek Technology Isocom Components Isotek Corp ITE Tech ITT Cannon, LLC ITT Semiconductors Ituner Networks Corp iWatt Inc IXYS Integrated Circuits J.S.T. Mfg. Co JACKSON ELECTRONICS IND. CROP. JAE Electronics JAI Ltd Jamicon Electronics JAVAN JCET Group Co JCI Jewel Hill Electronic Co JHDLCM Electronics Jiangsu Changjiang Electronics Jiangsu Donghai Semiconductor Jiangsu Juguang Jiangsu Runic Technology Co Jiangsu Szdhdtgd Electronics Jiangxi Jia Wei Cheng Electronic Jilin Sino-Microelectronics Co Jinan USR IOT Technology JING LI Power Electronics Jingcheng Electronics Co Jinghan Switch Electronic JMicron Technology Corp JNHuaMao Technology JODO International Johanson Dielectrics Johanson Technology Johnson Electric JPC Company JYE Tech Ltd JYH HSU(JEC) ELECTRONICS Kai Suh Suh Enterprise KSS Kaida Holding Kaihua Electronics Co Kangmu Sheng Electronics Ka-Ro electronics GmbH. KEC Semiconductor Keil Elektronik Keithley Instruments Kelly Controls, LLC KEMET Corporation Key Technology Keysight Technologies Keystone Electronic King Core Electronics Kingbor Technology Kingbright Electronic KingCCTV Technology Kingdatron Electronic Industrial Co Kingsignal Technology Kingstate Electronics Kingston KIOXIA America, Inc Kiwi Instruments Corp Knowles Electronics KOA Speer Electronics Kobiconn Kodenshi Corp Kohshin Electric Corporation KONE Elevator Kontron S&amp;T KT Micro Inc Kunshan Sino Silicon Technology KUOYUH W.L. Enterprise Co Kutai Electronics Kycon, Inc Kyocera Corporation Ladder Electronics Co Laird Performance Materials. Laird Technologies Laser Components Lattice Semiconductor LawMate International L-com, Inc LD-PD Inc. Leadtrend Technology Corp LEAP Electronic Legerity, Inc Lelon Electronics Corp LEM Components LEMO Lenovo LENZE Lesfuse Electric Co Leshan Radio Co LG Semiconductor LG.Philips Displays Lianchao Future Technology Lighting Integration System Ligitek Electronics Co Lime Microsystems Lineage Power Private Limited Linear Systems Linear Technology Linfinity Microelectronics Link-PP Int'l Technology LinkSmart LINP OMTER International Linx Technologies Lision Technology LITE-ON Semiconductor Littelfuse Inc Lixin Electromagnetic Clutch LIZE Electronic Technology LND, INC LOETRONIC LOGIC Devices Incorporated Longtech Optics Co Longview Technologies Co Lovid International Electronic Low Power Radio Solutions Ltd LOZEN TECHNOLOGY LS ELECTRIC LS Mtron Ltd LSI Computer Systems LTKCHIP LTN Servotechnik GmbH Lucent Technologies LUCKFOX Technology Lucky Light Electronic Luguang Electronic Technology Lumberg Holding Lumentum Operations LLC. Lumex Inc Lumileds Luminus, Inc. Lumissil Microsystems Luna Optoelectronics Lutron Electronic Enterprise Co Lyontek Inc M.S. Kennedy Corp M+R Multitronik GmbH MACOM Technology Macroblock, Inc Macronix International MacTek Corp MagnaChip Semiconductor Magnetics MagnTek Microelectronics Magtek Technology Inc Manorshi Electronics Marktech Optoelectronics, Inc Marlow Industries, Inc Marquardt Switches, Inc Marvell International Matsushita Electric Max Echo Technology Corp MaxBotix Inc Maxic Technology Corporation Maxim Integrated MaxLinear Inc Maxon motor Maxwell Technologies Mayloon Electronic Company MCS Logic Inc Mcuzone International MEAN WELL Enterprises Co Measurement Specialties Mechanic MediaTek Inc Megatek Melexis Technologies Memory Protection Devices MEMSIC, Inc Mentor GmbH Mercury Electronic Meritek Electronics Corporation Mersen EP Metalink Broadband Meticom GmbH. METRODYNE MICROSYSTEM CORP. MIC Electronic Micrel, Inc Micro Commercial Components Micro Crystal AG Micro Electronics Micro Linear Micro One Electronics Micro Power Systems MICRO SENSOR CO;LTD Microchip Technology Microdiode Semiconductor Micrometals, Inc Micron Technology Micronet Communication Microsemi Corporation Microtech Technology Co Ltd Microtherm Sentronic GmbH Microtips Technology Midori Precisions MikroElektronika MikroElektronika d.o.o MikroTik Mill-Max Mfg Milnec Interconnect Systems MindMotion Microelectronics Co. Mingtek Electronics Ltd Mini-Circuits Minilogic Device Corporation Ltd Minmax Technology Minsoo Electronic Co MiTAC Computing Technology Mitel Semiconductor Mitsubishi Electric Mitsubishi Rayon Co Mitsumi Electric Co Mixed Signal Integration Mixic Electronics MKMX America LLC MMI Semiconductors MOAI electronics co Mobicon Electronic Component Modulestek Inc MOKO TECHNOLOGY LTD. Molex Electronic Monitor Enterprises Inc Monolithic Power Systems Morethanall Co Morningstar Corporation MORNSUN Science &amp; Technology Mosdesign Semiconductor Corp Mosel Vitelic Co MOSPEC Semiconductor MOS-TECH Semiconductor Mostek MOTIEN Technology Motorola Mstar Semiconductor M-Systems Inc Multicomp Multi-Inno Technology Multi-Tech Systems Inc Murata Manufacturing Co MVSILICON MYIR Tech Myrra SAS Naina Semiconductor Limited. Nanjing Haichuan Electronic Nanjing Ouzhuo Tech Nanjing Qinheng Microelectronics Nanjing Shiheng Elec NanJing Top Power ASIC Nanjing Up Electronic Technology Nanjing Wotian Technology Co Nanjing Zeming Electronic Co Nanya Technology Co National Instruments National Semiconductor NDK America Inc NEC Electronics Nell Semiconductor Neltron Industrial Nemoto Sensor Engineering NeuroSky, Inc. Neutrik New Jersey Semiconductor NewAE Technology Inc. Newava Technology Inc. Newhaven Display Newport Corporation NewTec Display Co NexFlash Technologies, Inc Nexperia USA Inc Nextchip Nextion NIC Components Corp. Nichia Corporation Nichicon Corporation Nidec Copal Electronics NIDEC SERVO CORPORATION. Nihon Dempa Kogyo Nihon Inter Electronics NIKO Semiconductor Ningbo East Electronics Ningbo ForwardRelayCorporationLTD Ningbo Gosun Technology Co Ningbo Huaguan Electronics Ningbo KLS Electronic Co Ningbo MAX Electronic Technology Co., Ltd Ningbo MKX Electronic Technology Ningbo Rel Electric Co., Ltd. Ningbo Songle Relay Ningbo Tianbo Ganglian Electronics Ninigi Nippon Chemi-Con Nippon Pulse America, Inc Nisshinbo Micro Devices Inc NJR Corporation NKK Switches NMB Technologies Non-Brand Norcomp Inc Nordic Semiconductor Noritake Itron Co Novacap Novatek Microelectronics NTE Electronics NUAND LLC. Nuvoton Technology NVE Corporation Nvidia NVS Navigation Technologies NXP Semiconductors NYS Resistor O2Micro OCIC co Octavo Systems LLC Ogemray Technology Co Ohmite OKI Semiconductor Ole Wolff Electronics Inc Olimex OmniVision Technologies Omron Electronics Omten Electronics ON Semiconductor ON Semiconductor CHINA On Shore Technology On-Bright Electronics OPTEK Technology Inc OPTi Inc Opticon Inc Opto 22 Opto Diode Corp Opto Electronics Co,. LTD OPTOLAB Microsystems Orient Display Oriental Semiconductor Orion Orion Display Technology Co OSI Optoelectronics OSRAM Opto Semiconductors OTAX Corporation Other Oupiin Enterprise Co OWON Technology Inc P&amp;E Microcomputer Systems Pacific Silicon Sensor Panasonic Corporation Panavision Imaging LLC Pancon Corporation PandaBoard PANJIT International Inc Para Light Electronics P-DUKE Technology Co PEAK Electronics GmbH PEAK-System Technik Penny &amp; Giles Peregrine Semiconductor Pericom Semiconductor Corp PerkinElmer Inc Phidgets, Inc Philips Semiconductor Phison Electronics Phoenix Contact Pickering Electronics Ltd PICO Electronics Pico Technology Piher Sensors &amp; Controls SA Pingjing Semi Technology PIR Sensor Co PixArt Imaging Inc Planar Systems, Inc PLX Technology PMC-Sierra, Inc PNI Sensor Corporation POCO Magnetic Polyfet RF Devices Polytronics Technology Pomona Electronics Power Integrations Power Mate Technology Power Systems GmbH Power-Changer Electronic Co Powerex Inc PowerPlaza Powersem GmbH Powertip Technology Preci-Dip SA Precision Monolithics, Inc PREMA Semiconductor GmbH Premier Magnetics PRETEC/C-One Technology Corp. Princeton Technology Proant AB Profichip GmbH Prokit's Industries Prolific Technology Inc Promax-Johnton Semiconductor Pro-Signal ProTek Devices Pro-Wave Electronic PRT PUI Audio Pulse Electronics Qimei Optical &amp; Electric Qingdao Mefine Electronics Qingxian Zeming Langxi Electronic Devices Co Qingyuan Tesla Electronic Technology Qorvo QT Brightek (QTB) QT Optoelectronics Qualcomm Atheros, Inc Quality Semiconductor Qualtek Electronics Quarton inc Quasar Electronics Limited Quectel Wireless Solutions QuickLogic Corporation QX Micro Devices Radiall Radxa Computer Rafael Microelectronics RAFI GmbH &amp; Co RAiO TECHNOLOGY INC RAKwireless Technology Limited. RALEC Ltd Ralink Technology Raltron Electronics Corporation Ramtron International Rapid Electronics Ltd Raspberry Pi Raycom Co Raytac Corporation. Raytheon RCA Corporation Ready Made RC LLC Realtek Semiconductor RECOM Power GmbH Rectron Semiconductor Reichelt elektronik GmbH &amp; Co. KG RELPOL S.A Renata SA Renesas Technology Renhotec Group Ltd Reomax Electronics Reyed Electronics Co RF Digital Corporation. RF Micro Devices RF Solutions Ltd RFaxis, Inc RFHIC Corporation RFM Integrated Device, Inc. RFT Mikroelektronik Rhombus Industries Inc Richtek Technology Co RichWave Technology Ricoh Electronic Devices Riedon RIGOL Ring&amp;tone Electronic Technology Riverdi RLS Merilna tehnika d.o.o ROBOTIS Co Rockwell Rogers Corporation ROHM Semiconductor Roithner Lasertechnik GmbH Rongtech Industry Royal Electronic Factory Co RS Components Ltd RTD Embedded Technologies Rubycon RYCHIP Semiconductor s.m.a.e. GmbH Saft Groupe S.A Sagami Electronics Saia-Burgess Switches Sakae Tsushin Kogyo Saleae, Inc Salecom Electronics Same Sky SamHop Microelectronics Samsung Electronics Samtec Samwha Capacitor Samwin Electronic Technology Samyoung S &amp; C Co SANCO Electronics Co SanDisk Sanhe Enclosure Sanjiaozhou Electrical Technology Sanken Electric SanRex Corporation Sanyo Denki Sanyo Electric Savantic Electronic Sawnics Inc Schaffner Group Schott AG Schrack Technik GmbH Schurter Inc Sciosense B.V. SCTF Electronics Seagate Technology LLC Seaparks Machinery-Electronics Seaward Electronics SeCoS Corporation SEED International Ltd Seeed Technology SEEQ Technology Segger Microcontroller Systems Seiko Instruments Inc Seiko NPC Corporation Semiconductor Circuits, Inc SemiHow Semikron Semiment Technologies Semi-Powerex Corp. SEMITEC Corporation SemiWell Semiconductor Semtech Corporation Semtech Electronics Senba Sensing Technology Co Sendo Sensor Sensata Technologies Sensirion Sentry Manufacturing Inc SEP Electronic Corp Servotecnica SpA SERVO-TEK PRODUCTS COMPANY, INC. SG Micro Corp SGX Sensortech Shaanxi Fullstar Electronics Co Shaanxi Qunli Electric Shaanxi Reactor Microelectronics Shandong Jingdao Microelectronics Shanghai AVIC Optoelectronics Shanghai Belling Co,Ltd Shanghai Consonance Electronics Shanghai Fengxin Electronic Technology Shanghai Fudan Microelectronics Shanghai Gotop Technology Shanghai High-Flying Electronics Shanghai Houde Photo-electric Shanghai Mixinno Microelectronics Co Shanghai Natlinear Electronics Shanghai Xinlong Semiconductor Shanghai Zhichuan Electronic Tech SHARP Corporation Sheng Jay Automation Techno Shenyang Guangcheng Technology Co., Ltd Shenyang KingStar Automation ShenZhen AI-thinker CO Shenzhen AnBoShi Electronic Shenzhen Asenware Test Shenzhen Baishan Mechatronics Shenzhen Biosled Technology Shenzhen Bolutek Technology Shenzhen Chipsea Technologies ShenZhen ChipSourceTek Technology Shenzhen ExSAF Electronics Co Shenzhen Genesis-Systech ShenZhen Gerbole Shenzhen Getech Co Shenzhen GUANGSHIMEI Electronic Shenzhen Hanxia Electronics Shenzhen Haolin Electronics Shenzhen Heliwei Technology Shenzhen honglifa Electronics Co Shenzhen HongyeX Electronics Co ShenZhen HuaXinAn Electronics Co.,Ltd Shenzhen Injoinic Technology Co. Shenzhen Jin Yu Semiconductor Co ShenZhen JINCI Technology Shenzhen Jinrui Electronic Material Co Shenzhen JMRTH Co Shenzhen Kaiyuexiang Electronics Co Shenzhen LFN Technology Co Shenzhen Lodestar S.T Co Shenzhen Lumen Electronics Shenzhen Magnetic Technology Shenzhen MilkV Technology Shenzhen Milliohm Electronics Shenzhen Minewsemi Co., Ltd Shenzhen Nsiway Tech Shenzhen Ou Chuangxin Semiconductor ShenZhen Qi Dian Shi Dai Technology Shenzhen Ruichips Semiconductor Shenzhen Ruilongyuan Electronics Shenzhen Shiji Lighting Shenzhen SI Semiconductors Shenzhen SLKOR Micro Semicon Co Shenzhen Sunmoon Microelectronics Shenzhen Suosemi Tech Shenzhen TongYiFang Optoelectronic Technology CO,Ltd Shenzhen Topmay Electronic Shenzhen TPOWER Semiconductor Shenzhen Universal Micro-Electronics Shenzhen USBR Precision Hardware Electronics Shenzhen Weidy Industrial Development Co., Ltd. Shenzhen Xinbole Electronics Co. Shenzhen Xptek Technology Shenzhen Xunlong Shenzhen Yangxing Technology Co. SHENZHEN YeZhan Electronics Shenzhen Yiwei Technology Shenzhen ZVELL Electronics Shindengen Electric Shin-Etsu Chemical Co SHINYEI Technology SHOEI SIBA GmbH Sichuan huafeng enterprise group SICK, Inc. Siemens Semiconductor Group Si-En Technology SiFirst Technology SiGe Semiconductor Sigma Microelectronics Signetics Silego Technology Silergy Corp Silicon Image Silicon Integrated Systems Silicon Laboratories Silicon Microstructures, Inc. Silicon Motion, Inc Silicon Sensing Systems Limited Silicon Standard Corp Silicon Storage Technology Silicon Systems Inc Silicon Touch Technology Silvan Chip Electronics Silver Telecom Ltd SilverStone Technology SIMCom Wireless Solutions SIMTEK Electronic Components Sinda Photoelectricity Technology SINGULAR TECHNOLOGY CO., LTD. Sinomags Technologies Co Sinopower Semiconductor Sipex Corporation Sirectifier Semiconductors SiTime Corporation Sivago Semiconductor Co SIWARD Crystal Technology Siyang Microelectronics Sizto Tech Corp SKYLAB M&amp;C Technology Skyworks Solutions, Inc SL Power Electronics Corp. SMAR Smartec BV SMC Diode Solutions Co. Smiths Interconnect. SMSC Corporation Soberton Inc Softing Automotive Electronics Sola/Hevi-Duty Sola-IC Solarflex SA Soldex Solid State Scientific SOLIDIC Solitronics Engineering Limited SOL-LED Lighting Co Solomon Systech Song Chuan Song Huei Electric Sonix Technology Sony Corporation Soundwell Electronic South African Micro-Electronic Systems Spansion inc SparkFun Electronics SPEC Sensors LLC Spectra Symbol Corp. Spectrum Digital Incorporated Speed Tech Corp Spin Semiconductor Sprague Semiconductors SPX Flow Technology ST Engineering Stackpole Electronics Standex-Meder Electronics Stannol GmbH Stanson Technology StarChips Technology StarPower Semiconductor Ltd. Startek Electronic Technology STATEK CORPORATION Stäubli International AG. STCmicro Technology Co Stewart Connector STMicroelectronics Stocko Stork Solutions Ltd. Sullins Connector Solutions SUMIDA Corporation Sun Hydraulics Corporation Sun Microelectronics SunLED SUNLORD Sunltech Tech SUNMATE Electronic Sunonwealth Electric Machine Sunplus Technology Sunrise Electronics Suntan Technology Company Suntsu Electronics, Inc. SUNYUAN Technology Supertex Inc Susumu International Suzhou Innoson Technology Suzhou NOVOSENSE Microelectronics Co., Ltd Suzhou Silikron Semiconductor Corp Switchcraft Inc. Switec SYNC Power Crop SyncMOS Technologies Synoxo International System General Corp Tadiran Batteries TAG Semiconductors TA-I Technology TAIKO-NET Tai-Saw Technology Tai-Tech Advanced Electronics Taitien Electronics Taitron Components, Inc Taiwan Alpha Electronic Co Taiwan Semiconductor Taiyo Electric Co Taiyo Yuden Tak Cheong Electronics Talema Group, LLC Tamagawa seiki Co Tamron Tamura Corporation TANCAP Technology Taoglas Limited TDK Corporation (EPCOS) TDK-Lambda Corporation TDK-Micronas GmbH TE Connectivity Team Source Display tech.co,ltd. Techcode Semiconductor Techpoint Inc Techspray/Plato-EMX Enterprises Limited Techstar Electronics TechToys Company TelCom Semiconductor Telcon Ltd Telechips Inc Teledyne Technologies TELEFUNKEN Elektroakustik Telegesis Ltd Telit TEMIC Semiconductor Terawins, Inc Teridian Semiconductor TESLA Testo SE &amp; Co Texas Advanced Optoelectronic Solutions Texas Instruments THAT Corporation Thegioiic Corporation Thermonamic Electronics(Jiangxi) Corp THine Electronics, Inc Thinki Semiconductor Thinking Electronic THOMSON Inc THORLABS Thousand Hundred Industrial Thunder Precision Resistor TIANMA Titan Micro TLC Electronics TNI-U TOOL Token Electronics Industry Tokmas Semiconductor TOKO, Inc Tontek Design Technology Top-arm Topro Technology Topway Technology Torex Semiconductor Toshiba Corporation touchSEMI TOYO LED ELECTRONICS LIMITED. TOYODA TR Electronic Nordic AB. Traco Electronic AG Transcom, Inc Transko Electronics, Inc. TRENDnet, Inc Trenz Electronic Triad Magnetics Trident Microsystems Trimble Inc TRINAMIC Motion Control TRinno Technology Co Tripath Technology TriQuint Semiconductor Truly Semiconductors TRW Inc TT Electronics TTM Technologies, Inc. TXC Corporation UBIQ Semiconductor Ubiquiti Inc u-blox UCE Ultrasonic Co UDF Semiconductor Ultisensor Electronics UNI SEMICONDUCTOR LIMITED Unicorn Microelectronics Corporation Unictron Technologies Corporation. Union Semiconductor Uniroyal Electronics Industry Co Unisonic Technologies Unitra Cemi Uni-Trend Technology Co Unitrode Corporation Universal Microelectronics UPI Semiconductor Corp US Digital US Micro Products. Usha India Ltd Ushio Opto Semiconductors UTRON Technology, Inc Vacuumschmelze GmbH VADEM LTD Vango Technologies, Inc Varitronix Limited VARTA AG Vatronics Technologies Ltd VBsemi Electronics Co. Ltd V-Chip Microsystems VectorNav Vectron International Vehicles instrumentation Device Venkel Ltd VIA Technologies Vicor Corporation Vigortronix Ltd. Vincotech Vishay Visual communication company Vitesse Semiconductor Vivesea VLSI Solution Vweb Corporation W. L. Gore &amp; Associates, Inc WAGO Kontakttechnik GmbH Wakefield Thermal, Inc. Walsin Technology Corporation Walter Electronic Co WanTcom, Inc Wavecom Waveshare Electronics Wavespectrum Laser Inc Wavetronics Technologies WAYTRONIC ELECTRONIC CO.LTD WeEn Semiconductors Weidmüller Interface GmbH Weipu connector Weltrend Semiconductor WENSHING Electronics Western Digital Corporation Willas Electronic Corp WIMA Winbond Electronics</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10u</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C12,C14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/category/202/switches/%d8%b3%d9%88%d8%a6%db%8c%da%86-%d9%88-%da%a9%d9%84%db%8c%d8%af#dtl/7595</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10900</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>21800</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10uF</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10uF</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/category/202/switches/%d8%b3%d9%88%d8%a6%db%8c%da%86-%d9%88-%da%a9%d9%84%db%8c%d8%af#dtl/7595</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10900</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>10900</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>100nF/275V</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C18,C19</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CAP-TH_L18.0-W6.0-P15.00-D0.8</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/product/320/non-brand/polyester-capacitor-100nf-400v/%d8%ae%d8%a7%d8%b2%d9%86-%d9%be%d9%84%db%8c-%d8%a7%d8%b3%d8%aa%d8%b1-100-%d9%86%d8%a7%d9%86%d9%88-%d9%81%d8%a7%d8%b1%d8%a7%d8%af-400-%d9%88%d9%84%d8%aa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>خازن پلی استر 100 نانو فاراد 400 ولت خانه دسته‌بندی‌ها All Products Passive Components Capacitors Film Capacitors اوریجینال خازن پلی استر 100 نانو فاراد 400 ولت نام قطعه: POLYESTER CAPACITOR 100NF 400V نام کارخانه‌ای: CF104K450B10 برند: Non-Brand کشور سازنده: چین پکیج: Radial بسته‌بندی: Bulk - 1,000 عدد حداقل: 2 عدد عنوان گروه: Film Capacitors دیتاشیت: CF104K450B10 Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات خازن پلی استر 100 نانو فاراد 400 ولت خازن پلی استر 100 نانو فاراد 400 ولت از خانواده خازن فیلم می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج Radial دقت 10 درصد نوع قرار گیری Radial کارکرد DC and Low pulse circuit.E.G. Low frequency filter, block DC and by-pass Etc ظرفیت 100 نانو فاراد مقدار ولتاژ DC 400 ولت دی الکتریک Polyester Film Capacitor حداقل دمای عملیاتی -40 درجه سانتیگراد حداکثر دمای عملیاتی +85 درجه سانتیگراد فاصله پایه ها 10 میلیمتر مقدار ولتاژ AC 200 ولت POLYESTER CAPACITOR 100NF 400V یک خازن فیلم پلی‌استر (Polyester Film Capacitor / PET Film Capacitor) از نوع Radial Through-Hole است که برای فیلتر کردن نویز، حذف مؤلفه DC، کوپلینگ و دیکوپلینگ سیگنال، مدارهای Low Pulse و Snubber سبک طراحی شده است. به دلیل تحمل ولتاژ بالا (400VDC) این قطعه در منابع تغذیه، مدارهای صنعتی، پاور الکترونیک سبک و بخش‌های ولتاژ بالاتر کاربرد زیادی دارد. این خازن با ظرفیت 100nF (0.1µF) و ولتاژ نامی 400VDC / 200VAC معمولاً در فیلتر EMI، Bypass، Coupling، RC Network و مدارهای سرکوب نویز استفاده می‌شود. 🧩 مشخصات کلی: نوع: Polyester Film Capacitor دی‌الکتریک: Polyester Film (PET) برند: Non-Brand نوع نصب: Through Hole پکیج: Radial نوع پایه: Radial Lead فاصله پایه‌ها (Lead Spacing): 10 mm ⚙️ مشخصات فنی کلیدی: ظرفیت (Capacitance): 100nF (0.1µF) تلرانس (Tolerance): ±10% مناسب کاربردهای عمومی، Filtering و Bypass. ولتاژ نامی DC: 400VDC مناسب مدارهای ولتاژ بالا و پاور. ولتاژ نامی AC: 200VAC قابل استفاده در برخی کاربردهای AC کم‌فرکانس. بازه دمای کاری: −40°C تا +85°C نوع ترمینیشن: Radial Leads 💡 کاربردهای عملی: منابع تغذیه مدارهای پاور فیلتر EMI کنترل صنعتی Coupling/Decoupling Snubber سبک Signal Conditioning Audio Circuit مدارهای High Voltage Protection Circuit RC Timing Bypass Capacitor ✅ مزایا: تحمل ولتاژ بالا (400VDC) غیرقطبی (Non-Polarized) مناسب Filtering و Noise Suppression طول عمر بالا مقاومت عایقی خوب ابعاد مناسب برای Through-Hole مناسب کاربری صنعتی 🎯 جمع‌بندی: POLYESTER CAPACITOR 100NF 400V یک خازن فیلم پلی‌استر 100nF با تحمل 400VDC و 200VAC است که برای فیلتر فرکانس پایین، حذف DC، بای‌پس، Snubber سبک و کاهش نویز در مدارهای ولتاژ بالا طراحی شده است. مهم‌ترین ویژگی آن تحمل ولتاژ بالا، غیرقطبی بودن، عمر زیاد و پایداری مناسب در مدارهای صنعتی و منابع تغذیه است. از دید مهندسی الکترونیک، این قطعه یک Film Capacitor عمومی و قابل‌اعتماد برای مدارهای پاور و Signal Conditioning محسوب می‌شود. Features انتخاب ویژگی Tolerance 10 % ≤ = ≥ Capacitance 100 nF ≤ = ≥ Dielectric Polyester Film Capacitor Lead Spacing 10 mm ≤ = ≥ Voltage Rating AC 200 V ≤ = ≥ Function DC and Low pulse circuit.E.G. Low frequency filter, block DC and by-pass Etc Voltage Rating DC 400 V ≤ = ≥ Termination Style Radial Minimum Operating Temperature -40 °C ≤ = ≥ Maximum Operating Temperature +85 °C ≤ = ≥ Brand Non-Brand Package Radial جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 85 45,500 ریال 45,000 ریال 100
+                                                        عدد 44,500 ریال 500
+                                                        عدد 43,200 ریال 1,000
+                                                        عدد 42,300 ریال 5,000
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>45500</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>91000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B540CQ-13-F</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SMC(DO-214AB)</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>https://lionelectronic.ir/products/2816-SS34</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>لیون الکترونیک | SS34 خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products Discrete Semiconductors Diodes And Rectifiers Schottky Diodes SS34 2,202 موجودی محصول تعداد قیمت 5 46,680 ریال 25 42,634 ریال 500 41,701 ریال 5000 40,767 ریال افزودن به سبد خرید Full Reel: 5000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام SS34 SS34 Part Number 2816 Lion Part Download Datasheet Jingdao Microelectronics Manufacture دیود شاتکی 40 ولت 3 آمپر با پکیج SMA Schottky Diode 40V 3A SMA معرفی دیود شاتکی SS34 یکی از دیودهای شاتکی پرکاربرد در مدارهای الکترونیکی و قدرت است که به دلیل ویژگی‌های خاص خود در بسیاری از کاربردهای صنعتی و ...استفاده می‌شود. از مهم‌ترین ویژگی‌های این دیود می‌توان به ولتاژ معکوس 40 ولتی اشاره کرد. همچنین، این دیود قادر است جریان رو به جلو تا 3 آمپر را تحمل کند که برای کاربردهایی که نیاز به جریان بالا دارند، مناسب است. دیود SS34 دارای افت ولتاژ رو به جلو بسیار کمی است (کمتر از 0.55 ولت)، که این ویژگی باعث کاهش تلفات انرژی و افزایش راندمان در مدارها می‌شود. همچنین، این دیود به دلیل ساختار شاتکی خود، سرعت سوئیچینگ بالایی دارد که موجب می‌شود در کاربردهایی که نیاز به سوئیچینگ سریع دارند، بسیار مؤثر باشد. از دیگر ویژگی‌های دیود SS34 ، می‌توان به پایداری حرارتی آن اشاره کرد. این دیود می‌تواند در دماهای مختلف عملکرد مناسبی داشته باشد، اما در دماهای بالاتر نیاز به خنک‌سازی دارد تا از عملکرد بهینه آن محافظت شود. دیود SS34 به دلیل تحمل جریان بالا، افت ولتاژ کم و سرعت سوئیچینگ بالا، در مدارهای مختلفی مانند منابع تغذیه DC-DC و AC-DC برای تبدیل ولتاژ و تصحیح جریان استفاده می‌شود. این دیود همچنین در مدارهای محافظتی و شارژ باتری نیز کاربرد دارد. برای استعلام قیمت و ثبت سفارش واردات قطعات الکترونیکی کلیک کنید قیمت دیود SS34 قیمت دیود شاتکی SS34 به تعداد خرید و برند و کارخانه تولیدکننده آن متفاوت است. به طور کلی، قیمت این دیود در بازار به دلیل کاربرد گسترده‌اش و ساختار ساده آن، نسبتاً مقرون‌به‌صرفه است. برای خرید عمده، قیمت‌ها ممکن است پایین‌تر از خریدهای تکی باشد و معمولاً در بازارهای آنلاین و فروشگاه‌های الکترونیکی می‌توانید خریداری کنید. برای مشاهده انواع دیود یکسوساز و خرید دیود شاتکی اورجینال مورد نظر با بهترین قیمت و کیفیت کافیست به سایت لیون الکترونیک مراجعه نمایید. مشخصات دیود شاتکی SS34 دیود شاتکی SS34 Part Number 40V Vrrm - Repetitive Reverse Voltage -55C Minimum Operating Temperature Reel Packaging SMD/SMT Mounting Style 80A Ifsm - Forward Surge Current 550mV Vf - Forward Voltage +125C Maximum Operating Temperature 500uA Ir - Reverse Current Single Configuration 3A If - Forward Current DO-214AC (SMA) Package-Case نظرات کاربران ارسال نظر محصولات مرتبط 1N5819WT DFLS160-7 SK54BLF_R2_00001 SBL1045CTW C1045DW SDT5A50SA-13 B540C-13-F PDS540-13 PDS760-13 PDS5100-13 × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 2,202 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>46680</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>46680</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SMBJ18A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>D2,D3,D5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SMB_L4.3-W3.6-LS5.4-RD</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>https://lionelectronic.ir/products/116-SMBJ18A</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>لیون الکترونیک | SMBJ18A خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products Discrete Semiconductors Diodes And Rectifiers TVS Diodes - ESD Suppressors SMBJ18A 1,486 موجودی محصول تعداد قیمت 2 135,256 ریال 25 130,592 ریال 250 128,260 ریال 1000 124,062 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام SMBJ18A SMBJ18A Part Number 116 Lion Part Download Datasheet Littelfuse Manufacture دیود TVS یک جهته 18 ولت با بیشنه پالس جریان 20.6 آمپر با پکیج SMB TVS Diode Uni-directional 18V SMB مشخصات SMBJ18A SMBJ18A Part Number 1 Number of Channels -55C Minimum Operating Temperature 30kV Vesd - Voltage ESD Air Gap 30kV Vesd - Voltage ESD Contact Reel Packaging SMD/SMT Termination style Unidirectional Polarity 600W Pppm - Peak Pulse Power Dissipation +150C Maximum Operating Temperature 18V Working Voltage 29.2V Clamping Voltage N/A Cd - Diode Capacitance 22.1V Breakdown Voltage 20.6A Ipp - Peak Pulse Current TVS Diodes Product Type DO-214AA (SMB) Package-Case نظرات کاربران ارسال نظر محصولات مرتبط SD03C SD03 SMF26A SMBJ350CA SMBJ400CA PESD12VS1UA PESD12VL1BA D5V0P4UR6SO-7 NUF8410MNT4G SMAJ58CA × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 1,486 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>135256</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>405768</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SS34B</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SMB_L4.6-W3.6-LS5.3-RD</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>ok https://www.javanelec.com/shop?searchfilter=1n5822#dtl/626</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ERROR: [Errno 22] Invalid argument: 'ok https://www.javanelec.com/shop?searchfilter=1n5822#dtl/626'</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SMCJ6.5CA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>D6,D7</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SMC_L6.9-W5.9-LS7.9-BI</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>https://lionelectronic.ir/products/2867-SMBJ16A</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>لیون الکترونیک | SMBJ16A خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products Discrete Semiconductors Diodes And Rectifiers TVS Diodes - ESD Suppressors SMBJ16A 3,069 موجودی محصول تعداد قیمت 2 128,128 ریال 25 124,467 ریال 250 121,722 ریال 1000 119,891 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام SMBJ16A SMBJ16A Part Number 2867 Lion Part Download Datasheet Littelfuse Manufacture دیود TVS یک جهته 16 ولت با بیشنه پالس جریان 23.1 آمپر با پکیج SMB TVS Diode Uni-directional 16V SMB مشخصات دیود تی‌وی‌اس SMBJ16A دیود تی‌وی‌اس SMBJ16A Part Number 1 Number of Channels -65C Minimum Operating Temperature 30kV Vesd - Voltage ESD Air Gap Reel Packaging 30kV Vesd - Voltage ESD Contact SMD/SMT Termination style Unidirectional Polarity 600W Pppm - Peak Pulse Power Dissipation +150C Maximum Operating Temperature 16V Working Voltage 26V Clamping Voltage N/A Cd - Diode Capacitance 17.8V Breakdown Voltage 23.1A Ipp - Peak Pulse Current TVS Diodes Product Type DO-214AA (SMB) Package-Case نظرات کاربران ارسال نظر محصولات مرتبط SD03C SD03 SMF26A SMBJ350CA SMBJ400CA PESD12VS1UA PESD12VL1BA D5V0P4UR6SO-7 NUF8410MNT4G SMAJ58CA × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 3,069 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>128128</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>256256</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SMBJ16A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SMB_L4.5-W3.7-LS5.4-RD</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>https://lionelectronic.ir/products/2867-SMBJ16A</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>لیون الکترونیک | SMBJ16A خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products Discrete Semiconductors Diodes And Rectifiers TVS Diodes - ESD Suppressors SMBJ16A 3,069 موجودی محصول تعداد قیمت 2 128,128 ریال 25 124,467 ریال 250 121,722 ریال 1000 119,891 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام SMBJ16A SMBJ16A Part Number 2867 Lion Part Download Datasheet Littelfuse Manufacture دیود TVS یک جهته 16 ولت با بیشنه پالس جریان 23.1 آمپر با پکیج SMB TVS Diode Uni-directional 16V SMB مشخصات دیود تی‌وی‌اس SMBJ16A دیود تی‌وی‌اس SMBJ16A Part Number 1 Number of Channels -65C Minimum Operating Temperature 30kV Vesd - Voltage ESD Air Gap SMD/SMT Termination style 30kV Vesd - Voltage ESD Contact Reel Packaging Unidirectional Polarity 600W Pppm - Peak Pulse Power Dissipation +150C Maximum Operating Temperature 16V Working Voltage 26V Clamping Voltage N/A Cd - Diode Capacitance 17.8V Breakdown Voltage 23.1A Ipp - Peak Pulse Current TVS Diodes Product Type DO-214AA (SMB) Package-Case نظرات کاربران ارسال نظر محصولات مرتبط SD03C SD03 SMF26A SMBJ350CA SMBJ400CA PESD12VS1UA PESD12VL1BA D5V0P4UR6SO-7 NUF8410MNT4G SMAJ58CA × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 3,069 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>128128</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>128128</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TS-1094T-B2D2-T-Y</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DOWN,UP</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SW-TH_4P-L12.0-W12.0-P5.00-LS12.5</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/product/35210/non-brand/kfc-3*6*5-2p-smd-reel/%d8%aa%da%a9-%d8%b3%d9%88%d8%a6%db%8c%da%86-%d8%b1%db%8c%d9%85%d9%88%d8%aa%db%8c-2-%d9%be%d8%a7%db%8c%d9%87-3*6*5-smd</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>تک سوئیچ ریموتی 2 پایه 3*6*5 SMD خانه دسته‌بندی‌ها All Products Electromechanical Switches Tactile Switches اوریجینال تک سوئیچ ریموتی 2 پایه 3*6*5 SMD نام کارخانه‌ای: KFC-3*6*5-2P SMD REEL برند: Non-Brand کشور سازنده: چین پکیج: Switch بسته‌بندی: Tape &amp; Reel - 1,500 عدد حداقل: 3 عدد عنوان گروه: Tactile Switches دیتاشیت: KFC-3*6*5-2P SMD REEL Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات تک سوئیچ ریموتی 2 پایه 3*6*5 SMD تک سوئیچ ریموتی 2 پایه 3*6*5 SMD از خانواده تک سوئیچ می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج Switch مقدار ولتاژ DC 12 ولت مقدار جریان 50 میلی آمپر کارکرد Off-(ON) Momentary نوع نصب روی برد SMD طول (ارتفاع) 3 میلیمتر عرض (پهنا) 6 میلیمتر ارتفاع 5 میلیمتر Features انتخاب ویژگی Current Rating 50 mA ≤ = ≥ Voltage Rating DC 12 V ≤ = ≥ Function Off-(ON) Momentary Mounting Style SMD Length 3 mm ≤ = ≥ Width 6 mm ≤ = ≥ Height 5 mm ≤ = ≥ Brand Non-Brand Package Switch جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … ناموجود-سفارش دهید زمان تحویل 31 روزه محصول را به سبد سفارش اضافه کنید. ادامه فرآیند سبد سفارش را دنبال کنید. درخواست شما توسط کارشناسان جوان الکترونیک بررسی می‌شود. قیمت و زمان تحویل به شما پیشنهاد داده خواهد شد. در صورت تمایل پیش فاکتور صادر می شود. پیش پرداخت را واریز کنید و ادامه کار را به جوان الکترونیک بسپارید. اجناس خود را در زمان مقرر دریافت کنید. 82 مشاهده سوابق فروش اضافه به سبد سفارش دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2.4GHz</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ESP8266</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>WIFIM-SMD_ESP-12E-BR</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2.4GHz</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>https://shop.ideaelec.com/product/esp8266-12e/?utm_medium=PPC&amp;utm_source=Torob</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ERROR: 403 Client Error: Forbidden for url: https://shop.ideaelec.com/product/esp8266-12e/?utm_medium=PPC&amp;utm_source=Torob</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LC-3P-S-5.08-W</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FLOWMETER-1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CONN-TH_3P-P5.08_2EHDR-03P</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>KF2510-3AW</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FLOWMETER-2,POS-3-PIN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CONN-TH_KF2510-3AW</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/product/1973/cixi-kefa-electronics/phoenix-3-pin-ra/%d8%aa%d8%b1%d9%85%db%8c%d9%86%d8%a7%d9%84-%d9%81%d9%88%d9%86%db%8c%da%a9%d8%b3-3-%d9%be%db%8c%d9%86-%d8%b1%d8%a7%db%8c%d8%aa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ترمینال فونیکس 3 پین رایت خانه دسته‌بندی‌ها All Products Connectors Terminal Blocks Pluggable Terminal Blocks اوریجینال ترمینال فونیکس 3 پین رایت نام قطعه: PHOENIX 3 PIN RA نام کارخانه‌ای: KF2EDG-X-5.08-03P &amp; KF2EDGR-X-5.08-03P برند: Cixi Kefa Electronics پکیج: Connector بسته‌بندی: Bulk - 200 عدد عنوان گروه: Pluggable Terminal Blocks دیتاشیت: KF2EDG-X-5.08-03P &amp; KF2EDGR-X-5.08-03P Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات ترمینال فونیکس 3 پین رایت ترمینال فونیکس 3 پین رایت از خانواده ترمینال روبردی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Cixi Kefa Electronics پکیج Connector نوع Terminal Blocks مقدار ولتاژ DC 300 ولت تعداد پین ها 3 پین گام 5.08 میلیمتر مقدار جریان 10 آمپر نوع قرار گیری Screw PHOENIX 3 PIN RA یک ترمینال بلوک (Terminal Block) زاویه‌دار (Right Angle) با 3 پین است که توسط Cixi Kefa Electronics تولید می‌شود. این کانکتور برای اتصال ایمن سیم‌ها به برد مدار چاپی (PCB) طراحی شده و از مکانیزم پیچی (Screw Terminal) برای ایجاد اتصالی محکم، پایدار و قابل اطمینان استفاده می‌کند. با قابلیت تحمل 10 آمپر جریان ، 300 ولت DC و گام استاندارد 5.08 میلی‌متری ، این ترمینال گزینه‌ای مناسب برای تجهیزات صنعتی، منابع تغذیه، سیستم‌های کنترلی و انواع بردهای الکترونیکی است. 💡 کاربردهای اصلی منابع تغذیه سوئیچینگ (SMPS) تابلوهای برق و اتوماسیون صنعتی PLC و تجهیزات کنترل صنعتی سیستم‌های کنترل موتور تجهیزات اندازه‌گیری و ابزار دقیق سیستم‌های روشنایی تجهیزات مخابراتی سیستم‌های امنیتی و اعلام حریق بردهای کنترلی صنعتی انواع پروژه‌های الکترونیکی و صنعتی ✅ مزایا اتصال بسیار مطمئن: مکانیزم پیچی از شل شدن سیم‌ها در اثر لرزش جلوگیری می‌کند. تحمل جریان مناسب: قابلیت عبور جریان تا 10 آمپر برای هر پین. تحمل ولتاژ بالا: مناسب برای مدارهای تا 300 ولت DC . طراحی زاویه‌دار (Right Angle): خروج کابل به‌صورت افقی و کاهش فضای اشغال‌شده داخل دستگاه. گام استاندارد 5.08mm: سازگار با اکثر بردهای صنعتی و تجاری. نصب و سرویس آسان: امکان اتصال و جداسازی سیم‌ها بدون نیاز به لحیم‌کاری. استحکام مکانیکی بالا: مناسب برای کاربردهای صنعتی و محیط‌های دارای لرزش. 🎯 جمع‌بندی PHOENIX 3 PIN RA یک ترمینال بلوک زاویه‌دار 3 پین با اتصال پیچی (Screw Terminal) است که برای ایجاد اتصال مطمئن بین سیم و برد مدار چاپی طراحی شده است. این کانکتور با تحمل جریان 10 آمپر ، ولتاژ 300 ولت DC و گام استاندارد 5.08 میلی‌متری ، انتخابی مناسب برای منابع تغذیه، تجهیزات صنعتی، تابلوهای کنترل، سیستم‌های اتوماسیون و انواع بردهای الکترونیکی محسوب می‌شود. طراحی Right Angle باعث خروج افقی سیم‌ها، مدیریت بهتر کابل‌ها و کاهش فضای مورد نیاز در داخل تجهیزات شده و در کنار اتصال پیچی، دوام و اطمینان بالایی را در محیط‌های صنعتی فراهم می‌کند. Features انتخاب ویژگی Current Rating 10 A ≤ = ≥ Voltage Rating DC 300 V ≤ = ≥ Number of Pins 3 Pin ≤ = ≥ Pitch 5.08 mm Type Terminal Blocks Termination Style Screw Brand Cixi Kefa Electronics Package Connector جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 85 211,000 ریال 208,000 ریال 100
+                                                        عدد 206,000 ریال 200
+                                                        عدد 204,000 ریال 500
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>211000</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>422000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>47uH</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ECQ_10MM_12*6MM</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ERROR: [Errno 2] No such file or directory: 'ok'</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LC-2P-S-5.08-W</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LAMP-12V,PHOTOCELL,POWER-12V,RELE-2-12V-DC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CONN-TH_2P-P5.08_2EHDR-02P</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/product/1970/cixi-kefa-electronics/phoenix-2-pin-ra/%d8%aa%d8%b1%d9%85%db%8c%d9%86%d8%a7%d9%84-%d9%81%d9%88%d9%86%db%8c%da%a9%d8%b3-2-%d9%be%db%8c%d9%86-%d8%b1%d8%a7%db%8c%d8%aa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ترمینال فونیکس 2 پین رایت خانه دسته‌بندی‌ها All Products Connectors Terminal Blocks Pluggable Terminal Blocks اوریجینال ترمینال فونیکس 2 پین رایت نام قطعه: PHOENIX 2 PIN RA نام کارخانه‌ای: KF2EDG-X-5.08-02P &amp; KF2EDGR-X-5.08-02P برند: Cixi Kefa Electronics پکیج: Connector بسته‌بندی: Bulk - 500 عدد عنوان گروه: Pluggable Terminal Blocks دیتاشیت: KF2EDG-X-5.08-02P &amp; KF2EDGR-X-5.08-02P Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات ترمینال فونیکس 2 پین رایت ترمینال فونیکس 2 پین رایت از خانواده ترمینال روبردی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Cixi Kefa Electronics پکیج Connector نوع Terminal Blocks مقدار ولتاژ DC 300 ولت مقدار جریان 10 آمپر تعداد پین ها 2 پین گام 5.08 میلیمتر نوع قرار گیری Solder Pin PHOENIX 2 PIN RA یک ترمینال بلوک (Terminal Block) زاویه‌دار (Right Angle) با 2 پین است که توسط Cixi Kefa Electronics تولید می‌شود. این کانکتور برای ایجاد اتصال مطمئن بین سیم و برد مدار چاپی (PCB) طراحی شده و پایه‌های آن از نوع Solder Pin بوده که از طریق لحیم‌کاری روی برد نصب می‌شوند. با قابلیت تحمل 10 آمپر جریان ، 300 ولت DC و گام استاندارد 5.08 میلی‌متری ، این ترمینال گزینه‌ای مناسب برای تجهیزات صنعتی، منابع تغذیه، سیستم‌های کنترلی و انواع بردهای الکترونیکی است. 💡 کاربردهای اصلی ورودی و خروجی تغذیه بردهای الکترونیکی منابع تغذیه سوئیچینگ (SMPS) تجهیزات اتوماسیون صنعتی تابلوهای کنترل و برق PLC و تجهیزات کنترلی سیستم‌های روشنایی صنعتی تجهیزات اندازه‌گیری و ابزار دقیق سیستم‌های امنیتی و اعلام حریق کنترل‌کننده‌های موتور پروژه‌های الکترونیکی عمومی ✅ مزایا تحمل جریان مناسب: قابلیت عبور جریان تا 10 آمپر . تحمل ولتاژ بالا: مناسب برای مدارهای تا 300 ولت DC . طراحی زاویه‌دار (Right Angle): خروج کابل به‌صورت افقی و کاهش ارتفاع مجموعه روی برد. گام استاندارد 5.08mm: سازگار با بسیاری از بردهای صنعتی و تجاری. پایه‌های لحیمی مستحکم: ایجاد اتصال مکانیکی و الکتریکی پایدار به PCB. اشغال فضای کمتر: مناسب برای طراحی‌های فشرده و نصب در محفظه‌های کم‌ارتفاع. دوام بالا: مناسب برای استفاده در محیط‌های صنعتی. 🎯 جمع‌بندی PHOENIX 2 PIN RA یک ترمینال بلوک زاویه‌دار 2 پین با پایه‌های Solder Pin است که برای اتصال مطمئن سیم‌ها به برد مدار چاپی طراحی شده است. این کانکتور با تحمل جریان 10 آمپر ، ولتاژ 300 ولت DC و گام استاندارد 5.08 میلی‌متری ، انتخابی مناسب برای منابع تغذیه، تجهیزات صنعتی، سیستم‌های کنترلی و انواع بردهای الکترونیکی محسوب می‌شود. طراحی Right Angle باعث خروج افقی سیم‌ها، کاهش فضای اشغال‌شده و مدیریت بهتر کابل‌ها در داخل تجهیزات می‌شود و آن را به گزینه‌ای کاربردی برای طراحی‌های فشرده و صنعتی تبدیل می‌کند. Features انتخاب ویژگی Current Rating 10 A ≤ = ≥ Voltage Rating DC 300 V ≤ = ≥ Number of Pins 2 Pin ≤ = ≥ Pitch 5.08 mm Type Terminal Blocks Termination Style Solder Pin Brand Cixi Kefa Electronics Package Connector جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 85 175,000 ریال 173,000 ریال 100
+                                                        عدد 171,000 ریال 200
+                                                        عدد 169,000 ریال 500
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LED_0805-B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LAMP_1,LAMP_2,RELE_1,RELE_2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LED0805-RD_GREEN</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>https://lionelectronic.ir/products/2221-XL-3216UBC</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>لیون الکترونیک | XL-3216UBC خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products LED Lighting LED Color LEDs XL-3216UBC 9,900 موجودی محصول تعداد قیمت 100 9,456 ریال 500 9,141 ریال 1500 8,952 ریال 3000 8,826 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام XL-3216UBC XL-3216UBC Part Number 2221 Lion Part Download Datasheet XINGLIGHT Manufacture ال ای دی آبی پکیچ 1206 LED Blue 455-475nm 1206 25mA 75mW مشخصات ال‌ای‌دی آبی XL-3216UBC ال‌ای‌دی آبی XL-3216UBC Part Number 120° Viewing Angle Blue Illumination Color Reel Packaging SMD/SMT Mounting Style 75mW Power Rating -30C Minimum Operating Temperature 42-86mcd Luminous Intensity +85C Maximum Operating Temperature 25mA If - Forward Current 455-475nm Wavelength-Color Temperature 1206 (3216 metric) Package-Case 2.6-3.2V Vf - Forward Voltage نظرات کاربران ارسال نظر محصولات مرتبط XL-1005UYC XL-1005UWC XL-1005SURC XL-1005UBC XL-1005UGC SK6812MINI-E XL-3215UYC XL-3215UGC XL-3215SURC WS2812D-F8 × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 9,900 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>9456</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>37824</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FRJ11008-1100K6K20</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>POS-RJ11</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RJ11-TH_FRJ11008-1100K6K20</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ERROR: [Errno 2] No such file or directory: 'ok'</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DC-005_2.5</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>POWER-12V-DC,RELE-1-12V-DC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DC-IN-TH_DC-5520-1</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop?searchfilter=2.1#dtl/1726</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">محصولات خانه دسته‌بندی‌ها فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه عبارت 2.1 جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش برند 1666 3M Dynapro 3M Interconnect 3PEAK Incorporated 4D Systems Pty Ltd A Power microelectronics AAEON Technology Aavid Thermalloy ABC Taiwan Electronics ABLIC Inc Abracon Corporation Acam-Messelectronic Acrian, Inc Actel Corporation Active-Semi, Inc Actox Corporation. AD Semiconductor Confidential Adafruit Industries LLC Adam Technologies, Inc ADDA Corp ADDtek Corp Adesto Technologies ADMtek Inc Advanced Acoustic Technology Corp. Advanced Analog Technology Advanced Analogic Technologies Advanced Card Systems Advanced Ceramic X Corp Advanced Linear Devices Inc Advanced Monolithic Systems Advanced Photonix, Inc Advanced Power Electronics Corp Advanced Power Technology Advanced Semiconductor Advantech Corp Advantech Equipment Corporation Aegis Electronic Group AEL Crystals Limited AEM, Inc Aerosemi Technology Co Afa Technologies Inc AG Electrical Technology Agere Systems Agilent Technologies AGM Semiconductor AIC tech Inc. Aimtec Aimtron Corporation Airoha Technology Corp AIRWAVE Technologies Inc AiSHi Capacitors Aixin Opto-Electrical Technology Albright International Ltd Alcatel Microelectronics Alcor Micro Corp Alex Connector Co Ltd Alfa Electronics Algocraft Srl. ALi Corporation Alinx Electronic Technology All Sensors Corporation Allegro Microsystems Alliance Memory Allied Vision, Inc. Allwinner Technology Almita Co. Ltd Alpha &amp; Omega Semiconductor Alpha Micro Components Alpha Semiconductor Alpha Wire Alphasense Ltd, Sensor Technology Alps Electric Co Altera Corporation Amazing Electronic Co Amazing Microelectronic Corp AMD American Microsemiconductors American Microsystems Inc American Power Management American Technical Ceramics Corp American Zettler, Inc. Ametherm, Inc AMI Semiconductor AMIC Technology Corp Amidon Associates, Inc Amlogic Inc. Amotech Corp AMPAK Technology Inc Amphenol Advanced Sensors Amphenol Corporation Amphenol FCI Amphenol RF Ampleon USA Inc ams AG Anachip Corp ANADIGICS Anadigm, Inc Analog Devices Analog Integrations Corporation Analog Microelectronics Analog Power Analogix Semiconductor Inc Anaren, Inc Ancol Electronics Co Andigilog, Inc ANENG Anhui FOSAN Semiconductor Anhui Vico Technologes Co Anovay Technologies Limited ANPEC Electronics Corp Ante Intelligent Company Limited AP Memory Technology. APC Propellers APEM Inc Apex Material Technology Apex Precision Power API Delevan Inc API Technologies Aplus Integrated Circuits Inc APMKorea Apogee Technology, Inc Applent Instruments Applied Micro Circuits Co AppoTech Ltd APT Electronics Co., Ltd. Aptek Technologies ArchNet Technology Arcol UK Ltd Arduino Arduino Nicla Voice. Arima Lasers Corporation Aristotle Enterprises Inc ARTCHIP Semiconductor Artesyn Embedded Technologies AS ENERGI Asahi Kasei Microdevices ASAHI Solder Asia Vital Components Asiliant Technologies ASIX Electronics Corp AsLic Microelectronics Corporation ASMedia Technology Inc. Associated Opto-Electronics Astec Semiconductor. Astrodyne TDI Corporation. ATE Electronics s.r.l Atech Technology Co ATEN International Co Atheros Communications, Inc ATI Technologies Inc Atlas Scientific LLC. Attend Technology Inc AU Optronics Corp Audiowell Electronics Co Auk Contractors Co AUK Semiconductor AUO Corporation AUREL S.P.A Austar Technology AuthenTec, Inc Autonics Corporation Avago Technologies AVANTEK INC. AverLogic Technologies, Inc AVerMedia Technologies Avia Semiconductor Avnet, Inc AVX Corporation AXElite Technology Co Axiomtek Axis Communications AZ Displays, Inc Azoteq Ltd BAFO Technologies Corp Bahar Enclosure Baumer International BBT-China Inc BCD Semiconductor Beckhoff Automation Beijing Boshida Beijing HRH Information Co Beijing Ultrasonic Beijing Yihongtai Technology Beijing Zhongxun Sifang Science &amp; Technology Beken Corporation Bel Fuse Inc Bel Power Solutions Inc Belden Inc Bellnix Bencent Tzeng Ind. Co. Ltd Betlux Beyond Innovation Technology BI Technologies Bicker Elektronik GmbH Billionton Systems Inc Bird Technologies Bi-Sonic Technology Bivar, Inc Blackhawk BLOCK Inc Bluegiga Technologies BOLYMIN,INC BONGSHIN LOADCELL CO. Bookly Micro Electronic Bosch Security Systems Inc Bosch Semiconductors Bosch Sensortec Bothhand USA Boundary Devices Bourns Inc Bowin Microelectronics Brainboxes Limited BRIGHT LED ELECTRONICS CORP. Bright Power Semiconductor BrightKing Inc Brilliance Semiconductor, Inc Broadchip Technology Broadcom Limited BroadLight Inc Brooktree Corporation Burr-Brown Corporation BYD Microelectronics Co., Ltd. C&amp;D Technologies C&amp;K Components Caddock Electronics Inc California Eastern Laboratories California Micro Devices Calogic LLC Cambridge Integrated Circuits Cambridge Silicon Ra dio Limited Camille Bauer Ltd Catalyst Semiconductor Celduc relais CellWise Microelectronics Co Cenker Enterprise Ltd Centenary Materials Co CeNtRa Science Corp Central Components Manufacturing Central Georgia Generator Central Semiconductor CEVA Technologies CFSensor Challenge Electronics Champion Microelectronic Changzhou changjie Technology Co Changzhou Cre-sound Electronics Changzhou DRM Changzhou Esuntech Co Changzhou Kennon ELectronics Changzhou TDA Electronic Changzhou Yuanwang Fluid Technology Chaozhou Three-circle (Group) Co chargebyte GmbH. Chengdu Ebyte Electronic Technology Chengdu Guosheng Technology Chengdu Xincheng Huachuang Electronic ChenMoun Electronic ChenYang Technologies Cheuk Yui Innovation Co Chi Mei Optoelectronics Chieful Science ＆ Technology Chilisin Electronics Co China Base Electronic Technology China ECU Tools Centre China Resources Microelectronics China Software Industry Association Chinfa Electronics Chingis Technology Corp Chino-Excel Technology Chipanalog Incorporated ChipLink Tech Chiplus Semiconductor ChipON Chipower Electronics CHIPS Technology Chipstar Microelectronics CHK Electronics Ltd Chogori USA Chongqing Shengpu Electronics Chrontel, Inc Chunghwa Picture Tubes Churod Electronics Chyao Shiunn Electronic Cincon Electronics Cinetech Ind Cirrus Logic Inc Cisco Systems CIT Relay &amp; Switch Citizen Finedevice Co Cixi AnXon Electronic Cixi Dafa precise Linker Co CiXi KaiFeng Electronics Co Cixi Kefa Electronics Cixi Max Electronics Co.,Ltd Clare, Inc Cliff Electronic Components Limited Cmedia Electronics Inc CML Microsystems Coil Master Co Coil Winding Coilcraft Inc Coiltronics (Eaton) Comchip Technology Commodore Semiconductor Comtec Crystals comtech aha corporation CONEC Elektronische Bauelemente GmbH Conesys,Inc. Conexant Systems, Inc Connfly Electronic Co Connor-Winfield Conquer Electronic Continental Device India Controlair Inc Conversion Devices, Inc Cooper Bussmann Coretek Opto Corporation. Cornell Dubilier Electronics Cortina Systems, Inc Cosel Co Ltd COSINE Nanoelectronics Coto Technology CR Powtech Co Cree, Inc Crydom Inc Crystal Semiconductor Corporation Crystalfontz Crystek Corporation CSCONN PRECISE ELECTRONICS CO.,LTD CT Micro International Co CTS Corporation CUI Inc CVI Laser, LLC CW Industries Cyntec Co Cypress Semiconductor Cyrustek Corporation CYStech Electronics Corp. CYT Opto-Electronic Technology Dachang Electronics Daewoo Semiconductor Daier Electron Co Dailywell Electronics Daishinku Corp Daito Communication Apparatus Daiyo Electronics Dallas Semiconductor DANFOSS Daniels Manufacturing Co Data Device Corporation Davicom Semiconductor Davies Molding, LLC DB Lectro Inc DB Unlimited DC Components Co Dean Technology DECA SwitchLab Inc Decawave Ltd Dechang Electronic Deep Sea Electronics DEGSON Electronics Co Dell Inspiron Delta Electronics DeMint Electronics DENSO Destiny Technology Corp Detaik Technology Co Deva Electronic Controls Limited. Devantech Device Engineering Inc Dexter Magnetic Technologies DFRobot. Dialight Electronics Company Dialog Semiconductor Dielectric Laboratories Digi International Digilent, Inc Digital Voice Systems Digitrax, Inc Digitron Semiconductors Dinkle International Co. Ltd DIN-TEK Microelectronics Diodes Incorporated Diotec Semiconductor Diptronics Manufacturing Inc Display Solution AG DISPLAY VISIONS GmbH 2022. DMB Technology DOESTEK Co DOINGTER Semiconductor Domintech Co Don Connex Electronics DONG IL TECHNOLOGY LTD. Dongguan CHENGXING Electronic Co Dongguan City Wasi Electronic Technology Dongguan Cosson DongGuan HeLing Electronics Dongguan Lanbo Electronics Technology CO Dongguan Yuandi Electronics Dongguan Yuanze Electric Co.,Ltd Dongguan Yuxi Precise Connector Co., Ltd Dongke semiconductor Anhui Co., Ltd Donguan Keyouda Electronic Dosilicon Co DTK electronics Dualsky Models Co Duoxing Electronics Co Duty-Cycle Semiconductor Dynamic Technologies (DTCC) Dynex Semiconductor Ltd, E &amp; E Magnetic Products Limited EAST Semiconductor East Texas Integrated Circuits Eastrising Technology Co Eastsensor Technology Easy IoT Eaton’s Bussmann Ebm-papst inc Echelon Corporation Ecliptek Corporation ECOFIT &amp; ETRI ECS, Inc International EDAC EECO Switch E-Elements Technology Co Efficient Power Conversion Co EG Microelectronics Corp EIC Semiconductor Elan Microelectronics Co Elantec, Inc Electrolube Electronic Alliance Electronic Assembly Electronic Devices Inc Electroustic Ltd Eledis Element14 ELESTA GmbH Elite Semiconductor Memory Eljen Technology Elm Electronics ELM Technology Co Elmos Semiconductor AG ELNA Company Elpida Memory, Inc EM Microelectronic-Marin EMAD Embedded Artists Embest Technology Emerson Encitech Endress+Hauser Management ENE Technology Enplas Corporation Enrwey Co Ltd Eon Silicon Solution E-peas Semiconductors Epitex Inc Epoxy Technology Inc EPSON Electronics Ept Inc Ericsson Microelectronics ERNI Electronics ERSA UK LTD Espressif Systems ESS Technologies E-Switch, Inc ET Enterprises Limited E-T-A Circuit Breakers ETA Solutions E-tec Interconnect Ethertronics Inc Etron Technology, Inc EUCHNER GmbH Eupec semiconductor Euroquartz Ltd Eutech Microelectronics Everanalog Everest Semiconductor Everlight Electronics Everspin Technologies Exar Corporation Excel Cell Electronic Excelitas Technologies Excellence Opto, Inc Excelliance MOS Corporation Fagor Electronica Fairchild Semiconductor Fair-Rite Products Corp FANUC Corporation Faraday Technology Fastline Fastrax Ltd FASTRON Faulhaber GmbH FDK Corporation Feature Integration Technology Feei Cherng Enterprise Feeling Technology Feiyi Technology FEMA Electronics Corporation Fenghua Advanced Technology Ferroxcube International FERYSTER Sp. z.o.o Figaro Engineering Inc Finder Relays, Inc Fingerprint Cards First Semiconductor First Sensor FIS Inc Fischer Connectors Fischer Elektronik Fitipower Integrated Technology Force MOS Technology Co Formosa MS Formox Semiconductor Forsentrk Fortior Technology Co Fortune Semiconductor Forward International Electronics FOTEK Controls Fox Electronics Foxconn Technology Fractus S.A Franz Binder GmbH &amp; Co. Free2Move Holding AB. Freescale Semiconductor Fremont Micro Devices Friendcom Technology Develop FriendlyARM Computer Tech FTDI Chip Fuda Hisi Microelectronics Fuji Electric Fujikura Fujitsu Semiconductor Fujitsu-Takamisawa Fulihua Printer Ribbon Co Futaba Corporation Fu-Yao Technology Co Fuzetec Technology Co Fuzhou Rockchip Electronics Co., Ltd GainSpan Corporation GalaxyCore Inc GaNPower International Inc G-Antetech Industrial Garmin Ltd. Gas Sensing Solutions Ltd. Gaston Electronics GC GE Fanuc GEC Plessey Geehy Semiconductor Co General Electronic Devices General Monitors General Semiconductor Generalplus Technology GeneSiC Semiconductor Genesis Microchip Inc Genesys Logic, Inc Genicom Co., Ltd. Gennum Corporation GETE Electronics GigaDevice Semiconductor Global Connector Technology (GCT) Global Mixed-mode Technology GlobespanVirata, Inc GMC Instruments GME Technology, LLC GoChip Electronic Technology GoldStar Semiconductor Gonbes Technology Co Good Display Good Will Instrument Good-Ark Semiconductor Goodix Technology Governors America Co Gpixel Microelectronics Inc Grayhill Inc GreatLEDs Co Greenliant Systems GRUNER AG GSI Technology, Inc Guangdong Hottech Co Guangdong Huaguan Semiconductor Guangdong TIANQIU Electronics Technology Guangzhou Aosong Electronics Guangzhou Xinyue Electronic Guerrilla RF, Inc H&amp;M Semiconductor HABEY Halbleiter aus Frankfurt HALO Electronics Hamamatsu Photonics Hangzhou Grow Technology Co Hangzhou Nationalchip Science Hangzhou Prosper Hangzhou Silan Microelectronics Hannstar Display Corp HanRun Electronics Hanwei Electronics Co Hanyoung Nux Co HAOHAI ELECTRONICS HAOYU Electronics Harris Semiconductor HARTING Technology Harvatek Corporation Harwin Hawyang Semiconductor Hebei International Trading Co HEITEC AG. Hemingruizhi Electronic Henan Hanwei Electronics Co Hengda New Materials Technology HengJiaXing Electronics Co Henkel Corporation HenLv Power Technology Heter Electronics Hewlett-Packard Hexin Technology Highly Electric Hi-Link Electronic Technology Hi-Optel Technology Hirose Electric Hi-Sincerity Microelectronics Hitachi Maxell, Ltd Hitachi Semiconductor HITPOINT Inc Hittite Microwave Hivolt Capacitors Ltd H-JTAG Technology Hokuriku Electric Industry Co Ltd Hokuyo Automatic Co Holt Integrated Circuits Holtek Semiconductor Honeywell International Hong Kong Resistors Manufactory Hongfa Electroacoustic Co HONGHUA ELECTRONIC Hope Microelectronics HORIBA, Ltd. Hosiden Corporation Hosonic Electronic Co Hotchip Technology HTC Korea TAEJIN Technology Huada Connectors Huanor International Huaqi Microelectronics Co Huawei Technologies Huayu Technology HuaYuan Micro Electronic Huayue Microelectronics Co HUBER+SUHNER Huibei KENTO Electronic Huidu Technology Hukx Sensor Technology Humirel Hurricane Tech. Co HW group s.r.o HYCON Technology Corp. Hynix Semiconductor Hyundai Semiconductor IC Plus Corp ICE Components, Inc. iC-Haus GmbH Icom Inc ICP DAS CO ID Innovations ID TECH IDEC Corporation IEI Integration Ignion Iintelligent Motion Systems IK Semiconductor ILSI America LLC IMP, Inc Inchange Semiconductor Industrial Fiber Optics, Inc Industrial Technology Research Institute Infineon Technologies Initio Corporation INJOINIC TECHNOLOGY Innolux Corporation InnoSenT-Innovative Radar Sensor Technology Innovative Sensor Technology IST Innuovo Magnetics Co Inova Semiconductors InPlay Inc. InPower Semiconductor INTEGRAL JSC Integrated Circuit Solution Integrated Circuit Systems Integrated Crystal Technology Integrated Device Technology Integrated Sensor Technologies Integrated Silicon Solution Intel Corporation InterFET Corp Interlink Electronics International CMOS Technology International Rectifier Intersil Corporation Intronic Semiconductor Intronics Power, Inc InvenSense Inc IQD Frequency Products Ltd IRAN Ironwood Electronics IRXON Electronic Isabellenhütte Heusler GmbH &amp; Co KG Isahaya Electronics Co iSentek Technology Isocom Components Isotek Corp ITE Tech ITT Cannon, LLC ITT Semiconductors Ituner Networks Corp iWatt Inc IXYS Integrated Circuits J.S.T. Mfg. Co JACKSON ELECTRONICS IND. CROP. JAE Electronics JAI Ltd Jamicon Electronics JAVAN JCET Group Co JCI Jewel Hill Electronic Co JHDLCM Electronics Jiangsu Changjiang Electronics Jiangsu Donghai Semiconductor Jiangsu Juguang Jiangsu Runic Technology Co Jiangsu Szdhdtgd Electronics Jiangxi Jia Wei Cheng Electronic Jilin Sino-Microelectronics Co Jinan USR IOT Technology JING LI Power Electronics Jingcheng Electronics Co Jinghan Switch Electronic JMicron Technology Corp JNHuaMao Technology JODO International Johanson Dielectrics Johanson Technology Johnson Electric JPC Company JYE Tech Ltd JYH HSU(JEC) ELECTRONICS Kai Suh Suh Enterprise KSS Kaida Holding Kaihua Electronics Co Kangmu Sheng Electronics Ka-Ro electronics GmbH. KEC Semiconductor Keil Elektronik Keithley Instruments Kelly Controls, LLC KEMET Corporation Key Technology Keysight Technologies Keystone Electronic King Core Electronics Kingbor Technology Kingbright Electronic KingCCTV Technology Kingdatron Electronic Industrial Co Kingsignal Technology Kingstate Electronics Kingston KIOXIA America, Inc Kiwi Instruments Corp Knowles Electronics KOA Speer Electronics Kobiconn Kodenshi Corp Kohshin Electric Corporation KONE Elevator Kontron S&amp;T KT Micro Inc Kunshan Sino Silicon Technology KUOYUH W.L. Enterprise Co Kutai Electronics Kycon, Inc Kyocera Corporation Ladder Electronics Co Laird Performance Materials. Laird Technologies Laser Components Lattice Semiconductor LawMate International L-com, Inc LD-PD Inc. Leadtrend Technology Corp LEAP Electronic Legerity, Inc Lelon Electronics Corp LEM Components LEMO Lenovo LENZE Lesfuse Electric Co Leshan Radio Co LG Semiconductor LG.Philips Displays Lianchao Future Technology Lighting Integration System Ligitek Electronics Co Lime Microsystems Lineage Power Private Limited Linear Systems Linear Technology Linfinity Microelectronics Link-PP Int'l Technology LinkSmart LINP OMTER International Linx Technologies Lision Technology LITE-ON Semiconductor Littelfuse Inc Lixin Electromagnetic Clutch LIZE Electronic Technology LND, INC LOETRONIC LOGIC Devices Incorporated Longtech Optics Co Longview Technologies Co Lovid International Electronic Low Power Radio Solutions Ltd LOZEN TECHNOLOGY LS ELECTRIC LS Mtron Ltd LSI Computer Systems LTKCHIP LTN Servotechnik GmbH Lucent Technologies LUCKFOX Technology Lucky Light Electronic Luguang Electronic Technology Lumberg Holding Lumentum Operations LLC. Lumex Inc Lumileds Luminus, Inc. Lumissil Microsystems Luna Optoelectronics Lutron Electronic Enterprise Co Lyontek Inc M.S. Kennedy Corp M+R Multitronik GmbH MACOM Technology Macroblock, Inc Macronix International MacTek Corp MagnaChip Semiconductor Magnetics MagnTek Microelectronics Magtek Technology Inc Manorshi Electronics Marktech Optoelectronics, Inc Marlow Industries, Inc Marquardt Switches, Inc Marvell International Matsushita Electric Max Echo Technology Corp MaxBotix Inc Maxic Technology Corporation Maxim Integrated MaxLinear Inc Maxon motor Maxwell Technologies Mayloon Electronic Company MCS Logic Inc Mcuzone International MEAN WELL Enterprises Co Measurement Specialties Mechanic MediaTek Inc Megatek Melexis Technologies Memory Protection Devices MEMSIC, Inc Mentor GmbH Mercury Electronic Meritek Electronics Corporation Mersen EP Metalink Broadband Meticom GmbH. METRODYNE MICROSYSTEM CORP. MIC Electronic Micrel, Inc Micro Commercial Components Micro Crystal AG Micro Electronics Micro Linear Micro One Electronics Micro Power Systems MICRO SENSOR CO;LTD Microchip Technology Microdiode Semiconductor Micrometals, Inc Micron Technology Micronet Communication Microsemi Corporation Microtech Technology Co Ltd Microtherm Sentronic GmbH Microtips Technology Midori Precisions MikroElektronika MikroElektronika d.o.o MikroTik Mill-Max Mfg Milnec Interconnect Systems MindMotion Microelectronics Co. Mingtek Electronics Ltd Mini-Circuits Minilogic Device Corporation Ltd Minmax Technology Minsoo Electronic Co MiTAC Computing Technology Mitel Semiconductor Mitsubishi Electric Mitsubishi Rayon Co Mitsumi Electric Co Mixed Signal Integration Mixic Electronics MKMX America LLC MMI Semiconductors MOAI electronics co Mobicon Electronic Component Modulestek Inc MOKO TECHNOLOGY LTD. Molex Electronic Monitor Enterprises Inc Monolithic Power Systems Morethanall Co Morningstar Corporation MORNSUN Science &amp; Technology Mosdesign Semiconductor Corp Mosel Vitelic Co MOSPEC Semiconductor MOS-TECH Semiconductor Mostek MOTIEN Technology Motorola Mstar Semiconductor M-Systems Inc Multicomp Multi-Inno Technology Multi-Tech Systems Inc Murata Manufacturing Co MVSILICON MYIR Tech Myrra SAS Naina Semiconductor Limited. Nanjing Haichuan Electronic Nanjing Ouzhuo Tech Nanjing Qinheng Microelectronics Nanjing Shiheng Elec NanJing Top Power ASIC Nanjing Up Electronic Technology Nanjing Wotian Technology Co Nanjing Zeming Electronic Co Nanya Technology Co National Instruments National Semiconductor NDK America Inc NEC Electronics Nell Semiconductor Neltron Industrial Nemoto Sensor Engineering NeuroSky, Inc. Neutrik New Jersey Semiconductor NewAE Technology Inc. Newava Technology Inc. Newhaven Display Newport Corporation NewTec Display Co NexFlash Technologies, Inc Nexperia USA Inc Nextchip Nextion NIC Components Corp. Nichia Corporation Nichicon Corporation Nidec Copal Electronics NIDEC SERVO CORPORATION. Nihon Dempa Kogyo Nihon Inter Electronics NIKO Semiconductor Ningbo East Electronics Ningbo ForwardRelayCorporationLTD Ningbo Gosun Technology Co Ningbo Huaguan Electronics Ningbo KLS Electronic Co Ningbo MAX Electronic Technology Co., Ltd Ningbo MKX Electronic Technology Ningbo Rel Electric Co., Ltd. Ningbo Songle Relay Ningbo Tianbo Ganglian Electronics Ninigi Nippon Chemi-Con Nippon Pulse America, Inc Nisshinbo Micro Devices Inc NJR Corporation NKK Switches NMB Technologies Non-Brand Norcomp Inc Nordic Semiconductor Noritake Itron Co Novacap Novatek Microelectronics NTE Electronics NUAND LLC. Nuvoton Technology NVE Corporation Nvidia NVS Navigation Technologies NXP Semiconductors NYS Resistor O2Micro OCIC co Octavo Systems LLC Ogemray Technology Co Ohmite OKI Semiconductor Ole Wolff Electronics Inc Olimex OmniVision Technologies Omron Electronics Omten Electronics ON Semiconductor ON Semiconductor CHINA On Shore Technology On-Bright Electronics OPTEK Technology Inc OPTi Inc Opticon Inc Opto 22 Opto Diode Corp Opto Electronics Co,. LTD OPTOLAB Microsystems Orient Display Oriental Semiconductor Orion Orion Display Technology Co OSI Optoelectronics OSRAM Opto Semiconductors OTAX Corporation Other Oupiin Enterprise Co OWON Technology Inc P&amp;E Microcomputer Systems Pacific Silicon Sensor Panasonic Corporation Panavision Imaging LLC Pancon Corporation PandaBoard PANJIT International Inc Para Light Electronics P-DUKE Technology Co PEAK Electronics GmbH PEAK-System Technik Penny &amp; Giles Peregrine Semiconductor Pericom Semiconductor Corp PerkinElmer Inc Phidgets, Inc Philips Semiconductor Phison Electronics Phoenix Contact Pickering Electronics Ltd PICO Electronics Pico Technology Piher Sensors &amp; Controls SA Pingjing Semi Technology PIR Sensor Co PixArt Imaging Inc Planar Systems, Inc PLX Technology PMC-Sierra, Inc PNI Sensor Corporation POCO Magnetic Polyfet RF Devices Polytronics Technology Pomona Electronics Power Integrations Power Mate Technology Power Systems GmbH Power-Changer Electronic Co Powerex Inc PowerPlaza Powersem GmbH Powertip Technology Preci-Dip SA Precision Monolithics, Inc PREMA Semiconductor GmbH Premier Magnetics PRETEC/C-One Technology Corp. Princeton Technology Proant AB Profichip GmbH Prokit's Industries Prolific Technology Inc Promax-Johnton Semiconductor Pro-Signal ProTek Devices Pro-Wave Electronic PRT PUI Audio Pulse Electronics Qimei Optical &amp; Electric Qingdao Mefine Electronics Qingxian Zeming Langxi Electronic Devices Co Qingyuan Tesla Electronic Technology Qorvo QT Brightek (QTB) QT Optoelectronics Qualcomm Atheros, Inc Quality Semiconductor Qualtek Electronics Quarton inc Quasar Electronics Limited Quectel Wireless Solutions QuickLogic Corporation QX Micro Devices Radiall Radxa Computer Rafael Microelectronics RAFI GmbH &amp; Co RAiO TECHNOLOGY INC RAKwireless Technology Limited. RALEC Ltd Ralink Technology Raltron Electronics Corporation Ramtron International Rapid Electronics Ltd Raspberry Pi Raycom Co Raytac Corporation. Raytheon RCA Corporation Ready Made RC LLC Realtek Semiconductor RECOM Power GmbH Rectron Semiconductor Reichelt elektronik GmbH &amp; Co. KG RELPOL S.A Renata SA Renesas Technology Renhotec Group Ltd Reomax Electronics Reyed Electronics Co RF Digital Corporation. RF Micro Devices RF Solutions Ltd RFaxis, Inc RFHIC Corporation RFM Integrated Device, Inc. RFT Mikroelektronik Rhombus Industries Inc Richtek Technology Co RichWave Technology Ricoh Electronic Devices Riedon RIGOL Ring&amp;tone Electronic Technology Riverdi RLS Merilna tehnika d.o.o ROBOTIS Co Rockwell Rogers Corporation ROHM Semiconductor Roithner Lasertechnik GmbH Rongtech Industry Royal Electronic Factory Co RS Components Ltd RTD Embedded Technologies Rubycon RYCHIP Semiconductor s.m.a.e. GmbH Saft Groupe S.A Sagami Electronics Saia-Burgess Switches Sakae Tsushin Kogyo Saleae, Inc Salecom Electronics Same Sky SamHop Microelectronics Samsung Electronics Samtec Samwha Capacitor Samwin Electronic Technology Samyoung S &amp; C Co SANCO Electronics Co SanDisk Sanhe Enclosure Sanjiaozhou Electrical Technology Sanken Electric SanRex Corporation Sanyo Denki Sanyo Electric Savantic Electronic Sawnics Inc Schaffner Group Schott AG Schrack Technik GmbH Schurter Inc Sciosense B.V. SCTF Electronics Seagate Technology LLC Seaparks Machinery-Electronics Seaward Electronics SeCoS Corporation SEED International Ltd Seeed Technology SEEQ Technology Segger Microcontroller Systems Seiko Instruments Inc Seiko NPC Corporation Semiconductor Circuits, Inc SemiHow Semikron Semiment Technologies Semi-Powerex Corp. SEMITEC Corporation SemiWell Semiconductor Semtech Corporation Semtech Electronics Senba Sensing Technology Co Sendo Sensor Sensata Technologies Sensirion Sentry Manufacturing Inc SEP Electronic Corp Servotecnica SpA SERVO-TEK PRODUCTS COMPANY, INC. SG Micro Corp SGX Sensortech Shaanxi Fullstar Electronics Co Shaanxi Qunli Electric Shaanxi Reactor Microelectronics Shandong Jingdao Microelectronics Shanghai AVIC Optoelectronics Shanghai Belling Co,Ltd Shanghai Consonance Electronics Shanghai Fengxin Electronic Technology Shanghai Fudan Microelectronics Shanghai Gotop Technology Shanghai High-Flying Electronics Shanghai Houde Photo-electric Shanghai Mixinno Microelectronics Co Shanghai Natlinear Electronics Shanghai Xinlong Semiconductor Shanghai Zhichuan Electronic Tech SHARP Corporation Sheng Jay Automation Techno Shenyang Guangcheng Technology Co., Ltd Shenyang KingStar Automation ShenZhen AI-thinker CO Shenzhen AnBoShi Electronic Shenzhen Asenware Test Shenzhen Baishan Mechatronics Shenzhen Biosled Technology Shenzhen Bolutek Technology Shenzhen Chipsea Technologies ShenZhen ChipSourceTek Technology Shenzhen ExSAF Electronics Co Shenzhen Genesis-Systech ShenZhen Gerbole Shenzhen Getech Co Shenzhen GUANGSHIMEI Electronic Shenzhen Hanxia Electronics Shenzhen Haolin Electronics Shenzhen Heliwei Technology Shenzhen honglifa Electronics Co Shenzhen HongyeX Electronics Co ShenZhen HuaXinAn Electronics Co.,Ltd Shenzhen Injoinic Technology Co. Shenzhen Jin Yu Semiconductor Co ShenZhen JINCI Technology Shenzhen Jinrui Electronic Material Co Shenzhen JMRTH Co Shenzhen Kaiyuexiang Electronics Co Shenzhen LFN Technology Co Shenzhen Lodestar S.T Co Shenzhen Lumen Electronics Shenzhen Magnetic Technology Shenzhen MilkV Technology Shenzhen Milliohm Electronics Shenzhen Minewsemi Co., Ltd Shenzhen Nsiway Tech Shenzhen Ou Chuangxin Semiconductor ShenZhen Qi Dian Shi Dai Technology Shenzhen Ruichips Semiconductor Shenzhen Ruilongyuan Electronics Shenzhen Shiji Lighting Shenzhen SI Semiconductors Shenzhen SLKOR Micro Semicon Co Shenzhen Sunmoon Microelectronics Shenzhen Suosemi Tech Shenzhen TongYiFang Optoelectronic Technology CO,Ltd Shenzhen Topmay Electronic Shenzhen TPOWER Semiconductor Shenzhen Universal Micro-Electronics Shenzhen USBR Precision Hardware Electronics Shenzhen Weidy Industrial Development Co., Ltd. Shenzhen Xinbole Electronics Co. Shenzhen Xptek Technology Shenzhen Xunlong Shenzhen Yangxing Technology Co. SHENZHEN YeZhan Electronics Shenzhen Yiwei Technology Shenzhen ZVELL Electronics Shindengen Electric Shin-Etsu Chemical Co SHINYEI Technology SHOEI SIBA GmbH Sichuan huafeng enterprise group SICK, Inc. Siemens Semiconductor Group Si-En Technology SiFirst Technology SiGe Semiconductor Sigma Microelectronics Signetics Silego Technology Silergy Corp Silicon Image Silicon Integrated Systems Silicon Laboratories Silicon Microstructures, Inc. Silicon Motion, Inc Silicon Sensing Systems Limited Silicon Standard Corp Silicon Storage Technology Silicon Systems Inc Silicon Touch Technology Silvan Chip Electronics Silver Telecom Ltd SilverStone Technology SIMCom Wireless Solutions SIMTEK Electronic Components Sinda Photoelectricity Technology SINGULAR TECHNOLOGY CO., LTD. Sinomags Technologies Co Sinopower Semiconductor Sipex Corporation Sirectifier Semiconductors SiTime Corporation Sivago Semiconductor Co SIWARD Crystal Technology Siyang Microelectronics Sizto Tech Corp SKYLAB M&amp;C Technology Skyworks Solutions, Inc SL Power Electronics Corp. SMAR Smartec BV SMC Diode Solutions Co. Smiths Interconnect. SMSC Corporation Soberton Inc Softing Automotive Electronics Sola/Hevi-Duty Sola-IC Solarflex SA Soldex Solid State Scientific SOLIDIC Solitronics Engineering Limited SOL-LED Lighting Co Solomon Systech Song Chuan Song Huei Electric Sonix Technology Sony Corporation Soundwell Electronic South African Micro-Electronic Systems Spansion inc SparkFun Electronics SPEC Sensors LLC Spectra Symbol Corp. Spectrum Digital Incorporated Speed Tech Corp Spin Semiconductor Sprague Semiconductors SPX Flow Technology ST Engineering Stackpole Electronics Standex-Meder Electronics Stannol GmbH Stanson Technology StarChips Technology StarPower Semiconductor Ltd. Startek Electronic Technology STATEK CORPORATION Stäubli International AG. STCmicro Technology Co Stewart Connector STMicroelectronics Stocko Stork Solutions Ltd. Sullins Connector Solutions SUMIDA Corporation Sun Hydraulics Corporation Sun Microelectronics SunLED SUNLORD Sunltech Tech SUNMATE Electronic Sunonwealth Electric Machine Sunplus Technology Sunrise Electronics Suntan Technology Company Suntsu Electronics, Inc. SUNYUAN Technology Supertex Inc Susumu International Suzhou Innoson Technology Suzhou NOVOSENSE Microelectronics Co., Ltd Suzhou Silikron Semiconductor Corp Switchcraft Inc. Switec SYNC Power Crop SyncMOS Technologies Synoxo International System General Corp Tadiran Batteries TAG Semiconductors TA-I Technology TAIKO-NET Tai-Saw Technology Tai-Tech Advanced Electronics Taitien Electronics Taitron Components, Inc Taiwan Alpha Electronic Co Taiwan Semiconductor Taiyo Electric Co Taiyo Yuden Tak Cheong Electronics Talema Group, LLC Tamagawa seiki Co Tamron Tamura Corporation TANCAP Technology Taoglas Limited TDK Corporation (EPCOS) TDK-Lambda Corporation TDK-Micronas GmbH TE Connectivity Team Source Display tech.co,ltd. Techcode Semiconductor Techpoint Inc Techspray/Plato-EMX Enterprises Limited Techstar Electronics TechToys Company TelCom Semiconductor Telcon Ltd Telechips Inc Teledyne Technologies TELEFUNKEN Elektroakustik Telegesis Ltd Telit TEMIC Semiconductor Terawins, Inc Teridian Semiconductor TESLA Testo SE &amp; Co Texas Advanced Optoelectronic Solutions Texas Instruments THAT Corporation Thegioiic Corporation Thermonamic Electronics(Jiangxi) Corp THine Electronics, Inc Thinki Semiconductor Thinking Electronic THOMSON Inc THORLABS Thousand Hundred Industrial Thunder Precision Resistor TIANMA Titan Micro TLC Electronics TNI-U TOOL Token Electronics Industry Tokmas Semiconductor TOKO, Inc Tontek Design Technology Top-arm Topro Technology Topway Technology Torex Semiconductor Toshiba Corporation touchSEMI TOYO LED ELECTRONICS LIMITED. TOYODA TR Electronic Nordic AB. Traco Electronic AG Transcom, Inc Transko Electronics, Inc. TRENDnet, Inc Trenz Electronic Triad Magnetics Trident Microsystems Trimble Inc TRINAMIC Motion Control TRinno Technology Co Tripath Technology TriQuint Semiconductor Truly Semiconductors TRW Inc TT Electronics TTM Technologies, Inc. TXC Corporation UBIQ Semiconductor Ubiquiti Inc u-blox UCE Ultrasonic Co UDF Semiconductor Ultisensor Electronics UNI SEMICONDUCTOR LIMITED Unicorn Microelectronics Corporation Unictron Technologies Corporation. Union Semiconductor Uniroyal Electronics Industry Co Unisonic Technologies Unitra Cemi Uni-Trend Technology Co Unitrode Corporation Universal Microelectronics UPI Semiconductor Corp US Digital US Micro Products. Usha India Ltd Ushio Opto Semiconductors UTRON Technology, Inc Vacuumschmelze GmbH VADEM LTD Vango Technologies, Inc Varitronix Limited VARTA AG Vatronics Technologies Ltd VBsemi Electronics Co. Ltd V-Chip Microsystems VectorNav Vectron International Vehicles instrumentation Device Venkel Ltd VIA Technologies Vicor Corporation Vigortronix Ltd. Vincotech Vishay Visual communication company Vitesse Semiconductor Vivesea VLSI Solution Vweb Corporation W. L. Gore &amp; Associates, Inc WAGO Kontakttechnik GmbH Wakefield Thermal, Inc. Walsin Technology Corporation Walter Electronic Co WanTcom, Inc Wavecom Waveshare Electronics Wavespectrum Laser Inc Wavetronics Technologies WAYTRONIC ELECTRONIC CO.LTD WeEn Semiconductors Weidmüller Interface GmbH Weipu connector Weltrend Semiconductor WENSHING Electronics Western Digital Corporation Willas Electronic Corp WIMA Winbond Electronics </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>53300</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>106600</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AOD514</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Q1,Q2,Q3,Q4</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TO-252-2_L6.6-W6.1-P4.57-LS9.9-BR-CW</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>https://shop.ideaelec.com/product/aod4184a/?utm_medium=PPC&amp;utm_source=Torob</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ERROR: 403 Client Error: Forbidden for url: https://shop.ideaelec.com/product/aod4184a/?utm_medium=PPC&amp;utm_source=Torob</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BC817-40,215</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Q5,Q6</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SOT-23-3_L2.9-W1.6-P1.90-LS2.8-BR</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/category/202/switches/%d8%b3%d9%88%d8%a6%db%8c%da%86-%d9%88-%da%a9%d9%84%db%8c%d8%af#dtl/7760</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>10900</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>21800</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Designator</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Footprint</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>100Ω</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>R1,R11</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>100Ω</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/product/4021/non-brand/resistor-3-3kohms-0805-1%25-smd/%D9%85%D9%82%D8%A7%D9%88%D9%85%D8%AA-3-3-%DA%A9%DB%8C%D9%84%D9%88-%D8%A7%D9%87%D9%85-1-%D8%AF%D8%B1%D8%B5%D8%AF-0805-smd#dtl/17318</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>مقاومت 3.3 کیلو اهم 1 درصد 0805 smd خانه دسته‌بندی‌ها All Products Passive Components Resistors Film Resistors Thick Film Resistors-SMD اوریجینال مقاومت 3.3 کیلو اهم 1 درصد 0805 smd نام قطعه: RESISTOR 3.3KOHMS 0805 1% SMD نام کارخانه‌ای: SER0805F3301AR برند: Non-Brand کشور سازنده: چین پکیج: 0805 2012 بسته‌بندی: Tape &amp; Reel - 5,000 عدد حداقل: 50 عدد ضریب: 50 عدد عنوان گروه: Thick Film Resistors-SMD دیتاشیت: SER0805F3301AR Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات مقاومت 3.3 کیلو اهم 1 درصد 0805 smd مقاومت 3.3 کیلو اهم 1 درصد 0805 smd از خانواده مقاومت اس ام دی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج 0805 مقاومت 3.3 کیلو اهم توان (وات) 125 میلی وات دقت 1 درصد نوع قرار گیری SMD مقدار ولتاژ DC 150 ولت حداقل دمای عملیاتی -55 درجه سانتیگراد حداکثر دمای عملیاتی +155 درجه سانتیگراد کاربرد General Application حداقل ضریب دمایی -100 ضریب دمایی حداکثر ضریب دمایی 100 ضریب دمایی RESISTOR 3.3KOHMS 0805 1% SMD یک مقاومت ثابت (فیلم ضخیم) از نوع SMD با دقت بالا است. این قطعه در پکیج استاندارد 0805 ارائه می‌شود و با داشتن تلورانس دقیق 1% و پایداری مناسب، گزینه‌ای ایده‌آل برای کاربردهایی است که به دقت بیشتر و تکرارپذیری بهتر نسبت به نوع 5% معمولی نیاز دارند، مانند مدارهای اندازه‌گیری، مرجع و تقویت‌کننده‌های دقیق. 🧩 مشخصات کلی: نوع: مقاومت ثابت (Fixed Resistor) فناوری: فیلم ضخیم (Thick Film) - نوع دقیق 💡 کاربردهای اصلی: مدارهای دقیق تقسیم ولتاژ (Precision Voltage Dividers): در مدارهای سنسور، مرجع ولتاژ و نمونه‌برداری سیگنال‌های آنالوگ. مقاومت‌های فیدبک و تقویت‌کننده‌های عملیاتی (Op-Amp Circuits): برای تعیین بهره دقیق و پایداری مدار. مدارهای زمان‌بندی با دقت متوسط: در ترکیب با خازن‌های با دقت مناسب. مقاومت‌های Pull-up/Pull-down دقیق: در خطوطی که سطح ولتاژ آستانه دقیقی مورد نیاز است. مدارهای تطبیق امپدانس (Impedance Matching): در کاربردهای فرکانس بالا و خطوط انتقال. کاربردهای عمومی با نیاز به تکرارپذیری بالا در منابع تغذیه دقیق، ابزار دقیق و سیستم‌های اندازه‌گیری. ✅ مزایا: دقت 1%: انحراف بسیار کم از مقدار اسمی، که منجر به عملکرد قابل پیش‌بینی‌تر و تکرارپذیرتر مدار می‌شود. پکیج 0805: اندازه متعادل و مناسب برای مونتاژ، با قابلیت تحمل توان 125mW. ولتاژ کاری 150V: حاشیه اطمینان ولتاژی بالا برای اکثر کاربردهای صنعتی و مصرفی. TCR بهبودیافته: ضریب دمایی معمولاً بهتر از مقاومت‌های 5%، که پایداری بهتری در برابر تغییرات دما ایجاد می‌کند. قیمت مقرون‌به‌صرفه: نسبت به مقاومت‌های فیلم نازک (Thin Film) یا‌های دقیق، هزینه کمتری دارد. دامنه دمایی وسیع: عملکرد مطمئن در محیط‌های صنعتی. 🎯 جمع‌بندی: این مقاومت 3.3 کیلواهم با دقت 1% در پکیج 0805، یک ارتقاء مستقیم و مقرون‌به‌صرفه نسبت به نوع 5% است که دقت، تکرارپذیری و پایداری دمایی بهتری را برای طراحی‌های حساس‌تر ارائه می‌دهد. این قطعه تعادل خوبی بین عملکرد، هزینه و اندازه برقرار می‌کند و برای اکثر کاربردهای صنعتی، ابزار دقیق و مصرفی با نیاز به دقت بالا گزینه‌ای ایده‌آل است. با این حال، برای مدارهای با دقت و پایداری حساسیت بحرانی ، باید محدودیت‌های ذاتی فناوری فیلم ضخیم (TCR و اثر ولتاژ) در نظر گرفته شود. Features انتخاب ویژگی Resistance 3.3 kΩ ≤ = ≥ Power Rating 125 mW ≤ = ≥ Tolerance 1 % ≤ = ≥ Voltage Rating DC 150 V ≤ = ≥ Temperature Coefficient (Min) -100 PPM/°C ≤ = ≥ Temperature Coefficient (Max) 100 PPM/°C ≤ = ≥ Application General Application Termination Style SMD Minimum Operating Temperature -55 °C ≤ = ≥ Maximum Operating Temperature +155 °C ≤ = ≥ Brand Non-Brand Package 0805 جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 85 6,280 ریال 5,960 ریال 1,000
+                                                        عدد 5,650 ریال 5,000
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>6280</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>12560</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1.8kΩ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>R2,R12</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1.8kΩ</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/product/4021/non-brand/resistor-3-3kohms-0805-1%25-smd/%D9%85%D9%82%D8%A7%D9%88%D9%85%D8%AA-3-3-%DA%A9%DB%8C%D9%84%D9%88-%D8%A7%D9%87%D9%85-1-%D8%AF%D8%B1%D8%B5%D8%AF-0805-smd#dtl/50038</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>مقاومت 3.3 کیلو اهم 1 درصد 0805 smd خانه دسته‌بندی‌ها All Products Passive Components Resistors Film Resistors Thick Film Resistors-SMD اوریجینال مقاومت 3.3 کیلو اهم 1 درصد 0805 smd نام قطعه: RESISTOR 3.3KOHMS 0805 1% SMD نام کارخانه‌ای: SER0805F3301AR برند: Non-Brand کشور سازنده: چین پکیج: 0805 2012 بسته‌بندی: Tape &amp; Reel - 5,000 عدد حداقل: 50 عدد ضریب: 50 عدد عنوان گروه: Thick Film Resistors-SMD دیتاشیت: SER0805F3301AR Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات مقاومت 3.3 کیلو اهم 1 درصد 0805 smd مقاومت 3.3 کیلو اهم 1 درصد 0805 smd از خانواده مقاومت اس ام دی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج 0805 مقاومت 3.3 کیلو اهم توان (وات) 125 میلی وات دقت 1 درصد نوع قرار گیری SMD مقدار ولتاژ DC 150 ولت حداقل دمای عملیاتی -55 درجه سانتیگراد حداکثر دمای عملیاتی +155 درجه سانتیگراد کاربرد General Application حداقل ضریب دمایی -100 ضریب دمایی حداکثر ضریب دمایی 100 ضریب دمایی RESISTOR 3.3KOHMS 0805 1% SMD یک مقاومت ثابت (فیلم ضخیم) از نوع SMD با دقت بالا است. این قطعه در پکیج استاندارد 0805 ارائه می‌شود و با داشتن تلورانس دقیق 1% و پایداری مناسب، گزینه‌ای ایده‌آل برای کاربردهایی است که به دقت بیشتر و تکرارپذیری بهتر نسبت به نوع 5% معمولی نیاز دارند، مانند مدارهای اندازه‌گیری، مرجع و تقویت‌کننده‌های دقیق. 🧩 مشخصات کلی: نوع: مقاومت ثابت (Fixed Resistor) فناوری: فیلم ضخیم (Thick Film) - نوع دقیق 💡 کاربردهای اصلی: مدارهای دقیق تقسیم ولتاژ (Precision Voltage Dividers): در مدارهای سنسور، مرجع ولتاژ و نمونه‌برداری سیگنال‌های آنالوگ. مقاومت‌های فیدبک و تقویت‌کننده‌های عملیاتی (Op-Amp Circuits): برای تعیین بهره دقیق و پایداری مدار. مدارهای زمان‌بندی با دقت متوسط: در ترکیب با خازن‌های با دقت مناسب. مقاومت‌های Pull-up/Pull-down دقیق: در خطوطی که سطح ولتاژ آستانه دقیقی مورد نیاز است. مدارهای تطبیق امپدانس (Impedance Matching): در کاربردهای فرکانس بالا و خطوط انتقال. کاربردهای عمومی با نیاز به تکرارپذیری بالا در منابع تغذیه دقیق، ابزار دقیق و سیستم‌های اندازه‌گیری. ✅ مزایا: دقت 1%: انحراف بسیار کم از مقدار اسمی، که منجر به عملکرد قابل پیش‌بینی‌تر و تکرارپذیرتر مدار می‌شود. پکیج 0805: اندازه متعادل و مناسب برای مونتاژ، با قابلیت تحمل توان 125mW. ولتاژ کاری 150V: حاشیه اطمینان ولتاژی بالا برای اکثر کاربردهای صنعتی و مصرفی. TCR بهبودیافته: ضریب دمایی معمولاً بهتر از مقاومت‌های 5%، که پایداری بهتری در برابر تغییرات دما ایجاد می‌کند. قیمت مقرون‌به‌صرفه: نسبت به مقاومت‌های فیلم نازک (Thin Film) یا‌های دقیق، هزینه کمتری دارد. دامنه دمایی وسیع: عملکرد مطمئن در محیط‌های صنعتی. 🎯 جمع‌بندی: این مقاومت 3.3 کیلواهم با دقت 1% در پکیج 0805، یک ارتقاء مستقیم و مقرون‌به‌صرفه نسبت به نوع 5% است که دقت، تکرارپذیری و پایداری دمایی بهتری را برای طراحی‌های حساس‌تر ارائه می‌دهد. این قطعه تعادل خوبی بین عملکرد، هزینه و اندازه برقرار می‌کند و برای اکثر کاربردهای صنعتی، ابزار دقیق و مصرفی با نیاز به دقت بالا گزینه‌ای ایده‌آل است. با این حال، برای مدارهای با دقت و پایداری حساسیت بحرانی ، باید محدودیت‌های ذاتی فناوری فیلم ضخیم (TCR و اثر ولتاژ) در نظر گرفته شود. Features انتخاب ویژگی Resistance 3.3 kΩ ≤ = ≥ Power Rating 125 mW ≤ = ≥ Tolerance 1 % ≤ = ≥ Voltage Rating DC 150 V ≤ = ≥ Temperature Coefficient (Min) -100 PPM/°C ≤ = ≥ Temperature Coefficient (Max) 100 PPM/°C ≤ = ≥ Application General Application Termination Style SMD Minimum Operating Temperature -55 °C ≤ = ≥ Maximum Operating Temperature +155 °C ≤ = ≥ Brand Non-Brand Package 0805 جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 85 6,280 ریال 5,960 ریال 1,000
+                                                        عدد 5,650 ریال 5,000
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>6280</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>12560</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>100kΩ</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>R3,R13</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>100kΩ</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/product/4021/non-brand/resistor-3-3kohms-0805-1%25-smd/%D9%85%D9%82%D8%A7%D9%88%D9%85%D8%AA-3-3-%DA%A9%DB%8C%D9%84%D9%88-%D8%A7%D9%87%D9%85-1-%D8%AF%D8%B1%D8%B5%D8%AF-0805-smd#dtl/18246</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>مقاومت 3.3 کیلو اهم 1 درصد 0805 smd خانه دسته‌بندی‌ها All Products Passive Components Resistors Film Resistors Thick Film Resistors-SMD اوریجینال مقاومت 3.3 کیلو اهم 1 درصد 0805 smd نام قطعه: RESISTOR 3.3KOHMS 0805 1% SMD نام کارخانه‌ای: SER0805F3301AR برند: Non-Brand کشور سازنده: چین پکیج: 0805 2012 بسته‌بندی: Tape &amp; Reel - 5,000 عدد حداقل: 50 عدد ضریب: 50 عدد عنوان گروه: Thick Film Resistors-SMD دیتاشیت: SER0805F3301AR Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات مقاومت 3.3 کیلو اهم 1 درصد 0805 smd مقاومت 3.3 کیلو اهم 1 درصد 0805 smd از خانواده مقاومت اس ام دی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج 0805 مقاومت 3.3 کیلو اهم توان (وات) 125 میلی وات دقت 1 درصد نوع قرار گیری SMD مقدار ولتاژ DC 150 ولت حداقل دمای عملیاتی -55 درجه سانتیگراد حداکثر دمای عملیاتی +155 درجه سانتیگراد کاربرد General Application حداقل ضریب دمایی -100 ضریب دمایی حداکثر ضریب دمایی 100 ضریب دمایی RESISTOR 3.3KOHMS 0805 1% SMD یک مقاومت ثابت (فیلم ضخیم) از نوع SMD با دقت بالا است. این قطعه در پکیج استاندارد 0805 ارائه می‌شود و با داشتن تلورانس دقیق 1% و پایداری مناسب، گزینه‌ای ایده‌آل برای کاربردهایی است که به دقت بیشتر و تکرارپذیری بهتر نسبت به نوع 5% معمولی نیاز دارند، مانند مدارهای اندازه‌گیری، مرجع و تقویت‌کننده‌های دقیق. 🧩 مشخصات کلی: نوع: مقاومت ثابت (Fixed Resistor) فناوری: فیلم ضخیم (Thick Film) - نوع دقیق 💡 کاربردهای اصلی: مدارهای دقیق تقسیم ولتاژ (Precision Voltage Dividers): در مدارهای سنسور، مرجع ولتاژ و نمونه‌برداری سیگنال‌های آنالوگ. مقاومت‌های فیدبک و تقویت‌کننده‌های عملیاتی (Op-Amp Circuits): برای تعیین بهره دقیق و پایداری مدار. مدارهای زمان‌بندی با دقت متوسط: در ترکیب با خازن‌های با دقت مناسب. مقاومت‌های Pull-up/Pull-down دقیق: در خطوطی که سطح ولتاژ آستانه دقیقی مورد نیاز است. مدارهای تطبیق امپدانس (Impedance Matching): در کاربردهای فرکانس بالا و خطوط انتقال. کاربردهای عمومی با نیاز به تکرارپذیری بالا در منابع تغذیه دقیق، ابزار دقیق و سیستم‌های اندازه‌گیری. ✅ مزایا: دقت 1%: انحراف بسیار کم از مقدار اسمی، که منجر به عملکرد قابل پیش‌بینی‌تر و تکرارپذیرتر مدار می‌شود. پکیج 0805: اندازه متعادل و مناسب برای مونتاژ، با قابلیت تحمل توان 125mW. ولتاژ کاری 150V: حاشیه اطمینان ولتاژی بالا برای اکثر کاربردهای صنعتی و مصرفی. TCR بهبودیافته: ضریب دمایی معمولاً بهتر از مقاومت‌های 5%، که پایداری بهتری در برابر تغییرات دما ایجاد می‌کند. قیمت مقرون‌به‌صرفه: نسبت به مقاومت‌های فیلم نازک (Thin Film) یا‌های دقیق، هزینه کمتری دارد. دامنه دمایی وسیع: عملکرد مطمئن در محیط‌های صنعتی. 🎯 جمع‌بندی: این مقاومت 3.3 کیلواهم با دقت 1% در پکیج 0805، یک ارتقاء مستقیم و مقرون‌به‌صرفه نسبت به نوع 5% است که دقت، تکرارپذیری و پایداری دمایی بهتری را برای طراحی‌های حساس‌تر ارائه می‌دهد. این قطعه تعادل خوبی بین عملکرد، هزینه و اندازه برقرار می‌کند و برای اکثر کاربردهای صنعتی، ابزار دقیق و مصرفی با نیاز به دقت بالا گزینه‌ای ایده‌آل است. با این حال، برای مدارهای با دقت و پایداری حساسیت بحرانی ، باید محدودیت‌های ذاتی فناوری فیلم ضخیم (TCR و اثر ولتاژ) در نظر گرفته شود. Features انتخاب ویژگی Resistance 3.3 kΩ ≤ = ≥ Power Rating 125 mW ≤ = ≥ Tolerance 1 % ≤ = ≥ Voltage Rating DC 150 V ≤ = ≥ Temperature Coefficient (Min) -100 PPM/°C ≤ = ≥ Temperature Coefficient (Max) 100 PPM/°C ≤ = ≥ Application General Application Termination Style SMD Minimum Operating Temperature -55 °C ≤ = ≥ Maximum Operating Temperature +155 °C ≤ = ≥ Brand Non-Brand Package 0805 جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 85 6,280 ریال 5,960 ریال 1,000
+                                                        عدد 5,650 ریال 5,000
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>6280</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>12560</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/product/4080/non-brand/resistor-10kohms-1206-5%25-smd/%D9%85%D9%82%D8%A7%D9%88%D9%85%D8%AA-10-%DA%A9%DB%8C%D9%84%D9%88-%D8%A7%D9%87%D9%85-1206-smd</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>مقاومت 10 کیلو اهم 1206 smd خانه دسته‌بندی‌ها All Products Passive Components Resistors Film Resistors Thick Film Resistors-SMD اوریجینال مقاومت 10 کیلو اهم 1206 smd نام قطعه: RESISTOR 10KOHMS 1206 5% SMD نام کارخانه‌ای: SER1206J0103AR برند: Non-Brand کشور سازنده: چین پکیج: 1206 3216 بسته‌بندی: Tape &amp; Reel - 5,000 عدد حداقل: 50 عدد ضریب: 50 عدد عنوان گروه: Thick Film Resistors-SMD دیتاشیت: SER1206J0103AR Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات مقاومت 10 کیلو اهم 1206 smd مقاومت 10 کیلو اهم 1206 smd از خانواده مقاومت اس ام دی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج 1206 مقاومت 10 کیلو اهم توان (وات) 250 میلی وات دقت 5 درصد نوع قرار گیری SMD مقدار ولتاژ DC 200 ولت حداقل دمای عملیاتی -55 درجه سانتیگراد حداکثر دمای عملیاتی +155 درجه سانتیگراد کاربرد General Application حداقل ضریب دمایی -100 ضریب دمایی حداکثر ضریب دمایی 100 ضریب دمایی RESISTOR 10KOHMS 1206 5% SMD یک مقاومت ثابت (فیلم ضخیم) از نوع SMD با احتمالاً پرکاربردترین مقدار مقاومت در صنعت الکترونیک. این قطعه در پکیج بزرگ‌تر و با توان بالاتر 1206 ارائه می‌شود که آن را برای کاربردهایی که نیاز به قابلیت اطمینان بالا، تحمل توان بیشتر یا عملکرد در شرایط محیطی سخت‌تر دارند، بهینه می‌سازد. مقاومت 10 کیلواهم سنگ بنای بی‌شمار مدار تقسیم ولتاژ، Pull-up، فیلتر و زمان‌بندی است. 🧩 مشخصات کلی: نوع: مقاومت ثابت (Fixed Resistor) فناوری: فیلم ضخیم (Thick Film) 💡 کاربردهای اصلی: تقسیم‌کننده ولتاژ جهانی: همراه با سنسورها (به ویژه ترمیستورهای 10kΩ)، پتانسیومترها و در ورودی‌های ADC. مقاومت Pull-up/Pull-down استاندارد صنعتی: برای پایه‌های دیجیتال، خطوط Reset و پیکربندی. مقاومت فیدبک در تقویت‌کننده‌های عملیاتی و منابع تغذیه. مدارهای فیلتر و زمان‌بندی RC: در ترکیب با خازن‌های نانوفارادی برای تولید ثابت‌های زمانی پرکاربرد. مقاومت‌های بایاس و بار در مدارهای آنالوگ. کاربردهای عمومی در هر حوزه‌ای از الکترونیک مصرفی تا صنعتی. ✅ مزایا: پرکاربردترین مقدار مقاومت: 10kΩ سلطان غیرقابل انکار مقاومت‌هاست. توان نامی عالی (250mW): حاشیه ایمنی حرارتی بسیار بالا نسبت به نیاز واقعی در کاربردهای سیگنالی، که قابلیت اطمینان را به حداکثر می‌رساند. ولتاژ کاری 200V: امکان استفاده ایمن در مدارهای با ولتاژهای آنالوگ بالاتر. TCR خوب (±100 ppm/°C): پایداری دمایی قابل قبول برای اکثر کاربردها. پکیج 1206: استحکام مکانیکی، مقاومت در برابر خمش برد و مدیریت حرارتی برتر. 🎯 جمع‌بندی: این مقاومت 10 کیلواهم در پکیج 1206 با دقت 5%، تجسم یک قطعه الکترونیکی ایده‌آل: پرکاربرد، فوق‌العاده بادوام و با قابلیت اطمینان استثنایی است. این مقاومت همه مزایای اساسی و جهانی 10kΩ را با استحکام فیزیکی و حاشیه عملکرد الکتریکی یک پکیج صنعتی‌تر ترکیب می‌کند. انتخاب آن به جای پکیج‌های کوچک‌تر، یک تصمیم هوشمندانه برای طراحی‌های حرفه‌ای، صنعتی و هر پروژه‌ای که در آن قابلیت اطمینان و طول عمر از حداقل فضای اشغالی مهم‌تر است محسوب می‌شود. این قطعه یک سرمایه‌گذاری مطمئن برای هر برد الکترونیکی است. Features انتخاب ویژگی Resistance 10 kΩ ≤ = ≥ Power Rating 250 mW ≤ = ≥ Tolerance 5 % ≤ = ≥ Voltage Rating DC 200 V ≤ = ≥ Temperature Coefficient (Min) -100 PPM/°C ≤ = ≥ Temperature Coefficient (Max) 100 PPM/°C ≤ = ≥ Application General Application Termination Style SMD Minimum Operating Temperature -55 °C ≤ = ≥ Maximum Operating Temperature +155 °C ≤ = ≥ Brand Non-Brand Package 1206 جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 73 6,900 ریال 6,550 ریال 1,000
+                                                        عدد 6,210 ریال 5,000
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>6900</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3.3k</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/product/4021/non-brand/resistor-3-3kohms-0805-1%25-smd/%D9%85%D9%82%D8%A7%D9%88%D9%85%D8%AA-3-3-%DA%A9%DB%8C%D9%84%D9%88-%D8%A7%D9%87%D9%85-1-%D8%AF%D8%B1%D8%B5%D8%AF-0805-smd#dtl/4114</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>مقاومت 3.3 کیلو اهم 1 درصد 0805 smd خانه دسته‌بندی‌ها All Products Passive Components Resistors Film Resistors Thick Film Resistors-SMD اوریجینال مقاومت 3.3 کیلو اهم 1 درصد 0805 smd نام قطعه: RESISTOR 3.3KOHMS 0805 1% SMD نام کارخانه‌ای: SER0805F3301AR برند: Non-Brand کشور سازنده: چین پکیج: 0805 2012 بسته‌بندی: Tape &amp; Reel - 5,000 عدد حداقل: 50 عدد ضریب: 50 عدد عنوان گروه: Thick Film Resistors-SMD دیتاشیت: SER0805F3301AR Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات مقاومت 3.3 کیلو اهم 1 درصد 0805 smd مقاومت 3.3 کیلو اهم 1 درصد 0805 smd از خانواده مقاومت اس ام دی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج 0805 مقاومت 3.3 کیلو اهم توان (وات) 125 میلی وات دقت 1 درصد نوع قرار گیری SMD مقدار ولتاژ DC 150 ولت حداقل دمای عملیاتی -55 درجه سانتیگراد حداکثر دمای عملیاتی +155 درجه سانتیگراد کاربرد General Application حداقل ضریب دمایی -100 ضریب دمایی حداکثر ضریب دمایی 100 ضریب دمایی RESISTOR 3.3KOHMS 0805 1% SMD یک مقاومت ثابت (فیلم ضخیم) از نوع SMD با دقت بالا است. این قطعه در پکیج استاندارد 0805 ارائه می‌شود و با داشتن تلورانس دقیق 1% و پایداری مناسب، گزینه‌ای ایده‌آل برای کاربردهایی است که به دقت بیشتر و تکرارپذیری بهتر نسبت به نوع 5% معمولی نیاز دارند، مانند مدارهای اندازه‌گیری، مرجع و تقویت‌کننده‌های دقیق. 🧩 مشخصات کلی: نوع: مقاومت ثابت (Fixed Resistor) فناوری: فیلم ضخیم (Thick Film) - نوع دقیق 💡 کاربردهای اصلی: مدارهای دقیق تقسیم ولتاژ (Precision Voltage Dividers): در مدارهای سنسور، مرجع ولتاژ و نمونه‌برداری سیگنال‌های آنالوگ. مقاومت‌های فیدبک و تقویت‌کننده‌های عملیاتی (Op-Amp Circuits): برای تعیین بهره دقیق و پایداری مدار. مدارهای زمان‌بندی با دقت متوسط: در ترکیب با خازن‌های با دقت مناسب. مقاومت‌های Pull-up/Pull-down دقیق: در خطوطی که سطح ولتاژ آستانه دقیقی مورد نیاز است. مدارهای تطبیق امپدانس (Impedance Matching): در کاربردهای فرکانس بالا و خطوط انتقال. کاربردهای عمومی با نیاز به تکرارپذیری بالا در منابع تغذیه دقیق، ابزار دقیق و سیستم‌های اندازه‌گیری. ✅ مزایا: دقت 1%: انحراف بسیار کم از مقدار اسمی، که منجر به عملکرد قابل پیش‌بینی‌تر و تکرارپذیرتر مدار می‌شود. پکیج 0805: اندازه متعادل و مناسب برای مونتاژ، با قابلیت تحمل توان 125mW. ولتاژ کاری 150V: حاشیه اطمینان ولتاژی بالا برای اکثر کاربردهای صنعتی و مصرفی. TCR بهبودیافته: ضریب دمایی معمولاً بهتر از مقاومت‌های 5%، که پایداری بهتری در برابر تغییرات دما ایجاد می‌کند. قیمت مقرون‌به‌صرفه: نسبت به مقاومت‌های فیلم نازک (Thin Film) یا‌های دقیق، هزینه کمتری دارد. دامنه دمایی وسیع: عملکرد مطمئن در محیط‌های صنعتی. 🎯 جمع‌بندی: این مقاومت 3.3 کیلواهم با دقت 1% در پکیج 0805، یک ارتقاء مستقیم و مقرون‌به‌صرفه نسبت به نوع 5% است که دقت، تکرارپذیری و پایداری دمایی بهتری را برای طراحی‌های حساس‌تر ارائه می‌دهد. این قطعه تعادل خوبی بین عملکرد، هزینه و اندازه برقرار می‌کند و برای اکثر کاربردهای صنعتی، ابزار دقیق و مصرفی با نیاز به دقت بالا گزینه‌ای ایده‌آل است. با این حال، برای مدارهای با دقت و پایداری حساسیت بحرانی ، باید محدودیت‌های ذاتی فناوری فیلم ضخیم (TCR و اثر ولتاژ) در نظر گرفته شود. Features انتخاب ویژگی Resistance 3.3 kΩ ≤ = ≥ Power Rating 125 mW ≤ = ≥ Tolerance 1 % ≤ = ≥ Voltage Rating DC 150 V ≤ = ≥ Temperature Coefficient (Min) -100 PPM/°C ≤ = ≥ Temperature Coefficient (Max) 100 PPM/°C ≤ = ≥ Application General Application Termination Style SMD Minimum Operating Temperature -55 °C ≤ = ≥ Maximum Operating Temperature +155 °C ≤ = ≥ Brand Non-Brand Package 0805 جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 85 6,280 ریال 5,960 ریال 1,000
+                                                        عدد 5,650 ریال 5,000
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>6280</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>6280</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1kΩ</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>R7,R8,R9,R10</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1kΩ</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/Shops/ProductDetail/4097?part_number=1K%20%281206%29%201%25</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>مقاومت 1 کیلو اهم 1 درصد 1206 smd خانه دسته‌بندی‌ها All Products Passive Components Resistors Film Resistors Thick Film Resistors-SMD اوریجینال مقاومت 1 کیلو اهم 1 درصد 1206 smd نام قطعه: RESISTOR 1KOHMS 1206 1% SMD نام کارخانه‌ای: SER1206F1001AR برند: Non-Brand کشور سازنده: چین پکیج: 1206 3216 بسته‌بندی: Tape &amp; Reel - 5,000 عدد حداقل: 50 عدد ضریب: 50 عدد عنوان گروه: Thick Film Resistors-SMD دیتاشیت: SER1206F1001AR Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات مقاومت 1 کیلو اهم 1 درصد 1206 smd مقاومت 1 کیلو اهم 1 درصد 1206 smd از خانواده مقاومت اس ام دی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج 1206 مقاومت 1 کیلو اهم توان (وات) 250 میلی وات دقت 1 درصد نوع قرار گیری SMD مقدار ولتاژ DC 200 ولت حداقل دمای عملیاتی -55 درجه سانتیگراد حداکثر دمای عملیاتی +155 درجه سانتیگراد کاربرد General Application حداقل ضریب دمایی -100 ضریب دمایی حداکثر ضریب دمایی 100 ضریب دمایی RESISTOR 1KOHMS 1206 1% SMD یک مقاومت ثابت (فیلم ضخیم) از نوع SMD با دقت بالا و دارای یکی از پرکاربردترین مقادیر مقاومت در صنعت الکترونیک. این قطعه در پکیج قوی و با توان بالا 1206 ارائه می‌شود و با تلورانس دقیق 1% و ضریب دمایی بهبودیافته (±100 ppm/°C)، نسخه‌ی حرفه‌ای و قابل اعتماد نهایی از مقاومت اساسی 1 کیلواهم است. این ترکیب، دقت و قابلیت اطمینان را در سطح عالی برای این مقدار بنیادی ارائه می‌دهد. 🧩 مشخصات کلی: نوع: مقاومت ثابت (Fixed Resistor) فناوری: فیلم ضخیم (Thick Film) 💡 کاربردهای اصلی: مدارهای دقیق تقسیم ولتاژ: در شبکه‌های تقسیم‌کننده‌ای که نسبت دقیق 1:1 با مقاومت‌های دیگر یا ایجاد مراجع ولتاژی خاص مورد نیاز است. مقاومت‌های فیدبک دقیق: در منابع تغذیه، تقویت‌کننده‌های عملیاتی و مدارهای کنترلی که نیاز به تنظیم دقیق پارامترها دارند. مقاومت‌های Pull-up/Pull-down با عملکرد قابل اطمینان بالا: برای خطوط حیاتی که نوسانات ناشی از تلورانس مقاومت نباید روی سطوح منطقی تأثیر بگذارد. تنظیم بهره دقیق در تقویت‌کننده‌ها: در پیکربندی‌هایی که بهره به نسبت دقیق دو مقاومت (اغلب 1kΩ و مقدار دیگری) وابسته است. مدارهای زمان‌بندی RC با دقت و تکرارپذیری عالی. کاربردهای عمومی با نیاز به کیفیت، قابلیت تکرار و کاهش خطای سیستم در تولید انبوه. ✅ مزایا: دقت 1% در یک مقدار بنیادی: تضمین عملکرد دقیق و قابل پیش‌بینی هزاران مدار مبتنی بر 1kΩ. تکرارپذیری استثنایی در تولید: کاهش چشمگیر پراکندگی در مشخصه‌های مدار بین بردهای مختلف. TCR عالی (±100 ppm/°C): پایداری دمایی برتر که دقت را در گستره دمای کاری حفظ می‌کند. توان و ولتاژ کاری بالا (250mW / 200V): حاشیه ایمنی الکتریکی و حرارتی بسیار زیاد برای کاربردهای صنعتی. پکیج 1206: استحکام مکانیکی و قابلیت اطمینان فیزیکی بالا. 🎯 جمع‌بندی: این مقاومت 1 کیلواهم با دقت 1% و TCR ±100 ppm/°C در پکیج 1206، نماد بلوغ طراحی و توجه به جزئیات در مهندسی الکترونیک است. این قطعه قلب بسیاری از مدارهای دقیق را با قابلیت اطمینان فیزیکی یک پکیج صنعتی ترکیب می‌کند . انتخاب آن به جای نوع 5%، یک ارتقاء ساده اما حیاتی برای تضمین صحت عملکرد، کاهش خطای سیستم و افزایش قابلیت اطمینان نهایی محصول است و نشان‌دهنده استانداردهای طراحی سطح بالا می‌باشد. برای هر کاربرد حساس، صنعتی یا با نیاز به کیفیت متمایز که در آن مقدار 1kΩ نقش کلیدی دارد، این مقاومت انتخاب نهایی و بی‌رقیب است. Features انتخاب ویژگی Resistance 1 kΩ ≤ = ≥ Power Rating 250 mW ≤ = ≥ Tolerance 1 % ≤ = ≥ Voltage Rating DC 200 V ≤ = ≥ Temperature Coefficient (Min) -100 PPM/°C ≤ = ≥ Temperature Coefficient (Max) 100 PPM/°C ≤ = ≥ Application General Application Termination Style SMD Minimum Operating Temperature -55 °C ≤ = ≥ Maximum Operating Temperature +155 °C ≤ = ≥ Brand Non-Brand Package 1206 جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 73 11,000 ریال 10,400 ریال 1,000
+                                                        عدد 9,900 ریال 5,000
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" t="n">
+        <v>9</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1kΩ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>R14,R15,R16,R26,R27,R28,R31,R32,R34</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1kΩ</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/Shops/ProductDetail/4097?part_number=1K%20%281206%29%201%25</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>مقاومت 1 کیلو اهم 1 درصد 1206 smd خانه دسته‌بندی‌ها All Products Passive Components Resistors Film Resistors Thick Film Resistors-SMD اوریجینال مقاومت 1 کیلو اهم 1 درصد 1206 smd نام قطعه: RESISTOR 1KOHMS 1206 1% SMD نام کارخانه‌ای: SER1206F1001AR برند: Non-Brand کشور سازنده: چین پکیج: 1206 3216 بسته‌بندی: Tape &amp; Reel - 5,000 عدد حداقل: 50 عدد ضریب: 50 عدد عنوان گروه: Thick Film Resistors-SMD دیتاشیت: SER1206F1001AR Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات مقاومت 1 کیلو اهم 1 درصد 1206 smd مقاومت 1 کیلو اهم 1 درصد 1206 smd از خانواده مقاومت اس ام دی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج 1206 مقاومت 1 کیلو اهم توان (وات) 250 میلی وات دقت 1 درصد نوع قرار گیری SMD مقدار ولتاژ DC 200 ولت حداقل دمای عملیاتی -55 درجه سانتیگراد حداکثر دمای عملیاتی +155 درجه سانتیگراد کاربرد General Application حداقل ضریب دمایی -100 ضریب دمایی حداکثر ضریب دمایی 100 ضریب دمایی RESISTOR 1KOHMS 1206 1% SMD یک مقاومت ثابت (فیلم ضخیم) از نوع SMD با دقت بالا و دارای یکی از پرکاربردترین مقادیر مقاومت در صنعت الکترونیک. این قطعه در پکیج قوی و با توان بالا 1206 ارائه می‌شود و با تلورانس دقیق 1% و ضریب دمایی بهبودیافته (±100 ppm/°C)، نسخه‌ی حرفه‌ای و قابل اعتماد نهایی از مقاومت اساسی 1 کیلواهم است. این ترکیب، دقت و قابلیت اطمینان را در سطح عالی برای این مقدار بنیادی ارائه می‌دهد. 🧩 مشخصات کلی: نوع: مقاومت ثابت (Fixed Resistor) فناوری: فیلم ضخیم (Thick Film) 💡 کاربردهای اصلی: مدارهای دقیق تقسیم ولتاژ: در شبکه‌های تقسیم‌کننده‌ای که نسبت دقیق 1:1 با مقاومت‌های دیگر یا ایجاد مراجع ولتاژی خاص مورد نیاز است. مقاومت‌های فیدبک دقیق: در منابع تغذیه، تقویت‌کننده‌های عملیاتی و مدارهای کنترلی که نیاز به تنظیم دقیق پارامترها دارند. مقاومت‌های Pull-up/Pull-down با عملکرد قابل اطمینان بالا: برای خطوط حیاتی که نوسانات ناشی از تلورانس مقاومت نباید روی سطوح منطقی تأثیر بگذارد. تنظیم بهره دقیق در تقویت‌کننده‌ها: در پیکربندی‌هایی که بهره به نسبت دقیق دو مقاومت (اغلب 1kΩ و مقدار دیگری) وابسته است. مدارهای زمان‌بندی RC با دقت و تکرارپذیری عالی. کاربردهای عمومی با نیاز به کیفیت، قابلیت تکرار و کاهش خطای سیستم در تولید انبوه. ✅ مزایا: دقت 1% در یک مقدار بنیادی: تضمین عملکرد دقیق و قابل پیش‌بینی هزاران مدار مبتنی بر 1kΩ. تکرارپذیری استثنایی در تولید: کاهش چشمگیر پراکندگی در مشخصه‌های مدار بین بردهای مختلف. TCR عالی (±100 ppm/°C): پایداری دمایی برتر که دقت را در گستره دمای کاری حفظ می‌کند. توان و ولتاژ کاری بالا (250mW / 200V): حاشیه ایمنی الکتریکی و حرارتی بسیار زیاد برای کاربردهای صنعتی. پکیج 1206: استحکام مکانیکی و قابلیت اطمینان فیزیکی بالا. 🎯 جمع‌بندی: این مقاومت 1 کیلواهم با دقت 1% و TCR ±100 ppm/°C در پکیج 1206، نماد بلوغ طراحی و توجه به جزئیات در مهندسی الکترونیک است. این قطعه قلب بسیاری از مدارهای دقیق را با قابلیت اطمینان فیزیکی یک پکیج صنعتی ترکیب می‌کند . انتخاب آن به جای نوع 5%، یک ارتقاء ساده اما حیاتی برای تضمین صحت عملکرد، کاهش خطای سیستم و افزایش قابلیت اطمینان نهایی محصول است و نشان‌دهنده استانداردهای طراحی سطح بالا می‌باشد. برای هر کاربرد حساس، صنعتی یا با نیاز به کیفیت متمایز که در آن مقدار 1kΩ نقش کلیدی دارد، این مقاومت انتخاب نهایی و بی‌رقیب است. Features انتخاب ویژگی Resistance 1 kΩ ≤ = ≥ Power Rating 250 mW ≤ = ≥ Tolerance 1 % ≤ = ≥ Voltage Rating DC 200 V ≤ = ≥ Temperature Coefficient (Min) -100 PPM/°C ≤ = ≥ Temperature Coefficient (Max) 100 PPM/°C ≤ = ≥ Application General Application Termination Style SMD Minimum Operating Temperature -55 °C ≤ = ≥ Maximum Operating Temperature +155 °C ≤ = ≥ Brand Non-Brand Package 1206 جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 73 11,000 ریال 10,400 ریال 1,000
+                                                        عدد 9,900 ریال 5,000
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>10kΩ</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>R17,R24,R25,R29,R30,R33</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>10kΩ</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/product/4080/non-brand/resistor-10kohms-1206-5%25-smd/%D9%85%D9%82%D8%A7%D9%88%D9%85%D8%AA-10-%DA%A9%DB%8C%D9%84%D9%88-%D8%A7%D9%87%D9%85-1206-smd</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>مقاومت 10 کیلو اهم 1206 smd خانه دسته‌بندی‌ها All Products Passive Components Resistors Film Resistors Thick Film Resistors-SMD اوریجینال مقاومت 10 کیلو اهم 1206 smd نام قطعه: RESISTOR 10KOHMS 1206 5% SMD نام کارخانه‌ای: SER1206J0103AR برند: Non-Brand کشور سازنده: چین پکیج: 1206 3216 بسته‌بندی: Tape &amp; Reel - 5,000 عدد حداقل: 50 عدد ضریب: 50 عدد عنوان گروه: Thick Film Resistors-SMD دیتاشیت: SER1206J0103AR Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات مقاومت 10 کیلو اهم 1206 smd مقاومت 10 کیلو اهم 1206 smd از خانواده مقاومت اس ام دی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج 1206 مقاومت 10 کیلو اهم توان (وات) 250 میلی وات دقت 5 درصد نوع قرار گیری SMD مقدار ولتاژ DC 200 ولت حداقل دمای عملیاتی -55 درجه سانتیگراد حداکثر دمای عملیاتی +155 درجه سانتیگراد کاربرد General Application حداقل ضریب دمایی -100 ضریب دمایی حداکثر ضریب دمایی 100 ضریب دمایی RESISTOR 10KOHMS 1206 5% SMD یک مقاومت ثابت (فیلم ضخیم) از نوع SMD با احتمالاً پرکاربردترین مقدار مقاومت در صنعت الکترونیک. این قطعه در پکیج بزرگ‌تر و با توان بالاتر 1206 ارائه می‌شود که آن را برای کاربردهایی که نیاز به قابلیت اطمینان بالا، تحمل توان بیشتر یا عملکرد در شرایط محیطی سخت‌تر دارند، بهینه می‌سازد. مقاومت 10 کیلواهم سنگ بنای بی‌شمار مدار تقسیم ولتاژ، Pull-up، فیلتر و زمان‌بندی است. 🧩 مشخصات کلی: نوع: مقاومت ثابت (Fixed Resistor) فناوری: فیلم ضخیم (Thick Film) 💡 کاربردهای اصلی: تقسیم‌کننده ولتاژ جهانی: همراه با سنسورها (به ویژه ترمیستورهای 10kΩ)، پتانسیومترها و در ورودی‌های ADC. مقاومت Pull-up/Pull-down استاندارد صنعتی: برای پایه‌های دیجیتال، خطوط Reset و پیکربندی. مقاومت فیدبک در تقویت‌کننده‌های عملیاتی و منابع تغذیه. مدارهای فیلتر و زمان‌بندی RC: در ترکیب با خازن‌های نانوفارادی برای تولید ثابت‌های زمانی پرکاربرد. مقاومت‌های بایاس و بار در مدارهای آنالوگ. کاربردهای عمومی در هر حوزه‌ای از الکترونیک مصرفی تا صنعتی. ✅ مزایا: پرکاربردترین مقدار مقاومت: 10kΩ سلطان غیرقابل انکار مقاومت‌هاست. توان نامی عالی (250mW): حاشیه ایمنی حرارتی بسیار بالا نسبت به نیاز واقعی در کاربردهای سیگنالی، که قابلیت اطمینان را به حداکثر می‌رساند. ولتاژ کاری 200V: امکان استفاده ایمن در مدارهای با ولتاژهای آنالوگ بالاتر. TCR خوب (±100 ppm/°C): پایداری دمایی قابل قبول برای اکثر کاربردها. پکیج 1206: استحکام مکانیکی، مقاومت در برابر خمش برد و مدیریت حرارتی برتر. 🎯 جمع‌بندی: این مقاومت 10 کیلواهم در پکیج 1206 با دقت 5%، تجسم یک قطعه الکترونیکی ایده‌آل: پرکاربرد، فوق‌العاده بادوام و با قابلیت اطمینان استثنایی است. این مقاومت همه مزایای اساسی و جهانی 10kΩ را با استحکام فیزیکی و حاشیه عملکرد الکتریکی یک پکیج صنعتی‌تر ترکیب می‌کند. انتخاب آن به جای پکیج‌های کوچک‌تر، یک تصمیم هوشمندانه برای طراحی‌های حرفه‌ای، صنعتی و هر پروژه‌ای که در آن قابلیت اطمینان و طول عمر از حداقل فضای اشغالی مهم‌تر است محسوب می‌شود. این قطعه یک سرمایه‌گذاری مطمئن برای هر برد الکترونیکی است. Features انتخاب ویژگی Resistance 10 kΩ ≤ = ≥ Power Rating 250 mW ≤ = ≥ Tolerance 5 % ≤ = ≥ Voltage Rating DC 200 V ≤ = ≥ Temperature Coefficient (Min) -100 PPM/°C ≤ = ≥ Temperature Coefficient (Max) 100 PPM/°C ≤ = ≥ Application General Application Termination Style SMD Minimum Operating Temperature -55 °C ≤ = ≥ Maximum Operating Temperature +155 °C ≤ = ≥ Brand Non-Brand Package 1206 جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 73 6,900 ریال 6,550 ریال 1,000
+                                                        عدد 6,210 ریال 5,000
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>6900</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>41400</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>220Ω</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>R18,R22</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RES-TH_BD4.5-L11.5-P15.50-D0.8</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>220Ω</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/product/36494/non-brand/resistor-220kohms-1206-1%25-smd/%D9%85%D9%82%D8%A7%D9%88%D9%85%D8%AA-220-%DA%A9%DB%8C%D9%84%D9%88-%D8%A7%D9%87%D9%85-1-%D8%AF%D8%B1%D8%B5%D8%AF-1206-smd#dtl/4108</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>مقاومت 220 کیلو اهم 1 درصد 1206 smd خانه دسته‌بندی‌ها All Products Passive Components Resistors Film Resistors Thick Film Resistors-SMD اوریجینال مقاومت 220 کیلو اهم 1 درصد 1206 smd نام قطعه: RESISTOR 220KOHMS 1206 1% SMD نام کارخانه‌ای: SER1206F2203AR برند: Non-Brand کشور سازنده: چین پکیج: 1206 3216 بسته‌بندی: Tape &amp; Reel - 5,000 عدد حداقل: 50 عدد ضریب: 50 عدد عنوان گروه: Thick Film Resistors-SMD دیتاشیت: SER1206F2203AR Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات مقاومت 220 کیلو اهم 1 درصد 1206 smd مقاومت 220 کیلو اهم 1 درصد 1206 smd از خانواده مقاومت اس ام دی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج 1206 توان (وات) 250 میلی وات دقت 1 درصد نوع قرار گیری SMD حداقل دمای عملیاتی -55 درجه سانتیگراد کاربرد General Application حداقل ضریب دمایی -100 ضریب دمایی مقاومت 220 کیلو اهم مقدار ولتاژ DC 200 ولت حداکثر دمای عملیاتی +155 درجه سانتیگراد حداکثر ضریب دمایی 100 ضریب دمایی RESISTOR 220KOHMS 1206 1% SMD یک مقاومت ثابت با مقدار مقاومت بالا و دقت عالی از نوع SMD. این قطعه در پکیج صنعتی و با توان بالای 1206 ارائه می‌شود که ترکیبی استثنایی از دقت بالا، ولتاژ کاری قابل توجه، پایداری دمایی خوب و استحکام فیزیکی را برای کاربردهای حرفه‌ای و صنعتی فراهم می‌کند. مقاومت 220 کیلواهم یک مقدار استاندارد و پرکاربرد در محدوده صدها کیلواهم است. 🧩 مشخصات کلی: نوع: مقاومت ثابت (Fixed Resistor) فناوری: فیلم ضخیم (Thick Film) 💡 کاربردهای اصلی: تقسیم‌کننده ولتاژ دقیق برای ولتاژهای بالا: در مدارهای اندازه‌گیری ولتاژ (Voltage Sensing)، محافظت از اورولتاژ و رابط‌های ولتاژ بالا (مثلاً در منابع تغذیه سوئیچینگ 400V، درایورهای موتور یا سیستم‌های صنعتی 110/220VAC). مقاومت فیدبک در مبدل‌های Flyback و منابع تغذیه با ولتاژ خروجی بالا: برای نمونه‌برداری دقیق از ولتاژ خروجی و تنظیم آن. مقاومت Pull-up با امپدانس بسیار بالا: برای خطوطی که حداقل بارگذاری و کمترین مصرف جریان استاتیک مطلوب است (مانند سنسورهای با خروجی Open-drain). مدارهای زمان‌بندی RC با ثابت زمانی طولانی: در ترکیب با خازن‌های ظرفیت متوسط برای ایجاد تأخیرهای زمانی ثانیه‌ای. مقاومت‌های بایاس و بار در تقویت‌کننده‌های لوله خلأ یا ترانزیستورهای High-Voltage. کاربردهای ویژه در تجهیزات پزشکی، آزمایشگاهی، سیستم‌های کنترل صنعتی و منابع تغذیه با ایزولاسیون. ✅ مزایا: ولتاژ کاری بسیار بالا (200VDC): قابلیت استفاده ایمن و مستقیم در مدارهای با ولتاژهای آنالوگ بالا را فراهم می‌کند. این یک مزیت عمده نسبت به پکیج‌های کوچکتر است. دقت عالی (1%) و TCR کنترل‌شده (±100 ppm/°C): پایداری و دقت قابل اتکا برای طراحی‌های حرفه‌ای که نیاز به عملکرد دقیق در بازه دمایی وسیع دارند. توان نامی بالا (250mW): حاشیه ایمنی حرارتی عالی برای این مقدار مقاومت بالا، که قابلیت اطمینان طولانی‌مدت را تضمین می‌کند. پکیج 1206: استحکام مکانیکی و حرارتی برتر، مقاومت در برابر تنش‌های ناشی از انبساط حرارتی و مونتاژ، و سهولت در نمونه‌سازی دستی. مقدار مقاومت کلیدی: 220kΩ یک مقدار استاندارد حیاتی برای ایجاد نسبت‌های تقسیم متداول (مانند 1:10 یا 1:11 از ولتاژهای بالا). 🎯 جمع‌بندی: این مقاومت 220 کیلواهم در پکیج 1206 با دقت 1%، نماد یک قطعه صنعتی و باکیفیت است. این قطعه همه الزامات یک طراحی حرفه‌ای و محافظه‌کارانه را برآورده می‌کند: دقت، توانایی تحمل ولتاژ بالا، پایداری حرارتی و استحکام فیزیکی. انتخاب آن به جای پکیج‌های کوچک‌تر (مثل 0603 یا 0805)، یک تصمیم آگاهانه برای تضمین قابلیت اطمینان، ایمنی و عملکرد پایدار در طول زمان و در شرایط سخت کاری است. این مقاومت برای منابع تغذیه سوئیچینگ، مدارهای کنترلی صنعتی، تجهیزات اندازه‌گیری دقیق و هر پروژه‌ای که در آن ولتاژهای بالا، دقت یا شرایط محیطی چالش‌برانگیز مطرح است، انتخابی ایده‌آل و حرفه‌ای محسوب می‌شود. Features انتخاب ویژگی Resistance 220 kΩ ≤ = ≥ Power Rating 250 mW ≤ = ≥ Tolerance 1 % ≤ = ≥ Voltage Rating DC 200 V ≤ = ≥ Temperature Coefficient (Min) -100 PPM/°C ≤ = ≥ Temperature Coefficient (Max) 100 PPM/°C ≤ = ≥ Application General Application Termination Style SMD Minimum Operating Temperature -55 °C ≤ = ≥ Maximum Operating Temperature +155 °C ≤ = ≥ Brand Non-Brand Package 1206 جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 88 10,500 ریال 9,970 ریال 1,000
+                                                        عدد 9,450 ریال 5,000
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>10500</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MOV-10D471K</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>R19,R23</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RES-TH_L12.5-W5.4-P7.50-D0.8-S2.40</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/category/26/varistors/%d9%88%d8%b1%db%8c%d8%b3%d8%aa%d9%88%d8%b1#dtl/6574</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>وریستور خانه دسته‌بندی‌ها وریستور وریستور (Varistor) یک قطعه الکترونیکی است که برای محافظت از مدارها در برابر تغییرات ناگهانی ولتاژ استفاده می‌شود. این قطعه معمولاً در برابر ولتاژهای بالا مقاومت کمتری دارد و وقتی ولتاژ به حد مشخصی برسد، مقاومت آن به طور ناگهانی کاهش می‌یابد. این ویژگی به آن کمک می‌کند تا از آسیب به سایر اجزای مدار جلوگیری کند.
+وریستورها معمولاً در مدارهای حفاظتی برای مقابله با اضافه ولتاژهای ناشی از رعد و برق یا نوسانات شبکه برق استفاده می‌شوند. به طور معمول، آن‌ها به صورت موازی با مدارهای حساس نصب می‌شوند تا در صورت بروز اضافه ولتاژ، جریان اضافی از مدار عبور کرده و دستگاه اصلی را محافظت کنند. فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش مقدار ولتاژ AC 38 4 V 6.4 V 6.5 V 6.8 V 8 V 11 V 14 V 17 V 18.4 V 20 V 21.2 V 25 V 30 V 35 V 50 V 60 V 75 V 95 V 115 V 130 V 140 V 150 V 175 V 230 V 240 V 250 V 275 V 300 V 320 V 350 V 420 V 460 V 480 V 510 V 550 V 615 V 680 V 1.1 kV ≥ = ≤ = ولتاژ نگهدارنده 51 12.7 V 14 V 22 V 30 V 36 V 38 V 40 V 43 V 47 V 53 V 54 V 55 V 63 V 65 V 73 V 74 V 77 V 80 V 93 V 98 V 110 V 135 V 165 V 200 V 210 V 250 V 300 V 340 V 360 V 380 V 395 V 455 V 475 V 595 V 610 V 620 V 650 V 675 V 710 V 745 V 775 V 810 V 845 V 870 V 1.06 KV 1.12 KV 1.16 KV 1.24 KV 1.355 KV 1.5 KV 2.97 KV ≥ = ≤ = مقدار ولتاژ DC 42 1.465 V 3.5 V 5.5 V 5.6 V 9 V 12 V 14 V 18 V 22 V 24 V 26 V 30 V 31 V 38 V 45 V 56 V 65 V 85 V 100 V 125 V 150 V 170 V 180 V 200 V 225 V 300 V 320 V 350 V 385 V 390 V 415 V 420 V 430 V 517 V 560 V 615 V 640 V 670 V 745 V 750 V 895 V 1.465 kV ≥ = ≤ = نوع 22 Ceramic Transient Voltage Suppressor Chip Varistors Disk Varistors Leaded Varistors Line Voltage Operation, Radial Lead Varistor Low to Medium Voltage, Radial Lead Varistor Metal Oxide Chip Varistor Metal Oxide Varistor Metal Oxide Varistors Multilayer Ceramic Transient Voltage Suppressors Multilayer Varistor Overcurrent/Overvoltage Protection Device Oxide Varistors PA Series Varistor Polymeric Surface Mount Multilayer High Speed Varistor Symmetrical Type Silicon Varistors Transient/Surge Absorbers Varistor Varistors ZINC Oxide Varistors ZNR Transient/Surge Absorbers = نوع قرار گیری 2 Radial SMD/SMT = نوع نصب روی برد 3 PCB Mount SMD/SMT Through Hole = قطر خازن 13 1 mm 5 mm 7 mm 9 mm 10 mm 12 mm 14 mm 15 mm 20 mm 21.5 mm 22 mm 38 mm 178 mm ≥ = ≤ = حداقل دمای عملیاتی 2 -55 °C -40 °C ≥ = ≤ = حداکثر دمای عملیاتی 7 +85 °C 85 °C 100 °C 105 °C +125 °C 125 °C +130 °C ≥ = ≤ = برند 17 AVX Corporation Bourns Inc BrightKing Inc CeNtRa Science Corp Eaton’s Bussmann Fuji Electric Littelfuse Inc Matsushita Electric Meritek Electronics Corporation Murata Manufacturing Co NEC Electronics Nippon Chemi-Con Non-Brand Panasonic Corporation Sanken Electric TDK Corporation (EPCOS) Vishay = پکیج 8 0402 1005 0603 1608 0805 2012 1206 3216 3225 4032 DO-214AB SMCJ Radial = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز مقدار ولتاژ AC ولتاژ نگهدارنده مقدار ولتاژ DC نوع نوع قرار گیری نوع نصب روی برد قطر خازن حداقل دمای عملیاتی حداکثر دمای عملیاتی برند پکیج مرتب کردن مرتب سازی All Products Circuit Protection Varistors اوریجینال ZOV-07D390K Non-Brand Radial 28,200 ریال اضافه به سبد خرید اوریجینال ZOV-07D181K Non-Brand Radial 28,600 ریال اضافه به سبد خرید اوریجینال ZOV-07D180K Non-Brand Radial 28,800 ریال اضافه به سبد خرید اوریجینال ZOV-07D221K Non-Brand Radial 30,100 ریال اضافه به سبد خرید اوریجینال ZOV-07D271K Non-Brand Radial 30,400 ریال اضافه به سبد خرید اوریجینال ZOV-07D220K Non-Brand Radial 31,000 ریال اضافه به سبد خرید اوریجینال ZOV-07D560K Non-Brand Radial 31,200 ریال اضافه به سبد خرید اوریجینال ZOV-07D361K Non-Brand Radial 33,900 ریال اضافه به سبد خرید اوریجینال SV03YS Sanken Electric Radial 34,800 ریال اضافه به سبد خرید اوریجینال ZOV-07D391K Non-Brand Radial 37,000 ریال اضافه به سبد خرید اوریجینال ZOV-07D431K Non-Brand Radial 37,900 ریال اضافه به سبد خرید اوریجینال ZOV-07D471K Non-Brand Radial 43,000 ریال اضافه به سبد خرید اوریجینال ZOV-10D471K Non-Brand Radial 45,100 ریال اضافه به سبد خرید اوریجینال ZOV-10D561K Non-Brand Radial 46,900 ریال اضافه به سبد خرید اوریجینال ZOV-10D391K Non-Brand Radial 47,900 ریال اضافه به سبد خرید اوریجینال ZOV-10D431K Non-Brand Radial 50,400 ریال اضافه به سبد خرید اوریجینال ZOV-14D471K Non-Brand Radial 99,200 ریال اضافه به سبد خرید اوریجینال ZOV-14D431K Non-Brand Radial 103,000 ریال اضافه به سبد خرید اوریجینال ZOV-20D431K Non-Brand Radial 199,000 ریال اضافه به سبد خرید اوریجینال ZOV-20D471K Non-Brand Radial 202,000 ریال اضافه به سبد خرید اوریجینال ZOV-20D391K Non-Brand Radial 231,000 ریال اضافه به سبد خرید اوریجینال ZOV-20D681K Non-Brand Radial 240,000 ریال اضافه به سبد خرید اوریجینال ZOV-20D821K Non-Brand Radial 320,000 ریال اضافه به سبد خرید اوریجینال ZOV-20D911K Non-Brand Radial 407,000 ریال اضافه به سبد خرید اوریجینال ENE361D07A Fuji Electric Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال CNR-07D220K CeNtRa Science Corp Radial ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال TVR10101 Non-Brand Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال V150K14 Non-Brand Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال VDR 05K181 BrightKing Inc Radial ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال ZOV-10D391K SHORT LEGS Non-Brand Radial ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال NV047D03-TB1 NEC Electronics Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال TNR7V221K Nippon Chemi-Con Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال PA20-431C Non-Brand Module ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال MVS1206T330K Meritek Electronics Corporation 1206 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال ERZV10D271 Panasonic Corporation Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال ZOV-07D201K Non-Brand Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال NV082D07 NEC Electronics Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال ERZV14D201 Panasonic Corporation Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال SNR-180LD07 Sanken Electric Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال ZNR7K101U Matsushita Electric Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال VDR 26V (0805) Fenghua Advanced Technology 0805 ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال VDR 30V (0805) Fenghua Advanced Technology 0805 ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال ZOV-10D121K Non-Brand Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال VDR 07K270 BrightKing Inc Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال VDR 07K470 BrightKing Inc Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال SVR10D681K Non-Brand Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال ZOV-07D820K Non-Brand Radial ناموجود-تحویل 35 روزه اضافه به سبد سفارش اوریجینال VDR 07K221 BrightKing Inc Radial ناموجود-تحویل 33 روزه اضافه به سبد سفارش مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>28200</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>56400</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>R20,R21</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>C1206</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/product/4080/non-brand/resistor-10kohms-1206-5%25-smd/%D9%85%D9%82%D8%A7%D9%88%D9%85%D8%AA-10-%DA%A9%DB%8C%D9%84%D9%88-%D8%A7%D9%87%D9%85-1206-smd</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>مقاومت 10 کیلو اهم 1206 smd خانه دسته‌بندی‌ها All Products Passive Components Resistors Film Resistors Thick Film Resistors-SMD اوریجینال مقاومت 10 کیلو اهم 1206 smd نام قطعه: RESISTOR 10KOHMS 1206 5% SMD نام کارخانه‌ای: SER1206J0103AR برند: Non-Brand کشور سازنده: چین پکیج: 1206 3216 بسته‌بندی: Tape &amp; Reel - 5,000 عدد حداقل: 50 عدد ضریب: 50 عدد عنوان گروه: Thick Film Resistors-SMD دیتاشیت: SER1206J0103AR Datasheet روش‌های ارسال‌ متنوع سفارش خارج چت آنلاین پیش خرید هوشمندانه مشخصات مقاومت 10 کیلو اهم 1206 smd مقاومت 10 کیلو اهم 1206 smd از خانواده مقاومت اس ام دی می‌باشد. ویژگی‌های فنی این محصول براساس دیتاشیت ارایه شده از سوی تولید کننده آن به شرح زیر می باشد: برند Non-Brand پکیج 1206 مقاومت 10 کیلو اهم توان (وات) 250 میلی وات دقت 5 درصد نوع قرار گیری SMD مقدار ولتاژ DC 200 ولت حداقل دمای عملیاتی -55 درجه سانتیگراد حداکثر دمای عملیاتی +155 درجه سانتیگراد کاربرد General Application حداقل ضریب دمایی -100 ضریب دمایی حداکثر ضریب دمایی 100 ضریب دمایی RESISTOR 10KOHMS 1206 5% SMD یک مقاومت ثابت (فیلم ضخیم) از نوع SMD با احتمالاً پرکاربردترین مقدار مقاومت در صنعت الکترونیک. این قطعه در پکیج بزرگ‌تر و با توان بالاتر 1206 ارائه می‌شود که آن را برای کاربردهایی که نیاز به قابلیت اطمینان بالا، تحمل توان بیشتر یا عملکرد در شرایط محیطی سخت‌تر دارند، بهینه می‌سازد. مقاومت 10 کیلواهم سنگ بنای بی‌شمار مدار تقسیم ولتاژ، Pull-up، فیلتر و زمان‌بندی است. 🧩 مشخصات کلی: نوع: مقاومت ثابت (Fixed Resistor) فناوری: فیلم ضخیم (Thick Film) 💡 کاربردهای اصلی: تقسیم‌کننده ولتاژ جهانی: همراه با سنسورها (به ویژه ترمیستورهای 10kΩ)، پتانسیومترها و در ورودی‌های ADC. مقاومت Pull-up/Pull-down استاندارد صنعتی: برای پایه‌های دیجیتال، خطوط Reset و پیکربندی. مقاومت فیدبک در تقویت‌کننده‌های عملیاتی و منابع تغذیه. مدارهای فیلتر و زمان‌بندی RC: در ترکیب با خازن‌های نانوفارادی برای تولید ثابت‌های زمانی پرکاربرد. مقاومت‌های بایاس و بار در مدارهای آنالوگ. کاربردهای عمومی در هر حوزه‌ای از الکترونیک مصرفی تا صنعتی. ✅ مزایا: پرکاربردترین مقدار مقاومت: 10kΩ سلطان غیرقابل انکار مقاومت‌هاست. توان نامی عالی (250mW): حاشیه ایمنی حرارتی بسیار بالا نسبت به نیاز واقعی در کاربردهای سیگنالی، که قابلیت اطمینان را به حداکثر می‌رساند. ولتاژ کاری 200V: امکان استفاده ایمن در مدارهای با ولتاژهای آنالوگ بالاتر. TCR خوب (±100 ppm/°C): پایداری دمایی قابل قبول برای اکثر کاربردها. پکیج 1206: استحکام مکانیکی، مقاومت در برابر خمش برد و مدیریت حرارتی برتر. 🎯 جمع‌بندی: این مقاومت 10 کیلواهم در پکیج 1206 با دقت 5%، تجسم یک قطعه الکترونیکی ایده‌آل: پرکاربرد، فوق‌العاده بادوام و با قابلیت اطمینان استثنایی است. این مقاومت همه مزایای اساسی و جهانی 10kΩ را با استحکام فیزیکی و حاشیه عملکرد الکتریکی یک پکیج صنعتی‌تر ترکیب می‌کند. انتخاب آن به جای پکیج‌های کوچک‌تر، یک تصمیم هوشمندانه برای طراحی‌های حرفه‌ای، صنعتی و هر پروژه‌ای که در آن قابلیت اطمینان و طول عمر از حداقل فضای اشغالی مهم‌تر است محسوب می‌شود. این قطعه یک سرمایه‌گذاری مطمئن برای هر برد الکترونیکی است. Features انتخاب ویژگی Resistance 10 kΩ ≤ = ≥ Power Rating 250 mW ≤ = ≥ Tolerance 5 % ≤ = ≥ Voltage Rating DC 200 V ≤ = ≥ Temperature Coefficient (Min) -100 PPM/°C ≤ = ≥ Temperature Coefficient (Max) 100 PPM/°C ≤ = ≥ Application General Application Termination Style SMD Minimum Operating Temperature -55 °C ≤ = ≥ Maximum Operating Temperature +155 °C ≤ = ≥ Brand Non-Brand Package 1206 جستجوی مشابه نظرات ارسال نظر جدید نتایج بیشتر … موجود در انبار 73 6,900 ریال 6,550 ریال 1,000
+                                                        عدد 6,210 ریال 5,000
+                                                        عدد اضافه به سبد خرید دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>6900</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>13800</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>RELE_220</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>RE1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>G2R1E</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>رله امرن مدل G2R-1-E دارای 12 ولت 16 آمپر 8 پین - فروشگاه عارف الکترونیک</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ERROR: [Errno 2] No such file or directory: 'رله امرن مدل G2R-1-E دارای 12 ولت 16 آمپر 8 پین - فروشگاه عارف الکترونیک'</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>G2R-1-E/12VDC</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>RE2</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>G2R1E</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>رله امرن مدل G2R-1-E دارای 12 ولت 16 آمپر 8 پین - فروشگاه عارف الکترونیک</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ERROR: [Errno 2] No such file or directory: 'رله امرن مدل G2R-1-E دارای 12 ولت 16 آمپر 8 پین - فروشگاه عارف الکترونیک'</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LC-4P-S-5.08-W</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>RELE-220V-AC</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CONN-TH_4P-P5.08_2EHDR-04P</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ERROR: [Errno 2] No such file or directory: 'OK'</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>{Symbol!}</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Screw-Hole-M3</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>Javan</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ERROR: [Errno 2] No such file or directory: 'Javan'</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Screw-Hole-M3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>S2,S3,S4</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Screw-Hole-M3</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>Javan</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ERROR: [Errno 2] No such file or directory: 'Javan'</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TM1637</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>TM1637 4 DIGIT LED MODULE</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop?searchfilter=tm1637#dtl/35227</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>محصولات خانه دسته‌بندی‌ها فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه عبارت tm1637 جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش برند 1666 3M Dynapro 3M Interconnect 3PEAK Incorporated 4D Systems Pty Ltd A Power microelectronics AAEON Technology Aavid Thermalloy ABC Taiwan Electronics ABLIC Inc Abracon Corporation Acam-Messelectronic Acrian, Inc Actel Corporation Active-Semi, Inc Actox Corporation. AD Semiconductor Confidential Adafruit Industries LLC Adam Technologies, Inc ADDA Corp ADDtek Corp Adesto Technologies ADMtek Inc Advanced Acoustic Technology Corp. Advanced Analog Technology Advanced Analogic Technologies Advanced Card Systems Advanced Ceramic X Corp Advanced Linear Devices Inc Advanced Monolithic Systems Advanced Photonix, Inc Advanced Power Electronics Corp Advanced Power Technology Advanced Semiconductor Advantech Corp Advantech Equipment Corporation Aegis Electronic Group AEL Crystals Limited AEM, Inc Aerosemi Technology Co Afa Technologies Inc AG Electrical Technology Agere Systems Agilent Technologies AGM Semiconductor AIC tech Inc. Aimtec Aimtron Corporation Airoha Technology Corp AIRWAVE Technologies Inc AiSHi Capacitors Aixin Opto-Electrical Technology Albright International Ltd Alcatel Microelectronics Alcor Micro Corp Alex Connector Co Ltd Alfa Electronics Algocraft Srl. ALi Corporation Alinx Electronic Technology All Sensors Corporation Allegro Microsystems Alliance Memory Allied Vision, Inc. Allwinner Technology Almita Co. Ltd Alpha &amp; Omega Semiconductor Alpha Micro Components Alpha Semiconductor Alpha Wire Alphasense Ltd, Sensor Technology Alps Electric Co Altera Corporation Amazing Electronic Co Amazing Microelectronic Corp AMD American Microsemiconductors American Microsystems Inc American Power Management American Technical Ceramics Corp American Zettler, Inc. Ametherm, Inc AMI Semiconductor AMIC Technology Corp Amidon Associates, Inc Amlogic Inc. Amotech Corp AMPAK Technology Inc Amphenol Advanced Sensors Amphenol Corporation Amphenol FCI Amphenol RF Ampleon USA Inc ams AG Anachip Corp ANADIGICS Anadigm, Inc Analog Devices Analog Integrations Corporation Analog Microelectronics Analog Power Analogix Semiconductor Inc Anaren, Inc Ancol Electronics Co Andigilog, Inc ANENG Anhui FOSAN Semiconductor Anhui Vico Technologes Co Anovay Technologies Limited ANPEC Electronics Corp Ante Intelligent Company Limited AP Memory Technology. APC Propellers APEM Inc Apex Material Technology Apex Precision Power API Delevan Inc API Technologies Aplus Integrated Circuits Inc APMKorea Apogee Technology, Inc Applent Instruments Applied Micro Circuits Co AppoTech Ltd APT Electronics Co., Ltd. Aptek Technologies ArchNet Technology Arcol UK Ltd Arduino Arduino Nicla Voice. Arima Lasers Corporation Aristotle Enterprises Inc ARTCHIP Semiconductor Artesyn Embedded Technologies AS ENERGI Asahi Kasei Microdevices ASAHI Solder Asia Vital Components Asiliant Technologies ASIX Electronics Corp AsLic Microelectronics Corporation ASMedia Technology Inc. Associated Opto-Electronics Astec Semiconductor. Astrodyne TDI Corporation. ATE Electronics s.r.l Atech Technology Co ATEN International Co Atheros Communications, Inc ATI Technologies Inc Atlas Scientific LLC. Attend Technology Inc AU Optronics Corp Audiowell Electronics Co Auk Contractors Co AUK Semiconductor AUO Corporation AUREL S.P.A Austar Technology AuthenTec, Inc Autonics Corporation Avago Technologies AVANTEK INC. AverLogic Technologies, Inc AVerMedia Technologies Avia Semiconductor Avnet, Inc AVX Corporation AXElite Technology Co Axiomtek Axis Communications AZ Displays, Inc Azoteq Ltd BAFO Technologies Corp Bahar Enclosure Baumer International BBT-China Inc BCD Semiconductor Beckhoff Automation Beijing Boshida Beijing HRH Information Co Beijing Ultrasonic Beijing Yihongtai Technology Beijing Zhongxun Sifang Science &amp; Technology Beken Corporation Bel Fuse Inc Bel Power Solutions Inc Belden Inc Bellnix Bencent Tzeng Ind. Co. Ltd Betlux Beyond Innovation Technology BI Technologies Bicker Elektronik GmbH Billionton Systems Inc Bird Technologies Bi-Sonic Technology Bivar, Inc Blackhawk BLOCK Inc Bluegiga Technologies BOLYMIN,INC BONGSHIN LOADCELL CO. Bookly Micro Electronic Bosch Security Systems Inc Bosch Semiconductors Bosch Sensortec Bothhand USA Boundary Devices Bourns Inc Bowin Microelectronics Brainboxes Limited BRIGHT LED ELECTRONICS CORP. Bright Power Semiconductor BrightKing Inc Brilliance Semiconductor, Inc Broadchip Technology Broadcom Limited BroadLight Inc Brooktree Corporation Burr-Brown Corporation BYD Microelectronics Co., Ltd. C&amp;D Technologies C&amp;K Components Caddock Electronics Inc California Eastern Laboratories California Micro Devices Calogic LLC Cambridge Integrated Circuits Cambridge Silicon Ra dio Limited Camille Bauer Ltd Catalyst Semiconductor Celduc relais CellWise Microelectronics Co Cenker Enterprise Ltd Centenary Materials Co CeNtRa Science Corp Central Components Manufacturing Central Georgia Generator Central Semiconductor CEVA Technologies CFSensor Challenge Electronics Champion Microelectronic Changzhou changjie Technology Co Changzhou Cre-sound Electronics Changzhou DRM Changzhou Esuntech Co Changzhou Kennon ELectronics Changzhou TDA Electronic Changzhou Yuanwang Fluid Technology Chaozhou Three-circle (Group) Co chargebyte GmbH. Chengdu Ebyte Electronic Technology Chengdu Guosheng Technology Chengdu Xincheng Huachuang Electronic ChenMoun Electronic ChenYang Technologies Cheuk Yui Innovation Co Chi Mei Optoelectronics Chieful Science ＆ Technology Chilisin Electronics Co China Base Electronic Technology China ECU Tools Centre China Resources Microelectronics China Software Industry Association Chinfa Electronics Chingis Technology Corp Chino-Excel Technology Chipanalog Incorporated ChipLink Tech Chiplus Semiconductor ChipON Chipower Electronics CHIPS Technology Chipstar Microelectronics CHK Electronics Ltd Chogori USA Chongqing Shengpu Electronics Chrontel, Inc Chunghwa Picture Tubes Churod Electronics Chyao Shiunn Electronic Cincon Electronics Cinetech Ind Cirrus Logic Inc Cisco Systems CIT Relay &amp; Switch Citizen Finedevice Co Cixi AnXon Electronic Cixi Dafa precise Linker Co CiXi KaiFeng Electronics Co Cixi Kefa Electronics Cixi Max Electronics Co.,Ltd Clare, Inc Cliff Electronic Components Limited Cmedia Electronics Inc CML Microsystems Coil Master Co Coil Winding Coilcraft Inc Coiltronics (Eaton) Comchip Technology Commodore Semiconductor Comtec Crystals comtech aha corporation CONEC Elektronische Bauelemente GmbH Conesys,Inc. Conexant Systems, Inc Connfly Electronic Co Connor-Winfield Conquer Electronic Continental Device India Controlair Inc Conversion Devices, Inc Cooper Bussmann Coretek Opto Corporation. Cornell Dubilier Electronics Cortina Systems, Inc Cosel Co Ltd COSINE Nanoelectronics Coto Technology CR Powtech Co Cree, Inc Crydom Inc Crystal Semiconductor Corporation Crystalfontz Crystek Corporation CSCONN PRECISE ELECTRONICS CO.,LTD CT Micro International Co CTS Corporation CUI Inc CVI Laser, LLC CW Industries Cyntec Co Cypress Semiconductor Cyrustek Corporation CYStech Electronics Corp. CYT Opto-Electronic Technology Dachang Electronics Daewoo Semiconductor Daier Electron Co Dailywell Electronics Daishinku Corp Daito Communication Apparatus Daiyo Electronics Dallas Semiconductor DANFOSS Daniels Manufacturing Co Data Device Corporation Davicom Semiconductor Davies Molding, LLC DB Lectro Inc DB Unlimited DC Components Co Dean Technology DECA SwitchLab Inc Decawave Ltd Dechang Electronic Deep Sea Electronics DEGSON Electronics Co Dell Inspiron Delta Electronics DeMint Electronics DENSO Destiny Technology Corp Detaik Technology Co Deva Electronic Controls Limited. Devantech Device Engineering Inc Dexter Magnetic Technologies DFRobot. Dialight Electronics Company Dialog Semiconductor Dielectric Laboratories Digi International Digilent, Inc Digital Voice Systems Digitrax, Inc Digitron Semiconductors Dinkle International Co. Ltd DIN-TEK Microelectronics Diodes Incorporated Diotec Semiconductor Diptronics Manufacturing Inc Display Solution AG DISPLAY VISIONS GmbH 2022. DMB Technology DOESTEK Co DOINGTER Semiconductor Domintech Co Don Connex Electronics DONG IL TECHNOLOGY LTD. Dongguan CHENGXING Electronic Co Dongguan City Wasi Electronic Technology Dongguan Cosson DongGuan HeLing Electronics Dongguan Lanbo Electronics Technology CO Dongguan Yuandi Electronics Dongguan Yuanze Electric Co.,Ltd Dongguan Yuxi Precise Connector Co., Ltd Dongke semiconductor Anhui Co., Ltd Donguan Keyouda Electronic Dosilicon Co DTK electronics Dualsky Models Co Duoxing Electronics Co Duty-Cycle Semiconductor Dynamic Technologies (DTCC) Dynex Semiconductor Ltd, E &amp; E Magnetic Products Limited EAST Semiconductor East Texas Integrated Circuits Eastrising Technology Co Eastsensor Technology Easy IoT Eaton’s Bussmann Ebm-papst inc Echelon Corporation Ecliptek Corporation ECOFIT &amp; ETRI ECS, Inc International EDAC EECO Switch E-Elements Technology Co Efficient Power Conversion Co EG Microelectronics Corp EIC Semiconductor Elan Microelectronics Co Elantec, Inc Electrolube Electronic Alliance Electronic Assembly Electronic Devices Inc Electroustic Ltd Eledis Element14 ELESTA GmbH Elite Semiconductor Memory Eljen Technology Elm Electronics ELM Technology Co Elmos Semiconductor AG ELNA Company Elpida Memory, Inc EM Microelectronic-Marin EMAD Embedded Artists Embest Technology Emerson Encitech Endress+Hauser Management ENE Technology Enplas Corporation Enrwey Co Ltd Eon Silicon Solution E-peas Semiconductors Epitex Inc Epoxy Technology Inc EPSON Electronics Ept Inc Ericsson Microelectronics ERNI Electronics ERSA UK LTD Espressif Systems ESS Technologies E-Switch, Inc ET Enterprises Limited E-T-A Circuit Breakers ETA Solutions E-tec Interconnect Ethertronics Inc Etron Technology, Inc EUCHNER GmbH Eupec semiconductor Euroquartz Ltd Eutech Microelectronics Everanalog Everest Semiconductor Everlight Electronics Everspin Technologies Exar Corporation Excel Cell Electronic Excelitas Technologies Excellence Opto, Inc Excelliance MOS Corporation Fagor Electronica Fairchild Semiconductor Fair-Rite Products Corp FANUC Corporation Faraday Technology Fastline Fastrax Ltd FASTRON Faulhaber GmbH FDK Corporation Feature Integration Technology Feei Cherng Enterprise Feeling Technology Feiyi Technology FEMA Electronics Corporation Fenghua Advanced Technology Ferroxcube International FERYSTER Sp. z.o.o Figaro Engineering Inc Finder Relays, Inc Fingerprint Cards First Semiconductor First Sensor FIS Inc Fischer Connectors Fischer Elektronik Fitipower Integrated Technology Force MOS Technology Co Formosa MS Formox Semiconductor Forsentrk Fortior Technology Co Fortune Semiconductor Forward International Electronics FOTEK Controls Fox Electronics Foxconn Technology Fractus S.A Franz Binder GmbH &amp; Co. Free2Move Holding AB. Freescale Semiconductor Fremont Micro Devices Friendcom Technology Develop FriendlyARM Computer Tech FTDI Chip Fuda Hisi Microelectronics Fuji Electric Fujikura Fujitsu Semiconductor Fujitsu-Takamisawa Fulihua Printer Ribbon Co Futaba Corporation Fu-Yao Technology Co Fuzetec Technology Co Fuzhou Rockchip Electronics Co., Ltd GainSpan Corporation GalaxyCore Inc GaNPower International Inc G-Antetech Industrial Garmin Ltd. Gas Sensing Solutions Ltd. Gaston Electronics GC GE Fanuc GEC Plessey Geehy Semiconductor Co General Electronic Devices General Monitors General Semiconductor Generalplus Technology GeneSiC Semiconductor Genesis Microchip Inc Genesys Logic, Inc Genicom Co., Ltd. Gennum Corporation GETE Electronics GigaDevice Semiconductor Global Connector Technology (GCT) Global Mixed-mode Technology GlobespanVirata, Inc GMC Instruments GME Technology, LLC GoChip Electronic Technology GoldStar Semiconductor Gonbes Technology Co Good Display Good Will Instrument Good-Ark Semiconductor Goodix Technology Governors America Co Gpixel Microelectronics Inc Grayhill Inc GreatLEDs Co Greenliant Systems GRUNER AG GSI Technology, Inc Guangdong Hottech Co Guangdong Huaguan Semiconductor Guangdong TIANQIU Electronics Technology Guangzhou Aosong Electronics Guangzhou Xinyue Electronic Guerrilla RF, Inc H&amp;M Semiconductor HABEY Halbleiter aus Frankfurt HALO Electronics Hamamatsu Photonics Hangzhou Grow Technology Co Hangzhou Nationalchip Science Hangzhou Prosper Hangzhou Silan Microelectronics Hannstar Display Corp HanRun Electronics Hanwei Electronics Co Hanyoung Nux Co HAOHAI ELECTRONICS HAOYU Electronics Harris Semiconductor HARTING Technology Harvatek Corporation Harwin Hawyang Semiconductor Hebei International Trading Co HEITEC AG. Hemingruizhi Electronic Henan Hanwei Electronics Co Hengda New Materials Technology HengJiaXing Electronics Co Henkel Corporation HenLv Power Technology Heter Electronics Hewlett-Packard Hexin Technology Highly Electric Hi-Link Electronic Technology Hi-Optel Technology Hirose Electric Hi-Sincerity Microelectronics Hitachi Maxell, Ltd Hitachi Semiconductor HITPOINT Inc Hittite Microwave Hivolt Capacitors Ltd H-JTAG Technology Hokuriku Electric Industry Co Ltd Hokuyo Automatic Co Holt Integrated Circuits Holtek Semiconductor Honeywell International Hong Kong Resistors Manufactory Hongfa Electroacoustic Co HONGHUA ELECTRONIC Hope Microelectronics HORIBA, Ltd. Hosiden Corporation Hosonic Electronic Co Hotchip Technology HTC Korea TAEJIN Technology Huada Connectors Huanor International Huaqi Microelectronics Co Huawei Technologies Huayu Technology HuaYuan Micro Electronic Huayue Microelectronics Co HUBER+SUHNER Huibei KENTO Electronic Huidu Technology Hukx Sensor Technology Humirel Hurricane Tech. Co HW group s.r.o HYCON Technology Corp. Hynix Semiconductor Hyundai Semiconductor IC Plus Corp ICE Components, Inc. iC-Haus GmbH Icom Inc ICP DAS CO ID Innovations ID TECH IDEC Corporation IEI Integration Ignion Iintelligent Motion Systems IK Semiconductor ILSI America LLC IMP, Inc Inchange Semiconductor Industrial Fiber Optics, Inc Industrial Technology Research Institute Infineon Technologies Initio Corporation INJOINIC TECHNOLOGY Innolux Corporation InnoSenT-Innovative Radar Sensor Technology Innovative Sensor Technology IST Innuovo Magnetics Co Inova Semiconductors InPlay Inc. InPower Semiconductor INTEGRAL JSC Integrated Circuit Solution Integrated Circuit Systems Integrated Crystal Technology Integrated Device Technology Integrated Sensor Technologies Integrated Silicon Solution Intel Corporation InterFET Corp Interlink Electronics International CMOS Technology International Rectifier Intersil Corporation Intronic Semiconductor Intronics Power, Inc InvenSense Inc IQD Frequency Products Ltd IRAN Ironwood Electronics IRXON Electronic Isabellenhütte Heusler GmbH &amp; Co KG Isahaya Electronics Co iSentek Technology Isocom Components Isotek Corp ITE Tech ITT Cannon, LLC ITT Semiconductors Ituner Networks Corp iWatt Inc IXYS Integrated Circuits J.S.T. Mfg. Co JACKSON ELECTRONICS IND. CROP. JAE Electronics JAI Ltd Jamicon Electronics JAVAN JCET Group Co JCI Jewel Hill Electronic Co JHDLCM Electronics Jiangsu Changjiang Electronics Jiangsu Donghai Semiconductor Jiangsu Juguang Jiangsu Runic Technology Co Jiangsu Szdhdtgd Electronics Jiangxi Jia Wei Cheng Electronic Jilin Sino-Microelectronics Co Jinan USR IOT Technology JING LI Power Electronics Jingcheng Electronics Co Jinghan Switch Electronic JMicron Technology Corp JNHuaMao Technology JODO International Johanson Dielectrics Johanson Technology Johnson Electric JPC Company JYE Tech Ltd JYH HSU(JEC) ELECTRONICS Kai Suh Suh Enterprise KSS Kaida Holding Kaihua Electronics Co Kangmu Sheng Electronics Ka-Ro electronics GmbH. KEC Semiconductor Keil Elektronik Keithley Instruments Kelly Controls, LLC KEMET Corporation Key Technology Keysight Technologies Keystone Electronic King Core Electronics Kingbor Technology Kingbright Electronic KingCCTV Technology Kingdatron Electronic Industrial Co Kingsignal Technology Kingstate Electronics Kingston KIOXIA America, Inc Kiwi Instruments Corp Knowles Electronics KOA Speer Electronics Kobiconn Kodenshi Corp Kohshin Electric Corporation KONE Elevator Kontron S&amp;T KT Micro Inc Kunshan Sino Silicon Technology KUOYUH W.L. Enterprise Co Kutai Electronics Kycon, Inc Kyocera Corporation Ladder Electronics Co Laird Performance Materials. Laird Technologies Laser Components Lattice Semiconductor LawMate International L-com, Inc LD-PD Inc. Leadtrend Technology Corp LEAP Electronic Legerity, Inc Lelon Electronics Corp LEM Components LEMO Lenovo LENZE Lesfuse Electric Co Leshan Radio Co LG Semiconductor LG.Philips Displays Lianchao Future Technology Lighting Integration System Ligitek Electronics Co Lime Microsystems Lineage Power Private Limited Linear Systems Linear Technology Linfinity Microelectronics Link-PP Int'l Technology LinkSmart LINP OMTER International Linx Technologies Lision Technology LITE-ON Semiconductor Littelfuse Inc Lixin Electromagnetic Clutch LIZE Electronic Technology LND, INC LOETRONIC LOGIC Devices Incorporated Longtech Optics Co Longview Technologies Co Lovid International Electronic Low Power Radio Solutions Ltd LOZEN TECHNOLOGY LS ELECTRIC LS Mtron Ltd LSI Computer Systems LTKCHIP LTN Servotechnik GmbH Lucent Technologies LUCKFOX Technology Lucky Light Electronic Luguang Electronic Technology Lumberg Holding Lumentum Operations LLC. Lumex Inc Lumileds Luminus, Inc. Lumissil Microsystems Luna Optoelectronics Lutron Electronic Enterprise Co Lyontek Inc M.S. Kennedy Corp M+R Multitronik GmbH MACOM Technology Macroblock, Inc Macronix International MacTek Corp MagnaChip Semiconductor Magnetics MagnTek Microelectronics Magtek Technology Inc Manorshi Electronics Marktech Optoelectronics, Inc Marlow Industries, Inc Marquardt Switches, Inc Marvell International Matsushita Electric Max Echo Technology Corp MaxBotix Inc Maxic Technology Corporation Maxim Integrated MaxLinear Inc Maxon motor Maxwell Technologies Mayloon Electronic Company MCS Logic Inc Mcuzone International MEAN WELL Enterprises Co Measurement Specialties Mechanic MediaTek Inc Megatek Melexis Technologies Memory Protection Devices MEMSIC, Inc Mentor GmbH Mercury Electronic Meritek Electronics Corporation Mersen EP Metalink Broadband Meticom GmbH. METRODYNE MICROSYSTEM CORP. MIC Electronic Micrel, Inc Micro Commercial Components Micro Crystal AG Micro Electronics Micro Linear Micro One Electronics Micro Power Systems MICRO SENSOR CO;LTD Microchip Technology Microdiode Semiconductor Micrometals, Inc Micron Technology Micronet Communication Microsemi Corporation Microtech Technology Co Ltd Microtherm Sentronic GmbH Microtips Technology Midori Precisions MikroElektronika MikroElektronika d.o.o MikroTik Mill-Max Mfg Milnec Interconnect Systems MindMotion Microelectronics Co. Mingtek Electronics Ltd Mini-Circuits Minilogic Device Corporation Ltd Minmax Technology Minsoo Electronic Co MiTAC Computing Technology Mitel Semiconductor Mitsubishi Electric Mitsubishi Rayon Co Mitsumi Electric Co Mixed Signal Integration Mixic Electronics MKMX America LLC MMI Semiconductors MOAI electronics co Mobicon Electronic Component Modulestek Inc MOKO TECHNOLOGY LTD. Molex Electronic Monitor Enterprises Inc Monolithic Power Systems Morethanall Co Morningstar Corporation MORNSUN Science &amp; Technology Mosdesign Semiconductor Corp Mosel Vitelic Co MOSPEC Semiconductor MOS-TECH Semiconductor Mostek MOTIEN Technology Motorola Mstar Semiconductor M-Systems Inc Multicomp Multi-Inno Technology Multi-Tech Systems Inc Murata Manufacturing Co MVSILICON MYIR Tech Myrra SAS Naina Semiconductor Limited. Nanjing Haichuan Electronic Nanjing Ouzhuo Tech Nanjing Qinheng Microelectronics Nanjing Shiheng Elec NanJing Top Power ASIC Nanjing Up Electronic Technology Nanjing Wotian Technology Co Nanjing Zeming Electronic Co Nanya Technology Co National Instruments National Semiconductor NDK America Inc NEC Electronics Nell Semiconductor Neltron Industrial Nemoto Sensor Engineering NeuroSky, Inc. Neutrik New Jersey Semiconductor NewAE Technology Inc. Newava Technology Inc. Newhaven Display Newport Corporation NewTec Display Co NexFlash Technologies, Inc Nexperia USA Inc Nextchip Nextion NIC Components Corp. Nichia Corporation Nichicon Corporation Nidec Copal Electronics NIDEC SERVO CORPORATION. Nihon Dempa Kogyo Nihon Inter Electronics NIKO Semiconductor Ningbo East Electronics Ningbo ForwardRelayCorporationLTD Ningbo Gosun Technology Co Ningbo Huaguan Electronics Ningbo KLS Electronic Co Ningbo MAX Electronic Technology Co., Ltd Ningbo MKX Electronic Technology Ningbo Rel Electric Co., Ltd. Ningbo Songle Relay Ningbo Tianbo Ganglian Electronics Ninigi Nippon Chemi-Con Nippon Pulse America, Inc Nisshinbo Micro Devices Inc NJR Corporation NKK Switches NMB Technologies Non-Brand Norcomp Inc Nordic Semiconductor Noritake Itron Co Novacap Novatek Microelectronics NTE Electronics NUAND LLC. Nuvoton Technology NVE Corporation Nvidia NVS Navigation Technologies NXP Semiconductors NYS Resistor O2Micro OCIC co Octavo Systems LLC Ogemray Technology Co Ohmite OKI Semiconductor Ole Wolff Electronics Inc Olimex OmniVision Technologies Omron Electronics Omten Electronics ON Semiconductor ON Semiconductor CHINA On Shore Technology On-Bright Electronics OPTEK Technology Inc OPTi Inc Opticon Inc Opto 22 Opto Diode Corp Opto Electronics Co,. LTD OPTOLAB Microsystems Orient Display Oriental Semiconductor Orion Orion Display Technology Co OSI Optoelectronics OSRAM Opto Semiconductors OTAX Corporation Other Oupiin Enterprise Co OWON Technology Inc P&amp;E Microcomputer Systems Pacific Silicon Sensor Panasonic Corporation Panavision Imaging LLC Pancon Corporation PandaBoard PANJIT International Inc Para Light Electronics P-DUKE Technology Co PEAK Electronics GmbH PEAK-System Technik Penny &amp; Giles Peregrine Semiconductor Pericom Semiconductor Corp PerkinElmer Inc Phidgets, Inc Philips Semiconductor Phison Electronics Phoenix Contact Pickering Electronics Ltd PICO Electronics Pico Technology Piher Sensors &amp; Controls SA Pingjing Semi Technology PIR Sensor Co PixArt Imaging Inc Planar Systems, Inc PLX Technology PMC-Sierra, Inc PNI Sensor Corporation POCO Magnetic Polyfet RF Devices Polytronics Technology Pomona Electronics Power Integrations Power Mate Technology Power Systems GmbH Power-Changer Electronic Co Powerex Inc PowerPlaza Powersem GmbH Powertip Technology Preci-Dip SA Precision Monolithics, Inc PREMA Semiconductor GmbH Premier Magnetics PRETEC/C-One Technology Corp. Princeton Technology Proant AB Profichip GmbH Prokit's Industries Prolific Technology Inc Promax-Johnton Semiconductor Pro-Signal ProTek Devices Pro-Wave Electronic PRT PUI Audio Pulse Electronics Qimei Optical &amp; Electric Qingdao Mefine Electronics Qingxian Zeming Langxi Electronic Devices Co Qingyuan Tesla Electronic Technology Qorvo QT Brightek (QTB) QT Optoelectronics Qualcomm Atheros, Inc Quality Semiconductor Qualtek Electronics Quarton inc Quasar Electronics Limited Quectel Wireless Solutions QuickLogic Corporation QX Micro Devices Radiall Radxa Computer Rafael Microelectronics RAFI GmbH &amp; Co RAiO TECHNOLOGY INC RAKwireless Technology Limited. RALEC Ltd Ralink Technology Raltron Electronics Corporation Ramtron International Rapid Electronics Ltd Raspberry Pi Raycom Co Raytac Corporation. Raytheon RCA Corporation Ready Made RC LLC Realtek Semiconductor RECOM Power GmbH Rectron Semiconductor Reichelt elektronik GmbH &amp; Co. KG RELPOL S.A Renata SA Renesas Technology Renhotec Group Ltd Reomax Electronics Reyed Electronics Co RF Digital Corporation. RF Micro Devices RF Solutions Ltd RFaxis, Inc RFHIC Corporation RFM Integrated Device, Inc. RFT Mikroelektronik Rhombus Industries Inc Richtek Technology Co RichWave Technology Ricoh Electronic Devices Riedon RIGOL Ring&amp;tone Electronic Technology Riverdi RLS Merilna tehnika d.o.o ROBOTIS Co Rockwell Rogers Corporation ROHM Semiconductor Roithner Lasertechnik GmbH Rongtech Industry Royal Electronic Factory Co RS Components Ltd RTD Embedded Technologies Rubycon RYCHIP Semiconductor s.m.a.e. GmbH Saft Groupe S.A Sagami Electronics Saia-Burgess Switches Sakae Tsushin Kogyo Saleae, Inc Salecom Electronics Same Sky SamHop Microelectronics Samsung Electronics Samtec Samwha Capacitor Samwin Electronic Technology Samyoung S &amp; C Co SANCO Electronics Co SanDisk Sanhe Enclosure Sanjiaozhou Electrical Technology Sanken Electric SanRex Corporation Sanyo Denki Sanyo Electric Savantic Electronic Sawnics Inc Schaffner Group Schott AG Schrack Technik GmbH Schurter Inc Sciosense B.V. SCTF Electronics Seagate Technology LLC Seaparks Machinery-Electronics Seaward Electronics SeCoS Corporation SEED International Ltd Seeed Technology SEEQ Technology Segger Microcontroller Systems Seiko Instruments Inc Seiko NPC Corporation Semiconductor Circuits, Inc SemiHow Semikron Semiment Technologies Semi-Powerex Corp. SEMITEC Corporation SemiWell Semiconductor Semtech Corporation Semtech Electronics Senba Sensing Technology Co Sendo Sensor Sensata Technologies Sensirion Sentry Manufacturing Inc SEP Electronic Corp Servotecnica SpA SERVO-TEK PRODUCTS COMPANY, INC. SG Micro Corp SGX Sensortech Shaanxi Fullstar Electronics Co Shaanxi Qunli Electric Shaanxi Reactor Microelectronics Shandong Jingdao Microelectronics Shanghai AVIC Optoelectronics Shanghai Belling Co,Ltd Shanghai Consonance Electronics Shanghai Fengxin Electronic Technology Shanghai Fudan Microelectronics Shanghai Gotop Technology Shanghai High-Flying Electronics Shanghai Houde Photo-electric Shanghai Mixinno Microelectronics Co Shanghai Natlinear Electronics Shanghai Xinlong Semiconductor Shanghai Zhichuan Electronic Tech SHARP Corporation Sheng Jay Automation Techno Shenyang Guangcheng Technology Co., Ltd Shenyang KingStar Automation ShenZhen AI-thinker CO Shenzhen AnBoShi Electronic Shenzhen Asenware Test Shenzhen Baishan Mechatronics Shenzhen Biosled Technology Shenzhen Bolutek Technology Shenzhen Chipsea Technologies ShenZhen ChipSourceTek Technology Shenzhen ExSAF Electronics Co Shenzhen Genesis-Systech ShenZhen Gerbole Shenzhen Getech Co Shenzhen GUANGSHIMEI Electronic Shenzhen Hanxia Electronics Shenzhen Haolin Electronics Shenzhen Heliwei Technology Shenzhen honglifa Electronics Co Shenzhen HongyeX Electronics Co ShenZhen HuaXinAn Electronics Co.,Ltd Shenzhen Injoinic Technology Co. Shenzhen Jin Yu Semiconductor Co ShenZhen JINCI Technology Shenzhen Jinrui Electronic Material Co Shenzhen JMRTH Co Shenzhen Kaiyuexiang Electronics Co Shenzhen LFN Technology Co Shenzhen Lodestar S.T Co Shenzhen Lumen Electronics Shenzhen Magnetic Technology Shenzhen MilkV Technology Shenzhen Milliohm Electronics Shenzhen Minewsemi Co., Ltd Shenzhen Nsiway Tech Shenzhen Ou Chuangxin Semiconductor ShenZhen Qi Dian Shi Dai Technology Shenzhen Ruichips Semiconductor Shenzhen Ruilongyuan Electronics Shenzhen Shiji Lighting Shenzhen SI Semiconductors Shenzhen SLKOR Micro Semicon Co Shenzhen Sunmoon Microelectronics Shenzhen Suosemi Tech Shenzhen TongYiFang Optoelectronic Technology CO,Ltd Shenzhen Topmay Electronic Shenzhen TPOWER Semiconductor Shenzhen Universal Micro-Electronics Shenzhen USBR Precision Hardware Electronics Shenzhen Weidy Industrial Development Co., Ltd. Shenzhen Xinbole Electronics Co. Shenzhen Xptek Technology Shenzhen Xunlong Shenzhen Yangxing Technology Co. SHENZHEN YeZhan Electronics Shenzhen Yiwei Technology Shenzhen ZVELL Electronics Shindengen Electric Shin-Etsu Chemical Co SHINYEI Technology SHOEI SIBA GmbH Sichuan huafeng enterprise group SICK, Inc. Siemens Semiconductor Group Si-En Technology SiFirst Technology SiGe Semiconductor Sigma Microelectronics Signetics Silego Technology Silergy Corp Silicon Image Silicon Integrated Systems Silicon Laboratories Silicon Microstructures, Inc. Silicon Motion, Inc Silicon Sensing Systems Limited Silicon Standard Corp Silicon Storage Technology Silicon Systems Inc Silicon Touch Technology Silvan Chip Electronics Silver Telecom Ltd SilverStone Technology SIMCom Wireless Solutions SIMTEK Electronic Components Sinda Photoelectricity Technology SINGULAR TECHNOLOGY CO., LTD. Sinomags Technologies Co Sinopower Semiconductor Sipex Corporation Sirectifier Semiconductors SiTime Corporation Sivago Semiconductor Co SIWARD Crystal Technology Siyang Microelectronics Sizto Tech Corp SKYLAB M&amp;C Technology Skyworks Solutions, Inc SL Power Electronics Corp. SMAR Smartec BV SMC Diode Solutions Co. Smiths Interconnect. SMSC Corporation Soberton Inc Softing Automotive Electronics Sola/Hevi-Duty Sola-IC Solarflex SA Soldex Solid State Scientific SOLIDIC Solitronics Engineering Limited SOL-LED Lighting Co Solomon Systech Song Chuan Song Huei Electric Sonix Technology Sony Corporation Soundwell Electronic South African Micro-Electronic Systems Spansion inc SparkFun Electronics SPEC Sensors LLC Spectra Symbol Corp. Spectrum Digital Incorporated Speed Tech Corp Spin Semiconductor Sprague Semiconductors SPX Flow Technology ST Engineering Stackpole Electronics Standex-Meder Electronics Stannol GmbH Stanson Technology StarChips Technology StarPower Semiconductor Ltd. Startek Electronic Technology STATEK CORPORATION Stäubli International AG. STCmicro Technology Co Stewart Connector STMicroelectronics Stocko Stork Solutions Ltd. Sullins Connector Solutions SUMIDA Corporation Sun Hydraulics Corporation Sun Microelectronics SunLED SUNLORD Sunltech Tech SUNMATE Electronic Sunonwealth Electric Machine Sunplus Technology Sunrise Electronics Suntan Technology Company Suntsu Electronics, Inc. SUNYUAN Technology Supertex Inc Susumu International Suzhou Innoson Technology Suzhou NOVOSENSE Microelectronics Co., Ltd Suzhou Silikron Semiconductor Corp Switchcraft Inc. Switec SYNC Power Crop SyncMOS Technologies Synoxo International System General Corp Tadiran Batteries TAG Semiconductors TA-I Technology TAIKO-NET Tai-Saw Technology Tai-Tech Advanced Electronics Taitien Electronics Taitron Components, Inc Taiwan Alpha Electronic Co Taiwan Semiconductor Taiyo Electric Co Taiyo Yuden Tak Cheong Electronics Talema Group, LLC Tamagawa seiki Co Tamron Tamura Corporation TANCAP Technology Taoglas Limited TDK Corporation (EPCOS) TDK-Lambda Corporation TDK-Micronas GmbH TE Connectivity Team Source Display tech.co,ltd. Techcode Semiconductor Techpoint Inc Techspray/Plato-EMX Enterprises Limited Techstar Electronics TechToys Company TelCom Semiconductor Telcon Ltd Telechips Inc Teledyne Technologies TELEFUNKEN Elektroakustik Telegesis Ltd Telit TEMIC Semiconductor Terawins, Inc Teridian Semiconductor TESLA Testo SE &amp; Co Texas Advanced Optoelectronic Solutions Texas Instruments THAT Corporation Thegioiic Corporation Thermonamic Electronics(Jiangxi) Corp THine Electronics, Inc Thinki Semiconductor Thinking Electronic THOMSON Inc THORLABS Thousand Hundred Industrial Thunder Precision Resistor TIANMA Titan Micro TLC Electronics TNI-U TOOL Token Electronics Industry Tokmas Semiconductor TOKO, Inc Tontek Design Technology Top-arm Topro Technology Topway Technology Torex Semiconductor Toshiba Corporation touchSEMI TOYO LED ELECTRONICS LIMITED. TOYODA TR Electronic Nordic AB. Traco Electronic AG Transcom, Inc Transko Electronics, Inc. TRENDnet, Inc Trenz Electronic Triad Magnetics Trident Microsystems Trimble Inc TRINAMIC Motion Control TRinno Technology Co Tripath Technology TriQuint Semiconductor Truly Semiconductors TRW Inc TT Electronics TTM Technologies, Inc. TXC Corporation UBIQ Semiconductor Ubiquiti Inc u-blox UCE Ultrasonic Co UDF Semiconductor Ultisensor Electronics UNI SEMICONDUCTOR LIMITED Unicorn Microelectronics Corporation Unictron Technologies Corporation. Union Semiconductor Uniroyal Electronics Industry Co Unisonic Technologies Unitra Cemi Uni-Trend Technology Co Unitrode Corporation Universal Microelectronics UPI Semiconductor Corp US Digital US Micro Products. Usha India Ltd Ushio Opto Semiconductors UTRON Technology, Inc Vacuumschmelze GmbH VADEM LTD Vango Technologies, Inc Varitronix Limited VARTA AG Vatronics Technologies Ltd VBsemi Electronics Co. Ltd V-Chip Microsystems VectorNav Vectron International Vehicles instrumentation Device Venkel Ltd VIA Technologies Vicor Corporation Vigortronix Ltd. Vincotech Vishay Visual communication company Vitesse Semiconductor Vivesea VLSI Solution Vweb Corporation W. L. Gore &amp; Associates, Inc WAGO Kontakttechnik GmbH Wakefield Thermal, Inc. Walsin Technology Corporation Walter Electronic Co WanTcom, Inc Wavecom Waveshare Electronics Wavespectrum Laser Inc Wavetronics Technologies WAYTRONIC ELECTRONIC CO.LTD WeEn Semiconductors Weidmüller Interface GmbH Weipu connector Weltrend Semiconductor WENSHING Electronics Western Digital Corporation Willas Electronic Corp WIMA Winbond Electroni</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>205000</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>205000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>XL4015E1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>TO-263-5</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop?searchfilter=M3#dtl/35042</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>محصولات خانه دسته‌بندی‌ها فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه عبارت M3 جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش برند 1666 3M Dynapro 3M Interconnect 3PEAK Incorporated 4D Systems Pty Ltd A Power microelectronics AAEON Technology Aavid Thermalloy ABC Taiwan Electronics ABLIC Inc Abracon Corporation Acam-Messelectronic Acrian, Inc Actel Corporation Active-Semi, Inc Actox Corporation. AD Semiconductor Confidential Adafruit Industries LLC Adam Technologies, Inc ADDA Corp ADDtek Corp Adesto Technologies ADMtek Inc Advanced Acoustic Technology Corp. Advanced Analog Technology Advanced Analogic Technologies Advanced Card Systems Advanced Ceramic X Corp Advanced Linear Devices Inc Advanced Monolithic Systems Advanced Photonix, Inc Advanced Power Electronics Corp Advanced Power Technology Advanced Semiconductor Advantech Corp Advantech Equipment Corporation Aegis Electronic Group AEL Crystals Limited AEM, Inc Aerosemi Technology Co Afa Technologies Inc AG Electrical Technology Agere Systems Agilent Technologies AGM Semiconductor AIC tech Inc. Aimtec Aimtron Corporation Airoha Technology Corp AIRWAVE Technologies Inc AiSHi Capacitors Aixin Opto-Electrical Technology Albright International Ltd Alcatel Microelectronics Alcor Micro Corp Alex Connector Co Ltd Alfa Electronics Algocraft Srl. ALi Corporation Alinx Electronic Technology All Sensors Corporation Allegro Microsystems Alliance Memory Allied Vision, Inc. Allwinner Technology Almita Co. Ltd Alpha &amp; Omega Semiconductor Alpha Micro Components Alpha Semiconductor Alpha Wire Alphasense Ltd, Sensor Technology Alps Electric Co Altera Corporation Amazing Electronic Co Amazing Microelectronic Corp AMD American Microsemiconductors American Microsystems Inc American Power Management American Technical Ceramics Corp American Zettler, Inc. Ametherm, Inc AMI Semiconductor AMIC Technology Corp Amidon Associates, Inc Amlogic Inc. Amotech Corp AMPAK Technology Inc Amphenol Advanced Sensors Amphenol Corporation Amphenol FCI Amphenol RF Ampleon USA Inc ams AG Anachip Corp ANADIGICS Anadigm, Inc Analog Devices Analog Integrations Corporation Analog Microelectronics Analog Power Analogix Semiconductor Inc Anaren, Inc Ancol Electronics Co Andigilog, Inc ANENG Anhui FOSAN Semiconductor Anhui Vico Technologes Co Anovay Technologies Limited ANPEC Electronics Corp Ante Intelligent Company Limited AP Memory Technology. APC Propellers APEM Inc Apex Material Technology Apex Precision Power API Delevan Inc API Technologies Aplus Integrated Circuits Inc APMKorea Apogee Technology, Inc Applent Instruments Applied Micro Circuits Co AppoTech Ltd APT Electronics Co., Ltd. Aptek Technologies ArchNet Technology Arcol UK Ltd Arduino Arduino Nicla Voice. Arima Lasers Corporation Aristotle Enterprises Inc ARTCHIP Semiconductor Artesyn Embedded Technologies AS ENERGI Asahi Kasei Microdevices ASAHI Solder Asia Vital Components Asiliant Technologies ASIX Electronics Corp AsLic Microelectronics Corporation ASMedia Technology Inc. Associated Opto-Electronics Astec Semiconductor. Astrodyne TDI Corporation. ATE Electronics s.r.l Atech Technology Co ATEN International Co Atheros Communications, Inc ATI Technologies Inc Atlas Scientific LLC. Attend Technology Inc AU Optronics Corp Audiowell Electronics Co Auk Contractors Co AUK Semiconductor AUO Corporation AUREL S.P.A Austar Technology AuthenTec, Inc Autonics Corporation Avago Technologies AVANTEK INC. AverLogic Technologies, Inc AVerMedia Technologies Avia Semiconductor Avnet, Inc AVX Corporation AXElite Technology Co Axiomtek Axis Communications AZ Displays, Inc Azoteq Ltd BAFO Technologies Corp Bahar Enclosure Baumer International BBT-China Inc BCD Semiconductor Beckhoff Automation Beijing Boshida Beijing HRH Information Co Beijing Ultrasonic Beijing Yihongtai Technology Beijing Zhongxun Sifang Science &amp; Technology Beken Corporation Bel Fuse Inc Bel Power Solutions Inc Belden Inc Bellnix Bencent Tzeng Ind. Co. Ltd Betlux Beyond Innovation Technology BI Technologies Bicker Elektronik GmbH Billionton Systems Inc Bird Technologies Bi-Sonic Technology Bivar, Inc Blackhawk BLOCK Inc Bluegiga Technologies BOLYMIN,INC BONGSHIN LOADCELL CO. Bookly Micro Electronic Bosch Security Systems Inc Bosch Semiconductors Bosch Sensortec Bothhand USA Boundary Devices Bourns Inc Bowin Microelectronics Brainboxes Limited BRIGHT LED ELECTRONICS CORP. Bright Power Semiconductor BrightKing Inc Brilliance Semiconductor, Inc Broadchip Technology Broadcom Limited BroadLight Inc Brooktree Corporation Burr-Brown Corporation BYD Microelectronics Co., Ltd. C&amp;D Technologies C&amp;K Components Caddock Electronics Inc California Eastern Laboratories California Micro Devices Calogic LLC Cambridge Integrated Circuits Cambridge Silicon Ra dio Limited Camille Bauer Ltd Catalyst Semiconductor Celduc relais CellWise Microelectronics Co Cenker Enterprise Ltd Centenary Materials Co CeNtRa Science Corp Central Components Manufacturing Central Georgia Generator Central Semiconductor CEVA Technologies CFSensor Challenge Electronics Champion Microelectronic Changzhou changjie Technology Co Changzhou Cre-sound Electronics Changzhou DRM Changzhou Esuntech Co Changzhou Kennon ELectronics Changzhou TDA Electronic Changzhou Yuanwang Fluid Technology Chaozhou Three-circle (Group) Co chargebyte GmbH. Chengdu Ebyte Electronic Technology Chengdu Guosheng Technology Chengdu Xincheng Huachuang Electronic ChenMoun Electronic ChenYang Technologies Cheuk Yui Innovation Co Chi Mei Optoelectronics Chieful Science ＆ Technology Chilisin Electronics Co China Base Electronic Technology China ECU Tools Centre China Resources Microelectronics China Software Industry Association Chinfa Electronics Chingis Technology Corp Chino-Excel Technology Chipanalog Incorporated ChipLink Tech Chiplus Semiconductor ChipON Chipower Electronics CHIPS Technology Chipstar Microelectronics CHK Electronics Ltd Chogori USA Chongqing Shengpu Electronics Chrontel, Inc Chunghwa Picture Tubes Churod Electronics Chyao Shiunn Electronic Cincon Electronics Cinetech Ind Cirrus Logic Inc Cisco Systems CIT Relay &amp; Switch Citizen Finedevice Co Cixi AnXon Electronic Cixi Dafa precise Linker Co CiXi KaiFeng Electronics Co Cixi Kefa Electronics Cixi Max Electronics Co.,Ltd Clare, Inc Cliff Electronic Components Limited Cmedia Electronics Inc CML Microsystems Coil Master Co Coil Winding Coilcraft Inc Coiltronics (Eaton) Comchip Technology Commodore Semiconductor Comtec Crystals comtech aha corporation CONEC Elektronische Bauelemente GmbH Conesys,Inc. Conexant Systems, Inc Connfly Electronic Co Connor-Winfield Conquer Electronic Continental Device India Controlair Inc Conversion Devices, Inc Cooper Bussmann Coretek Opto Corporation. Cornell Dubilier Electronics Cortina Systems, Inc Cosel Co Ltd COSINE Nanoelectronics Coto Technology CR Powtech Co Cree, Inc Crydom Inc Crystal Semiconductor Corporation Crystalfontz Crystek Corporation CSCONN PRECISE ELECTRONICS CO.,LTD CT Micro International Co CTS Corporation CUI Inc CVI Laser, LLC CW Industries Cyntec Co Cypress Semiconductor Cyrustek Corporation CYStech Electronics Corp. CYT Opto-Electronic Technology Dachang Electronics Daewoo Semiconductor Daier Electron Co Dailywell Electronics Daishinku Corp Daito Communication Apparatus Daiyo Electronics Dallas Semiconductor DANFOSS Daniels Manufacturing Co Data Device Corporation Davicom Semiconductor Davies Molding, LLC DB Lectro Inc DB Unlimited DC Components Co Dean Technology DECA SwitchLab Inc Decawave Ltd Dechang Electronic Deep Sea Electronics DEGSON Electronics Co Dell Inspiron Delta Electronics DeMint Electronics DENSO Destiny Technology Corp Detaik Technology Co Deva Electronic Controls Limited. Devantech Device Engineering Inc Dexter Magnetic Technologies DFRobot. Dialight Electronics Company Dialog Semiconductor Dielectric Laboratories Digi International Digilent, Inc Digital Voice Systems Digitrax, Inc Digitron Semiconductors Dinkle International Co. Ltd DIN-TEK Microelectronics Diodes Incorporated Diotec Semiconductor Diptronics Manufacturing Inc Display Solution AG DISPLAY VISIONS GmbH 2022. DMB Technology DOESTEK Co DOINGTER Semiconductor Domintech Co Don Connex Electronics DONG IL TECHNOLOGY LTD. Dongguan CHENGXING Electronic Co Dongguan City Wasi Electronic Technology Dongguan Cosson DongGuan HeLing Electronics Dongguan Lanbo Electronics Technology CO Dongguan Yuandi Electronics Dongguan Yuanze Electric Co.,Ltd Dongguan Yuxi Precise Connector Co., Ltd Dongke semiconductor Anhui Co., Ltd Donguan Keyouda Electronic Dosilicon Co DTK electronics Dualsky Models Co Duoxing Electronics Co Duty-Cycle Semiconductor Dynamic Technologies (DTCC) Dynex Semiconductor Ltd, E &amp; E Magnetic Products Limited EAST Semiconductor East Texas Integrated Circuits Eastrising Technology Co Eastsensor Technology Easy IoT Eaton’s Bussmann Ebm-papst inc Echelon Corporation Ecliptek Corporation ECOFIT &amp; ETRI ECS, Inc International EDAC EECO Switch E-Elements Technology Co Efficient Power Conversion Co EG Microelectronics Corp EIC Semiconductor Elan Microelectronics Co Elantec, Inc Electrolube Electronic Alliance Electronic Assembly Electronic Devices Inc Electroustic Ltd Eledis Element14 ELESTA GmbH Elite Semiconductor Memory Eljen Technology Elm Electronics ELM Technology Co Elmos Semiconductor AG ELNA Company Elpida Memory, Inc EM Microelectronic-Marin EMAD Embedded Artists Embest Technology Emerson Encitech Endress+Hauser Management ENE Technology Enplas Corporation Enrwey Co Ltd Eon Silicon Solution E-peas Semiconductors Epitex Inc Epoxy Technology Inc EPSON Electronics Ept Inc Ericsson Microelectronics ERNI Electronics ERSA UK LTD Espressif Systems ESS Technologies E-Switch, Inc ET Enterprises Limited E-T-A Circuit Breakers ETA Solutions E-tec Interconnect Ethertronics Inc Etron Technology, Inc EUCHNER GmbH Eupec semiconductor Euroquartz Ltd Eutech Microelectronics Everanalog Everest Semiconductor Everlight Electronics Everspin Technologies Exar Corporation Excel Cell Electronic Excelitas Technologies Excellence Opto, Inc Excelliance MOS Corporation Fagor Electronica Fairchild Semiconductor Fair-Rite Products Corp FANUC Corporation Faraday Technology Fastline Fastrax Ltd FASTRON Faulhaber GmbH FDK Corporation Feature Integration Technology Feei Cherng Enterprise Feeling Technology Feiyi Technology FEMA Electronics Corporation Fenghua Advanced Technology Ferroxcube International FERYSTER Sp. z.o.o Figaro Engineering Inc Finder Relays, Inc Fingerprint Cards First Semiconductor First Sensor FIS Inc Fischer Connectors Fischer Elektronik Fitipower Integrated Technology Force MOS Technology Co Formosa MS Formox Semiconductor Forsentrk Fortior Technology Co Fortune Semiconductor Forward International Electronics FOTEK Controls Fox Electronics Foxconn Technology Fractus S.A Franz Binder GmbH &amp; Co. Free2Move Holding AB. Freescale Semiconductor Fremont Micro Devices Friendcom Technology Develop FriendlyARM Computer Tech FTDI Chip Fuda Hisi Microelectronics Fuji Electric Fujikura Fujitsu Semiconductor Fujitsu-Takamisawa Fulihua Printer Ribbon Co Futaba Corporation Fu-Yao Technology Co Fuzetec Technology Co Fuzhou Rockchip Electronics Co., Ltd GainSpan Corporation GalaxyCore Inc GaNPower International Inc G-Antetech Industrial Garmin Ltd. Gas Sensing Solutions Ltd. Gaston Electronics GC GE Fanuc GEC Plessey Geehy Semiconductor Co General Electronic Devices General Monitors General Semiconductor Generalplus Technology GeneSiC Semiconductor Genesis Microchip Inc Genesys Logic, Inc Genicom Co., Ltd. Gennum Corporation GETE Electronics GigaDevice Semiconductor Global Connector Technology (GCT) Global Mixed-mode Technology GlobespanVirata, Inc GMC Instruments GME Technology, LLC GoChip Electronic Technology GoldStar Semiconductor Gonbes Technology Co Good Display Good Will Instrument Good-Ark Semiconductor Goodix Technology Governors America Co Gpixel Microelectronics Inc Grayhill Inc GreatLEDs Co Greenliant Systems GRUNER AG GSI Technology, Inc Guangdong Hottech Co Guangdong Huaguan Semiconductor Guangdong TIANQIU Electronics Technology Guangzhou Aosong Electronics Guangzhou Xinyue Electronic Guerrilla RF, Inc H&amp;M Semiconductor HABEY Halbleiter aus Frankfurt HALO Electronics Hamamatsu Photonics Hangzhou Grow Technology Co Hangzhou Nationalchip Science Hangzhou Prosper Hangzhou Silan Microelectronics Hannstar Display Corp HanRun Electronics Hanwei Electronics Co Hanyoung Nux Co HAOHAI ELECTRONICS HAOYU Electronics Harris Semiconductor HARTING Technology Harvatek Corporation Harwin Hawyang Semiconductor Hebei International Trading Co HEITEC AG. Hemingruizhi Electronic Henan Hanwei Electronics Co Hengda New Materials Technology HengJiaXing Electronics Co Henkel Corporation HenLv Power Technology Heter Electronics Hewlett-Packard Hexin Technology Highly Electric Hi-Link Electronic Technology Hi-Optel Technology Hirose Electric Hi-Sincerity Microelectronics Hitachi Maxell, Ltd Hitachi Semiconductor HITPOINT Inc Hittite Microwave Hivolt Capacitors Ltd H-JTAG Technology Hokuriku Electric Industry Co Ltd Hokuyo Automatic Co Holt Integrated Circuits Holtek Semiconductor Honeywell International Hong Kong Resistors Manufactory Hongfa Electroacoustic Co HONGHUA ELECTRONIC Hope Microelectronics HORIBA, Ltd. Hosiden Corporation Hosonic Electronic Co Hotchip Technology HTC Korea TAEJIN Technology Huada Connectors Huanor International Huaqi Microelectronics Co Huawei Technologies Huayu Technology HuaYuan Micro Electronic Huayue Microelectronics Co HUBER+SUHNER Huibei KENTO Electronic Huidu Technology Hukx Sensor Technology Humirel Hurricane Tech. Co HW group s.r.o HYCON Technology Corp. Hynix Semiconductor Hyundai Semiconductor IC Plus Corp ICE Components, Inc. iC-Haus GmbH Icom Inc ICP DAS CO ID Innovations ID TECH IDEC Corporation IEI Integration Ignion Iintelligent Motion Systems IK Semiconductor ILSI America LLC IMP, Inc Inchange Semiconductor Industrial Fiber Optics, Inc Industrial Technology Research Institute Infineon Technologies Initio Corporation INJOINIC TECHNOLOGY Innolux Corporation InnoSenT-Innovative Radar Sensor Technology Innovative Sensor Technology IST Innuovo Magnetics Co Inova Semiconductors InPlay Inc. InPower Semiconductor INTEGRAL JSC Integrated Circuit Solution Integrated Circuit Systems Integrated Crystal Technology Integrated Device Technology Integrated Sensor Technologies Integrated Silicon Solution Intel Corporation InterFET Corp Interlink Electronics International CMOS Technology International Rectifier Intersil Corporation Intronic Semiconductor Intronics Power, Inc InvenSense Inc IQD Frequency Products Ltd IRAN Ironwood Electronics IRXON Electronic Isabellenhütte Heusler GmbH &amp; Co KG Isahaya Electronics Co iSentek Technology Isocom Components Isotek Corp ITE Tech ITT Cannon, LLC ITT Semiconductors Ituner Networks Corp iWatt Inc IXYS Integrated Circuits J.S.T. Mfg. Co JACKSON ELECTRONICS IND. CROP. JAE Electronics JAI Ltd Jamicon Electronics JAVAN JCET Group Co JCI Jewel Hill Electronic Co JHDLCM Electronics Jiangsu Changjiang Electronics Jiangsu Donghai Semiconductor Jiangsu Juguang Jiangsu Runic Technology Co Jiangsu Szdhdtgd Electronics Jiangxi Jia Wei Cheng Electronic Jilin Sino-Microelectronics Co Jinan USR IOT Technology JING LI Power Electronics Jingcheng Electronics Co Jinghan Switch Electronic JMicron Technology Corp JNHuaMao Technology JODO International Johanson Dielectrics Johanson Technology Johnson Electric JPC Company JYE Tech Ltd JYH HSU(JEC) ELECTRONICS Kai Suh Suh Enterprise KSS Kaida Holding Kaihua Electronics Co Kangmu Sheng Electronics Ka-Ro electronics GmbH. KEC Semiconductor Keil Elektronik Keithley Instruments Kelly Controls, LLC KEMET Corporation Key Technology Keysight Technologies Keystone Electronic King Core Electronics Kingbor Technology Kingbright Electronic KingCCTV Technology Kingdatron Electronic Industrial Co Kingsignal Technology Kingstate Electronics Kingston KIOXIA America, Inc Kiwi Instruments Corp Knowles Electronics KOA Speer Electronics Kobiconn Kodenshi Corp Kohshin Electric Corporation KONE Elevator Kontron S&amp;T KT Micro Inc Kunshan Sino Silicon Technology KUOYUH W.L. Enterprise Co Kutai Electronics Kycon, Inc Kyocera Corporation Ladder Electronics Co Laird Performance Materials. Laird Technologies Laser Components Lattice Semiconductor LawMate International L-com, Inc LD-PD Inc. Leadtrend Technology Corp LEAP Electronic Legerity, Inc Lelon Electronics Corp LEM Components LEMO Lenovo LENZE Lesfuse Electric Co Leshan Radio Co LG Semiconductor LG.Philips Displays Lianchao Future Technology Lighting Integration System Ligitek Electronics Co Lime Microsystems Lineage Power Private Limited Linear Systems Linear Technology Linfinity Microelectronics Link-PP Int'l Technology LinkSmart LINP OMTER International Linx Technologies Lision Technology LITE-ON Semiconductor Littelfuse Inc Lixin Electromagnetic Clutch LIZE Electronic Technology LND, INC LOETRONIC LOGIC Devices Incorporated Longtech Optics Co Longview Technologies Co Lovid International Electronic Low Power Radio Solutions Ltd LOZEN TECHNOLOGY LS ELECTRIC LS Mtron Ltd LSI Computer Systems LTKCHIP LTN Servotechnik GmbH Lucent Technologies LUCKFOX Technology Lucky Light Electronic Luguang Electronic Technology Lumberg Holding Lumentum Operations LLC. Lumex Inc Lumileds Luminus, Inc. Lumissil Microsystems Luna Optoelectronics Lutron Electronic Enterprise Co Lyontek Inc M.S. Kennedy Corp M+R Multitronik GmbH MACOM Technology Macroblock, Inc Macronix International MacTek Corp MagnaChip Semiconductor Magnetics MagnTek Microelectronics Magtek Technology Inc Manorshi Electronics Marktech Optoelectronics, Inc Marlow Industries, Inc Marquardt Switches, Inc Marvell International Matsushita Electric Max Echo Technology Corp MaxBotix Inc Maxic Technology Corporation Maxim Integrated MaxLinear Inc Maxon motor Maxwell Technologies Mayloon Electronic Company MCS Logic Inc Mcuzone International MEAN WELL Enterprises Co Measurement Specialties Mechanic MediaTek Inc Megatek Melexis Technologies Memory Protection Devices MEMSIC, Inc Mentor GmbH Mercury Electronic Meritek Electronics Corporation Mersen EP Metalink Broadband Meticom GmbH. METRODYNE MICROSYSTEM CORP. MIC Electronic Micrel, Inc Micro Commercial Components Micro Crystal AG Micro Electronics Micro Linear Micro One Electronics Micro Power Systems MICRO SENSOR CO;LTD Microchip Technology Microdiode Semiconductor Micrometals, Inc Micron Technology Micronet Communication Microsemi Corporation Microtech Technology Co Ltd Microtherm Sentronic GmbH Microtips Technology Midori Precisions MikroElektronika MikroElektronika d.o.o MikroTik Mill-Max Mfg Milnec Interconnect Systems MindMotion Microelectronics Co. Mingtek Electronics Ltd Mini-Circuits Minilogic Device Corporation Ltd Minmax Technology Minsoo Electronic Co MiTAC Computing Technology Mitel Semiconductor Mitsubishi Electric Mitsubishi Rayon Co Mitsumi Electric Co Mixed Signal Integration Mixic Electronics MKMX America LLC MMI Semiconductors MOAI electronics co Mobicon Electronic Component Modulestek Inc MOKO TECHNOLOGY LTD. Molex Electronic Monitor Enterprises Inc Monolithic Power Systems Morethanall Co Morningstar Corporation MORNSUN Science &amp; Technology Mosdesign Semiconductor Corp Mosel Vitelic Co MOSPEC Semiconductor MOS-TECH Semiconductor Mostek MOTIEN Technology Motorola Mstar Semiconductor M-Systems Inc Multicomp Multi-Inno Technology Multi-Tech Systems Inc Murata Manufacturing Co MVSILICON MYIR Tech Myrra SAS Naina Semiconductor Limited. Nanjing Haichuan Electronic Nanjing Ouzhuo Tech Nanjing Qinheng Microelectronics Nanjing Shiheng Elec NanJing Top Power ASIC Nanjing Up Electronic Technology Nanjing Wotian Technology Co Nanjing Zeming Electronic Co Nanya Technology Co National Instruments National Semiconductor NDK America Inc NEC Electronics Nell Semiconductor Neltron Industrial Nemoto Sensor Engineering NeuroSky, Inc. Neutrik New Jersey Semiconductor NewAE Technology Inc. Newava Technology Inc. Newhaven Display Newport Corporation NewTec Display Co NexFlash Technologies, Inc Nexperia USA Inc Nextchip Nextion NIC Components Corp. Nichia Corporation Nichicon Corporation Nidec Copal Electronics NIDEC SERVO CORPORATION. Nihon Dempa Kogyo Nihon Inter Electronics NIKO Semiconductor Ningbo East Electronics Ningbo ForwardRelayCorporationLTD Ningbo Gosun Technology Co Ningbo Huaguan Electronics Ningbo KLS Electronic Co Ningbo MAX Electronic Technology Co., Ltd Ningbo MKX Electronic Technology Ningbo Rel Electric Co., Ltd. Ningbo Songle Relay Ningbo Tianbo Ganglian Electronics Ninigi Nippon Chemi-Con Nippon Pulse America, Inc Nisshinbo Micro Devices Inc NJR Corporation NKK Switches NMB Technologies Non-Brand Norcomp Inc Nordic Semiconductor Noritake Itron Co Novacap Novatek Microelectronics NTE Electronics NUAND LLC. Nuvoton Technology NVE Corporation Nvidia NVS Navigation Technologies NXP Semiconductors NYS Resistor O2Micro OCIC co Octavo Systems LLC Ogemray Technology Co Ohmite OKI Semiconductor Ole Wolff Electronics Inc Olimex OmniVision Technologies Omron Electronics Omten Electronics ON Semiconductor ON Semiconductor CHINA On Shore Technology On-Bright Electronics OPTEK Technology Inc OPTi Inc Opticon Inc Opto 22 Opto Diode Corp Opto Electronics Co,. LTD OPTOLAB Microsystems Orient Display Oriental Semiconductor Orion Orion Display Technology Co OSI Optoelectronics OSRAM Opto Semiconductors OTAX Corporation Other Oupiin Enterprise Co OWON Technology Inc P&amp;E Microcomputer Systems Pacific Silicon Sensor Panasonic Corporation Panavision Imaging LLC Pancon Corporation PandaBoard PANJIT International Inc Para Light Electronics P-DUKE Technology Co PEAK Electronics GmbH PEAK-System Technik Penny &amp; Giles Peregrine Semiconductor Pericom Semiconductor Corp PerkinElmer Inc Phidgets, Inc Philips Semiconductor Phison Electronics Phoenix Contact Pickering Electronics Ltd PICO Electronics Pico Technology Piher Sensors &amp; Controls SA Pingjing Semi Technology PIR Sensor Co PixArt Imaging Inc Planar Systems, Inc PLX Technology PMC-Sierra, Inc PNI Sensor Corporation POCO Magnetic Polyfet RF Devices Polytronics Technology Pomona Electronics Power Integrations Power Mate Technology Power Systems GmbH Power-Changer Electronic Co Powerex Inc PowerPlaza Powersem GmbH Powertip Technology Preci-Dip SA Precision Monolithics, Inc PREMA Semiconductor GmbH Premier Magnetics PRETEC/C-One Technology Corp. Princeton Technology Proant AB Profichip GmbH Prokit's Industries Prolific Technology Inc Promax-Johnton Semiconductor Pro-Signal ProTek Devices Pro-Wave Electronic PRT PUI Audio Pulse Electronics Qimei Optical &amp; Electric Qingdao Mefine Electronics Qingxian Zeming Langxi Electronic Devices Co Qingyuan Tesla Electronic Technology Qorvo QT Brightek (QTB) QT Optoelectronics Qualcomm Atheros, Inc Quality Semiconductor Qualtek Electronics Quarton inc Quasar Electronics Limited Quectel Wireless Solutions QuickLogic Corporation QX Micro Devices Radiall Radxa Computer Rafael Microelectronics RAFI GmbH &amp; Co RAiO TECHNOLOGY INC RAKwireless Technology Limited. RALEC Ltd Ralink Technology Raltron Electronics Corporation Ramtron International Rapid Electronics Ltd Raspberry Pi Raycom Co Raytac Corporation. Raytheon RCA Corporation Ready Made RC LLC Realtek Semiconductor RECOM Power GmbH Rectron Semiconductor Reichelt elektronik GmbH &amp; Co. KG RELPOL S.A Renata SA Renesas Technology Renhotec Group Ltd Reomax Electronics Reyed Electronics Co RF Digital Corporation. RF Micro Devices RF Solutions Ltd RFaxis, Inc RFHIC Corporation RFM Integrated Device, Inc. RFT Mikroelektronik Rhombus Industries Inc Richtek Technology Co RichWave Technology Ricoh Electronic Devices Riedon RIGOL Ring&amp;tone Electronic Technology Riverdi RLS Merilna tehnika d.o.o ROBOTIS Co Rockwell Rogers Corporation ROHM Semiconductor Roithner Lasertechnik GmbH Rongtech Industry Royal Electronic Factory Co RS Components Ltd RTD Embedded Technologies Rubycon RYCHIP Semiconductor s.m.a.e. GmbH Saft Groupe S.A Sagami Electronics Saia-Burgess Switches Sakae Tsushin Kogyo Saleae, Inc Salecom Electronics Same Sky SamHop Microelectronics Samsung Electronics Samtec Samwha Capacitor Samwin Electronic Technology Samyoung S &amp; C Co SANCO Electronics Co SanDisk Sanhe Enclosure Sanjiaozhou Electrical Technology Sanken Electric SanRex Corporation Sanyo Denki Sanyo Electric Savantic Electronic Sawnics Inc Schaffner Group Schott AG Schrack Technik GmbH Schurter Inc Sciosense B.V. SCTF Electronics Seagate Technology LLC Seaparks Machinery-Electronics Seaward Electronics SeCoS Corporation SEED International Ltd Seeed Technology SEEQ Technology Segger Microcontroller Systems Seiko Instruments Inc Seiko NPC Corporation Semiconductor Circuits, Inc SemiHow Semikron Semiment Technologies Semi-Powerex Corp. SEMITEC Corporation SemiWell Semiconductor Semtech Corporation Semtech Electronics Senba Sensing Technology Co Sendo Sensor Sensata Technologies Sensirion Sentry Manufacturing Inc SEP Electronic Corp Servotecnica SpA SERVO-TEK PRODUCTS COMPANY, INC. SG Micro Corp SGX Sensortech Shaanxi Fullstar Electronics Co Shaanxi Qunli Electric Shaanxi Reactor Microelectronics Shandong Jingdao Microelectronics Shanghai AVIC Optoelectronics Shanghai Belling Co,Ltd Shanghai Consonance Electronics Shanghai Fengxin Electronic Technology Shanghai Fudan Microelectronics Shanghai Gotop Technology Shanghai High-Flying Electronics Shanghai Houde Photo-electric Shanghai Mixinno Microelectronics Co Shanghai Natlinear Electronics Shanghai Xinlong Semiconductor Shanghai Zhichuan Electronic Tech SHARP Corporation Sheng Jay Automation Techno Shenyang Guangcheng Technology Co., Ltd Shenyang KingStar Automation ShenZhen AI-thinker CO Shenzhen AnBoShi Electronic Shenzhen Asenware Test Shenzhen Baishan Mechatronics Shenzhen Biosled Technology Shenzhen Bolutek Technology Shenzhen Chipsea Technologies ShenZhen ChipSourceTek Technology Shenzhen ExSAF Electronics Co Shenzhen Genesis-Systech ShenZhen Gerbole Shenzhen Getech Co Shenzhen GUANGSHIMEI Electronic Shenzhen Hanxia Electronics Shenzhen Haolin Electronics Shenzhen Heliwei Technology Shenzhen honglifa Electronics Co Shenzhen HongyeX Electronics Co ShenZhen HuaXinAn Electronics Co.,Ltd Shenzhen Injoinic Technology Co. Shenzhen Jin Yu Semiconductor Co ShenZhen JINCI Technology Shenzhen Jinrui Electronic Material Co Shenzhen JMRTH Co Shenzhen Kaiyuexiang Electronics Co Shenzhen LFN Technology Co Shenzhen Lodestar S.T Co Shenzhen Lumen Electronics Shenzhen Magnetic Technology Shenzhen MilkV Technology Shenzhen Milliohm Electronics Shenzhen Minewsemi Co., Ltd Shenzhen Nsiway Tech Shenzhen Ou Chuangxin Semiconductor ShenZhen Qi Dian Shi Dai Technology Shenzhen Ruichips Semiconductor Shenzhen Ruilongyuan Electronics Shenzhen Shiji Lighting Shenzhen SI Semiconductors Shenzhen SLKOR Micro Semicon Co Shenzhen Sunmoon Microelectronics Shenzhen Suosemi Tech Shenzhen TongYiFang Optoelectronic Technology CO,Ltd Shenzhen Topmay Electronic Shenzhen TPOWER Semiconductor Shenzhen Universal Micro-Electronics Shenzhen USBR Precision Hardware Electronics Shenzhen Weidy Industrial Development Co., Ltd. Shenzhen Xinbole Electronics Co. Shenzhen Xptek Technology Shenzhen Xunlong Shenzhen Yangxing Technology Co. SHENZHEN YeZhan Electronics Shenzhen Yiwei Technology Shenzhen ZVELL Electronics Shindengen Electric Shin-Etsu Chemical Co SHINYEI Technology SHOEI SIBA GmbH Sichuan huafeng enterprise group SICK, Inc. Siemens Semiconductor Group Si-En Technology SiFirst Technology SiGe Semiconductor Sigma Microelectronics Signetics Silego Technology Silergy Corp Silicon Image Silicon Integrated Systems Silicon Laboratories Silicon Microstructures, Inc. Silicon Motion, Inc Silicon Sensing Systems Limited Silicon Standard Corp Silicon Storage Technology Silicon Systems Inc Silicon Touch Technology Silvan Chip Electronics Silver Telecom Ltd SilverStone Technology SIMCom Wireless Solutions SIMTEK Electronic Components Sinda Photoelectricity Technology SINGULAR TECHNOLOGY CO., LTD. Sinomags Technologies Co Sinopower Semiconductor Sipex Corporation Sirectifier Semiconductors SiTime Corporation Sivago Semiconductor Co SIWARD Crystal Technology Siyang Microelectronics Sizto Tech Corp SKYLAB M&amp;C Technology Skyworks Solutions, Inc SL Power Electronics Corp. SMAR Smartec BV SMC Diode Solutions Co. Smiths Interconnect. SMSC Corporation Soberton Inc Softing Automotive Electronics Sola/Hevi-Duty Sola-IC Solarflex SA Soldex Solid State Scientific SOLIDIC Solitronics Engineering Limited SOL-LED Lighting Co Solomon Systech Song Chuan Song Huei Electric Sonix Technology Sony Corporation Soundwell Electronic South African Micro-Electronic Systems Spansion inc SparkFun Electronics SPEC Sensors LLC Spectra Symbol Corp. Spectrum Digital Incorporated Speed Tech Corp Spin Semiconductor Sprague Semiconductors SPX Flow Technology ST Engineering Stackpole Electronics Standex-Meder Electronics Stannol GmbH Stanson Technology StarChips Technology StarPower Semiconductor Ltd. Startek Electronic Technology STATEK CORPORATION Stäubli International AG. STCmicro Technology Co Stewart Connector STMicroelectronics Stocko Stork Solutions Ltd. Sullins Connector Solutions SUMIDA Corporation Sun Hydraulics Corporation Sun Microelectronics SunLED SUNLORD Sunltech Tech SUNMATE Electronic Sunonwealth Electric Machine Sunplus Technology Sunrise Electronics Suntan Technology Company Suntsu Electronics, Inc. SUNYUAN Technology Supertex Inc Susumu International Suzhou Innoson Technology Suzhou NOVOSENSE Microelectronics Co., Ltd Suzhou Silikron Semiconductor Corp Switchcraft Inc. Switec SYNC Power Crop SyncMOS Technologies Synoxo International System General Corp Tadiran Batteries TAG Semiconductors TA-I Technology TAIKO-NET Tai-Saw Technology Tai-Tech Advanced Electronics Taitien Electronics Taitron Components, Inc Taiwan Alpha Electronic Co Taiwan Semiconductor Taiyo Electric Co Taiyo Yuden Tak Cheong Electronics Talema Group, LLC Tamagawa seiki Co Tamron Tamura Corporation TANCAP Technology Taoglas Limited TDK Corporation (EPCOS) TDK-Lambda Corporation TDK-Micronas GmbH TE Connectivity Team Source Display tech.co,ltd. Techcode Semiconductor Techpoint Inc Techspray/Plato-EMX Enterprises Limited Techstar Electronics TechToys Company TelCom Semiconductor Telcon Ltd Telechips Inc Teledyne Technologies TELEFUNKEN Elektroakustik Telegesis Ltd Telit TEMIC Semiconductor Terawins, Inc Teridian Semiconductor TESLA Testo SE &amp; Co Texas Advanced Optoelectronic Solutions Texas Instruments THAT Corporation Thegioiic Corporation Thermonamic Electronics(Jiangxi) Corp THine Electronics, Inc Thinki Semiconductor Thinking Electronic THOMSON Inc THORLABS Thousand Hundred Industrial Thunder Precision Resistor TIANMA Titan Micro TLC Electronics TNI-U TOOL Token Electronics Industry Tokmas Semiconductor TOKO, Inc Tontek Design Technology Top-arm Topro Technology Topway Technology Torex Semiconductor Toshiba Corporation touchSEMI TOYO LED ELECTRONICS LIMITED. TOYODA TR Electronic Nordic AB. Traco Electronic AG Transcom, Inc Transko Electronics, Inc. TRENDnet, Inc Trenz Electronic Triad Magnetics Trident Microsystems Trimble Inc TRINAMIC Motion Control TRinno Technology Co Tripath Technology TriQuint Semiconductor Truly Semiconductors TRW Inc TT Electronics TTM Technologies, Inc. TXC Corporation UBIQ Semiconductor Ubiquiti Inc u-blox UCE Ultrasonic Co UDF Semiconductor Ultisensor Electronics UNI SEMICONDUCTOR LIMITED Unicorn Microelectronics Corporation Unictron Technologies Corporation. Union Semiconductor Uniroyal Electronics Industry Co Unisonic Technologies Unitra Cemi Uni-Trend Technology Co Unitrode Corporation Universal Microelectronics UPI Semiconductor Corp US Digital US Micro Products. Usha India Ltd Ushio Opto Semiconductors UTRON Technology, Inc Vacuumschmelze GmbH VADEM LTD Vango Technologies, Inc Varitronix Limited VARTA AG Vatronics Technologies Ltd VBsemi Electronics Co. Ltd V-Chip Microsystems VectorNav Vectron International Vehicles instrumentation Device Venkel Ltd VIA Technologies Vicor Corporation Vigortronix Ltd. Vincotech Vishay Visual communication company Vitesse Semiconductor Vivesea VLSI Solution Vweb Corporation W. L. Gore &amp; Associates, Inc WAGO Kontakttechnik GmbH Wakefield Thermal, Inc. Walsin Technology Corporation Walter Electronic Co WanTcom, Inc Wavecom Waveshare Electronics Wavespectrum Laser Inc Wavetronics Technologies WAYTRONIC ELECTRONIC CO.LTD WeEn Semiconductors Weidmüller Interface GmbH Weipu connector Weltrend Semiconductor WENSHING Electronics Western Digital Corporation Willas Electronic Corp WIMA Winbond Electronics W</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>69900</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>69900</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PC817X3CSP9F</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>U7,U12</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OPTO-SMD-4_L4.6-W6.5-P2.54-LS10.3-TL</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/category/637/transistor-output-optocouplers/%d8%a2%db%8c-%d8%b3%db%8c-%d8%a7%d9%be%d8%aa%d9%88-%d8%aa%d8%b1%d8%a7%d9%86%d8%b2%db%8c%d8%b3%d8%aa%d9%88%d8%b1#dtl/5800</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>آی سی اپتو ترانزیستور خانه دسته‌بندی‌ها آی سی اپتو ترانزیستور معرفی کوتاه و حرفه‌ای
+آی‌سی اپتو ترانزیستور یک قطعه الکترونیکی است که برای ایزولاسیون و انتقال سیگنال‌ها بین دو بخش مدار با استفاده از نور طراحی شده است. این قطعه شامل یک LED برای ارسال نور و یک ترانزیستور برای دریافت و تقویت سیگنال نوری است. اپتو ترانزیستورها در مدارهایی که نیاز به جداسازی الکتریکی بین ورودی و خروجی دارند، کاربرد دارند.
+ساختار
+LED مادون قرمز: برای ارسال سیگنال نوری به گیرنده
+فوتودیود یا ترانزیستور: برای دریافت سیگنال نوری و تبدیل آن به سیگنال الکتریکی
+ترانزیستور خروجی: که سیگنال دریافت شده را تقویت و به خروجی دیجیتال تبدیل می‌کند
+عایق نوری: که بین بخش‌های ورودی و خروجی جداسازی الکتریکی فراهم می‌کند
+ویژگی‌ها
+ایزولاسیون الکتریکی بین ورودی و خروجی
+خروجی دیجیتال یا آنالوگ برای کنترل مدارها
+سرعت سوئیچینگ بالا
+کاهش نویز و تداخل الکتریکی
+طراحی فشرده و نصب آسان
+مصرف انرژی پایین
+کاربردها
+سیستم‌های کنترل از راه دور
+ارتباطات بین مدارهای با ولتاژهای مختلف
+ایزولاسیون میکروکنترلرها و سیستم‌های دیجیتال
+مدارهای سوئیچینگ و منابع تغذیه
+سیستم‌های اندازه‌گیری و کنترل صنعتی
+استفاده در سیستم‌های هشدار و رگولاتورها
+چند نمونه از قطعه
+PC817 (اپتو ترانزیستور برای ارتباطات دیجیتال و کنترل‌ها)
+4N25 (اپتو ترانزیستور برای کاربردهای عمومی)
+4N35 (اپتو ترانزیستور برای ایزولاسیون و سیستم‌های صنعتی)
+توضیحات تکمیلی
+آی‌سی‌های اپتو ترانزیستور به دلیل ایزولاسیون الکتریکی که فراهم می‌کنند، در بسیاری از سیستم‌های الکترونیکی که نیاز به جداسازی ورودی و خروجی دارند، به‌ویژه در میکروکنترلرها و مدارهای حساس به نویز و تداخل، کاربرد دارند. این قطعات به‌طور گسترده در منابع تغذیه، سیستم‌های کنترل صنعتی و تجهیزات ارتباطی استفاده می‌شوند و به‌ویژه برای کاربردهایی که به ایمنی و حفاظت نیاز دارند، بسیار مفید هستند. فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش تعداد کانال 4 1 Channel 2 Channel 3 Channel 4 Channel ≥ = ≤ = جریان 14 1 mA 5 mA 10 mA 16 mA 20 mA 25 mA 30 mA 50 mA 60 mA 70 mA 80 mA 90 mA 100 mA 150 mA ≥ = ≤ = ولتاژ کلکتور-امیتر 14 6 V 20 V 30 V 32 V 35 V 40 V 55 V 60 V 70 V 80 V 90 V 100 V 300 V 350 V ≥ = ≤ = جریان کلکتور 20 0.00005 mA 0.1 mA 0.5 mA 1 mA 2 mA 2.5 mA 10 mA 13 mA 16 mA 30 mA 40 mA 44 mA 50 mA 80 mA 100 mA 125 mA 0.15 A 150 mA 200 mA 400 mA ≥ = ≤ = ولتاژ معکوس 9 0.7 V 2 V 3 V 4 V 5 V 6 V 7 V 25 V 200 V ≥ = ≤ = نوع خروجی 18 AC , Zero Cross DC DC-Output N Phototransistor NPN Photodarlington NPN Phototransistor Opto-Emulator with Analog Transistor Optoisolators Opto-Transistor Photocoupler Photodarlington Phototransistor Phototransistor Darlington Phototransistor NPN Phototransistor,Open Collector PNPN Poto SCR Transistor Transistor with Base = ولتاژ مستقیم 15 1.1 V 1.15 V 1.17 V 1.2 V 1.25 V 1.3 V 1.4 V 1.5 V 1.55 V 1.6 V 1.65 V 1.7 V 1.9 V 2 V 2.6 V ≥ = ≤ = ولتاژ جداسازی 24 3.750 Vrms 5.3 Vrms 5.300 Vrms 0.5 kVrms 500 Vrms 1.5 kVrms 2 kVrms 2.5 kVrms 2.500 kVrms 2.8 kVrms 3 kVrms 3.55 kVrms 3.75 kVrms 3.750 kVrms 4 kVrms 4.170 kVrms 5 kVrms 5.3 kVrms 5.300 kVrms 7.5 kVrms 8.2 kVrms 8.200 kVrms 11.6 kVrms 15 kVrms ≥ = ≤ = حداقل نسبت انتقال فعلی 33 10 % 12.5 % 15 % 20 % 25 % 30 % 34 % 35 % 40 % 50 % 60 % 63 % 80 % 100 % 120 % 125 % 130 % 150 % 160 % 173 % 200 % 260 % 295 % 300 % 320 % 400 % 500 % 600 % 1000 % 1200 % 1500 % 2000 % 4000 % ≥ = ≤ = نوع نصب روی برد 2 SMD Through Hole = حداقل دمای عملیاتی 7 -55 °C -50 °C -45 °C -40 °C -30 °C -25 °C -20 °C ≥ = ≤ = حداکثر دمای عملیاتی 9 80 °C +85 °C 85 °C +100 °C 100 °C +110 °C 110 °C +125 °C 125 °C ≥ = ≤ = برند 28 Alpha Micro Components Avago Technologies AZ Displays, Inc Broadcom Limited California Eastern Laboratories Cheuk Yui Innovation Co CT Micro International Co Everlight Electronics Fairchild Semiconductor Harris Semiconductor Huibei KENTO Electronic Infineon Technologies Isocom Components LITE-ON Semiconductor Matsushita Electric Motorola NEC Electronics Non-Brand ON Semiconductor Panasonic Corporation QT Optoelectronics Renesas Technology SHARP Corporation Siemens Semiconductor Group TEMIC Semiconductor Texas Instruments Toshiba Corporation Vishay = پکیج 16 DIP-12 DIP-16 DIP-4 DIP-4 HV DIP-6 DIP-8 MFSO-4 MFSO-5 SIP-9 SMD-16 Gull Wing SMD-4 Gull Wing SMD-6 Gull Wing SO-16 SO-4 SO-8 SOP-8 SSOP-4 = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز تعداد کانال جریان ولتاژ کلکتور-امیتر جریان کلکتور ولتاژ معکوس نوع خروجی ولتاژ مستقیم ولتاژ جداسازی حداقل نسبت انتقال فعلی نوع نصب روی برد حداقل دمای عملیاتی حداکثر دمای عملیاتی برند پکیج مرتب کردن مرتب سازی All Products Optoelectronics Optocouplers / Photocouplers Transistor Output Optocouplers کپی PC817 SHARP Corporation DIP-4 44,200 ریال اضافه به سبد خرید اوریجینال EL817C Everlight Electronics DIP-4 50,100 ریال اضافه به سبد خرید کپی PS2501-1 Renesas Technology DIP-4 51,400 ریال اضافه به سبد خرید اوریجینال EL817 SMD Everlight Electronics SMD-4 Gull Wing 54,500 ریال اضافه به سبد خرید اوریجینال LTV817B LITE-ON Semiconductor DIP-4 63,300 ریال اضافه به سبد خرید کپی PS2501L-1 SMD Renesas Technology SMD-4 Gull Wing 64,600 ریال اضافه به سبد خرید اوریجینال LTV817S LITE-ON Semiconductor SMD-4 Gull Wing 77,600 ریال اضافه به سبد خرید کپی TLP521-1GB Toshiba Corporation DIP-4 88,400 ریال اضافه به سبد خرید کپی TLP521LF1 Toshiba Corporation SMD-4 Gull Wing 93,300 ریال اضافه به سبد خرید اوریجینال PC817 SHARP Corporation DIP-4 95,000 ریال اضافه به سبد خرید اوریجینال CYTLP181GB OCIC co MFSO-4 121,000 ریال اضافه به سبد خرید اوریجینال LTV814S LITE-ON Semiconductor SMD-4 Gull Wing 121,000 ریال اضافه به سبد خرید اوریجینال CYTLP521-1GB OCIC co DIP-4 127,000 ریال اضافه به سبد خرید اوریجینال LTV814A LITE-ON Semiconductor DIP-4 138,000 ریال اضافه به سبد خرید اوریجینال CYTLP521-1GB-TP2 SMD Cheuk Yui Innovation Co SMD-4 Gull Wing 149,000 ریال اضافه به سبد خرید اوریجینال TLP291GB Toshiba Corporation SSOP-4 154,000 ریال اضافه به سبد خرید اوریجینال 4N25 Everlight Electronics DIP-6 188,000 ریال اضافه به سبد خرید اوریجینال TLP781GB Toshiba Corporation DIP-4 237,000 ریال اضافه به سبد خرید اوریجینال PS2501-1 Renesas Technology DIP-4 302,000 ریال اضافه به سبد خرید اوریجینال 4N35M ON Semiconductor DIP-6 353,000 ریال اضافه به سبد خرید اوریجینال TCET1108 Vishay DIP-4 371,000 ریال اضافه به سبد خرید اوریجینال 4N27M Fairchild Semiconductor DIP-6 373,000 ریال اضافه به سبد خرید اوریجینال CNY17-3M ON Semiconductor DIP-6 377,000 ریال اضافه به سبد خرید اوریجینال TLP521-2XGB Isocom Components DIP-8 417,000 ریال اضافه به سبد خرید اوریجینال 4N25M ON Semiconductor DIP-6 433,000 ریال اضافه به سبد خرید اوریجینال 4N26M Fairchild Semiconductor DIP-6 503,000 ریال اضافه به سبد خرید اوریجینال PC814XP SHARP Corporation SMD-4 Gull Wing 508,000 ریال اضافه به سبد خرید اوریجینال 4N28M Fairchild Semiconductor DIP-6 537,000 ریال اضافه به سبد خرید اوریجینال 4N33M ON Semiconductor DIP-6 583,000 ریال اضافه به سبد خرید بازسازی شده ON3184 Panasonic Corporation DIP-16 706,000 ریال اضافه به سبد خرید اوریجینال TLP521-4XGBSM Isocom Components SMD-16 Gull Wing 728,000 ریال اضافه به سبد خرید اوریجینال PS2801C-4-F3 Renesas Technology SO-16 734,000 ریال اضافه به سبد خرید بازسازی شده TLP521-4GB Toshiba Corporation DIP-16 762,000 ریال اضافه به سبد خرید اوریجینال TLP521-4XGB Isocom Components DIP-16 786,000 ریال اضافه به سبد خرید اوریجینال TLP521-1GB Toshiba Corporation DIP-4 842,000 ریال اضافه به سبد خرید اوریجینال MCT6 ON Semiconductor DIP-8 1,010,000 ریال اضافه به سبد خرید اوریجینال TLP521-4GB Toshiba Corporation DIP-16 2,725,000 ریال اضافه به سبد خرید اوریجینال PS2501L-1-F3-A Renesas Technology SMD-4 Gull Wing اضافه به سبد سفارش اوریجینال CT521-1GB CT Micro International Co DIP-4 ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال TLP785(GB-TP6,F Toshiba Corporation DIP-4 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال PC851XNNIP9F SHARP Corporation SO-4 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال TLP187 Toshiba Corporation MFSO-4 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال EL816S1(J)(TU)-V Everlight Electronics SMD-4 Gull Wing ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال TCLT1600 Vishay SO-4 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال 4N36 Fairchild Semiconductor DIP-6 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال ON3401 Panasonic Corporation DIP-6 ناموجود-تحویل 33 روزه اضافه به سبد سفارش بازسازی شده TLP521-1GB Toshiba Corporation DIP-4 ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال EL817C-V Everlight Electronics DIP-4 ناموجود-تحویل 33 روزه اضافه به سبد سفارش مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>44200</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>88400</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MAX3232CSE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>U9</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SOIC-16_L9.9-W3.8-P1.27-LS6.0-BL</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop?searchfilter=max3232#dtl/4689</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>محصولات خانه دسته‌بندی‌ها فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه عبارت max3232 جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش برند 1666 3M Dynapro 3M Interconnect 3PEAK Incorporated 4D Systems Pty Ltd A Power microelectronics AAEON Technology Aavid Thermalloy ABC Taiwan Electronics ABLIC Inc Abracon Corporation Acam-Messelectronic Acrian, Inc Actel Corporation Active-Semi, Inc Actox Corporation. AD Semiconductor Confidential Adafruit Industries LLC Adam Technologies, Inc ADDA Corp ADDtek Corp Adesto Technologies ADMtek Inc Advanced Acoustic Technology Corp. Advanced Analog Technology Advanced Analogic Technologies Advanced Card Systems Advanced Ceramic X Corp Advanced Linear Devices Inc Advanced Monolithic Systems Advanced Photonix, Inc Advanced Power Electronics Corp Advanced Power Technology Advanced Semiconductor Advantech Corp Advantech Equipment Corporation Aegis Electronic Group AEL Crystals Limited AEM, Inc Aerosemi Technology Co Afa Technologies Inc AG Electrical Technology Agere Systems Agilent Technologies AGM Semiconductor AIC tech Inc. Aimtec Aimtron Corporation Airoha Technology Corp AIRWAVE Technologies Inc AiSHi Capacitors Aixin Opto-Electrical Technology Albright International Ltd Alcatel Microelectronics Alcor Micro Corp Alex Connector Co Ltd Alfa Electronics Algocraft Srl. ALi Corporation Alinx Electronic Technology All Sensors Corporation Allegro Microsystems Alliance Memory Allied Vision, Inc. Allwinner Technology Almita Co. Ltd Alpha &amp; Omega Semiconductor Alpha Micro Components Alpha Semiconductor Alpha Wire Alphasense Ltd, Sensor Technology Alps Electric Co Altera Corporation Amazing Electronic Co Amazing Microelectronic Corp AMD American Microsemiconductors American Microsystems Inc American Power Management American Technical Ceramics Corp American Zettler, Inc. Ametherm, Inc AMI Semiconductor AMIC Technology Corp Amidon Associates, Inc Amlogic Inc. Amotech Corp AMPAK Technology Inc Amphenol Advanced Sensors Amphenol Corporation Amphenol FCI Amphenol RF Ampleon USA Inc ams AG Anachip Corp ANADIGICS Anadigm, Inc Analog Devices Analog Integrations Corporation Analog Microelectronics Analog Power Analogix Semiconductor Inc Anaren, Inc Ancol Electronics Co Andigilog, Inc ANENG Anhui FOSAN Semiconductor Anhui Vico Technologes Co Anovay Technologies Limited ANPEC Electronics Corp Ante Intelligent Company Limited AP Memory Technology. APC Propellers APEM Inc Apex Material Technology Apex Precision Power API Delevan Inc API Technologies Aplus Integrated Circuits Inc APMKorea Apogee Technology, Inc Applent Instruments Applied Micro Circuits Co AppoTech Ltd APT Electronics Co., Ltd. Aptek Technologies ArchNet Technology Arcol UK Ltd Arduino Arduino Nicla Voice. Arima Lasers Corporation Aristotle Enterprises Inc ARTCHIP Semiconductor Artesyn Embedded Technologies AS ENERGI Asahi Kasei Microdevices ASAHI Solder Asia Vital Components Asiliant Technologies ASIX Electronics Corp AsLic Microelectronics Corporation ASMedia Technology Inc. Associated Opto-Electronics Astec Semiconductor. Astrodyne TDI Corporation. ATE Electronics s.r.l Atech Technology Co ATEN International Co Atheros Communications, Inc ATI Technologies Inc Atlas Scientific LLC. Attend Technology Inc AU Optronics Corp Audiowell Electronics Co Auk Contractors Co AUK Semiconductor AUO Corporation AUREL S.P.A Austar Technology AuthenTec, Inc Autonics Corporation Avago Technologies AVANTEK INC. AverLogic Technologies, Inc AVerMedia Technologies Avia Semiconductor Avnet, Inc AVX Corporation AXElite Technology Co Axiomtek Axis Communications AZ Displays, Inc Azoteq Ltd BAFO Technologies Corp Bahar Enclosure Baumer International BBT-China Inc BCD Semiconductor Beckhoff Automation Beijing Boshida Beijing HRH Information Co Beijing Ultrasonic Beijing Yihongtai Technology Beijing Zhongxun Sifang Science &amp; Technology Beken Corporation Bel Fuse Inc Bel Power Solutions Inc Belden Inc Bellnix Bencent Tzeng Ind. Co. Ltd Betlux Beyond Innovation Technology BI Technologies Bicker Elektronik GmbH Billionton Systems Inc Bird Technologies Bi-Sonic Technology Bivar, Inc Blackhawk BLOCK Inc Bluegiga Technologies BOLYMIN,INC BONGSHIN LOADCELL CO. Bookly Micro Electronic Bosch Security Systems Inc Bosch Semiconductors Bosch Sensortec Bothhand USA Boundary Devices Bourns Inc Bowin Microelectronics Brainboxes Limited BRIGHT LED ELECTRONICS CORP. Bright Power Semiconductor BrightKing Inc Brilliance Semiconductor, Inc Broadchip Technology Broadcom Limited BroadLight Inc Brooktree Corporation Burr-Brown Corporation BYD Microelectronics Co., Ltd. C&amp;D Technologies C&amp;K Components Caddock Electronics Inc California Eastern Laboratories California Micro Devices Calogic LLC Cambridge Integrated Circuits Cambridge Silicon Ra dio Limited Camille Bauer Ltd Catalyst Semiconductor Celduc relais CellWise Microelectronics Co Cenker Enterprise Ltd Centenary Materials Co CeNtRa Science Corp Central Components Manufacturing Central Georgia Generator Central Semiconductor CEVA Technologies CFSensor Challenge Electronics Champion Microelectronic Changzhou changjie Technology Co Changzhou Cre-sound Electronics Changzhou DRM Changzhou Esuntech Co Changzhou Kennon ELectronics Changzhou TDA Electronic Changzhou Yuanwang Fluid Technology Chaozhou Three-circle (Group) Co chargebyte GmbH. Chengdu Ebyte Electronic Technology Chengdu Guosheng Technology Chengdu Xincheng Huachuang Electronic ChenMoun Electronic ChenYang Technologies Cheuk Yui Innovation Co Chi Mei Optoelectronics Chieful Science ＆ Technology Chilisin Electronics Co China Base Electronic Technology China ECU Tools Centre China Resources Microelectronics China Software Industry Association Chinfa Electronics Chingis Technology Corp Chino-Excel Technology Chipanalog Incorporated ChipLink Tech Chiplus Semiconductor ChipON Chipower Electronics CHIPS Technology Chipstar Microelectronics CHK Electronics Ltd Chogori USA Chongqing Shengpu Electronics Chrontel, Inc Chunghwa Picture Tubes Churod Electronics Chyao Shiunn Electronic Cincon Electronics Cinetech Ind Cirrus Logic Inc Cisco Systems CIT Relay &amp; Switch Citizen Finedevice Co Cixi AnXon Electronic Cixi Dafa precise Linker Co CiXi KaiFeng Electronics Co Cixi Kefa Electronics Cixi Max Electronics Co.,Ltd Clare, Inc Cliff Electronic Components Limited Cmedia Electronics Inc CML Microsystems Coil Master Co Coil Winding Coilcraft Inc Coiltronics (Eaton) Comchip Technology Commodore Semiconductor Comtec Crystals comtech aha corporation CONEC Elektronische Bauelemente GmbH Conesys,Inc. Conexant Systems, Inc Connfly Electronic Co Connor-Winfield Conquer Electronic Continental Device India Controlair Inc Conversion Devices, Inc Cooper Bussmann Coretek Opto Corporation. Cornell Dubilier Electronics Cortina Systems, Inc Cosel Co Ltd COSINE Nanoelectronics Coto Technology CR Powtech Co Cree, Inc Crydom Inc Crystal Semiconductor Corporation Crystalfontz Crystek Corporation CSCONN PRECISE ELECTRONICS CO.,LTD CT Micro International Co CTS Corporation CUI Inc CVI Laser, LLC CW Industries Cyntec Co Cypress Semiconductor Cyrustek Corporation CYStech Electronics Corp. CYT Opto-Electronic Technology Dachang Electronics Daewoo Semiconductor Daier Electron Co Dailywell Electronics Daishinku Corp Daito Communication Apparatus Daiyo Electronics Dallas Semiconductor DANFOSS Daniels Manufacturing Co Data Device Corporation Davicom Semiconductor Davies Molding, LLC DB Lectro Inc DB Unlimited DC Components Co Dean Technology DECA SwitchLab Inc Decawave Ltd Dechang Electronic Deep Sea Electronics DEGSON Electronics Co Dell Inspiron Delta Electronics DeMint Electronics DENSO Destiny Technology Corp Detaik Technology Co Deva Electronic Controls Limited. Devantech Device Engineering Inc Dexter Magnetic Technologies DFRobot. Dialight Electronics Company Dialog Semiconductor Dielectric Laboratories Digi International Digilent, Inc Digital Voice Systems Digitrax, Inc Digitron Semiconductors Dinkle International Co. Ltd DIN-TEK Microelectronics Diodes Incorporated Diotec Semiconductor Diptronics Manufacturing Inc Display Solution AG DISPLAY VISIONS GmbH 2022. DMB Technology DOESTEK Co DOINGTER Semiconductor Domintech Co Don Connex Electronics DONG IL TECHNOLOGY LTD. Dongguan CHENGXING Electronic Co Dongguan City Wasi Electronic Technology Dongguan Cosson DongGuan HeLing Electronics Dongguan Lanbo Electronics Technology CO Dongguan Yuandi Electronics Dongguan Yuanze Electric Co.,Ltd Dongguan Yuxi Precise Connector Co., Ltd Dongke semiconductor Anhui Co., Ltd Donguan Keyouda Electronic Dosilicon Co DTK electronics Dualsky Models Co Duoxing Electronics Co Duty-Cycle Semiconductor Dynamic Technologies (DTCC) Dynex Semiconductor Ltd, E &amp; E Magnetic Products Limited EAST Semiconductor East Texas Integrated Circuits Eastrising Technology Co Eastsensor Technology Easy IoT Eaton’s Bussmann Ebm-papst inc Echelon Corporation Ecliptek Corporation ECOFIT &amp; ETRI ECS, Inc International EDAC EECO Switch E-Elements Technology Co Efficient Power Conversion Co EG Microelectronics Corp EIC Semiconductor Elan Microelectronics Co Elantec, Inc Electrolube Electronic Alliance Electronic Assembly Electronic Devices Inc Electroustic Ltd Eledis Element14 ELESTA GmbH Elite Semiconductor Memory Eljen Technology Elm Electronics ELM Technology Co Elmos Semiconductor AG ELNA Company Elpida Memory, Inc EM Microelectronic-Marin EMAD Embedded Artists Embest Technology Emerson Encitech Endress+Hauser Management ENE Technology Enplas Corporation Enrwey Co Ltd Eon Silicon Solution E-peas Semiconductors Epitex Inc Epoxy Technology Inc EPSON Electronics Ept Inc Ericsson Microelectronics ERNI Electronics ERSA UK LTD Espressif Systems ESS Technologies E-Switch, Inc ET Enterprises Limited E-T-A Circuit Breakers ETA Solutions E-tec Interconnect Ethertronics Inc Etron Technology, Inc EUCHNER GmbH Eupec semiconductor Euroquartz Ltd Eutech Microelectronics Everanalog Everest Semiconductor Everlight Electronics Everspin Technologies Exar Corporation Excel Cell Electronic Excelitas Technologies Excellence Opto, Inc Excelliance MOS Corporation Fagor Electronica Fairchild Semiconductor Fair-Rite Products Corp FANUC Corporation Faraday Technology Fastline Fastrax Ltd FASTRON Faulhaber GmbH FDK Corporation Feature Integration Technology Feei Cherng Enterprise Feeling Technology Feiyi Technology FEMA Electronics Corporation Fenghua Advanced Technology Ferroxcube International FERYSTER Sp. z.o.o Figaro Engineering Inc Finder Relays, Inc Fingerprint Cards First Semiconductor First Sensor FIS Inc Fischer Connectors Fischer Elektronik Fitipower Integrated Technology Force MOS Technology Co Formosa MS Formox Semiconductor Forsentrk Fortior Technology Co Fortune Semiconductor Forward International Electronics FOTEK Controls Fox Electronics Foxconn Technology Fractus S.A Franz Binder GmbH &amp; Co. Free2Move Holding AB. Freescale Semiconductor Fremont Micro Devices Friendcom Technology Develop FriendlyARM Computer Tech FTDI Chip Fuda Hisi Microelectronics Fuji Electric Fujikura Fujitsu Semiconductor Fujitsu-Takamisawa Fulihua Printer Ribbon Co Futaba Corporation Fu-Yao Technology Co Fuzetec Technology Co Fuzhou Rockchip Electronics Co., Ltd GainSpan Corporation GalaxyCore Inc GaNPower International Inc G-Antetech Industrial Garmin Ltd. Gas Sensing Solutions Ltd. Gaston Electronics GC GE Fanuc GEC Plessey Geehy Semiconductor Co General Electronic Devices General Monitors General Semiconductor Generalplus Technology GeneSiC Semiconductor Genesis Microchip Inc Genesys Logic, Inc Genicom Co., Ltd. Gennum Corporation GETE Electronics GigaDevice Semiconductor Global Connector Technology (GCT) Global Mixed-mode Technology GlobespanVirata, Inc GMC Instruments GME Technology, LLC GoChip Electronic Technology GoldStar Semiconductor Gonbes Technology Co Good Display Good Will Instrument Good-Ark Semiconductor Goodix Technology Governors America Co Gpixel Microelectronics Inc Grayhill Inc GreatLEDs Co Greenliant Systems GRUNER AG GSI Technology, Inc Guangdong Hottech Co Guangdong Huaguan Semiconductor Guangdong TIANQIU Electronics Technology Guangzhou Aosong Electronics Guangzhou Xinyue Electronic Guerrilla RF, Inc H&amp;M Semiconductor HABEY Halbleiter aus Frankfurt HALO Electronics Hamamatsu Photonics Hangzhou Grow Technology Co Hangzhou Nationalchip Science Hangzhou Prosper Hangzhou Silan Microelectronics Hannstar Display Corp HanRun Electronics Hanwei Electronics Co Hanyoung Nux Co HAOHAI ELECTRONICS HAOYU Electronics Harris Semiconductor HARTING Technology Harvatek Corporation Harwin Hawyang Semiconductor Hebei International Trading Co HEITEC AG. Hemingruizhi Electronic Henan Hanwei Electronics Co Hengda New Materials Technology HengJiaXing Electronics Co Henkel Corporation HenLv Power Technology Heter Electronics Hewlett-Packard Hexin Technology Highly Electric Hi-Link Electronic Technology Hi-Optel Technology Hirose Electric Hi-Sincerity Microelectronics Hitachi Maxell, Ltd Hitachi Semiconductor HITPOINT Inc Hittite Microwave Hivolt Capacitors Ltd H-JTAG Technology Hokuriku Electric Industry Co Ltd Hokuyo Automatic Co Holt Integrated Circuits Holtek Semiconductor Honeywell International Hong Kong Resistors Manufactory Hongfa Electroacoustic Co HONGHUA ELECTRONIC Hope Microelectronics HORIBA, Ltd. Hosiden Corporation Hosonic Electronic Co Hotchip Technology HTC Korea TAEJIN Technology Huada Connectors Huanor International Huaqi Microelectronics Co Huawei Technologies Huayu Technology HuaYuan Micro Electronic Huayue Microelectronics Co HUBER+SUHNER Huibei KENTO Electronic Huidu Technology Hukx Sensor Technology Humirel Hurricane Tech. Co HW group s.r.o HYCON Technology Corp. Hynix Semiconductor Hyundai Semiconductor IC Plus Corp ICE Components, Inc. iC-Haus GmbH Icom Inc ICP DAS CO ID Innovations ID TECH IDEC Corporation IEI Integration Ignion Iintelligent Motion Systems IK Semiconductor ILSI America LLC IMP, Inc Inchange Semiconductor Industrial Fiber Optics, Inc Industrial Technology Research Institute Infineon Technologies Initio Corporation INJOINIC TECHNOLOGY Innolux Corporation InnoSenT-Innovative Radar Sensor Technology Innovative Sensor Technology IST Innuovo Magnetics Co Inova Semiconductors InPlay Inc. InPower Semiconductor INTEGRAL JSC Integrated Circuit Solution Integrated Circuit Systems Integrated Crystal Technology Integrated Device Technology Integrated Sensor Technologies Integrated Silicon Solution Intel Corporation InterFET Corp Interlink Electronics International CMOS Technology International Rectifier Intersil Corporation Intronic Semiconductor Intronics Power, Inc InvenSense Inc IQD Frequency Products Ltd IRAN Ironwood Electronics IRXON Electronic Isabellenhütte Heusler GmbH &amp; Co KG Isahaya Electronics Co iSentek Technology Isocom Components Isotek Corp ITE Tech ITT Cannon, LLC ITT Semiconductors Ituner Networks Corp iWatt Inc IXYS Integrated Circuits J.S.T. Mfg. Co JACKSON ELECTRONICS IND. CROP. JAE Electronics JAI Ltd Jamicon Electronics JAVAN JCET Group Co JCI Jewel Hill Electronic Co JHDLCM Electronics Jiangsu Changjiang Electronics Jiangsu Donghai Semiconductor Jiangsu Juguang Jiangsu Runic Technology Co Jiangsu Szdhdtgd Electronics Jiangxi Jia Wei Cheng Electronic Jilin Sino-Microelectronics Co Jinan USR IOT Technology JING LI Power Electronics Jingcheng Electronics Co Jinghan Switch Electronic JMicron Technology Corp JNHuaMao Technology JODO International Johanson Dielectrics Johanson Technology Johnson Electric JPC Company JYE Tech Ltd JYH HSU(JEC) ELECTRONICS Kai Suh Suh Enterprise KSS Kaida Holding Kaihua Electronics Co Kangmu Sheng Electronics Ka-Ro electronics GmbH. KEC Semiconductor Keil Elektronik Keithley Instruments Kelly Controls, LLC KEMET Corporation Key Technology Keysight Technologies Keystone Electronic King Core Electronics Kingbor Technology Kingbright Electronic KingCCTV Technology Kingdatron Electronic Industrial Co Kingsignal Technology Kingstate Electronics Kingston KIOXIA America, Inc Kiwi Instruments Corp Knowles Electronics KOA Speer Electronics Kobiconn Kodenshi Corp Kohshin Electric Corporation KONE Elevator Kontron S&amp;T KT Micro Inc Kunshan Sino Silicon Technology KUOYUH W.L. Enterprise Co Kutai Electronics Kycon, Inc Kyocera Corporation Ladder Electronics Co Laird Performance Materials. Laird Technologies Laser Components Lattice Semiconductor LawMate International L-com, Inc LD-PD Inc. Leadtrend Technology Corp LEAP Electronic Legerity, Inc Lelon Electronics Corp LEM Components LEMO Lenovo LENZE Lesfuse Electric Co Leshan Radio Co LG Semiconductor LG.Philips Displays Lianchao Future Technology Lighting Integration System Ligitek Electronics Co Lime Microsystems Lineage Power Private Limited Linear Systems Linear Technology Linfinity Microelectronics Link-PP Int'l Technology LinkSmart LINP OMTER International Linx Technologies Lision Technology LITE-ON Semiconductor Littelfuse Inc Lixin Electromagnetic Clutch LIZE Electronic Technology LND, INC LOETRONIC LOGIC Devices Incorporated Longtech Optics Co Longview Technologies Co Lovid International Electronic Low Power Radio Solutions Ltd LOZEN TECHNOLOGY LS ELECTRIC LS Mtron Ltd LSI Computer Systems LTKCHIP LTN Servotechnik GmbH Lucent Technologies LUCKFOX Technology Lucky Light Electronic Luguang Electronic Technology Lumberg Holding Lumentum Operations LLC. Lumex Inc Lumileds Luminus, Inc. Lumissil Microsystems Luna Optoelectronics Lutron Electronic Enterprise Co Lyontek Inc M.S. Kennedy Corp M+R Multitronik GmbH MACOM Technology Macroblock, Inc Macronix International MacTek Corp MagnaChip Semiconductor Magnetics MagnTek Microelectronics Magtek Technology Inc Manorshi Electronics Marktech Optoelectronics, Inc Marlow Industries, Inc Marquardt Switches, Inc Marvell International Matsushita Electric Max Echo Technology Corp MaxBotix Inc Maxic Technology Corporation Maxim Integrated MaxLinear Inc Maxon motor Maxwell Technologies Mayloon Electronic Company MCS Logic Inc Mcuzone International MEAN WELL Enterprises Co Measurement Specialties Mechanic MediaTek Inc Megatek Melexis Technologies Memory Protection Devices MEMSIC, Inc Mentor GmbH Mercury Electronic Meritek Electronics Corporation Mersen EP Metalink Broadband Meticom GmbH. METRODYNE MICROSYSTEM CORP. MIC Electronic Micrel, Inc Micro Commercial Components Micro Crystal AG Micro Electronics Micro Linear Micro One Electronics Micro Power Systems MICRO SENSOR CO;LTD Microchip Technology Microdiode Semiconductor Micrometals, Inc Micron Technology Micronet Communication Microsemi Corporation Microtech Technology Co Ltd Microtherm Sentronic GmbH Microtips Technology Midori Precisions MikroElektronika MikroElektronika d.o.o MikroTik Mill-Max Mfg Milnec Interconnect Systems MindMotion Microelectronics Co. Mingtek Electronics Ltd Mini-Circuits Minilogic Device Corporation Ltd Minmax Technology Minsoo Electronic Co MiTAC Computing Technology Mitel Semiconductor Mitsubishi Electric Mitsubishi Rayon Co Mitsumi Electric Co Mixed Signal Integration Mixic Electronics MKMX America LLC MMI Semiconductors MOAI electronics co Mobicon Electronic Component Modulestek Inc MOKO TECHNOLOGY LTD. Molex Electronic Monitor Enterprises Inc Monolithic Power Systems Morethanall Co Morningstar Corporation MORNSUN Science &amp; Technology Mosdesign Semiconductor Corp Mosel Vitelic Co MOSPEC Semiconductor MOS-TECH Semiconductor Mostek MOTIEN Technology Motorola Mstar Semiconductor M-Systems Inc Multicomp Multi-Inno Technology Multi-Tech Systems Inc Murata Manufacturing Co MVSILICON MYIR Tech Myrra SAS Naina Semiconductor Limited. Nanjing Haichuan Electronic Nanjing Ouzhuo Tech Nanjing Qinheng Microelectronics Nanjing Shiheng Elec NanJing Top Power ASIC Nanjing Up Electronic Technology Nanjing Wotian Technology Co Nanjing Zeming Electronic Co Nanya Technology Co National Instruments National Semiconductor NDK America Inc NEC Electronics Nell Semiconductor Neltron Industrial Nemoto Sensor Engineering NeuroSky, Inc. Neutrik New Jersey Semiconductor NewAE Technology Inc. Newava Technology Inc. Newhaven Display Newport Corporation NewTec Display Co NexFlash Technologies, Inc Nexperia USA Inc Nextchip Nextion NIC Components Corp. Nichia Corporation Nichicon Corporation Nidec Copal Electronics NIDEC SERVO CORPORATION. Nihon Dempa Kogyo Nihon Inter Electronics NIKO Semiconductor Ningbo East Electronics Ningbo ForwardRelayCorporationLTD Ningbo Gosun Technology Co Ningbo Huaguan Electronics Ningbo KLS Electronic Co Ningbo MAX Electronic Technology Co., Ltd Ningbo MKX Electronic Technology Ningbo Rel Electric Co., Ltd. Ningbo Songle Relay Ningbo Tianbo Ganglian Electronics Ninigi Nippon Chemi-Con Nippon Pulse America, Inc Nisshinbo Micro Devices Inc NJR Corporation NKK Switches NMB Technologies Non-Brand Norcomp Inc Nordic Semiconductor Noritake Itron Co Novacap Novatek Microelectronics NTE Electronics NUAND LLC. Nuvoton Technology NVE Corporation Nvidia NVS Navigation Technologies NXP Semiconductors NYS Resistor O2Micro OCIC co Octavo Systems LLC Ogemray Technology Co Ohmite OKI Semiconductor Ole Wolff Electronics Inc Olimex OmniVision Technologies Omron Electronics Omten Electronics ON Semiconductor ON Semiconductor CHINA On Shore Technology On-Bright Electronics OPTEK Technology Inc OPTi Inc Opticon Inc Opto 22 Opto Diode Corp Opto Electronics Co,. LTD OPTOLAB Microsystems Orient Display Oriental Semiconductor Orion Orion Display Technology Co OSI Optoelectronics OSRAM Opto Semiconductors OTAX Corporation Other Oupiin Enterprise Co OWON Technology Inc P&amp;E Microcomputer Systems Pacific Silicon Sensor Panasonic Corporation Panavision Imaging LLC Pancon Corporation PandaBoard PANJIT International Inc Para Light Electronics P-DUKE Technology Co PEAK Electronics GmbH PEAK-System Technik Penny &amp; Giles Peregrine Semiconductor Pericom Semiconductor Corp PerkinElmer Inc Phidgets, Inc Philips Semiconductor Phison Electronics Phoenix Contact Pickering Electronics Ltd PICO Electronics Pico Technology Piher Sensors &amp; Controls SA Pingjing Semi Technology PIR Sensor Co PixArt Imaging Inc Planar Systems, Inc PLX Technology PMC-Sierra, Inc PNI Sensor Corporation POCO Magnetic Polyfet RF Devices Polytronics Technology Pomona Electronics Power Integrations Power Mate Technology Power Systems GmbH Power-Changer Electronic Co Powerex Inc PowerPlaza Powersem GmbH Powertip Technology Preci-Dip SA Precision Monolithics, Inc PREMA Semiconductor GmbH Premier Magnetics PRETEC/C-One Technology Corp. Princeton Technology Proant AB Profichip GmbH Prokit's Industries Prolific Technology Inc Promax-Johnton Semiconductor Pro-Signal ProTek Devices Pro-Wave Electronic PRT PUI Audio Pulse Electronics Qimei Optical &amp; Electric Qingdao Mefine Electronics Qingxian Zeming Langxi Electronic Devices Co Qingyuan Tesla Electronic Technology Qorvo QT Brightek (QTB) QT Optoelectronics Qualcomm Atheros, Inc Quality Semiconductor Qualtek Electronics Quarton inc Quasar Electronics Limited Quectel Wireless Solutions QuickLogic Corporation QX Micro Devices Radiall Radxa Computer Rafael Microelectronics RAFI GmbH &amp; Co RAiO TECHNOLOGY INC RAKwireless Technology Limited. RALEC Ltd Ralink Technology Raltron Electronics Corporation Ramtron International Rapid Electronics Ltd Raspberry Pi Raycom Co Raytac Corporation. Raytheon RCA Corporation Ready Made RC LLC Realtek Semiconductor RECOM Power GmbH Rectron Semiconductor Reichelt elektronik GmbH &amp; Co. KG RELPOL S.A Renata SA Renesas Technology Renhotec Group Ltd Reomax Electronics Reyed Electronics Co RF Digital Corporation. RF Micro Devices RF Solutions Ltd RFaxis, Inc RFHIC Corporation RFM Integrated Device, Inc. RFT Mikroelektronik Rhombus Industries Inc Richtek Technology Co RichWave Technology Ricoh Electronic Devices Riedon RIGOL Ring&amp;tone Electronic Technology Riverdi RLS Merilna tehnika d.o.o ROBOTIS Co Rockwell Rogers Corporation ROHM Semiconductor Roithner Lasertechnik GmbH Rongtech Industry Royal Electronic Factory Co RS Components Ltd RTD Embedded Technologies Rubycon RYCHIP Semiconductor s.m.a.e. GmbH Saft Groupe S.A Sagami Electronics Saia-Burgess Switches Sakae Tsushin Kogyo Saleae, Inc Salecom Electronics Same Sky SamHop Microelectronics Samsung Electronics Samtec Samwha Capacitor Samwin Electronic Technology Samyoung S &amp; C Co SANCO Electronics Co SanDisk Sanhe Enclosure Sanjiaozhou Electrical Technology Sanken Electric SanRex Corporation Sanyo Denki Sanyo Electric Savantic Electronic Sawnics Inc Schaffner Group Schott AG Schrack Technik GmbH Schurter Inc Sciosense B.V. SCTF Electronics Seagate Technology LLC Seaparks Machinery-Electronics Seaward Electronics SeCoS Corporation SEED International Ltd Seeed Technology SEEQ Technology Segger Microcontroller Systems Seiko Instruments Inc Seiko NPC Corporation Semiconductor Circuits, Inc SemiHow Semikron Semiment Technologies Semi-Powerex Corp. SEMITEC Corporation SemiWell Semiconductor Semtech Corporation Semtech Electronics Senba Sensing Technology Co Sendo Sensor Sensata Technologies Sensirion Sentry Manufacturing Inc SEP Electronic Corp Servotecnica SpA SERVO-TEK PRODUCTS COMPANY, INC. SG Micro Corp SGX Sensortech Shaanxi Fullstar Electronics Co Shaanxi Qunli Electric Shaanxi Reactor Microelectronics Shandong Jingdao Microelectronics Shanghai AVIC Optoelectronics Shanghai Belling Co,Ltd Shanghai Consonance Electronics Shanghai Fengxin Electronic Technology Shanghai Fudan Microelectronics Shanghai Gotop Technology Shanghai High-Flying Electronics Shanghai Houde Photo-electric Shanghai Mixinno Microelectronics Co Shanghai Natlinear Electronics Shanghai Xinlong Semiconductor Shanghai Zhichuan Electronic Tech SHARP Corporation Sheng Jay Automation Techno Shenyang Guangcheng Technology Co., Ltd Shenyang KingStar Automation ShenZhen AI-thinker CO Shenzhen AnBoShi Electronic Shenzhen Asenware Test Shenzhen Baishan Mechatronics Shenzhen Biosled Technology Shenzhen Bolutek Technology Shenzhen Chipsea Technologies ShenZhen ChipSourceTek Technology Shenzhen ExSAF Electronics Co Shenzhen Genesis-Systech ShenZhen Gerbole Shenzhen Getech Co Shenzhen GUANGSHIMEI Electronic Shenzhen Hanxia Electronics Shenzhen Haolin Electronics Shenzhen Heliwei Technology Shenzhen honglifa Electronics Co Shenzhen HongyeX Electronics Co ShenZhen HuaXinAn Electronics Co.,Ltd Shenzhen Injoinic Technology Co. Shenzhen Jin Yu Semiconductor Co ShenZhen JINCI Technology Shenzhen Jinrui Electronic Material Co Shenzhen JMRTH Co Shenzhen Kaiyuexiang Electronics Co Shenzhen LFN Technology Co Shenzhen Lodestar S.T Co Shenzhen Lumen Electronics Shenzhen Magnetic Technology Shenzhen MilkV Technology Shenzhen Milliohm Electronics Shenzhen Minewsemi Co., Ltd Shenzhen Nsiway Tech Shenzhen Ou Chuangxin Semiconductor ShenZhen Qi Dian Shi Dai Technology Shenzhen Ruichips Semiconductor Shenzhen Ruilongyuan Electronics Shenzhen Shiji Lighting Shenzhen SI Semiconductors Shenzhen SLKOR Micro Semicon Co Shenzhen Sunmoon Microelectronics Shenzhen Suosemi Tech Shenzhen TongYiFang Optoelectronic Technology CO,Ltd Shenzhen Topmay Electronic Shenzhen TPOWER Semiconductor Shenzhen Universal Micro-Electronics Shenzhen USBR Precision Hardware Electronics Shenzhen Weidy Industrial Development Co., Ltd. Shenzhen Xinbole Electronics Co. Shenzhen Xptek Technology Shenzhen Xunlong Shenzhen Yangxing Technology Co. SHENZHEN YeZhan Electronics Shenzhen Yiwei Technology Shenzhen ZVELL Electronics Shindengen Electric Shin-Etsu Chemical Co SHINYEI Technology SHOEI SIBA GmbH Sichuan huafeng enterprise group SICK, Inc. Siemens Semiconductor Group Si-En Technology SiFirst Technology SiGe Semiconductor Sigma Microelectronics Signetics Silego Technology Silergy Corp Silicon Image Silicon Integrated Systems Silicon Laboratories Silicon Microstructures, Inc. Silicon Motion, Inc Silicon Sensing Systems Limited Silicon Standard Corp Silicon Storage Technology Silicon Systems Inc Silicon Touch Technology Silvan Chip Electronics Silver Telecom Ltd SilverStone Technology SIMCom Wireless Solutions SIMTEK Electronic Components Sinda Photoelectricity Technology SINGULAR TECHNOLOGY CO., LTD. Sinomags Technologies Co Sinopower Semiconductor Sipex Corporation Sirectifier Semiconductors SiTime Corporation Sivago Semiconductor Co SIWARD Crystal Technology Siyang Microelectronics Sizto Tech Corp SKYLAB M&amp;C Technology Skyworks Solutions, Inc SL Power Electronics Corp. SMAR Smartec BV SMC Diode Solutions Co. Smiths Interconnect. SMSC Corporation Soberton Inc Softing Automotive Electronics Sola/Hevi-Duty Sola-IC Solarflex SA Soldex Solid State Scientific SOLIDIC Solitronics Engineering Limited SOL-LED Lighting Co Solomon Systech Song Chuan Song Huei Electric Sonix Technology Sony Corporation Soundwell Electronic South African Micro-Electronic Systems Spansion inc SparkFun Electronics SPEC Sensors LLC Spectra Symbol Corp. Spectrum Digital Incorporated Speed Tech Corp Spin Semiconductor Sprague Semiconductors SPX Flow Technology ST Engineering Stackpole Electronics Standex-Meder Electronics Stannol GmbH Stanson Technology StarChips Technology StarPower Semiconductor Ltd. Startek Electronic Technology STATEK CORPORATION Stäubli International AG. STCmicro Technology Co Stewart Connector STMicroelectronics Stocko Stork Solutions Ltd. Sullins Connector Solutions SUMIDA Corporation Sun Hydraulics Corporation Sun Microelectronics SunLED SUNLORD Sunltech Tech SUNMATE Electronic Sunonwealth Electric Machine Sunplus Technology Sunrise Electronics Suntan Technology Company Suntsu Electronics, Inc. SUNYUAN Technology Supertex Inc Susumu International Suzhou Innoson Technology Suzhou NOVOSENSE Microelectronics Co., Ltd Suzhou Silikron Semiconductor Corp Switchcraft Inc. Switec SYNC Power Crop SyncMOS Technologies Synoxo International System General Corp Tadiran Batteries TAG Semiconductors TA-I Technology TAIKO-NET Tai-Saw Technology Tai-Tech Advanced Electronics Taitien Electronics Taitron Components, Inc Taiwan Alpha Electronic Co Taiwan Semiconductor Taiyo Electric Co Taiyo Yuden Tak Cheong Electronics Talema Group, LLC Tamagawa seiki Co Tamron Tamura Corporation TANCAP Technology Taoglas Limited TDK Corporation (EPCOS) TDK-Lambda Corporation TDK-Micronas GmbH TE Connectivity Team Source Display tech.co,ltd. Techcode Semiconductor Techpoint Inc Techspray/Plato-EMX Enterprises Limited Techstar Electronics TechToys Company TelCom Semiconductor Telcon Ltd Telechips Inc Teledyne Technologies TELEFUNKEN Elektroakustik Telegesis Ltd Telit TEMIC Semiconductor Terawins, Inc Teridian Semiconductor TESLA Testo SE &amp; Co Texas Advanced Optoelectronic Solutions Texas Instruments THAT Corporation Thegioiic Corporation Thermonamic Electronics(Jiangxi) Corp THine Electronics, Inc Thinki Semiconductor Thinking Electronic THOMSON Inc THORLABS Thousand Hundred Industrial Thunder Precision Resistor TIANMA Titan Micro TLC Electronics TNI-U TOOL Token Electronics Industry Tokmas Semiconductor TOKO, Inc Tontek Design Technology Top-arm Topro Technology Topway Technology Torex Semiconductor Toshiba Corporation touchSEMI TOYO LED ELECTRONICS LIMITED. TOYODA TR Electronic Nordic AB. Traco Electronic AG Transcom, Inc Transko Electronics, Inc. TRENDnet, Inc Trenz Electronic Triad Magnetics Trident Microsystems Trimble Inc TRINAMIC Motion Control TRinno Technology Co Tripath Technology TriQuint Semiconductor Truly Semiconductors TRW Inc TT Electronics TTM Technologies, Inc. TXC Corporation UBIQ Semiconductor Ubiquiti Inc u-blox UCE Ultrasonic Co UDF Semiconductor Ultisensor Electronics UNI SEMICONDUCTOR LIMITED Unicorn Microelectronics Corporation Unictron Technologies Corporation. Union Semiconductor Uniroyal Electronics Industry Co Unisonic Technologies Unitra Cemi Uni-Trend Technology Co Unitrode Corporation Universal Microelectronics UPI Semiconductor Corp US Digital US Micro Products. Usha India Ltd Ushio Opto Semiconductors UTRON Technology, Inc Vacuumschmelze GmbH VADEM LTD Vango Technologies, Inc Varitronix Limited VARTA AG Vatronics Technologies Ltd VBsemi Electronics Co. Ltd V-Chip Microsystems VectorNav Vectron International Vehicles instrumentation Device Venkel Ltd VIA Technologies Vicor Corporation Vigortronix Ltd. Vincotech Vishay Visual communication company Vitesse Semiconductor Vivesea VLSI Solution Vweb Corporation W. L. Gore &amp; Associates, Inc WAGO Kontakttechnik GmbH Wakefield Thermal, Inc. Walsin Technology Corporation Walter Electronic Co WanTcom, Inc Wavecom Waveshare Electronics Wavespectrum Laser Inc Wavetronics Technologies WAYTRONIC ELECTRONIC CO.LTD WeEn Semiconductors Weidmüller Interface GmbH Weipu connector Weltrend Semiconductor WENSHING Electronics Western Digital Corporation Willas Electronic Corp WIMA Winbond Electron</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>162000</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>162000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMS1117-3.3</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SOT-223_L6.7-W3.5-P2.30-BR</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop?searchfilter=1117#dtl/8350</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>محصولات خانه دسته‌بندی‌ها فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه عبارت 1117 جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش برند 1666 3M Dynapro 3M Interconnect 3PEAK Incorporated 4D Systems Pty Ltd A Power microelectronics AAEON Technology Aavid Thermalloy ABC Taiwan Electronics ABLIC Inc Abracon Corporation Acam-Messelectronic Acrian, Inc Actel Corporation Active-Semi, Inc Actox Corporation. AD Semiconductor Confidential Adafruit Industries LLC Adam Technologies, Inc ADDA Corp ADDtek Corp Adesto Technologies ADMtek Inc Advanced Acoustic Technology Corp. Advanced Analog Technology Advanced Analogic Technologies Advanced Card Systems Advanced Ceramic X Corp Advanced Linear Devices Inc Advanced Monolithic Systems Advanced Photonix, Inc Advanced Power Electronics Corp Advanced Power Technology Advanced Semiconductor Advantech Corp Advantech Equipment Corporation Aegis Electronic Group AEL Crystals Limited AEM, Inc Aerosemi Technology Co Afa Technologies Inc AG Electrical Technology Agere Systems Agilent Technologies AGM Semiconductor AIC tech Inc. Aimtec Aimtron Corporation Airoha Technology Corp AIRWAVE Technologies Inc AiSHi Capacitors Aixin Opto-Electrical Technology Albright International Ltd Alcatel Microelectronics Alcor Micro Corp Alex Connector Co Ltd Alfa Electronics Algocraft Srl. ALi Corporation Alinx Electronic Technology All Sensors Corporation Allegro Microsystems Alliance Memory Allied Vision, Inc. Allwinner Technology Almita Co. Ltd Alpha &amp; Omega Semiconductor Alpha Micro Components Alpha Semiconductor Alpha Wire Alphasense Ltd, Sensor Technology Alps Electric Co Altera Corporation Amazing Electronic Co Amazing Microelectronic Corp AMD American Microsemiconductors American Microsystems Inc American Power Management American Technical Ceramics Corp American Zettler, Inc. Ametherm, Inc AMI Semiconductor AMIC Technology Corp Amidon Associates, Inc Amlogic Inc. Amotech Corp AMPAK Technology Inc Amphenol Advanced Sensors Amphenol Corporation Amphenol FCI Amphenol RF Ampleon USA Inc ams AG Anachip Corp ANADIGICS Anadigm, Inc Analog Devices Analog Integrations Corporation Analog Microelectronics Analog Power Analogix Semiconductor Inc Anaren, Inc Ancol Electronics Co Andigilog, Inc ANENG Anhui FOSAN Semiconductor Anhui Vico Technologes Co Anovay Technologies Limited ANPEC Electronics Corp Ante Intelligent Company Limited AP Memory Technology. APC Propellers APEM Inc Apex Material Technology Apex Precision Power API Delevan Inc API Technologies Aplus Integrated Circuits Inc APMKorea Apogee Technology, Inc Applent Instruments Applied Micro Circuits Co AppoTech Ltd APT Electronics Co., Ltd. Aptek Technologies ArchNet Technology Arcol UK Ltd Arduino Arduino Nicla Voice. Arima Lasers Corporation Aristotle Enterprises Inc ARTCHIP Semiconductor Artesyn Embedded Technologies AS ENERGI Asahi Kasei Microdevices ASAHI Solder Asia Vital Components Asiliant Technologies ASIX Electronics Corp AsLic Microelectronics Corporation ASMedia Technology Inc. Associated Opto-Electronics Astec Semiconductor. Astrodyne TDI Corporation. ATE Electronics s.r.l Atech Technology Co ATEN International Co Atheros Communications, Inc ATI Technologies Inc Atlas Scientific LLC. Attend Technology Inc AU Optronics Corp Audiowell Electronics Co Auk Contractors Co AUK Semiconductor AUO Corporation AUREL S.P.A Austar Technology AuthenTec, Inc Autonics Corporation Avago Technologies AVANTEK INC. AverLogic Technologies, Inc AVerMedia Technologies Avia Semiconductor Avnet, Inc AVX Corporation AXElite Technology Co Axiomtek Axis Communications AZ Displays, Inc Azoteq Ltd BAFO Technologies Corp Bahar Enclosure Baumer International BBT-China Inc BCD Semiconductor Beckhoff Automation Beijing Boshida Beijing HRH Information Co Beijing Ultrasonic Beijing Yihongtai Technology Beijing Zhongxun Sifang Science &amp; Technology Beken Corporation Bel Fuse Inc Bel Power Solutions Inc Belden Inc Bellnix Bencent Tzeng Ind. Co. Ltd Betlux Beyond Innovation Technology BI Technologies Bicker Elektronik GmbH Billionton Systems Inc Bird Technologies Bi-Sonic Technology Bivar, Inc Blackhawk BLOCK Inc Bluegiga Technologies BOLYMIN,INC BONGSHIN LOADCELL CO. Bookly Micro Electronic Bosch Security Systems Inc Bosch Semiconductors Bosch Sensortec Bothhand USA Boundary Devices Bourns Inc Bowin Microelectronics Brainboxes Limited BRIGHT LED ELECTRONICS CORP. Bright Power Semiconductor BrightKing Inc Brilliance Semiconductor, Inc Broadchip Technology Broadcom Limited BroadLight Inc Brooktree Corporation Burr-Brown Corporation BYD Microelectronics Co., Ltd. C&amp;D Technologies C&amp;K Components Caddock Electronics Inc California Eastern Laboratories California Micro Devices Calogic LLC Cambridge Integrated Circuits Cambridge Silicon Ra dio Limited Camille Bauer Ltd Catalyst Semiconductor Celduc relais CellWise Microelectronics Co Cenker Enterprise Ltd Centenary Materials Co CeNtRa Science Corp Central Components Manufacturing Central Georgia Generator Central Semiconductor CEVA Technologies CFSensor Challenge Electronics Champion Microelectronic Changzhou changjie Technology Co Changzhou Cre-sound Electronics Changzhou DRM Changzhou Esuntech Co Changzhou Kennon ELectronics Changzhou TDA Electronic Changzhou Yuanwang Fluid Technology Chaozhou Three-circle (Group) Co chargebyte GmbH. Chengdu Ebyte Electronic Technology Chengdu Guosheng Technology Chengdu Xincheng Huachuang Electronic ChenMoun Electronic ChenYang Technologies Cheuk Yui Innovation Co Chi Mei Optoelectronics Chieful Science ＆ Technology Chilisin Electronics Co China Base Electronic Technology China ECU Tools Centre China Resources Microelectronics China Software Industry Association Chinfa Electronics Chingis Technology Corp Chino-Excel Technology Chipanalog Incorporated ChipLink Tech Chiplus Semiconductor ChipON Chipower Electronics CHIPS Technology Chipstar Microelectronics CHK Electronics Ltd Chogori USA Chongqing Shengpu Electronics Chrontel, Inc Chunghwa Picture Tubes Churod Electronics Chyao Shiunn Electronic Cincon Electronics Cinetech Ind Cirrus Logic Inc Cisco Systems CIT Relay &amp; Switch Citizen Finedevice Co Cixi AnXon Electronic Cixi Dafa precise Linker Co CiXi KaiFeng Electronics Co Cixi Kefa Electronics Cixi Max Electronics Co.,Ltd Clare, Inc Cliff Electronic Components Limited Cmedia Electronics Inc CML Microsystems Coil Master Co Coil Winding Coilcraft Inc Coiltronics (Eaton) Comchip Technology Commodore Semiconductor Comtec Crystals comtech aha corporation CONEC Elektronische Bauelemente GmbH Conesys,Inc. Conexant Systems, Inc Connfly Electronic Co Connor-Winfield Conquer Electronic Continental Device India Controlair Inc Conversion Devices, Inc Cooper Bussmann Coretek Opto Corporation. Cornell Dubilier Electronics Cortina Systems, Inc Cosel Co Ltd COSINE Nanoelectronics Coto Technology CR Powtech Co Cree, Inc Crydom Inc Crystal Semiconductor Corporation Crystalfontz Crystek Corporation CSCONN PRECISE ELECTRONICS CO.,LTD CT Micro International Co CTS Corporation CUI Inc CVI Laser, LLC CW Industries Cyntec Co Cypress Semiconductor Cyrustek Corporation CYStech Electronics Corp. CYT Opto-Electronic Technology Dachang Electronics Daewoo Semiconductor Daier Electron Co Dailywell Electronics Daishinku Corp Daito Communication Apparatus Daiyo Electronics Dallas Semiconductor DANFOSS Daniels Manufacturing Co Data Device Corporation Davicom Semiconductor Davies Molding, LLC DB Lectro Inc DB Unlimited DC Components Co Dean Technology DECA SwitchLab Inc Decawave Ltd Dechang Electronic Deep Sea Electronics DEGSON Electronics Co Dell Inspiron Delta Electronics DeMint Electronics DENSO Destiny Technology Corp Detaik Technology Co Deva Electronic Controls Limited. Devantech Device Engineering Inc Dexter Magnetic Technologies DFRobot. Dialight Electronics Company Dialog Semiconductor Dielectric Laboratories Digi International Digilent, Inc Digital Voice Systems Digitrax, Inc Digitron Semiconductors Dinkle International Co. Ltd DIN-TEK Microelectronics Diodes Incorporated Diotec Semiconductor Diptronics Manufacturing Inc Display Solution AG DISPLAY VISIONS GmbH 2022. DMB Technology DOESTEK Co DOINGTER Semiconductor Domintech Co Don Connex Electronics DONG IL TECHNOLOGY LTD. Dongguan CHENGXING Electronic Co Dongguan City Wasi Electronic Technology Dongguan Cosson DongGuan HeLing Electronics Dongguan Lanbo Electronics Technology CO Dongguan Yuandi Electronics Dongguan Yuanze Electric Co.,Ltd Dongguan Yuxi Precise Connector Co., Ltd Dongke semiconductor Anhui Co., Ltd Donguan Keyouda Electronic Dosilicon Co DTK electronics Dualsky Models Co Duoxing Electronics Co Duty-Cycle Semiconductor Dynamic Technologies (DTCC) Dynex Semiconductor Ltd, E &amp; E Magnetic Products Limited EAST Semiconductor East Texas Integrated Circuits Eastrising Technology Co Eastsensor Technology Easy IoT Eaton’s Bussmann Ebm-papst inc Echelon Corporation Ecliptek Corporation ECOFIT &amp; ETRI ECS, Inc International EDAC EECO Switch E-Elements Technology Co Efficient Power Conversion Co EG Microelectronics Corp EIC Semiconductor Elan Microelectronics Co Elantec, Inc Electrolube Electronic Alliance Electronic Assembly Electronic Devices Inc Electroustic Ltd Eledis Element14 ELESTA GmbH Elite Semiconductor Memory Eljen Technology Elm Electronics ELM Technology Co Elmos Semiconductor AG ELNA Company Elpida Memory, Inc EM Microelectronic-Marin EMAD Embedded Artists Embest Technology Emerson Encitech Endress+Hauser Management ENE Technology Enplas Corporation Enrwey Co Ltd Eon Silicon Solution E-peas Semiconductors Epitex Inc Epoxy Technology Inc EPSON Electronics Ept Inc Ericsson Microelectronics ERNI Electronics ERSA UK LTD Espressif Systems ESS Technologies E-Switch, Inc ET Enterprises Limited E-T-A Circuit Breakers ETA Solutions E-tec Interconnect Ethertronics Inc Etron Technology, Inc EUCHNER GmbH Eupec semiconductor Euroquartz Ltd Eutech Microelectronics Everanalog Everest Semiconductor Everlight Electronics Everspin Technologies Exar Corporation Excel Cell Electronic Excelitas Technologies Excellence Opto, Inc Excelliance MOS Corporation Fagor Electronica Fairchild Semiconductor Fair-Rite Products Corp FANUC Corporation Faraday Technology Fastline Fastrax Ltd FASTRON Faulhaber GmbH FDK Corporation Feature Integration Technology Feei Cherng Enterprise Feeling Technology Feiyi Technology FEMA Electronics Corporation Fenghua Advanced Technology Ferroxcube International FERYSTER Sp. z.o.o Figaro Engineering Inc Finder Relays, Inc Fingerprint Cards First Semiconductor First Sensor FIS Inc Fischer Connectors Fischer Elektronik Fitipower Integrated Technology Force MOS Technology Co Formosa MS Formox Semiconductor Forsentrk Fortior Technology Co Fortune Semiconductor Forward International Electronics FOTEK Controls Fox Electronics Foxconn Technology Fractus S.A Franz Binder GmbH &amp; Co. Free2Move Holding AB. Freescale Semiconductor Fremont Micro Devices Friendcom Technology Develop FriendlyARM Computer Tech FTDI Chip Fuda Hisi Microelectronics Fuji Electric Fujikura Fujitsu Semiconductor Fujitsu-Takamisawa Fulihua Printer Ribbon Co Futaba Corporation Fu-Yao Technology Co Fuzetec Technology Co Fuzhou Rockchip Electronics Co., Ltd GainSpan Corporation GalaxyCore Inc GaNPower International Inc G-Antetech Industrial Garmin Ltd. Gas Sensing Solutions Ltd. Gaston Electronics GC GE Fanuc GEC Plessey Geehy Semiconductor Co General Electronic Devices General Monitors General Semiconductor Generalplus Technology GeneSiC Semiconductor Genesis Microchip Inc Genesys Logic, Inc Genicom Co., Ltd. Gennum Corporation GETE Electronics GigaDevice Semiconductor Global Connector Technology (GCT) Global Mixed-mode Technology GlobespanVirata, Inc GMC Instruments GME Technology, LLC GoChip Electronic Technology GoldStar Semiconductor Gonbes Technology Co Good Display Good Will Instrument Good-Ark Semiconductor Goodix Technology Governors America Co Gpixel Microelectronics Inc Grayhill Inc GreatLEDs Co Greenliant Systems GRUNER AG GSI Technology, Inc Guangdong Hottech Co Guangdong Huaguan Semiconductor Guangdong TIANQIU Electronics Technology Guangzhou Aosong Electronics Guangzhou Xinyue Electronic Guerrilla RF, Inc H&amp;M Semiconductor HABEY Halbleiter aus Frankfurt HALO Electronics Hamamatsu Photonics Hangzhou Grow Technology Co Hangzhou Nationalchip Science Hangzhou Prosper Hangzhou Silan Microelectronics Hannstar Display Corp HanRun Electronics Hanwei Electronics Co Hanyoung Nux Co HAOHAI ELECTRONICS HAOYU Electronics Harris Semiconductor HARTING Technology Harvatek Corporation Harwin Hawyang Semiconductor Hebei International Trading Co HEITEC AG. Hemingruizhi Electronic Henan Hanwei Electronics Co Hengda New Materials Technology HengJiaXing Electronics Co Henkel Corporation HenLv Power Technology Heter Electronics Hewlett-Packard Hexin Technology Highly Electric Hi-Link Electronic Technology Hi-Optel Technology Hirose Electric Hi-Sincerity Microelectronics Hitachi Maxell, Ltd Hitachi Semiconductor HITPOINT Inc Hittite Microwave Hivolt Capacitors Ltd H-JTAG Technology Hokuriku Electric Industry Co Ltd Hokuyo Automatic Co Holt Integrated Circuits Holtek Semiconductor Honeywell International Hong Kong Resistors Manufactory Hongfa Electroacoustic Co HONGHUA ELECTRONIC Hope Microelectronics HORIBA, Ltd. Hosiden Corporation Hosonic Electronic Co Hotchip Technology HTC Korea TAEJIN Technology Huada Connectors Huanor International Huaqi Microelectronics Co Huawei Technologies Huayu Technology HuaYuan Micro Electronic Huayue Microelectronics Co HUBER+SUHNER Huibei KENTO Electronic Huidu Technology Hukx Sensor Technology Humirel Hurricane Tech. Co HW group s.r.o HYCON Technology Corp. Hynix Semiconductor Hyundai Semiconductor IC Plus Corp ICE Components, Inc. iC-Haus GmbH Icom Inc ICP DAS CO ID Innovations ID TECH IDEC Corporation IEI Integration Ignion Iintelligent Motion Systems IK Semiconductor ILSI America LLC IMP, Inc Inchange Semiconductor Industrial Fiber Optics, Inc Industrial Technology Research Institute Infineon Technologies Initio Corporation INJOINIC TECHNOLOGY Innolux Corporation InnoSenT-Innovative Radar Sensor Technology Innovative Sensor Technology IST Innuovo Magnetics Co Inova Semiconductors InPlay Inc. InPower Semiconductor INTEGRAL JSC Integrated Circuit Solution Integrated Circuit Systems Integrated Crystal Technology Integrated Device Technology Integrated Sensor Technologies Integrated Silicon Solution Intel Corporation InterFET Corp Interlink Electronics International CMOS Technology International Rectifier Intersil Corporation Intronic Semiconductor Intronics Power, Inc InvenSense Inc IQD Frequency Products Ltd IRAN Ironwood Electronics IRXON Electronic Isabellenhütte Heusler GmbH &amp; Co KG Isahaya Electronics Co iSentek Technology Isocom Components Isotek Corp ITE Tech ITT Cannon, LLC ITT Semiconductors Ituner Networks Corp iWatt Inc IXYS Integrated Circuits J.S.T. Mfg. Co JACKSON ELECTRONICS IND. CROP. JAE Electronics JAI Ltd Jamicon Electronics JAVAN JCET Group Co JCI Jewel Hill Electronic Co JHDLCM Electronics Jiangsu Changjiang Electronics Jiangsu Donghai Semiconductor Jiangsu Juguang Jiangsu Runic Technology Co Jiangsu Szdhdtgd Electronics Jiangxi Jia Wei Cheng Electronic Jilin Sino-Microelectronics Co Jinan USR IOT Technology JING LI Power Electronics Jingcheng Electronics Co Jinghan Switch Electronic JMicron Technology Corp JNHuaMao Technology JODO International Johanson Dielectrics Johanson Technology Johnson Electric JPC Company JYE Tech Ltd JYH HSU(JEC) ELECTRONICS Kai Suh Suh Enterprise KSS Kaida Holding Kaihua Electronics Co Kangmu Sheng Electronics Ka-Ro electronics GmbH. KEC Semiconductor Keil Elektronik Keithley Instruments Kelly Controls, LLC KEMET Corporation Key Technology Keysight Technologies Keystone Electronic King Core Electronics Kingbor Technology Kingbright Electronic KingCCTV Technology Kingdatron Electronic Industrial Co Kingsignal Technology Kingstate Electronics Kingston KIOXIA America, Inc Kiwi Instruments Corp Knowles Electronics KOA Speer Electronics Kobiconn Kodenshi Corp Kohshin Electric Corporation KONE Elevator Kontron S&amp;T KT Micro Inc Kunshan Sino Silicon Technology KUOYUH W.L. Enterprise Co Kutai Electronics Kycon, Inc Kyocera Corporation Ladder Electronics Co Laird Performance Materials. Laird Technologies Laser Components Lattice Semiconductor LawMate International L-com, Inc LD-PD Inc. Leadtrend Technology Corp LEAP Electronic Legerity, Inc Lelon Electronics Corp LEM Components LEMO Lenovo LENZE Lesfuse Electric Co Leshan Radio Co LG Semiconductor LG.Philips Displays Lianchao Future Technology Lighting Integration System Ligitek Electronics Co Lime Microsystems Lineage Power Private Limited Linear Systems Linear Technology Linfinity Microelectronics Link-PP Int'l Technology LinkSmart LINP OMTER International Linx Technologies Lision Technology LITE-ON Semiconductor Littelfuse Inc Lixin Electromagnetic Clutch LIZE Electronic Technology LND, INC LOETRONIC LOGIC Devices Incorporated Longtech Optics Co Longview Technologies Co Lovid International Electronic Low Power Radio Solutions Ltd LOZEN TECHNOLOGY LS ELECTRIC LS Mtron Ltd LSI Computer Systems LTKCHIP LTN Servotechnik GmbH Lucent Technologies LUCKFOX Technology Lucky Light Electronic Luguang Electronic Technology Lumberg Holding Lumentum Operations LLC. Lumex Inc Lumileds Luminus, Inc. Lumissil Microsystems Luna Optoelectronics Lutron Electronic Enterprise Co Lyontek Inc M.S. Kennedy Corp M+R Multitronik GmbH MACOM Technology Macroblock, Inc Macronix International MacTek Corp MagnaChip Semiconductor Magnetics MagnTek Microelectronics Magtek Technology Inc Manorshi Electronics Marktech Optoelectronics, Inc Marlow Industries, Inc Marquardt Switches, Inc Marvell International Matsushita Electric Max Echo Technology Corp MaxBotix Inc Maxic Technology Corporation Maxim Integrated MaxLinear Inc Maxon motor Maxwell Technologies Mayloon Electronic Company MCS Logic Inc Mcuzone International MEAN WELL Enterprises Co Measurement Specialties Mechanic MediaTek Inc Megatek Melexis Technologies Memory Protection Devices MEMSIC, Inc Mentor GmbH Mercury Electronic Meritek Electronics Corporation Mersen EP Metalink Broadband Meticom GmbH. METRODYNE MICROSYSTEM CORP. MIC Electronic Micrel, Inc Micro Commercial Components Micro Crystal AG Micro Electronics Micro Linear Micro One Electronics Micro Power Systems MICRO SENSOR CO;LTD Microchip Technology Microdiode Semiconductor Micrometals, Inc Micron Technology Micronet Communication Microsemi Corporation Microtech Technology Co Ltd Microtherm Sentronic GmbH Microtips Technology Midori Precisions MikroElektronika MikroElektronika d.o.o MikroTik Mill-Max Mfg Milnec Interconnect Systems MindMotion Microelectronics Co. Mingtek Electronics Ltd Mini-Circuits Minilogic Device Corporation Ltd Minmax Technology Minsoo Electronic Co MiTAC Computing Technology Mitel Semiconductor Mitsubishi Electric Mitsubishi Rayon Co Mitsumi Electric Co Mixed Signal Integration Mixic Electronics MKMX America LLC MMI Semiconductors MOAI electronics co Mobicon Electronic Component Modulestek Inc MOKO TECHNOLOGY LTD. Molex Electronic Monitor Enterprises Inc Monolithic Power Systems Morethanall Co Morningstar Corporation MORNSUN Science &amp; Technology Mosdesign Semiconductor Corp Mosel Vitelic Co MOSPEC Semiconductor MOS-TECH Semiconductor Mostek MOTIEN Technology Motorola Mstar Semiconductor M-Systems Inc Multicomp Multi-Inno Technology Multi-Tech Systems Inc Murata Manufacturing Co MVSILICON MYIR Tech Myrra SAS Naina Semiconductor Limited. Nanjing Haichuan Electronic Nanjing Ouzhuo Tech Nanjing Qinheng Microelectronics Nanjing Shiheng Elec NanJing Top Power ASIC Nanjing Up Electronic Technology Nanjing Wotian Technology Co Nanjing Zeming Electronic Co Nanya Technology Co National Instruments National Semiconductor NDK America Inc NEC Electronics Nell Semiconductor Neltron Industrial Nemoto Sensor Engineering NeuroSky, Inc. Neutrik New Jersey Semiconductor NewAE Technology Inc. Newava Technology Inc. Newhaven Display Newport Corporation NewTec Display Co NexFlash Technologies, Inc Nexperia USA Inc Nextchip Nextion NIC Components Corp. Nichia Corporation Nichicon Corporation Nidec Copal Electronics NIDEC SERVO CORPORATION. Nihon Dempa Kogyo Nihon Inter Electronics NIKO Semiconductor Ningbo East Electronics Ningbo ForwardRelayCorporationLTD Ningbo Gosun Technology Co Ningbo Huaguan Electronics Ningbo KLS Electronic Co Ningbo MAX Electronic Technology Co., Ltd Ningbo MKX Electronic Technology Ningbo Rel Electric Co., Ltd. Ningbo Songle Relay Ningbo Tianbo Ganglian Electronics Ninigi Nippon Chemi-Con Nippon Pulse America, Inc Nisshinbo Micro Devices Inc NJR Corporation NKK Switches NMB Technologies Non-Brand Norcomp Inc Nordic Semiconductor Noritake Itron Co Novacap Novatek Microelectronics NTE Electronics NUAND LLC. Nuvoton Technology NVE Corporation Nvidia NVS Navigation Technologies NXP Semiconductors NYS Resistor O2Micro OCIC co Octavo Systems LLC Ogemray Technology Co Ohmite OKI Semiconductor Ole Wolff Electronics Inc Olimex OmniVision Technologies Omron Electronics Omten Electronics ON Semiconductor ON Semiconductor CHINA On Shore Technology On-Bright Electronics OPTEK Technology Inc OPTi Inc Opticon Inc Opto 22 Opto Diode Corp Opto Electronics Co,. LTD OPTOLAB Microsystems Orient Display Oriental Semiconductor Orion Orion Display Technology Co OSI Optoelectronics OSRAM Opto Semiconductors OTAX Corporation Other Oupiin Enterprise Co OWON Technology Inc P&amp;E Microcomputer Systems Pacific Silicon Sensor Panasonic Corporation Panavision Imaging LLC Pancon Corporation PandaBoard PANJIT International Inc Para Light Electronics P-DUKE Technology Co PEAK Electronics GmbH PEAK-System Technik Penny &amp; Giles Peregrine Semiconductor Pericom Semiconductor Corp PerkinElmer Inc Phidgets, Inc Philips Semiconductor Phison Electronics Phoenix Contact Pickering Electronics Ltd PICO Electronics Pico Technology Piher Sensors &amp; Controls SA Pingjing Semi Technology PIR Sensor Co PixArt Imaging Inc Planar Systems, Inc PLX Technology PMC-Sierra, Inc PNI Sensor Corporation POCO Magnetic Polyfet RF Devices Polytronics Technology Pomona Electronics Power Integrations Power Mate Technology Power Systems GmbH Power-Changer Electronic Co Powerex Inc PowerPlaza Powersem GmbH Powertip Technology Preci-Dip SA Precision Monolithics, Inc PREMA Semiconductor GmbH Premier Magnetics PRETEC/C-One Technology Corp. Princeton Technology Proant AB Profichip GmbH Prokit's Industries Prolific Technology Inc Promax-Johnton Semiconductor Pro-Signal ProTek Devices Pro-Wave Electronic PRT PUI Audio Pulse Electronics Qimei Optical &amp; Electric Qingdao Mefine Electronics Qingxian Zeming Langxi Electronic Devices Co Qingyuan Tesla Electronic Technology Qorvo QT Brightek (QTB) QT Optoelectronics Qualcomm Atheros, Inc Quality Semiconductor Qualtek Electronics Quarton inc Quasar Electronics Limited Quectel Wireless Solutions QuickLogic Corporation QX Micro Devices Radiall Radxa Computer Rafael Microelectronics RAFI GmbH &amp; Co RAiO TECHNOLOGY INC RAKwireless Technology Limited. RALEC Ltd Ralink Technology Raltron Electronics Corporation Ramtron International Rapid Electronics Ltd Raspberry Pi Raycom Co Raytac Corporation. Raytheon RCA Corporation Ready Made RC LLC Realtek Semiconductor RECOM Power GmbH Rectron Semiconductor Reichelt elektronik GmbH &amp; Co. KG RELPOL S.A Renata SA Renesas Technology Renhotec Group Ltd Reomax Electronics Reyed Electronics Co RF Digital Corporation. RF Micro Devices RF Solutions Ltd RFaxis, Inc RFHIC Corporation RFM Integrated Device, Inc. RFT Mikroelektronik Rhombus Industries Inc Richtek Technology Co RichWave Technology Ricoh Electronic Devices Riedon RIGOL Ring&amp;tone Electronic Technology Riverdi RLS Merilna tehnika d.o.o ROBOTIS Co Rockwell Rogers Corporation ROHM Semiconductor Roithner Lasertechnik GmbH Rongtech Industry Royal Electronic Factory Co RS Components Ltd RTD Embedded Technologies Rubycon RYCHIP Semiconductor s.m.a.e. GmbH Saft Groupe S.A Sagami Electronics Saia-Burgess Switches Sakae Tsushin Kogyo Saleae, Inc Salecom Electronics Same Sky SamHop Microelectronics Samsung Electronics Samtec Samwha Capacitor Samwin Electronic Technology Samyoung S &amp; C Co SANCO Electronics Co SanDisk Sanhe Enclosure Sanjiaozhou Electrical Technology Sanken Electric SanRex Corporation Sanyo Denki Sanyo Electric Savantic Electronic Sawnics Inc Schaffner Group Schott AG Schrack Technik GmbH Schurter Inc Sciosense B.V. SCTF Electronics Seagate Technology LLC Seaparks Machinery-Electronics Seaward Electronics SeCoS Corporation SEED International Ltd Seeed Technology SEEQ Technology Segger Microcontroller Systems Seiko Instruments Inc Seiko NPC Corporation Semiconductor Circuits, Inc SemiHow Semikron Semiment Technologies Semi-Powerex Corp. SEMITEC Corporation SemiWell Semiconductor Semtech Corporation Semtech Electronics Senba Sensing Technology Co Sendo Sensor Sensata Technologies Sensirion Sentry Manufacturing Inc SEP Electronic Corp Servotecnica SpA SERVO-TEK PRODUCTS COMPANY, INC. SG Micro Corp SGX Sensortech Shaanxi Fullstar Electronics Co Shaanxi Qunli Electric Shaanxi Reactor Microelectronics Shandong Jingdao Microelectronics Shanghai AVIC Optoelectronics Shanghai Belling Co,Ltd Shanghai Consonance Electronics Shanghai Fengxin Electronic Technology Shanghai Fudan Microelectronics Shanghai Gotop Technology Shanghai High-Flying Electronics Shanghai Houde Photo-electric Shanghai Mixinno Microelectronics Co Shanghai Natlinear Electronics Shanghai Xinlong Semiconductor Shanghai Zhichuan Electronic Tech SHARP Corporation Sheng Jay Automation Techno Shenyang Guangcheng Technology Co., Ltd Shenyang KingStar Automation ShenZhen AI-thinker CO Shenzhen AnBoShi Electronic Shenzhen Asenware Test Shenzhen Baishan Mechatronics Shenzhen Biosled Technology Shenzhen Bolutek Technology Shenzhen Chipsea Technologies ShenZhen ChipSourceTek Technology Shenzhen ExSAF Electronics Co Shenzhen Genesis-Systech ShenZhen Gerbole Shenzhen Getech Co Shenzhen GUANGSHIMEI Electronic Shenzhen Hanxia Electronics Shenzhen Haolin Electronics Shenzhen Heliwei Technology Shenzhen honglifa Electronics Co Shenzhen HongyeX Electronics Co ShenZhen HuaXinAn Electronics Co.,Ltd Shenzhen Injoinic Technology Co. Shenzhen Jin Yu Semiconductor Co ShenZhen JINCI Technology Shenzhen Jinrui Electronic Material Co Shenzhen JMRTH Co Shenzhen Kaiyuexiang Electronics Co Shenzhen LFN Technology Co Shenzhen Lodestar S.T Co Shenzhen Lumen Electronics Shenzhen Magnetic Technology Shenzhen MilkV Technology Shenzhen Milliohm Electronics Shenzhen Minewsemi Co., Ltd Shenzhen Nsiway Tech Shenzhen Ou Chuangxin Semiconductor ShenZhen Qi Dian Shi Dai Technology Shenzhen Ruichips Semiconductor Shenzhen Ruilongyuan Electronics Shenzhen Shiji Lighting Shenzhen SI Semiconductors Shenzhen SLKOR Micro Semicon Co Shenzhen Sunmoon Microelectronics Shenzhen Suosemi Tech Shenzhen TongYiFang Optoelectronic Technology CO,Ltd Shenzhen Topmay Electronic Shenzhen TPOWER Semiconductor Shenzhen Universal Micro-Electronics Shenzhen USBR Precision Hardware Electronics Shenzhen Weidy Industrial Development Co., Ltd. Shenzhen Xinbole Electronics Co. Shenzhen Xptek Technology Shenzhen Xunlong Shenzhen Yangxing Technology Co. SHENZHEN YeZhan Electronics Shenzhen Yiwei Technology Shenzhen ZVELL Electronics Shindengen Electric Shin-Etsu Chemical Co SHINYEI Technology SHOEI SIBA GmbH Sichuan huafeng enterprise group SICK, Inc. Siemens Semiconductor Group Si-En Technology SiFirst Technology SiGe Semiconductor Sigma Microelectronics Signetics Silego Technology Silergy Corp Silicon Image Silicon Integrated Systems Silicon Laboratories Silicon Microstructures, Inc. Silicon Motion, Inc Silicon Sensing Systems Limited Silicon Standard Corp Silicon Storage Technology Silicon Systems Inc Silicon Touch Technology Silvan Chip Electronics Silver Telecom Ltd SilverStone Technology SIMCom Wireless Solutions SIMTEK Electronic Components Sinda Photoelectricity Technology SINGULAR TECHNOLOGY CO., LTD. Sinomags Technologies Co Sinopower Semiconductor Sipex Corporation Sirectifier Semiconductors SiTime Corporation Sivago Semiconductor Co SIWARD Crystal Technology Siyang Microelectronics Sizto Tech Corp SKYLAB M&amp;C Technology Skyworks Solutions, Inc SL Power Electronics Corp. SMAR Smartec BV SMC Diode Solutions Co. Smiths Interconnect. SMSC Corporation Soberton Inc Softing Automotive Electronics Sola/Hevi-Duty Sola-IC Solarflex SA Soldex Solid State Scientific SOLIDIC Solitronics Engineering Limited SOL-LED Lighting Co Solomon Systech Song Chuan Song Huei Electric Sonix Technology Sony Corporation Soundwell Electronic South African Micro-Electronic Systems Spansion inc SparkFun Electronics SPEC Sensors LLC Spectra Symbol Corp. Spectrum Digital Incorporated Speed Tech Corp Spin Semiconductor Sprague Semiconductors SPX Flow Technology ST Engineering Stackpole Electronics Standex-Meder Electronics Stannol GmbH Stanson Technology StarChips Technology StarPower Semiconductor Ltd. Startek Electronic Technology STATEK CORPORATION Stäubli International AG. STCmicro Technology Co Stewart Connector STMicroelectronics Stocko Stork Solutions Ltd. Sullins Connector Solutions SUMIDA Corporation Sun Hydraulics Corporation Sun Microelectronics SunLED SUNLORD Sunltech Tech SUNMATE Electronic Sunonwealth Electric Machine Sunplus Technology Sunrise Electronics Suntan Technology Company Suntsu Electronics, Inc. SUNYUAN Technology Supertex Inc Susumu International Suzhou Innoson Technology Suzhou NOVOSENSE Microelectronics Co., Ltd Suzhou Silikron Semiconductor Corp Switchcraft Inc. Switec SYNC Power Crop SyncMOS Technologies Synoxo International System General Corp Tadiran Batteries TAG Semiconductors TA-I Technology TAIKO-NET Tai-Saw Technology Tai-Tech Advanced Electronics Taitien Electronics Taitron Components, Inc Taiwan Alpha Electronic Co Taiwan Semiconductor Taiyo Electric Co Taiyo Yuden Tak Cheong Electronics Talema Group, LLC Tamagawa seiki Co Tamron Tamura Corporation TANCAP Technology Taoglas Limited TDK Corporation (EPCOS) TDK-Lambda Corporation TDK-Micronas GmbH TE Connectivity Team Source Display tech.co,ltd. Techcode Semiconductor Techpoint Inc Techspray/Plato-EMX Enterprises Limited Techstar Electronics TechToys Company TelCom Semiconductor Telcon Ltd Telechips Inc Teledyne Technologies TELEFUNKEN Elektroakustik Telegesis Ltd Telit TEMIC Semiconductor Terawins, Inc Teridian Semiconductor TESLA Testo SE &amp; Co Texas Advanced Optoelectronic Solutions Texas Instruments THAT Corporation Thegioiic Corporation Thermonamic Electronics(Jiangxi) Corp THine Electronics, Inc Thinki Semiconductor Thinking Electronic THOMSON Inc THORLABS Thousand Hundred Industrial Thunder Precision Resistor TIANMA Titan Micro TLC Electronics TNI-U TOOL Token Electronics Industry Tokmas Semiconductor TOKO, Inc Tontek Design Technology Top-arm Topro Technology Topway Technology Torex Semiconductor Toshiba Corporation touchSEMI TOYO LED ELECTRONICS LIMITED. TOYODA TR Electronic Nordic AB. Traco Electronic AG Transcom, Inc Transko Electronics, Inc. TRENDnet, Inc Trenz Electronic Triad Magnetics Trident Microsystems Trimble Inc TRINAMIC Motion Control TRinno Technology Co Tripath Technology TriQuint Semiconductor Truly Semiconductors TRW Inc TT Electronics TTM Technologies, Inc. TXC Corporation UBIQ Semiconductor Ubiquiti Inc u-blox UCE Ultrasonic Co UDF Semiconductor Ultisensor Electronics UNI SEMICONDUCTOR LIMITED Unicorn Microelectronics Corporation Unictron Technologies Corporation. Union Semiconductor Uniroyal Electronics Industry Co Unisonic Technologies Unitra Cemi Uni-Trend Technology Co Unitrode Corporation Universal Microelectronics UPI Semiconductor Corp US Digital US Micro Products. Usha India Ltd Ushio Opto Semiconductors UTRON Technology, Inc Vacuumschmelze GmbH VADEM LTD Vango Technologies, Inc Varitronix Limited VARTA AG Vatronics Technologies Ltd VBsemi Electronics Co. Ltd V-Chip Microsystems VectorNav Vectron International Vehicles instrumentation Device Venkel Ltd VIA Technologies Vicor Corporation Vigortronix Ltd. Vincotech Vishay Visual communication company Vitesse Semiconductor Vivesea VLSI Solution Vweb Corporation W. L. Gore &amp; Associates, Inc WAGO Kontakttechnik GmbH Wakefield Thermal, Inc. Walsin Technology Corporation Walter Electronic Co WanTcom, Inc Wavecom Waveshare Electronics Wavespectrum Laser Inc Wavetronics Technologies WAYTRONIC ELECTRONIC CO.LTD WeEn Semiconductors Weidmüller Interface GmbH Weipu connector Weltrend Semiconductor WENSHING Electronics Western Digital Corporation Willas Electronic Corp WIMA Winbond Electronics</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>38600</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>102</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>کلید فشاری دو حالته 5.8*5.8</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/category/431/pushbutton-switches/%da%a9%d9%84%db%8c%d8%af-%d9%81%d8%b4%d8%a7%d8%b1%db%8c#dtl/46485</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>کلید فشاری خانه دسته‌بندی‌ها کلید فشاری کلید فشاری (Push Button Switch) یکی از پرکاربردترین قطعات در مدارهای کنترلی و الکترونیکی است که با فشردن لحظه‌ای یا پایدار، وظیفه روشن، خاموش یا ارسال سیگنال به مدار را دارد.
+ساختار:
+دارای بدنه پلاستیکی یا فلزی، ترمینال‌های اتصال، مکانیزم فنری داخلی و کلاهک رنگی یا ساده برای فشردن است. در انواع لحظه‌ای (Momentary) و قفل‌شونده (Latching) موجود است.
+ویژگی‌ها:
+انواع SPST، SPDT و DPDT
+عملکرد لحظه‌ای یا قفل‌دار
+تحمل جریان از میلی‌آمپر تا چند آمپر
+رنگ‌بندی متنوع برای کاربردهای مشخص
+نصب روی پنل یا برد PCB
+کاربردها:
+راه‌اندازی یا توقف دستگاه‌ها
+ریست مدارهای میکروکنترلری
+آسانسورها، تابلو برق، سیستم‌های امنیتی
+کنترل ربات، بازی و پروژه‌های DIY
+چند نمونه از قطعه:
+کلید فشاری پنلی 12mm با پایه لحیمی
+کلید کوچک SMD یا DIP بردی
+مدل صنعتی فلزی ضدآب
+کلید فشاری LEDدار 5V
+توضیحات تکمیلی:
+کلیدهای فشاری در مدل‌های متنوعی عرضه می‌شوند و باید بر اساس نوع مصرف، ولتاژ، جریان و مکان نصب انتخاب شوند. برای میکروکنترلرها، استفاده از مقاومت پول‌داون یا آپ جهت جلوگیری از نویز توصیه می‌شود. فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش مقدار جریان 13 30 mA 50 mA 65 mA 100 mA 300 mA 0.5 A 500 mA 1 A 2 A 3 A 5 A 6 A 10 A ≥ = ≤ = مقدار ولتاژ AC 7 28 V 50 V 120 V 125 V 250 V 500 V 2.5 kV ≥ = ≤ = فرم اتصال 11 (ON)-OFF 1 Form X 1NO1NC 2: ON-ON 2P2T 3NO DPDT ON-OFF SPDT SPST SPST-NO = کارکرد 10 Industrial Switches ON-OFF Momentary Momentary or Latching OFF-(ON) Off-Mom ON-OFF Standard Switches Switch Switche Water Proof = مقدار ولتاژ DC 11 3 V 12 V 24 V 28 V 30 V 36 V 50 V 60 V 220 V 250 V 500 V ≥ = ≤ = نوع 17 Anti-Vandal Hoist Switch Metal Button Switch Metal Button Switch Waterproof With LED Light Metal Push Button Switch Push Button Switch Push Buttons Push Buttons Switch Push Switch Push-Key Switch Sealed Self-Locking Switch Standard Standard, llluminated Switch Touch Switch Touch Switch 4 Feet = نوع قرار گیری 5 PC Pin Screw Solder Solder Lug Through Hole = نوع نصب روی برد 3 Panel Mount PCB Mount Through Hole = برند 11 C&amp;K Components Daier Electron Co Eledis E-Switch, Inc Excel Cell Electronic Hanyoung Nux Co Kaihua Electronics Co NKK Switches Non-Brand Sinomags Technologies Co TE Connectivity = پکیج 1 Switch = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز مقدار جریان مقدار ولتاژ AC فرم اتصال کارکرد مقدار ولتاژ DC نوع نوع قرار گیری نوع نصب روی برد برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches Pushbutton Switches اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال PS-12F03 Non-Brand Switch 106,000 ریال اضافه به سبد خرید اوریجینال PS-22F03-2P2T Non-Brand Switch 145,000 ریال اضافه به سبد خرید اوریجینال PS-22F93 Non-Brand Switch 183,000 ریال اضافه به سبد خرید اوریجینال R13-507-B Non-Brand Switch 243,000 ریال اضافه به سبد خرید اوریجینال R13-507-R Non-Brand Switch 245,000 ریال اضافه به سبد خرید اوریجینال R13-507-W Non-Brand Switch 259,000 ریال اضافه به سبد خرید اوریجینال R13-507-Y Non-Brand Switch 291,000 ریال اضافه به سبد خرید اوریجینال R13-507-G Non-Brand Switch 291,000 ریال اضافه به سبد خرید اوریجینال TS4-3TW BLUE Non-Brand Switch 350,000 ریال اضافه به سبد خرید اوریجینال TS4-3TW RED Non-Brand Switch 350,000 ریال اضافه به سبد خرید اوریجینال TS4-3TW GRAY Non-Brand Switch 350,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF NO LIGHT SELF RESETTING 12MM Non-Brand Switch 953,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF NO LIGHT SELF-LOCKING 12MM Non-Brand Switch 1,305,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF NO LIGHT SELF-LOCKING 16MM Non-Brand Switch 2,026,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF NO LIGHT SELF RESETTING 16MM Non-Brand Switch 2,610,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF WITH LIGHT SELF-LOCKING 12MM Non-Brand Switch 2,694,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF WITH LIGHT SELF-LOCKING 16MM Non-Brand Switch 2,909,000 ریال اضافه به سبد خرید اوریجینال LP11OA1NBSRG E-Switch, Inc Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال LP11OA1NASRG E-Switch, Inc Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال PUSH BUTTON SPST RED Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال KEY DS-211 GREEN Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال TS4-3TW GREEN Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال DS-213-R Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال FL13NW5 Non-Brand Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال KAN-L5-01-A Non-Brand Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال PUSH BUTTON SWITCH (SE38) Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال 8121SHZGE C&amp;K Components Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال EPU0122PZ Excel Cell Electronic Switch ناموجود-تحویل 60 روزه اضافه به سبد سفارش اوریجینال R16-503 (RED) Daier Electron Co Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال R16-503 (YELLOW) Daier Electron Co Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال R16-503 (GREEN) Daier Electron Co Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال A16-11SJ RED Daier Electron Co Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال A16-11SJ YELLOW Daier Electron Co Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال A16-11SJ BLUE Daier Electron Co Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال A16-11SJ GREEN Daier Electron Co Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال METAL SWITCH WATERPROOF WITH LIGHT RESET 16MM Non-Brand Switch ناموجود-تحویل 35 روزه اضافه به سبد سفارش اوریجینال 5A11-SFST SE22 Eledis Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال PLC-N1NRN-BTW Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال PLC-N1NRN-ATW Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال PLC-N1NFN-BTW Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال METAL SWITCH WATERPROOF WITH LIGHT RESET 22MM Non-Brand Switch ناموجود-تحویل 35 روزه اضافه به سبد سفارش اوریجینال PBS-24-212P Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>52600</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>5365200</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>کلید کشویی دو حالته 6 پین 9*3.5</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop/category/202/switches/%d8%b3%d9%88%d8%a6%db%8c%da%86-%d9%88-%da%a9%d9%84%db%8c%d8%af#dtl/46496</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>10900</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>10900</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ch340g</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop?searchfilter=M3#dtl/22921</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>محصولات خانه دسته‌بندی‌ها فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه عبارت M3 جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش برند 1666 3M Dynapro 3M Interconnect 3PEAK Incorporated 4D Systems Pty Ltd A Power microelectronics AAEON Technology Aavid Thermalloy ABC Taiwan Electronics ABLIC Inc Abracon Corporation Acam-Messelectronic Acrian, Inc Actel Corporation Active-Semi, Inc Actox Corporation. AD Semiconductor Confidential Adafruit Industries LLC Adam Technologies, Inc ADDA Corp ADDtek Corp Adesto Technologies ADMtek Inc Advanced Acoustic Technology Corp. Advanced Analog Technology Advanced Analogic Technologies Advanced Card Systems Advanced Ceramic X Corp Advanced Linear Devices Inc Advanced Monolithic Systems Advanced Photonix, Inc Advanced Power Electronics Corp Advanced Power Technology Advanced Semiconductor Advantech Corp Advantech Equipment Corporation Aegis Electronic Group AEL Crystals Limited AEM, Inc Aerosemi Technology Co Afa Technologies Inc AG Electrical Technology Agere Systems Agilent Technologies AGM Semiconductor AIC tech Inc. Aimtec Aimtron Corporation Airoha Technology Corp AIRWAVE Technologies Inc AiSHi Capacitors Aixin Opto-Electrical Technology Albright International Ltd Alcatel Microelectronics Alcor Micro Corp Alex Connector Co Ltd Alfa Electronics Algocraft Srl. ALi Corporation Alinx Electronic Technology All Sensors Corporation Allegro Microsystems Alliance Memory Allied Vision, Inc. Allwinner Technology Almita Co. Ltd Alpha &amp; Omega Semiconductor Alpha Micro Components Alpha Semiconductor Alpha Wire Alphasense Ltd, Sensor Technology Alps Electric Co Altera Corporation Amazing Electronic Co Amazing Microelectronic Corp AMD American Microsemiconductors American Microsystems Inc American Power Management American Technical Ceramics Corp American Zettler, Inc. Ametherm, Inc AMI Semiconductor AMIC Technology Corp Amidon Associates, Inc Amlogic Inc. Amotech Corp AMPAK Technology Inc Amphenol Advanced Sensors Amphenol Corporation Amphenol FCI Amphenol RF Ampleon USA Inc ams AG Anachip Corp ANADIGICS Anadigm, Inc Analog Devices Analog Integrations Corporation Analog Microelectronics Analog Power Analogix Semiconductor Inc Anaren, Inc Ancol Electronics Co Andigilog, Inc ANENG Anhui FOSAN Semiconductor Anhui Vico Technologes Co Anovay Technologies Limited ANPEC Electronics Corp Ante Intelligent Company Limited AP Memory Technology. APC Propellers APEM Inc Apex Material Technology Apex Precision Power API Delevan Inc API Technologies Aplus Integrated Circuits Inc APMKorea Apogee Technology, Inc Applent Instruments Applied Micro Circuits Co AppoTech Ltd APT Electronics Co., Ltd. Aptek Technologies ArchNet Technology Arcol UK Ltd Arduino Arduino Nicla Voice. Arima Lasers Corporation Aristotle Enterprises Inc ARTCHIP Semiconductor Artesyn Embedded Technologies AS ENERGI Asahi Kasei Microdevices ASAHI Solder Asia Vital Components Asiliant Technologies ASIX Electronics Corp AsLic Microelectronics Corporation ASMedia Technology Inc. Associated Opto-Electronics Astec Semiconductor. Astrodyne TDI Corporation. ATE Electronics s.r.l Atech Technology Co ATEN International Co Atheros Communications, Inc ATI Technologies Inc Atlas Scientific LLC. Attend Technology Inc AU Optronics Corp Audiowell Electronics Co Auk Contractors Co AUK Semiconductor AUO Corporation AUREL S.P.A Austar Technology AuthenTec, Inc Autonics Corporation Avago Technologies AVANTEK INC. AverLogic Technologies, Inc AVerMedia Technologies Avia Semiconductor Avnet, Inc AVX Corporation AXElite Technology Co Axiomtek Axis Communications AZ Displays, Inc Azoteq Ltd BAFO Technologies Corp Bahar Enclosure Baumer International BBT-China Inc BCD Semiconductor Beckhoff Automation Beijing Boshida Beijing HRH Information Co Beijing Ultrasonic Beijing Yihongtai Technology Beijing Zhongxun Sifang Science &amp; Technology Beken Corporation Bel Fuse Inc Bel Power Solutions Inc Belden Inc Bellnix Bencent Tzeng Ind. Co. Ltd Betlux Beyond Innovation Technology BI Technologies Bicker Elektronik GmbH Billionton Systems Inc Bird Technologies Bi-Sonic Technology Bivar, Inc Blackhawk BLOCK Inc Bluegiga Technologies BOLYMIN,INC BONGSHIN LOADCELL CO. Bookly Micro Electronic Bosch Security Systems Inc Bosch Semiconductors Bosch Sensortec Bothhand USA Boundary Devices Bourns Inc Bowin Microelectronics Brainboxes Limited BRIGHT LED ELECTRONICS CORP. Bright Power Semiconductor BrightKing Inc Brilliance Semiconductor, Inc Broadchip Technology Broadcom Limited BroadLight Inc Brooktree Corporation Burr-Brown Corporation BYD Microelectronics Co., Ltd. C&amp;D Technologies C&amp;K Components Caddock Electronics Inc California Eastern Laboratories California Micro Devices Calogic LLC Cambridge Integrated Circuits Cambridge Silicon Ra dio Limited Camille Bauer Ltd Catalyst Semiconductor Celduc relais CellWise Microelectronics Co Cenker Enterprise Ltd Centenary Materials Co CeNtRa Science Corp Central Components Manufacturing Central Georgia Generator Central Semiconductor CEVA Technologies CFSensor Challenge Electronics Champion Microelectronic Changzhou changjie Technology Co Changzhou Cre-sound Electronics Changzhou DRM Changzhou Esuntech Co Changzhou Kennon ELectronics Changzhou TDA Electronic Changzhou Yuanwang Fluid Technology Chaozhou Three-circle (Group) Co chargebyte GmbH. Chengdu Ebyte Electronic Technology Chengdu Guosheng Technology Chengdu Xincheng Huachuang Electronic ChenMoun Electronic ChenYang Technologies Cheuk Yui Innovation Co Chi Mei Optoelectronics Chieful Science ＆ Technology Chilisin Electronics Co China Base Electronic Technology China ECU Tools Centre China Resources Microelectronics China Software Industry Association Chinfa Electronics Chingis Technology Corp Chino-Excel Technology Chipanalog Incorporated ChipLink Tech Chiplus Semiconductor ChipON Chipower Electronics CHIPS Technology Chipstar Microelectronics CHK Electronics Ltd Chogori USA Chongqing Shengpu Electronics Chrontel, Inc Chunghwa Picture Tubes Churod Electronics Chyao Shiunn Electronic Cincon Electronics Cinetech Ind Cirrus Logic Inc Cisco Systems CIT Relay &amp; Switch Citizen Finedevice Co Cixi AnXon Electronic Cixi Dafa precise Linker Co CiXi KaiFeng Electronics Co Cixi Kefa Electronics Cixi Max Electronics Co.,Ltd Clare, Inc Cliff Electronic Components Limited Cmedia Electronics Inc CML Microsystems Coil Master Co Coil Winding Coilcraft Inc Coiltronics (Eaton) Comchip Technology Commodore Semiconductor Comtec Crystals comtech aha corporation CONEC Elektronische Bauelemente GmbH Conesys,Inc. Conexant Systems, Inc Connfly Electronic Co Connor-Winfield Conquer Electronic Continental Device India Controlair Inc Conversion Devices, Inc Cooper Bussmann Coretek Opto Corporation. Cornell Dubilier Electronics Cortina Systems, Inc Cosel Co Ltd COSINE Nanoelectronics Coto Technology CR Powtech Co Cree, Inc Crydom Inc Crystal Semiconductor Corporation Crystalfontz Crystek Corporation CSCONN PRECISE ELECTRONICS CO.,LTD CT Micro International Co CTS Corporation CUI Inc CVI Laser, LLC CW Industries Cyntec Co Cypress Semiconductor Cyrustek Corporation CYStech Electronics Corp. CYT Opto-Electronic Technology Dachang Electronics Daewoo Semiconductor Daier Electron Co Dailywell Electronics Daishinku Corp Daito Communication Apparatus Daiyo Electronics Dallas Semiconductor DANFOSS Daniels Manufacturing Co Data Device Corporation Davicom Semiconductor Davies Molding, LLC DB Lectro Inc DB Unlimited DC Components Co Dean Technology DECA SwitchLab Inc Decawave Ltd Dechang Electronic Deep Sea Electronics DEGSON Electronics Co Dell Inspiron Delta Electronics DeMint Electronics DENSO Destiny Technology Corp Detaik Technology Co Deva Electronic Controls Limited. Devantech Device Engineering Inc Dexter Magnetic Technologies DFRobot. Dialight Electronics Company Dialog Semiconductor Dielectric Laboratories Digi International Digilent, Inc Digital Voice Systems Digitrax, Inc Digitron Semiconductors Dinkle International Co. Ltd DIN-TEK Microelectronics Diodes Incorporated Diotec Semiconductor Diptronics Manufacturing Inc Display Solution AG DISPLAY VISIONS GmbH 2022. DMB Technology DOESTEK Co DOINGTER Semiconductor Domintech Co Don Connex Electronics DONG IL TECHNOLOGY LTD. Dongguan CHENGXING Electronic Co Dongguan City Wasi Electronic Technology Dongguan Cosson DongGuan HeLing Electronics Dongguan Lanbo Electronics Technology CO Dongguan Yuandi Electronics Dongguan Yuanze Electric Co.,Ltd Dongguan Yuxi Precise Connector Co., Ltd Dongke semiconductor Anhui Co., Ltd Donguan Keyouda Electronic Dosilicon Co DTK electronics Dualsky Models Co Duoxing Electronics Co Duty-Cycle Semiconductor Dynamic Technologies (DTCC) Dynex Semiconductor Ltd, E &amp; E Magnetic Products Limited EAST Semiconductor East Texas Integrated Circuits Eastrising Technology Co Eastsensor Technology Easy IoT Eaton’s Bussmann Ebm-papst inc Echelon Corporation Ecliptek Corporation ECOFIT &amp; ETRI ECS, Inc International EDAC EECO Switch E-Elements Technology Co Efficient Power Conversion Co EG Microelectronics Corp EIC Semiconductor Elan Microelectronics Co Elantec, Inc Electrolube Electronic Alliance Electronic Assembly Electronic Devices Inc Electroustic Ltd Eledis Element14 ELESTA GmbH Elite Semiconductor Memory Eljen Technology Elm Electronics ELM Technology Co Elmos Semiconductor AG ELNA Company Elpida Memory, Inc EM Microelectronic-Marin EMAD Embedded Artists Embest Technology Emerson Encitech Endress+Hauser Management ENE Technology Enplas Corporation Enrwey Co Ltd Eon Silicon Solution E-peas Semiconductors Epitex Inc Epoxy Technology Inc EPSON Electronics Ept Inc Ericsson Microelectronics ERNI Electronics ERSA UK LTD Espressif Systems ESS Technologies E-Switch, Inc ET Enterprises Limited E-T-A Circuit Breakers ETA Solutions E-tec Interconnect Ethertronics Inc Etron Technology, Inc EUCHNER GmbH Eupec semiconductor Euroquartz Ltd Eutech Microelectronics Everanalog Everest Semiconductor Everlight Electronics Everspin Technologies Exar Corporation Excel Cell Electronic Excelitas Technologies Excellence Opto, Inc Excelliance MOS Corporation Fagor Electronica Fairchild Semiconductor Fair-Rite Products Corp FANUC Corporation Faraday Technology Fastline Fastrax Ltd FASTRON Faulhaber GmbH FDK Corporation Feature Integration Technology Feei Cherng Enterprise Feeling Technology Feiyi Technology FEMA Electronics Corporation Fenghua Advanced Technology Ferroxcube International FERYSTER Sp. z.o.o Figaro Engineering Inc Finder Relays, Inc Fingerprint Cards First Semiconductor First Sensor FIS Inc Fischer Connectors Fischer Elektronik Fitipower Integrated Technology Force MOS Technology Co Formosa MS Formox Semiconductor Forsentrk Fortior Technology Co Fortune Semiconductor Forward International Electronics FOTEK Controls Fox Electronics Foxconn Technology Fractus S.A Franz Binder GmbH &amp; Co. Free2Move Holding AB. Freescale Semiconductor Fremont Micro Devices Friendcom Technology Develop FriendlyARM Computer Tech FTDI Chip Fuda Hisi Microelectronics Fuji Electric Fujikura Fujitsu Semiconductor Fujitsu-Takamisawa Fulihua Printer Ribbon Co Futaba Corporation Fu-Yao Technology Co Fuzetec Technology Co Fuzhou Rockchip Electronics Co., Ltd GainSpan Corporation GalaxyCore Inc GaNPower International Inc G-Antetech Industrial Garmin Ltd. Gas Sensing Solutions Ltd. Gaston Electronics GC GE Fanuc GEC Plessey Geehy Semiconductor Co General Electronic Devices General Monitors General Semiconductor Generalplus Technology GeneSiC Semiconductor Genesis Microchip Inc Genesys Logic, Inc Genicom Co., Ltd. Gennum Corporation GETE Electronics GigaDevice Semiconductor Global Connector Technology (GCT) Global Mixed-mode Technology GlobespanVirata, Inc GMC Instruments GME Technology, LLC GoChip Electronic Technology GoldStar Semiconductor Gonbes Technology Co Good Display Good Will Instrument Good-Ark Semiconductor Goodix Technology Governors America Co Gpixel Microelectronics Inc Grayhill Inc GreatLEDs Co Greenliant Systems GRUNER AG GSI Technology, Inc Guangdong Hottech Co Guangdong Huaguan Semiconductor Guangdong TIANQIU Electronics Technology Guangzhou Aosong Electronics Guangzhou Xinyue Electronic Guerrilla RF, Inc H&amp;M Semiconductor HABEY Halbleiter aus Frankfurt HALO Electronics Hamamatsu Photonics Hangzhou Grow Technology Co Hangzhou Nationalchip Science Hangzhou Prosper Hangzhou Silan Microelectronics Hannstar Display Corp HanRun Electronics Hanwei Electronics Co Hanyoung Nux Co HAOHAI ELECTRONICS HAOYU Electronics Harris Semiconductor HARTING Technology Harvatek Corporation Harwin Hawyang Semiconductor Hebei International Trading Co HEITEC AG. Hemingruizhi Electronic Henan Hanwei Electronics Co Hengda New Materials Technology HengJiaXing Electronics Co Henkel Corporation HenLv Power Technology Heter Electronics Hewlett-Packard Hexin Technology Highly Electric Hi-Link Electronic Technology Hi-Optel Technology Hirose Electric Hi-Sincerity Microelectronics Hitachi Maxell, Ltd Hitachi Semiconductor HITPOINT Inc Hittite Microwave Hivolt Capacitors Ltd H-JTAG Technology Hokuriku Electric Industry Co Ltd Hokuyo Automatic Co Holt Integrated Circuits Holtek Semiconductor Honeywell International Hong Kong Resistors Manufactory Hongfa Electroacoustic Co HONGHUA ELECTRONIC Hope Microelectronics HORIBA, Ltd. Hosiden Corporation Hosonic Electronic Co Hotchip Technology HTC Korea TAEJIN Technology Huada Connectors Huanor International Huaqi Microelectronics Co Huawei Technologies Huayu Technology HuaYuan Micro Electronic Huayue Microelectronics Co HUBER+SUHNER Huibei KENTO Electronic Huidu Technology Hukx Sensor Technology Humirel Hurricane Tech. Co HW group s.r.o HYCON Technology Corp. Hynix Semiconductor Hyundai Semiconductor IC Plus Corp ICE Components, Inc. iC-Haus GmbH Icom Inc ICP DAS CO ID Innovations ID TECH IDEC Corporation IEI Integration Ignion Iintelligent Motion Systems IK Semiconductor ILSI America LLC IMP, Inc Inchange Semiconductor Industrial Fiber Optics, Inc Industrial Technology Research Institute Infineon Technologies Initio Corporation INJOINIC TECHNOLOGY Innolux Corporation InnoSenT-Innovative Radar Sensor Technology Innovative Sensor Technology IST Innuovo Magnetics Co Inova Semiconductors InPlay Inc. InPower Semiconductor INTEGRAL JSC Integrated Circuit Solution Integrated Circuit Systems Integrated Crystal Technology Integrated Device Technology Integrated Sensor Technologies Integrated Silicon Solution Intel Corporation InterFET Corp Interlink Electronics International CMOS Technology International Rectifier Intersil Corporation Intronic Semiconductor Intronics Power, Inc InvenSense Inc IQD Frequency Products Ltd IRAN Ironwood Electronics IRXON Electronic Isabellenhütte Heusler GmbH &amp; Co KG Isahaya Electronics Co iSentek Technology Isocom Components Isotek Corp ITE Tech ITT Cannon, LLC ITT Semiconductors Ituner Networks Corp iWatt Inc IXYS Integrated Circuits J.S.T. Mfg. Co JACKSON ELECTRONICS IND. CROP. JAE Electronics JAI Ltd Jamicon Electronics JAVAN JCET Group Co JCI Jewel Hill Electronic Co JHDLCM Electronics Jiangsu Changjiang Electronics Jiangsu Donghai Semiconductor Jiangsu Juguang Jiangsu Runic Technology Co Jiangsu Szdhdtgd Electronics Jiangxi Jia Wei Cheng Electronic Jilin Sino-Microelectronics Co Jinan USR IOT Technology JING LI Power Electronics Jingcheng Electronics Co Jinghan Switch Electronic JMicron Technology Corp JNHuaMao Technology JODO International Johanson Dielectrics Johanson Technology Johnson Electric JPC Company JYE Tech Ltd JYH HSU(JEC) ELECTRONICS Kai Suh Suh Enterprise KSS Kaida Holding Kaihua Electronics Co Kangmu Sheng Electronics Ka-Ro electronics GmbH. KEC Semiconductor Keil Elektronik Keithley Instruments Kelly Controls, LLC KEMET Corporation Key Technology Keysight Technologies Keystone Electronic King Core Electronics Kingbor Technology Kingbright Electronic KingCCTV Technology Kingdatron Electronic Industrial Co Kingsignal Technology Kingstate Electronics Kingston KIOXIA America, Inc Kiwi Instruments Corp Knowles Electronics KOA Speer Electronics Kobiconn Kodenshi Corp Kohshin Electric Corporation KONE Elevator Kontron S&amp;T KT Micro Inc Kunshan Sino Silicon Technology KUOYUH W.L. Enterprise Co Kutai Electronics Kycon, Inc Kyocera Corporation Ladder Electronics Co Laird Performance Materials. Laird Technologies Laser Components Lattice Semiconductor LawMate International L-com, Inc LD-PD Inc. Leadtrend Technology Corp LEAP Electronic Legerity, Inc Lelon Electronics Corp LEM Components LEMO Lenovo LENZE Lesfuse Electric Co Leshan Radio Co LG Semiconductor LG.Philips Displays Lianchao Future Technology Lighting Integration System Ligitek Electronics Co Lime Microsystems Lineage Power Private Limited Linear Systems Linear Technology Linfinity Microelectronics Link-PP Int'l Technology LinkSmart LINP OMTER International Linx Technologies Lision Technology LITE-ON Semiconductor Littelfuse Inc Lixin Electromagnetic Clutch LIZE Electronic Technology LND, INC LOETRONIC LOGIC Devices Incorporated Longtech Optics Co Longview Technologies Co Lovid International Electronic Low Power Radio Solutions Ltd LOZEN TECHNOLOGY LS ELECTRIC LS Mtron Ltd LSI Computer Systems LTKCHIP LTN Servotechnik GmbH Lucent Technologies LUCKFOX Technology Lucky Light Electronic Luguang Electronic Technology Lumberg Holding Lumentum Operations LLC. Lumex Inc Lumileds Luminus, Inc. Lumissil Microsystems Luna Optoelectronics Lutron Electronic Enterprise Co Lyontek Inc M.S. Kennedy Corp M+R Multitronik GmbH MACOM Technology Macroblock, Inc Macronix International MacTek Corp MagnaChip Semiconductor Magnetics MagnTek Microelectronics Magtek Technology Inc Manorshi Electronics Marktech Optoelectronics, Inc Marlow Industries, Inc Marquardt Switches, Inc Marvell International Matsushita Electric Max Echo Technology Corp MaxBotix Inc Maxic Technology Corporation Maxim Integrated MaxLinear Inc Maxon motor Maxwell Technologies Mayloon Electronic Company MCS Logic Inc Mcuzone International MEAN WELL Enterprises Co Measurement Specialties Mechanic MediaTek Inc Megatek Melexis Technologies Memory Protection Devices MEMSIC, Inc Mentor GmbH Mercury Electronic Meritek Electronics Corporation Mersen EP Metalink Broadband Meticom GmbH. METRODYNE MICROSYSTEM CORP. MIC Electronic Micrel, Inc Micro Commercial Components Micro Crystal AG Micro Electronics Micro Linear Micro One Electronics Micro Power Systems MICRO SENSOR CO;LTD Microchip Technology Microdiode Semiconductor Micrometals, Inc Micron Technology Micronet Communication Microsemi Corporation Microtech Technology Co Ltd Microtherm Sentronic GmbH Microtips Technology Midori Precisions MikroElektronika MikroElektronika d.o.o MikroTik Mill-Max Mfg Milnec Interconnect Systems MindMotion Microelectronics Co. Mingtek Electronics Ltd Mini-Circuits Minilogic Device Corporation Ltd Minmax Technology Minsoo Electronic Co MiTAC Computing Technology Mitel Semiconductor Mitsubishi Electric Mitsubishi Rayon Co Mitsumi Electric Co Mixed Signal Integration Mixic Electronics MKMX America LLC MMI Semiconductors MOAI electronics co Mobicon Electronic Component Modulestek Inc MOKO TECHNOLOGY LTD. Molex Electronic Monitor Enterprises Inc Monolithic Power Systems Morethanall Co Morningstar Corporation MORNSUN Science &amp; Technology Mosdesign Semiconductor Corp Mosel Vitelic Co MOSPEC Semiconductor MOS-TECH Semiconductor Mostek MOTIEN Technology Motorola Mstar Semiconductor M-Systems Inc Multicomp Multi-Inno Technology Multi-Tech Systems Inc Murata Manufacturing Co MVSILICON MYIR Tech Myrra SAS Naina Semiconductor Limited. Nanjing Haichuan Electronic Nanjing Ouzhuo Tech Nanjing Qinheng Microelectronics Nanjing Shiheng Elec NanJing Top Power ASIC Nanjing Up Electronic Technology Nanjing Wotian Technology Co Nanjing Zeming Electronic Co Nanya Technology Co National Instruments National Semiconductor NDK America Inc NEC Electronics Nell Semiconductor Neltron Industrial Nemoto Sensor Engineering NeuroSky, Inc. Neutrik New Jersey Semiconductor NewAE Technology Inc. Newava Technology Inc. Newhaven Display Newport Corporation NewTec Display Co NexFlash Technologies, Inc Nexperia USA Inc Nextchip Nextion NIC Components Corp. Nichia Corporation Nichicon Corporation Nidec Copal Electronics NIDEC SERVO CORPORATION. Nihon Dempa Kogyo Nihon Inter Electronics NIKO Semiconductor Ningbo East Electronics Ningbo ForwardRelayCorporationLTD Ningbo Gosun Technology Co Ningbo Huaguan Electronics Ningbo KLS Electronic Co Ningbo MAX Electronic Technology Co., Ltd Ningbo MKX Electronic Technology Ningbo Rel Electric Co., Ltd. Ningbo Songle Relay Ningbo Tianbo Ganglian Electronics Ninigi Nippon Chemi-Con Nippon Pulse America, Inc Nisshinbo Micro Devices Inc NJR Corporation NKK Switches NMB Technologies Non-Brand Norcomp Inc Nordic Semiconductor Noritake Itron Co Novacap Novatek Microelectronics NTE Electronics NUAND LLC. Nuvoton Technology NVE Corporation Nvidia NVS Navigation Technologies NXP Semiconductors NYS Resistor O2Micro OCIC co Octavo Systems LLC Ogemray Technology Co Ohmite OKI Semiconductor Ole Wolff Electronics Inc Olimex OmniVision Technologies Omron Electronics Omten Electronics ON Semiconductor ON Semiconductor CHINA On Shore Technology On-Bright Electronics OPTEK Technology Inc OPTi Inc Opticon Inc Opto 22 Opto Diode Corp Opto Electronics Co,. LTD OPTOLAB Microsystems Orient Display Oriental Semiconductor Orion Orion Display Technology Co OSI Optoelectronics OSRAM Opto Semiconductors OTAX Corporation Other Oupiin Enterprise Co OWON Technology Inc P&amp;E Microcomputer Systems Pacific Silicon Sensor Panasonic Corporation Panavision Imaging LLC Pancon Corporation PandaBoard PANJIT International Inc Para Light Electronics P-DUKE Technology Co PEAK Electronics GmbH PEAK-System Technik Penny &amp; Giles Peregrine Semiconductor Pericom Semiconductor Corp PerkinElmer Inc Phidgets, Inc Philips Semiconductor Phison Electronics Phoenix Contact Pickering Electronics Ltd PICO Electronics Pico Technology Piher Sensors &amp; Controls SA Pingjing Semi Technology PIR Sensor Co PixArt Imaging Inc Planar Systems, Inc PLX Technology PMC-Sierra, Inc PNI Sensor Corporation POCO Magnetic Polyfet RF Devices Polytronics Technology Pomona Electronics Power Integrations Power Mate Technology Power Systems GmbH Power-Changer Electronic Co Powerex Inc PowerPlaza Powersem GmbH Powertip Technology Preci-Dip SA Precision Monolithics, Inc PREMA Semiconductor GmbH Premier Magnetics PRETEC/C-One Technology Corp. Princeton Technology Proant AB Profichip GmbH Prokit's Industries Prolific Technology Inc Promax-Johnton Semiconductor Pro-Signal ProTek Devices Pro-Wave Electronic PRT PUI Audio Pulse Electronics Qimei Optical &amp; Electric Qingdao Mefine Electronics Qingxian Zeming Langxi Electronic Devices Co Qingyuan Tesla Electronic Technology Qorvo QT Brightek (QTB) QT Optoelectronics Qualcomm Atheros, Inc Quality Semiconductor Qualtek Electronics Quarton inc Quasar Electronics Limited Quectel Wireless Solutions QuickLogic Corporation QX Micro Devices Radiall Radxa Computer Rafael Microelectronics RAFI GmbH &amp; Co RAiO TECHNOLOGY INC RAKwireless Technology Limited. RALEC Ltd Ralink Technology Raltron Electronics Corporation Ramtron International Rapid Electronics Ltd Raspberry Pi Raycom Co Raytac Corporation. Raytheon RCA Corporation Ready Made RC LLC Realtek Semiconductor RECOM Power GmbH Rectron Semiconductor Reichelt elektronik GmbH &amp; Co. KG RELPOL S.A Renata SA Renesas Technology Renhotec Group Ltd Reomax Electronics Reyed Electronics Co RF Digital Corporation. RF Micro Devices RF Solutions Ltd RFaxis, Inc RFHIC Corporation RFM Integrated Device, Inc. RFT Mikroelektronik Rhombus Industries Inc Richtek Technology Co RichWave Technology Ricoh Electronic Devices Riedon RIGOL Ring&amp;tone Electronic Technology Riverdi RLS Merilna tehnika d.o.o ROBOTIS Co Rockwell Rogers Corporation ROHM Semiconductor Roithner Lasertechnik GmbH Rongtech Industry Royal Electronic Factory Co RS Components Ltd RTD Embedded Technologies Rubycon RYCHIP Semiconductor s.m.a.e. GmbH Saft Groupe S.A Sagami Electronics Saia-Burgess Switches Sakae Tsushin Kogyo Saleae, Inc Salecom Electronics Same Sky SamHop Microelectronics Samsung Electronics Samtec Samwha Capacitor Samwin Electronic Technology Samyoung S &amp; C Co SANCO Electronics Co SanDisk Sanhe Enclosure Sanjiaozhou Electrical Technology Sanken Electric SanRex Corporation Sanyo Denki Sanyo Electric Savantic Electronic Sawnics Inc Schaffner Group Schott AG Schrack Technik GmbH Schurter Inc Sciosense B.V. SCTF Electronics Seagate Technology LLC Seaparks Machinery-Electronics Seaward Electronics SeCoS Corporation SEED International Ltd Seeed Technology SEEQ Technology Segger Microcontroller Systems Seiko Instruments Inc Seiko NPC Corporation Semiconductor Circuits, Inc SemiHow Semikron Semiment Technologies Semi-Powerex Corp. SEMITEC Corporation SemiWell Semiconductor Semtech Corporation Semtech Electronics Senba Sensing Technology Co Sendo Sensor Sensata Technologies Sensirion Sentry Manufacturing Inc SEP Electronic Corp Servotecnica SpA SERVO-TEK PRODUCTS COMPANY, INC. SG Micro Corp SGX Sensortech Shaanxi Fullstar Electronics Co Shaanxi Qunli Electric Shaanxi Reactor Microelectronics Shandong Jingdao Microelectronics Shanghai AVIC Optoelectronics Shanghai Belling Co,Ltd Shanghai Consonance Electronics Shanghai Fengxin Electronic Technology Shanghai Fudan Microelectronics Shanghai Gotop Technology Shanghai High-Flying Electronics Shanghai Houde Photo-electric Shanghai Mixinno Microelectronics Co Shanghai Natlinear Electronics Shanghai Xinlong Semiconductor Shanghai Zhichuan Electronic Tech SHARP Corporation Sheng Jay Automation Techno Shenyang Guangcheng Technology Co., Ltd Shenyang KingStar Automation ShenZhen AI-thinker CO Shenzhen AnBoShi Electronic Shenzhen Asenware Test Shenzhen Baishan Mechatronics Shenzhen Biosled Technology Shenzhen Bolutek Technology Shenzhen Chipsea Technologies ShenZhen ChipSourceTek Technology Shenzhen ExSAF Electronics Co Shenzhen Genesis-Systech ShenZhen Gerbole Shenzhen Getech Co Shenzhen GUANGSHIMEI Electronic Shenzhen Hanxia Electronics Shenzhen Haolin Electronics Shenzhen Heliwei Technology Shenzhen honglifa Electronics Co Shenzhen HongyeX Electronics Co ShenZhen HuaXinAn Electronics Co.,Ltd Shenzhen Injoinic Technology Co. Shenzhen Jin Yu Semiconductor Co ShenZhen JINCI Technology Shenzhen Jinrui Electronic Material Co Shenzhen JMRTH Co Shenzhen Kaiyuexiang Electronics Co Shenzhen LFN Technology Co Shenzhen Lodestar S.T Co Shenzhen Lumen Electronics Shenzhen Magnetic Technology Shenzhen MilkV Technology Shenzhen Milliohm Electronics Shenzhen Minewsemi Co., Ltd Shenzhen Nsiway Tech Shenzhen Ou Chuangxin Semiconductor ShenZhen Qi Dian Shi Dai Technology Shenzhen Ruichips Semiconductor Shenzhen Ruilongyuan Electronics Shenzhen Shiji Lighting Shenzhen SI Semiconductors Shenzhen SLKOR Micro Semicon Co Shenzhen Sunmoon Microelectronics Shenzhen Suosemi Tech Shenzhen TongYiFang Optoelectronic Technology CO,Ltd Shenzhen Topmay Electronic Shenzhen TPOWER Semiconductor Shenzhen Universal Micro-Electronics Shenzhen USBR Precision Hardware Electronics Shenzhen Weidy Industrial Development Co., Ltd. Shenzhen Xinbole Electronics Co. Shenzhen Xptek Technology Shenzhen Xunlong Shenzhen Yangxing Technology Co. SHENZHEN YeZhan Electronics Shenzhen Yiwei Technology Shenzhen ZVELL Electronics Shindengen Electric Shin-Etsu Chemical Co SHINYEI Technology SHOEI SIBA GmbH Sichuan huafeng enterprise group SICK, Inc. Siemens Semiconductor Group Si-En Technology SiFirst Technology SiGe Semiconductor Sigma Microelectronics Signetics Silego Technology Silergy Corp Silicon Image Silicon Integrated Systems Silicon Laboratories Silicon Microstructures, Inc. Silicon Motion, Inc Silicon Sensing Systems Limited Silicon Standard Corp Silicon Storage Technology Silicon Systems Inc Silicon Touch Technology Silvan Chip Electronics Silver Telecom Ltd SilverStone Technology SIMCom Wireless Solutions SIMTEK Electronic Components Sinda Photoelectricity Technology SINGULAR TECHNOLOGY CO., LTD. Sinomags Technologies Co Sinopower Semiconductor Sipex Corporation Sirectifier Semiconductors SiTime Corporation Sivago Semiconductor Co SIWARD Crystal Technology Siyang Microelectronics Sizto Tech Corp SKYLAB M&amp;C Technology Skyworks Solutions, Inc SL Power Electronics Corp. SMAR Smartec BV SMC Diode Solutions Co. Smiths Interconnect. SMSC Corporation Soberton Inc Softing Automotive Electronics Sola/Hevi-Duty Sola-IC Solarflex SA Soldex Solid State Scientific SOLIDIC Solitronics Engineering Limited SOL-LED Lighting Co Solomon Systech Song Chuan Song Huei Electric Sonix Technology Sony Corporation Soundwell Electronic South African Micro-Electronic Systems Spansion inc SparkFun Electronics SPEC Sensors LLC Spectra Symbol Corp. Spectrum Digital Incorporated Speed Tech Corp Spin Semiconductor Sprague Semiconductors SPX Flow Technology ST Engineering Stackpole Electronics Standex-Meder Electronics Stannol GmbH Stanson Technology StarChips Technology StarPower Semiconductor Ltd. Startek Electronic Technology STATEK CORPORATION Stäubli International AG. STCmicro Technology Co Stewart Connector STMicroelectronics Stocko Stork Solutions Ltd. Sullins Connector Solutions SUMIDA Corporation Sun Hydraulics Corporation Sun Microelectronics SunLED SUNLORD Sunltech Tech SUNMATE Electronic Sunonwealth Electric Machine Sunplus Technology Sunrise Electronics Suntan Technology Company Suntsu Electronics, Inc. SUNYUAN Technology Supertex Inc Susumu International Suzhou Innoson Technology Suzhou NOVOSENSE Microelectronics Co., Ltd Suzhou Silikron Semiconductor Corp Switchcraft Inc. Switec SYNC Power Crop SyncMOS Technologies Synoxo International System General Corp Tadiran Batteries TAG Semiconductors TA-I Technology TAIKO-NET Tai-Saw Technology Tai-Tech Advanced Electronics Taitien Electronics Taitron Components, Inc Taiwan Alpha Electronic Co Taiwan Semiconductor Taiyo Electric Co Taiyo Yuden Tak Cheong Electronics Talema Group, LLC Tamagawa seiki Co Tamron Tamura Corporation TANCAP Technology Taoglas Limited TDK Corporation (EPCOS) TDK-Lambda Corporation TDK-Micronas GmbH TE Connectivity Team Source Display tech.co,ltd. Techcode Semiconductor Techpoint Inc Techspray/Plato-EMX Enterprises Limited Techstar Electronics TechToys Company TelCom Semiconductor Telcon Ltd Telechips Inc Teledyne Technologies TELEFUNKEN Elektroakustik Telegesis Ltd Telit TEMIC Semiconductor Terawins, Inc Teridian Semiconductor TESLA Testo SE &amp; Co Texas Advanced Optoelectronic Solutions Texas Instruments THAT Corporation Thegioiic Corporation Thermonamic Electronics(Jiangxi) Corp THine Electronics, Inc Thinki Semiconductor Thinking Electronic THOMSON Inc THORLABS Thousand Hundred Industrial Thunder Precision Resistor TIANMA Titan Micro TLC Electronics TNI-U TOOL Token Electronics Industry Tokmas Semiconductor TOKO, Inc Tontek Design Technology Top-arm Topro Technology Topway Technology Torex Semiconductor Toshiba Corporation touchSEMI TOYO LED ELECTRONICS LIMITED. TOYODA TR Electronic Nordic AB. Traco Electronic AG Transcom, Inc Transko Electronics, Inc. TRENDnet, Inc Trenz Electronic Triad Magnetics Trident Microsystems Trimble Inc TRINAMIC Motion Control TRinno Technology Co Tripath Technology TriQuint Semiconductor Truly Semiconductors TRW Inc TT Electronics TTM Technologies, Inc. TXC Corporation UBIQ Semiconductor Ubiquiti Inc u-blox UCE Ultrasonic Co UDF Semiconductor Ultisensor Electronics UNI SEMICONDUCTOR LIMITED Unicorn Microelectronics Corporation Unictron Technologies Corporation. Union Semiconductor Uniroyal Electronics Industry Co Unisonic Technologies Unitra Cemi Uni-Trend Technology Co Unitrode Corporation Universal Microelectronics UPI Semiconductor Corp US Digital US Micro Products. Usha India Ltd Ushio Opto Semiconductors UTRON Technology, Inc Vacuumschmelze GmbH VADEM LTD Vango Technologies, Inc Varitronix Limited VARTA AG Vatronics Technologies Ltd VBsemi Electronics Co. Ltd V-Chip Microsystems VectorNav Vectron International Vehicles instrumentation Device Venkel Ltd VIA Technologies Vicor Corporation Vigortronix Ltd. Vincotech Vishay Visual communication company Vitesse Semiconductor Vivesea VLSI Solution Vweb Corporation W. L. Gore &amp; Associates, Inc WAGO Kontakttechnik GmbH Wakefield Thermal, Inc. Walsin Technology Corporation Walter Electronic Co WanTcom, Inc Wavecom Waveshare Electronics Wavespectrum Laser Inc Wavetronics Technologies WAYTRONIC ELECTRONIC CO.LTD WeEn Semiconductors Weidmüller Interface GmbH Weipu connector Weltrend Semiconductor WENSHING Electronics Western Digital Corporation Willas Electronic Corp WIMA Winbond Electronics W</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>69900</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>69900</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ME6210A33PG</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>https://lionelectronic.ir/products/2834-ME6210A33PG</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>لیون الکترونیک | ME6210A33PG خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products Power Management Regulators LDO Voltage Regulators ME6210A33PG 962 موجودی محصول تعداد قیمت 5 87,046 ریال 50 84,045 ریال 500 81,043 ریال افزودن به سبد خرید Full Reel: 1000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام ME6210A33PG ME6210A33PG Part Number 2834 Lion Part Download Datasheet MicrOne Manufacture رگولاتور(لُو دراپ) 3.3 ولت 500 میلی آمپر با پکیج SOT-89-3 Fixed LDO Low Quiescent, Low Dropout 3.3V 500mA SOT-89-3 مشخصات رگولاتور(LDO) ME6210A33PG رگولاتور(LDO) ME6210A33PG Part Number 1 Number of Outputs 12mV Load Regulation Reel Packaging Positive Polarity 1.5uA Quiescent Current SMD/SMT Mounting Style +85C Maximum Operating Temperature -25C Minimum Operating Temperature Fixed Output Type 220mV Dropout Voltage 18V Input Voltage Max N/A PSRR - Ripple Rejection - Typ 2V Input Voltage Min 0.1%/V Line Regulation 500mA Output Current 3.3V Output Voltage SOT-89 Package-Case نظرات کاربران ارسال نظر محصولات مرتبط TPS7A8500ARGRT TPS7A2033PDBVR TLV76133DCYR AZ1117CH-1.2TRG1 XC6206P302PR TLV74330PDBVR TLV74328PDBVR TLV74325PDBVR TLV74318PDBVR TLV74315PDBVR × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 962 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>87046</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>87046</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>rele 24</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>https://arefelectronic.com/%d8%b1%d9%84%d9%87-%d8%a7%d9%85%d8%b1%d9%86-g2r-1-e-%d8%af%d8%a7%d8%b1%d8%a7%db%8c-24-%d9%88%d9%84%d8%aa/</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>رله امرن مدل G2R-1-E – 24V | 8PIN | 16A - فروشگاه عارف الکترونیک Skip to content جستجو برای: سبد خرید سبد خرید شما خالی است. بازگشت به فروشگاه ورود / عضویت سبد خرید سبد خرید شما خالی است. بازگشت به فروشگاه صفحه اصلی قطعات الکترونیک رله میلون بچه میلون پکیجی SSR SMD قدرت (آمپربالا) خودرویی مینیاتوری پایه گرد (تابلویی) T شکل مخابراتی کتابی PCB کولری رله PLC روسی لودسل تک پایه خمشی خمشی دو طرفه فشاری (سیلندری) کششی باسکولی خاص سوکت رله ریلی PCB (سوزنی) ای سی smd دیپ پتانسیومتر PT5 PT10 PT15 اسپانیایی چینی کارت رله ۲ کانال ۴ کانال ۸ کانال ۱۶ کانال سوئیچینگ فلزی پلاستیکی صنعتی خازن پل دیود کانکتور Micro-D J30J انواع سیم تجهیزات الکترونیک نمایشگر لودسل کاموس yaohua vista قلع ASAHI (اورجینال) طرح ASAHI RX_70 S ARTANIC (آرتانیک) PROSKIT تجهیزات شارژ و روشنایی باتری قلمی (AA) نیم قلمی (AAA) باتری 18650 باتری ویپ قابل شارژ کتابی (9V) سکه ای سایز C سایز D باتری سیلد اسید تلفن بی سیم لیتیوم ایون لیتیوم پلیمر سمعکی ساعت ریموت کنترل شارژر باتری VARTA (وارتا) NITECORE (نایتکور) پاوربانک 10000mAh 15000mAh 20000mAh WIRELESS چراغ قوه حرفه ای معمولی خودکاری هندلی هدلایت باتری لپ تاپ چسب و خمیر برندها zemic bongshin varta NHG OMRON panasonic RX_70 NITECORE Yaohua ASAHI ACP F&amp;T microchip molicell R&amp;A SCHRACK S CAMOS راهنما خرید وبلاگ ارتباط با ما جستجو برای: 1% خانه / رله / رله امرن ( OMRON ) رله امرن مدل G2R-1-E – 24V | 8PIN | 16A تومان ۳۱۲,۱۸۰ قیمت اصلی: تومان۳۱۲,۱۸۰ بود. تومان ۳۰۹,۶۰۰ قیمت فعلی: تومان۳۰۹,۶۰۰. رله امرن G2R-1-E دارای 24 ولت و جریان 16 آمپر و 1 کنتاکت و 8 پین می باشد. این رله محصول کشور اندونزی می باشد. تخفیف در تعداد خرید تعداد 50 - 100 101 - 500 501 - 1000 قیمت تومان ۳۰۳,۴۰۸ تومان ۳۰۰,۳۱۲ تومان ۲۹۷,۲۱۶ 3037 در انبار رله امرن مدل G2R-1-E – 24V | 8PIN | 16A عدد افزودن به سبد خرید جهت خرید محصولات به صورت عمده با شماره تلفن های فروشگاه تماس و یا در واتساپ پیام دهید. مقایسه دسته: رله , رله امرن ( OMRON ) , رله کتابی برچسب: 24 ولت دسته‌ بندی محصولات لودسل (92) لودسل زمیک ( zemic ) (68) لودسل bongshin (21) لودسل تک پایه (36) لودسل خمشی (14) لودسل فشاری ( سیلندری ) (14) لودسل کششی (29) پاوربانک (6) 10000mAh (2) 15000mAh (2) 20000mAh (2) WIRELESS (3) SCHRACK (8) کانکتور (60) پتانسیومتر (26) پتانسیومتر PT10 (10) پتانسیومتر PT15 (16) پتانسیومتر اسپانیایی (13) پتانسیومتر چینی (9) R&amp;A (11) Micro-D (14) سوئیچینگ (4) سوئیچینگ فلزی (3) سوئیچینگ پلاستیکی (1) کارت رله (7) ۸ کانال (3) ۱۶ کانال (1) ۴ کانال (3) molicell (1) J30J (14) کولری (13) ASAHI (3) آداپتور (4) رله (336) رله روسی (5) رله آمپربالا (قدرت) (62) رله مینیاتوری (7) رله خودرویی (18) رله پایه گرد ( تابلویی ) (9) پاور (50) رله PCB (8) رله بچه میلون (3) رله T شکل (10) رله امرن ( OMRON ) (139) رله PLC (7) رله مخابراتی (23) رله پکیجی (31) رله کتابی (43) رله SSR (8) رله NHG (43) رله میلون (16) ACP (8) سوکت رله (23) سوکت رله ریلی (12) سوکت رله سوزنی (13) پل دیود (1) F&amp;T (2) باتری (208) باتری قلمی (26) باتری دزدگیر (2) باتری سیلد اسید (6) باتری نیم قلمی (26) باتری لیتیوم پلیمر (3) باتری شیر چشمی (1) باتری کتابی (14) باتری پک شده (1) باتری سایز C (6) باتری ریموت کنترل (8) باتری سایز D (8) باتری لیتیوم (30) باتری ساعت (8) باتری وارتا (80) باتری شارژی (23) باتری سکه ای (23) باتری پاناسونیک (26) باتری تلفن بی سیم (12) باتری ۱۸۶۵۰ (13) باتری لپ تاپ (16) باتری ویپ (12) باتری لیتیوم یون (13) باتری سمعکی (5) شارژر باتری (17) VARTA (وارتا) (3) NITECORE (نایتکور) (9) خازن (2) BLAUPUNKT (3) قلع (8) ASAHI (اورجینال) (2) طرح ASAHI (1) RX_70 (1) S (1) ARTANIC (آرتانیک) (1) PROSKIT (1) نمایشگر لودسل (16) نمایشگر لودسل کاموس (5) نمایشگر لودسل yaohua (2) نمایشگر لودسل vista (2) چراغ قوه (11) هندلی (1) حرفه ای (6) معمولی (1) خودکاری (1) ای سی (5) اتمگا (2) دیپ (1) smd (1) شارژر لپ تاپ (7) هدلایت (4) چسب و خمیر (5) توضیحات رله های همه منظوره از تک قطب 10A و دو قطب 5A  می باشد. قدرت دی الکتریک از 5000V بین سیم پیچ ها  و اتصالات و افزایش مقاومت 10000V طراحی شده است. انواع AC ,DC برای عملیات سیم پیچ در دسترس است. فروشگاه عارف الکترونیک با 4 دهه تجربه در حوزه ی الکترونیک است. همچنین تاییدیه و مجوز رسمی از اتحادیه قطعات الکترونیکی و دستگاه های صوتی و تصویری را نیز دارا می باشد. این فروشگاه به عنوان نماینده رسمی معروف ترین برند های قطعات الکترونیکی آماده ارسال محصولات به تمامی نقاط کشور می باشد. تمامی محصولات این فروشگاه اوریجنال و مناسب ترین قیمت در بازار می باشد. مشخصات فنی ولتاژ رله 24V کنتاکت رله 1C جریان رله 16A برند امرن کشور سازنده اندونزی نظرات (0) دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “رله امرن مدل G2R-1-E – 24V | 8PIN | 16A” لغو پاسخ امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. محصولات مشابه مشاهده سوکت رله ریلی 2 کنتاکت کتابی 8 پین (24_12_48_5 ولت DC) تماس بگیرید 1% مشاهده رله امرن مدل G2R-1-E – 12V | 8PIN | 16A تومان ۳۱۲,۱۸۰ قیمت اصلی: تومان۳۱۲,۱۸۰ بود. تومان ۳۰۹,۶۰۰ قیمت فعلی: تومان۳۰۹,۶۰۰. آدرس فروشگاه نشانی: تهران , خیابان جمهوری , بعد از پل حافظ , نبش پاساژ فرشته , پلاک ۶۳۴ ایمیل: info@arefelectronic.com میزبان صدای گرمتان هستیم ایام هفته : ۹:۳۰ الی ۱۸ پنج شنبه ها : ۹:۳۰ الی ۱۳:۳۰ تلفن: 52 84 70 66 (021) تلفن: 78 69 73 66 (021) همراه: 89 22 932 0902 اطلاعات عارف الکترونیک درباره ما قوانین و مقررات وبلاگ راهنما خرید فروشگاه اینترنتی عارف الکترونیک عارف الکترونیک با ۴۰ سال سابقه در زمینه صادرات و واردات قطعات الکترونیک در تمامی این سال ها به دنبال بهترین و ساده ترین روش ها برای خدمات ارزنده تر به مشتریان عزیز خود بوده است. ما به دنبال ارائه خدمات بهتر و سریع تر و فروش محصولات الکترونیکی با بهترین قیمت در بازار با تضمین اصالت کالا می باشیم. تمامی حقوق این سایت متعلق به شرکت عارف الکترونیک می باشد. | 
+طراحی سایت و سئو: امیررضا سعیدآبادی صفحه اصلی قطعات الکترونیک رله رله میلون رله بچه میلون رله کتابی رله پایه گرد ( تابلویی ) رله T شکل رله پکیجی رله خودرویی رله آمپربالا (قدرت) رله مخابراتی رله مینیاتوری رله امرن ( OMRON ) رله NHG رله PCB رله SMD رله SSR کولری رله PLC لودسل لودسل باسکولی لودسل تک پایه لودسل خمشی لودسل خمشی دو طرفه لودسل خاص لودسل فشاری ( سیلندری ) لودسل کششی لودسل bongshin لودسل زمیک ( zemic ) سوکت رله سوکت رله ریلی سوکت رله PCB (سوزنی) ای سی smd دیپ پتانسیومتر پتانسیومتر PT5 پتانسیومتر PT10 پتانسیومتر PT15 پتانسیومتر اسپانیایی پتانسیومتر چینی کارت رله ۲ کانال ۴ کانال ۸ کانال ۱۶ کانال سوئیچینگ سوئیچینگ فلزی سوئیچینگ پلاستیکی سوئیچینگ صنعتی خازن پل دیود کانکتور تجهیزات الکترونیک نمایشگر لودسل نمایشگر لودسل کاموس نمایشگر لودسل yaohua نمایشگر لودسل vista قلع ASAHI (اورجینال) طرح ASAHI ARTANIC (آرتانیک) PROSKIT RX_70 S تجهیزات شارژ و روشنایی باتری باتری قلمی (AA) باتری نیم قلمی (AAA) باتری ۱۸۶۵۰ باتری ویپ باتری قابل شارژ باتری سایز C باتری سایز D باتری کتابی (9V) باتری پاناسونیک باتری وارتا باتری ریموت کنترل باتری ساعت باتری سکه ای باتری سمعکی باتری لپ تاپ باتری لیتیوم یون باتری لیتیوم پلیمر شارژر باتری VARTA (وارتا) NITECORE (نایتکور) پاوربانک 10000mAh 15000mAh 20000mAh WIRELESS چراغ قوه حرفه ای معمولی خودکاری هندلی هدلایت باتری لپ تاپ چسب و خمیر برندها ACP ASAHI F&amp;T microchip molicell R&amp;A SCHRACK RX_70 S NITECORE VARTA panasonic OMRON bongshin yaohua camos zemic NHG راهنمای خرید از سایت ارتباط با ما وبلاگ درباره ما ورود / عضویت استفاده از موبایل ادامه رله امرن مدل G2R-1-E – 24V | 8PIN | 16A 3037 در انبار رله امرن مدل G2R-1-E – 24V | 8PIN | 16A عدد افزودن به سبد خرید</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>303408</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>esp32</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>https://www.javanelec.com/shop?searchfilter=ESP32-WROOM-32#dtl/38986</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>محصولات خانه دسته‌بندی‌ها فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه عبارت ESP32-WROOM-32 جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش برند 1666 3M Dynapro 3M Interconnect 3PEAK Incorporated 4D Systems Pty Ltd A Power microelectronics AAEON Technology Aavid Thermalloy ABC Taiwan Electronics ABLIC Inc Abracon Corporation Acam-Messelectronic Acrian, Inc Actel Corporation Active-Semi, Inc Actox Corporation. AD Semiconductor Confidential Adafruit Industries LLC Adam Technologies, Inc ADDA Corp ADDtek Corp Adesto Technologies ADMtek Inc Advanced Acoustic Technology Corp. Advanced Analog Technology Advanced Analogic Technologies Advanced Card Systems Advanced Ceramic X Corp Advanced Linear Devices Inc Advanced Monolithic Systems Advanced Photonix, Inc Advanced Power Electronics Corp Advanced Power Technology Advanced Semiconductor Advantech Corp Advantech Equipment Corporation Aegis Electronic Group AEL Crystals Limited AEM, Inc Aerosemi Technology Co Afa Technologies Inc AG Electrical Technology Agere Systems Agilent Technologies AGM Semiconductor AIC tech Inc. Aimtec Aimtron Corporation Airoha Technology Corp AIRWAVE Technologies Inc AiSHi Capacitors Aixin Opto-Electrical Technology Albright International Ltd Alcatel Microelectronics Alcor Micro Corp Alex Connector Co Ltd Alfa Electronics Algocraft Srl. ALi Corporation Alinx Electronic Technology All Sensors Corporation Allegro Microsystems Alliance Memory Allied Vision, Inc. Allwinner Technology Almita Co. Ltd Alpha &amp; Omega Semiconductor Alpha Micro Components Alpha Semiconductor Alpha Wire Alphasense Ltd, Sensor Technology Alps Electric Co Altera Corporation Amazing Electronic Co Amazing Microelectronic Corp AMD American Microsemiconductors American Microsystems Inc American Power Management American Technical Ceramics Corp American Zettler, Inc. Ametherm, Inc AMI Semiconductor AMIC Technology Corp Amidon Associates, Inc Amlogic Inc. Amotech Corp AMPAK Technology Inc Amphenol Advanced Sensors Amphenol Corporation Amphenol FCI Amphenol RF Ampleon USA Inc ams AG Anachip Corp ANADIGICS Anadigm, Inc Analog Devices Analog Integrations Corporation Analog Microelectronics Analog Power Analogix Semiconductor Inc Anaren, Inc Ancol Electronics Co Andigilog, Inc ANENG Anhui FOSAN Semiconductor Anhui Vico Technologes Co Anovay Technologies Limited ANPEC Electronics Corp Ante Intelligent Company Limited AP Memory Technology. APC Propellers APEM Inc Apex Material Technology Apex Precision Power API Delevan Inc API Technologies Aplus Integrated Circuits Inc APMKorea Apogee Technology, Inc Applent Instruments Applied Micro Circuits Co AppoTech Ltd APT Electronics Co., Ltd. Aptek Technologies ArchNet Technology Arcol UK Ltd Arduino Arduino Nicla Voice. Arima Lasers Corporation Aristotle Enterprises Inc ARTCHIP Semiconductor Artesyn Embedded Technologies AS ENERGI Asahi Kasei Microdevices ASAHI Solder Asia Vital Components Asiliant Technologies ASIX Electronics Corp AsLic Microelectronics Corporation ASMedia Technology Inc. Associated Opto-Electronics Astec Semiconductor. Astrodyne TDI Corporation. ATE Electronics s.r.l Atech Technology Co ATEN International Co Atheros Communications, Inc ATI Technologies Inc Atlas Scientific LLC. Attend Technology Inc AU Optronics Corp Audiowell Electronics Co Auk Contractors Co AUK Semiconductor AUO Corporation AUREL S.P.A Austar Technology AuthenTec, Inc Autonics Corporation Avago Technologies AVANTEK INC. AverLogic Technologies, Inc AVerMedia Technologies Avia Semiconductor Avnet, Inc AVX Corporation AXElite Technology Co Axiomtek Axis Communications AZ Displays, Inc Azoteq Ltd BAFO Technologies Corp Bahar Enclosure Baumer International BBT-China Inc BCD Semiconductor Beckhoff Automation Beijing Boshida Beijing HRH Information Co Beijing Ultrasonic Beijing Yihongtai Technology Beijing Zhongxun Sifang Science &amp; Technology Beken Corporation Bel Fuse Inc Bel Power Solutions Inc Belden Inc Bellnix Bencent Tzeng Ind. Co. Ltd Betlux Beyond Innovation Technology BI Technologies Bicker Elektronik GmbH Billionton Systems Inc Bird Technologies Bi-Sonic Technology Bivar, Inc Blackhawk BLOCK Inc Bluegiga Technologies BOLYMIN,INC BONGSHIN LOADCELL CO. Bookly Micro Electronic Bosch Security Systems Inc Bosch Semiconductors Bosch Sensortec Bothhand USA Boundary Devices Bourns Inc Bowin Microelectronics Brainboxes Limited BRIGHT LED ELECTRONICS CORP. Bright Power Semiconductor BrightKing Inc Brilliance Semiconductor, Inc Broadchip Technology Broadcom Limited BroadLight Inc Brooktree Corporation Burr-Brown Corporation BYD Microelectronics Co., Ltd. C&amp;D Technologies C&amp;K Components Caddock Electronics Inc California Eastern Laboratories California Micro Devices Calogic LLC Cambridge Integrated Circuits Cambridge Silicon Ra dio Limited Camille Bauer Ltd Catalyst Semiconductor Celduc relais CellWise Microelectronics Co Cenker Enterprise Ltd Centenary Materials Co CeNtRa Science Corp Central Components Manufacturing Central Georgia Generator Central Semiconductor CEVA Technologies CFSensor Challenge Electronics Champion Microelectronic Changzhou changjie Technology Co Changzhou Cre-sound Electronics Changzhou DRM Changzhou Esuntech Co Changzhou Kennon ELectronics Changzhou TDA Electronic Changzhou Yuanwang Fluid Technology Chaozhou Three-circle (Group) Co chargebyte GmbH. Chengdu Ebyte Electronic Technology Chengdu Guosheng Technology Chengdu Xincheng Huachuang Electronic ChenMoun Electronic ChenYang Technologies Cheuk Yui Innovation Co Chi Mei Optoelectronics Chieful Science ＆ Technology Chilisin Electronics Co China Base Electronic Technology China ECU Tools Centre China Resources Microelectronics China Software Industry Association Chinfa Electronics Chingis Technology Corp Chino-Excel Technology Chipanalog Incorporated ChipLink Tech Chiplus Semiconductor ChipON Chipower Electronics CHIPS Technology Chipstar Microelectronics CHK Electronics Ltd Chogori USA Chongqing Shengpu Electronics Chrontel, Inc Chunghwa Picture Tubes Churod Electronics Chyao Shiunn Electronic Cincon Electronics Cinetech Ind Cirrus Logic Inc Cisco Systems CIT Relay &amp; Switch Citizen Finedevice Co Cixi AnXon Electronic Cixi Dafa precise Linker Co CiXi KaiFeng Electronics Co Cixi Kefa Electronics Cixi Max Electronics Co.,Ltd Clare, Inc Cliff Electronic Components Limited Cmedia Electronics Inc CML Microsystems Coil Master Co Coil Winding Coilcraft Inc Coiltronics (Eaton) Comchip Technology Commodore Semiconductor Comtec Crystals comtech aha corporation CONEC Elektronische Bauelemente GmbH Conesys,Inc. Conexant Systems, Inc Connfly Electronic Co Connor-Winfield Conquer Electronic Continental Device India Controlair Inc Conversion Devices, Inc Cooper Bussmann Coretek Opto Corporation. Cornell Dubilier Electronics Cortina Systems, Inc Cosel Co Ltd COSINE Nanoelectronics Coto Technology CR Powtech Co Cree, Inc Crydom Inc Crystal Semiconductor Corporation Crystalfontz Crystek Corporation CSCONN PRECISE ELECTRONICS CO.,LTD CT Micro International Co CTS Corporation CUI Inc CVI Laser, LLC CW Industries Cyntec Co Cypress Semiconductor Cyrustek Corporation CYStech Electronics Corp. CYT Opto-Electronic Technology Dachang Electronics Daewoo Semiconductor Daier Electron Co Dailywell Electronics Daishinku Corp Daito Communication Apparatus Daiyo Electronics Dallas Semiconductor DANFOSS Daniels Manufacturing Co Data Device Corporation Davicom Semiconductor Davies Molding, LLC DB Lectro Inc DB Unlimited DC Components Co Dean Technology DECA SwitchLab Inc Decawave Ltd Dechang Electronic Deep Sea Electronics DEGSON Electronics Co Dell Inspiron Delta Electronics DeMint Electronics DENSO Destiny Technology Corp Detaik Technology Co Deva Electronic Controls Limited. Devantech Device Engineering Inc Dexter Magnetic Technologies DFRobot. Dialight Electronics Company Dialog Semiconductor Dielectric Laboratories Digi International Digilent, Inc Digital Voice Systems Digitrax, Inc Digitron Semiconductors Dinkle International Co. Ltd DIN-TEK Microelectronics Diodes Incorporated Diotec Semiconductor Diptronics Manufacturing Inc Display Solution AG DISPLAY VISIONS GmbH 2022. DMB Technology DOESTEK Co DOINGTER Semiconductor Domintech Co Don Connex Electronics DONG IL TECHNOLOGY LTD. Dongguan CHENGXING Electronic Co Dongguan City Wasi Electronic Technology Dongguan Cosson DongGuan HeLing Electronics Dongguan Lanbo Electronics Technology CO Dongguan Yuandi Electronics Dongguan Yuanze Electric Co.,Ltd Dongguan Yuxi Precise Connector Co., Ltd Dongke semiconductor Anhui Co., Ltd Donguan Keyouda Electronic Dosilicon Co DTK electronics Dualsky Models Co Duoxing Electronics Co Duty-Cycle Semiconductor Dynamic Technologies (DTCC) Dynex Semiconductor Ltd, E &amp; E Magnetic Products Limited EAST Semiconductor East Texas Integrated Circuits Eastrising Technology Co Eastsensor Technology Easy IoT Eaton’s Bussmann Ebm-papst inc Echelon Corporation Ecliptek Corporation ECOFIT &amp; ETRI ECS, Inc International EDAC EECO Switch E-Elements Technology Co Efficient Power Conversion Co EG Microelectronics Corp EIC Semiconductor Elan Microelectronics Co Elantec, Inc Electrolube Electronic Alliance Electronic Assembly Electronic Devices Inc Electroustic Ltd Eledis Element14 ELESTA GmbH Elite Semiconductor Memory Eljen Technology Elm Electronics ELM Technology Co Elmos Semiconductor AG ELNA Company Elpida Memory, Inc EM Microelectronic-Marin EMAD Embedded Artists Embest Technology Emerson Encitech Endress+Hauser Management ENE Technology Enplas Corporation Enrwey Co Ltd Eon Silicon Solution E-peas Semiconductors Epitex Inc Epoxy Technology Inc EPSON Electronics Ept Inc Ericsson Microelectronics ERNI Electronics ERSA UK LTD Espressif Systems ESS Technologies E-Switch, Inc ET Enterprises Limited E-T-A Circuit Breakers ETA Solutions E-tec Interconnect Ethertronics Inc Etron Technology, Inc EUCHNER GmbH Eupec semiconductor Euroquartz Ltd Eutech Microelectronics Everanalog Everest Semiconductor Everlight Electronics Everspin Technologies Exar Corporation Excel Cell Electronic Excelitas Technologies Excellence Opto, Inc Excelliance MOS Corporation Fagor Electronica Fairchild Semiconductor Fair-Rite Products Corp FANUC Corporation Faraday Technology Fastline Fastrax Ltd FASTRON Faulhaber GmbH FDK Corporation Feature Integration Technology Feei Cherng Enterprise Feeling Technology Feiyi Technology FEMA Electronics Corporation Fenghua Advanced Technology Ferroxcube International FERYSTER Sp. z.o.o Figaro Engineering Inc Finder Relays, Inc Fingerprint Cards First Semiconductor First Sensor FIS Inc Fischer Connectors Fischer Elektronik Fitipower Integrated Technology Force MOS Technology Co Formosa MS Formox Semiconductor Forsentrk Fortior Technology Co Fortune Semiconductor Forward International Electronics FOTEK Controls Fox Electronics Foxconn Technology Fractus S.A Franz Binder GmbH &amp; Co. Free2Move Holding AB. Freescale Semiconductor Fremont Micro Devices Friendcom Technology Develop FriendlyARM Computer Tech FTDI Chip Fuda Hisi Microelectronics Fuji Electric Fujikura Fujitsu Semiconductor Fujitsu-Takamisawa Fulihua Printer Ribbon Co Futaba Corporation Fu-Yao Technology Co Fuzetec Technology Co Fuzhou Rockchip Electronics Co., Ltd GainSpan Corporation GalaxyCore Inc GaNPower International Inc G-Antetech Industrial Garmin Ltd. Gas Sensing Solutions Ltd. Gaston Electronics GC GE Fanuc GEC Plessey Geehy Semiconductor Co General Electronic Devices General Monitors General Semiconductor Generalplus Technology GeneSiC Semiconductor Genesis Microchip Inc Genesys Logic, Inc Genicom Co., Ltd. Gennum Corporation GETE Electronics GigaDevice Semiconductor Global Connector Technology (GCT) Global Mixed-mode Technology GlobespanVirata, Inc GMC Instruments GME Technology, LLC GoChip Electronic Technology GoldStar Semiconductor Gonbes Technology Co Good Display Good Will Instrument Good-Ark Semiconductor Goodix Technology Governors America Co Gpixel Microelectronics Inc Grayhill Inc GreatLEDs Co Greenliant Systems GRUNER AG GSI Technology, Inc Guangdong Hottech Co Guangdong Huaguan Semiconductor Guangdong TIANQIU Electronics Technology Guangzhou Aosong Electronics Guangzhou Xinyue Electronic Guerrilla RF, Inc H&amp;M Semiconductor HABEY Halbleiter aus Frankfurt HALO Electronics Hamamatsu Photonics Hangzhou Grow Technology Co Hangzhou Nationalchip Science Hangzhou Prosper Hangzhou Silan Microelectronics Hannstar Display Corp HanRun Electronics Hanwei Electronics Co Hanyoung Nux Co HAOHAI ELECTRONICS HAOYU Electronics Harris Semiconductor HARTING Technology Harvatek Corporation Harwin Hawyang Semiconductor Hebei International Trading Co HEITEC AG. Hemingruizhi Electronic Henan Hanwei Electronics Co Hengda New Materials Technology HengJiaXing Electronics Co Henkel Corporation HenLv Power Technology Heter Electronics Hewlett-Packard Hexin Technology Highly Electric Hi-Link Electronic Technology Hi-Optel Technology Hirose Electric Hi-Sincerity Microelectronics Hitachi Maxell, Ltd Hitachi Semiconductor HITPOINT Inc Hittite Microwave Hivolt Capacitors Ltd H-JTAG Technology Hokuriku Electric Industry Co Ltd Hokuyo Automatic Co Holt Integrated Circuits Holtek Semiconductor Honeywell International Hong Kong Resistors Manufactory Hongfa Electroacoustic Co HONGHUA ELECTRONIC Hope Microelectronics HORIBA, Ltd. Hosiden Corporation Hosonic Electronic Co Hotchip Technology HTC Korea TAEJIN Technology Huada Connectors Huanor International Huaqi Microelectronics Co Huawei Technologies Huayu Technology HuaYuan Micro Electronic Huayue Microelectronics Co HUBER+SUHNER Huibei KENTO Electronic Huidu Technology Hukx Sensor Technology Humirel Hurricane Tech. Co HW group s.r.o HYCON Technology Corp. Hynix Semiconductor Hyundai Semiconductor IC Plus Corp ICE Components, Inc. iC-Haus GmbH Icom Inc ICP DAS CO ID Innovations ID TECH IDEC Corporation IEI Integration Ignion Iintelligent Motion Systems IK Semiconductor ILSI America LLC IMP, Inc Inchange Semiconductor Industrial Fiber Optics, Inc Industrial Technology Research Institute Infineon Technologies Initio Corporation INJOINIC TECHNOLOGY Innolux Corporation InnoSenT-Innovative Radar Sensor Technology Innovative Sensor Technology IST Innuovo Magnetics Co Inova Semiconductors InPlay Inc. InPower Semiconductor INTEGRAL JSC Integrated Circuit Solution Integrated Circuit Systems Integrated Crystal Technology Integrated Device Technology Integrated Sensor Technologies Integrated Silicon Solution Intel Corporation InterFET Corp Interlink Electronics International CMOS Technology International Rectifier Intersil Corporation Intronic Semiconductor Intronics Power, Inc InvenSense Inc IQD Frequency Products Ltd IRAN Ironwood Electronics IRXON Electronic Isabellenhütte Heusler GmbH &amp; Co KG Isahaya Electronics Co iSentek Technology Isocom Components Isotek Corp ITE Tech ITT Cannon, LLC ITT Semiconductors Ituner Networks Corp iWatt Inc IXYS Integrated Circuits J.S.T. Mfg. Co JACKSON ELECTRONICS IND. CROP. JAE Electronics JAI Ltd Jamicon Electronics JAVAN JCET Group Co JCI Jewel Hill Electronic Co JHDLCM Electronics Jiangsu Changjiang Electronics Jiangsu Donghai Semiconductor Jiangsu Juguang Jiangsu Runic Technology Co Jiangsu Szdhdtgd Electronics Jiangxi Jia Wei Cheng Electronic Jilin Sino-Microelectronics Co Jinan USR IOT Technology JING LI Power Electronics Jingcheng Electronics Co Jinghan Switch Electronic JMicron Technology Corp JNHuaMao Technology JODO International Johanson Dielectrics Johanson Technology Johnson Electric JPC Company JYE Tech Ltd JYH HSU(JEC) ELECTRONICS Kai Suh Suh Enterprise KSS Kaida Holding Kaihua Electronics Co Kangmu Sheng Electronics Ka-Ro electronics GmbH. KEC Semiconductor Keil Elektronik Keithley Instruments Kelly Controls, LLC KEMET Corporation Key Technology Keysight Technologies Keystone Electronic King Core Electronics Kingbor Technology Kingbright Electronic KingCCTV Technology Kingdatron Electronic Industrial Co Kingsignal Technology Kingstate Electronics Kingston KIOXIA America, Inc Kiwi Instruments Corp Knowles Electronics KOA Speer Electronics Kobiconn Kodenshi Corp Kohshin Electric Corporation KONE Elevator Kontron S&amp;T KT Micro Inc Kunshan Sino Silicon Technology KUOYUH W.L. Enterprise Co Kutai Electronics Kycon, Inc Kyocera Corporation Ladder Electronics Co Laird Performance Materials. Laird Technologies Laser Components Lattice Semiconductor LawMate International L-com, Inc LD-PD Inc. Leadtrend Technology Corp LEAP Electronic Legerity, Inc Lelon Electronics Corp LEM Components LEMO Lenovo LENZE Lesfuse Electric Co Leshan Radio Co LG Semiconductor LG.Philips Displays Lianchao Future Technology Lighting Integration System Ligitek Electronics Co Lime Microsystems Lineage Power Private Limited Linear Systems Linear Technology Linfinity Microelectronics Link-PP Int'l Technology LinkSmart LINP OMTER International Linx Technologies Lision Technology LITE-ON Semiconductor Littelfuse Inc Lixin Electromagnetic Clutch LIZE Electronic Technology LND, INC LOETRONIC LOGIC Devices Incorporated Longtech Optics Co Longview Technologies Co Lovid International Electronic Low Power Radio Solutions Ltd LOZEN TECHNOLOGY LS ELECTRIC LS Mtron Ltd LSI Computer Systems LTKCHIP LTN Servotechnik GmbH Lucent Technologies LUCKFOX Technology Lucky Light Electronic Luguang Electronic Technology Lumberg Holding Lumentum Operations LLC. Lumex Inc Lumileds Luminus, Inc. Lumissil Microsystems Luna Optoelectronics Lutron Electronic Enterprise Co Lyontek Inc M.S. Kennedy Corp M+R Multitronik GmbH MACOM Technology Macroblock, Inc Macronix International MacTek Corp MagnaChip Semiconductor Magnetics MagnTek Microelectronics Magtek Technology Inc Manorshi Electronics Marktech Optoelectronics, Inc Marlow Industries, Inc Marquardt Switches, Inc Marvell International Matsushita Electric Max Echo Technology Corp MaxBotix Inc Maxic Technology Corporation Maxim Integrated MaxLinear Inc Maxon motor Maxwell Technologies Mayloon Electronic Company MCS Logic Inc Mcuzone International MEAN WELL Enterprises Co Measurement Specialties Mechanic MediaTek Inc Megatek Melexis Technologies Memory Protection Devices MEMSIC, Inc Mentor GmbH Mercury Electronic Meritek Electronics Corporation Mersen EP Metalink Broadband Meticom GmbH. METRODYNE MICROSYSTEM CORP. MIC Electronic Micrel, Inc Micro Commercial Components Micro Crystal AG Micro Electronics Micro Linear Micro One Electronics Micro Power Systems MICRO SENSOR CO;LTD Microchip Technology Microdiode Semiconductor Micrometals, Inc Micron Technology Micronet Communication Microsemi Corporation Microtech Technology Co Ltd Microtherm Sentronic GmbH Microtips Technology Midori Precisions MikroElektronika MikroElektronika d.o.o MikroTik Mill-Max Mfg Milnec Interconnect Systems MindMotion Microelectronics Co. Mingtek Electronics Ltd Mini-Circuits Minilogic Device Corporation Ltd Minmax Technology Minsoo Electronic Co MiTAC Computing Technology Mitel Semiconductor Mitsubishi Electric Mitsubishi Rayon Co Mitsumi Electric Co Mixed Signal Integration Mixic Electronics MKMX America LLC MMI Semiconductors MOAI electronics co Mobicon Electronic Component Modulestek Inc MOKO TECHNOLOGY LTD. Molex Electronic Monitor Enterprises Inc Monolithic Power Systems Morethanall Co Morningstar Corporation MORNSUN Science &amp; Technology Mosdesign Semiconductor Corp Mosel Vitelic Co MOSPEC Semiconductor MOS-TECH Semiconductor Mostek MOTIEN Technology Motorola Mstar Semiconductor M-Systems Inc Multicomp Multi-Inno Technology Multi-Tech Systems Inc Murata Manufacturing Co MVSILICON MYIR Tech Myrra SAS Naina Semiconductor Limited. Nanjing Haichuan Electronic Nanjing Ouzhuo Tech Nanjing Qinheng Microelectronics Nanjing Shiheng Elec NanJing Top Power ASIC Nanjing Up Electronic Technology Nanjing Wotian Technology Co Nanjing Zeming Electronic Co Nanya Technology Co National Instruments National Semiconductor NDK America Inc NEC Electronics Nell Semiconductor Neltron Industrial Nemoto Sensor Engineering NeuroSky, Inc. Neutrik New Jersey Semiconductor NewAE Technology Inc. Newava Technology Inc. Newhaven Display Newport Corporation NewTec Display Co NexFlash Technologies, Inc Nexperia USA Inc Nextchip Nextion NIC Components Corp. Nichia Corporation Nichicon Corporation Nidec Copal Electronics NIDEC SERVO CORPORATION. Nihon Dempa Kogyo Nihon Inter Electronics NIKO Semiconductor Ningbo East Electronics Ningbo ForwardRelayCorporationLTD Ningbo Gosun Technology Co Ningbo Huaguan Electronics Ningbo KLS Electronic Co Ningbo MAX Electronic Technology Co., Ltd Ningbo MKX Electronic Technology Ningbo Rel Electric Co., Ltd. Ningbo Songle Relay Ningbo Tianbo Ganglian Electronics Ninigi Nippon Chemi-Con Nippon Pulse America, Inc Nisshinbo Micro Devices Inc NJR Corporation NKK Switches NMB Technologies Non-Brand Norcomp Inc Nordic Semiconductor Noritake Itron Co Novacap Novatek Microelectronics NTE Electronics NUAND LLC. Nuvoton Technology NVE Corporation Nvidia NVS Navigation Technologies NXP Semiconductors NYS Resistor O2Micro OCIC co Octavo Systems LLC Ogemray Technology Co Ohmite OKI Semiconductor Ole Wolff Electronics Inc Olimex OmniVision Technologies Omron Electronics Omten Electronics ON Semiconductor ON Semiconductor CHINA On Shore Technology On-Bright Electronics OPTEK Technology Inc OPTi Inc Opticon Inc Opto 22 Opto Diode Corp Opto Electronics Co,. LTD OPTOLAB Microsystems Orient Display Oriental Semiconductor Orion Orion Display Technology Co OSI Optoelectronics OSRAM Opto Semiconductors OTAX Corporation Other Oupiin Enterprise Co OWON Technology Inc P&amp;E Microcomputer Systems Pacific Silicon Sensor Panasonic Corporation Panavision Imaging LLC Pancon Corporation PandaBoard PANJIT International Inc Para Light Electronics P-DUKE Technology Co PEAK Electronics GmbH PEAK-System Technik Penny &amp; Giles Peregrine Semiconductor Pericom Semiconductor Corp PerkinElmer Inc Phidgets, Inc Philips Semiconductor Phison Electronics Phoenix Contact Pickering Electronics Ltd PICO Electronics Pico Technology Piher Sensors &amp; Controls SA Pingjing Semi Technology PIR Sensor Co PixArt Imaging Inc Planar Systems, Inc PLX Technology PMC-Sierra, Inc PNI Sensor Corporation POCO Magnetic Polyfet RF Devices Polytronics Technology Pomona Electronics Power Integrations Power Mate Technology Power Systems GmbH Power-Changer Electronic Co Powerex Inc PowerPlaza Powersem GmbH Powertip Technology Preci-Dip SA Precision Monolithics, Inc PREMA Semiconductor GmbH Premier Magnetics PRETEC/C-One Technology Corp. Princeton Technology Proant AB Profichip GmbH Prokit's Industries Prolific Technology Inc Promax-Johnton Semiconductor Pro-Signal ProTek Devices Pro-Wave Electronic PRT PUI Audio Pulse Electronics Qimei Optical &amp; Electric Qingdao Mefine Electronics Qingxian Zeming Langxi Electronic Devices Co Qingyuan Tesla Electronic Technology Qorvo QT Brightek (QTB) QT Optoelectronics Qualcomm Atheros, Inc Quality Semiconductor Qualtek Electronics Quarton inc Quasar Electronics Limited Quectel Wireless Solutions QuickLogic Corporation QX Micro Devices Radiall Radxa Computer Rafael Microelectronics RAFI GmbH &amp; Co RAiO TECHNOLOGY INC RAKwireless Technology Limited. RALEC Ltd Ralink Technology Raltron Electronics Corporation Ramtron International Rapid Electronics Ltd Raspberry Pi Raycom Co Raytac Corporation. Raytheon RCA Corporation Ready Made RC LLC Realtek Semiconductor RECOM Power GmbH Rectron Semiconductor Reichelt elektronik GmbH &amp; Co. KG RELPOL S.A Renata SA Renesas Technology Renhotec Group Ltd Reomax Electronics Reyed Electronics Co RF Digital Corporation. RF Micro Devices RF Solutions Ltd RFaxis, Inc RFHIC Corporation RFM Integrated Device, Inc. RFT Mikroelektronik Rhombus Industries Inc Richtek Technology Co RichWave Technology Ricoh Electronic Devices Riedon RIGOL Ring&amp;tone Electronic Technology Riverdi RLS Merilna tehnika d.o.o ROBOTIS Co Rockwell Rogers Corporation ROHM Semiconductor Roithner Lasertechnik GmbH Rongtech Industry Royal Electronic Factory Co RS Components Ltd RTD Embedded Technologies Rubycon RYCHIP Semiconductor s.m.a.e. GmbH Saft Groupe S.A Sagami Electronics Saia-Burgess Switches Sakae Tsushin Kogyo Saleae, Inc Salecom Electronics Same Sky SamHop Microelectronics Samsung Electronics Samtec Samwha Capacitor Samwin Electronic Technology Samyoung S &amp; C Co SANCO Electronics Co SanDisk Sanhe Enclosure Sanjiaozhou Electrical Technology Sanken Electric SanRex Corporation Sanyo Denki Sanyo Electric Savantic Electronic Sawnics Inc Schaffner Group Schott AG Schrack Technik GmbH Schurter Inc Sciosense B.V. SCTF Electronics Seagate Technology LLC Seaparks Machinery-Electronics Seaward Electronics SeCoS Corporation SEED International Ltd Seeed Technology SEEQ Technology Segger Microcontroller Systems Seiko Instruments Inc Seiko NPC Corporation Semiconductor Circuits, Inc SemiHow Semikron Semiment Technologies Semi-Powerex Corp. SEMITEC Corporation SemiWell Semiconductor Semtech Corporation Semtech Electronics Senba Sensing Technology Co Sendo Sensor Sensata Technologies Sensirion Sentry Manufacturing Inc SEP Electronic Corp Servotecnica SpA SERVO-TEK PRODUCTS COMPANY, INC. SG Micro Corp SGX Sensortech Shaanxi Fullstar Electronics Co Shaanxi Qunli Electric Shaanxi Reactor Microelectronics Shandong Jingdao Microelectronics Shanghai AVIC Optoelectronics Shanghai Belling Co,Ltd Shanghai Consonance Electronics Shanghai Fengxin Electronic Technology Shanghai Fudan Microelectronics Shanghai Gotop Technology Shanghai High-Flying Electronics Shanghai Houde Photo-electric Shanghai Mixinno Microelectronics Co Shanghai Natlinear Electronics Shanghai Xinlong Semiconductor Shanghai Zhichuan Electronic Tech SHARP Corporation Sheng Jay Automation Techno Shenyang Guangcheng Technology Co., Ltd Shenyang KingStar Automation ShenZhen AI-thinker CO Shenzhen AnBoShi Electronic Shenzhen Asenware Test Shenzhen Baishan Mechatronics Shenzhen Biosled Technology Shenzhen Bolutek Technology Shenzhen Chipsea Technologies ShenZhen ChipSourceTek Technology Shenzhen ExSAF Electronics Co Shenzhen Genesis-Systech ShenZhen Gerbole Shenzhen Getech Co Shenzhen GUANGSHIMEI Electronic Shenzhen Hanxia Electronics Shenzhen Haolin Electronics Shenzhen Heliwei Technology Shenzhen honglifa Electronics Co Shenzhen HongyeX Electronics Co ShenZhen HuaXinAn Electronics Co.,Ltd Shenzhen Injoinic Technology Co. Shenzhen Jin Yu Semiconductor Co ShenZhen JINCI Technology Shenzhen Jinrui Electronic Material Co Shenzhen JMRTH Co Shenzhen Kaiyuexiang Electronics Co Shenzhen LFN Technology Co Shenzhen Lodestar S.T Co Shenzhen Lumen Electronics Shenzhen Magnetic Technology Shenzhen MilkV Technology Shenzhen Milliohm Electronics Shenzhen Minewsemi Co., Ltd Shenzhen Nsiway Tech Shenzhen Ou Chuangxin Semiconductor ShenZhen Qi Dian Shi Dai Technology Shenzhen Ruichips Semiconductor Shenzhen Ruilongyuan Electronics Shenzhen Shiji Lighting Shenzhen SI Semiconductors Shenzhen SLKOR Micro Semicon Co Shenzhen Sunmoon Microelectronics Shenzhen Suosemi Tech Shenzhen TongYiFang Optoelectronic Technology CO,Ltd Shenzhen Topmay Electronic Shenzhen TPOWER Semiconductor Shenzhen Universal Micro-Electronics Shenzhen USBR Precision Hardware Electronics Shenzhen Weidy Industrial Development Co., Ltd. Shenzhen Xinbole Electronics Co. Shenzhen Xptek Technology Shenzhen Xunlong Shenzhen Yangxing Technology Co. SHENZHEN YeZhan Electronics Shenzhen Yiwei Technology Shenzhen ZVELL Electronics Shindengen Electric Shin-Etsu Chemical Co SHINYEI Technology SHOEI SIBA GmbH Sichuan huafeng enterprise group SICK, Inc. Siemens Semiconductor Group Si-En Technology SiFirst Technology SiGe Semiconductor Sigma Microelectronics Signetics Silego Technology Silergy Corp Silicon Image Silicon Integrated Systems Silicon Laboratories Silicon Microstructures, Inc. Silicon Motion, Inc Silicon Sensing Systems Limited Silicon Standard Corp Silicon Storage Technology Silicon Systems Inc Silicon Touch Technology Silvan Chip Electronics Silver Telecom Ltd SilverStone Technology SIMCom Wireless Solutions SIMTEK Electronic Components Sinda Photoelectricity Technology SINGULAR TECHNOLOGY CO., LTD. Sinomags Technologies Co Sinopower Semiconductor Sipex Corporation Sirectifier Semiconductors SiTime Corporation Sivago Semiconductor Co SIWARD Crystal Technology Siyang Microelectronics Sizto Tech Corp SKYLAB M&amp;C Technology Skyworks Solutions, Inc SL Power Electronics Corp. SMAR Smartec BV SMC Diode Solutions Co. Smiths Interconnect. SMSC Corporation Soberton Inc Softing Automotive Electronics Sola/Hevi-Duty Sola-IC Solarflex SA Soldex Solid State Scientific SOLIDIC Solitronics Engineering Limited SOL-LED Lighting Co Solomon Systech Song Chuan Song Huei Electric Sonix Technology Sony Corporation Soundwell Electronic South African Micro-Electronic Systems Spansion inc SparkFun Electronics SPEC Sensors LLC Spectra Symbol Corp. Spectrum Digital Incorporated Speed Tech Corp Spin Semiconductor Sprague Semiconductors SPX Flow Technology ST Engineering Stackpole Electronics Standex-Meder Electronics Stannol GmbH Stanson Technology StarChips Technology StarPower Semiconductor Ltd. Startek Electronic Technology STATEK CORPORATION Stäubli International AG. STCmicro Technology Co Stewart Connector STMicroelectronics Stocko Stork Solutions Ltd. Sullins Connector Solutions SUMIDA Corporation Sun Hydraulics Corporation Sun Microelectronics SunLED SUNLORD Sunltech Tech SUNMATE Electronic Sunonwealth Electric Machine Sunplus Technology Sunrise Electronics Suntan Technology Company Suntsu Electronics, Inc. SUNYUAN Technology Supertex Inc Susumu International Suzhou Innoson Technology Suzhou NOVOSENSE Microelectronics Co., Ltd Suzhou Silikron Semiconductor Corp Switchcraft Inc. Switec SYNC Power Crop SyncMOS Technologies Synoxo International System General Corp Tadiran Batteries TAG Semiconductors TA-I Technology TAIKO-NET Tai-Saw Technology Tai-Tech Advanced Electronics Taitien Electronics Taitron Components, Inc Taiwan Alpha Electronic Co Taiwan Semiconductor Taiyo Electric Co Taiyo Yuden Tak Cheong Electronics Talema Group, LLC Tamagawa seiki Co Tamron Tamura Corporation TANCAP Technology Taoglas Limited TDK Corporation (EPCOS) TDK-Lambda Corporation TDK-Micronas GmbH TE Connectivity Team Source Display tech.co,ltd. Techcode Semiconductor Techpoint Inc Techspray/Plato-EMX Enterprises Limited Techstar Electronics TechToys Company TelCom Semiconductor Telcon Ltd Telechips Inc Teledyne Technologies TELEFUNKEN Elektroakustik Telegesis Ltd Telit TEMIC Semiconductor Terawins, Inc Teridian Semiconductor TESLA Testo SE &amp; Co Texas Advanced Optoelectronic Solutions Texas Instruments THAT Corporation Thegioiic Corporation Thermonamic Electronics(Jiangxi) Corp THine Electronics, Inc Thinki Semiconductor Thinking Electronic THOMSON Inc THORLABS Thousand Hundred Industrial Thunder Precision Resistor TIANMA Titan Micro TLC Electronics TNI-U TOOL Token Electronics Industry Tokmas Semiconductor TOKO, Inc Tontek Design Technology Top-arm Topro Technology Topway Technology Torex Semiconductor Toshiba Corporation touchSEMI TOYO LED ELECTRONICS LIMITED. TOYODA TR Electronic Nordic AB. Traco Electronic AG Transcom, Inc Transko Electronics, Inc. TRENDnet, Inc Trenz Electronic Triad Magnetics Trident Microsystems Trimble Inc TRINAMIC Motion Control TRinno Technology Co Tripath Technology TriQuint Semiconductor Truly Semiconductors TRW Inc TT Electronics TTM Technologies, Inc. TXC Corporation UBIQ Semiconductor Ubiquiti Inc u-blox UCE Ultrasonic Co UDF Semiconductor Ultisensor Electronics UNI SEMICONDUCTOR LIMITED Unicorn Microelectronics Corporation Unictron Technologies Corporation. Union Semiconductor Uniroyal Electronics Industry Co Unisonic Technologies Unitra Cemi Uni-Trend Technology Co Unitrode Corporation Universal Microelectronics UPI Semiconductor Corp US Digital US Micro Products. Usha India Ltd Ushio Opto Semiconductors UTRON Technology, Inc Vacuumschmelze GmbH VADEM LTD Vango Technologies, Inc Varitronix Limited VARTA AG Vatronics Technologies Ltd VBsemi Electronics Co. Ltd V-Chip Microsystems VectorNav Vectron International Vehicles instrumentation Device Venkel Ltd VIA Technologies Vicor Corporation Vigortronix Ltd. Vincotech Vishay Visual communication company Vitesse Semiconductor Vivesea VLSI Solution Vweb Corporation W. L. Gore &amp; Associates, Inc WAGO Kontakttechnik GmbH Wakefield Thermal, Inc. Walsin Technology Corporation Walter Electronic Co WanTcom, Inc Wavecom Waveshare Electronics Wavespectrum Laser Inc Wavetronics Technologies WAYTRONIC ELECTRONIC CO.LTD WeEn Semiconductors Weidmüller Interface GmbH Weipu connector Weltrend Semiconductor WENSHING Electronics Western Digital Corporation Willas Electronic Corp WIMA Winbond E</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>5139000</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>5139000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CH49</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output.xlsx
+++ b/output.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,7 +568,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>لیون الکترونیک | XL-3216UBC خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products LED Lighting LED Color LEDs XL-3216UBC 9,900 موجودی محصول تعداد قیمت 100 9,456 ریال 500 9,141 ریال 1500 8,952 ریال 3000 8,826 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام XL-3216UBC XL-3216UBC Part Number 2221 Lion Part Download Datasheet XINGLIGHT Manufacture ال ای دی آبی پکیچ 1206 LED Blue 455-475nm 1206 25mA 75mW مشخصات ال‌ای‌دی آبی XL-3216UBC ال‌ای‌دی آبی XL-3216UBC Part Number Blue Illumination Color 120° Viewing Angle Reel Packaging SMD/SMT Mounting Style 75mW Power Rating -30C Minimum Operating Temperature 42-86mcd Luminous Intensity +85C Maximum Operating Temperature 25mA If - Forward Current 455-475nm Wavelength-Color Temperature 1206 (3216 metric) Package-Case 2.6-3.2V Vf - Forward Voltage نظرات کاربران ارسال نظر محصولات مرتبط XL-1005UYC XL-1005UWC XL-1005SURC XL-1005UBC XL-1005UGC SK6812MINI-E XL-3215UYC XL-3215UGC XL-3215SURC WS2812D-F8 × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 9,900 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
+          <t>لیون الکترونیک | XL-3216UBC خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products LED Lighting LED Color LEDs XL-3216UBC 9,900 موجودی محصول تعداد قیمت 100 9,456 ریال 500 9,141 ریال 1500 8,952 ریال 3000 8,826 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام XL-3216UBC XL-3216UBC Part Number 2221 Lion Part Download Datasheet XINGLIGHT Manufacture ال ای دی آبی پکیچ 1206 LED Blue 455-475nm 1206 25mA 75mW مشخصات ال‌ای‌دی آبی XL-3216UBC ال‌ای‌دی آبی XL-3216UBC Part Number Blue Illumination Color 120° Viewing Angle Reel Packaging 75mW Power Rating SMD/SMT Mounting Style -30C Minimum Operating Temperature 42-86mcd Luminous Intensity +85C Maximum Operating Temperature 25mA If - Forward Current 455-475nm Wavelength-Color Temperature 1206 (3216 metric) Package-Case 2.6-3.2V Vf - Forward Voltage نظرات کاربران ارسال نظر محصولات مرتبط XL-1005UYC XL-1005UWC XL-1005SURC XL-1005UBC XL-1005UGC SK6812MINI-E XL-3215UYC XL-3215UGC XL-3215SURC WS2812D-F8 × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 9,900 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>لیون الکترونیک | SMBJ16A خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products Discrete Semiconductors Diodes And Rectifiers TVS Diodes - ESD Suppressors SMBJ16A 3,069 موجودی محصول تعداد قیمت 2 128,128 ریال 25 124,467 ریال 250 121,722 ریال 1000 119,891 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام SMBJ16A SMBJ16A Part Number 2867 Lion Part Download Datasheet Littelfuse Manufacture دیود TVS یک جهته 16 ولت با بیشنه پالس جریان 23.1 آمپر با پکیج SMB TVS Diode Uni-directional 16V SMB مشخصات دیود تی‌وی‌اس SMBJ16A دیود تی‌وی‌اس SMBJ16A Part Number 1 Number of Channels -65C Minimum Operating Temperature 30kV Vesd - Voltage ESD Air Gap Reel Packaging 30kV Vesd - Voltage ESD Contact SMD/SMT Termination style Unidirectional Polarity 600W Pppm - Peak Pulse Power Dissipation +150C Maximum Operating Temperature 16V Working Voltage 26V Clamping Voltage N/A Cd - Diode Capacitance 17.8V Breakdown Voltage 23.1A Ipp - Peak Pulse Current TVS Diodes Product Type DO-214AA (SMB) Package-Case نظرات کاربران ارسال نظر محصولات مرتبط SD03C SD03 SMF26A SMBJ350CA SMBJ400CA PESD12VS1UA PESD12VL1BA D5V0P4UR6SO-7 NUF8410MNT4G SMAJ58CA × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 3,069 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
+          <t>لیون الکترونیک | SMBJ16A خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products Discrete Semiconductors Diodes And Rectifiers TVS Diodes - ESD Suppressors SMBJ16A 3,069 موجودی محصول تعداد قیمت 2 128,128 ریال 25 124,467 ریال 250 121,722 ریال 1000 119,891 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام SMBJ16A SMBJ16A Part Number 2867 Lion Part Download Datasheet Littelfuse Manufacture دیود TVS یک جهته 16 ولت با بیشنه پالس جریان 23.1 آمپر با پکیج SMB TVS Diode Uni-directional 16V SMB مشخصات دیود تی‌وی‌اس SMBJ16A دیود تی‌وی‌اس SMBJ16A Part Number 1 Number of Channels -65C Minimum Operating Temperature 30kV Vesd - Voltage ESD Air Gap SMD/SMT Termination style 30kV Vesd - Voltage ESD Contact Reel Packaging Unidirectional Polarity 600W Pppm - Peak Pulse Power Dissipation +150C Maximum Operating Temperature 16V Working Voltage 26V Clamping Voltage N/A Cd - Diode Capacitance 17.8V Breakdown Voltage 23.1A Ipp - Peak Pulse Current TVS Diodes Product Type DO-214AA (SMB) Package-Case نظرات کاربران ارسال نظر محصولات مرتبط SD03C SD03 SMF26A SMBJ350CA SMBJ400CA PESD12VS1UA PESD12VL1BA D5V0P4UR6SO-7 NUF8410MNT4G SMAJ58CA × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 3,069 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>لیون الکترونیک | XL-3216UBC خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products LED Lighting LED Color LEDs XL-3216UBC 9,900 موجودی محصول تعداد قیمت 100 9,456 ریال 500 9,141 ریال 1500 8,952 ریال 3000 8,826 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام XL-3216UBC XL-3216UBC Part Number 2221 Lion Part Download Datasheet XINGLIGHT Manufacture ال ای دی آبی پکیچ 1206 LED Blue 455-475nm 1206 25mA 75mW مشخصات ال‌ای‌دی آبی XL-3216UBC ال‌ای‌دی آبی XL-3216UBC Part Number 120° Viewing Angle Blue Illumination Color Reel Packaging SMD/SMT Mounting Style 75mW Power Rating -30C Minimum Operating Temperature 42-86mcd Luminous Intensity +85C Maximum Operating Temperature 25mA If - Forward Current 455-475nm Wavelength-Color Temperature 1206 (3216 metric) Package-Case 2.6-3.2V Vf - Forward Voltage نظرات کاربران ارسال نظر محصولات مرتبط XL-1005UYC XL-1005UWC XL-1005SURC XL-1005UBC XL-1005UGC SK6812MINI-E XL-3215UYC XL-3215UGC XL-3215SURC WS2812D-F8 × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 9,900 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
+          <t>لیون الکترونیک | XL-3216UBC خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products LED Lighting LED Color LEDs XL-3216UBC 9,900 موجودی محصول تعداد قیمت 100 9,456 ریال 500 9,141 ریال 1500 8,952 ریال 3000 8,826 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام XL-3216UBC XL-3216UBC Part Number 2221 Lion Part Download Datasheet XINGLIGHT Manufacture ال ای دی آبی پکیچ 1206 LED Blue 455-475nm 1206 25mA 75mW مشخصات ال‌ای‌دی آبی XL-3216UBC ال‌ای‌دی آبی XL-3216UBC Part Number Blue Illumination Color 120° Viewing Angle Reel Packaging 75mW Power Rating SMD/SMT Mounting Style -30C Minimum Operating Temperature 42-86mcd Luminous Intensity +85C Maximum Operating Temperature 25mA If - Forward Current 455-475nm Wavelength-Color Temperature 1206 (3216 metric) Package-Case 2.6-3.2V Vf - Forward Voltage نظرات کاربران ارسال نظر محصولات مرتبط XL-1005UYC XL-1005UWC XL-1005SURC XL-1005UBC XL-1005UGC SK6812MINI-E XL-3215UYC XL-3215UGC XL-3215SURC WS2812D-F8 × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 9,900 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2612,7 +2612,7 @@
 4N25 (اپتو ترانزیستور برای کاربردهای عمومی)
 4N35 (اپتو ترانزیستور برای ایزولاسیون و سیستم‌های صنعتی)
 توضیحات تکمیلی
-آی‌سی‌های اپتو ترانزیستور به دلیل ایزولاسیون الکتریکی که فراهم می‌کنند، در بسیاری از سیستم‌های الکترونیکی که نیاز به جداسازی ورودی و خروجی دارند، به‌ویژه در میکروکنترلرها و مدارهای حساس به نویز و تداخل، کاربرد دارند. این قطعات به‌طور گسترده در منابع تغذیه، سیستم‌های کنترل صنعتی و تجهیزات ارتباطی استفاده می‌شوند و به‌ویژه برای کاربردهایی که به ایمنی و حفاظت نیاز دارند، بسیار مفید هستند. فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش تعداد کانال 4 1 Channel 2 Channel 3 Channel 4 Channel ≥ = ≤ = جریان 14 1 mA 5 mA 10 mA 16 mA 20 mA 25 mA 30 mA 50 mA 60 mA 70 mA 80 mA 90 mA 100 mA 150 mA ≥ = ≤ = ولتاژ کلکتور-امیتر 14 6 V 20 V 30 V 32 V 35 V 40 V 55 V 60 V 70 V 80 V 90 V 100 V 300 V 350 V ≥ = ≤ = جریان کلکتور 20 0.00005 mA 0.1 mA 0.5 mA 1 mA 2 mA 2.5 mA 10 mA 13 mA 16 mA 30 mA 40 mA 44 mA 50 mA 80 mA 100 mA 125 mA 0.15 A 150 mA 200 mA 400 mA ≥ = ≤ = ولتاژ معکوس 9 0.7 V 2 V 3 V 4 V 5 V 6 V 7 V 25 V 200 V ≥ = ≤ = نوع خروجی 18 AC , Zero Cross DC DC-Output N Phototransistor NPN Photodarlington NPN Phototransistor Opto-Emulator with Analog Transistor Optoisolators Opto-Transistor Photocoupler Photodarlington Phototransistor Phototransistor Darlington Phototransistor NPN Phototransistor,Open Collector PNPN Poto SCR Transistor Transistor with Base = ولتاژ مستقیم 15 1.1 V 1.15 V 1.17 V 1.2 V 1.25 V 1.3 V 1.4 V 1.5 V 1.55 V 1.6 V 1.65 V 1.7 V 1.9 V 2 V 2.6 V ≥ = ≤ = ولتاژ جداسازی 24 3.750 Vrms 5.3 Vrms 5.300 Vrms 0.5 kVrms 500 Vrms 1.5 kVrms 2 kVrms 2.5 kVrms 2.500 kVrms 2.8 kVrms 3 kVrms 3.55 kVrms 3.75 kVrms 3.750 kVrms 4 kVrms 4.170 kVrms 5 kVrms 5.3 kVrms 5.300 kVrms 7.5 kVrms 8.2 kVrms 8.200 kVrms 11.6 kVrms 15 kVrms ≥ = ≤ = حداقل نسبت انتقال فعلی 33 10 % 12.5 % 15 % 20 % 25 % 30 % 34 % 35 % 40 % 50 % 60 % 63 % 80 % 100 % 120 % 125 % 130 % 150 % 160 % 173 % 200 % 260 % 295 % 300 % 320 % 400 % 500 % 600 % 1000 % 1200 % 1500 % 2000 % 4000 % ≥ = ≤ = نوع نصب روی برد 2 SMD Through Hole = حداقل دمای عملیاتی 7 -55 °C -50 °C -45 °C -40 °C -30 °C -25 °C -20 °C ≥ = ≤ = حداکثر دمای عملیاتی 9 80 °C +85 °C 85 °C +100 °C 100 °C +110 °C 110 °C +125 °C 125 °C ≥ = ≤ = برند 28 Alpha Micro Components Avago Technologies AZ Displays, Inc Broadcom Limited California Eastern Laboratories Cheuk Yui Innovation Co CT Micro International Co Everlight Electronics Fairchild Semiconductor Harris Semiconductor Huibei KENTO Electronic Infineon Technologies Isocom Components LITE-ON Semiconductor Matsushita Electric Motorola NEC Electronics Non-Brand ON Semiconductor Panasonic Corporation QT Optoelectronics Renesas Technology SHARP Corporation Siemens Semiconductor Group TEMIC Semiconductor Texas Instruments Toshiba Corporation Vishay = پکیج 16 DIP-12 DIP-16 DIP-4 DIP-4 HV DIP-6 DIP-8 MFSO-4 MFSO-5 SIP-9 SMD-16 Gull Wing SMD-4 Gull Wing SMD-6 Gull Wing SO-16 SO-4 SO-8 SOP-8 SSOP-4 = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز تعداد کانال جریان ولتاژ کلکتور-امیتر جریان کلکتور ولتاژ معکوس نوع خروجی ولتاژ مستقیم ولتاژ جداسازی حداقل نسبت انتقال فعلی نوع نصب روی برد حداقل دمای عملیاتی حداکثر دمای عملیاتی برند پکیج مرتب کردن مرتب سازی All Products Optoelectronics Optocouplers / Photocouplers Transistor Output Optocouplers کپی PC817 SHARP Corporation DIP-4 44,200 ریال اضافه به سبد خرید اوریجینال EL817C Everlight Electronics DIP-4 50,100 ریال اضافه به سبد خرید کپی PS2501-1 Renesas Technology DIP-4 51,400 ریال اضافه به سبد خرید اوریجینال EL817 SMD Everlight Electronics SMD-4 Gull Wing 54,500 ریال اضافه به سبد خرید اوریجینال LTV817B LITE-ON Semiconductor DIP-4 63,300 ریال اضافه به سبد خرید کپی PS2501L-1 SMD Renesas Technology SMD-4 Gull Wing 64,600 ریال اضافه به سبد خرید اوریجینال LTV817S LITE-ON Semiconductor SMD-4 Gull Wing 77,600 ریال اضافه به سبد خرید کپی TLP521-1GB Toshiba Corporation DIP-4 88,400 ریال اضافه به سبد خرید کپی TLP521LF1 Toshiba Corporation SMD-4 Gull Wing 93,300 ریال اضافه به سبد خرید اوریجینال PC817 SHARP Corporation DIP-4 95,000 ریال اضافه به سبد خرید اوریجینال CYTLP181GB OCIC co MFSO-4 121,000 ریال اضافه به سبد خرید اوریجینال LTV814S LITE-ON Semiconductor SMD-4 Gull Wing 121,000 ریال اضافه به سبد خرید اوریجینال CYTLP521-1GB OCIC co DIP-4 127,000 ریال اضافه به سبد خرید اوریجینال LTV814A LITE-ON Semiconductor DIP-4 138,000 ریال اضافه به سبد خرید اوریجینال CYTLP521-1GB-TP2 SMD Cheuk Yui Innovation Co SMD-4 Gull Wing 149,000 ریال اضافه به سبد خرید اوریجینال TLP291GB Toshiba Corporation SSOP-4 154,000 ریال اضافه به سبد خرید اوریجینال 4N25 Everlight Electronics DIP-6 188,000 ریال اضافه به سبد خرید اوریجینال TLP781GB Toshiba Corporation DIP-4 237,000 ریال اضافه به سبد خرید اوریجینال PS2501-1 Renesas Technology DIP-4 302,000 ریال اضافه به سبد خرید اوریجینال 4N35M ON Semiconductor DIP-6 353,000 ریال اضافه به سبد خرید اوریجینال TCET1108 Vishay DIP-4 371,000 ریال اضافه به سبد خرید اوریجینال 4N27M Fairchild Semiconductor DIP-6 373,000 ریال اضافه به سبد خرید اوریجینال CNY17-3M ON Semiconductor DIP-6 377,000 ریال اضافه به سبد خرید اوریجینال TLP521-2XGB Isocom Components DIP-8 417,000 ریال اضافه به سبد خرید اوریجینال 4N25M ON Semiconductor DIP-6 433,000 ریال اضافه به سبد خرید اوریجینال 4N26M Fairchild Semiconductor DIP-6 503,000 ریال اضافه به سبد خرید اوریجینال PC814XP SHARP Corporation SMD-4 Gull Wing 508,000 ریال اضافه به سبد خرید اوریجینال 4N28M Fairchild Semiconductor DIP-6 537,000 ریال اضافه به سبد خرید اوریجینال 4N33M ON Semiconductor DIP-6 583,000 ریال اضافه به سبد خرید بازسازی شده ON3184 Panasonic Corporation DIP-16 706,000 ریال اضافه به سبد خرید اوریجینال TLP521-4XGBSM Isocom Components SMD-16 Gull Wing 728,000 ریال اضافه به سبد خرید اوریجینال PS2801C-4-F3 Renesas Technology SO-16 734,000 ریال اضافه به سبد خرید بازسازی شده TLP521-4GB Toshiba Corporation DIP-16 762,000 ریال اضافه به سبد خرید اوریجینال TLP521-4XGB Isocom Components DIP-16 786,000 ریال اضافه به سبد خرید اوریجینال TLP521-1GB Toshiba Corporation DIP-4 842,000 ریال اضافه به سبد خرید اوریجینال MCT6 ON Semiconductor DIP-8 1,010,000 ریال اضافه به سبد خرید اوریجینال TLP521-4GB Toshiba Corporation DIP-16 2,725,000 ریال اضافه به سبد خرید اوریجینال PS2501L-1-F3-A Renesas Technology SMD-4 Gull Wing اضافه به سبد سفارش اوریجینال CT521-1GB CT Micro International Co DIP-4 ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال TLP785(GB-TP6,F Toshiba Corporation DIP-4 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال PC851XNNIP9F SHARP Corporation SO-4 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال TLP187 Toshiba Corporation MFSO-4 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال EL816S1(J)(TU)-V Everlight Electronics SMD-4 Gull Wing ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال TCLT1600 Vishay SO-4 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال 4N36 Fairchild Semiconductor DIP-6 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال ON3401 Panasonic Corporation DIP-6 ناموجود-تحویل 33 روزه اضافه به سبد سفارش بازسازی شده TLP521-1GB Toshiba Corporation DIP-4 ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال EL817C-V Everlight Electronics DIP-4 ناموجود-تحویل 33 روزه اضافه به سبد سفارش مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+آی‌سی‌های اپتو ترانزیستور به دلیل ایزولاسیون الکتریکی که فراهم می‌کنند، در بسیاری از سیستم‌های الکترونیکی که نیاز به جداسازی ورودی و خروجی دارند، به‌ویژه در میکروکنترلرها و مدارهای حساس به نویز و تداخل، کاربرد دارند. این قطعات به‌طور گسترده در منابع تغذیه، سیستم‌های کنترل صنعتی و تجهیزات ارتباطی استفاده می‌شوند و به‌ویژه برای کاربردهایی که به ایمنی و حفاظت نیاز دارند، بسیار مفید هستند. فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش تعداد کانال 4 1 Channel 2 Channel 3 Channel 4 Channel ≥ = ≤ = جریان 14 1 mA 5 mA 10 mA 16 mA 20 mA 25 mA 30 mA 50 mA 60 mA 70 mA 80 mA 90 mA 100 mA 150 mA ≥ = ≤ = ولتاژ کلکتور-امیتر 14 6 V 20 V 30 V 32 V 35 V 40 V 55 V 60 V 70 V 80 V 90 V 100 V 300 V 350 V ≥ = ≤ = جریان کلکتور 20 0.00005 mA 0.1 mA 0.5 mA 1 mA 2 mA 2.5 mA 10 mA 13 mA 16 mA 30 mA 40 mA 44 mA 50 mA 80 mA 100 mA 125 mA 0.15 A 150 mA 200 mA 400 mA ≥ = ≤ = ولتاژ معکوس 9 0.7 V 2 V 3 V 4 V 5 V 6 V 7 V 25 V 200 V ≥ = ≤ = نوع خروجی 18 AC , Zero Cross DC DC-Output N Phototransistor NPN Photodarlington NPN Phototransistor Opto-Emulator with Analog Transistor Optoisolators Opto-Transistor Photocoupler Photodarlington Phototransistor Phototransistor Darlington Phototransistor NPN Phototransistor,Open Collector PNPN Poto SCR Transistor Transistor with Base = ولتاژ مستقیم 15 1.1 V 1.15 V 1.17 V 1.2 V 1.25 V 1.3 V 1.4 V 1.5 V 1.55 V 1.6 V 1.65 V 1.7 V 1.9 V 2 V 2.6 V ≥ = ≤ = ولتاژ جداسازی 24 3.750 Vrms 5.3 Vrms 5.300 Vrms 0.5 kVrms 500 Vrms 1.5 kVrms 2 kVrms 2.5 kVrms 2.500 kVrms 2.8 kVrms 3 kVrms 3.55 kVrms 3.75 kVrms 3.750 kVrms 4 kVrms 4.170 kVrms 5 kVrms 5.3 kVrms 5.300 kVrms 7.5 kVrms 8.2 kVrms 8.200 kVrms 11.6 kVrms 15 kVrms ≥ = ≤ = حداقل نسبت انتقال فعلی 33 10 % 12.5 % 15 % 20 % 25 % 30 % 34 % 35 % 40 % 50 % 60 % 63 % 80 % 100 % 120 % 125 % 130 % 150 % 160 % 173 % 200 % 260 % 295 % 300 % 320 % 400 % 500 % 600 % 1000 % 1200 % 1500 % 2000 % 4000 % ≥ = ≤ = نوع نصب روی برد 2 SMD Through Hole = حداقل دمای عملیاتی 7 -55 °C -50 °C -45 °C -40 °C -30 °C -25 °C -20 °C ≥ = ≤ = حداکثر دمای عملیاتی 9 80 °C +85 °C 85 °C +100 °C 100 °C +110 °C 110 °C +125 °C 125 °C ≥ = ≤ = برند 28 Alpha Micro Components Avago Technologies AZ Displays, Inc Broadcom Limited California Eastern Laboratories Cheuk Yui Innovation Co CT Micro International Co Everlight Electronics Fairchild Semiconductor Harris Semiconductor Huibei KENTO Electronic Infineon Technologies Isocom Components LITE-ON Semiconductor Matsushita Electric Motorola NEC Electronics Non-Brand ON Semiconductor Panasonic Corporation QT Optoelectronics Renesas Technology SHARP Corporation Siemens Semiconductor Group TEMIC Semiconductor Texas Instruments Toshiba Corporation Vishay = پکیج 16 DIP-12 DIP-16 DIP-4 DIP-4 HV DIP-6 DIP-8 MFSO-4 MFSO-5 SIP-9 SMD-16 Gull Wing SMD-4 Gull Wing SMD-6 Gull Wing SO-16 SO-4 SO-8 SOP-8 SSOP-4 = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز تعداد کانال جریان ولتاژ کلکتور-امیتر جریان کلکتور ولتاژ معکوس نوع خروجی ولتاژ مستقیم ولتاژ جداسازی حداقل نسبت انتقال فعلی نوع نصب روی برد حداقل دمای عملیاتی حداکثر دمای عملیاتی برند پکیج مرتب کردن مرتب سازی All Products Optoelectronics Optocouplers / Photocouplers Transistor Output Optocouplers کپی PC817 SHARP Corporation DIP-4 44,200 ریال اضافه به سبد خرید اوریجینال EL817C Everlight Electronics DIP-4 50,100 ریال اضافه به سبد خرید کپی PS2501-1 Renesas Technology DIP-4 51,400 ریال اضافه به سبد خرید اوریجینال EL817 SMD Everlight Electronics SMD-4 Gull Wing 54,500 ریال اضافه به سبد خرید اوریجینال LTV817B LITE-ON Semiconductor DIP-4 63,300 ریال اضافه به سبد خرید کپی PS2501L-1 SMD Renesas Technology SMD-4 Gull Wing 64,600 ریال اضافه به سبد خرید اوریجینال LTV817S LITE-ON Semiconductor SMD-4 Gull Wing 77,600 ریال اضافه به سبد خرید کپی TLP521-1GB Toshiba Corporation DIP-4 88,400 ریال اضافه به سبد خرید کپی TLP521LF1 Toshiba Corporation SMD-4 Gull Wing 93,300 ریال اضافه به سبد خرید اوریجینال PC817 SHARP Corporation DIP-4 95,000 ریال اضافه به سبد خرید اوریجینال LTV814S LITE-ON Semiconductor SMD-4 Gull Wing 121,000 ریال اضافه به سبد خرید اوریجینال CYTLP181GB OCIC co MFSO-4 121,000 ریال اضافه به سبد خرید اوریجینال CYTLP521-1GB OCIC co DIP-4 127,000 ریال اضافه به سبد خرید اوریجینال LTV814A LITE-ON Semiconductor DIP-4 138,000 ریال اضافه به سبد خرید اوریجینال CYTLP521-1GB-TP2 SMD Cheuk Yui Innovation Co SMD-4 Gull Wing 149,000 ریال اضافه به سبد خرید اوریجینال TLP291GB Toshiba Corporation SSOP-4 154,000 ریال اضافه به سبد خرید اوریجینال 4N25 Everlight Electronics DIP-6 188,000 ریال اضافه به سبد خرید اوریجینال TLP781GB Toshiba Corporation DIP-4 237,000 ریال اضافه به سبد خرید اوریجینال PS2501-1 Renesas Technology DIP-4 302,000 ریال اضافه به سبد خرید اوریجینال 4N35M ON Semiconductor DIP-6 353,000 ریال اضافه به سبد خرید اوریجینال TCET1108 Vishay DIP-4 371,000 ریال اضافه به سبد خرید اوریجینال 4N27M Fairchild Semiconductor DIP-6 373,000 ریال اضافه به سبد خرید اوریجینال CNY17-3M ON Semiconductor DIP-6 377,000 ریال اضافه به سبد خرید اوریجینال TLP521-2XGB Isocom Components DIP-8 417,000 ریال اضافه به سبد خرید اوریجینال 4N25M ON Semiconductor DIP-6 433,000 ریال اضافه به سبد خرید اوریجینال 4N26M Fairchild Semiconductor DIP-6 503,000 ریال اضافه به سبد خرید اوریجینال PC814XP SHARP Corporation SMD-4 Gull Wing 508,000 ریال اضافه به سبد خرید اوریجینال 4N28M Fairchild Semiconductor DIP-6 537,000 ریال اضافه به سبد خرید اوریجینال 4N33M ON Semiconductor DIP-6 583,000 ریال اضافه به سبد خرید بازسازی شده ON3184 Panasonic Corporation DIP-16 706,000 ریال اضافه به سبد خرید اوریجینال TLP521-4XGBSM Isocom Components SMD-16 Gull Wing 728,000 ریال اضافه به سبد خرید اوریجینال PS2801C-4-F3 Renesas Technology SO-16 734,000 ریال اضافه به سبد خرید بازسازی شده TLP521-4GB Toshiba Corporation DIP-16 762,000 ریال اضافه به سبد خرید اوریجینال TLP521-4XGB Isocom Components DIP-16 786,000 ریال اضافه به سبد خرید اوریجینال TLP521-1GB Toshiba Corporation DIP-4 842,000 ریال اضافه به سبد خرید اوریجینال MCT6 ON Semiconductor DIP-8 1,010,000 ریال اضافه به سبد خرید اوریجینال TLP521-4GB Toshiba Corporation DIP-16 2,725,000 ریال اضافه به سبد خرید اوریجینال PS2501L-1-F3-A Renesas Technology SMD-4 Gull Wing اضافه به سبد سفارش اوریجینال CT521-1GB CT Micro International Co DIP-4 ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال EL816S1(J)(TU)-V Everlight Electronics SMD-4 Gull Wing ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال PC851XNNIP9F SHARP Corporation SO-4 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال TLP785(GB-TP6,F Toshiba Corporation DIP-4 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال TLP187 Toshiba Corporation MFSO-4 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال TCLT1600 Vishay SO-4 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال 4N36 Fairchild Semiconductor DIP-6 ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال ON3401 Panasonic Corporation DIP-6 ناموجود-تحویل 33 روزه اضافه به سبد سفارش بازسازی شده TLP521-1GB Toshiba Corporation DIP-4 ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال EL817C-V Everlight Electronics DIP-4 ناموجود-تحویل 33 روزه اضافه به سبد سفارش مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2757,7 +2757,7 @@
 مدل صنعتی فلزی ضدآب
 کلید فشاری LEDدار 5V
 توضیحات تکمیلی:
-کلیدهای فشاری در مدل‌های متنوعی عرضه می‌شوند و باید بر اساس نوع مصرف، ولتاژ، جریان و مکان نصب انتخاب شوند. برای میکروکنترلرها، استفاده از مقاومت پول‌داون یا آپ جهت جلوگیری از نویز توصیه می‌شود. فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش مقدار جریان 13 30 mA 50 mA 65 mA 100 mA 300 mA 0.5 A 500 mA 1 A 2 A 3 A 5 A 6 A 10 A ≥ = ≤ = مقدار ولتاژ AC 7 28 V 50 V 120 V 125 V 250 V 500 V 2.5 kV ≥ = ≤ = فرم اتصال 11 (ON)-OFF 1 Form X 1NO1NC 2: ON-ON 2P2T 3NO DPDT ON-OFF SPDT SPST SPST-NO = کارکرد 10 Industrial Switches ON-OFF Momentary Momentary or Latching OFF-(ON) Off-Mom ON-OFF Standard Switches Switch Switche Water Proof = مقدار ولتاژ DC 11 3 V 12 V 24 V 28 V 30 V 36 V 50 V 60 V 220 V 250 V 500 V ≥ = ≤ = نوع 17 Anti-Vandal Hoist Switch Metal Button Switch Metal Button Switch Waterproof With LED Light Metal Push Button Switch Push Button Switch Push Buttons Push Buttons Switch Push Switch Push-Key Switch Sealed Self-Locking Switch Standard Standard, llluminated Switch Touch Switch Touch Switch 4 Feet = نوع قرار گیری 5 PC Pin Screw Solder Solder Lug Through Hole = نوع نصب روی برد 3 Panel Mount PCB Mount Through Hole = برند 11 C&amp;K Components Daier Electron Co Eledis E-Switch, Inc Excel Cell Electronic Hanyoung Nux Co Kaihua Electronics Co NKK Switches Non-Brand Sinomags Technologies Co TE Connectivity = پکیج 1 Switch = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز مقدار جریان مقدار ولتاژ AC فرم اتصال کارکرد مقدار ولتاژ DC نوع نوع قرار گیری نوع نصب روی برد برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches Pushbutton Switches اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال PS-12F03 Non-Brand Switch 106,000 ریال اضافه به سبد خرید اوریجینال PS-22F03-2P2T Non-Brand Switch 145,000 ریال اضافه به سبد خرید اوریجینال PS-22F93 Non-Brand Switch 183,000 ریال اضافه به سبد خرید اوریجینال R13-507-B Non-Brand Switch 243,000 ریال اضافه به سبد خرید اوریجینال R13-507-R Non-Brand Switch 245,000 ریال اضافه به سبد خرید اوریجینال R13-507-W Non-Brand Switch 259,000 ریال اضافه به سبد خرید اوریجینال R13-507-Y Non-Brand Switch 291,000 ریال اضافه به سبد خرید اوریجینال R13-507-G Non-Brand Switch 291,000 ریال اضافه به سبد خرید اوریجینال TS4-3TW BLUE Non-Brand Switch 350,000 ریال اضافه به سبد خرید اوریجینال TS4-3TW RED Non-Brand Switch 350,000 ریال اضافه به سبد خرید اوریجینال TS4-3TW GRAY Non-Brand Switch 350,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF NO LIGHT SELF RESETTING 12MM Non-Brand Switch 953,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF NO LIGHT SELF-LOCKING 12MM Non-Brand Switch 1,305,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF NO LIGHT SELF-LOCKING 16MM Non-Brand Switch 2,026,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF NO LIGHT SELF RESETTING 16MM Non-Brand Switch 2,610,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF WITH LIGHT SELF-LOCKING 12MM Non-Brand Switch 2,694,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF WITH LIGHT SELF-LOCKING 16MM Non-Brand Switch 2,909,000 ریال اضافه به سبد خرید اوریجینال LP11OA1NBSRG E-Switch, Inc Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال LP11OA1NASRG E-Switch, Inc Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال PUSH BUTTON SPST RED Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال KEY DS-211 GREEN Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال TS4-3TW GREEN Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال DS-213-R Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال FL13NW5 Non-Brand Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال KAN-L5-01-A Non-Brand Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال PUSH BUTTON SWITCH (SE38) Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال 8121SHZGE C&amp;K Components Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال EPU0122PZ Excel Cell Electronic Switch ناموجود-تحویل 60 روزه اضافه به سبد سفارش اوریجینال R16-503 (RED) Daier Electron Co Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال R16-503 (YELLOW) Daier Electron Co Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال R16-503 (GREEN) Daier Electron Co Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال A16-11SJ RED Daier Electron Co Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال A16-11SJ YELLOW Daier Electron Co Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال A16-11SJ BLUE Daier Electron Co Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال A16-11SJ GREEN Daier Electron Co Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال METAL SWITCH WATERPROOF WITH LIGHT RESET 16MM Non-Brand Switch ناموجود-تحویل 35 روزه اضافه به سبد سفارش اوریجینال 5A11-SFST SE22 Eledis Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال PLC-N1NRN-BTW Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال PLC-N1NRN-ATW Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال PLC-N1NFN-BTW Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال METAL SWITCH WATERPROOF WITH LIGHT RESET 22MM Non-Brand Switch ناموجود-تحویل 35 روزه اضافه به سبد سفارش اوریجینال PBS-24-212P Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+کلیدهای فشاری در مدل‌های متنوعی عرضه می‌شوند و باید بر اساس نوع مصرف، ولتاژ، جریان و مکان نصب انتخاب شوند. برای میکروکنترلرها، استفاده از مقاومت پول‌داون یا آپ جهت جلوگیری از نویز توصیه می‌شود. فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش مقدار جریان 13 30 mA 50 mA 65 mA 100 mA 300 mA 0.5 A 500 mA 1 A 2 A 3 A 5 A 6 A 10 A ≥ = ≤ = مقدار ولتاژ AC 7 28 V 50 V 120 V 125 V 250 V 500 V 2.5 kV ≥ = ≤ = فرم اتصال 11 (ON)-OFF 1 Form X 1NO1NC 2: ON-ON 2P2T 3NO DPDT ON-OFF SPDT SPST SPST-NO = کارکرد 10 Industrial Switches ON-OFF Momentary Momentary or Latching OFF-(ON) Off-Mom ON-OFF Standard Switches Switch Switche Water Proof = مقدار ولتاژ DC 11 3 V 12 V 24 V 28 V 30 V 36 V 50 V 60 V 220 V 250 V 500 V ≥ = ≤ = نوع 17 Anti-Vandal Hoist Switch Metal Button Switch Metal Button Switch Waterproof With LED Light Metal Push Button Switch Push Button Switch Push Buttons Push Buttons Switch Push Switch Push-Key Switch Sealed Self-Locking Switch Standard Standard, llluminated Switch Touch Switch Touch Switch 4 Feet = نوع قرار گیری 5 PC Pin Screw Solder Solder Lug Through Hole = نوع نصب روی برد 3 Panel Mount PCB Mount Through Hole = برند 11 C&amp;K Components Daier Electron Co Eledis E-Switch, Inc Excel Cell Electronic Hanyoung Nux Co Kaihua Electronics Co NKK Switches Non-Brand Sinomags Technologies Co TE Connectivity = پکیج 1 Switch = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز مقدار جریان مقدار ولتاژ AC فرم اتصال کارکرد مقدار ولتاژ DC نوع نوع قرار گیری نوع نصب روی برد برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches Pushbutton Switches اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال PS-12F03 Non-Brand Switch 106,000 ریال اضافه به سبد خرید اوریجینال PS-22F03-2P2T Non-Brand Switch 145,000 ریال اضافه به سبد خرید اوریجینال PS-22F93 Non-Brand Switch 183,000 ریال اضافه به سبد خرید اوریجینال R13-507-B Non-Brand Switch 243,000 ریال اضافه به سبد خرید اوریجینال R13-507-R Non-Brand Switch 245,000 ریال اضافه به سبد خرید اوریجینال R13-507-W Non-Brand Switch 259,000 ریال اضافه به سبد خرید اوریجینال R13-507-G Non-Brand Switch 291,000 ریال اضافه به سبد خرید اوریجینال R13-507-Y Non-Brand Switch 291,000 ریال اضافه به سبد خرید اوریجینال TS4-3TW GRAY Non-Brand Switch 350,000 ریال اضافه به سبد خرید اوریجینال TS4-3TW BLUE Non-Brand Switch 350,000 ریال اضافه به سبد خرید اوریجینال TS4-3TW RED Non-Brand Switch 350,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF NO LIGHT SELF RESETTING 12MM Non-Brand Switch 953,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF NO LIGHT SELF-LOCKING 12MM Non-Brand Switch 1,305,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF NO LIGHT SELF-LOCKING 16MM Non-Brand Switch 2,026,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF NO LIGHT SELF RESETTING 16MM Non-Brand Switch 2,610,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF WITH LIGHT SELF-LOCKING 12MM Non-Brand Switch 2,694,000 ریال اضافه به سبد خرید اوریجینال METAL SWITCH WATERPROOF WITH LIGHT SELF-LOCKING 16MM Non-Brand Switch 2,909,000 ریال اضافه به سبد خرید اوریجینال LP11OA1NBSRG E-Switch, Inc Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال LP11OA1NASRG E-Switch, Inc Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال PUSH BUTTON SPST RED Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال KEY DS-211 GREEN Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال TS4-3TW GREEN Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال DS-213-R Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال FL13NW5 Non-Brand Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال KAN-L5-01-A Non-Brand Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال PUSH BUTTON SWITCH (SE38) Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال 8121SHZGE C&amp;K Components Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال EPU0122PZ Excel Cell Electronic Switch ناموجود-تحویل 60 روزه اضافه به سبد سفارش اوریجینال R16-503 (GREEN) Daier Electron Co Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال R16-503 (RED) Daier Electron Co Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال R16-503 (YELLOW) Daier Electron Co Switch ناموجود-تحویل 30 روزه اضافه به سبد سفارش اوریجینال A16-11SJ BLUE Daier Electron Co Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال A16-11SJ GREEN Daier Electron Co Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال A16-11SJ RED Daier Electron Co Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال A16-11SJ YELLOW Daier Electron Co Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال METAL SWITCH WATERPROOF WITH LIGHT RESET 16MM Non-Brand Switch ناموجود-تحویل 35 روزه اضافه به سبد سفارش اوریجینال 5A11-SFST SE22 Eledis Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال PLC-N1NRN-BTW Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال PLC-N1NRN-ATW Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال PLC-N1NFN-BTW Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش اوریجینال METAL SWITCH WATERPROOF WITH LIGHT RESET 22MM Non-Brand Switch ناموجود-تحویل 35 روزه اضافه به سبد سفارش اوریجینال PLC-N1NFN-ATW Non-Brand Switch ناموجود-تحویل 33 روزه اضافه به سبد سفارش مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
+          <t>سوئیچ و کلید خانه دسته‌بندی‌ها سوئیچ و کلید فیلترها مرتب سازی مشاهده نتایج بازگشت فیلتر 0 محصول فیلترهای فعال حذف همه جستجو در نتایج دسته‌بندی‌های نتایج محدوده قیمت از ریال تا ریال اعمال فیلتر قیمت راهنما نمایش محصولات موجود محصولات ویژه جدید خاص پایدار پرفروش نوع قرار گیری 14 Gull Wing PC Pin SMD/SMT Solder Pin Through Hole Screw Solder Solder Lug PCB Crimp Pin Quick Connect Wire Leads Axial = برند 41 Alps Electric Co APEM Inc Bosch Sensortec Bourns Inc C&amp;K Components CiXi KaiFeng Electronics Co Coto Technology CTS Corporation Daier Electron Co Diptronics Manufacturing Inc Eledis Enrwey Co Ltd E-Switch, Inc Excel Cell Electronic Grayhill Inc Hanyoung Nux Co Highly Electric Honeywell International IDEC Corporation JACKSON ELECTRONICS IND. CROP. Jinghan Switch Electronic Kaihua Electronics Co Littelfuse Inc Marquardt Switches, Inc Multicomp Nidec Copal Electronics Ninigi NKK Switches Non-Brand Omron Electronics Omten Electronics OTAX Corporation Other Panasonic Corporation Penny &amp; Giles RAFI GmbH &amp; Co Saia-Burgess Switches Salecom Electronics Sinomags Technologies Co Taiwan Alpha Electronic Co TE Connectivity = پکیج 38 Axial Axial Surface Mount Connector DIP-12 DIP-14 DIP-16 DIP-18 DIP-2 DIP-20 DIP-24 DIP-4 DIP-6 DIP-8 Module Panel Mount Radial SDIP-10 SMD-10 SMD-12 Gull Wing SMD-16 Gull Wing SMD-20 Gull Wing SMD-6 Gull Wing SMD-8 Gull Wing SO-4 SO-6 SO-8 SOP-8 SOEIAJ-10 SOEIAJ-12 SOEIAJ-16 SOEIAJ-2 SOEIAJ-20 SOEIAJ-4 SOEIAJ-6 SOEIAJ-8 Surface Mount Switch Switch Cap Through-hole = مرتب سازی افزایشی کاهشی قیمت فروش امتیاز نوع قرار گیری برند پکیج مرتب کردن مرتب سازی All Products Electromechanical Switches اوریجینال A56 6*6 WHITE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GRAY Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 RED Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 YELLOW Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A56 6*6 GREEN Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 BLUE Non-Brand Switch Cap 10,900 ریال اضافه به سبد خرید اوریجینال A24 12*12 RED Non-Brand Switch Cap 11,000 ریال اضافه به سبد خرید اوریجینال A29-6 R Non-Brand Switch Cap 11,400 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD Non-Brand Switch 12,700 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P BLACK Non-Brand Switch 14,000 ریال اضافه به سبد خرید اوریجینال KFC-6X6X7-4P Non-Brand Switch 15,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-4P Non-Brand Switch 15,400 ریال اضافه به سبد خرید اوریجینال SS-12D00G3 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال SS-12F15G5 Non-Brand Switch 18,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD Non-Brand Switch 18,800 ریال اضافه به سبد خرید اوریجینال KFC-6*6*5-2P Non-Brand Switch 19,400 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P Non-Brand Switch 19,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P Non-Brand Switch 20,800 ریال اضافه به سبد خرید اوریجینال TSUY-3SL Non-Brand Switch 21,100 ریال اضافه به سبد خرید اوریجینال KFC-3*6*5-2P SMD REEL Non-Brand Switch ناموجود-تحویل 31 روزه اضافه به سبد سفارش اوریجینال KFC-6*6*11.5-4P Non-Brand Switch 21,700 ریال اضافه به سبد خرید اوریجینال SS12D07 Non-Brand Switch 24,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-2P Non-Brand Switch 25,100 ریال اضافه به سبد خرید اوریجینال KFC-6*6*13.5-4P Non-Brand Switch 25,500 ریال اضافه به سبد خرید اوریجینال KFC-6*6*4.5-4P SMD REEL Non-Brand Switch 25,700 ریال اضافه به سبد خرید اوریجینال KFC-6*6*15-4P Non-Brand Switch 26,000 ریال اضافه به سبد خرید اوریجینال KFC-6*6*19-4P Non-Brand Switch 31,200 ریال اضافه به سبد خرید اوریجینال KFC-6*6*9.5-4P RA Non-Brand Switch 32,400 ریال اضافه به سبد خرید اوریجینال KFC-12*12*4.5 Non-Brand Switch 48,700 ریال اضافه به سبد خرید اوریجینال KFC-12*12*5 Non-Brand Switch 51,200 ریال اضافه به سبد خرید اوریجینال SS-12F23 Non-Brand Switch 51,700 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-7*7 Non-Brand Switch 52,600 ریال اضافه به سبد خرید اوریجینال SS-12F44 Non-Brand Switch 53,300 ریال اضافه به سبد خرید اوریجینال KFC-12*12*8.5 Non-Brand Switch 59,600 ریال اضافه به سبد خرید اوریجینال MS12D16-1P2T Non-Brand Switch 60,800 ریال اضافه به سبد خرید اوریجینال MS22D16-2P2T Non-Brand Switch 61,000 ریال اضافه به سبد خرید اوریجینال B3F-4055 Non-Brand Switch 61,300 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-1 SILVER POINT Non-Brand Switch 62,100 ریال اضافه به سبد خرید اوریجینال MICRO SWITCH KW10-2 SILVER POINT Non-Brand Switch 64,500 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-8.5*8.5 Non-Brand Switch 64,800 ریال اضافه به سبد خرید اوریجینال KFC-12*12*13 Non-Brand Switch 65,500 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-5.8*5.8 Non-Brand Switch 66,800 ریال اضافه به سبد خرید اوریجینال SELF-NON LOCKING KFC-7*7 Non-Brand Switch 67,000 ریال اضافه به سبد خرید اوریجینال KFC-12*12*15 Non-Brand Switch 67,500 ریال اضافه به سبد خرید اوریجینال PS-22F03-00 Non-Brand Switch 68,000 ریال اضافه به سبد خرید اوریجینال SELF-LOCKING KFC-8.5*8.5 Non-Brand Switch 68,300 ریال اضافه به سبد خرید اوریجینال MK22D10-2P2T Non-Brand Switch 70,600 ریال اضافه به سبد خرید اوریجینال KFC-12*12*18 Non-Brand Switch 72,400 ریال اضافه به سبد خرید مشاهده نتایج بیشتر … دسته‌بندی محصولات EN/فا در حال بارگذاری</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>رله امرن مدل G2R-1-E – 24V | 8PIN | 16A - فروشگاه عارف الکترونیک Skip to content جستجو برای: سبد خرید سبد خرید شما خالی است. بازگشت به فروشگاه ورود / عضویت سبد خرید سبد خرید شما خالی است. بازگشت به فروشگاه صفحه اصلی قطعات الکترونیک رله میلون بچه میلون پکیجی SSR SMD قدرت (آمپربالا) خودرویی مینیاتوری پایه گرد (تابلویی) T شکل مخابراتی کتابی PCB کولری رله PLC روسی لودسل تک پایه خمشی خمشی دو طرفه فشاری (سیلندری) کششی باسکولی خاص سوکت رله ریلی PCB (سوزنی) ای سی smd دیپ پتانسیومتر PT5 PT10 PT15 اسپانیایی چینی کارت رله ۲ کانال ۴ کانال ۸ کانال ۱۶ کانال سوئیچینگ فلزی پلاستیکی صنعتی خازن پل دیود کانکتور Micro-D J30J انواع سیم تجهیزات الکترونیک نمایشگر لودسل کاموس yaohua vista قلع ASAHI (اورجینال) طرح ASAHI RX_70 S ARTANIC (آرتانیک) PROSKIT تجهیزات شارژ و روشنایی باتری قلمی (AA) نیم قلمی (AAA) باتری 18650 باتری ویپ قابل شارژ کتابی (9V) سکه ای سایز C سایز D باتری سیلد اسید تلفن بی سیم لیتیوم ایون لیتیوم پلیمر سمعکی ساعت ریموت کنترل شارژر باتری VARTA (وارتا) NITECORE (نایتکور) پاوربانک 10000mAh 15000mAh 20000mAh WIRELESS چراغ قوه حرفه ای معمولی خودکاری هندلی هدلایت باتری لپ تاپ چسب و خمیر برندها zemic bongshin varta NHG OMRON panasonic RX_70 NITECORE Yaohua ASAHI ACP F&amp;T microchip molicell R&amp;A SCHRACK S CAMOS راهنما خرید وبلاگ ارتباط با ما جستجو برای: 1% خانه / رله / رله امرن ( OMRON ) رله امرن مدل G2R-1-E – 24V | 8PIN | 16A تومان ۳۱۲,۱۸۰ قیمت اصلی: تومان۳۱۲,۱۸۰ بود. تومان ۳۰۹,۶۰۰ قیمت فعلی: تومان۳۰۹,۶۰۰. رله امرن G2R-1-E دارای 24 ولت و جریان 16 آمپر و 1 کنتاکت و 8 پین می باشد. این رله محصول کشور اندونزی می باشد. تخفیف در تعداد خرید تعداد 50 - 100 101 - 500 501 - 1000 قیمت تومان ۳۰۳,۴۰۸ تومان ۳۰۰,۳۱۲ تومان ۲۹۷,۲۱۶ 3037 در انبار رله امرن مدل G2R-1-E – 24V | 8PIN | 16A عدد افزودن به سبد خرید جهت خرید محصولات به صورت عمده با شماره تلفن های فروشگاه تماس و یا در واتساپ پیام دهید. مقایسه دسته: رله , رله امرن ( OMRON ) , رله کتابی برچسب: 24 ولت دسته‌ بندی محصولات لودسل (92) لودسل زمیک ( zemic ) (68) لودسل bongshin (21) لودسل تک پایه (36) لودسل خمشی (14) لودسل فشاری ( سیلندری ) (14) لودسل کششی (29) پاوربانک (6) 10000mAh (2) 15000mAh (2) 20000mAh (2) WIRELESS (3) SCHRACK (8) کانکتور (60) پتانسیومتر (26) پتانسیومتر PT10 (10) پتانسیومتر PT15 (16) پتانسیومتر اسپانیایی (13) پتانسیومتر چینی (9) R&amp;A (11) Micro-D (14) سوئیچینگ (4) سوئیچینگ فلزی (3) سوئیچینگ پلاستیکی (1) کارت رله (7) ۸ کانال (3) ۱۶ کانال (1) ۴ کانال (3) molicell (1) J30J (14) کولری (13) ASAHI (3) آداپتور (4) رله (336) رله روسی (5) رله آمپربالا (قدرت) (62) رله مینیاتوری (7) رله خودرویی (18) رله پایه گرد ( تابلویی ) (9) پاور (50) رله PCB (8) رله بچه میلون (3) رله T شکل (10) رله امرن ( OMRON ) (139) رله PLC (7) رله مخابراتی (23) رله پکیجی (31) رله کتابی (43) رله SSR (8) رله NHG (43) رله میلون (16) ACP (8) سوکت رله (23) سوکت رله ریلی (12) سوکت رله سوزنی (13) پل دیود (1) F&amp;T (2) باتری (208) باتری قلمی (26) باتری دزدگیر (2) باتری سیلد اسید (6) باتری نیم قلمی (26) باتری لیتیوم پلیمر (3) باتری شیر چشمی (1) باتری کتابی (14) باتری پک شده (1) باتری سایز C (6) باتری ریموت کنترل (8) باتری سایز D (8) باتری لیتیوم (30) باتری ساعت (8) باتری وارتا (80) باتری شارژی (23) باتری سکه ای (23) باتری پاناسونیک (26) باتری تلفن بی سیم (12) باتری ۱۸۶۵۰ (13) باتری لپ تاپ (16) باتری ویپ (12) باتری لیتیوم یون (13) باتری سمعکی (5) شارژر باتری (17) VARTA (وارتا) (3) NITECORE (نایتکور) (9) خازن (2) BLAUPUNKT (3) قلع (8) ASAHI (اورجینال) (2) طرح ASAHI (1) RX_70 (1) S (1) ARTANIC (آرتانیک) (1) PROSKIT (1) نمایشگر لودسل (16) نمایشگر لودسل کاموس (5) نمایشگر لودسل yaohua (2) نمایشگر لودسل vista (2) چراغ قوه (11) هندلی (1) حرفه ای (6) معمولی (1) خودکاری (1) ای سی (5) اتمگا (2) دیپ (1) smd (1) شارژر لپ تاپ (7) هدلایت (4) چسب و خمیر (5) توضیحات رله های همه منظوره از تک قطب 10A و دو قطب 5A  می باشد. قدرت دی الکتریک از 5000V بین سیم پیچ ها  و اتصالات و افزایش مقاومت 10000V طراحی شده است. انواع AC ,DC برای عملیات سیم پیچ در دسترس است. فروشگاه عارف الکترونیک با 4 دهه تجربه در حوزه ی الکترونیک است. همچنین تاییدیه و مجوز رسمی از اتحادیه قطعات الکترونیکی و دستگاه های صوتی و تصویری را نیز دارا می باشد. این فروشگاه به عنوان نماینده رسمی معروف ترین برند های قطعات الکترونیکی آماده ارسال محصولات به تمامی نقاط کشور می باشد. تمامی محصولات این فروشگاه اوریجنال و مناسب ترین قیمت در بازار می باشد. مشخصات فنی ولتاژ رله 24V کنتاکت رله 1C جریان رله 16A برند امرن کشور سازنده اندونزی نظرات (0) دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “رله امرن مدل G2R-1-E – 24V | 8PIN | 16A” لغو پاسخ امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. محصولات مشابه مشاهده سوکت رله ریلی 2 کنتاکت کتابی 8 پین (24_12_48_5 ولت DC) تماس بگیرید 1% مشاهده رله امرن مدل G2R-1-E – 12V | 8PIN | 16A تومان ۳۱۲,۱۸۰ قیمت اصلی: تومان۳۱۲,۱۸۰ بود. تومان ۳۰۹,۶۰۰ قیمت فعلی: تومان۳۰۹,۶۰۰. آدرس فروشگاه نشانی: تهران , خیابان جمهوری , بعد از پل حافظ , نبش پاساژ فرشته , پلاک ۶۳۴ ایمیل: info@arefelectronic.com میزبان صدای گرمتان هستیم ایام هفته : ۹:۳۰ الی ۱۸ پنج شنبه ها : ۹:۳۰ الی ۱۳:۳۰ تلفن: 52 84 70 66 (021) تلفن: 78 69 73 66 (021) همراه: 89 22 932 0902 اطلاعات عارف الکترونیک درباره ما قوانین و مقررات وبلاگ راهنما خرید فروشگاه اینترنتی عارف الکترونیک عارف الکترونیک با ۴۰ سال سابقه در زمینه صادرات و واردات قطعات الکترونیک در تمامی این سال ها به دنبال بهترین و ساده ترین روش ها برای خدمات ارزنده تر به مشتریان عزیز خود بوده است. ما به دنبال ارائه خدمات بهتر و سریع تر و فروش محصولات الکترونیکی با بهترین قیمت در بازار با تضمین اصالت کالا می باشیم. تمامی حقوق این سایت متعلق به شرکت عارف الکترونیک می باشد. | 
+          <t>رله امرن مدل G2R-1-E – 24V | 8PIN | 16A - فروشگاه عارف الکترونیک Skip to content جستجو برای: سبد خرید سبد خرید شما خالی است. بازگشت به فروشگاه ورود / عضویت سبد خرید سبد خرید شما خالی است. بازگشت به فروشگاه صفحه اصلی قطعات الکترونیک رله میلون بچه میلون پکیجی SSR SMD قدرت (آمپربالا) خودرویی مینیاتوری پایه گرد (تابلویی) T شکل مخابراتی کتابی PCB کولری رله PLC روسی لودسل تک پایه خمشی خمشی دو طرفه فشاری (سیلندری) کششی باسکولی خاص سوکت رله ریلی PCB (سوزنی) ای سی smd دیپ پتانسیومتر PT5 PT10 PT15 اسپانیایی چینی کارت رله ۲ کانال ۴ کانال ۸ کانال ۱۶ کانال سوئیچینگ فلزی پلاستیکی صنعتی خازن پل دیود کانکتور Micro-D J30J انواع سیم تجهیزات الکترونیک نمایشگر لودسل کاموس yaohua vista قلع ASAHI (اورجینال) طرح ASAHI RX_70 S ARTANIC (آرتانیک) PROSKIT تجهیزات شارژ و روشنایی باتری قلمی (AA) نیم قلمی (AAA) باتری 18650 باتری ویپ قابل شارژ کتابی (9V) سکه ای سایز C سایز D باتری سیلد اسید تلفن بی سیم لیتیوم ایون لیتیوم پلیمر سمعکی ساعت ریموت کنترل شارژر باتری VARTA (وارتا) NITECORE (نایتکور) پاوربانک 10000mAh 15000mAh 20000mAh WIRELESS چراغ قوه حرفه ای معمولی خودکاری هندلی هدلایت باتری لپ تاپ چسب و خمیر برندها zemic bongshin varta NHG OMRON panasonic RX_70 NITECORE Yaohua ASAHI ACP F&amp;T microchip molicell R&amp;A SCHRACK S CAMOS راهنما خرید وبلاگ ارتباط با ما جستجو برای: 1% خانه / رله / رله امرن ( OMRON ) رله امرن مدل G2R-1-E – 24V | 8PIN | 16A تومان ۳۱۲,۱۸۰ قیمت اصلی: تومان۳۱۲,۱۸۰ بود. تومان ۳۰۹,۶۰۰ قیمت فعلی: تومان۳۰۹,۶۰۰. رله امرن G2R-1-E دارای 24 ولت و جریان 16 آمپر و 1 کنتاکت و 8 پین می باشد. این رله محصول کشور اندونزی می باشد. تخفیف در تعداد خرید تعداد 50 - 100 101 - 500 501 - 1000 قیمت تومان ۳۰۳,۴۰۸ تومان ۳۰۰,۳۱۲ تومان ۲۹۷,۲۱۶ 3037 در انبار رله امرن مدل G2R-1-E – 24V | 8PIN | 16A عدد افزودن به سبد خرید جهت خرید محصولات به صورت عمده با شماره تلفن های فروشگاه تماس و یا در واتساپ پیام دهید. مقایسه دسته: رله , رله امرن ( OMRON ) , رله کتابی برچسب: 24 ولت دسته‌ بندی محصولات لودسل (92) لودسل زمیک ( zemic ) (68) لودسل bongshin (21) لودسل تک پایه (36) لودسل خمشی (14) لودسل فشاری ( سیلندری ) (14) لودسل کششی (29) پاوربانک (6) 10000mAh (2) 15000mAh (2) 20000mAh (2) WIRELESS (3) SCHRACK (8) کانکتور (60) پتانسیومتر (26) پتانسیومتر PT10 (10) پتانسیومتر PT15 (16) پتانسیومتر اسپانیایی (13) پتانسیومتر چینی (9) R&amp;A (11) Micro-D (14) سوئیچینگ (4) سوئیچینگ پلاستیکی (1) سوئیچینگ فلزی (3) کارت رله (7) ۱۶ کانال (1) ۴ کانال (3) ۸ کانال (3) molicell (1) J30J (14) کولری (13) ASAHI (3) آداپتور (4) رله (336) رله روسی (5) رله آمپربالا (قدرت) (62) رله مینیاتوری (7) رله خودرویی (18) رله پایه گرد ( تابلویی ) (9) پاور (50) رله PCB (8) رله بچه میلون (3) رله T شکل (10) رله امرن ( OMRON ) (139) رله PLC (7) رله مخابراتی (23) رله پکیجی (31) رله کتابی (43) رله SSR (8) رله NHG (43) رله میلون (16) ACP (8) سوکت رله (23) سوکت رله ریلی (12) سوکت رله سوزنی (13) پل دیود (1) F&amp;T (2) باتری (208) باتری نیم قلمی (26) باتری لیتیوم پلیمر (3) باتری شیر چشمی (1) باتری کتابی (14) باتری پک شده (1) باتری سایز C (6) باتری ریموت کنترل (8) باتری سایز D (8) باتری لیتیوم (30) باتری ساعت (8) باتری وارتا (80) باتری شارژی (23) باتری سکه ای (23) باتری پاناسونیک (26) باتری تلفن بی سیم (12) باتری ۱۸۶۵۰ (13) باتری لپ تاپ (16) باتری ویپ (12) باتری لیتیوم یون (13) باتری سمعکی (5) باتری قلمی (26) باتری دزدگیر (2) باتری سیلد اسید (6) شارژر باتری (17) VARTA (وارتا) (3) NITECORE (نایتکور) (9) خازن (2) BLAUPUNKT (3) قلع (8) ASAHI (اورجینال) (2) طرح ASAHI (1) RX_70 (1) S (1) ARTANIC (آرتانیک) (1) PROSKIT (1) نمایشگر لودسل (16) نمایشگر لودسل کاموس (5) نمایشگر لودسل yaohua (2) نمایشگر لودسل vista (2) چراغ قوه (11) حرفه ای (6) معمولی (1) خودکاری (1) هندلی (1) ای سی (5) اتمگا (2) دیپ (1) smd (1) شارژر لپ تاپ (7) هدلایت (4) چسب و خمیر (5) توضیحات رله های همه منظوره از تک قطب 10A و دو قطب 5A  می باشد. قدرت دی الکتریک از 5000V بین سیم پیچ ها  و اتصالات و افزایش مقاومت 10000V طراحی شده است. انواع AC ,DC برای عملیات سیم پیچ در دسترس است. فروشگاه عارف الکترونیک با 4 دهه تجربه در حوزه ی الکترونیک است. همچنین تاییدیه و مجوز رسمی از اتحادیه قطعات الکترونیکی و دستگاه های صوتی و تصویری را نیز دارا می باشد. این فروشگاه به عنوان نماینده رسمی معروف ترین برند های قطعات الکترونیکی آماده ارسال محصولات به تمامی نقاط کشور می باشد. تمامی محصولات این فروشگاه اوریجنال و مناسب ترین قیمت در بازار می باشد. مشخصات فنی ولتاژ رله 24V کنتاکت رله 1C جریان رله 16A برند امرن کشور سازنده اندونزی نظرات (0) دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “رله امرن مدل G2R-1-E – 24V | 8PIN | 16A” لغو پاسخ امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. محصولات مشابه مشاهده سوکت رله ریلی 2 کنتاکت کتابی 8 پین (24_12_48_5 ولت DC) تماس بگیرید 1% مشاهده رله امرن مدل G2R-1-E – 12V | 8PIN | 16A تومان ۳۱۲,۱۸۰ قیمت اصلی: تومان۳۱۲,۱۸۰ بود. تومان ۳۰۹,۶۰۰ قیمت فعلی: تومان۳۰۹,۶۰۰. آدرس فروشگاه نشانی: تهران , خیابان جمهوری , بعد از پل حافظ , نبش پاساژ فرشته , پلاک ۶۳۴ ایمیل: info@arefelectronic.com میزبان صدای گرمتان هستیم ایام هفته : ۹:۳۰ الی ۱۸ پنج شنبه ها : ۹:۳۰ الی ۱۳:۳۰ تلفن: 52 84 70 66 (021) تلفن: 78 69 73 66 (021) همراه: 89 22 932 0902 اطلاعات عارف الکترونیک درباره ما قوانین و مقررات وبلاگ راهنما خرید فروشگاه اینترنتی عارف الکترونیک عارف الکترونیک با ۴۰ سال سابقه در زمینه صادرات و واردات قطعات الکترونیک در تمامی این سال ها به دنبال بهترین و ساده ترین روش ها برای خدمات ارزنده تر به مشتریان عزیز خود بوده است. ما به دنبال ارائه خدمات بهتر و سریع تر و فروش محصولات الکترونیکی با بهترین قیمت در بازار با تضمین اصالت کالا می باشیم. تمامی حقوق این سایت متعلق به شرکت عارف الکترونیک می باشد. | 
 طراحی سایت و سئو: امیررضا سعیدآبادی صفحه اصلی قطعات الکترونیک رله رله میلون رله بچه میلون رله کتابی رله پایه گرد ( تابلویی ) رله T شکل رله پکیجی رله خودرویی رله آمپربالا (قدرت) رله مخابراتی رله مینیاتوری رله امرن ( OMRON ) رله NHG رله PCB رله SMD رله SSR کولری رله PLC لودسل لودسل باسکولی لودسل تک پایه لودسل خمشی لودسل خمشی دو طرفه لودسل خاص لودسل فشاری ( سیلندری ) لودسل کششی لودسل bongshin لودسل زمیک ( zemic ) سوکت رله سوکت رله ریلی سوکت رله PCB (سوزنی) ای سی smd دیپ پتانسیومتر پتانسیومتر PT5 پتانسیومتر PT10 پتانسیومتر PT15 پتانسیومتر اسپانیایی پتانسیومتر چینی کارت رله ۲ کانال ۴ کانال ۸ کانال ۱۶ کانال سوئیچینگ سوئیچینگ فلزی سوئیچینگ پلاستیکی سوئیچینگ صنعتی خازن پل دیود کانکتور تجهیزات الکترونیک نمایشگر لودسل نمایشگر لودسل کاموس نمایشگر لودسل yaohua نمایشگر لودسل vista قلع ASAHI (اورجینال) طرح ASAHI ARTANIC (آرتانیک) PROSKIT RX_70 S تجهیزات شارژ و روشنایی باتری باتری قلمی (AA) باتری نیم قلمی (AAA) باتری ۱۸۶۵۰ باتری ویپ باتری قابل شارژ باتری سایز C باتری سایز D باتری کتابی (9V) باتری پاناسونیک باتری وارتا باتری ریموت کنترل باتری ساعت باتری سکه ای باتری سمعکی باتری لپ تاپ باتری لیتیوم یون باتری لیتیوم پلیمر شارژر باتری VARTA (وارتا) NITECORE (نایتکور) پاوربانک 10000mAh 15000mAh 20000mAh WIRELESS چراغ قوه حرفه ای معمولی خودکاری هندلی هدلایت باتری لپ تاپ چسب و خمیر برندها ACP ASAHI F&amp;T microchip molicell R&amp;A SCHRACK RX_70 S NITECORE VARTA panasonic OMRON bongshin yaohua camos zemic NHG راهنمای خرید از سایت ارتباط با ما وبلاگ درباره ما ورود / عضویت استفاده از موبایل ادامه رله امرن مدل G2R-1-E – 24V | 8PIN | 16A 3037 در انبار رله امرن مدل G2R-1-E – 24V | 8PIN | 16A عدد افزودن به سبد خرید</t>
         </is>
       </c>
@@ -2950,6 +2950,16 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>13937078</v>
       </c>
     </row>
   </sheetData>

--- a/output.xlsx
+++ b/output.xlsx
@@ -138,10 +138,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -149,11 +150,11 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -585,10 +586,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>4610</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>13830</v>
       </c>
     </row>
@@ -599,14 +600,14 @@
       <c r="B3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>https://lionelectronic.ir/products/2221-XL-3216UBC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>لیون الکترونیک | XL-3216UBC خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products LED Lighting LED Color LEDs XL-3216UBC 9,900 موجودی محصول تعداد قیمت 100 9,456 ریال 500 9,141 ریال 1500 8,952 ریال 3000 8,826 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام XL-3216UBC XL-3216UBC Part Number 2221 Lion Part Download Datasheet XINGLIGHT Manufacture ال ای دی آبی پکیچ 1206 LED Blue 455-475nm 1206 25mA 75mW مشخصات ال‌ای‌دی آبی XL-3216UBC ال‌ای‌دی آبی XL-3216UBC Part Number Blue Illumination Color 120° Viewing Angle Reel Packaging 75mW Power Rating SMD/SMT Mounting Style -30C Minimum Operating Temperature 42-86mcd Luminous Intensity +85C Maximum Operating Temperature 25mA If - Forward Current 455-475nm Wavelength-Color Temperature 1206 (3216 metric) Package-Case 2.6-3.2V Vf - Forward Voltage نظرات کاربران ارسال نظر محصولات مرتبط XL-1005UYC XL-1005UWC XL-1005SURC XL-1005UBC XL-1005UGC SK6812MINI-E XL-3215UYC XL-3215UGC XL-3215SURC WS2812D-F8 × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 9,900 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
+          <t>لیون الکترونیک | XL-3216UBC خانه محصولات 0 سبد خرید 0 واردات حساب کاربری ✕ Categories Passive Component تمام محصولات Passive Component RF Components Antenna RF Cable Other RF Component Buzzers Buzzer Capacitors Aluminum Electrolytic Capacitors - Leaded Feed Through Capacitors Film Capacitor SMD Aluminum Electrolytic Capacitors SMD Ceramic Capacitors SMD Tantalum Capacitors Safety Capacitors Super Capacitors Other Type Capacitors Ferrites Ferrite Beads Ferrite Cores Frequency Control Crystals Oscillators Resonators Inductors, Chokes And Coils Fixed Inductors Common Mode Chokes/Filters Transformers Signal transformers Current Transformers Resistors SMD Resistors Precision Resistors Current Sense Resistors Resistor Networks And Array Multi Turn Trimmer Resistors Potentiometers Integrated Circuits - ICs تمام محصولات Integrated Circuits - ICs Audio ICs Microphone Preamplifiers Audio Amplifiers Amplifier ICs Analog Comparators Current Sense Amplifiers Differential Amplifiers Instrumentation Amplifiers Isolation Amplifiers Operational Amplifiers - OPAMP Data Converter ICs ADC Digital Potentiometer IC DAC Analog Front End - AFE Energy Metering ICs Touch Screen Controllers Interface ICs 4-20mA Transmitter IO Expander Audio Interface ICs CAN Interface IC Digital Isolators Ethernet Interface IC RS-485 RS-232 Sensor Interface IC Telecom Interface IC USB Interface IC Other  Interface ICs Logic ICs Supervisory Logic IC Switch ICs Analog Switch Bus Switch Wireless And RF IC NFC/RFID Tag And Transponder RF Detector RF Amplifier Phase Locked Loops - PLL RF Transceiver RF System on a Chip - SoC Other ICs Real Time Clock IC Other IC Power Management تمام محصولات Power Management AC/DC Converters Adaptors/Power Supplies Offline Switcher PWM Controller Power Factor Correction Batteries Coin Cell Battery Battery DC/DC Converters Isolated DC/DC Converters Battery Management تمام محصولات Drivers Gate Drivers Seven-Segment Drivers LED Array Drivers Isolated Gate Drivers LED Lighting Drivers Motor Drivers Power Switches تمام محصولات Smart Switches تمام محصولات Specialised - PMIC تمام محصولات Synchronous Rectifiers تمام محصولات Reference تمام محصولات Regulators Linear Voltage Regulators Charge Pump Converters LDO Voltage Regulators Switching Regulators Switching Controllers Memories تمام محصولات Memories Memory Cards SD Card Memory IC DRAM EEPROM F-RAM NAND Flash NOR Flash PSRAM SRAM Processors And Controllers تمام محصولات Processors And Controllers Computing تمام محصولات Programmable Logic ICs CPLD FPGA MCU AVR ARM STM8 PIC RF Microcontrollers - MCU Systems on a Chip - SoC Other MCU Discrete Semiconductors تمام محصولات Discrete Semiconductors Thyristors Diacs SCRs SCR Module Triacs SIDAC Diodes And Rectifiers Bridge Rectifiers Fast Diodes General Purpose Schottky Diodes TVS Diodes - ESD Suppressors Zener Diodes Transistors Bipolar Transistor -BJT IGBT Transistor IGBT Module Mosfet Displays &amp; Drivers تمام محصولات Displays &amp; Drivers Displays 7 Segment Display Electronic Paper Displays HMI LCD Character Display LCD Graphic Display OLED Display TFT Display Display Controller ICs LCD Drivers Digital Interface Converter Circuit Protection تمام محصولات Circuit Protection Fuses Disposable Fuses SMD Resettable Fuses Fuse Holders Fuse Holder Thermistors NTC Thermistors PTC Thermistors Varistors Varistor Other Type Circuit Protection Gas Discharge Tubes LED Protection Devices LED Lighting تمام محصولات LED Lighting LED IR LEDs Color LEDs White SMD LEDs COB LEDs Opto electronics تمام محصولات Opto electronics Optocoupler - Photocoupler High Speed Optocouplers Transistor Output Optocouplers Triac And SCR Output Optocouplers Module And Boards تمام محصولات Module And Boards Embedded Boards Embedded Board Modules ADC Modules Camera Module DDS Modules ESP32 Modules ESP8266 Modules GPS And GSM Modules Interface Modules UPS Modules Motor Driver Modules PCB Adaptor Modules Proprietary RF Modules Power Supply Modules Radar Modules Sensor Modules Thermoelectric Module Wifi And Bluetooth Modules Wireless Audio Module Programmers And Debuggers Programmer Sensors تمام محصولات Sensors Biometric Sensors تمام محصولات Current Sensors تمام محصولات Distance Sensors تمام محصولات Environmental Sensors Gas Sensors Humidity And Temperature Sensors Temperature Sensors Flow Sensors تمام محصولات Force Sensors And Load Cells تمام محصولات Megnetic Switches تمام محصولات Magnetic Sensors تمام محصولات Microphones تمام محصولات Motion And Position Sensors تمام محصولات Optical Detectors And Sensors Ambient Light Sensors Photoresistor(LDR) Optical Sensors Pressure Sensors تمام محصولات Proximity Sensors تمام محصولات Touch Sensors تمام محصولات Vibration Sensors تمام محصولات Connectors تمام محصولات Connectors Audio And Video Connectors Audio Connectors Video Connector Battery Holders Coin Cell Battery Holders Cylindrical Battery Contacts Board to Board Board to Board And Mezzanine Connectors Card Edge Connectors تمام محصولات Ethernet Connectors Ethernet Connector FFC/FPC FFC/FPC Connectors FFC/FPC Jumper Cables Headers And Wire Housings Pin Headers Jumpers تمام محصولات Memory Connectors SD Card Connectors Power Connectors AC Power Entry Modules DC Power Connectors PCB Welding Terminal RF Interconnects RF Connectors/Coaxial Connectors Sim Card Connectors Sim Card Connector Terminal Blocks Barrier Terminal Blocks Pluggable Terminal Blocks Screw Terminal Blocks Spring Clamp Terminal Blocks Test Connectors Banana Connectors POGO-PIN Test Points Test Clip USB Connectors USB Connector Wire To Board/Wire To Wire Wire to Board Connectors Circular Connectors Wire To Wire Connectors PicoBlade Electromechanical تمام محصولات Electromechanical Printers Thermal Printers Relays High Frequency - RF Relays General Purpose Relays Solid State Relays Switches Detector Switches DIP Switches Slide Switches Tactile Switches Rocker Switches Rotary Encoders Switch Accessories Tools &amp; Supplies تمام محصولات Tools &amp; Supplies (ابزار لحیم کاری) Soldering (هویه) Soldering Irons (سیم قلع) Solder Wire (خمیر قلع) Solder paste (فلاکس) Soldering Flux (نوک هویه) Soldering Tips (لوازم یدکی)Soldering Spare Parts (لوازم جانبی)Soldering Accessories (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers (آچارهای پرس و سوکت زن)Crimping Tools تمام محصولات (انبر و پنس) Pliers And Tweezers (پنس) Tweezers (انبر و سیم چین)Pliers (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat (ابزار برش) Cutting Tools (انواع اسپری) Spray (خمیر سیلیکون) Silicone Paste (متفرقه) Others (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers (تست و اندازه گیری) Test And Measurement Component Testers Thermal Management Heat Sinks دوستان عزیز در صورت نیاز به فاکتور کاغذی حتما در مراحل ثبت سفارش تیک آن را فعال کنید. اطلاعات بیشتر... × کاربر مهمان واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما 0 0 عضویت در سایت ورود به حساب کاربری دسته بندی محصولات Passive Component Passive Component (1807) RF Components Antenna 34 RF Cable 2 Other RF Component 1 Buzzers Buzzer 8 Capacitors Aluminum Electrolytic Capacitors - Leaded 29 Feed Through Capacitors 2 Film Capacitor 21 SMD Aluminum Electrolytic Capacitors 87 SMD Ceramic Capacitors 236 SMD Tantalum Capacitors 39 Safety Capacitors 18 Super Capacitors 4 Other Type Capacitors 0 Ferrites Ferrite Beads 13 Ferrite Cores 1 Frequency Control Crystals 100 Oscillators 28 Resonators 2 Inductors, Chokes And Coils Fixed Inductors 161 Common Mode Chokes/Filters 23 Transformers Signal transformers 11 Current Transformers 16 Resistors SMD Resistors 869 Precision Resistors 29 Current Sense Resistors 38 Resistor Networks And Array 13 Multi Turn 13 Trimmer Resistors 5 Potentiometers 4 Integrated Circuits - ICs Integrated Circuits - ICs (585) Audio ICs Microphone Preamplifiers 1 Audio Amplifiers 18 Amplifier ICs Analog Comparators 23 Current Sense Amplifiers 20 Differential Amplifiers 0 Instrumentation Amplifiers 10 Isolation Amplifiers 4 Operational Amplifiers - OPAMP 124 Data Converter ICs ADC 60 Digital Potentiometer IC 2 DAC 14 Analog Front End - AFE 2 Energy Metering ICs 9 Touch Screen Controllers 4 Interface ICs 4-20mA Transmitter 6 IO Expander 4 Audio Interface ICs 4 CAN Interface IC 12 Digital Isolators 27 Ethernet Interface IC 18 RS-485 34 RS-232 8 Sensor Interface IC 4 Telecom Interface IC 2 USB Interface IC 32 Other  Interface ICs 4 Logic ICs Supervisory 10 Logic IC 54 Switch ICs Analog Switch 20 Bus Switch 3 Wireless And RF IC NFC/RFID Tag And Transponder 6 RF Detector 1 RF Amplifier 9 Phase Locked Loops - PLL 7 RF Transceiver 8 RF System on a Chip - SoC 8 Other ICs Real Time Clock IC 10 Other IC 2 Power Management Power Management (794) AC/DC Converters Adaptors/Power Supplies 51 Offline Switcher 30 PWM Controller 30 Power Factor Correction 11 Batteries Coin Cell Battery 3 Battery 7 DC/DC Converters Isolated DC/DC Converters 84 Battery Management Drivers Gate Drivers 57 Seven-Segment Drivers 10 LED Array Drivers 9 Isolated Gate Drivers 15 LED Lighting Drivers 27 Motor Drivers 30 Power Switches Smart Switches Specialised - PMIC Synchronous Rectifiers Reference Regulators Linear Voltage Regulators 36 Charge Pump Converters 5 LDO Voltage Regulators 113 Switching Regulators 123 Switching Controllers 16 Memories Memories (63) Memory Cards SD Card 2 Memory IC DRAM 7 EEPROM 26 F-RAM 4 NAND Flash 11 NOR Flash 10 PSRAM 2 SRAM 1 Processors And Controllers Processors And Controllers (256) Computing Programmable Logic ICs CPLD 5 FPGA 6 MCU AVR 23 ARM 140 STM8 6 PIC 33 RF Microcontrollers - MCU 7 Systems on a Chip - SoC 12 Other MCU 24 Discrete Semiconductors Discrete Semiconductors (807) Thyristors Diacs 1 SCRs 7 SCR Module 0 Triacs 18 SIDAC 2 Diodes And Rectifiers Bridge Rectifiers 20 Fast Diodes 44 General Purpose 22 Schottky Diodes 64 TVS Diodes - ESD Suppressors 174 Zener Diodes 87 Transistors Bipolar Transistor -BJT 76 IGBT Transistor 21 IGBT Module 13 Mosfet 258 Displays &amp; Drivers Displays &amp; Drivers (55) Displays 7 Segment Display 9 Electronic Paper Displays 2 HMI 16 LCD Character Display 1 LCD Graphic Display 4 OLED Display 5 TFT Display 14 Display Controller ICs LCD Drivers 1 Digital Interface Converter 3 Circuit Protection Circuit Protection (113) Fuses Disposable Fuses 33 SMD Resettable Fuses 31 Fuse Holders Fuse Holder 10 Thermistors NTC Thermistors 15 PTC Thermistors 2 Varistors Varistor 15 Other Type Circuit Protection Gas Discharge Tubes 7 LED Protection Devices 0 LED Lighting LED Lighting (91) LED IR LEDs 5 Color LEDs 56 White SMD LEDs 29 COB LEDs 1 Opto electronics Opto electronics (52) Optocoupler - Photocoupler High Speed Optocouplers 12 Transistor Output Optocouplers 31 Triac And SCR Output Optocouplers 9 Module And Boards Module And Boards (208) Embedded Boards Embedded Board 43 Modules ADC Modules 0 Camera Module 1 DDS Modules 0 ESP32 Modules 68 ESP8266 Modules 4 GPS And GSM Modules 9 Interface Modules 5 UPS Modules 1 Motor Driver Modules 1 PCB Adaptor Modules 3 Proprietary RF Modules 33 Power Supply Modules 7 Radar Modules 1 Sensor Modules 0 Thermoelectric Module 4 Wifi And Bluetooth Modules 16 Wireless Audio Module 3 Programmers And Debuggers Programmer 8 Sensors Sensors (201) Biometric Sensors Current Sensors Distance Sensors Environmental Sensors Gas Sensors 16 Humidity And Temperature Sensors 18 Temperature Sensors 9 Flow Sensors Force Sensors And Load Cells Megnetic Switches Magnetic Sensors Microphones Motion And Position Sensors Optical Detectors And Sensors Ambient Light Sensors 6 Photoresistor(LDR) 6 Optical Sensors 13 Pressure Sensors Proximity Sensors Touch Sensors Vibration Sensors Connectors Connectors (748) Audio And Video Connectors Audio Connectors 3 Video Connector 4 Battery Holders Coin Cell Battery Holders 4 Cylindrical Battery Contacts 2 Board to Board Board to Board And Mezzanine Connectors 12 Card Edge Connectors Ethernet Connectors Ethernet Connector 8 FFC/FPC FFC/FPC Connectors 91 FFC/FPC Jumper Cables 312 Headers And Wire Housings Pin Headers 29 Jumpers Memory Connectors SD Card Connectors 4 Power Connectors AC Power Entry Modules 2 DC Power Connectors 12 PCB Welding Terminal 10 RF Interconnects RF Connectors/Coaxial Connectors 8 Sim Card Connectors Sim Card Connector 7 Terminal Blocks Barrier Terminal Blocks 82 Pluggable Terminal Blocks 44 Screw Terminal Blocks 2 Spring Clamp Terminal Blocks 6 Test Connectors Banana Connectors 11 POGO-PIN 4 Test Points 5 Test Clip 4 USB Connectors USB Connector 29 Wire To Board/Wire To Wire Wire to Board Connectors 37 Circular Connectors 6 Wire To Wire Connectors 0 PicoBlade 0 Electromechanical Electromechanical (161) Printers Thermal Printers 6 Relays High Frequency - RF Relays 1 General Purpose Relays 33 Solid State Relays 2 Switches Detector Switches 5 DIP Switches 23 Slide Switches 6 Tactile Switches 76 Rocker Switches 1 Rotary Encoders 4 Switch Accessories 4 Tools &amp; Supplies Tools &amp; Supplies (140) (ابزار لحیم کاری) Soldering (هویه) Soldering Irons 3 (سیم قلع) Solder Wire 10 (خمیر قلع) Solder paste 4 (فلاکس) Soldering Flux 5 (نوک هویه) Soldering Tips 9 (لوازم یدکی)Soldering Spare Parts 4 (لوازم جانبی)Soldering Accessories 10 (پیچ گوشتی و آچار)Screwdrivers And Nut Drivers (پیچ گوشتی)Screwdrivers 4 (آچارهای پرس و سوکت زن)Crimping Tools (انبر و پنس) Pliers And Tweezers (پنس) Tweezers 4 (انبر و سیم چین)Pliers 5 (متفرقه) Miscellaneous (پد تعمیرات سیلیکونی) Soldering Mat 2 (ابزار برش) Cutting Tools 2 (انواع اسپری) Spray 3 (خمیر سیلیکون) Silicone Paste 3 (متفرقه) Others 4 (پیچ، مهره و اسپیسر) Knots And Bolts (انواع اسپیسر) Spacers 60 (تست و اندازه گیری) Test And Measurement Component Testers 1 Thermal Management Heat Sinks 5 View All Products واردات قطعات الکترونیک قطعات جدید قطعات تجدید موجودی تخفیف خورده سفارش PCB تامین کنندگان مقالات تماس با ما Home Products LED Lighting LED Color LEDs XL-3216UBC 9,800 موجودی محصول تعداد قیمت 100 9,456 ریال 500 9,141 ریال 1500 8,952 ریال 3000 8,826 ریال افزودن به سبد خرید Full Reel: 3000 در صورت کمبود موجودی، می توانید محصول را به لیست استعلام سفارشات خارجی اضافه کنید تا توسط کارشناسان بررسی و نتیجه اعلام شود. افزودن به لیست استعلام XL-3216UBC XL-3216UBC Part Number 2221 Lion Part Download Datasheet XINGLIGHT Manufacture ال ای دی آبی پکیچ 1206 LED Blue 455-475nm 1206 25mA 75mW مشخصات ال‌ای‌دی آبی XL-3216UBC ال‌ای‌دی آبی XL-3216UBC Part Number Blue Illumination Color 120° Viewing Angle Reel Packaging SMD/SMT Mounting Style 75mW Power Rating 42-86mcd Luminous Intensity -30C Minimum Operating Temperature +85C Maximum Operating Temperature 25mA If - Forward Current 455-475nm Wavelength-Color Temperature 1206 (3216 metric) Package-Case 2.6-3.2V Vf - Forward Voltage نظرات کاربران ارسال نظر محصولات مرتبط XL-1005UYC XL-1005UWC XL-1005SURC XL-1005UBC XL-1005UGC SK6812MINI-E XL-3215UYC XL-3215UGC XL-3215SURC WS2812D-F8 × افزودن به سبد خرید × افزودن به لیست استعلام موجودی محصول 9,800 وضعیت موجودی مورد نیاز افزودن به لیست استعلام × اطلاع رسانی برای ثبت درخواست اطلاع رسانی موجود شدن این کالا باید وارد حساب کاربری خود شوید کمی صبر کنید... × اطلاع رسانی برای افزودن این کالا به لیست علاقه مندی ها باید وارد حساب کاربری خود شوید خدمات مشتریان مشاوره فنی پیشنهاد قطعه واردات قطعات الکترونیک فروشگاه قطعات الکترونیک همراه با لیون الکترونیک درباره ما تماس با ما تجربه خرید از لیون الکترونیک انتقادات و پیشنهادات قوانین و مقررات دسته بندی های برگزیده مبدل آنالوگ به دیجیتال آپ امپ ماسفت میکروکنترلر AVR میکروکنترلر ARM تماس با ما ساعات کاری: شنبه تا چهارشنبه ۹ تا ۱۷ پنجشنبه ۹ تا ۱۴ شماره تماس: 02192003849 آدرس فروشگاه: تهران، خیابان جمهوری، نرسیده به پل حافظ، روبروی پاساژ توکل، پاساژ خانه موبایل، طبقه منفی1، واحد B4 (خرید حضوری به دلیل فاصله انبار و فروشگاه مقدور نیست) فروشگاه اینترنتی لیون الکترونیک لیون الکترونیک مرکز خرید و فروش قطعات الکترونیک در تهران | خرید قطعات الکترونیک اورجینال از فروشگاه قطعات الکترونیک لیون</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -614,10 +615,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>9456</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>28368</v>
       </c>
     </row>
@@ -628,14 +629,14 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>https://arefelectronic.com/%d8%b1%d9%84%d9%87-%d8%a7%d9%85%d8%b1%d9%86-%d9%85%d8%af%d9%84-g2r-1-e-%d8%af%d8%a7%d8%b1%d8%a7%db%8c-12-%d9%88%d9%84%d8%aa-%d9%88-8-%d9%be%db%8c%d9%86/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>رله امرن مدل G2R-1-E – 12V | 8PIN | 16A - فروشگاه عارف الکترونیک Skip to content جستجو برای: سبد خرید سبد خرید شما خالی است. بازگشت به فروشگاه ورود / عضویت سبد خرید سبد خرید شما خالی است. بازگشت به فروشگاه صفحه اصلی قطعات الکترونیک رله میلون بچه میلون پکیجی SSR SMD قدرت (آمپربالا) خودرویی مینیاتوری پایه گرد (تابلویی) T شکل مخابراتی کتابی PCB کولری رله PLC روسی لودسل تک پایه خمشی خمشی دو طرفه فشاری (سیلندری) کششی باسکولی خاص سوکت رله ریلی PCB (سوزنی) ای سی smd دیپ پتانسیومتر PT5 PT10 PT15 اسپانیایی چینی کارت رله ۲ کانال ۴ کانال ۸ کانال ۱۶ کانال سوئیچینگ فلزی پلاستیکی صنعتی خازن پل دیود کانکتور Micro-D J30J انواع سیم تجهیزات الکترونیک نمایشگر لودسل کاموس yaohua vista قلع ASAHI (اورجینال) طرح ASAHI RX_70 S ARTANIC (آرتانیک) PROSKIT تجهیزات شارژ و روشنایی باتری قلمی (AA) نیم قلمی (AAA) باتری 18650 باتری ویپ قابل شارژ کتابی (9V) سکه ای سایز C سایز D باتری سیلد اسید تلفن بی سیم لیتیوم ایون لیتیوم پلیمر سمعکی ساعت ریموت کنترل شارژر باتری VARTA (وارتا) NITECORE (نایتکور) پاوربانک 10000mAh 15000mAh 20000mAh WIRELESS چراغ قوه حرفه ای معمولی خودکاری هندلی هدلایت باتری لپ تاپ چسب و خمیر برندها zemic bongshin varta NHG OMRON panasonic RX_70 NITECORE Yaohua ASAHI ACP F&amp;T microchip molicell R&amp;A SCHRACK S CAMOS راهنما خرید وبلاگ ارتباط با ما جستجو برای: 1% خانه / رله / رله امرن ( OMRON ) رله امرن مدل G2R-1-E – 12V | 8PIN | 16A تومان ۳۱۲,۱۸۰ قیمت اصلی: تومان۳۱۲,۱۸۰ بود. تومان ۳۰۹,۶۰۰ قیمت فعلی: تومان۳۰۹,۶۰۰. رله امرن مدل G2R-1-E دارای 12 ولت و 8 پین و 1 کنتاکت و 16 آمپر می باشد. این رله محصول کشور اندونزی می باشد. تخفیف در تعداد خرید تعداد 50 - 100 101 - 500 501 - 1000 قیمت تومان ۳۰۳,۴۰۸ تومان ۳۰۰,۳۱۲ تومان ۲۹۷,۲۱۶ 190 در انبار (فعال برای پیش سفارش) رله امرن مدل G2R-1-E – 12V | 8PIN | 16A عدد افزودن به سبد خرید جهت خرید محصولات به صورت عمده با شماره تلفن های فروشگاه تماس و یا در واتساپ پیام دهید. مقایسه دسته: رله , رله امرن ( OMRON ) , رله کتابی برچسب: 12 ولت دسته‌ بندی محصولات کارت رله (7) ۴ کانال (3) ۸ کانال (3) ۱۶ کانال (1) molicell (1) J30J (14) کولری (13) ASAHI (3) آداپتور (4) رله (336) رله PCB (8) رله بچه میلون (3) رله T شکل (10) رله امرن ( OMRON ) (139) رله PLC (7) رله مخابراتی (23) رله پکیجی (31) رله کتابی (43) رله SSR (8) رله NHG (43) رله میلون (16) رله روسی (5) رله آمپربالا (قدرت) (62) رله مینیاتوری (7) رله خودرویی (18) رله پایه گرد ( تابلویی ) (9) پاور (50) ACP (8) سوکت رله (23) سوکت رله ریلی (12) سوکت رله سوزنی (13) پل دیود (1) F&amp;T (2) باتری (208) باتری ریموت کنترل (8) باتری سایز D (8) باتری لیتیوم (30) باتری ساعت (8) باتری وارتا (80) باتری شارژی (23) باتری سکه ای (23) باتری پاناسونیک (26) باتری تلفن بی سیم (12) باتری ۱۸۶۵۰ (13) باتری لپ تاپ (16) باتری ویپ (12) باتری لیتیوم یون (13) باتری سمعکی (5) باتری قلمی (26) باتری دزدگیر (2) باتری سیلد اسید (6) باتری نیم قلمی (26) باتری لیتیوم پلیمر (3) باتری شیر چشمی (1) باتری کتابی (14) باتری پک شده (1) باتری سایز C (6) شارژر باتری (17) VARTA (وارتا) (3) NITECORE (نایتکور) (9) خازن (2) BLAUPUNKT (3) قلع (8) طرح ASAHI (1) RX_70 (1) S (1) ARTANIC (آرتانیک) (1) PROSKIT (1) ASAHI (اورجینال) (2) نمایشگر لودسل (16) نمایشگر لودسل کاموس (5) نمایشگر لودسل yaohua (2) نمایشگر لودسل vista (2) چراغ قوه (11) حرفه ای (6) معمولی (1) خودکاری (1) هندلی (1) ای سی (5) اتمگا (2) دیپ (1) smd (1) شارژر لپ تاپ (7) هدلایت (4) چسب و خمیر (5) لودسل (92) لودسل bongshin (21) لودسل تک پایه (36) لودسل خمشی (14) لودسل فشاری ( سیلندری ) (14) لودسل کششی (29) لودسل زمیک ( zemic ) (68) پاوربانک (6) 10000mAh (2) 15000mAh (2) 20000mAh (2) WIRELESS (3) SCHRACK (8) کانکتور (60) پتانسیومتر (26) پتانسیومتر PT10 (10) پتانسیومتر PT15 (16) پتانسیومتر اسپانیایی (13) پتانسیومتر چینی (9) R&amp;A (11) Micro-D (14) سوئیچینگ (4) سوئیچینگ فلزی (3) سوئیچینگ پلاستیکی (1) توضیحات رله امرن مدل G2R-1-E دارای 12 ولت و 8 پین در عارف الکترونیک قابل سفارش می باشد. فروشگاه عارف الکترونیک با 4 دهه تجربه در حوزه ی الکترونیک است. همچنین تاییدیه و مجوز رسمی از اتحادیه قطعات الکترونیکی و دستگاه های صوتی و تصویری را نیز دارا می باشد. این فروشگاه به عنوان نماینده رسمی معروف ترین برند های قطعات الکترونیکی آماده ارسال محصولات به تمامی نقاط کشور می باشد. تمامی محصولات این فروشگاه اوریجنال و مناسب ترین قیمت در بازار می باشد. مشخصات فنی ولتاژ رله 12V کنتاکت رله 1C جریان رله 16A برند امرن کشور سازنده اندونزی نظرات (0) دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “رله امرن مدل G2R-1-E – 12V | 8PIN | 16A” لغو پاسخ امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. محصولات مشابه 1% مشاهده رله امرن مدل G2R-1-E – 24V | 8PIN | 16A تومان ۳۱۲,۱۸۰ قیمت اصلی: تومان۳۱۲,۱۸۰ بود. تومان ۳۰۹,۶۰۰ قیمت فعلی: تومان۳۰۹,۶۰۰. مشاهده سوکت رله ریلی 2 کنتاکت کتابی 8 پین (24_12_48_5 ولت DC) تماس بگیرید آدرس فروشگاه نشانی: تهران , خیابان جمهوری , بعد از پل حافظ , نبش پاساژ فرشته , پلاک ۶۳۴ ایمیل: info@arefelectronic.com میزبان صدای گرمتان هستیم ایام هفته : ۹:۳۰ الی ۱۸ پنج شنبه ها : ۹:۳۰ الی ۱۳:۳۰ تلفن: 52 84 70 66 (021) تلفن: 78 69 73 66 (021) همراه: 89 22 932 0902 اطلاعات عارف الکترونیک درباره ما قوانین و مقررات وبلاگ راهنما خرید فروشگاه اینترنتی عارف الکترونیک عارف الکترونیک با ۴۰ سال سابقه در زمینه صادرات و واردات قطعات الکترونیک در تمامی این سال ها به دنبال بهترین و ساده ترین روش ها برای خدمات ارزنده تر به مشتریان عزیز خود بوده است. ما به دنبال ارائه خدمات بهتر و سریع تر و فروش محصولات الکترونیکی با بهترین قیمت در بازار با تضمین اصالت کالا می باشیم. تمامی حقوق این سایت متعلق به شرکت عارف الکترونیک می باشد. | 
+          <t>رله امرن مدل G2R-1-E – 12V | 8PIN | 16A - فروشگاه عارف الکترونیک Skip to content جستجو برای: سبد خرید سبد خرید شما خالی است. بازگشت به فروشگاه ورود / عضویت سبد خرید سبد خرید شما خالی است. بازگشت به فروشگاه صفحه اصلی قطعات الکترونیک رله میلون بچه میلون پکیجی SSR SMD قدرت (آمپربالا) خودرویی مینیاتوری پایه گرد (تابلویی) T شکل مخابراتی کتابی PCB کولری رله PLC روسی لودسل تک پایه خمشی خمشی دو طرفه فشاری (سیلندری) کششی باسکولی خاص سوکت رله ریلی PCB (سوزنی) ای سی smd دیپ پتانسیومتر PT5 PT10 PT15 اسپانیایی چینی کارت رله ۲ کانال ۴ کانال ۸ کانال ۱۶ کانال سوئیچینگ فلزی پلاستیکی صنعتی خازن پل دیود کانکتور Micro-D J30J انواع سیم تجهیزات الکترونیک نمایشگر لودسل کاموس yaohua vista قلع ASAHI (اورجینال) طرح ASAHI RX_70 S ARTANIC (آرتانیک) PROSKIT تجهیزات شارژ و روشنایی باتری قلمی (AA) نیم قلمی (AAA) باتری 18650 باتری ویپ قابل شارژ کتابی (9V) سکه ای سایز C سایز D باتری سیلد اسید تلفن بی سیم لیتیوم ایون لیتیوم پلیمر سمعکی ساعت ریموت کنترل شارژر باتری VARTA (وارتا) NITECORE (نایتکور) پاوربانک 10000mAh 15000mAh 20000mAh WIRELESS چراغ قوه حرفه ای معمولی خودکاری هندلی هدلایت باتری لپ تاپ چسب و خمیر برندها zemic bongshin varta NHG OMRON panasonic RX_70 NITECORE Yaohua ASAHI ACP F&amp;T microchip molicell R&amp;A SCHRACK S CAMOS راهنما خرید وبلاگ ارتباط با ما جستجو برای: 1% خانه / رله / رله امرن ( OMRON ) رله امرن مدل G2R-1-E – 12V | 8PIN | 16A تومان ۳۱۲,۱۸۰ قیمت اصلی: تومان۳۱۲,۱۸۰ بود. تومان ۳۰۹,۶۰۰ قیمت فعلی: تومان۳۰۹,۶۰۰. رله امرن مدل G2R-1-E دارای 12 ولت و 8 پین و 1 کنتاکت و 16 آمپر می باشد. این رله محصول کشور اندونزی می باشد. تخفیف در تعداد خرید تعداد 50 - 100 101 - 500 501 - 1000 قیمت تومان ۳۰۳,۴۰۸ تومان ۳۰۰,۳۱۲ تومان ۲۹۷,۲۱۶ 190 در انبار (فعال برای پیش سفارش) رله امرن مدل G2R-1-E – 12V | 8PIN | 16A عدد افزودن به سبد خرید جهت خرید محصولات به صورت عمده با شماره تلفن های فروشگاه تماس و یا در واتساپ پیام دهید. مقایسه دسته: رله , رله امرن ( OMRON ) , رله کتابی برچسب: 12 ولت دسته‌ بندی محصولات آداپتور (4) رله (336) رله پکیجی (31) رله کتابی (43) رله SSR (8) رله NHG (43) رله میلون (16) رله روسی (5) رله آمپربالا (قدرت) (62) رله مینیاتوری (7) رله خودرویی (18) رله پایه گرد ( تابلویی ) (9) پاور (50) رله PCB (8) رله بچه میلون (3) رله T شکل (10) رله امرن ( OMRON ) (139) رله PLC (7) رله مخابراتی (23) ACP (8) سوکت رله (23) سوکت رله ریلی (12) سوکت رله سوزنی (13) پل دیود (1) F&amp;T (2) باتری (208) باتری تلفن بی سیم (12) باتری ۱۸۶۵۰ (13) باتری لپ تاپ (16) باتری ویپ (12) باتری لیتیوم یون (13) باتری سمعکی (5) باتری قلمی (26) باتری دزدگیر (2) باتری سیلد اسید (6) باتری نیم قلمی (26) باتری لیتیوم پلیمر (3) باتری شیر چشمی (1) باتری کتابی (14) باتری پک شده (1) باتری سایز C (6) باتری ریموت کنترل (8) باتری سایز D (8) باتری لیتیوم (30) باتری ساعت (8) باتری وارتا (80) باتری شارژی (23) باتری سکه ای (23) باتری پاناسونیک (26) شارژر باتری (17) VARTA (وارتا) (3) NITECORE (نایتکور) (9) خازن (2) BLAUPUNKT (3) قلع (8) ARTANIC (آرتانیک) (1) PROSKIT (1) ASAHI (اورجینال) (2) طرح ASAHI (1) RX_70 (1) S (1) نمایشگر لودسل (16) نمایشگر لودسل yaohua (2) نمایشگر لودسل vista (2) نمایشگر لودسل کاموس (5) چراغ قوه (11) حرفه ای (6) معمولی (1) خودکاری (1) هندلی (1) ای سی (5) اتمگا (2) دیپ (1) smd (1) شارژر لپ تاپ (7) هدلایت (4) چسب و خمیر (5) لودسل (92) لودسل تک پایه (36) لودسل خمشی (14) لودسل فشاری ( سیلندری ) (14) لودسل کششی (29) لودسل زمیک ( zemic ) (68) لودسل bongshin (21) پاوربانک (6) 20000mAh (2) WIRELESS (3) 10000mAh (2) 15000mAh (2) SCHRACK (8) کانکتور (60) پتانسیومتر (26) پتانسیومتر PT10 (10) پتانسیومتر PT15 (16) پتانسیومتر اسپانیایی (13) پتانسیومتر چینی (9) R&amp;A (11) Micro-D (14) سوئیچینگ (4) سوئیچینگ فلزی (3) سوئیچینگ پلاستیکی (1) کارت رله (7) ۴ کانال (3) ۸ کانال (3) ۱۶ کانال (1) molicell (1) J30J (14) کولری (13) ASAHI (3) توضیحات رله امرن مدل G2R-1-E دارای 12 ولت و 8 پین در عارف الکترونیک قابل سفارش می باشد. فروشگاه عارف الکترونیک با 4 دهه تجربه در حوزه ی الکترونیک است. همچنین تاییدیه و مجوز رسمی از اتحادیه قطعات الکترونیکی و دستگاه های صوتی و تصویری را نیز دارا می باشد. این فروشگاه به عنوان نماینده رسمی معروف ترین برند های قطعات الکترونیکی آماده ارسال محصولات به تمامی نقاط کشور می باشد. تمامی محصولات این فروشگاه اوریجنال و مناسب ترین قیمت در بازار می باشد. مشخصات فنی ولتاژ رله 12V کنتاکت رله 1C جریان رله 16A برند امرن کشور سازنده اندونزی نظرات (0) دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “رله امرن مدل G2R-1-E – 12V | 8PIN | 16A” لغو پاسخ امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. محصولات مشابه مشاهده سوکت رله ریلی 2 کنتاکت کتابی 8 پین (24_12_48_5 ولت DC) تماس بگیرید 1% مشاهده رله امرن مدل G2R-1-E – 24V | 8PIN | 16A تومان ۳۱۲,۱۸۰ قیمت اصلی: تومان۳۱۲,۱۸۰ بود. تومان ۳۰۹,۶۰۰ قیمت فعلی: تومان۳۰۹,۶۰۰. آدرس فروشگاه نشانی: تهران , خیابان جمهوری , بعد از پل حافظ , نبش پاساژ فرشته , پلاک ۶۳۴ ایمیل: info@arefelectronic.com میزبان صدای گرمتان هستیم ایام هفته : ۹:۳۰ الی ۱۸ پنج شنبه ها : ۹:۳۰ الی ۱۳:۳۰ تلفن: 52 84 70 66 (021) تلفن: 78 69 73 66 (021) همراه: 89 22 932 0902 اطلاعات عارف الکترونیک درباره ما قوانین و مقررات وبلاگ راهنما خرید فروشگاه اینترنتی عارف الکترونیک عارف الکترونیک با ۴۰ سال سابقه در زمینه صادرات و واردات قطعات الکترونیک در تمامی این سال ها به دنبال بهترین و ساده ترین روش ها برای خدمات ارزنده تر به مشتریان عزیز خود بوده است. ما به دنبال ارائه خدمات بهتر و سریع تر و فروش محصولات الکترونیکی با بهترین قیمت در بازار با تضمین اصالت کالا می باشیم. تمامی حقوق این سایت متعلق به شرکت عارف الکترونیک می باشد. | 
 طراحی سایت و سئو: امیررضا سعیدآبادی صفحه اصلی قطعات الکترونیک رله رله میلون رله بچه میلون رله کتابی رله پایه گرد ( تابلویی ) رله T شکل رله پکیجی رله خودرویی رله آمپربالا (قدرت) رله مخابراتی رله مینیاتوری رله امرن ( OMRON ) رله NHG رله PCB رله SMD رله SSR کولری رله PLC لودسل لودسل باسکولی لودسل تک پایه لودسل خمشی لودسل خمشی دو طرفه لودسل خاص لودسل فشاری ( سیلندری ) لودسل کششی لودسل bongshin لودسل زمیک ( zemic ) سوکت رله سوکت رله ریلی سوکت رله PCB (سوزنی) ای سی smd دیپ پتانسیومتر پتانسیومتر PT5 پتانسیومتر PT10 پتانسیومتر PT15 پتانسیومتر اسپانیایی پتانسیومتر چینی کارت رله ۲ کانال ۴ کانال ۸ کانال ۱۶ کانال سوئیچینگ سوئیچینگ فلزی سوئیچینگ پلاستیکی سوئیچینگ صنعتی خازن پل دیود کانکتور تجهیزات الکترونیک نمایشگر لودسل نمایشگر لودسل کاموس نمایشگر لودسل yaohua نمایشگر لودسل vista قلع ASAHI (اورجینال) طرح ASAHI ARTANIC (آرتانیک) PROSKIT RX_70 S تجهیزات شارژ و روشنایی باتری باتری قلمی (AA) باتری نیم قلمی (AAA) باتری ۱۸۶۵۰ باتری ویپ باتری قابل شارژ باتری سایز C باتری سایز D باتری کتابی (9V) باتری پاناسونیک باتری وارتا باتری ریموت کنترل باتری ساعت باتری سکه ای باتری سمعکی باتری لپ تاپ باتری لیتیوم یون باتری لیتیوم پلیمر شارژر باتری VARTA (وارتا) NITECORE (نایتکور) پاوربانک 10000mAh 15000mAh 20000mAh WIRELESS چراغ قوه حرفه ای معمولی خودکاری هندلی هدلایت باتری لپ تاپ چسب و خمیر برندها ACP ASAHI F&amp;T microchip molicell R&amp;A SCHRACK RX_70 S NITECORE VARTA panasonic OMRON bongshin yaohua camos zemic NHG راهنمای خرید از سایت ارتباط با ما وبلاگ درباره ما ورود / عضویت استفاده از موبایل ادامه رله امرن مدل G2R-1-E – 12V | 8PIN | 16A 190 در انبار (فعال برای پیش سفارش) رله امرن مدل G2R-1-E – 12V | 8PIN | 16A عدد افزودن به سبد خرید</t>
         </is>
       </c>
@@ -644,10 +645,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>3034080</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>3034080</v>
       </c>
     </row>
@@ -658,7 +659,7 @@
       <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>https://voltatech.ir/product/%d8%a8%d8%b1%d8%af-%d8%aa%d9%88%d8%b3%d8%b9%d9%87-esp32-c3-super-mini-%d8%a8%d8%a7-%d9%88%d8%b1%d9%88%d8%af%db%8c-type-c/</t>
         </is>
@@ -673,10 +674,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>5900000</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>11800000</v>
       </c>
     </row>
@@ -687,14 +688,14 @@
       <c r="B6" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>https://ariaebox.com/product/%d8%a8%d8%a7%da%a9%d8%b3-%d8%b4%d9%81%d8%a7%d9%81-%d8%a8%d8%b1%d8%af-%da%a9%d9%86%d8%aa%d8%b1%d9%84-%d8%b5%d9%86%d8%b9%d8%aa%db%8c-%d8%b1%db%8c%d9%84%db%8c-abr113-a2t-%d8%a8%d8%a7-%d8%a7%d8%a8%d8%b9/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>باکس شفاف برد کنترل صنعتی ریلی ABR113-A2T با ابعاد 40×90×125 میلی متر - آریا باکس پرش به ناوبری رفتن به محتوای اصلی سفارش و واردات انواع PCB، قطعات الکترونیکی (ماژول، آی سی، ال سی دی، سنسور، کانکتور و ...) از چین پذیرفته می شود. سفارش و واردات انواع PCB، قطعات الکترونیکی (ماژول، آی سی، ال سی دی، سنسور، کانکتور و ...) از چین پذیرفته می شود. جستجو 0 موارد 0 تومان ورود | ثبت‌نام منو 0 موارد ورود | ثبت‌نام مرور دسته بندی ها باکس جعبه های ریلی استاندارد عمودی ماژولار براکت ریل برد جعبه های دستی قابل حمل GPS بدون نمایشگر با نمایشگر جعبه های تجهیزات شبکه پاوربانک جعبه های رومیزی شیب دار ساده جعبه های ضد آب آلومینیومی رومیزی و دیواری تابلویی جعبه تقسیم جعبه های آلومینیومی پایه دار رومیزی جعبه های دیواری سایر محصولات دستگیره سر ولوم کیپد درایور باکس رسپبری جا باتری کیف تجهیزات کیف های ابزار کیف های ضدآب و ضدضربه جعبه های پنلی جعبه های کنترل تردد دیجیتال کارتخوان جعبه های هوشند سازی کلید هاب و روتر پریز و سوکت جعبه های نمایشگر ابزار ابزار و مونتاژ لحیم کاری هیتر ، هویه و وان قلع نوک هویه و المنت سیم لحیم و خمیر قلع روغن و فلاکس لحیم کاری قلع کش و انواع تمیز کننده خمیر و چسب سیلیکون ابزار تعمیرات موبایل سپراتور التراسونیک لوپ ، میکروسکوپ و ذره بین ست پیچ گوشتی قاب باز کن و تاچ کش شابلون آی سی پد نسوز مولتی متر منبع تغذیه پراپ و کابل تست پیچ گوشتی سیم چین، کف چین و لخت کن انبردست و دم باریک پنس و کاتر آچار سوکت زن و پرسی مته و ابزار سوراخ کاری سشوار و چسب حرارتی دماسنج و رطوبت سنج انواع اسپری و محلول جعبه ابزار و کشوی قطعات قطعات الکترونیکی ماژول ماژول جرقه زن ماژول تغذیه و شارژ ماژول بخار سرد سنسور سنسور دما و رطوبت آی سی باکس ابزار قطعات الکترونیکی همه محصولات ثبت سفارش از چین سفارش pcb قوانین و مقررات سوالات متداول درباره ما تماس با ما پیگیری سفارشات خانه / باکس / جعبه های ریلی استاندارد / ماژولار / باکس شفاف برد کنترل صنعتی ریلی ABR113-A2T با ابعاد 40×90×125 میلی متر باکس شفاف برد کنترل صنعتی ریلی ABR113-A2T با ابعاد 40×90×125 میلی متر برای بزرگنمایی کلیک کنید 378,000 تومان ثبت سفارش از چین 143 در انبار باکس شفاف برد کنترل صنعتی ریلی ABR113-A2T با ابعاد 40×90×125 میلی متر عدد افزودن به سبد خرید ابعاد خارجی: 40×90×125 میلی متر فاصله نقاط نصب: 80×115 میلی متر نام مدل: ABR113-A2T متعلقات: بدنه + پیچ دانلود فایل دیتاشیت لینک خرید رنگ مشکی درب مات مدل ABR113-A2 لینک خرید رنگ کرم درب مات مدل ABR113-A1 وزن 80 گرم ابعاد 40 × 90 × 125 میلی‌متر رنگ مشکی مواد تشکیل دهنده ABS کلاس حفاظت بدون IP تضمین بهترین قیمت بازار مشاوره و پشتیبانی آنلاین تضمین اصالت و سلامت کالا ارسال سریع سفارشات 378,000 تومان 143 در انبار باکس شفاف برد کنترل صنعتی ریلی ABR113-A2T با ابعاد 40×90×125 میلی متر عدد افزودن به سبد خرید ثبت سفارش از چین دسته بندی: ماژولار برچسب: باکس PLC , باکس الکترونیک , باکس برد الکترونیک , باکس پلاستیکی , باکس تجهیزات الکترونیکی , باکس ریلی استاندارد , باکس شفاف ریلی , باکس قطعات الکترونیکی , باکس کنترل صنعتی , باکس ماژولار , جعبه الکترونیک , جعبه برد الکترونیکی , جعبه پلاستیکی , جعبه تجهیزات الکترونیکی , جعبه ریلی استاندارد , جعبه قطعات الکترونیکی , قاب توضیحات توضیحات تکمیلی نظرات (0) توضیحات الکترونیک ریلی از زمان های طولانی در زمینه اتوماسیون سازی خانه و کارخانه استفاده می شود و روز به روز در حال گسترش می باشد. باکس های پلاستیکی ریلی از اتصالات برقی روی ریل ها محافظت می کنند. به دلیل استفاده آسان و ایمن (برای سیستم هشدار) به طور گسترده ای مورد استفاده قرار می گیرند. کاربردها : در زمینه های الکترونیک، ابزار دقیق، اتوماسیون، مخابرات، واحد های منبع تغذیه، تقویت کننده ها، پروژه های دانشجویی، تجهیزات سلامتی و پزشکی، تجهیزات تست و اندازه گیری، کنترل صنعتی، الکترومکانیکی از جمله رله ها ، دستگاه های سنجش و مانیتورینگ ، تایمر ، مبدل ، PCB و موارد دیگر استفاده می شوند. انواع: جعبه های ریلی در طرح های مختلف و با ابعاد استاندارد ارائه می شوند. این باکس ها را می توان به چهار دسته زیر تقسیم کرد: جعبه های ماژولار ریلی جعبه های ریلی عمودی براکت ها (گیره) نصب ریلی ریل بردها (ریل های نصب PCB) جعبه های ریلی ماژولار: جعبه های ریلی ماژولار در قالب استاندارد و از مواد پلاستیکی ABS و یا پلی کربنات و در ابعاد مختلفی ساخته شده اند. این باکس ها به صورت جعبه هایی با / بدون جای ترمینال و با / بدون شکاف های تهویه در دسترس می باشند. جعبه های ریلی عمودی: این باکس های از مواد پلاستیکی UL94-V0 ساخته شده اند. در دو طرف باکس ترمینال هایی با پین های مشخص، برای سهولت دسترسی به اتصالات داخلی و لحیم کاری فراهم شده است. پنل جلوی باکس قابلیت نصب برچسب و سوراخ کاری برای نصب LED را دارد. براکت های ریلی: این گیره های ریلی برای نصب تجهیزات الکترونیکی روی ریل استاندارد استفاده می شوند. ریل بردها: این پروفیل های اکسترود شده از جنس پلی آمید UL94-V0 و به صورت استاندارد در رنگ های سبز، خاکستری، نارنجی و یا مشکی ساخته می شوند. ریل بردها با عرض 45، 72، 108، 122 و … ارائه می شوند. ویژگی ها: متناسب با ریل استاندارد TH35 (35 میلی متر) قابلیت نصب به دیوار امکان نصب انواع ترمینال سوراخ های نصب برد PCB شیارهای تهویه هوا جهت کاهش دمای داخلی باکس مقاومت بالا در برابر سایش ، هوازدگی ، خوردگی مقاومت در برابر رطوبت بالا، محافظت مکانیکی عالی امکان چاپ و برش لیزر و CNC بر روی باکس استفاده آسان و ایمن (برای سیستم هشدار) قابلیت تغییر طول در ریل بردها طبق سفارش مشتری توضیحات تکمیلی وزن 80 گرم ابعاد 40 × 90 × 125 میلی‌متر رنگ مشکی مواد تشکیل دهنده ABS کلاس حفاظت بدون IP نظرات (0) دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “باکس شفاف برد کنترل صنعتی ریلی ABR113-A2T با ابعاد 40×90×125 میلی متر” لغو پاسخ نشانی ایمیل شما منتشر نخواهد شد. بخش‌های موردنیاز علامت‌گذاری شده‌اند * امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. محصولات مشابه مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس الکترونیکی 32 کاناله ریلی 27-23 با ابعاد 113×70×150 میلی متر ماژولار 1,630,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس الکترونیکی PLC ریلی تک ترمینال ABR103-A1 با ابعاد 72×90×115 میلی متر ماژولار 284,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس برد کنترل صنعتی PLC ریلی ABR113-A1 با ابعاد 40×90×145 میلی متر ماژولار نمره 4.00 از 5 276,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس پلاستیکی ریلی تجهیزات الکترونیکی ABR105-A1 با ابعاد 59×88×72 میلی متر ماژولار 207,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها انتخاب گزینه ها این محصول دارای انواع مختلفی می باشد. گزینه ها ممکن است در صفحه محصول انتخاب شوند باکس پلاستیکی فرستنده ریلی ماژولار ABR116-A1 با ابعاد 59×88×158 میلی متر ماژولار 388,000 تومان – 279,000 تومان قیمت: 279,000تومان تا 388,000تومان فروخته شده مقایسه مشاهده سریع افزودن به علاقه مندی ها اطلاعات بیشتر باکس تک ترمینال PLC ریلی ماژولار ABR123-A1 با ابعاد 72×90×145 میلی متر ماژولار نمره 4.00 از 5 225,500 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس ریلی تجهیزات PLC صنعتی ABR100-A2 با ابعاد 40×90×145 میلی متر ماژولار 200,000 تومان فروخته شده مقایسه مشاهده سریع افزودن به علاقه مندی ها اطلاعات بیشتر باکس ریلی کنترلر با دو پورت RS232 RS485 مدل ABR129-A2 با ابعاد 62×80×195 میلی متر ماژولار 1,020,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس ریلی ماژولار الکترونیکی ABR106-A10 با ابعاد 59×88×54 میلی متر ماژولار 176,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها انتخاب گزینه ها این محصول دارای انواع مختلفی می باشد. گزینه ها ممکن است در صفحه محصول انتخاب شوند باکس ریلی ماژولار کوچک ABR108-A با ابعاد 59×88×37 میلی متر ماژولار 133,000 تومان ارسال سریع برای تهران و شهرستان ها امکان تست و تعویض 48 ساعت امکان تست و عودت باکس سفارش مستقیم قطعات سفارش مستقیم انواع قطعات الکترونیک خرید از واتساپ وتلگرام @ariaebox / 09333603323 دسترسی سریع سبد خرید پیگیری سفارشات حساب کاربری من لینک های مفید تماس با ما درباره آریا باکس قوانین و مقررات در آریا باکس دسته بندی پرفروش کیف تجهیزات جعبه های ریلی جعبه های هوشمندسازی با ما همراه باشید با آریا باکس در ارتباط باشید 02166704819 02166754554 02166738683 02166765997 02166740303 02166765916 ایمیل : ariaebox.shop@gmail.com ساعت کاری: شنبه تا چهارشنبه از ساعت 9 الی 18  پنجشنبه ها 9 الی 14 تمام حقوق این وب سایت متعلق به آریا باکس می باشد. جستجو منو همه دسته بندی ها باکس جعبه های ریلی استاندارد عمودی ماژولار براکت ریل برد پاوربانک جعبه های آلومینیومی پایه دار رومیزی جعبه های پنلی جعبه های تجهیزات شبکه جعبه های دستی قابل حمل GPS بدون نمایشگر با نمایشگر جعبه های دیواری جعبه های رومیزی شیب دار ساده جعبه های ضدآب تابلویی جعبه تقسیم آلومینیومی رومیزی و دیواری جعبه های کنترل تردد دیجیتال کارتخوان جعبه های نمایشگر جعبه های هوشمندسازی باکس پریز و سوکت باکس کلید باکس هاب و روتر سایر محصولات درایور باکس رسپبری جا باتری جعبه های آداپتور سر ولوم کیپد کیف تجهیزات ابزار قطعات الکترونیکی ماژول ماژول جرقه زن ماژول تغذیه و شارژ باکس ابزار قطعات الکترونیکی همه محصولات ثبت سفارش از چین سفارش pcb قوانین و مقررات سوالات متداول درباره ما تماس با ما لیست علاقه مندی ها مقایسه ورود / ثبت نام سبد خرید بستن</t>
+          <t>باکس شفاف برد کنترل صنعتی ریلی ABR113-A2T با ابعاد 40×90×125 میلی متر - آریا باکس پرش به ناوبری رفتن به محتوای اصلی سفارش و واردات انواع PCB، قطعات الکترونیکی (ماژول، آی سی، ال سی دی، سنسور، کانکتور و ...) از چین پذیرفته می شود. سفارش و واردات انواع PCB، قطعات الکترونیکی (ماژول، آی سی، ال سی دی، سنسور، کانکتور و ...) از چین پذیرفته می شود. جستجو 0 موارد 0 تومان ورود | ثبت‌نام منو 0 موارد ورود | ثبت‌نام مرور دسته بندی ها باکس جعبه های ریلی استاندارد عمودی ماژولار براکت ریل برد جعبه های دستی قابل حمل GPS بدون نمایشگر با نمایشگر جعبه های تجهیزات شبکه پاوربانک جعبه های رومیزی شیب دار ساده جعبه های ضد آب آلومینیومی رومیزی و دیواری تابلویی جعبه تقسیم جعبه های آلومینیومی پایه دار رومیزی جعبه های دیواری سایر محصولات دستگیره سر ولوم کیپد درایور باکس رسپبری جا باتری کیف تجهیزات کیف های ابزار کیف های ضدآب و ضدضربه جعبه های پنلی جعبه های کنترل تردد دیجیتال کارتخوان جعبه های هوشند سازی کلید هاب و روتر پریز و سوکت جعبه های نمایشگر ابزار ابزار و مونتاژ لحیم کاری هیتر ، هویه و وان قلع نوک هویه و المنت سیم لحیم و خمیر قلع روغن و فلاکس لحیم کاری قلع کش و انواع تمیز کننده خمیر و چسب سیلیکون ابزار تعمیرات موبایل سپراتور التراسونیک لوپ ، میکروسکوپ و ذره بین ست پیچ گوشتی قاب باز کن و تاچ کش شابلون آی سی پد نسوز مولتی متر منبع تغذیه پراپ و کابل تست پیچ گوشتی سیم چین، کف چین و لخت کن انبردست و دم باریک پنس و کاتر آچار سوکت زن و پرسی مته و ابزار سوراخ کاری سشوار و چسب حرارتی دماسنج و رطوبت سنج انواع اسپری و محلول جعبه ابزار و کشوی قطعات قطعات الکترونیکی ماژول ماژول جرقه زن ماژول تغذیه و شارژ ماژول بخار سرد سنسور سنسور دما و رطوبت آی سی باکس ابزار قطعات الکترونیکی همه محصولات ثبت سفارش از چین سفارش pcb قوانین و مقررات سوالات متداول درباره ما تماس با ما پیگیری سفارشات خانه / باکس / جعبه های ریلی استاندارد / ماژولار / باکس شفاف برد کنترل صنعتی ریلی ABR113-A2T با ابعاد 40×90×125 میلی متر باکس شفاف برد کنترل صنعتی ریلی ABR113-A2T با ابعاد 40×90×125 میلی متر برای بزرگنمایی کلیک کنید 378,000 تومان ثبت سفارش از چین 143 در انبار باکس شفاف برد کنترل صنعتی ریلی ABR113-A2T با ابعاد 40×90×125 میلی متر عدد افزودن به سبد خرید ابعاد خارجی: 40×90×125 میلی متر فاصله نقاط نصب: 80×115 میلی متر نام مدل: ABR113-A2T متعلقات: بدنه + پیچ دانلود فایل دیتاشیت لینک خرید رنگ مشکی درب مات مدل ABR113-A2 لینک خرید رنگ کرم درب مات مدل ABR113-A1 وزن 80 گرم ابعاد 40 × 90 × 125 میلی‌متر رنگ مشکی مواد تشکیل دهنده ABS کلاس حفاظت بدون IP تضمین بهترین قیمت بازار مشاوره و پشتیبانی آنلاین تضمین اصالت و سلامت کالا ارسال سریع سفارشات 378,000 تومان 143 در انبار باکس شفاف برد کنترل صنعتی ریلی ABR113-A2T با ابعاد 40×90×125 میلی متر عدد افزودن به سبد خرید ثبت سفارش از چین دسته بندی: ماژولار برچسب: باکس PLC , باکس الکترونیک , باکس برد الکترونیک , باکس پلاستیکی , باکس تجهیزات الکترونیکی , باکس ریلی استاندارد , باکس شفاف ریلی , باکس قطعات الکترونیکی , باکس کنترل صنعتی , باکس ماژولار , جعبه الکترونیک , جعبه برد الکترونیکی , جعبه پلاستیکی , جعبه تجهیزات الکترونیکی , جعبه ریلی استاندارد , جعبه قطعات الکترونیکی , قاب توضیحات توضیحات تکمیلی نظرات (0) توضیحات الکترونیک ریلی از زمان های طولانی در زمینه اتوماسیون سازی خانه و کارخانه استفاده می شود و روز به روز در حال گسترش می باشد. باکس های پلاستیکی ریلی از اتصالات برقی روی ریل ها محافظت می کنند. به دلیل استفاده آسان و ایمن (برای سیستم هشدار) به طور گسترده ای مورد استفاده قرار می گیرند. کاربردها : در زمینه های الکترونیک، ابزار دقیق، اتوماسیون، مخابرات، واحد های منبع تغذیه، تقویت کننده ها، پروژه های دانشجویی، تجهیزات سلامتی و پزشکی، تجهیزات تست و اندازه گیری، کنترل صنعتی، الکترومکانیکی از جمله رله ها ، دستگاه های سنجش و مانیتورینگ ، تایمر ، مبدل ، PCB و موارد دیگر استفاده می شوند. انواع: جعبه های ریلی در طرح های مختلف و با ابعاد استاندارد ارائه می شوند. این باکس ها را می توان به چهار دسته زیر تقسیم کرد: جعبه های ماژولار ریلی جعبه های ریلی عمودی براکت ها (گیره) نصب ریلی ریل بردها (ریل های نصب PCB) جعبه های ریلی ماژولار: جعبه های ریلی ماژولار در قالب استاندارد و از مواد پلاستیکی ABS و یا پلی کربنات و در ابعاد مختلفی ساخته شده اند. این باکس ها به صورت جعبه هایی با / بدون جای ترمینال و با / بدون شکاف های تهویه در دسترس می باشند. جعبه های ریلی عمودی: این باکس های از مواد پلاستیکی UL94-V0 ساخته شده اند. در دو طرف باکس ترمینال هایی با پین های مشخص، برای سهولت دسترسی به اتصالات داخلی و لحیم کاری فراهم شده است. پنل جلوی باکس قابلیت نصب برچسب و سوراخ کاری برای نصب LED را دارد. براکت های ریلی: این گیره های ریلی برای نصب تجهیزات الکترونیکی روی ریل استاندارد استفاده می شوند. ریل بردها: این پروفیل های اکسترود شده از جنس پلی آمید UL94-V0 و به صورت استاندارد در رنگ های سبز، خاکستری، نارنجی و یا مشکی ساخته می شوند. ریل بردها با عرض 45، 72، 108، 122 و … ارائه می شوند. ویژگی ها: متناسب با ریل استاندارد TH35 (35 میلی متر) قابلیت نصب به دیوار امکان نصب انواع ترمینال سوراخ های نصب برد PCB شیارهای تهویه هوا جهت کاهش دمای داخلی باکس مقاومت بالا در برابر سایش ، هوازدگی ، خوردگی مقاومت در برابر رطوبت بالا، محافظت مکانیکی عالی امکان چاپ و برش لیزر و CNC بر روی باکس استفاده آسان و ایمن (برای سیستم هشدار) قابلیت تغییر طول در ریل بردها طبق سفارش مشتری توضیحات تکمیلی وزن 80 گرم ابعاد 40 × 90 × 125 میلی‌متر رنگ مشکی مواد تشکیل دهنده ABS کلاس حفاظت بدون IP نظرات (0) دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “باکس شفاف برد کنترل صنعتی ریلی ABR113-A2T با ابعاد 40×90×125 میلی متر” لغو پاسخ نشانی ایمیل شما منتشر نخواهد شد. بخش‌های موردنیاز علامت‌گذاری شده‌اند * امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. محصولات مشابه مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس الکترونیکی PLC ریلی تک ترمینال ABR103-A1 با ابعاد 72×90×115 میلی متر ماژولار 284,000 تومان جدید مقایسه مشاهده سریع افزودن به علاقه مندی ها انتخاب گزینه ها این محصول دارای انواع مختلفی می باشد. گزینه ها ممکن است در صفحه محصول انتخاب شوند باکس پلاستیکی ریلی استاندارد ABR112 با ابعاد 40×90×90 میلی متر ماژولار نمره 4.00 از 5 200,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس پلاستیکی کنترل صنعتی PLC ریلی ABR122-A1 با ابعاد 110×110×300 میلی متر ماژولار 1,350,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس توزیع کنترل PLC ریلی ماژولار ABR123-A22 با ابعاد 72×90×145 میلی متر ماژولار نمره 5.00 از 5 508,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس ریلی ماژول EM-235 PLC زیمنس 51-14 با ابعاد 64×71×80 میلی متر ماژولار نمره 4.00 از 5 426,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس ریلی ماژولار تجهیزات الکترونیکی ABR106-A20 با ابعاد 59×88×54 میلی متر ماژولار 176,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس ریلی ماژولار توزیع پروژه های الکترونیکی ABR119-A1M با ابعاد 40×90×115 میلی متر ماژولار 214,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس ریلی ماژولار سوئیچ تغذیه ABR109-A1 با ابعاد 44×54×88 میلی متر ماژولار 181,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها انتخاب گزینه ها این محصول دارای انواع مختلفی می باشد. گزینه ها ممکن است در صفحه محصول انتخاب شوند باکس ریلی ماژولار شیاردار ABR108-Axx با ابعاد 59×88×37 میلی متر ماژولار 137,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید باکس کنترل PLC ریلی ABR125-A1 با ابعاد 65×110×250 میلی متر ماژولار 960,000 تومان ارسال سریع برای تهران و شهرستان ها امکان تست و تعویض 48 ساعت امکان تست و عودت باکس سفارش مستقیم قطعات سفارش مستقیم انواع قطعات الکترونیک خرید از واتساپ وتلگرام @ariaebox / 09333603323 دسترسی سریع سبد خرید پیگیری سفارشات حساب کاربری من لینک های مفید تماس با ما درباره آریا باکس قوانین و مقررات در آریا باکس دسته بندی پرفروش کیف تجهیزات جعبه های ریلی جعبه های هوشمندسازی با ما همراه باشید با آریا باکس در ارتباط باشید 02166704819 02166754554 02166738683 02166765997 02166740303 02166765916 ایمیل : ariaebox.shop@gmail.com ساعت کاری: شنبه تا چهارشنبه از ساعت 9 الی 18  پنجشنبه ها 9 الی 14 تمام حقوق این وب سایت متعلق به آریا باکس می باشد. جستجو منو همه دسته بندی ها باکس جعبه های ریلی استاندارد عمودی ماژولار براکت ریل برد پاوربانک جعبه های آلومینیومی پایه دار رومیزی جعبه های پنلی جعبه های تجهیزات شبکه جعبه های دستی قابل حمل GPS بدون نمایشگر با نمایشگر جعبه های دیواری جعبه های رومیزی شیب دار ساده جعبه های ضدآب تابلویی جعبه تقسیم آلومینیومی رومیزی و دیواری جعبه های کنترل تردد دیجیتال کارتخوان جعبه های نمایشگر جعبه های هوشمندسازی باکس پریز و سوکت باکس کلید باکس هاب و روتر سایر محصولات درایور باکس رسپبری جا باتری جعبه های آداپتور سر ولوم کیپد کیف تجهیزات ابزار قطعات الکترونیکی ماژول ماژول جرقه زن ماژول تغذیه و شارژ باکس ابزار قطعات الکترونیکی همه محصولات ثبت سفارش از چین سفارش pcb قوانین و مقررات سوالات متداول درباره ما تماس با ما لیست علاقه مندی ها مقایسه ورود / ثبت نام سبد خرید بستن</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -702,10 +703,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>3780000</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3" t="n">
         <v>7560000</v>
       </c>
     </row>
@@ -716,7 +717,7 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>https://efarvahar.ir/usb-connector/493-male-3.html</t>
         </is>
@@ -749,10 +750,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="3" t="n">
         <v>435990</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3" t="n">
         <v>435990</v>
       </c>
     </row>
@@ -763,14 +764,14 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>https://www.iran-module.ir/product_info.php/products_id/2658/pname/%D9%85%D8%A7%DA%98%D9%88%D9%84-%D8%B1%DA%AF%D9%88%D9%84%D8%A7%D8%AA%D9%88%D8%B1-DC-%D8%A8%D9%87-DC-%D8%A7%D9%81%D8%B2%D8%A7%DB%8C%D9%86%D8%AF%D9%87-100-%D9%88%D8%A7%D8%AA-LTC1871-%D9%87%D9%85%D8%B1%D8%A7%D9%87-%D8%A8%D8%A7-%D9%86%D9%85%D8%A7%DB%8C%D8%B4%DA%AF%D8%B1-%D9%88%D9%84%D8%AA%D8%A7%DA%98</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>پاور، تغذيه و باتری - POW-00315 - ماژول رگولاتور DC به DC افزاینده 100 وات LTC1871 همراه با نمایشگر ولتاژ - ايران ماژول الكترونيك انتخاب واحد پولی: دلار یورو ريال تومان سبد خرید: ( 0 ) مورد خوش آمدید, کاربر گرامی صفحه اصلی سفارشات خارجی جستجوی پیشرفته تماس با ما درباره ما ورود پشتیبانی آنلاین Start Live Help Chat شاخه ها حراج قطعات Arduino GPS آنتن ماژول گيرنده GSM/GPRS LCD Single Board Computer ابزار DAQ بخار سرد برد برد برد رله پمپ خنک کننده/گرم کننده دستگاه های اندازه گيری ديتالاگر شیر برقی قفل برقی و سلونوئید لیزر متفرقه بردهای توسعه Android ARM LPC SAM SAMSUNG AVR Banana Pi Beagle Cypress FPGA LattePanda Intel Micro:bit MSP NET. NanoPI Odroid بـــورد اصلی تجهیزات جانبی NVIDEA Orange Pi PIC Raspberry Pi RENESAS ST Teensy TI Wiznet بردهای Breakout پاور، تغذيه و باتری پرنده بدون سرنشين اتوپايلوت رادیو کنترل و تلمتری ربات پرنده سنسور موتور و بدنه پروگرمر ARM AVR PIC پرینتر پرینتر حرارتی پرینتر سه بعدی تبلت ها لوازم جانبی خانه هوشمند کنترلرهای بلوتوث كنترلرهای شبكه خودرو الکتریکی قطعات و تجهیزات جانبی کنترلر موتور درایورها راديويیRF و ارتباطات Bluetooth General Modem Nordic RFID WiFi ZigBee آنتن فرستنده و گیرنده تصویر فرستنده و گیرنده صوت قطعات مخابراتی کانکتور مخابراتی رباتيك درايور قطعات مكانيكی چرخ ربات غيره كيت ربات موتور ردیابی سلول های خورشیدی سنسور IMU/AHRS PIR التراسونيك بيومتری تاچ تشخیص سطح مایعات تشعشعات جریان/ولتاژ حسگر مجاورتی دما رطوبت زاويه سنج ژيروسكوپ 1 محوری 2 محوری 3 محوری شتاب سنج 1 محوری 2 محوری 3 محوری شعله آتش صوت فشار فلومتر گاز ليزر مادون قرمز مایکروویو مغناطيس و قطب نما نور/تصوير/رنگ نيرو/گشتاور/خمش/لرزش هواشناسی هويت ID صوت قطعات آی سی های SMD آی سی های عمومی اسيلاتور و نوسانگر پتانسیومتر خازن دیود و ترانزیستور رگولاتور سلف و القاگر سوپر خازن قطعات عمومی کانکتورها كليد/سوییچ ميكروكنترلرهای AVR ميكروكنترلرهای ARM ميكروكنترلرهای PIC كابل HDMI USB پارالل سریال شبكه فایر وایر فیبر نوری مبدل اينترفيس نور و LED 3mm 5mm 10mm RGB SMD پر توان سون سگمنت ماوراء بنفش اطلاعيه ها مرا از تغييرات محصول ماژول رگولاتور DC به DC افزاینده 100 وات LTC1871 همراه با نمایشگر ولتاژ آگاه كن. مقایسه محصولات محصولی برای مقایسه انتخاب نشده است! ورود به سيستم آدرس پست الكترونيك: كلمه عبور: کلمه عبورتان را فراموش کرده اید؟ هنوز ثبت نام نکرده اید؟ تگ محصولات 2322ttl d2a 4222232 opamp av2hdmi 4852ttl 2322lan USB2485 2322422 waveshare 2sma ttl2lan ttl2485 rpi kit a2d 4852232 usb2232 2smaf lan2ser wifi2ser 4852usb زیگبی usb2ttl 2322485 lan2ttl ttl2usb lan2232 2ufl rpic 2322usb ser2wifi hdmi2vga vga2hdmi usb2ser CASE ttl2232 ser2usb ser2lan op-amp مقالات مقالات جدید تمامی مقالات تمامی موضوعات مقالات متفرقه RSS مقالات فروشگاه » پاور، تغذيه و باتری » POW-00315 ماژول رگولاتور DC به DC افزاینده 100 وات LTC1871 همراه با نمایشگر ولتاژ [ POW-00315 ] کد کالا : POW-00315 قیمت: 807,000تومان https://www.iran-module.ir/media/uploads/catalog/extra/product_2658_1624100391_42821.jpg https://www.iran-module.ir/media/uploads/catalog/extra/product_2658_1624100391_12071.jpg https://www.iran-module.ir/media/uploads/catalog/extra/product_2658_1624100392_16202.jpg https://www.iran-module.ir/media/uploads/catalog/extra/product_2658_1624100392_38832.jpg توضیحات: مبدل DC-DC یک مدار الکتریکی است که سطح ولتاژ از یک منبع DC را به سطح ولتاژ دیگری در طرف ثانویه تبدیل می‌کند. این تبدیل ولتاژ می‌تواند به صورت سوئیچینگ و یا به صورت رگولاسیون خطی باشد. بازدهی سوئیچینگ در رنج 75% تا 98% بوده و این مقدار معمولا از بازدهی در رگولاسیون خطی بیشتر می‌باشد. اگر بازدهی را 100% در نظربگیریم، می‌توان گفت که توان طرف اولیه با طرف ثانویه برابر است. نکته: در صورتی که ولتاژ خروجی با ولتاژ ورودی برابر است و تغییر نمی‌کند، مولتی ترن را آن قدر بچرخانید تا ولتاژ خروجی تغییر کند. کاربردهای ماژول رگولاتور DC به DC افزاینده 100 وات LTC1871: تثبیت ولتاژ انواع سیستم های الکترونیکی مشخصات فنی ماژول رگولاتور DC به DC افزاینده 100 وات LTC1871: ولتاژ ورودی :3 - 35 ولت جریان ورودی : (9A (Max ولتاژ خروجی :از 3.5 تا 35 ولت قابل تنظیم (ولتاژ خروجی بزرگتر مساوی ولتاژ ورودی است) جریان خروجی : (6A (Max توان : 75 وات (اگر ولتاژ ورودی و خروجی بزرگتر از 20 ولت باشد، توان تا 128 وات می‌باشد.) رنج ولت‌متر:4 تا 40 ولت خطای ولت متر :  0.1V-+ دارای نمایشگر ولتاژ با سون سگمنت های قرمز رنگ ابعاد : 67.5mm x 41.5mm بازده تبدیل :  96.4% (Max.) محافظت اتصال کوتاه: دارد (جریان محدود 14 آمپر) محافظت جلوگیری از ولتاژ معکوس : ندارد (به مثبت و منفی ماژول دقت کنید.) اطلاعات تماس Iran Module Electronic 02166720648 با بیان پوزش در اغلب اوقات قادر به مشاوره تلفنی نخواهیم بود. 021 کالاهای ناموجود فاقد لینک افزودن به سبد خرید میباشند bel_elc@yahoo.com www.iran-module.ir 02166713123 09391963671 به دلیل محدودیتهای اعمال شده کرونایی امکان پذیرایی هنگام مراجعه وجود ندارد. آدرس تهران خ جمهوری بین پل حافظ و سی تیر پاساژ فرشته پلاک 267 [ [ [ تا بهبود شرایط بهداشتی جامعه خدمت رسانی ترجیحاً غیرحضوری خواهد بود ] ] ] ساعت شنبه تا چهارشنبه 22:00 ~ 10:00 ♢ ♡ با آرزوی سلامتی توجه کالاهای ناموجود فاقد لینک افزودن به سبد خرید می باشند پرفروشترین محصولات ماژول DC/DC کاهنده ولتاژ با LM2596 ماژول رگولاتور DC/DC کاهنده ولتاژ Mini-360 جریان 3آمپر قابل تنظیم ولتاژ خروجی ماژول DC/DC افزاینده ولتاژ MT3608 جریان 2آمپر قابل تنظیم ولتاژ خروجی مبدل DC/DC ایزولاسیون 5ولت به 5ولت 1وات ایزوله تا 1500ولت مدل B0505S-1W ماژول کاهنده MP2315 DC-DC STEP DOWN BPW34 سلول خورشیدی مینیاتوری ماژول رگولاتور DC/DC کاهنده ولتاژ MP1584EN جریان 3آمپر قابل تنظیم ولتاژ خروجی ماژول رگولاتور 3.3 ولت با AMS1117-3.3 مبدل AC/DC سوییچینگ ایزوله 220 ولت به 5 ولت 3 وات مدل HLK-PM01 ماژول DC/DC کاهنده ولتاژ  LM2596HVS مبدل DC-DC افزاینده 32-10 ولت به 35-12 ولت 150 وات ماژول DC/DC افزاینده ولتاژ با LM2577 سنسور مانیتورینگ جریان و ولتاژ پورت USB با دو خروجیkws  USB Tester 3-9 Volt 0-3 Amper ماژول DC/DC افزاینده ولتاژ کوچک MT3608 قابل تنظیم ولتاژ خروجی با امکان تغذیه از MicroUSB صفحه مونتاژ و هیت سینک آلومینیومی LED توان بالا منبع تغذیه برد بورد Bread Board Power Supply ماژول مبدل DC-DC کاهنده 5 آمپر XL4015 با کنترل شارژ باتری شاخص میزان شارژ باتریهای لیتیوم پلیمر MAX17043 مبدل DC-DC کاهنده 4-40 ولت به 1.25-36 ولت 200W 8A XL4016E1 ماژول رگولاتورکاهنده 5 ولت با AMS1117-5 مبدل باتری کتابی 9 ولت به جک آداپتوری 5.5 میلی متر شارژر باطری لیتیوم TP5100 , 2CELL ماژول رگولاتور اتوماتیک DC به DC کاهنده / افزاینده LTC3780 مناسب برای شارژرهای خورشیدی تماس با ما کپی‌رایت © 2026 ایران ماژول الکترونیک راه اندازی شده توسط فروشگاه ساز ویرچو</t>
+          <t>پاور، تغذيه و باتری - POW-00315 - ماژول رگولاتور DC به DC افزاینده 100 وات LTC1871 همراه با نمایشگر ولتاژ - ايران ماژول الكترونيك انتخاب واحد پولی: دلار یورو ريال تومان سبد خرید: ( 0 ) مورد خوش آمدید, کاربر گرامی صفحه اصلی سفارشات خارجی جستجوی پیشرفته تماس با ما درباره ما ورود پشتیبانی آنلاین Start Live Help Chat شاخه ها حراج قطعات Arduino GPS آنتن ماژول گيرنده GSM/GPRS LCD Single Board Computer ابزار DAQ بخار سرد برد برد برد رله پمپ خنک کننده/گرم کننده دستگاه های اندازه گيری ديتالاگر شیر برقی قفل برقی و سلونوئید لیزر متفرقه بردهای توسعه Android ARM LPC SAM SAMSUNG AVR Banana Pi Beagle Cypress FPGA LattePanda Intel Micro:bit MSP NET. NanoPI Odroid بـــورد اصلی تجهیزات جانبی NVIDEA Orange Pi PIC Raspberry Pi RENESAS ST Teensy TI Wiznet بردهای Breakout پاور، تغذيه و باتری پرنده بدون سرنشين اتوپايلوت رادیو کنترل و تلمتری ربات پرنده سنسور موتور و بدنه پروگرمر ARM AVR PIC پرینتر پرینتر حرارتی پرینتر سه بعدی تبلت ها لوازم جانبی خانه هوشمند کنترلرهای بلوتوث كنترلرهای شبكه خودرو الکتریکی قطعات و تجهیزات جانبی کنترلر موتور درایورها راديويیRF و ارتباطات Bluetooth General Modem Nordic RFID WiFi ZigBee آنتن فرستنده و گیرنده تصویر فرستنده و گیرنده صوت قطعات مخابراتی کانکتور مخابراتی رباتيك درايور قطعات مكانيكی چرخ ربات غيره كيت ربات موتور ردیابی سلول های خورشیدی سنسور IMU/AHRS PIR التراسونيك بيومتری تاچ تشخیص سطح مایعات تشعشعات جریان/ولتاژ حسگر مجاورتی دما رطوبت زاويه سنج ژيروسكوپ 1 محوری 2 محوری 3 محوری شتاب سنج 1 محوری 2 محوری 3 محوری شعله آتش صوت فشار فلومتر گاز ليزر مادون قرمز مایکروویو مغناطيس و قطب نما نور/تصوير/رنگ نيرو/گشتاور/خمش/لرزش هواشناسی هويت ID صوت قطعات آی سی های SMD آی سی های عمومی اسيلاتور و نوسانگر پتانسیومتر خازن دیود و ترانزیستور رگولاتور سلف و القاگر سوپر خازن قطعات عمومی کانکتورها كليد/سوییچ ميكروكنترلرهای AVR ميكروكنترلرهای ARM ميكروكنترلرهای PIC كابل HDMI USB پارالل سریال شبكه فایر وایر فیبر نوری مبدل اينترفيس نور و LED 3mm 5mm 10mm RGB SMD پر توان سون سگمنت ماوراء بنفش اطلاعيه ها مرا از تغييرات محصول ماژول رگولاتور DC به DC افزاینده 100 وات LTC1871 همراه با نمایشگر ولتاژ آگاه كن. مقایسه محصولات محصولی برای مقایسه انتخاب نشده است! ورود به سيستم آدرس پست الكترونيك: كلمه عبور: کلمه عبورتان را فراموش کرده اید؟ هنوز ثبت نام نکرده اید؟ تگ محصولات vga2hdmi usb2ttl ttl2lan 2322485 4222232 2322ttl 2322lan rpic 4852usb opamp 2322usb lan2232 2smaf ttl2232 4852232 ser2usb ser2wifi lan2ser kit d2a rpi 4852ttl 2ufl waveshare op-amp USB2485 usb2232 CASE 2322422 hdmi2vga usb2ser 2sma a2d ser2lan ttl2485 av2hdmi زیگبی lan2ttl wifi2ser ttl2usb مقالات مقالات جدید تمامی مقالات تمامی موضوعات مقالات متفرقه RSS مقالات فروشگاه » پاور، تغذيه و باتری » POW-00315 ماژول رگولاتور DC به DC افزاینده 100 وات LTC1871 همراه با نمایشگر ولتاژ [ POW-00315 ] کد کالا : POW-00315 قیمت: 807,000تومان https://www.iran-module.ir/media/uploads/catalog/extra/product_2658_1624100391_42821.jpg https://www.iran-module.ir/media/uploads/catalog/extra/product_2658_1624100391_12071.jpg https://www.iran-module.ir/media/uploads/catalog/extra/product_2658_1624100392_16202.jpg https://www.iran-module.ir/media/uploads/catalog/extra/product_2658_1624100392_38832.jpg توضیحات: مبدل DC-DC یک مدار الکتریکی است که سطح ولتاژ از یک منبع DC را به سطح ولتاژ دیگری در طرف ثانویه تبدیل می‌کند. این تبدیل ولتاژ می‌تواند به صورت سوئیچینگ و یا به صورت رگولاسیون خطی باشد. بازدهی سوئیچینگ در رنج 75% تا 98% بوده و این مقدار معمولا از بازدهی در رگولاسیون خطی بیشتر می‌باشد. اگر بازدهی را 100% در نظربگیریم، می‌توان گفت که توان طرف اولیه با طرف ثانویه برابر است. نکته: در صورتی که ولتاژ خروجی با ولتاژ ورودی برابر است و تغییر نمی‌کند، مولتی ترن را آن قدر بچرخانید تا ولتاژ خروجی تغییر کند. کاربردهای ماژول رگولاتور DC به DC افزاینده 100 وات LTC1871: تثبیت ولتاژ انواع سیستم های الکترونیکی مشخصات فنی ماژول رگولاتور DC به DC افزاینده 100 وات LTC1871: ولتاژ ورودی :3 - 35 ولت جریان ورودی : (9A (Max ولتاژ خروجی :از 3.5 تا 35 ولت قابل تنظیم (ولتاژ خروجی بزرگتر مساوی ولتاژ ورودی است) جریان خروجی : (6A (Max توان : 75 وات (اگر ولتاژ ورودی و خروجی بزرگتر از 20 ولت باشد، توان تا 128 وات می‌باشد.) رنج ولت‌متر:4 تا 40 ولت خطای ولت متر :  0.1V-+ دارای نمایشگر ولتاژ با سون سگمنت های قرمز رنگ ابعاد : 67.5mm x 41.5mm بازده تبدیل :  96.4% (Max.) محافظت اتصال کوتاه: دارد (جریان محدود 14 آمپر) محافظت جلوگیری از ولتاژ معکوس : ندارد (به مثبت و منفی ماژول دقت کنید.) اطلاعات تماس Iran Module Electronic 02166720648 با بیان پوزش در اغلب اوقات قادر به مشاوره تلفنی نخواهیم بود. 021 کالاهای ناموجود فاقد لینک افزودن به سبد خرید میباشند bel_elc@yahoo.com www.iran-module.ir 02166713123 09391963671 به دلیل محدودیتهای اعمال شده کرونایی امکان پذیرایی هنگام مراجعه وجود ندارد. آدرس تهران خ جمهوری بین پل حافظ و سی تیر پاساژ فرشته پلاک 267 [ [ [ تا بهبود شرایط بهداشتی جامعه خدمت رسانی ترجیحاً غیرحضوری خواهد بود ] ] ] ساعت شنبه تا چهارشنبه 22:00 ~ 10:00 ♢ ♡ با آرزوی سلامتی توجه کالاهای ناموجود فاقد لینک افزودن به سبد خرید می باشند پرفروشترین محصولات ماژول DC/DC کاهنده ولتاژ با LM2596 ماژول رگولاتور DC/DC کاهنده ولتاژ Mini-360 جریان 3آمپر قابل تنظیم ولتاژ خروجی ماژول DC/DC افزاینده ولتاژ MT3608 جریان 2آمپر قابل تنظیم ولتاژ خروجی مبدل DC/DC ایزولاسیون 5ولت به 5ولت 1وات ایزوله تا 1500ولت مدل B0505S-1W ماژول کاهنده MP2315 DC-DC STEP DOWN BPW34 سلول خورشیدی مینیاتوری ماژول رگولاتور DC/DC کاهنده ولتاژ MP1584EN جریان 3آمپر قابل تنظیم ولتاژ خروجی ماژول رگولاتور 3.3 ولت با AMS1117-3.3 مبدل AC/DC سوییچینگ ایزوله 220 ولت به 5 ولت 3 وات مدل HLK-PM01 ماژول DC/DC کاهنده ولتاژ  LM2596HVS مبدل DC-DC افزاینده 32-10 ولت به 35-12 ولت 150 وات ماژول DC/DC افزاینده ولتاژ با LM2577 سنسور مانیتورینگ جریان و ولتاژ پورت USB با دو خروجیkws  USB Tester 3-9 Volt 0-3 Amper ماژول DC/DC افزاینده ولتاژ کوچک MT3608 قابل تنظیم ولتاژ خروجی با امکان تغذیه از MicroUSB صفحه مونتاژ و هیت سینک آلومینیومی LED توان بالا منبع تغذیه برد بورد Bread Board Power Supply ماژول مبدل DC-DC کاهنده 5 آمپر XL4015 با کنترل شارژ باتری شاخص میزان شارژ باتریهای لیتیوم پلیمر MAX17043 مبدل DC-DC کاهنده 4-40 ولت به 1.25-36 ولت 200W 8A XL4016E1 ماژول رگولاتورکاهنده 5 ولت با AMS1117-5 مبدل باتری کتابی 9 ولت به جک آداپتوری 5.5 میلی متر شارژر باطری لیتیوم TP5100 , 2CELL ماژول رگولاتور اتوماتیک DC به DC کاهنده / افزاینده LTC3780 مناسب برای شارژرهای خورشیدی تماس با ما کپی‌رایت © 2026 ایران ماژول الکترونیک راه اندازی شده توسط فروشگاه ساز ویرچو</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -778,10 +779,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>8070000</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3" t="n">
         <v>8070000</v>
       </c>
     </row>
@@ -792,27 +793,23 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>https://electronic724.com/Product/E724-23395/%d8%a8%d8%b1%d8%af-%d9%85%d8%a7%da%98%d9%88%d9%84-sim800c-board-hw-537/</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>مشخصات، قیمت و خرید برد ماژول SIM800C Board HW-537 ورود / ثبت نام شماره تماس یا ایمیل خود را وارد کنید شرایط و قوانین استفاده از سرویس های فروشگاه اینترنتی الکترونیک 724 را می پذیرم دریافت کد تایید ورود / ثبت نام رمزعبور را فراموش کرده ام ورود / ثبت نام با پسورد ورود با رمز یکبار مصرف کد تایید 4 رقمی ارسال شده به شماره موبایل زیر را وارد کنید. ویرایش شماره تایید کد ارسال مجدد کد رمز عبور خود را وارد کنید. ورود / ثبت نام جستجوی محصولات کاربری ورود / ثبت نام سبد خرید خالی است سبد خرید 0 می‌توانید برای مشاهده محصولات بیشتر به صفحات زیر بروید علاقه مندی های من بازگشت به فروشگاه دسته بندی ها ماژول‌های الکترونیکی مبدل‌ها تغذیه صدا و تصویر دما و رطوبت موتورها و درایور موتور GPS &amp; GSM IMU &amp; GYRO RFID &amp; NFC فاصله یاب KeyBoard &amp; Keypad تشخیص گاز Infrared (IR) اسکنر بارکد و QR سنسور اثر انگشت علائم حیاتی گرد و غبار ماژول ساعت (RTC) TCP/IP ماژول سنسور جریان Water Flow ماژول رله و سوئیچ تشخیص رنگ و نور وزن فشارسنج شتاب سنج ماژولهای Encoder تشخیص حرکت و لرزش پرینتر قطب نما RF &amp; بی سیم آنتن &amp; UFL Radio Frequency (RF) 2.4GHz WiFi Bluetooth Zigbee LoRa ماژولهای متفرقه آردوینو Arduino بردهای آردوینو شیلدها لوازم جانبی آردوینو کامپیوترهای تک بردی Banana Pi Beagle Bone Nano PI ODROID Orange PI Raspberry PI لوازم جانبی کامپیوترهای تک بردی بردهای کاربردی و آموزشی برد میکروکنترلرهای STM بردهای Atmel بردهای FPGA بردهای متفرقه نمایشگر ال سی دی (LCD) اولد (OLED) سون سگمنت (7Segment) Car LCD ال ای دی (LED) کانکتور ATX ای تی اکس SM بین راهی VH پاور قفل دار پین گرد کانکتور PH پی اِچ کانکتور XH یا دزدگیری کانکتور مخابراتی 2510 جعبه و قاب باکس‌های ریلی استاندارد باکس‌های ریلی عمودی باکس‌های ریلی ماژولار براکت‌های ریلی استاندارد بردهای ریلی استاندارد جعبه‌های آلومینیومی آلومینیومی دیواری گوشواره‌دار آلومینیومی رومیزی جعبه‌های پنلی جعبه‌های تجهیزات شبکه جعبه‌های دستی قابل حمل جعبه‌های GPS جعبه‌های دستی بدون نمایشگر جعبه‌های دستی نمایشگردار جعبه‌های دیواری جعبه‌های رومیزی جعبه‌های رومیزی ساده جعبه‌های رومیزی شیب‌دار جعبه‌های رومیزی نمایشگردار جعبه‌های ضد آب ضد آب تابلویی جعبه تقسیم ضد آب ضد آب آلومینیومی ضد آب پلاستیکی رومیزی و دیواری جعبه‌های کنترل تردد کنترل تردد اثرانگشتی کنترل تردد ترکیبی کنترل تردد دیجیتال (کیپددار) کنترل تردد کارتخوان RFID جعبه‌های نمایشگر جعبه‌های هوشمندسازی پریز و سوکت هوشمند کلیدهای هوشمند هاب و روتر هوشمند کیف‌های ضد ضربه و ضد آب سایر باکس‌ها باکس درایور LED باکس رسپبری پای و مینی کامپیوتر جا باتری جعبه‌ آداپتور سر ولوم کیپد باکس‌های متفرقه سایر دسته‌بندی‌ها پروگرامر پاوربانک ریموت کنترل و گیرنده ولت‌متر و آمپرمتر PCB های مبدل آی سی ها (IC) رگولاتور میکروکنترلر STM آی سی متفرقه لوازم جانبی باتری (باطری) کارت حافظه و Flash   «««««جدید»»»»» متفرقه مجله الکترونیک 724 سفارش چاپ PCB تماس با ما 02166769124 فروشگاه اینترنتی الکترونیک 724 ماژول‌های الکترونیکی GPS &amp; GSM برد ماژول SIM800C Board HW-537 203003 0 دیدگاه افزودن به علاقه‌مندی‌ها اشتراک گذاری مرا مطلع کن مقایسه نمودار قیمت آیا قیمت مناسب‌تری سراغ دارید؟ بله | خیر بازخورد درباره این کالا اشتراک گذاری این محصول را با دوستان خود به اشتراک بگذارید! کپی کردن لینک برد ماژول SIM800C Board HW-537 SIM800C Board HW-537 دسته بندی: GPS &amp; GSM برد ماژول SIM800C Board HW-537، ماژول جی اس ام Sim800C محصول شرکت SIMCOM به همراه برد راه انداز مدل HW-537، دارای ابعاد کوچک و رابط سریال آماده ارسال بازگشت آماده ارسال این کالا در حال حاضر در انبار فروشگاه موجود ، آماده پردازش و ارسال است 620,400 تومان موجود تعداد افزودن به سبد تحویل اکسپرس پرداخت آنلاین ارسال سراسری بهترین قیمت محصولات مرتبط AC to DC 5V/2A + USB 10w Charger 234,500 تومان ADS1115 I2C Compact 241,600 تومان ANOLOG MULTIPLEXER CD74HC4067 65,300 تومان Antenna GPS 25x25x6 Active 172,800 تومان High-Power Mosfet Driver 100A 158,500 تومان High-Power Mosfet Driver 20A 45,500 تومان High-Power Mosfet Driver 50A 71,800 تومان LASER MODULE KY-008 47,300 تومان LM2577 با نمایشگر ولتاژ ورودی و خروجی 308,900 تومان logic level converter 3.3V to 5V bi directional 29,400 تومان نقد و بررسی دیدگاه ها پرسش و پاسخ امتیاز کاربران به: برد ماژول SIM800C Board HW-537 | (0 نفر                    ) هنوز امتیازی ثبت نشده است نظر خود را در مورد این محصول بیان کنید. افزودن نظر جدید شما هم می‌توانید در مورد این کالا نظر دهید. اگر این محصول را قبلا خریده باشید، دیدگاه شما به عنوان خریدار ثبت خواهد شد. دیدگاه خود را ثبت کنید برای ثبت دیدگاه باید ابتدا وارد سایت شوید! ثبت نظر شما همچنین می توانید یک پرسش در مورد این محصول ثبت کنید ثبت پرسش نمودار قیمت کالا جهت فیلترکردن نمودارها، بر روی هر عنوان کلیک کنید. مقایسه ( 0 مورد ) مقایسه( 0 مورد ) حذف همه بازگشت به بالا پشتیبانی شماره تماس فروشگاه : [02166757479] هفت روز هفته، ۲۴ ساعت شبانه‌روز پاسخگوی شما هستیم. تهران - خ جمهوری - بعد از پل حافظ - پاساژ امجد - ط سوم - واحد 11 آدرس ایمیل : info@electronic724.com تحویل اکسپرس پرداخت آنلاین ارسال سراسری بهترین قیمت تحویل اکسپرس پرداخت آنلاین ارسال سراسری بهترین قیمت راهنمای خرید راهنمای خرید روش‌های ارسال روش‌های پرداخت خدمات پیگیری سفارشات حریم خصوصی پرسش‌های متداول خدمات مشتریان راهنمای خرید روش‌های ارسال روش‌های پرداخت با ما همراه باشید فروشگاه اینترنتی الکترونیک 724، بررسی، انتخاب و خرید آنلاین ﺗﻤﺎمی ﻛﺎﻻﻫﺎ و ﺧﺪﻣﺎت اﻳﻦ ﻓﺮوﺷﮕﺎه، ﺣﺴﺐ ﻣﻮرد، دارای ﻣﺠﻮزﻫﺎی ﻻزم از ﻣﺮاﺟﻊ ﻣﺮﺑﻮﻃﻪ میﺑﺎﺷﻨﺪ و ﻓﻌﺎﻟﻴﺖ‌ﻫﺎی اﻳﻦ ﺳﺎﻳﺖ ﺗﺎﺑﻊ ﻗﻮاﻧﻴﻦ و ﻣﻘﺮرات ﺟﻤﻬﻮری اﺳﻼمی اﻳﺮان اﺳﺖ. آدرس : تهران - خ جمهوری - بعد از پل حافظ - پاساژ امجد - ط سوم - واحد 11   [ساعات کار دفتر : شنبه تا چهارشنبه : 10 الی 17 و  پنج شنبه ها : 10 الی 12:30] نمایش بیشتر کليه حقوق اين سايت متعلق فروشگاه اینترنتی الکترونیک 724 می‌باشد. Copyright © 2006 - 2026 Electronic724 آخرین جستجوهای شما جستجوهای پرطرفدار باکس ماژول ال ای دی باتری جعبه این محصول به سبد خرید اضافه شد! رفتن به سبد خرید تماس با ما پاسخگوی شما هستیم یکی از راه های زیر را برای ارتباط انتخاب کنید تماس با شماره ثابت ارتباط از طریق واتساپ ارتباط از طریق تلگرام پیج اینستاگرام ما از کوکی‌ها برای ارائه خدمات بهتر و تجزیه و تحلیل رفتار کاربران استفاده می‌کنیم. لطفاً با تأیید این مورد ما را در مسیر بهبود تجربه کاربری یاری فرمایید. مشاهده شرایط رد کردن پذیرش همه 0 سبد خرید 0 شما این محصولات را انتخاب کرده اید 0 می‌توانید برای مشاهده محصولات بیشتر به صفحات زیر بروید علاقه مندی های من بازگشت به فروشگاه تصاویر رسمی دیدگاه خریدار برد ماژول SIM800C Board HW-537</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>6204000</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6204000</v>
-      </c>
+          <t>ERROR: HTTPSConnectionPool(host='electronic724.com', port=443): Max retries exceeded with url: /Product/E724-23395/%D8%A8%D8%B1%D8%AF-%D9%85%D8%A7%DA%98%D9%88%D9%84-sim800c-board-hw-537/ (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='electronic724.com', port=443) at 0x21cd66916d0&gt;, 'Connection to electronic724.com timed out. (connect timeout=30)'))</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -821,14 +818,14 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>https://nemonehsaz.com/%D9%87%DB%8C%D8%AA-%D8%A8%D8%AF-%D9%BE%D8%B1%DB%8C%D9%86%D8%AA%D8%B1-%D8%B3%D9%87-%D8%A8%D8%B9%D8%AF%DB%8C-214x214-PCB-Heat-Bed</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>هیت بد 214*214 (PCB Heatbed) مدل MK2B Dual Power/ نمونه ساز info@nemonehsaz.com   |   04136674173  = 09144100446 حساب کاربری عضویت ورود لیست دلخواه (0) جستجو جستجو سبد خرید 0 محصول سبد خرید شما خالی است! دسته بندی ها پرینتر سه بعدی پرینتر سه بعدی (4) قلم سه بعدی (3) فیلامنت پرینتر سه بعدی فیلامنت PLA PLUS برند SUNLU (سانلو ) (31) فیلامنت PLA قطر 1.75 میلیمتر  (30) فیلامنت PLA PLUS پلاس ایسان eSUN PLA PRO PLUS  (29) فیلامنت +PLA پلاس ایسان سرعت بالا High Speed (4) فیلامنت ABS PLUS eSUN ( ABS+) (29) فیلامنت PC پلی کربنات 1.75 (PC Polycarbonate) (4) فیلامنت PETG ایسان PETG filament eSUN (20) فیلامنت PVA پرینتر سه بعدی (محلول در آب) (2) فیلامنت چوب Wood PLA (2) فیلامنت انعطاف پذیر Flexible قطر 1.75 (23) فیلامنت Silk PLA ایسان (  ابریشمی ) (24) فیلامنت فیبر کربن PA-CF 1.75 (11) فیلامنت HIPS قطر 1.75mm  (1) فیلامنت متال ePLA Metal - فیلامنت فلز    (5) فیلامنت PCL قطر 1.75 (3) فیلامنت PEEK Pro ایسان  (1) فیلامنت تمیز کننده نازل پرینتر سه بعدی eCleaning eSUN (2) فیلامنت ASA قطر 1.75 میلی متر(ASA filament) (3) فیلامنت PA نایلون PA Nylon (2) فیلامنت PETG بسته 100 گرمی (PETG Filament) (14) فیلامنت نایلون-پشم شیشه PA-GF (2) فیلامنت POM (3) قطعات پرینتر سه بعدی اکسترودر پرینتر سه بعدی 3D printer extruder (48) قطعات الکترونیکی (187) قطعات الکتریکی (37) قطعات جانبی (29) قطعات مکانیکی  (777) محفظه آلومینیومی هیتر Heater block 3d printer (28) نازل اکسترودر (نازل پرینتر سه بعدی ) (227) قطعات مکانیکی انرژی چین زنجیر محافظ کابل (8) جوراب کابل (17) کوپلینگ یونیور سال-Universal Couplings (25) مهره (92) واشر (7) اسپیسر Spacer (25) اتصالات پروفیل آلومینیوم (39) انواع پیچ (180) ماشین ابزار و CNC ابزار الات و تجهیزات (137) قطعات الکترونیکی CNC (13) قطعات مکانیکی CNC (348) کانکتور شفت سه نظام  (40) رباتیک قطعات رباتیک (8) موتور  (5) موتور (39) خدمات پرینت سه بعدی هیت بد 214*214 (PCB Heatbed) مدل MK2B Dual Power هیت بد 214*214 (PCB Heatbed) مدل MK2B Dual Power کد محصول: PCB Heated MK2B Dual Power Bed Red موجودی: 3 بازدید: 25455 قیمت : 1,362,400 تومان تعداد : اضافه به سبد خرید 0 نظر / نظر بدهید توضیحات نظرات (0) هیت‌بد مدل MK2B یکی از پرکاربردترین صفحات گرم‌کن برای پرینترهای سه‌بعدی (3D Printer)، به‌ویژه در مدل‌های DIY یا پرینترهای نوع Prusa i3 ساخته شده است هیت‌بد در پرینتر سه‌بعدی وظیفه دارد جلوگیری از انقباض ناگهانی (Warping) در هنگام چاپ را انجام دهد. مشخصات فنی: مدل : هیت بد MK2B ابعاد:   214×214 میلی‌متر جنس برد     فایبرگلاس مقاوم (FR4 PCB) با پوشش مسی ولتاژ کاری     12 ولت یا 24 ولت (دوحالته) توان تقریبی     بین 100 تا 180 وات، بسته به ولتاژ دمای عملیاتی     تا حدود 110°C ویژگی ایمنی     نشانگر LED برای وضعیت داغ بودن لمینت : FR4 1.6 میلی متر سطح قابل چاپ  معمولاً با شیشه بوروسیلیکات یا صفحه آلومینیومی پوشیده می‌شود برای توزیع حرارت یکنواخت‌تر کاربرد : هیت‌بد در پرینتر سه‌بعدی وظیفه دارد جلوگیری از انقباض ناگهانی (Warping) در هنگام چاپ را انجام دهد. با گرم نگه‌داشتن بستر چاپ، باعث می‌شود لایه‌های اول پرینت به‌خوبی بچسبند و قطعه تغییر شکل ندهد — مخصوصاً برای مواد زیر: ABS PETG PLA+ نحوه اتصال و تغذیه: روی برد دو ورودی وجود دارد: ترمینال 12V برای منبع تغذیه معمول پرینترهای خانگی (معمولاً 10 آمپر) ترمینال 24V برای ریپرَپ‌های حرفه‌ای‌تر با گرمایش سریع‌تر نکته: فقط یکی از دو ترمینال را باید متصل کنید، نه هر دو! نکات ایمنی هنگام استفاده: حتماً از ماسفت (MOSFET) یا ماژول رله حرارتی مجزا بین برد کنترل و هیت‌بد استفاده شود تا از سوختن برد جلوگیری گردد. تا خاموش شدن LED صبر کنید قبل از لمس. از سنسور حرارتی (Thermistor) استفاده کنید تا دمای هیت بد کنترل شود. نظر بدهید لطفا وارد شوید یا ثبت نام کنید تا نظر بدهید محصولات مرتبط هیت بد 214*214 (PCB Heatbed) مدل MK2B Dual Power هیت‌بد مدل MK2B یکی از پرکاربردترین صفحات گرم‌کن برای پرینترهای سه‌بعدی (3D Printer)، به‌ویژه در مدل.. 1,362,400 تومان اضافه به سبد خرید هیت بد ( PCB Heatbed Bed) پرینترهای سه بعدی دلتا هیت بد پرینتر 3 بعدی زیر قطعه پرینت سه بعدی قرار می گیرد و با استفاده از اتصالات (پیچ و فنر) به سازه.. {ناموجود} اضافه به سبد خرید هیت بد PCB Heat Bed MK2B ابعاد 214mmX214mm این هیت بد Heatbed در دو ولتاژ 12 و 24 ولت کار می کند که امکان استفاده از آن را با منابع تغذیه 12 ول.. {ناموجود} اضافه به سبد خرید هیت بد آلومینیومی MK3 پرینتر سه بعدی در ابعاد 220x220x3 یکی از مسائل مهم در کار با پرینتر های سه بعدی این است که در هنگام 
+          <t>هیت بد 214*214 (PCB Heatbed) مدل MK2B Dual Power/ نمونه ساز info@nemonehsaz.com   |   04136674173  = 09144100446 حساب کاربری عضویت ورود لیست دلخواه (0) جستجو جستجو سبد خرید 0 محصول سبد خرید شما خالی است! دسته بندی ها پرینتر سه بعدی پرینتر سه بعدی (4) قلم سه بعدی (3) فیلامنت پرینتر سه بعدی فیلامنت PLA PLUS برند SUNLU (سانلو ) (31) فیلامنت PLA قطر 1.75 میلیمتر  (30) فیلامنت PLA PLUS پلاس ایسان eSUN PLA PRO PLUS  (29) فیلامنت +PLA پلاس ایسان سرعت بالا High Speed (4) فیلامنت ABS PLUS eSUN ( ABS+) (29) فیلامنت PC پلی کربنات 1.75 (PC Polycarbonate) (4) فیلامنت PETG ایسان PETG filament eSUN (20) فیلامنت PVA پرینتر سه بعدی (محلول در آب) (2) فیلامنت چوب Wood PLA (2) فیلامنت انعطاف پذیر Flexible قطر 1.75 (23) فیلامنت Silk PLA ایسان (  ابریشمی ) (24) فیلامنت فیبر کربن PA-CF 1.75 (11) فیلامنت HIPS قطر 1.75mm  (1) فیلامنت متال ePLA Metal - فیلامنت فلز    (5) فیلامنت PCL قطر 1.75 (3) فیلامنت PEEK Pro ایسان  (1) فیلامنت تمیز کننده نازل پرینتر سه بعدی eCleaning eSUN (2) فیلامنت ASA قطر 1.75 میلی متر(ASA filament) (3) فیلامنت PA نایلون PA Nylon (2) فیلامنت PETG بسته 100 گرمی (PETG Filament) (14) فیلامنت نایلون-پشم شیشه PA-GF (2) فیلامنت POM (3) قطعات پرینتر سه بعدی اکسترودر پرینتر سه بعدی 3D printer extruder (48) قطعات الکترونیکی (187) قطعات الکتریکی (37) قطعات جانبی (29) قطعات مکانیکی  (777) محفظه آلومینیومی هیتر Heater block 3d printer (28) نازل اکسترودر (نازل پرینتر سه بعدی ) (227) قطعات مکانیکی انرژی چین زنجیر محافظ کابل (8) جوراب کابل (17) کوپلینگ یونیور سال-Universal Couplings (25) مهره (92) واشر (7) اسپیسر Spacer (25) اتصالات پروفیل آلومینیوم (39) انواع پیچ (180) ماشین ابزار و CNC ابزار الات و تجهیزات (137) قطعات الکترونیکی CNC (13) قطعات مکانیکی CNC (348) کانکتور شفت سه نظام  (40) رباتیک قطعات رباتیک (8) موتور  (5) موتور (39) خدمات پرینت سه بعدی هیت بد 214*214 (PCB Heatbed) مدل MK2B Dual Power هیت بد 214*214 (PCB Heatbed) مدل MK2B Dual Power کد محصول: PCB Heated MK2B Dual Power Bed Red موجودی: 3 بازدید: 25457 قیمت : 1,362,400 تومان تعداد : اضافه به سبد خرید 0 نظر / نظر بدهید توضیحات نظرات (0) هیت‌بد مدل MK2B یکی از پرکاربردترین صفحات گرم‌کن برای پرینترهای سه‌بعدی (3D Printer)، به‌ویژه در مدل‌های DIY یا پرینترهای نوع Prusa i3 ساخته شده است هیت‌بد در پرینتر سه‌بعدی وظیفه دارد جلوگیری از انقباض ناگهانی (Warping) در هنگام چاپ را انجام دهد. مشخصات فنی: مدل : هیت بد MK2B ابعاد:   214×214 میلی‌متر جنس برد     فایبرگلاس مقاوم (FR4 PCB) با پوشش مسی ولتاژ کاری     12 ولت یا 24 ولت (دوحالته) توان تقریبی     بین 100 تا 180 وات، بسته به ولتاژ دمای عملیاتی     تا حدود 110°C ویژگی ایمنی     نشانگر LED برای وضعیت داغ بودن لمینت : FR4 1.6 میلی متر سطح قابل چاپ  معمولاً با شیشه بوروسیلیکات یا صفحه آلومینیومی پوشیده می‌شود برای توزیع حرارت یکنواخت‌تر کاربرد : هیت‌بد در پرینتر سه‌بعدی وظیفه دارد جلوگیری از انقباض ناگهانی (Warping) در هنگام چاپ را انجام دهد. با گرم نگه‌داشتن بستر چاپ، باعث می‌شود لایه‌های اول پرینت به‌خوبی بچسبند و قطعه تغییر شکل ندهد — مخصوصاً برای مواد زیر: ABS PETG PLA+ نحوه اتصال و تغذیه: روی برد دو ورودی وجود دارد: ترمینال 12V برای منبع تغذیه معمول پرینترهای خانگی (معمولاً 10 آمپر) ترمینال 24V برای ریپرَپ‌های حرفه‌ای‌تر با گرمایش سریع‌تر نکته: فقط یکی از دو ترمینال را باید متصل کنید، نه هر دو! نکات ایمنی هنگام استفاده: حتماً از ماسفت (MOSFET) یا ماژول رله حرارتی مجزا بین برد کنترل و هیت‌بد استفاده شود تا از سوختن برد جلوگیری گردد. تا خاموش شدن LED صبر کنید قبل از لمس. از سنسور حرارتی (Thermistor) استفاده کنید تا دمای هیت بد کنترل شود. نظر بدهید لطفا وارد شوید یا ثبت نام کنید تا نظر بدهید محصولات مرتبط هیت بد 214*214 (PCB Heatbed) مدل MK2B Dual Power هیت‌بد مدل MK2B یکی از پرکاربردترین صفحات گرم‌کن برای پرینترهای سه‌بعدی (3D Printer)، به‌ویژه در مدل.. 1,362,400 تومان اضافه به سبد خرید هیت بد ( PCB Heatbed Bed) پرینترهای سه بعدی دلتا هیت بد پرینتر 3 بعدی زیر قطعه پرینت سه بعدی قرار می گیرد و با استفاده از اتصالات (پیچ و فنر) به سازه.. {ناموجود} اضافه به سبد خرید هیت بد PCB Heat Bed MK2B ابعاد 214mmX214mm این هیت بد Heatbed در دو ولتاژ 12 و 24 ولت کار می کند که امکان استفاده از آن را با منابع تغذیه 12 ول.. {ناموجود} اضافه به سبد خرید هیت بد آلومینیومی MK3 پرینتر سه بعدی در ابعاد 220x220x3 یکی از مسائل مهم در کار با پرینتر های سه بعدی این است که در هنگام 
 خشک شدن ماده ی پلاستیکی مذاب پری.. {ناموجود} اضافه به سبد خرید هیت بد پرینتر سه بعدی ابعاد 214mmX214mm ترمیستور داخلی برای اینکه چاپهای سه بعدی (پرینت سه بعدی ) بتوانند به بستر چاپ بچسبند باید گرم شود برای این منظور با.. {ناموجود} اضافه به سبد خرید هیت بد کیفیت فوق العاده 235-235mm با سیم و سنسور داخلی PCB Heat Bedقدرت: ۱۲-۲۴ ولتمناسب برای پرینتر های سه بعدی ریپرپاندازه: ۲۳۵*۲۳5 میلی متر.. {ناموجود} اضافه به سبد خرید هیت بد PCB Heated Bed MK2A 328x328mm با سیم و سنسور هیت بد زیر قطعه پرینت سه بعدی قرار می گیرد و با استفاده از اتصالات (پیچ و
  فنر ) به سازه پرینتر متص.. {ناموجود} اضافه به سبد خرید هیت بد آلومینیومی مدل MK2A در ابعاد 328X328X3 میلیمتر هیت بد آلومینیومی MK2A سایز 328x328mm مشخصات فنی :مدل :MK2aضخامت: 3 میلی مترابعاد کلی :328 * 328 میل.. {ناموجود} اضافه به سبد خرید هیت بد سیلیکونی Silicone در ابعاد 300X300 میلی متر این کالا شامل مرجوعی نمی باشد لطفا در خرید خود دقت فرمایید دمای کار: -۶۰ تا +۲۳۰ .Cعرض: ۴۸اینچولتاژ:.. {ناموجود} اضافه به سبد خرید هیت بد آلومینیومی MK3 214X214mm  با سیم و سنسور هیت بد تمام آلومینیومی  مخصوص پرینترهای سه بعدی در دو  ولتاژ کاری 12 و 24 ولت برای پرینت ن.. {ناموجود} اضافه به سبد خرید هیت بد آلومینیومی MK2A سایز 328x328mm با سیم و سنسور در شرایط ولتاژ 12 ولت فقط می تواند تا 60 درجه گرم کند  جریان از طریق 
 مقاومت گرم می شود و توان.. {ناموجود} اضافه به سبد خرید هیت بد MK2A PCB Heated Bead سایز 328x328 میلیمتر با سیم و سنسور هیت بد زیر قطعه پرینت سه بعدی قرار می گیرد و با استفاده از اتصالات (پیچ و فنر ) به سازه پرینتر متصل .. {ناموجود} اضافه به سبد خرید هیت بد مدل PCB Heat Bed MK2B سفید 214mmX214mm هیت بد پرینتر سه بعدی MK2B برای استفاده در چاپگرهای 3D RepRap، Mendel، Prusa مناسب است. اندازه آن مش.. {ناموجود} اضافه به سبد خرید هیت بد PCB Heated Bed مدل MK2A ابعاد 328X328 میلیمتر هیت بد  گرم کننده صفحه زیرین پرینترهای سه بعدی هیت بد نام دارد که یک مدار چاپی است که توسط دو ع.. {ناموجود} اضافه به سبد خرید هیت بد PCB Heated Bed مدل MK2A درابعاد 300X300 میلیمتر مدل : MK2aضخامت : 2 میلی متر اندازه کلی : 328mmX328mmاندازه مورد استفاده: 300mX300mولتاژ کار : 12 ول.. {ناموجود} اضافه به سبد خرید هیت بد آلومینیومی 235X235mm مدل CR10-S Ender-3-S این هیت بد با مواد آلیاژ آلومینیومی ساخته شده و با عملکرد گرمای بسیار خوب با ضخامت 3 میلی متر و با و.. {ناموجود} اضافه به سبد خرید هیت بد آلومینیومی پرینترهای سه بعدی Anet ET4 به طور کلی اگر بخواهیم در مورد عملکرد هیت بد توضیح بدهیم این است که هیت بد زیر قطعه پرینت سه بعدی قر.. {ناموجود} اضافه به سبد خرید هیت بد آلومینیومی پرینترهای سه بعدی Anet ET5 به طور کلی اگر بخواهیم در مورد عملکرد هیت بد توضیح بدهیم این است که هیت بد زیر قطعه پرینت سه بعدی قر.. {ناموجود} اضافه به سبد خرید برچسب ها: هیت بد , هیت بد پرینتر سه بعدی , قطعات الکتریکی , هیت بد 214*214 (PCB Heatbed) مدل MK2B Dual Power خبرنامه با عضویت در خبرنامه ما از آخرین اخبار مطلع شوید! اطلاعات درباره ما آموزش نمونه ساز سیستم رباتیک پرینتر سه بعدی شرایط و قوانین شکایات نمایندگی های فروشگاه نمونه ساز استرداد محصول خدمات مشتریان تماس با ما استرداد محصول نقشه سایت محصولات ویژه تولید کنندگان کارت هدیه حساب کاربری بازاریابی حساب کاربری تاریخچه سفارش ها لیست دلخواه استرداد محصول اشتراک خبرنامه تماس با ما آذربایجان شرقی-تبریز-میدان شهید فهمیده-رشدیه ولی امر میدان فرهنگ دوم خیابان شفق یک شمالی نبش یاس ۵ پلاک ۷۳۲ info@nemonehsaz.com 04136674173  = 09144100446 نمونه ساز در شبکه های اجتماعی پشتیبانی و توسعه توسط اپن کارت فارسی نمونه ساز © 1405 بالا</t>
@@ -839,10 +836,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>13624000</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3" t="n">
         <v>13624000</v>
       </c>
     </row>
@@ -853,27 +850,23 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>https://elecohm.com/product/%da%a9%d8%a7%d8%a8%d9%84-usb-%d9%be%d8%b1%d9%8a%d9%86%d8%aa%d8%b1-30-%d8%b3%d8%a7%d9%86%d8%aa%db%8c%d9%85%d8%aa%d8%b1-%d9%85%d9%86%d8%a7%d8%b3%d8%a8-%d8%a8%d8%b1%d8%a7%db%8c-%d9%be%d8%b1/</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>کابل USB پرينتر 30 سانتی‌متر مناسب برای پروگرام بردهای آردوینو - فروشگاه اهم الکترونیک Skip to navigation Skip to main content به اهم الکترونیک، مرجع فروش قطعات الکترونیک و رباتیک خوش آمدید ارتباط با ما ساعت کاری: 09:30 تا 13:00 | 17:30 تا 20:00 034-32460892 034-32460892 ساعت کاری: 09:30 تا 13:00 | 17:30 تا 20:00 انتخاب دسته بندی انتخاب دسته بندی ابزار آچار انبردست، دم باریک و سیم چین انواع پراب انواع پنس و کاتر چسب – اسپری سایر تجهیزات فازمتر و پیچ گوشتی مته و ابزار سوراخ کاری مولتی متر نوک هویه – المنت هویه و ابزار لحیم گیره مونتاژ و پایه هویه باتری و تغذیه باتری های سکه ای باتری های قلمی و نیم قلمی باتری های کتابی جاباتری سایر باتری ها شارژر باتری منبع تغذیه و آداپتور بردهای توسعه آردوینو بردهای آردوینو شیلدهای آردوینو کیس و نگهدارنده لوازم جانبی آردوینو رسپبری پای بردهای رسپبری پای دوربین های رسپبری پای لوازم جانبی رسپبری پای میکروکنترلرها ESP32 ESP8266 STM سایر میکروکنترلرها برق و ساختمان تجهیزات جانبی درایور و کنترلر موتور رباتیک اسپیسر پیچ و مهره قفل برقی و سلونوئید سنسورها اولتراسونیک تشخیص حرکت تشخیص سطح و جریان مایعات تشخیص گاز حسگر مجاورتی دما و رطوبت رنگ – نور – تصویر زاویه سنج صوت فشار و ارتفاع لرزش – نیرو مادون قرمز مغناطیس و قطب نما نبض و فشار خون قطعات الکترونیکی LED و تجهیزات LED اوال و کلاهی آی سی IC آپ امپ OP-AMP آمپلی فایر آی سی های انکدر و دیکدر اپتوکوپلر تایمر تراشه CMOS درایور سایر تراشه ها سوئیچینگ میکروکنترلرها انواع خازن خازن MKT – MKP خازن الکترولیت SMD خازن الکترولیتی خازن تانتالیوم خازن تانتالیوم SMD خازن سرامیکی – عدسی خازن مولتی لایر انواع دیود پل دیودها دیود زنر دیود های TVS دیودهای Fast دیودهای شاتکی انواع سگمنت انواع سلف سلف SMD سلف بشکه ای سلف تورویدی سلف مقاومتی انواع فیوز جا فیوزی فیوز SMD فیوز حرارتی فیوز قابل برگشت فیوز گچی فیوزهای شیشه ای میکرو فیوز گرد میکرو فیوز مکعبی انواع مقاومت پتانسیومتر ترمیستور NTC مقاومت 1 وات مقاومت 2 وات مقاومت 3 وات مقاومت SMD 1206 مقاومت شانه ای – Array مولتی ترن ولوم برد بورد پین هدر ترانزیستورها ترانزیستورهای BJT ماسفت MOSFET ترایاک ترمینال تریستور دیاک رگولاتور رله سوكت – کانکتور باکس هدر و IDC جک اسپیکر و میکروفن سوکت IC معمولی سوکت IC نظامی سوکت سیم کارت – حافظه فیش و تبدیل پاور فیش و جک آداپتور فن و محافظ فن فیبر – برد سوراخ دار قطعات صوتی کریستال کلید – سوئیچ تک سوئیچ دیپ سوئیچ شستی کلید راکر میکروسوئیچ لیزر مبدل DIP هیت سینک – المان های حرارتی وریستور کابل، سیم و کانکتور انواع کانکتور سیم دار جامپر و سیم جامپر سایر سیم و کابل کابل فلت کابل های انتقال دیتا و USB کابل و گیره سوسماری کانکتورها ماژول ها پروگرامرها دما و رطوبت سایر ماژول ها سنسور بخار سرد کی پد و جوی استیک ماژول GPS-GPRS ماژول رله و سوییچ ماژول شبکه ماژول نمایشگر ماژول های RF ماژول های RFID ماژول های پخش صدا ماژول های پردازش تصویر ماژول های تاریخ و ساعت ماژول های تغذیه – ولتاژ – جریان ماژول های شتاب سنج و ژیروسکوپ ماژول های مبدل ماژول های محافظ شارژ باتری ماژول های مولد پالس ماژول ولتمتر و آمپرمتر مخابرات آنتن بلوتوث کنترل از دور مبدل ها وای فای WiFi موتور و عملگر سرور موتور جستجو 0 محصول 0 تومان 0 علاقه مندی 0 مقایسه منو 0 محصول دسته بندی کالاها ماژول ها پروگرامرها دما و رطوبت سایر ماژول ها سنسور بخار سرد کی پد و جوی استیک ماژول GPS-GPRS ماژول رله و سوییچ ماژول شبکه ماژول نمایشگر ماژول های RF ماژول های RFID ماژول های پخش صدا ماژول های پردازش تصویر ماژول های تاریخ و ساعت ماژول های تغذیه – ولتاژ – جریان ماژول های ذخیره داده ماژول های شتاب سنج و ژیروسکوپ ماژول های مبدل ماژول های محافظ شارژ باتری ماژول های مولد پالس ماژول ولتمتر و آمپرمتر سنسورها اولتراسونیک تشخیص حرکت تشخیص سطح و جریان مایعات تشخیص گاز حسگر مجاورتی دما و رطوبت رنگ – نور – تصویر زاویه سنج صوت فشار و ارتفاع لرزش – نیرو مادون قرمز مغناطیس و قطب نما نبض و فشار خون بردهای توسعه آردوینو بردهای آردوینو شیلدهای آردوینو کیس و نگهدارنده لوازم جانبی آردوینو رسپبری پای بردهای رسپبری پای دوربین های رسپبری پای لوازم جانبی رسپبری پای میکروکنترلرها درایور و کنترلر موتور موتور و عملگر رباتیک اسپیسر پیچ و مهره قفل برقی و سلونوئید مخابرات آنتن بلوتوث مبدل ها وای فای WiFi قطعات الکترونیکی ابزار آچار انبردست، دم باریک و سیم چین فازمتر و پیچ گوشتی مته و ابزار سوراخ کاری نوک هویه – المنت هویه و ابزار لحیم برق و ساختمان باتری و تغذیه باتری های سکه ای باتری های قلمی و نیم قلمی باتری های کتابی سایر باتری ها جاباتری کابل، سیم و کانکتور کنترل از دور صفحه نخست فروشگاه سبد خرید پنل کاربری محصولات حراجی شرایط خرید پیگیری سفارشات درباره ما تماس با ما % تخفیف های روز خانه » فروشگاه » کابل USB پرينتر 30 سانتی‌متر مناسب برای پروگرام بردهای آردوینو ماژول مبدل CAN TO TTL TJA1051 MODULE 158,000 تومان بازگشت به محصولات کابل مبدل USB به سریال TTL مدل PL2303HX 185,000 تومان بزرگنمایی تصویر کابل USB پرينتر 30 سانتی‌متر مناسب برای پروگرام بردهای آردوینو 75,000 تومان موجود - کابل USB پرينتر 30 سانتی‌متر مناسب برای پروگرام بردهای آردوینو عدد + افزودن به سبد خرید خرید کنید مقایسه افزودن به علاقه مندی 10 نفر در حال مشاهده این محصول هستند! دسته: آردوینو , بردهای توسعه , لوازم جانبی آردوینو اشتراک گذاری: بستن توضیحات نظرات (0) توضیحات Description Cable For Arduino UNO/MEGA is a Cable for board compatible with arduino (USB A to B). This Can be used for “Arduino Uno”, “Arduino Mega 2560″ compatible boards or any board with the USB female A port of your computer. Specifications Type: Type-A to Type-B Color: Blue Length: 30 cm. Package Includes 1 x Cable For Arduino UNO/MEGA (USB A to B)-30 cm نظرات (0) نقد و بررسی‌ها هنوز بررسی‌ای ثبت نشده است. اولین کسی باشید که دیدگاهی می نویسد “کابل USB پرينتر 30 سانتی‌متر مناسب برای پروگرام بردهای آردوینو” برای فرستادن دیدگاه، باید وارد شده باشید. محصولات مرتبط مقایسه برد آردوینو Digispark ATtiny85 USB بردهای توسعه , آردوینو , بردهای آردوینو ATTINY85 Development Board The ATtiny85 based mini development board is similar to the Arduino, but cheaper and smaller (of course افزودن به علاقه مندی اطلاعات بیشتر مشاهده سریع مقایسه برد آردوینو مگا Arduino Mega 2560 ch340 بردهای توسعه , آردوینو , بردهای آردوینو This board is quite similar to other Arduino Mega 2560 boards, except that instead of using ATMEGA16U2, the CH340G IC افزودن به علاقه مندی اطلاعات بیشتر مشاهده سریع مقایسه ست سه تایی هیت سینک آلومینیومی ویژه برد رسپبری پای بردهای توسعه , رسپبری پای , لوازم جانبی رسپبری پای افزودن به علاقه مندی اطلاعات بیشتر مشاهده سریع مقایسه آردوینو پرومینی 3.3 ولت Arduino Pro Mini بردهای توسعه , آردوینو , بردهای آردوینو 285,000 تومان Pro Mini ATMEGA328P Module 3.3V 8M Interactive Media Development Board Description Professional version Mini is a micro-controller board. It has افزودن به علاقه مندی افزودن به سبد خرید مشاهده سریع مقایسه برد آردوینو پرو میکرو Arduino Pro Micro بردهای توسعه , آردوینو , بردهای آردوینو Pro Micro 5V 16M Mini Leonardo Microcontroller Development Board For Arduino Description This microcontroller development board has 4 channel 10 افزودن به علاقه مندی اطلاعات بیشتر مشاهده سریع مقایسه کابل تبدیل USB به miniUSB مناسب برای برد آردوینو نانو بردهای توسعه , آردوینو , لوازم جانبی آردوینو Cable for Arduino Nano (USB 2.0 A to USB 2.0 Mini B) 30cm The Cable for Arduino Nano (USB 2.0 افزودن به علاقه مندی اطلاعات بیشتر مشاهده سریع مقایسه ماژول دوربین رسپبری پای V1.3 رسپبری پای , دوربین های رسپبری پای , بردهای توسعه RASPBERRY PI CAMERA BOARD V1.3 This is camera module for Raspberry Pi can be used for Raspberry Pi 3 Model افزودن به علاقه مندی اطلاعات بیشتر مشاهده سریع کپی مقایسه هدر برد HK32F103CBT6 میکروکنترلرها , STM , بردهای توسعه SPECIFICATIONS AND FEATURES Type: STM32F103C Blue Pill Card Chip: HK32F103CBT6 Dimensions: 23mm x 53mm PCB Color: Blue Voltage supply: Any افزودن به علاقه مندی اطلاعات بیشتر مشاهده سریع اطلاعات تماس تلفن ثابت: ۰۳۴۳۲۴۶۰۸۹۲ تلفن همراه: 	۰۹۲۰۱۴۰۱۳۲۹ ایمیل: Eleco.ohm@gmail.com آدرس دفتر مرکزی: کرمان، خیابان شهید نامجو (اقبال)، نبش کوچه هفتم تخفیفات و پیشنهاد ها برای اطلاع از آخرین تخفیف‌ها و جدیدترین کالاها در خبرنامه ثبت‌نام کنید. [mc4wp_form id="68"] نماد اعتماد تمامی حقوق این وب سایت متعلق فروشگاه اینترنتی اهم الکترونیک می باشد. جستجو منو دسته بندی ها ماژول ها دما و رطوبت پروگرامرها سایر ماژول ها ماژول ولتمتر و آمپرمتر ماژول شبکه ماژول نمایشگر ماژول های پردازش تصویر ماژول رله و سوییچ ماژول GPS-GPRS ماژول های تغذیه – ولتاژ – جریان ماژول های RFID ماژول های پخش صدا ماژول های مولد پالس ماژول های RF ماژول های تاریخ و ساعت ماژول های ذخیره داده ماژول های شتاب سنج و ژیروسکوپ ماژول های مبدل کی پد و جوی استیک ماژول های محافظ شارژ باتری سنسور بخار سرد سنسورها رنگ – نور – تصویر تشخیص حرکت زاویه سنج حسگر مجاورتی تشخیص سطح و جریان مایعات تشخیص گاز ژیروسکوپ IMU / AHRS اولتراسونیک GPS و مکان یابی اثر انگشت امواج عصبی و مغزی جریان و ولتاژ مغناطیس و قطب نما مادون قرمز لرزش – نیرو لمس صوت فشار و ارتفاع بردهای توسعه آردوینو بردهای آردوینو شیلدهای آردوینو کیس و نگهدارنده لوازم جانبی آردوینو کیت های آردوینو رسپبری پای بردهای رسپبری پای دوربین های رسپبری پای کیت های رسپبری پای لوازم جانبی رسپبری پای میکروکنترلرها ESP32 ESP8266 STM سایر میکروکنترلرها درایور و کنترلر موتور موتور و عملگر سرور موتور رباتیک مخابرات آنتن اینترنت و شبکه بلوتوث انتقال داده مودم GSM کنترل از دور مبدل ها قطعات الکترونیکی تریستور انواع خازن خازن الکترولیتی خازن مولتی لایر خازن تانتالیوم SMD خازن تانتالیوم خازن MKT – MKP خازن سرامیکی – عدسی خازن پلی استر خازن SMD پکیج 1206 خازن الکترولیت SMD انواع مقاومت مقاومت شانه ای – Array مقاومت SMD 1206 مقاومت 3 وات مقاومت 2 وات مقاومت 1 وات ولوم مولتی ترن تک سوئیچ رله آی سی IC سایر تراشه ها سوئیچینگ برد بورد آمپلی فایر انواع دیود دیودهای شاتکی پل دیودها دیودهای Fast دیود زنر دیود های TVS انواع سگمنت انواع سلف سلف SMD سلف بشکه ای سلف تورویدی سلف مقاومتی انواع فیوز میکرو فیوز گرد میکرو فیوز مکعبی فیوزهای شیشه ای فیوز گچی فیوز قابل برگشت فیوز SMD فیوز حرارتی جا فیوزی اپتوکوپلر رگولاتور پتانسیومتر آپ امپ OP-AMP دیاک ترایاک ترانزیستورهای BJT درایور تراشه CMOS آی سی های انکدر و دیکدر ترانزیستورها سایر میکروکنترلرها کریستال ماسفت MOSFET سایر تراشه ها لیزر مبدل DIP کلید – سوئیچ شستی کلید راکر دیپ سوئیچ LED اوال و کلاهی LED و تجهیزات سوكت – کانکتور باکس هدر و IDC فیش و جک آداپتور سوکت IC نظامی سوکت IC معمولی فیش و تبدیل پاور سوکت سیم کارت – حافظه جک اسپیکر و میکروفن پین هدر ترمینال فیبر – برد سوراخ دار قطعات صوتی فن و محافظ فن تایمر ابزار انواع پنس و کاتر آچار انبردست، دم باریک و سیم چین انواع پراب فازمتر و پیچ گوشتی مولتی متر گیره مونتاژ و پایه هویه فازمتر و پیچ گوشتی مته و ابزار سوراخ کاری سایر تجهیزات چسب – اسپری باتری و تغذیه باتری های سکه ای باتری های کتابی باتری های قلمی و نیم قلمی سایر باتری ها منبع تغذیه و آداپتور شارژر باتری جاباتری کابل، سیم و کانکتور کابل و گیره سوسماری کانکتورها سایر سیم و کابل انواع کانکتور سیم دار جامپر و سیم جامپر تجهیزات جانبی صفحه نخست فروشگاه سبد خرید پنل کاربری محصولات حراجی شرایط خرید پیگیری سفارشات درباره ما تماس با ما علاقه مندی مقایسه ورود / ثبت نام سبد خرید بستن ورود close ورود | ثبت نام ورود به سایت یا ثبت نام ورود با رمز یکبار مصرف فراموشی رمز عبور ورود به سایت کلمه عبور جدید تغییر کلمه عبور نام شما نام خانوادگی شما ایمیل کلمه عبور ذخیره کردن سایدبار فروشگاه 0 محصول سبد خرید حساب کاربری من منو کابل USB پرينتر 30 سانتی‌متر مناسب برای پروگرام بردهای آردوینو 75,000 تومان موجود - کابل USB پرينتر 30 سانتی‌متر مناسب برای پروگرام بردهای آردوینو عدد + افزودن به سبد خرید خرید کنید مقایسه افزودن به علاقه مندی ورود | ثبت نام ورود به سایت یا ثبت نام ورود با رمز یکبار مصرف فراموشی رمز عبور ورود به سایت کلمه عبور جدید تغییر کلمه عبور نام شما نام خانوادگی شما ایمیل کلمه عبور ذخیره کردن</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>750000</v>
-      </c>
-      <c r="G11" t="n">
-        <v>750000</v>
-      </c>
+          <t>ERROR: HTTPSConnectionPool(host='elecohm.com', port=443): Max retries exceeded with url: /product/%DA%A9%D8%A7%D8%A8%D9%84-usb-%D9%BE%D8%B1%D9%8A%D9%86%D8%AA%D8%B1-30-%D8%B3%D8%A7%D9%86%D8%AA%DB%8C%D9%85%D8%AA%D8%B1-%D9%85%D9%86%D8%A7%D8%B3%D8%A8-%D8%A8%D8%B1%D8%A7%DB%8C-%D9%BE%D8%B1/ (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='elecohm.com', port=443) at 0x21cd66916d0&gt;, 'Connection to elecohm.com timed out. (connect timeout=30)'))</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -882,7 +875,7 @@
       <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>https://roboeq.ir/products/detail/0201059/%DA%86%D8%B1%D8%AE-%D8%A8%D8%A7%D8%B1%DB%8C%DA%A9-5-%D8%B3%D8%A7%D9%86%D8%AA%DB%8C-%D9%85%D8%AA%D8%B1-%D8%A2%D9%84%D9%88%D9%85%DB%8C%D9%86%DB%8C%D9%88%D9%85%DB%8C-%D8%A8%D8%A7-%D8%B3%D9%88%D8%B1%D8%A7%D8%AE-4/</t>
         </is>
@@ -890,7 +883,7 @@
       <c r="D12" t="inlineStr">
         <is>
           <t>چرخ باریک 5 سانتی متر آلومینیومی با سوراخ 4 | روبوایکیو سبد خرید خالی است راهنمای خرید ۰۳۱۳۲۴۰۴۴۳۹ ۰۳۱۳۲۴۰۴۴۳۸ جزئیات بیشتر دسته‌بندی کالاها بدون نتیجه نیمه هادی دیود، ترانزیستور و تریستور ترانزیستور تریستور دیود پردازنده Embedded پردازنده تراشه منطقی برنامه پذیر ماژول منطقی برنامه پذیر ماژول و کیت توسعه میکروکنترلر و پردازنده میکروکنترلر مدیریت و کنترل توان آی سی تصحیح ضریب توان آی سی درایور LED آی سی درایور و کنترلر موتور آی سی مبدل سوئیچینگ AC به DC آی سی مدیریت باتری آی سی نظارت و ریست رگولاتور و کنترل کننده سوئیچ و مالتی پلکسر قدرت گیت درایور مبدل RMS به DC مرجع ولتاژ RFID و RF/IF آنتن RF و RFID آی سی RF و IR تگ و ماژول RFID شیلد RF ماژول فرستنده/گیرنده RF آی سی منطقی ALU اشمیت تریگر انکودر منطقی بافر و لاین درایور تشخیص و تصحیح خطا تغییر سطح منطقی جمع کننده و تفریق کننده منطقی دیکودر و دی مالتی پلکسر رجیستر شمارنده و شیفت رجیستر فرستنده و گیرنده باس فلیپ فلاپ گیت منطقی لچ مالتی پلکسر مقایسه کننده منطقی مولتی ویبراتور تقویت کننده و مقایسه کننده آپ امپ آمپلی فایر مولتی مدیا تقویت کننده RF تقویت کننده ابزاری ضرب کننده و تقسیم کننده آنالوگ ماژول آمپلی فایر مقایسه کننده رابط و اینترفیس آی سی رابط USB ایزولاتور دیجیتال رابط UART رابط با کاربرد خاص رابط سنسور و آشکارساز ضبط و پخش صدا فرستنده و گیرنده خط باس گسترش دهنده ورودی/خروجی ماژول رابط کنترلر تاچ اسکرین کنترلر و درایور نمایشگر جمع آوری و تبدیل داده Sample and Hold پتانسیومتر دیجیتال ماژول مبدل داده مبدل داده مبدل ولتاژ به فرکانس و فرکانس به ولتاژ حافظه تراشه حافظه کارت حافظه و فلش مموری کنترلر حافظه ماژول حافظه کلاک و زمان بندی CDR PLL DDS RTC بافر و درایور کلاک تایمر ماژول کلاک و زمان بندی مولد کلاک و سینتی سایزر ارتباطات آی سی CODEC آی سی کنترل کننده و پردازشگر شبکه پروتکل و شبکه تراشه مودم تلفن ثابت و رادیو حذف کننده ECHO ماژول شبکه و اترنت سوئیچ الکترونیکی سوئیچ اترنت مالتی پلکسر آنالوگ و باس سوئیچ آی سی خودرو پک آی سی های پرکاربرد مولتی مدیا آی سی موزیک و آژیر سایر آی سی های مولتی مدیا آمپلی فایر مولتی مدیا المان پسیو مقاومت شنت پک مقاومت های پرکاربرد لوازم جانبی مقاومت مقاومت ثابت مقاومت متغیر خازن پک خازن های پرکاربرد خازن ثابت خازن متغیر سلف، سیم پیچ و چوک پک سلف های پرکاربرد سلف ثابت سیم لاکی هسته فریت اسیلاتور، کریستال و رزوناتور اسیلاتور کریستال فیلتر چوک مد مشترک فریت بید فیلتر EMI/RFI ماژول فیلتر EMI ابزارآلات و تجهیزات ابزارآلات ابزار مکانیکی ابزارآلات برقی ابزارآلات دستی اتصالات و قطعات مکانیکی انتقال توان مکانیکی بست و اتصالات مکانیکی تجهیزات اندازه گیری و آزمایشگاهی تجهیزات آزمایشگاهی تجهیزات اندازه گیری لوازم جانبی تجهیزات آزمایشگاهی تجهیزات لحیم کاری و مونتاژ ابزار مونتاژ خمیر قلع، روغن لحیم و سیم لحیم لوازم جانبی لحیم کاری و مونتاژ میکروسکوپ و ذره بین هویه، هیتر و وان قلع اسپری و مواد تمیزکننده جعبه و نظم دهنده جعبه مدار نظم دهنده چسب و مواد شیمیایی اسپری و مواد تمیزکننده چسب رنگ اسید و رنگ مدار چاپی مواد ظهور و پاک کننده الکترومکانیکال موتور استپ موتور سرو موتور AC سرو موتور DC لوازم جانبی موتور ماژول درایور و کنترلر موتور موتور AC موتور DC موتور DC براشلس موتور پمپ میکرو موتور رله سوکت رله رله پاور رله حالت جامد (SSR) رله سیگنال ماژول رله رید رله سلونوئید و عملگر سوئیچ الکترومکانیکال تک سوئیچ جوی استیک و سوئیچ navigation دیپ سوئیچ رید رله سایر سوئیچ ها کلید راکر کلید شستی و فشاری کلید کشوئی کلید کلنگی کیپد لوازم جانبی سوئیچ میکروسوئیچ المان صوتی بازر و آلارم بلندگو سنسور صوتی و میکروفون ماژول صوتی انکودر انکودر مغناطیسی انکودر مکانیکی انکودر نوری دیسک انکودر رباتیک شاسی و بدنه ربات المان و سازه رباتیک شاسی آماده شاسی لوله ای شاسی مستطیلی چرخ ربات چرخ خورشیدی چرخ هرزگرد چرخ همه جهته سایر چرخ ها اتصالات و قطعات مکانیکی انتقال توان مکانیکی بست و اتصالات مکانیکی کتاب رباتیک کیت رباتیک کیت ربات پروازی کیت سایر ربات ها موتور استپ موتور سرو موتور AC سرو موتور DC لوازم جانبی موتور ماژول درایور و کنترلر موتور موتور AC موتور DC موتور DC براشلس موتور پمپ میکرو موتور ملخ و پروانه پروانه ملخ پروازی ربات پروازی رادیو کنترلر فلایت کنترلر کیت ربات پروازی ملخ پروازی مدل های آماده لوازم جانبی مدل های آماده مدل الکتریکی تغذیه، توان و قدرت باتری لوازم جانبی باتری باتری غیر قابل شارژ باتری قابل شارژ پاوربانک و لوازم جانبی شارژر باتری فندکی خودرو ماژول محافظ و شارژ و دشارژ باتری نگهدارنده و اتصالات باتری منبع تغذیه برق اضطراری اینورتر DC به AC درایور LED سایر منابع تغذیه مبدل AC به AC مبدل AC به DC مبدل DC به DC ماژول درایور و کنترلر موتور منبع تغذیه آزمایشگاهی منبع تغذیه ریلی منبع تغذیه صنعتی ترانسفورمر ترانس های خاص تجهیزات نصب و نگهدارنده بوبین و سیم پیچ ترانس ایزوله و اتوترانس ترانس جریان ترانس صوتی ترانس قدرت سیم لاکی هسته فریت سلول و پنل خورشیدی کانکتور کانکتور ورودی / خروجی کانکتور D شکل کانکتور USB کانکتور اینترفیس کانکتور پاور کانکتور تلفن و شبکه کانکتور دایره ای شکل کانکتور صوتی/تصویری کانکتور مخابراتی کانکتور PCB کانکتور Backplane کانکتور اسلات جامپر و شنت کانکتور FFC-FPC هدر و کانکتور روبردی پین کانکتور لوازم جانبی کانکتور سایر کانکتورها ترمینال بلوکی سرسیم و وایرشو سوکت کانکتور RF کانکتور مموری و سیم کارت سنسور ماژول و برد توسعه سنسور سایر ماژول و برد توسعه سنسور ماژول سنسور اثر انگشت ماژول سنسور تشخیص حرکت و PIR ماژول سنسور جریان ماژول سنسور حرکت و موقعیت ماژول سنسور دما و رطوبت ماژول سنسور فشار ماژول سنسور گاز ماژول سنسور لمسی ماژول سنسور مغناطیسی ماژول سنسور نوری ماژول فاصله سنج ماژول فرستنده و گیرنده مادون قرمز ماژول قطب نما و زاویه سنج سنسور صوتی و میکروفون سنسور دما و رطوبت ترمیستور سنسور دما سنسور دمای صنعتی سنسور رطوبت ترموستات سنسور نوری آشکارساز نوری سنسور تصویر سنسور رنگ سنسور نور محیطی سوئیچ نوری فرستنده و گیرنده مادون قرمز فوتوترانزیستور فوتودیود فتوسل سنسور فشار، لودسل و استرین گیج بخار سرد و پیزوالکتریک لوازم جانبی سنسور سنسور حرکت و موقعیت ژیروسکوپ سنسور تشخیص حرکت و PIR سنسور شیب سنسور لرزش شتاب سنج انکودر سنسور گاز، کیفیت هوا و دود سنسور مغناطیسی سایر سنسورهای مغناطیسی رید رله فرستنده و گیرنده آلتراسونیک سنسور جریان سنسور تاچ خازنی سنسور تشخیص فلز سنسور جریان سیالات و فلومتر سنسور خمیدگی سایر سنسورها سنسور مجاورت روشنایی، نمایشگر و LED بر اساس کاربرد نور پردازی دکوراسیون نور پردازی دیجیتال ویژه تابلوسازی ویژه تعمیرات ویژه تولید ویژه خودرو ویژه رشد گیاه و گلخانه ویژه لاینر و لوستر کنترلر و درایور LED رفلکتور ال ای دی روشنایی برد SMD - COB -DOB بلوک LED سایر تجهیزات روشنایی فلاشر لامپ و پروژکتور ماژول LED دیود LED چیپ ال ای دی DIP چیپ ال ای دی SMD چیپ هدلایت (CSP) چیپ COB لنز ال ای دی مجتمع نمایشگر ماژول نمایشگر نمایشگر LCD نمایشگر LED لنز ال ای دی تکی برد ال ای دی DOB برد ال ای دی COB برد ال ای دی SMD آمپلی فایر ال ای دی سنسور ال ای دی باکس درایور ال ای دی درایور ال ای دی ضد آب درایور بردی جریان ثابت ایزوله و غیر ایزوله ال ای دی نواری لاینر ریموت ال ای دی دیمر شدت نور و دمای رنگ تستر هدلایت تستر ال ای دی ال ای دی لاس وگاسی ال ای دی بلوکی نواری دیجیتال کنترلر دیجیتال LED نواری و شاخه ای و نئون فلکسی لنز و پایه LED لنز تکی لنز مجتمع لوازم جانبی روشنایی، نمایشگر و LED تاچ خازنی و مقاومتی کنترلر تاچ اسکرین کنترلر و آمپلی فایر LED کنترلر و درایور نمایشگر لوازم جانبی روشنایی درایور LED ماژول و ابزار توسعه پروگرامر، دیباگر و شبیه ساز ماژول سایر ماژول های کاربردی بخار سرد و پیزوالکتریک تگ و ماژول RFID ماژول LED ماژول حافظه ماژول درایور و کنترلر موتور ماژول دوربین ماژول رابط ماژول رله ماژول شبکه و اترنت ماژول فرستنده/گیرنده RF ماژول مبدل داده ماژول منطقی برنامه پذیر ماژول نمایشگر ماژول و برد توسعه سنسور ماژول و کیت توسعه میکروکنترلر و پردازنده سوکت و برد تبدیل نرم افزار سیم و کابل سیم سیم برد بوردی و جامپر سیم تک رشته سیم چند رشته سیم لاکی کابل سایر کابل ها کابل USB کابل پاور کابل شبکه کابل صنعتی کابل صوتی/ تصویری کابل فلت / ریبون کابل کواکسیال لوازم جانبی سیم و کابل روکش کابل وارنیش حرارتی سرسیم و وایرشو گلند و سیم گیر تجهیزات نمونه سازی و ساخت لوازم چاپ PCB اسید و رنگ مدار چاپی پک ساخت PCB سایر ملزومات مدار چاپی فیبر مدار چاپی مواد ظهور و پاک کننده لوازم جانبی پرینتر سه بعدی بردبورد و ورابرد پرینتر سه بعدی سیم برد بوردی و جامپر دستگاه تراش و CNC کیت و منابع آموزشی کیت کیت الکترونیک کیت رباتیک مجموعه آموزشی مقدماتی کتاب سایر کتاب ها کتاب برق و الکترونیک کتاب رباتیک اپتوالکتریک اپتوکوپلر و فوتوکوپلر لیزر دیود لیزری گیرنده لیزر لیزر پوینتر ماژول لیزر دوربین سایر دوربین ها لوازم جانبی دوربین ماژول دوربین فیبر نوری سنسور نوری آشکارساز نوری سنسور تصویر سنسور رنگ سنسور نور محیطی سوئیچ نوری فرستنده و گیرنده مادون قرمز فوتوترانزیستور فوتودیود فتوسل میکروسکوپ و ذره بین تجهیزات حرارتی تجهیزات خنک کننده المان سرد کننده فن هیت سینک و رادیاتور چسب، خمیر و پد سیلیکون تجهیزات گرم کننده المان گرم کننده المنت حرارتی لوازم جانبی تجهیزات حرارتی حفاظت از مدار GDT حفاظت از  ولتاژ حفاظت از ولتاژ حفاظت از اضافه جریان فیوز فیوز برگشت پذیر لوازم جانبی فیوز حفاظت از تخلیه الکترواستاتیک (ESD) TVS حذف و کاهش ESD وریستور اتوماسیون و برق صنعتی و ساختمان پنوماتیک برق صنعتی تجهیزات فرمان کنتاکتور تابلو و تجهیزات جانبی چند شاخه و پریز صنعتی رله صنعتی کلید مینیاتوری و محافظ جان کنترلر، حفاظت کننده و نمایشگر منبع تغذیه ریلی منبع تغذیه صنعتی کابل صنعتی روشنایی و برق ساختمان هوشمند سازی چند شاخه، کلید و پریز خانگی محافظ و چند راهی لامپ و پروژکتور لوازم جانبی روشنایی در روبوایکیو بفروشید ثبت سفارش از خارج روبوایکیو کلاب انجمن تخصصی الکترونیک و رباتیک ماشین‌حساب الکترونیک خانه رباتیک چرخ ربات سایر چرخ ها چرخ باریک 5 سانتی متر آلومینیومی با سوراخ 4 شناسه 0201059 4 (3 رای) 0 تصویر ممکن است تفاوت‌های جزیی با کالای ارسالی داشته باشد. اما این تفاوت‌ها تاثیری بر عملکرد و کارایی آن ندارند. بهترین فروشندگان براساس قیمت تعدادی 1 روبوایکیو 480,000 50 روبوایکیو 475,000 100 روبوایکیو 470,000 300 روبوایکیو 465,000 500 روبوایکیو 460,000 1,000 روبوایکیو 455,000 بهترین فروشنده حداقل تعداد قابل سفارش 1 عدد می‌باشد فروشگاه این کالا را با حداقل سفارش عدد موجود دارد. روبوایکیو موجود در انبار روبوایکیو سلامت فیزیکی کالا مشاهده سایر پله های قیمتی ۴۶% ۹۰۰,۰۰۰ ۴۸۰,۰۰۰ افزودن به سبد موجود شد بهم خبر بده قیمت بهتری سراغ دارید؟ ثبت قیمت کمتر نام فروشنده داخلی ۱+ عدد ۵۰+ عدد ۱۰۰+ عدد ۳۰۰+ عدد ۵۰۰+ عدد ۱۰۰۰+ عدد ویژگی‌ها روبوایکیو 480,000 475,000 470,000 465,000 460,000 455,000 سلامت فیزیکی کالا افزودن به سبد مستندات فنی عنوان مقدار وزن ۱۸/۹۱
-گرم عنوان انگلیسی 50mm Narrow Aluminum Robot Wheel 4mm Bore توضیحات محصول مشخصات فنی : قطر کل: 49.9mm جنس: آلومینیوم با روکش لاستیکی برای اصطکاک مناسب قطر سوراخ مرکز: 4mm پهنای کل: 7mm دارای پیچ نگه دارنده شافت در داخل سوراخ مرکز خریداران این کالا موارد زیر را هم خریده‌اند چرخ 4 سانتی متر آلومینیومی با سوراخ 4 سایر چرخ ها موجود ۱,۷۹۰,۰۰۰ روبوایکیو یاتاقان MM 20*20 با سوراخ 4 بست و براکت موجود ۲۹۰,۰۰۰ روبوایکیو شفت 4 میلی متری بوش دار کوپلینگ موجود ۲۶۳,۰۰۰ روبوایکیو چرخ 4 سانتی متر آلومینیومی با سوراخ 3 سایر چرخ ها موجود ۱,۱۶۰,۰۰۰ روبوایکیو شفت 6 میلی متری ساده کوپلینگ موجود ۱۹۳,۰۰۰ روبوایکیو جا موتوری  2825 لوازم جانبی موتور موجود ۶۳,۰۰۰ روبوایکیو شفت 4 میلی متری ساده کوپلینگ با امکان تامین ۱۸۲,۰۰۰ روبوایکیو پرسش و پاسخ دیدگاه‌ها با ثبت درخواست تا ۲ ساعت کاری آینده با شما تماس گرفته خواهد شد با دریافت نمونه می‌توانید با اطمینان خاطر از کیفیت کالا، سفارش خود را ثبت کنید. درصورت دریافت نمونه، گارانتی "تضمین تطابق با نمونه" برای سفارش شما فعال خواهد شد. ثبت درخواست انصراف با زدن روی دکمه تایید، سفارش شما ثبت و تا ۱ روز کاری آینده با شما تماس گرفته خواهد تایید انصراف روزهای کاری شنبه تا پنجشنبه از ساعت ۸:۳۰ الی ۱۷:۳۰ پاسخگوی شما هستیم. ۰۳۱۳۲۴۰۴۴۳۹ — ۰۳۱۳۲۴۰۴۴۳۸ روبوایکیو در شبکه‌های اجتماعی اصفهان، روبروی ارگ جهان‌نما، خیابان سرلت، بن‌بست شماره ۲ ایمان، ساختمان روبوایکیو 
+گرم عنوان انگلیسی 50mm Narrow Aluminum Robot Wheel 4mm Bore توضیحات محصول مشخصات فنی : قطر کل: 49.9mm جنس: آلومینیوم با روکش لاستیکی برای اصطکاک مناسب قطر سوراخ مرکز: 4mm پهنای کل: 7mm دارای پیچ نگه دارنده شافت در داخل سوراخ مرکز خریداران این کالا موارد زیر را هم خریده‌اند چرخ 4 سانتی متر آلومینیومی با سوراخ 4 سایر چرخ ها موجود ۱,۷۹۰,۰۰۰ روبوایکیو یاتاقان MM 20*20 با سوراخ 4 بست و براکت موجود ۲۹۰,۰۰۰ روبوایکیو شفت 4 میلی متری بوش دار کوپلینگ موجود ۲۶۳,۰۰۰ روبوایکیو شفت 6 میلی متری ساده کوپلینگ موجود ۱۹۳,۰۰۰ روبوایکیو جا موتوری  2825 لوازم جانبی موتور موجود ۶۳,۰۰۰ روبوایکیو چرخ 4 سانتی متر آلومینیومی با سوراخ 3 سایر چرخ ها موجود ۱,۱۶۰,۰۰۰ روبوایکیو چرخ 5 سانتی متر پلاستیکی ساده سایر چرخ ها با امکان تامین ۶۰۸,۰۰۰ روبوایکیو پرسش و پاسخ دیدگاه‌ها با ثبت درخواست تا ۲ ساعت کاری آینده با شما تماس گرفته خواهد شد با دریافت نمونه می‌توانید با اطمینان خاطر از کیفیت کالا، سفارش خود را ثبت کنید. درصورت دریافت نمونه، گارانتی "تضمین تطابق با نمونه" برای سفارش شما فعال خواهد شد. ثبت درخواست انصراف با زدن روی دکمه تایید، سفارش شما ثبت و تا ۱ روز کاری آینده با شما تماس گرفته خواهد تایید انصراف روزهای کاری شنبه تا پنجشنبه از ساعت ۸:۳۰ الی ۱۷:۳۰ پاسخگوی شما هستیم. ۰۳۱۳۲۴۰۴۴۳۹ — ۰۳۱۳۲۴۰۴۴۳۸ روبوایکیو در شبکه‌های اجتماعی اصفهان، روبروی ارگ جهان‌نما، خیابان سرلت، بن‌بست شماره ۲ ایمان، ساختمان روبوایکیو 
 کد پستی : ۸۱۳۶۷۴۷۹۱۵ همراه با روبوایکیو آکادمی روبوایکیو انجمن تخصصی الکترونیک و رباتیک فرصت‌های شغلی درباره روبوایکیو خدمات و پشتیبانی گزارش مشکل در سایت انتقاد و پیشنهاد پاسخ به سوالات متداول تماس با فروشگاه راهنمای خرید از روبوایکیو ثبت سفارش از خارج قوانین خرید راهنمای خرید کیفیت کالاها رویه‌های بازگشت کالا ارائه فاکتور رسمی روبوایکیو کلاب روبوایکیو، زنجیره تامین قطعات الکترونیک و رباتیک فروشگاه روبوایکیو از سال ۱۳۸۴ فعالیت خود را در زمینه طراحی ، تولید و تامین قطعات رباتیک و الکترونیک آغاز کرد. این فروشگاه با ارائه انواع قطعات و ماژول‌های رباتیک و الکترونیک سهم عمده‌ای در تامین و رفع نیازهای تولیدکنندگان ، عرضه کنندگان، دانشجویان و علاقه‌مندان به این رشته داشته و توانسته است سهم عمده‌ای از این بازار را چه در بازار آنلاین و چه در بازار سنتی به دست آورد. این فروشگاه با عنوان تجاری روبوایکیو فعالیت میکند و تمام تلاش خود را میکند تا به عنوان عضوی از صنعت ایران نقش کوچکی در رشد و شکوفایی هر چه بیشتر این صنعت و اقتصاد کشور داشته باشد. فروشگاه روبوایکیو در حال حاضر با بیش از ۲۰۰۰۰ محصول در زمینه قطعات الکترونیک و رباتیک فعالیت میکند و امیدواریم به زودی بتوانیم بیشتر نیازهای شما عزیزان را پاسخگو باشیم. واردات قطعات و کالاهای مرتبط در این زمینه از نقاط مختلف دنیا از جمله فعالیت‌های این فروشگاه است. همچنین تولید قطعات خاص و انحصاری و صادرات آن به چند کشور اروپایی و آسیایی نیز برگ زرینی از فعالیت‌های این فروشگاه به شمار می آید. وجود پرسنل مجرب و متعهد در کنار کارگاه تولیدی و امکانات جدید آن توانسته بصورت همزمان بسیاری از نیازهای تهیه و تولید را مرتفع نماید. بخش فروش با ارائه قطعات و محصولات مرتبط و به روز نگهداشتن قیمت‌های آن مرجع مناسبی برای قیمت‌های بازار بوجود آورده است. بخش خرید قطعات علاوه بر تسلط بر بازارهای داخلی و تهیه قطعه مورد نظر در کوتاه ترین زمان و به بهترین قیمت، میتوانند محصول مورد نظر شما را در نقاط مختلف جهان استعلام قیمت و وارد نمایند. وجود دفتر فروشگاه در هنگ کنگ ارتباط بسیار مناسبی برای واردات از کشورهای مختلف را ایجاد کرده است. به همین دلیل است که بسیاری از دانشگاه‌ها، پژوهشسراها، ادارات آموزش و پرورش، فنی حرفه‌ای‌ها، شرکت‌های تولیدی به نام و برگزار کنندگان رسمی مسابقات داخلی و خارجی روبوایکیو را به عنوان مرجع مناسب خریدهای خود انتخاب کرده اند. مشاهده بیشتر تمام حقوق مادی و معنوی متعلق به روبوایکیو است. طراحی سایت توسط آیدیانت</t>
         </is>
       </c>
@@ -899,10 +892,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="3" t="n">
         <v>480000</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="3" t="n">
         <v>480000</v>
       </c>
     </row>
@@ -913,14 +906,14 @@
       <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>https://partelec.ir/product/8-inch-resistive-touch-screen/</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>مشخصات، قیمت، خریدتاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول ورود / ثبت نام لطفا شماره موبایل خود را درج نمایید شرایط و قوانین استفاده از سرویس های فروشگاه پارت الکترونیک را می پذیرم مرا به خاطر بسپار دریافت کد تایید ورود / ثبت نام رمزعبور را فراموش کرده ام ورود / ثبت نام با پسورد ورود با رمز یکبار مصرف کد تایید 4 رقمی ارسال شده به شماره موبایل زیر را وارد کنید. ویرایش شماره تایید کد ارسال مجدد کد Products search کاربری ورود / ثبت نام سبد خرید خالی است سبد خرید 0 می‌توانید برای مشاهده محصولات بیشتر به صفحات زیر بروید علاقه مندی های من بازگشت به فروشگاه محصولات قطعات الکترونیک الکترونیک صنعتی و قدرت ماژول IGBT گیت درایور نمایشگر و تاچ اسکرین تاچ اسکرین نمایشگر LED نمایشگر LCD ترانزیستور ترانزیستور IGBT ترانزیستور MOSFET ترانزیستور BJT IC رگولاتور و مبدل ولتاژ آی سی درایور آی سی مبدل دیتا آی سی تایمر و ساعت سایر آی سی های کاربردی خازن دیود سایر دیودها سوکت ها، کانکتورها و اتصالات سایر قطعات آنتن رله آداپتور و پاور سوئیچینگ سنسور، ماژول و بردهای توسعه سنسور دما و رطوبت ترموسوییچ سایر سنسورها ماژول تغذیه و مبدل ماژول ارتباط بی سیم ماژول RFID ماژول GPS-GPRS-GSM ماژول بلوتوث سایر ماژول ها ماژول درایور ماژول دوربین و پردازش تصویر ماژول های کاربردی انواع بردهای توسعه بردهای آردوینو ابزار و تجهیزات تست و اندازه گیری تجهیزات تست و اندازه گیری منبع تغذیه خطی تک منبع تغذیه خطی دوبل منبع تغذیه سوئیچینگ تک منبع تغذیه سوئیچینگ صنعتی فانکشن ژنراتور مولتی متر اسیلوسکوپ دیجیتال ابزار و وسایل ابزار لحیم کاری و مونتاژ جعبه قطعات کابل و سیم سایر ابزار و وسایل سایر تجهیزات کلمپ آمپرمتر قطعات برقی (الکتریکی) انواع لامپ و ریسه لامپ سیگنال لامپ LED هوشمندسازی مرکز کنترل هوشمند محافظ و پریز هوشمند کلید لمسی ترانسفورماتور قطعات ترانس هسته قالپاق قرقره چسب ترمینال سفارش ساخت ترانس صفحه اصلی سفارش خارج آکادمی تماس با پارت الکترونیک 02136348190 خانه قطعات الکترونیک سایر قطعات نمایشگر و تاچ اسکرین تاچ اسکرین تاچ اسکرین مقاومتی تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول PDA-1259 14 دیدگاه افزودن به علاقه‌مندی‌ها اشتراک گذاری مرا مطلع کن مقایسه نمودار قیمت آیا قیمت مناسب‌تری سراغ دارید؟ بله | خیر بازخورد درباره این کالا اشتراک گذاری این محصول را با دوستان خود به اشتراک بگذارید! کپی کردن لینک تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول 8inch resistive touch screen دسته بندی: تاچ اسکرین مقاومتی ویژگی‌های محصول ابعاد 141×183 میلی متر نوع فلت ضخیم- سوکت دار مشاهده همه ویژگی ها گارانتی اصالت و سلامت فیزیکی کالا آماده ارسال بازگشت آماده ارسال این کالا در حال حاضر در انبار فروشگاه موجود ، آماده پردازش و ارسال است ۲,۸۷۵,۰۰۰ تومان بروزرسانی قیمت: 4 دقیقه پیش تعداد بروزرسانی : افزودن به سبد ارتباط با کارشناسان در بله! پشتیبانی و مشاوره فنی، استعلام و خرید! تامین قطعات از خارج ارسال به سراسر ایران مشاوره فنی و تخصصی ضمانت سلامت و اصالت کالا نقد و بررسی مشخصات پرسش و پاسخ دیدگاه ها نقد و بررسی تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول تاچ اسکرین قطعه ای است که بر روی نمایشگر نصب می شود و به کمک آن می توان المان های نمایش داده شده بر روی نمایشگر را کنترل کرد. تاچ اسکرین ها انواع مختلفی دارند و به صورت کلی به دو نوع مقاومتی و خازنی تقسیم می شوند. بسته به نوع تاچ اسکرین می بایست آی سی درایور مناسب برای تشخیص تغییرات خروجی قطعه در نظر گرفت. تاچ مقاومتی 8 اینچ، مناسب نمایشگرهای 8 اینچ می باشد. این تاچ اسکرین دارای ابعاد 141×183 میلی متر است. مکان قرار گیری فلت این قطعه بر روی ضلع بزرگتر تاچ اسکرین می باشد. این تاچ اسکرین معمولا برای دستگاه های صنعتی و تجاری مانند نمایشگرهای صنعتی (HMI)، آیفون های تصویری، پخش کننده های اتوموبیل، دستگاه های حضور و غیاب و … استفاده می شود. مشخصات تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول اطلاعات کلی ابعاد تاچ 141×183 میلی متر سایز تاچ 8 اینچ اطلاعات فنی نوع تاچ مقاومتی تعداد سیم 4 سیم شما همچنین می توانید یک پرسش در مورد این محصول ثبت کنید ثبت پرسش امتیاز کاربران به: تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول | (14 نفر                    ) هنوز امتیازی ثبت نشده است نظر خود را در مورد این محصول بیان کنید. افزودن نظر جدید شما هم می‌توانید در مورد این کالا نظر دهید. اگر این محصول را قبلا خریده باشید، دیدگاه شما به عنوان خریدار ثبت خواهد شد. دیدگاه خود را ثبت کنید تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول 8inch resistive touch screen ارزش خرید به نسبت قیمت عالی کیفیت ساخت عالی لغو پاسخ نشانی ایمیل شما منتشر نخواهد شد. بخش‌های موردنیاز علامت‌گذاری شده‌اند * عنوان نظر شما (اجباری) * نقاط قوت نقاط ضعف متن نظر شما (اجباری) نام * ایمیل * وب‌ سایت با انتخاب دکمه "ثبت نظر" موافقت خود را با قوانین انتشار محتوا در فروشگاه پارت الکترونیک اعلام می‌کنم. دیگران را با نوشتن نظرات خود، برای انتخاب این محصول راهنمایی کنید. لطفا پیش از ارسال نظر، خلاصه قوانین زیر را مطالعه کنید: فارسی بنویسید و از کیبورد فارسی استفاده کنید. بهتر است از فضای خالی (Space) بیش‌از‌حدِ معمول، شکلک یا ایموجی استفاده نکنید و از کشیدن حروف یا کلمات با صفحه‌کلید بپرهیزید. نظرات خود را براساس تجربه و استفاده‌ی عملی و با دقت به نکات فنی ارسال کنید؛ بدون تعصب به محصول خاص، مزایا و معایب را بازگو کنید و بهتر است از ارسال نظرات چندکلمه‌‌ای خودداری کنید. بهتر است در نظرات خود از تمرکز روی عناصر متغیر مثل قیمت، پرهیز کنید. به کاربران و سایر اشخاص احترام بگذارید. پیام‌هایی که شامل محتوای توهین‌آمیز و کلمات نامناسب باشند، حذف می‌شوند. از ارسال لینک‌های سایت‌های دیگر و ارایه‌ی اطلاعات شخصی خودتان مثل شماره تماس، ایمیل و آی‌دی شبکه‌های اجتماعی پرهیز کنید. با توجه به ساختار بخش نظرات، از پرسیدن سوال یا درخواست راهنمایی در این بخش خودداری کرده و سوالات خود را در بخش «پرسش و پاسخ» مطرح کنید. هرگونه نقد و نظر در خصوص سایت فروشگاه ما، خدمات و درخواست کالا را با ایمیل info@yourdomain.com یا با شماره‌ی ۰۰۰۰ - ۰۲۱ در میان بگذارید و از نوشتن آن‌ها در بخش نظرات خودداری کنید. ثبت نظر نمودار قیمت کالا جهت فیلترکردن نمودارها، بر روی هر عنوان کلیک کنید. محصولات مشابه تاچ اسکرین مقاومتی 5.7 اینچ ماتریسی HZD5.7 تاچ اسکرین مقاومتی 5 اینچ ۱,۰۸۳,۰۰۰ تومان تاچ اسکرین مقاومتی 15 اینچ فلت در عرض-وسط تماس بگیرید تاچ اسکرین مقاومتی 7 اینچ فلت راست ۱,۶۶۱,۷۰۰ تومان تاچ اسکرین مقاومتی 8 اینچ فلت در عرض-کنار ۳,۰۱۹,۷۰۰ تومان تاچ اسکرین مقاومتی 7 اینچ فلت چپ ۱,۶۸۱,۷۰۰ تومان تاچ اسکرین مقاومتی 4.3 اینچ ۶۰۵,۴۰۰ تومان تاچ اسکرین مقاومتی 12.1 اینچ 5 سیم ۶,۴۷۷,۲۰۰ تومان تاچ اسکرین مقاومتی 7 اینچ فلت وسط ۱,۶۴۶,۷۰۰ تومان تاچ اسکرین مقاومتی 10.4 اینچ 5 سیم ۵,۸۸۳,۶۰۰ تومان تاچ اسکرین مقاومتی 10.1 اینچ فلت کنار ۳,۷۵۰,۰۰۰ تومان تاچ اسکرین مقاومتی 10.4 اینچ فلت پهن-وسط ۴,۴۷۰,۲۰۰ تومان تاچ اسکرین مقاومتی 8 اینچ فلت در عرض-وسط تماس بگیرید تاچ اسکرین مقاومتی 5.2 اینچ ۱,۸۶۰,۴۰۰ تومان تاچ اسکرین مقاومتی 5.7 اینچ ۱,۷۴۱,۷۰۰ تومان تاچ اسکرین مقاومتی 3.1 اینچ 128 در 64 ۷۸۳,۴۰۰ تومان تاچ اسکرین مقاومتی 6.5 اینچ AMT10515 تماس بگیرید تاچ اسکرین مقاومتی 9 اینچ تماس بگیرید تاچ اسکرین مقاومتی 10.1 اینچ فلت وسط تماس بگیرید تاچ اسکرین مقاومتی 4.3 اینچ 62×102 ۵۷۹,۹۰۰ تومان خریداران این محصول ، محصولات زیر را هم خریده اند کابل فلت FFC 4PIN 10CM سوکت دار ۷۳,۲۰۰ تومان تاچ اسکرین مقاومتی 7 اینچ فلت وسط ۱,۶۴۶,۷۰۰ تومان نمایشگر 7 اینچ TFT LCD 7 INCH AT070TN92 ۳,۷۶۱,۳۰۰ تومان تاچ اسکرین مقاومتی 10.4 اینچ فلت باریک-کنار ۴,۸۴۰,۷۰۰ تومان تاچ اسکرین مقاومتی 10.4 اینچ فلت باریک-وسط ۴,۸۴۲,۳۰۰ تومان کابل فلت FFC-4PIN-15CM تماس بگیرید تاچ اسکرین مقاومتی 5.7 اینچ ۱,۷۴۱,۷۰۰ تومان تاچ تاچ 4 سیم تاچ اسکرین تاچ اسکرین مقاومتی تاچ صنعتی تاچ مقاومتی فروشگاه پارت الکترونیک، بررسی، انتخاب و خرید فروشگاه پارت الکترونیک در سال 1394 و در راستای خدمت رسانی به جامعه مهندسی برق کشور عزیزمان ایران شروع به فعالیت کرد. فعالیت مجموعه پارت الکترونیک همواره در راستای رفع نیازهای بازار برق و الکترونیک کشور بوده است و به همبن دلیل با همکاری دیگر متخصصین حوزه برق و الکترونیک اقدام به ارائه مشاوره های تخصصی قبل و پس از خرید به مشتریان گرامی نموده است. نمایش بیشتر لاله زار جنوبی - مجتمع بوشهری تلفن : 021-36348190 | 021-36348259 ایمیل : info@Partelec.ir خدمات مشتریان ارسال لیست خرید قطعات پیگیری سفارشات ثبت اطلاعات پرداخت ثبت شکایات دسترسی سریع درباره ما شماره حساب ها شرایط و قوانین پرسش های متداول لینک های مفید Tektronix GWinstek Hioki Fluke با ما همراه باشید استفاده از مطالب وبسایت پارت الکترونیک تنها در موارد غیر تجاری و با ذکر نام وبسایت مجاز است. تمام حقوق اين وب‌سايت نیز برای شرکت هسته طراحی (فروشگاه پارت الکترونیک) است. برگشت به بالا تماس با ما پاسخگوی شما هستیم یکی از راه های زیر را برای ارتباط انتخاب کنید تماس با فروشگاه تماس با پشتیبان فروشگاه ارتباط از طریق واتساپ ارتباط از طریق تلگرام پیج اینستاگرام 0 سبد خرید 0 شما این محصولات را انتخاب کرده اید 0 می‌توانید برای مشاهده محصولات بیشتر به صفحات زیر بروید علاقه مندی های من بازگشت به فروشگاه تصاویر رسمی دیدگاه خریدار تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول</t>
+          <t>مشخصات، قیمت، خریدتاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول ورود / ثبت نام لطفا شماره موبایل خود را درج نمایید شرایط و قوانین استفاده از سرویس های فروشگاه پارت الکترونیک را می پذیرم مرا به خاطر بسپار دریافت کد تایید ورود / ثبت نام رمزعبور را فراموش کرده ام ورود / ثبت نام با پسورد ورود با رمز یکبار مصرف کد تایید 4 رقمی ارسال شده به شماره موبایل زیر را وارد کنید. ویرایش شماره تایید کد ارسال مجدد کد Products search کاربری ورود / ثبت نام سبد خرید خالی است سبد خرید 0 می‌توانید برای مشاهده محصولات بیشتر به صفحات زیر بروید علاقه مندی های من بازگشت به فروشگاه محصولات قطعات الکترونیک الکترونیک صنعتی و قدرت ماژول IGBT گیت درایور نمایشگر و تاچ اسکرین تاچ اسکرین نمایشگر LED نمایشگر LCD ترانزیستور ترانزیستور IGBT ترانزیستور MOSFET ترانزیستور BJT IC رگولاتور و مبدل ولتاژ آی سی درایور آی سی مبدل دیتا آی سی تایمر و ساعت سایر آی سی های کاربردی خازن دیود سایر دیودها سوکت ها، کانکتورها و اتصالات سایر قطعات آنتن رله آداپتور و پاور سوئیچینگ سنسور، ماژول و بردهای توسعه سنسور دما و رطوبت ترموسوییچ سایر سنسورها ماژول تغذیه و مبدل ماژول ارتباط بی سیم ماژول RFID ماژول GPS-GPRS-GSM ماژول بلوتوث سایر ماژول ها ماژول درایور ماژول دوربین و پردازش تصویر ماژول های کاربردی انواع بردهای توسعه بردهای آردوینو ابزار و تجهیزات تست و اندازه گیری تجهیزات تست و اندازه گیری منبع تغذیه خطی تک منبع تغذیه خطی دوبل منبع تغذیه سوئیچینگ تک منبع تغذیه سوئیچینگ صنعتی فانکشن ژنراتور مولتی متر اسیلوسکوپ دیجیتال ابزار و وسایل ابزار لحیم کاری و مونتاژ جعبه قطعات کابل و سیم سایر ابزار و وسایل سایر تجهیزات کلمپ آمپرمتر قطعات برقی (الکتریکی) انواع لامپ و ریسه لامپ سیگنال لامپ LED هوشمندسازی مرکز کنترل هوشمند محافظ و پریز هوشمند کلید لمسی ترانسفورماتور قطعات ترانس هسته قالپاق قرقره چسب ترمینال سفارش ساخت ترانس صفحه اصلی سفارش خارج آکادمی تماس با پارت الکترونیک 02136348190 خانه قطعات الکترونیک سایر قطعات نمایشگر و تاچ اسکرین تاچ اسکرین تاچ اسکرین مقاومتی تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول PDA-1259 14 دیدگاه افزودن به علاقه‌مندی‌ها اشتراک گذاری مرا مطلع کن مقایسه نمودار قیمت آیا قیمت مناسب‌تری سراغ دارید؟ بله | خیر بازخورد درباره این کالا اشتراک گذاری این محصول را با دوستان خود به اشتراک بگذارید! کپی کردن لینک تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول 8inch resistive touch screen دسته بندی: تاچ اسکرین مقاومتی ویژگی‌های محصول ابعاد 141×183 میلی متر نوع فلت ضخیم- سوکت دار مشاهده همه ویژگی ها گارانتی اصالت و سلامت فیزیکی کالا آماده ارسال بازگشت آماده ارسال این کالا در حال حاضر در انبار فروشگاه موجود ، آماده پردازش و ارسال است ۲,۸۷۵,۰۰۰ تومان بروزرسانی قیمت: 3 ساعت پیش تعداد بروزرسانی : افزودن به سبد ارتباط با کارشناسان در بله! پشتیبانی و مشاوره فنی، استعلام و خرید! تامین قطعات از خارج ارسال به سراسر ایران مشاوره فنی و تخصصی ضمانت سلامت و اصالت کالا نقد و بررسی مشخصات پرسش و پاسخ دیدگاه ها نقد و بررسی تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول تاچ اسکرین قطعه ای است که بر روی نمایشگر نصب می شود و به کمک آن می توان المان های نمایش داده شده بر روی نمایشگر را کنترل کرد. تاچ اسکرین ها انواع مختلفی دارند و به صورت کلی به دو نوع مقاومتی و خازنی تقسیم می شوند. بسته به نوع تاچ اسکرین می بایست آی سی درایور مناسب برای تشخیص تغییرات خروجی قطعه در نظر گرفت. تاچ مقاومتی 8 اینچ، مناسب نمایشگرهای 8 اینچ می باشد. این تاچ اسکرین دارای ابعاد 141×183 میلی متر است. مکان قرار گیری فلت این قطعه بر روی ضلع بزرگتر تاچ اسکرین می باشد. این تاچ اسکرین معمولا برای دستگاه های صنعتی و تجاری مانند نمایشگرهای صنعتی (HMI)، آیفون های تصویری، پخش کننده های اتوموبیل، دستگاه های حضور و غیاب و … استفاده می شود. مشخصات تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول اطلاعات کلی ابعاد تاچ 141×183 میلی متر سایز تاچ 8 اینچ اطلاعات فنی نوع تاچ مقاومتی تعداد سیم 4 سیم شما همچنین می توانید یک پرسش در مورد این محصول ثبت کنید ثبت پرسش امتیاز کاربران به: تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول | (14 نفر                    ) هنوز امتیازی ثبت نشده است نظر خود را در مورد این محصول بیان کنید. افزودن نظر جدید شما هم می‌توانید در مورد این کالا نظر دهید. اگر این محصول را قبلا خریده باشید، دیدگاه شما به عنوان خریدار ثبت خواهد شد. دیدگاه خود را ثبت کنید تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول 8inch resistive touch screen ارزش خرید به نسبت قیمت عالی کیفیت ساخت عالی لغو پاسخ نشانی ایمیل شما منتشر نخواهد شد. بخش‌های موردنیاز علامت‌گذاری شده‌اند * عنوان نظر شما (اجباری) * نقاط قوت نقاط ضعف متن نظر شما (اجباری) نام * ایمیل * وب‌ سایت با انتخاب دکمه "ثبت نظر" موافقت خود را با قوانین انتشار محتوا در فروشگاه پارت الکترونیک اعلام می‌کنم. دیگران را با نوشتن نظرات خود، برای انتخاب این محصول راهنمایی کنید. لطفا پیش از ارسال نظر، خلاصه قوانین زیر را مطالعه کنید: فارسی بنویسید و از کیبورد فارسی استفاده کنید. بهتر است از فضای خالی (Space) بیش‌از‌حدِ معمول، شکلک یا ایموجی استفاده نکنید و از کشیدن حروف یا کلمات با صفحه‌کلید بپرهیزید. نظرات خود را براساس تجربه و استفاده‌ی عملی و با دقت به نکات فنی ارسال کنید؛ بدون تعصب به محصول خاص، مزایا و معایب را بازگو کنید و بهتر است از ارسال نظرات چندکلمه‌‌ای خودداری کنید. بهتر است در نظرات خود از تمرکز روی عناصر متغیر مثل قیمت، پرهیز کنید. به کاربران و سایر اشخاص احترام بگذارید. پیام‌هایی که شامل محتوای توهین‌آمیز و کلمات نامناسب باشند، حذف می‌شوند. از ارسال لینک‌های سایت‌های دیگر و ارایه‌ی اطلاعات شخصی خودتان مثل شماره تماس، ایمیل و آی‌دی شبکه‌های اجتماعی پرهیز کنید. با توجه به ساختار بخش نظرات، از پرسیدن سوال یا درخواست راهنمایی در این بخش خودداری کرده و سوالات خود را در بخش «پرسش و پاسخ» مطرح کنید. هرگونه نقد و نظر در خصوص سایت فروشگاه ما، خدمات و درخواست کالا را با ایمیل info@yourdomain.com یا با شماره‌ی ۰۰۰۰ - ۰۲۱ در میان بگذارید و از نوشتن آن‌ها در بخش نظرات خودداری کنید. ثبت نظر نمودار قیمت کالا جهت فیلترکردن نمودارها، بر روی هر عنوان کلیک کنید. محصولات مشابه تاچ اسکرین مقاومتی 8 اینچ فلت در عرض-وسط تماس بگیرید تاچ اسکرین مقاومتی 10.4 اینچ فلت باریک-کنار ۴,۸۴۰,۷۰۰ تومان تاچ اسکرین مقاومتی 8 اینچ فلت در طول-وسط تماس بگیرید تاچ اسکرین مقاومتی 3.5 اینچ ۸۸۰,۴۰۰ تومان تاچ اسکرین مقاومتی 7 اینچ فلت وسط ۱,۶۴۶,۷۰۰ تومان تاچ اسکرین مقاومتی 12.12 اینچ AMT9542 تماس بگیرید تاچ اسکرین مقاومتی 4.3 اینچ ۶۰۵,۴۰۰ تومان تاچ اسکرین مقاومتی 6.5 اینچ AMT10515 تماس بگیرید تاچ اسکرین مقاومتی 15 اینچ 5 سیم ۶,۸۹۴,۴۰۰ تومان تاچ اسکرین مقاومتی 12.1 اینچ فلت پهن ۴,۷۳۳,۴۰۰ تومان تاچ اسکرین مقاومتی 5.7 اینچ ۱,۷۴۱,۷۰۰ تومان تاچ اسکرین مقاومتی 7 اینچ فلت چپ ۱,۶۸۱,۷۰۰ تومان تاچ اسکرین مقاومتی 7 اینچ فلت راست ۱,۶۶۱,۷۰۰ تومان تاچ اسکرین مقاومتی 15 اینچ فلت در عرض-وسط تماس بگیرید تاچ اسکرین مقاومتی 10.4 اینچ 5 سیم ۵,۸۸۳,۶۰۰ تومان تاچ اسکرین مقاومتی 10.4 اینچ فلت پهن-کنار ۴,۷۱۰,۰۰۰ تومان تاچ اسکرین مقاومتی 10.4 اینچ فلت باریک-وسط ۴,۸۴۲,۳۰۰ تومان تاچ اسکرین مقاومتی 4.3 اینچ 62×102 ۵۷۹,۹۰۰ تومان تاچ اسکرین مقاومتی 10.4 اینچ AMT9509 تماس بگیرید تاچ اسکرین مقاومتی 5 اینچ ۱,۰۸۳,۰۰۰ تومان خریداران این محصول ، محصولات زیر را هم خریده اند تاچ اسکرین مقاومتی 7 اینچ فلت وسط ۱,۶۴۶,۷۰۰ تومان کابل فلت FFC 4PIN 10CM سوکت دار ۷۳,۲۰۰ تومان کابل فلت FFC-4PIN-15CM تماس بگیرید تاچ اسکرین مقاومتی 10.4 اینچ فلت باریک-وسط ۴,۸۴۲,۳۰۰ تومان نمایشگر 7 اینچ TFT LCD 7 INCH AT070TN92 ۳,۷۶۱,۳۰۰ تومان تاچ اسکرین مقاومتی 10.4 اینچ فلت باریک-کنار ۴,۸۴۰,۷۰۰ تومان تاچ اسکرین مقاومتی 5.7 اینچ ۱,۷۴۱,۷۰۰ تومان تاچ تاچ 4 سیم تاچ اسکرین تاچ اسکرین مقاومتی تاچ صنعتی تاچ مقاومتی فروشگاه پارت الکترونیک، بررسی، انتخاب و خرید فروشگاه پارت الکترونیک در سال 1394 و در راستای خدمت رسانی به جامعه مهندسی برق کشور عزیزمان ایران شروع به فعالیت کرد. فعالیت مجموعه پارت الکترونیک همواره در راستای رفع نیازهای بازار برق و الکترونیک کشور بوده است و به همبن دلیل با همکاری دیگر متخصصین حوزه برق و الکترونیک اقدام به ارائه مشاوره های تخصصی قبل و پس از خرید به مشتریان گرامی نموده است. نمایش بیشتر لاله زار جنوبی - مجتمع بوشهری تلفن : 021-36348190 | 021-36348259 ایمیل : info@Partelec.ir خدمات مشتریان ارسال لیست خرید قطعات پیگیری سفارشات ثبت اطلاعات پرداخت ثبت شکایات دسترسی سریع درباره ما شماره حساب ها شرایط و قوانین پرسش های متداول لینک های مفید Tektronix GWinstek Hioki Fluke با ما همراه باشید استفاده از مطالب وبسایت پارت الکترونیک تنها در موارد غیر تجاری و با ذکر نام وبسایت مجاز است. تمام حقوق اين وب‌سايت نیز برای شرکت هسته طراحی (فروشگاه پارت الکترونیک) است. برگشت به بالا تماس با ما پاسخگوی شما هستیم یکی از راه های زیر را برای ارتباط انتخاب کنید تماس با فروشگاه تماس با پشتیبان فروشگاه ارتباط از طریق واتساپ ارتباط از طریق تلگرام پیج اینستاگرام 0 سبد خرید 0 شما این محصولات را انتخاب کرده اید 0 می‌توانید برای مشاهده محصولات بیشتر به صفحات زیر بروید علاقه مندی های من بازگشت به فروشگاه تصاویر رسمی دیدگاه خریدار تاچ اسکرین مقاومتی 8 اینچ فلت پهن در طول</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -928,10 +921,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="3" t="n">
         <v>28750000</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="3" t="n">
         <v>28750000</v>
       </c>
     </row>
@@ -957,10 +950,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="3" t="n">
         <v>5600000</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="3" t="n">
         <v>5600000</v>
       </c>
     </row>
@@ -971,27 +964,23 @@
       <c r="B15" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>https://electronic724.com/Product/E724-37597/high-power-mosfet-driver-100a/</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>مشخصات، قیمت و خرید High-Power Mosfet Driver 100A ورود / ثبت نام شماره تماس یا ایمیل خود را وارد کنید شرایط و قوانین استفاده از سرویس های فروشگاه اینترنتی الکترونیک 724 را می پذیرم دریافت کد تایید ورود / ثبت نام رمزعبور را فراموش کرده ام ورود / ثبت نام با پسورد ورود با رمز یکبار مصرف کد تایید 4 رقمی ارسال شده به شماره موبایل زیر را وارد کنید. ویرایش شماره تایید کد ارسال مجدد کد رمز عبور خود را وارد کنید. ورود / ثبت نام جستجوی محصولات کاربری ورود / ثبت نام سبد خرید خالی است سبد خرید 0 می‌توانید برای مشاهده محصولات بیشتر به صفحات زیر بروید علاقه مندی های من بازگشت به فروشگاه دسته بندی ها ماژول‌های الکترونیکی مبدل‌ها تغذیه صدا و تصویر دما و رطوبت موتورها و درایور موتور GPS &amp; GSM IMU &amp; GYRO RFID &amp; NFC فاصله یاب KeyBoard &amp; Keypad تشخیص گاز Infrared (IR) اسکنر بارکد و QR سنسور اثر انگشت علائم حیاتی گرد و غبار ماژول ساعت (RTC) TCP/IP ماژول سنسور جریان Water Flow ماژول رله و سوئیچ تشخیص رنگ و نور وزن فشارسنج شتاب سنج ماژولهای Encoder تشخیص حرکت و لرزش پرینتر قطب نما RF &amp; بی سیم آنتن &amp; UFL Radio Frequency (RF) 2.4GHz WiFi Bluetooth Zigbee LoRa ماژولهای متفرقه آردوینو Arduino بردهای آردوینو شیلدها لوازم جانبی آردوینو کامپیوترهای تک بردی Banana Pi Beagle Bone Nano PI ODROID Orange PI Raspberry PI لوازم جانبی کامپیوترهای تک بردی بردهای کاربردی و آموزشی برد میکروکنترلرهای STM بردهای Atmel بردهای FPGA بردهای متفرقه نمایشگر ال سی دی (LCD) اولد (OLED) سون سگمنت (7Segment) Car LCD ال ای دی (LED) کانکتور ATX ای تی اکس SM بین راهی VH پاور قفل دار پین گرد کانکتور PH پی اِچ کانکتور XH یا دزدگیری کانکتور مخابراتی 2510 جعبه و قاب باکس‌های ریلی استاندارد باکس‌های ریلی عمودی باکس‌های ریلی ماژولار براکت‌های ریلی استاندارد بردهای ریلی استاندارد جعبه‌های آلومینیومی آلومینیومی دیواری گوشواره‌دار آلومینیومی رومیزی جعبه‌های پنلی جعبه‌های تجهیزات شبکه جعبه‌های دستی قابل حمل جعبه‌های GPS جعبه‌های دستی بدون نمایشگر جعبه‌های دستی نمایشگردار جعبه‌های دیواری جعبه‌های رومیزی جعبه‌های رومیزی ساده جعبه‌های رومیزی شیب‌دار جعبه‌های رومیزی نمایشگردار جعبه‌های ضد آب ضد آب تابلویی جعبه تقسیم ضد آب ضد آب آلومینیومی ضد آب پلاستیکی رومیزی و دیواری جعبه‌های کنترل تردد کنترل تردد اثرانگشتی کنترل تردد ترکیبی کنترل تردد دیجیتال (کیپددار) کنترل تردد کارتخوان RFID جعبه‌های نمایشگر جعبه‌های هوشمندسازی پریز و سوکت هوشمند کلیدهای هوشمند هاب و روتر هوشمند کیف‌های ضد ضربه و ضد آب سایر باکس‌ها باکس درایور LED باکس رسپبری پای و مینی کامپیوتر جا باتری جعبه‌ آداپتور سر ولوم کیپد باکس‌های متفرقه سایر دسته‌بندی‌ها پروگرامر پاوربانک ریموت کنترل و گیرنده ولت‌متر و آمپرمتر PCB های مبدل آی سی ها (IC) رگولاتور میکروکنترلر STM آی سی متفرقه لوازم جانبی باتری (باطری) کارت حافظه و Flash   «««««جدید»»»»» متفرقه مجله الکترونیک 724 سفارش چاپ PCB تماس با ما 02166769124 فروشگاه اینترنتی الکترونیک 724 ماژول‌های الکترونیکی ماژول رله و سوئیچ High-Power Mosfet Driver 100A 1205015 0 دیدگاه افزودن به علاقه‌مندی‌ها اشتراک گذاری مرا مطلع کن مقایسه آیا قیمت مناسب‌تری سراغ دارید؟ بله | خیر بازخورد درباره این کالا اشتراک گذاری این محصول را با دوستان خود به اشتراک بگذارید! کپی کردن لینک High-Power Mosfet Driver 100A دسته بندی: ماژول رله و سوئیچ High-Power Mosfet Driver 100A آماده ارسال بازگشت آماده ارسال این کالا در حال حاضر در انبار فروشگاه موجود ، آماده پردازش و ارسال است 158,500 تومان موجود تعداد افزودن به سبد تحویل اکسپرس پرداخت آنلاین ارسال سراسری بهترین قیمت محصولات مرتبط High-Power Mosfet Driver 20A 45,500 تومان High-Power Mosfet Driver 50A 71,800 تومان ایزولاتور 2 کانال اپتوکوپلری 2ch PC817 Optocoupler Isolation 105,300 تومان رله 5 ولت SSR OMRON 5V DC 106,000 تومان سوییچ latch 5-24v 70A 265,500 تومان ماژول رله 5 ولت دو کاناله Relay Module 231,200 تومان ماژول رله تک کانال SSR 250V/2A OMRON 150,000 تومان ماژول رله دو کاناله OMRON SSR 250V/2A 335,100 تومان نقد و بررسی دیدگاه ها پرسش و پاسخ امتیاز کاربران به: High-Power Mosfet Driver 100A | (0 نفر                    ) هنوز امتیازی ثبت نشده است نظر خود را در مورد این محصول بیان کنید. افزودن نظر جدید شما هم می‌توانید در مورد این کالا نظر دهید. اگر این محصول را قبلا خریده باشید، دیدگاه شما به عنوان خریدار ثبت خواهد شد. دیدگاه خود را ثبت کنید برای ثبت دیدگاه باید ابتدا وارد سایت شوید! ثبت نظر شما همچنین می توانید یک پرسش در مورد این محصول ثبت کنید ثبت پرسش مقایسه ( 0 مورد ) مقایسه( 0 مورد ) حذف همه بازگشت به بالا پشتیبانی شماره تماس فروشگاه : [02166757479] هفت روز هفته، ۲۴ ساعت شبانه‌روز پاسخگوی شما هستیم. تهران - خ جمهوری - بعد از پل حافظ - پاساژ امجد - ط سوم - واحد 11 آدرس ایمیل : info@electronic724.com تحویل اکسپرس پرداخت آنلاین ارسال سراسری بهترین قیمت تحویل اکسپرس پرداخت آنلاین ارسال سراسری بهترین قیمت راهنمای خرید راهنمای خرید روش‌های ارسال روش‌های پرداخت خدمات پیگیری سفارشات حریم خصوصی پرسش‌های متداول خدمات مشتریان راهنمای خرید روش‌های ارسال روش‌های پرداخت با ما همراه باشید فروشگاه اینترنتی الکترونیک 724، بررسی، انتخاب و خرید آنلاین ﺗﻤﺎمی ﻛﺎﻻﻫﺎ و ﺧﺪﻣﺎت اﻳﻦ ﻓﺮوﺷﮕﺎه، ﺣﺴﺐ ﻣﻮرد، دارای ﻣﺠﻮزﻫﺎی ﻻزم از ﻣﺮاﺟﻊ ﻣﺮﺑﻮﻃﻪ میﺑﺎﺷﻨﺪ و ﻓﻌﺎﻟﻴﺖ‌ﻫﺎی اﻳﻦ ﺳﺎﻳﺖ ﺗﺎﺑﻊ ﻗﻮاﻧﻴﻦ و ﻣﻘﺮرات ﺟﻤﻬﻮری اﺳﻼمی اﻳﺮان اﺳﺖ. آدرس : تهران - خ جمهوری - بعد از پل حافظ - پاساژ امجد - ط سوم - واحد 11   [ساعات کار دفتر : شنبه تا چهارشنبه : 10 الی 17 و  پنج شنبه ها : 10 الی 12:30] نمایش بیشتر کليه حقوق اين سايت متعلق فروشگاه اینترنتی الکترونیک 724 می‌باشد. Copyright © 2006 - 2026 Electronic724 آخرین جستجوهای شما جستجوهای پرطرفدار باکس ماژول ال ای دی باتری جعبه این محصول به سبد خرید اضافه شد! رفتن به سبد خرید تماس با ما پاسخگوی شما هستیم یکی از راه های زیر را برای ارتباط انتخاب کنید تماس با شماره ثابت ارتباط از طریق واتساپ ارتباط از طریق تلگرام پیج اینستاگرام ما از کوکی‌ها برای ارائه خدمات بهتر و تجزیه و تحلیل رفتار کاربران استفاده می‌کنیم. لطفاً با تأیید این مورد ما را در مسیر بهبود تجربه کاربری یاری فرمایید. مشاهده شرایط رد کردن پذیرش همه 0 سبد خرید 0 شما این محصولات را انتخاب کرده اید 0 می‌توانید برای مشاهده محصولات بیشتر به صفحات زیر بروید علاقه مندی های من بازگشت به فروشگاه تصاویر رسمی دیدگاه خریدار High-Power Mosfet Driver 100A</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1585000</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3170000</v>
-      </c>
+          <t>ERROR: HTTPSConnectionPool(host='electronic724.com', port=443): Max retries exceeded with url: /Product/E724-37597/high-power-mosfet-driver-100a/ (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='electronic724.com', port=443) at 0x21cd6691950&gt;, 'Connection to electronic724.com timed out. (connect timeout=30)'))</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1000,14 +989,14 @@
       <c r="B16" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>https://avaelectronic.ir/product/%d9%87%db%8c%d8%aa-%d8%b3%db%8c%d9%86%da%a9-%d9%85%d9%86%d8%a7%d8%b3%d8%a8-%d8%b1%d8%b2%d8%a8%d8%b1%db%8c-%d9%be%d8%a7%db%8c-raspberry-pi-4/</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>هیت سینک مناسب رزبری پای Raspberry Pi 4 - آوا الکترونیک . آوا الکترونیک سبد خرید --تمام گروه ها-- ولتمتر ها دماسنج درایور موتور آردوینو سنسور ها - سنسور اثرانگشت - اثرهال - فشار و ارتفاع - دما و رطوبت - سنسورهای کاربردی - سنسور IR و PIR ماژول ها - ماژول کارت خوان - پخش و ضبط صدا - ماژول های رله - ماژول بخار - ماژولهای Bluetooth - ماژول های سرد کننده - اندازه گیر ولتاژ و جریان - ماژول های مبدل - ماژول ساعت - تایمر - ماژول آلتراسونیک - ماژول GSM-GPS-SPRS - ماژول های Wifi - انواع ریموت و ماژول های RF - ماژول شبکه - کوره القایی موتورها - براشلس - سرو موتور - پمپ های هوا و آب - موتور گیربکس - استپ موتور - موتور DC - موتور Coreless - موتور ویبره و لنگ نمایشگرها - LCD قطعات الکترونیکی - آی سی ها -  - سری CMOS - 40XX -  - سری TTL - 74XX -  - آی سی تایمر - پالس -  - تراشه واسط -  - تراشه درایور -  - اپتوکوپلر و اپتوکانتر -  - تراشه OP-AMP -  - صوت و آمپلی فایر -  - سایر آی سی ها - برد برد ها - آنتن ها - بلندگو ها - مقاومت ها -  - مقاومت 1/4 وات -  - مقاومت 1 وات -  - مقاومت 2 وات -  - انواع ولوم و سر ولوم -  - پتانسیومتر -  - مولتی ترن -  - ترمیستور NTC و PTC - انواع کانکتور - ترانزیستورها -  - ماسفت MOSFET -  - BJT ها - سوکت IC - پین هدر - انواع رله - انواع خازن -  - خازن سرامیکی و عدسی -  - خازن الکترولیتی -  - خازن پلی استر - قطعات نوری - انواع فیوز و جافیوزی - کلید، سوئیچ، کیپد - رگولاتورها - دیودها -  - دیود زنر Zener - کریستال و اسیلاتور Raspberry Pi تجهیزات مکانیکی - قفل الکتریکی - شیر برقی سلونوئیدی - انواع آهنربا -  - نئودیمیوم -  -  - بلوک -  -  - استوانه و دیسکی -  -  - کونیک و حلقه ای -  - فریت -  -  - حلقه ای و استوانه تجهیزات الکترونیکی - مولتی متر ها - فن ها - سوئیچینگ های صنعتی - آداپتور ها - سیم لحیم - میکروسکوپ ها - منابع تغذیه آزمایشگاهی - سیم و کابل -  - وارنیش اتوماسیون - کلید مینیاتوری - رله ها -  - تک کنتاکت Uncategorized پروگرامرها پرینتر سه بعدی - کیت پرینتر سه بعدی - لوازم جانبی پرینتر سه بعدی میکروکنترلرها - AVR / PIC - STM انواع باتری، جاباتری و شارژر - انواع جاباتری - انواع پاور بانک شارژر و تستر باتری - انواع باتری ابزارآلات و تجهیزات - ابزار - ابزار مونتاژ و لحیم کاری قطعات رباتیک - چرخ ربات - چرخ دنده - ملخ پروازی - سازه های رباتیک - دسته کنترل - پک آموزشی صفحه اصلی تسویه حساب راهنمای مشتریان حساب کاربری من تماس با ما سبد خرید صفحه اصلی تسویه حساب راهنمای مشتریان حساب کاربری من تماس با ما سبد خرید خانه / Raspberry Pi / هیت سینک مناسب رزبری پای Raspberry Pi 4 هیت سینک مناسب رزبری پای Raspberry Pi 4 143,900 تومان در انبار موجود نمی باشد شناسه محصول: 21121061 دسته: Raspberry Pi اشتراک گذاری این محصول نظرات (0) همه نقد ها هیچ دیدگاهی نوشته نشده است. اولین کسی باشید که نقد می نویسید: “هیت سینک مناسب رزبری پای Raspberry Pi 4” نظر شما نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. محصولات مشابه 15,870,000 تومان افزودن به سبد خرید مشاهده سریع برد رزبری پای +raspberry pi 3 model B اورجینال 15,870,000 تومان 21,060,100 تومان افزودن به سبد خرید مشاهده سریع برد رزبری پای Raspberry Pi 4 مدل B با رم ۲GB ساخت UK 21,060,100 تومان 0 تومان افزودن به سبد خرید مشاهده سریع ماژول فرستنده و گیرنده IR با ریموت کنترل مادون قرمز مناسب برای رزبری پای 0 تومان 151,100 تومان افزودن به سبد خرید مشاهده سریع شیلد پروتوتایپ رزبری پای Raspberry Pi 151,100 تومان 0 تومان افزودن به سبد خرید مشاهده سریع برد توسعه رزبری پای – ۴۰ پایه Raspberry Pi Expansion Board 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع شیلد مولتی فانکشن رزبری Multifunction GPIO Extension Board 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع دوربین رزپری پای ۵ مگاپیکسل با قابلیت دید در شب 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع شیلد افزایش GPIO رزبری پای Raspberry Pi Expansion Shield 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع کیس ABS رزبری پای Raspberry Pi 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع نمایشگر ۳٫۵ اینچ مخصوص Raspberry Pi 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع آداپتور ۵ ولت ۳ آمپر Type C مناسب رزبری پای ۴ 0 تومان 10,004,600 تومان افزودن به سبد خرید مشاهده سریع برد رزبری پای سه Raspberry Pi 3 مدل +A ساخت انگلستان 10,004,600 تومان 0 تومان افزودن به سبد خرید مشاهده سریع برد چهار هسته ای ۶۴ بیتی Orange Pi Lite 2 دارای RAM 1GB و قابلیت بوت اندروید / Ubuntu 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع نمایشگر ۳٫۲ اینچ مخصوص Raspberry Pi 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع ماژول دوربین ۸ مگاپیکسل با قابلیت دید در شب IMX219 مناسب برد رسپبری پای 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع LCD 2×16 به همراه کی پد ویژه رزبری پای 0 تومان دسته های محصولات Raspberry Pi آردوینو ابزارآلات و تجهیزات ابزار ابزار مونتاژ و لحیم کاری اتوماسیون رله ها تک کنتاکت کلید مینیاتوری انواع باتری، جاباتری و شارژر انواع باتری انواع پاور بانک شارژر و تستر باتری انواع جاباتری پروگرامرها پرینتر سه بعدی کیت پرینتر سه بعدی لوازم جانبی پرینتر سه بعدی تجهیزات الکترونیکی آداپتور ها سوئیچینگ های صنعتی سیم لحیم سیم و کابل وارنیش فن ها منابع تغذیه آزمایشگاهی مولتی متر ها میکروسکوپ ها تجهیزات مکانیکی انواع آهنربا فریت حلقه ای و استوانه نئودیمیوم استوانه و دیسکی بلوک کونیک و حلقه ای شیر برقی سلونوئیدی قفل الکتریکی درایور موتور دماسنج سنسور ها اثرهال دما و رطوبت سنسور IR و PIR سنسور اثرانگشت سنسور گاز سنسورهای کاربردی فشار و ارتفاع قطعات الکترونیکی آنتن ها آی سی ها آی سی تایمر - پالس اپتوکوپلر و اپتوکانتر تراشه OP-AMP تراشه درایور تراشه واسط سایر آی سی ها سری CMOS - 40XX سری TTL - 74XX صوت و آمپلی فایر انواع خازن خازن الکترولیتی خازن پلی استر خازن سرامیکی و عدسی انواع رله انواع فیوز و جافیوزی انواع کانکتور برد برد ها بلندگو ها پین هدر ترانزیستورها BJT ها ماسفت MOSFET دیودها دیود زنر Zener رگولاتورها سوکت IC قطعات نوری کریستال و اسیلاتور کلید، سوئیچ، کیپد مقاومت ها انواع ولوم و سر ولوم پتانسیومتر ترمیستور NTC و PTC مقاومت 1 وات مقاومت 1/4 وات مقاومت 2 وات مولتی ترن قطعات رباتیک پک آموزشی چرخ دنده چرخ ربات دسته کنترل سازه های رباتیک ملخ پروازی ماژول ها اندازه گیر ولتاژ و جریان انواع ریموت و ماژول های RF پخش و ضبط صدا کوره القایی ماژول GSM-GPS-SPRS ماژول آلتراسونیک ماژول بخار ماژول ساعت - تایمر ماژول شبکه ماژول کارت خوان ماژول های Wifi ماژول های حرکت و شتاب ماژول های رله ماژول های سرد کننده ماژول های کاربردی ماژول های مبدل ماژولهای Bluetooth ماژولهای ولتاژ و تغذیه موتورها استپ موتور براشلس پمپ های هوا و آب سرو موتور موتور Coreless موتور DC موتور گیربکس موتور ویبره و لنگ میکروکنترلرها AVR / PIC STM نمایشگرها LCD ولتمتر ها پر امتیازترین محصولات اسیلوسکوپ دیجیتال دو کاناله پرتابل مدل SDTEK 9,000,000 تومان سروو موتور دنده فلزی MG995 با زاویه چرخش 360 درجه 794,100 تومان موتور سروو دنده فلزی MG995 با زاویه چرخش 270 درجه 794,100 تومان شماره پشتیبان تلگرام : 09309220303 شماره پشتیبان واتساپ : 09309220303 تماس با ما مشهد ، میدان صاحب الزمان(عج) ، پاساژ برق و الکترونیک سبحان ، طبقه 3+ 051-37257337 09309220303 ساعات کاری :  شنبه تا پنج شنبه : 9  الی  19 «کلیه حقوق مادی و معنوی این سایت متعلق به آوا الکترونیک می باشد» طراحی سایت به آوا الکترونیک خوش آمدید. رد کردن</t>
+          <t>هیت سینک مناسب رزبری پای Raspberry Pi 4 - آوا الکترونیک . آوا الکترونیک سبد خرید --تمام گروه ها-- ولتمتر ها دماسنج درایور موتور آردوینو سنسور ها - سنسور اثرانگشت - اثرهال - فشار و ارتفاع - دما و رطوبت - سنسورهای کاربردی - سنسور IR و PIR ماژول ها - ماژول کارت خوان - پخش و ضبط صدا - ماژول های رله - ماژول بخار - ماژولهای Bluetooth - ماژول های سرد کننده - اندازه گیر ولتاژ و جریان - ماژول های مبدل - ماژول ساعت - تایمر - ماژول آلتراسونیک - ماژول GSM-GPS-SPRS - ماژول های Wifi - انواع ریموت و ماژول های RF - ماژول شبکه - کوره القایی موتورها - براشلس - سرو موتور - پمپ های هوا و آب - موتور گیربکس - استپ موتور - موتور DC - موتور Coreless - موتور ویبره و لنگ نمایشگرها - LCD قطعات الکترونیکی - آی سی ها -  - سری CMOS - 40XX -  - سری TTL - 74XX -  - آی سی تایمر - پالس -  - تراشه واسط -  - تراشه درایور -  - اپتوکوپلر و اپتوکانتر -  - تراشه OP-AMP -  - صوت و آمپلی فایر -  - سایر آی سی ها - برد برد ها - آنتن ها - بلندگو ها - مقاومت ها -  - مقاومت 1/4 وات -  - مقاومت 1 وات -  - مقاومت 2 وات -  - انواع ولوم و سر ولوم -  - پتانسیومتر -  - مولتی ترن -  - ترمیستور NTC و PTC - انواع کانکتور - ترانزیستورها -  - ماسفت MOSFET -  - BJT ها - سوکت IC - پین هدر - انواع رله - انواع خازن -  - خازن سرامیکی و عدسی -  - خازن الکترولیتی -  - خازن پلی استر - قطعات نوری - انواع فیوز و جافیوزی - کلید، سوئیچ، کیپد - رگولاتورها - دیودها -  - دیود زنر Zener - کریستال و اسیلاتور Raspberry Pi تجهیزات مکانیکی - قفل الکتریکی - شیر برقی سلونوئیدی - انواع آهنربا -  - نئودیمیوم -  -  - بلوک -  -  - استوانه و دیسکی -  -  - کونیک و حلقه ای -  - فریت -  -  - حلقه ای و استوانه تجهیزات الکترونیکی - مولتی متر ها - فن ها - سوئیچینگ های صنعتی - آداپتور ها - سیم لحیم - میکروسکوپ ها - منابع تغذیه آزمایشگاهی - سیم و کابل -  - وارنیش اتوماسیون - کلید مینیاتوری - رله ها -  - تک کنتاکت Uncategorized پروگرامرها پرینتر سه بعدی - کیت پرینتر سه بعدی - لوازم جانبی پرینتر سه بعدی میکروکنترلرها - AVR / PIC - STM انواع باتری، جاباتری و شارژر - انواع جاباتری - انواع پاور بانک شارژر و تستر باتری - انواع باتری ابزارآلات و تجهیزات - ابزار - ابزار مونتاژ و لحیم کاری قطعات رباتیک - چرخ ربات - چرخ دنده - ملخ پروازی - سازه های رباتیک - دسته کنترل - پک آموزشی صفحه اصلی تسویه حساب راهنمای مشتریان حساب کاربری من تماس با ما سبد خرید صفحه اصلی تسویه حساب راهنمای مشتریان حساب کاربری من تماس با ما سبد خرید خانه / Raspberry Pi / هیت سینک مناسب رزبری پای Raspberry Pi 4 هیت سینک مناسب رزبری پای Raspberry Pi 4 143,900 تومان در انبار موجود نمی باشد شناسه محصول: 21121061 دسته: Raspberry Pi اشتراک گذاری این محصول نظرات (0) همه نقد ها هیچ دیدگاهی نوشته نشده است. اولین کسی باشید که نقد می نویسید: “هیت سینک مناسب رزبری پای Raspberry Pi 4” نظر شما نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. محصولات مشابه 0 تومان افزودن به سبد خرید مشاهده سریع برد چهار هسته ای ۶۴ بیتی Orange Pi Lite 2 دارای RAM 1GB و قابلیت بوت اندروید / Ubuntu 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع برد توسعه مولتی فانکش رزبری پای Raspberry Pi 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع کیس ABS رزبری پای Raspberry Pi 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع شیلد افزایش GPIO رزبری پای Raspberry Pi Expansion Shield 0 تومان 151,100 تومان افزودن به سبد خرید مشاهده سریع شیلد پروتوتایپ رزبری پای Raspberry Pi 151,100 تومان 0 تومان افزودن به سبد خرید مشاهده سریع کیس مشکی رزبری پای Raspberry Pi 0 تومان 5,189,100 تومان افزودن به سبد خرید مشاهده سریع نمایشگر ۵ اینچ با تاچ مقاومتی و دارای ورودی HDMI 5,189,100 تومان 0 تومان افزودن به سبد خرید مشاهده سریع دوربین رزپری پای ۵ مگاپیکسل با قابلیت دید در شب 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع کیس شفاف رزبری پای Raspberry Pi 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع برد چهار هسته ای نانو پای NanoPi M1 رم ۱GB 0 تومان 10,004,600 تومان افزودن به سبد خرید مشاهده سریع برد رزبری پای سه Raspberry Pi 3 مدل +A ساخت انگلستان 10,004,600 تومان 0 تومان افزودن به سبد خرید مشاهده سریع شیلد مولتی فانکشن رزبری Multifunction GPIO Extension Board 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع برد رزبری پای Raspberry Pi 4 مدل B با رم ۱GB ساخت UK 0 تومان 0 تومان افزودن به سبد خرید مشاهده سریع آداپتور ۵ ولت ۳ آمپر Type C مناسب رزبری پای ۴ 0 تومان 36,750,000 تومان افزودن به سبد خرید مشاهده سریع برد رزبری پای Raspberry Pi 4 مدل B با رم ۴GB ساخت UK 36,750,000 تومان 15,870,000 تومان افزودن به سبد خرید مشاهده سریع برد رزبری پای +raspberry pi 3 model B اورجینال 15,870,000 تومان دسته های محصولات Raspberry Pi آردوینو ابزارآلات و تجهیزات ابزار ابزار مونتاژ و لحیم کاری اتوماسیون رله ها تک کنتاکت کلید مینیاتوری انواع باتری، جاباتری و شارژر انواع باتری انواع پاور بانک شارژر و تستر باتری انواع جاباتری پروگرامرها پرینتر سه بعدی کیت پرینتر سه بعدی لوازم جانبی پرینتر سه بعدی تجهیزات الکترونیکی آداپتور ها سوئیچینگ های صنعتی سیم لحیم سیم و کابل وارنیش فن ها منابع تغذیه آزمایشگاهی مولتی متر ها میکروسکوپ ها تجهیزات مکانیکی انواع آهنربا فریت حلقه ای و استوانه نئودیمیوم استوانه و دیسکی بلوک کونیک و حلقه ای شیر برقی سلونوئیدی قفل الکتریکی درایور موتور دماسنج سنسور ها اثرهال دما و رطوبت سنسور IR و PIR سنسور اثرانگشت سنسور گاز سنسورهای کاربردی فشار و ارتفاع قطعات الکترونیکی آنتن ها آی سی ها آی سی تایمر - پالس اپتوکوپلر و اپتوکانتر تراشه OP-AMP تراشه درایور تراشه واسط سایر آی سی ها سری CMOS - 40XX سری TTL - 74XX صوت و آمپلی فایر انواع خازن خازن الکترولیتی خازن پلی استر خازن سرامیکی و عدسی انواع رله انواع فیوز و جافیوزی انواع کانکتور برد برد ها بلندگو ها پین هدر ترانزیستورها BJT ها ماسفت MOSFET دیودها دیود زنر Zener رگولاتورها سوکت IC قطعات نوری کریستال و اسیلاتور کلید، سوئیچ، کیپد مقاومت ها انواع ولوم و سر ولوم پتانسیومتر ترمیستور NTC و PTC مقاومت 1 وات مقاومت 1/4 وات مقاومت 2 وات مولتی ترن قطعات رباتیک پک آموزشی چرخ دنده چرخ ربات دسته کنترل سازه های رباتیک ملخ پروازی ماژول ها اندازه گیر ولتاژ و جریان انواع ریموت و ماژول های RF پخش و ضبط صدا کوره القایی ماژول GSM-GPS-SPRS ماژول آلتراسونیک ماژول بخار ماژول ساعت - تایمر ماژول شبکه ماژول کارت خوان ماژول های Wifi ماژول های حرکت و شتاب ماژول های رله ماژول های سرد کننده ماژول های کاربردی ماژول های مبدل ماژولهای Bluetooth ماژولهای ولتاژ و تغذیه موتورها استپ موتور براشلس پمپ های هوا و آب سرو موتور موتور Coreless موتور DC موتور گیربکس موتور ویبره و لنگ میکروکنترلرها AVR / PIC STM نمایشگرها LCD ولتمتر ها پر امتیازترین محصولات اسیلوسکوپ دیجیتال دو کاناله پرتابل مدل SDTEK 9,000,000 تومان سروو موتور دنده فلزی MG995 با زاویه چرخش 360 درجه 794,100 تومان موتور سروو دنده فلزی MG995 با زاویه چرخش 270 درجه 794,100 تومان شماره پشتیبان تلگرام : 09309220303 شماره پشتیبان واتساپ : 09309220303 تماس با ما مشهد ، میدان صاحب الزمان(عج) ، پاساژ برق و الکترونیک سبحان ، طبقه 3+ 051-37257337 09309220303 ساعات کاری :  شنبه تا پنج شنبه : 9  الی  19 «کلیه حقوق مادی و معنوی این سایت متعلق به آوا الکترونیک می باشد» طراحی سایت به آوا الکترونیک خوش آمدید. رد کردن</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1015,10 +1004,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="3" t="n">
         <v>1439000</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="3" t="n">
         <v>1439000</v>
       </c>
     </row>
@@ -1029,7 +1018,7 @@
       <c r="B17" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>https://sepehrelec.com/Products/%d8%a8%d9%84%d9%86%d8%af%da%af%d9%88%db%8c-8-%d8%a7%d9%87%d9%85-YD50-%d9%86%db%8c%d9%85-%d9%88%d8%a7%d8%aa-P103006021.aspx</t>
         </is>
@@ -1044,10 +1033,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="3" t="n">
         <v>840000</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="3" t="n">
         <v>840000</v>
       </c>
     </row>
@@ -1058,7 +1047,7 @@
       <c r="B18" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>https://thecaferobot.com/store/t-nuts-for-2020-series-extruded-aluminium-profile-thread</t>
         </is>
@@ -1073,10 +1062,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="3" t="n">
         <v>60000</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="3" t="n">
         <v>60000</v>
       </c>
     </row>
@@ -1087,7 +1076,7 @@
       <c r="B19" t="n">
         <v>10</v>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>https://www.generalelec.com/product/10749/MARR-5-32-38</t>
         </is>
@@ -1102,10 +1091,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="3" t="n">
         <v>2880500</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="3" t="n">
         <v>28805000</v>
       </c>
     </row>
@@ -1116,14 +1105,14 @@
       <c r="B20" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>https://irenx.ir/shop/product/rain-sensor-module/</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>خرید ماژول سنسور باران و قطره - فروشگاه آیرنکس Skip to navigation Skip to main content به فروشگاه قطعات و برد الکترونیکی سایت تخصصی آیرنکس خوش آمدید بازگشت به آیرنکس ورود / ثبت نام فروشگاه دوره ها تخفیف! قوانین تماس با ما تسویه حساب منو 0 محصول 0 تومان دسته بندی کالاها برد های توسعه پروگرامر برد های ESP برد های STM برد های آردوینو برد های رزبری پای برد های NodeMCU ماژول و سنسور تشخیص و اندازه گیری ماژول فاصله سنج ماژول دما و رطوبت ماژول های سلامتی ماژول شتاب سنج مادون قرمز تشخیص نور تشخیص گاز ارتباطی ماژول GPS رادیویی وای فای سیم کارت GSM ماژول بلوتوث کاربردی ماژول رله کیپد نمایشگر ها ماژول RFID ماژول دوربین دوربین سایر ماژول ها قطعات الکترونیکی قطعات پایه فیوز دیود سلف خازن مقاومت ال ای دی ترانزیستور پتانسیومتر دکمه و سوئیچ تراشه میکروکنترلر موتور درایور رگولاتور رباتیک شاسی ربات انواع موتور لوازم جانبی هویه و لحیم کاری مولتی متر سیم جامپر و کابل برد بورد آداپتور باتری جستجو ورود / ثبت نام 0 محصول 0 تومان -7% بزرگنمایی تصویر خانه ماژول و سنسور سنسور دما و رطوبت ماژول سنسور باران و قطره سنسور دما DS18B20 81,325 تومان بازگشت به محصولات جا باتری 4 تایی قلمی (مناسب ربات) 133,100 تومان قیمت اصلی: 133,100تومان بود. 116,160 تومان قیمت فعلی: 116,160تومان. ماژول سنسور باران و قطره 139,000 تومان قیمت اصلی: 139,000تومان بود. 129,000 تومان قیمت فعلی: 129,000تومان. تعداد قیمت کاستن 5-9 126,420 تومان 2% 10-49 122,550 تومان 5% 50+ 118,680 تومان 8% موجود ماژول سنسور باران و قطره عدد افزودن به سبد خرید توضیحات مشخصات نظرات (0) توضیحات همانطور که از نام این سنسور مشخص است، شما می توانید توسط این سنسور شروع بارش باران یا وجود آب را در مکانی حس کنید و با توجه به آن، عملیات یا واکنش های مورد نظر را در محیط اعمال کنید. خروجی آنالوگ این سنسور با توجه به میزان آب واکنس نشان میدهد. به این شکل که در حالت کاملا خشک ولتاژ 5 ولت را در پین خروجی دارد و در حالتی غیر از این ولتاژ پایین تر را نشان خواهد داد. معرفی ماژول سنسور باران و قطره ماژول سنسور باران و قطره یک قطعه کاربردی برای تشخیص وجود آب یا قطرات باران روی سطح مخصوص خود است. این ماژول در پروژه‌های هوشمندسازی، گلخانه‌های خودکار، دستگاه‌های هشدار بارش و سیستم‌های کنترل محیطی کاربرد فراوان دارد. ویژگی‌های ساختاری و عملکردی شامل صفحه فلزی با پوشش ضد‌اکسید به‌عنوان سطح تشخیص قطره دارای برد الکترونیکی با خروجی دیجیتال و آنالوگ برای تشخیص میزان رطوبت یا وجود آب ولتاژ کاری: 3.3 تا 5 ولت DC مناسب برای Arduino، ESP و Raspberry Pi قابلیت تنظیم حساسیت خروجی دیجیتال با پتانسیومتر روی برد دارای LED وضعیت برای نمایش اتصال یا شناسایی قطره کاربردها و موارد استفاده ساخت سیستم‌های هشدار باران یا قطع آبیاری خودکار تشخیص رطوبت و قطره آب در پروژه‌های گلخانه یا محیط‌زیست ترکیب با سیستم‌های اتوماسیون جهت فعال‌سازی موتور یا پمپ پس از تشخیص بارش پروژه‌های DIY آموزشی برای یادگیری سیگنال آنالوگ و دیجیتال استفاده در ربات‌ها برای تشخیص محیط مرطوب یا شرایط بارانی نتیجه‌گیری ماژول سنسور باران و قطره با نصب آسان، قیمت اقتصادی و عملکرد قابل‌اعتماد، ابزاری مناسب برای تشخیص وجود آب یا قطرات باران در پروژه‌های هوشمند است. اگر به‌دنبال مانیتورینگ شرایط آب‌و‌هوایی یا اتوماسیون کشاورزی هستید، این سنسور یکی از گزینه‌های جذاب و کاربردی خواهد بود. مشخصات ولتاژ تغذیه 5 ولت ولتاژ خروجی 0 تا 5 ولت آنالوگ قابلیت ها دارای پتانسیومتر برای تنظیم میزان حساسیت دارای نشانگر LED برای نمایش رطوبت بیش از حد مجاز نظرات (0) دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “ماژول سنسور باران و قطره” لغو پاسخ نشانی ایمیل شما منتشر نخواهد شد. بخش‌های موردنیاز علامت‌گذاری شده‌اند * امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. محصولات مشابه نمایشگر OLED SSD1306 نمره 5.00 از 5 406,621 تومان – 389,318 تومان Price range: 389,318تومان through 406,621تومان انتخاب گزینه ها این محصول دارای انواع مختلفی می باشد. گزینه ها ممکن است در صفحه محصول انتخاب شوند -50% ماژول دوربین OV7670 788,716 تومان قیمت اصلی: 788,716تومان بود. 395,670 تومان قیمت فعلی: 395,670تومان. افزودن به سبد خرید سنسور نور GY-30 263,780 تومان افزودن به سبد خرید ماژول التراسونیک HC-SR04 204,490 تومان افزودن به سبد خرید -7% ماژول فشار سنج BMP180 119,006 تومان قیمت اصلی: 119,006تومان بود. 110,740 تومان قیمت فعلی: 110,740تومان. افزودن به سبد خرید سنسور دما و رطوبت DHT11 107,690 تومان افزودن به سبد خرید ماژول LDR 79,860 تومان افزودن به سبد خرید سون سگمنت تکی قرمز (آند) 36,337 تومان افزودن به سبد خرید درباره فروشگاه آیرنکس مجموعه آیرنکس با بیش از 8 سال سابقه در زمینه الکترونیک و برنامه نویسی برد های مختلف اکنون در زمینه فروش قطعات و برد ها با بالا ترین کیفیت فعالیت میکند. تماس با ما بهترین روش ارتباط گفتگو با پشتیبان آنلاین است واتساپ و تلگرام: 09926776982 (فعلا تماس پاسخگو نیستیم) آدرس: بجنورد، میدان خرمشهر، خیابان شانزده متری سوم فرهنگیان، دفتر آیرنکس نماد اعتماد الکترونیکی © تمامی حقوق برای فروشگاه آیرنکس محفوظ است. by REMIM.IR جستجو منو دسته بندی ها برد های توسعه پروگرامر برد های ESP برد های STM برد های آردوینو برد های رزبری پای برد های NodeMCU ماژول و سنسور تشخیص و اندازه گیری ماژول فاصله سنج ماژول دما و رطوبت ماژول های سلامتی ماژول شتاب سنج مادون قرمز تشخیص نور تشخیص گاز ارتباطی ماژول GPS رادیویی وای فای سیم کارت GSM ماژول بلوتوث کاربردی ماژول رله کیپد نمایشگر ها ماژول RFID ماژول دوربین دوربین سایر ماژول ها قطعات الکترونیکی قطعات پایه فیوز دیود سلف خازن مقاومت ال ای دی ترانزیستور پتانسیومتر دکمه و سوئیچ تراشه میکروکنترلر موتور درایور رگولاتور رباتیک شاسی ربات انواع موتور لوازم جانبی هویه و لحیم کاری مولتی متر سیم جامپر و کابل برد بورد آداپتور باتری فروشگاه دوره ها تخفیف! قوانین تماس با ما تسویه حساب سبد خرید بستن سفارشات ثبت شده در 8 و 9 مرداد، شنبه 10 مرداد تحویل پست میشود. سفارشات ثبت شده در شنبه 10 مرداد به بعد، شنبه هفته بعد 17 مرداد ارسال میشود. ورود بستن نام کاربری یا آدرس ایمیل * الزامی رمز عبور * الزامی ورود رمز عبور را فراموش کرده اید؟ مرا به خاطر بسپار ادامه هنوز حساب کاربری ندارید؟ ایجاد حساب کاربری ماژول سنسور باران و قطره 139,000 تومان قیمت اصلی: 139,000تومان بود. 129,000 تومان قیمت فعلی: 129,000تومان. موجود ماژول سنسور باران و قطره عدد افزودن به سبد خرید ورود / عضویت استفاده از موبایل مرا به خاطر بسپار ادامه بازنشانی رمز عبور استفاده از موبایل ادامه خانه حساب کاربری من 0 محصول سبد خرید</t>
+          <t>خرید ماژول سنسور باران و قطره - فروشگاه آیرنکس Skip to navigation Skip to main content به فروشگاه قطعات و برد الکترونیکی سایت تخصصی آیرنکس خوش آمدید بازگشت به آیرنکس ورود / ثبت نام فروشگاه دوره ها تخفیف! قوانین تماس با ما تسویه حساب منو 0 محصول 0 تومان دسته بندی کالاها برد های توسعه پروگرامر برد های ESP برد های STM برد های آردوینو برد های رزبری پای برد های NodeMCU ماژول و سنسور تشخیص و اندازه گیری ماژول فاصله سنج ماژول دما و رطوبت ماژول های سلامتی ماژول شتاب سنج مادون قرمز تشخیص نور تشخیص گاز ارتباطی ماژول GPS رادیویی وای فای سیم کارت GSM ماژول بلوتوث کاربردی ماژول رله کیپد نمایشگر ها ماژول RFID ماژول دوربین دوربین سایر ماژول ها قطعات الکترونیکی قطعات پایه فیوز دیود سلف خازن مقاومت ال ای دی ترانزیستور پتانسیومتر دکمه و سوئیچ تراشه میکروکنترلر موتور درایور رگولاتور رباتیک شاسی ربات انواع موتور لوازم جانبی هویه و لحیم کاری مولتی متر سیم جامپر و کابل برد بورد آداپتور باتری جستجو ورود / ثبت نام 0 محصول 0 تومان -7% بزرگنمایی تصویر خانه ماژول و سنسور سنسور دما و رطوبت ماژول سنسور باران و قطره سنسور دما DS18B20 81,325 تومان بازگشت به محصولات جا باتری 4 تایی قلمی (مناسب ربات) 133,100 تومان قیمت اصلی: 133,100تومان بود. 116,160 تومان قیمت فعلی: 116,160تومان. ماژول سنسور باران و قطره 139,000 تومان قیمت اصلی: 139,000تومان بود. 129,000 تومان قیمت فعلی: 129,000تومان. تعداد قیمت کاستن 5-9 126,420 تومان 2% 10-49 122,550 تومان 5% 50+ 118,680 تومان 8% موجود ماژول سنسور باران و قطره عدد افزودن به سبد خرید توضیحات مشخصات نظرات (0) توضیحات همانطور که از نام این سنسور مشخص است، شما می توانید توسط این سنسور شروع بارش باران یا وجود آب را در مکانی حس کنید و با توجه به آن، عملیات یا واکنش های مورد نظر را در محیط اعمال کنید. خروجی آنالوگ این سنسور با توجه به میزان آب واکنس نشان میدهد. به این شکل که در حالت کاملا خشک ولتاژ 5 ولت را در پین خروجی دارد و در حالتی غیر از این ولتاژ پایین تر را نشان خواهد داد. معرفی ماژول سنسور باران و قطره ماژول سنسور باران و قطره یک قطعه کاربردی برای تشخیص وجود آب یا قطرات باران روی سطح مخصوص خود است. این ماژول در پروژه‌های هوشمندسازی، گلخانه‌های خودکار، دستگاه‌های هشدار بارش و سیستم‌های کنترل محیطی کاربرد فراوان دارد. ویژگی‌های ساختاری و عملکردی شامل صفحه فلزی با پوشش ضد‌اکسید به‌عنوان سطح تشخیص قطره دارای برد الکترونیکی با خروجی دیجیتال و آنالوگ برای تشخیص میزان رطوبت یا وجود آب ولتاژ کاری: 3.3 تا 5 ولت DC مناسب برای Arduino، ESP و Raspberry Pi قابلیت تنظیم حساسیت خروجی دیجیتال با پتانسیومتر روی برد دارای LED وضعیت برای نمایش اتصال یا شناسایی قطره کاربردها و موارد استفاده ساخت سیستم‌های هشدار باران یا قطع آبیاری خودکار تشخیص رطوبت و قطره آب در پروژه‌های گلخانه یا محیط‌زیست ترکیب با سیستم‌های اتوماسیون جهت فعال‌سازی موتور یا پمپ پس از تشخیص بارش پروژه‌های DIY آموزشی برای یادگیری سیگنال آنالوگ و دیجیتال استفاده در ربات‌ها برای تشخیص محیط مرطوب یا شرایط بارانی نتیجه‌گیری ماژول سنسور باران و قطره با نصب آسان، قیمت اقتصادی و عملکرد قابل‌اعتماد، ابزاری مناسب برای تشخیص وجود آب یا قطرات باران در پروژه‌های هوشمند است. اگر به‌دنبال مانیتورینگ شرایط آب‌و‌هوایی یا اتوماسیون کشاورزی هستید، این سنسور یکی از گزینه‌های جذاب و کاربردی خواهد بود. مشخصات ولتاژ تغذیه 5 ولت ولتاژ خروجی 0 تا 5 ولت آنالوگ قابلیت ها دارای پتانسیومتر برای تنظیم میزان حساسیت دارای نشانگر LED برای نمایش رطوبت بیش از حد مجاز نظرات (0) دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “ماژول سنسور باران و قطره” لغو پاسخ نشانی ایمیل شما منتشر نخواهد شد. بخش‌های موردنیاز علامت‌گذاری شده‌اند * امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. محصولات مشابه ماژول بلوتوث HC-05 471,900 تومان افزودن به سبد خرید نمایشگر OLED SSD1306 نمره 5.00 از 5 406,621 تومان – 389,318 تومان Price range: 389,318تومان through 406,621تومان انتخاب گزینه ها این محصول دارای انواع مختلفی می باشد. گزینه ها ممکن است در صفحه محصول انتخاب شوند ماژول FTDI FT232rl نمره 5.00 از 5 265,523 تومان افزودن به سبد خرید -25% ماژول رطوبت سنج خاک 158,835 تومان قیمت اصلی: 158,835تومان بود. 119,790 تومان قیمت فعلی: 119,790تومان. افزودن به سبد خرید ماژول جوی استیک 114,950 تومان افزودن به سبد خرید -7% ماژول فشار سنج BMP180 119,006 تومان قیمت اصلی: 119,006تومان بود. 110,740 تومان قیمت فعلی: 110,740تومان. افزودن به سبد خرید سنسور دما و رطوبت DHT11 107,690 تومان افزودن به سبد خرید ماژول LDR 79,860 تومان افزودن به سبد خرید درباره فروشگاه آیرنکس مجموعه آیرنکس با بیش از 8 سال سابقه در زمینه الکترونیک و برنامه نویسی برد های مختلف اکنون در زمینه فروش قطعات و برد ها با بالا ترین کیفیت فعالیت میکند. تماس با ما بهترین روش ارتباط گفتگو با پشتیبان آنلاین است واتساپ و تلگرام: 09926776982 (فعلا تماس پاسخگو نیستیم) آدرس: بجنورد، میدان خرمشهر، خیابان شانزده متری سوم فرهنگیان، دفتر آیرنکس نماد اعتماد الکترونیکی © تمامی حقوق برای فروشگاه آیرنکس محفوظ است. by REMIM.IR جستجو منو دسته بندی ها برد های توسعه پروگرامر برد های ESP برد های STM برد های آردوینو برد های رزبری پای برد های NodeMCU ماژول و سنسور تشخیص و اندازه گیری ماژول فاصله سنج ماژول دما و رطوبت ماژول های سلامتی ماژول شتاب سنج مادون قرمز تشخیص نور تشخیص گاز ارتباطی ماژول GPS رادیویی وای فای سیم کارت GSM ماژول بلوتوث کاربردی ماژول رله کیپد نمایشگر ها ماژول RFID ماژول دوربین دوربین سایر ماژول ها قطعات الکترونیکی قطعات پایه فیوز دیود سلف خازن مقاومت ال ای دی ترانزیستور پتانسیومتر دکمه و سوئیچ تراشه میکروکنترلر موتور درایور رگولاتور رباتیک شاسی ربات انواع موتور لوازم جانبی هویه و لحیم کاری مولتی متر سیم جامپر و کابل برد بورد آداپتور باتری فروشگاه دوره ها تخفیف! قوانین تماس با ما تسویه حساب سبد خرید بستن سفارشات ثبت شده در 8 و 9 مرداد، شنبه 10 مرداد تحویل پست میشود. سفارشات ثبت شده در شنبه 10 مرداد به بعد، شنبه هفته بعد 17 مرداد ارسال میشود. ورود بستن نام کاربری یا آدرس ایمیل * الزامی رمز عبور * الزامی ورود رمز عبور را فراموش کرده اید؟ مرا به خاطر بسپار ادامه هنوز حساب کاربری ندارید؟ ایجاد حساب کاربری ماژول سنسور باران و قطره 139,000 تومان قیمت اصلی: 139,000تومان بود. 129,000 تومان قیمت فعلی: 129,000تومان. موجود ماژول سنسور باران و قطره عدد افزودن به سبد خرید ورود / عضویت استفاده از موبایل مرا به خاطر بسپار ادامه بازنشانی رمز عبور استفاده از موبایل ادامه خانه حساب کاربری من 0 محصول سبد خرید</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1131,10 +1120,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="3" t="n">
         <v>1290000</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="3" t="n">
         <v>1290000</v>
       </c>
     </row>
@@ -1145,7 +1134,7 @@
       <c r="B21" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>https://jamtronic.com/product/%d9%85%d8%a7%da%98%d9%88%d9%84-%d8%b4%d8%a7%d8%b1%da%98%d8%b1-%d9%88-%d8%a8%d9%88%d8%b3%d8%aa%d8%b1-type-c/</t>
         </is>
@@ -1177,7 +1166,7 @@
 (به زودی) کیبورد و کیپد جامپر و سیم جامپر
 (به زودی) سایر تجهیزات
 (به زودی) سیم و کابل کواکسیال
-(به زودی) شبکه سیم و کابل فرمان، دیتا، سنسوری(AWG) سیم و کابل برق و پاور مخابراتی و آیفونی و تلفنی کابل فلت و FFC سیم باندی (اسپیکری) سایر سیم و کابل ها فیلامنت سیم لاکی سیم نسوز سیلیکونی سیم وایر رپ محصولات کلکسیونی تولید داخل انتخاب دسته بندی انتخاب دسته بندی ابزارآلات و تجهیزات آچار آچار سوکت زن و پرسی ابزار تعمیر موبایل اسیلوسکوپ پد نسوز پیچ گوشتی موبایلی سایر تجهیزات موبایل قاب بازکن و تاچ کش منبع تغذیه ابزار سوراخ کاری و مته ابزار مونتاژ، تعمیر و لحیم کاری اسید، روغن، فلاکس لحیم کاری اسید، رنگ و ملزومات مدارچاپی روغن و فلاکس لحیم کاری خمیر و چسب سیلیکون سایر ملزومات مونتاژ محلول سیم لحیم، خمیر و ساچمه قلع فرچه، جامایع و الکل قلع کش و انواع تمیزکننده ها هویه، هیتر، وان قلع، نوک، سرهویه و المنت نوک، سرهویه و المنت هویه، هیتر و وان قلع اسپری تمیز کننده انبردست و دم باریک بست کمری پنس و کاتر پیچ گوشتی تجهیزات اندازه گیری مولتی متر تجهیزات حفاظتی و کنترلی جامپر و سیم جامپر جعبه ابزار و قطعات چسب چسب آلومینیومی چسب برق چسب ترانس چسب حرارتی چسب دوطرفه چسب مسی چسب نسوز و ساده چسب، حلال و موادشیمیایی سایر ابزار الکترونیک پراب و کابل تست میکروسکوپ و ذره بین سشوار و چسب حرارتی سوهان سیم چین، کف چین گیره سوسماری وارنیش پروگرامر و بردهای آموزشی بردهای خانواده RASPBERRY بردهای خانواده آردوینو Arduino پروگرامر مینی کامپیوتر Mini PC سایر مینی کامپیوترها تجهیزات جانبی انواع نمایشگر LCD/TFT/OLED نمایشگر HDMI/VGA نمایشگر LCD/GLCD نمایشگر OLED درایور LCD کابل و مبدل صوتی تصویری کابل و مبدل کامپیوتری کابل، شارژر و مبدل USB کیبورد و کیپد لامپ و چراغ قوه محافظ تیراژه موتور STEP موتور سروو موتور موتور DC موتور گیربكس تولید داخل دوره های آموزشی ESP-32 سنسور سایر سنسورها سنسور القایی سنسور جریان سنسور دما و رطوبت سنسور گاز سنسور نور و IR سنسور و لنز PIR سنسور وزن سیم و کابل سایر سیم و کابل ها سیم افشان سیم باندی، اسپیکری سیم لاکی سیم نسوز سیلیکونی سیم وایر رپ شبکه فیلامنت کابل برق کابل فلت مخابراتی و آیفونی و تلفنی فروش عمده قطعات الکترونیکی کانکتور قطعات الکترونیکی LED و تجهیزات مرتبط LED اوال و کلاهی LED شیشه ای، هایبرایت و لیزری LED مات و خودرنگ درایور POWER LED سایر تجهیزات مرتبط لنز Power LED آنتن آنتن GPS آنتن UHF و رادیویی آنتن WIFI/GSM/GPRS آی سی Voltage Reference آی سی رگولاتور سوئیچینگ آی سی مقایسه‌گر آی سی های حافظه آی سی های ریموت کنترل اپتوکوپلر و اپتوکانتر تایمر و پالس تراشه CMOS تراشه OP-AMP تراشه TTL تراشه واسط درایور موتور سایر تراشه ها صوت و آمپلی فایر مبدل ADC و DAC مبدل های ولتاژ، جریان، فرکانس باتری برد برد (Bread Board) پیچ و اسپیسر پین هدر ترانزیستور ترانزیستور BJT ترانزیستور ماسفت (MOSFET) ترایاک و تریستور جاباتری خازن خازن MKT خازن الکترولیتی خازن های الکترولیت 16V خازن های الکترولیت 25V خازن های الکترولیت 35V خازن های الکترولیت 50V خازن های الکترولیت بالای 50V خازن پلی استر خازن تانتال خازن سرامیکی و عدسی خازن مایلار خازن مولتی لایر دیود پل دیودها دیود زنر ZENER دیود سریع Fast دیود شاتکی سایر دیودها رگولاتور رله رله الکترومکانیکی سایر قطعات الکترونیک ZIF سوکت تبدیل و کانکتور USB ترمینال و سوکت فونیکس جک اسپیکر و میکروفن سرسیم و وایرشو فیش و جک آداپتور قطعات صوتی کانکتور BNC و Coaxial کانکتور FPC کانکتور فیش شبکه و تلفن کانکتور کامپیوتری سگمنت و ماتریس سون سگمنت سلف سلف بشکه ای و دمبلی سلف مقاومتی سوكت، کانکتور، فیش باکس هدر و IDC ترمینال سوکت IC معمولی سوکت IC نظامی کانکتور XH کانکتور پاور کانکتور مخابراتی و بین راهی فن حلزونی فیبر، برد تبدیل، برد سوراخ دار برد تبدیل فیبر مدارچاپی فیوز جا فیوزی فیوز بشکه ای فیوز حرارتی فیوز شیشه ای فیوز گچی کریستال کلید، سوئیچ، کیپد تک سوئیچ دیپ سوئیچ سلکتور شستی کلید راکر کلید کلنگی و کشویی کیپد و صفحه کلید میکروسوئیچ کیس دستگاه لیزر مقاومت پتانسیومتر ترمیستور NTC و PTC مقاومت 1 وات مقاومت 1/2 وات مقاومت 1/4 وات مقاومت ntc مقاومت دیود مقاومت شانه ای و Array مولتی ترن ولوم میکروکنترلر و پروسسور ARM AVR سایر میکروکنترلرها میکروکنترلر PIC هیت سینک و المان حرارتی المان سرد/گرم کننده پد عایق هیت سینک وریستور ماژول سایر ماژول های کاربردی ماژول LED ماژول ZigBee ماژول اثر انگشت ماژول بخار سرد ماژول پرینتر، چاپگر ماژول پزشکی ماژول تایمر ماژول تغذیه، ولتاژ و جریان سایر ماژول آداپتور ماژول افزاینده ولتاژ ماژول پاوربانک ماژول کاهنده ولتاژ ماژول حرکتی و شتاب ماژول حرکت و لرزش ماژول شتاب سنج ماژول درایور موتور ماژول دما، رطوبت، فشار و گاز ماژول سنسور گاز ماژول فشار سنج ماژول کنترل دما ماژول رله ماژول صوتی و آلتراسونیک ماژول آلتراسونیک ماژول آمپلی فایر ماژول مبدل و واسط ماژول نمایشگر و دوربین ماژول دوربین ماژول نمایشگر ماژول وایرلس ماژول GPS-GSM-GPRS ماژول rf ماژول rfid آنتن و تگ RFID ماژول های RFID ماژول wifi ماژول بلوتوث ماژول و سوئیچ PIR ولتمتر و آمپرمتر روپنلی محصولات کاربردی محصولات کلکسیونی جستجو درخواست های محبوب ماژول ابزارآلات و تجهیزات تجهیزات جانبی سنسور 0 مورد / 0 تومان 0 0 ورود ایجاد یک حساب کاربری نام کاربری یا آدرس ایمیل * الزامی رمز عبور * الزامی ورود رمز عبور را فراموش کرده اید؟ مرا به خاطر بسپار جستجو ورود ایجاد یک حساب کاربری نام کاربری یا آدرس ایمیل * الزامی رمز عبور * الزامی ورود رمز عبور را فراموش کرده اید؟ مرا به خاطر بسپار خانه / ماژول / ماژول تغذیه، ولتاژ و جریان / ماژول پاوربانک / ماژول شارژر و بوستر باتری لیتیومی TYPE-C 2A ماژول سنسور ضربان قلب مناسب ARDUINO 358,000 تومان بازگشت به محصولات ای دی سی فلت خور 26 پین IDC 2*13 12,000 تومان برای بزرگنمایی کلیک کنید ماژول شارژر و بوستر باتری لیتیومی TYPE-C 2A امتیازدهی 5.00 از 5 در 3 امتیازدهی مشتری ( 3 بازخورد مشتری) شارژر و مبدل  افزاینده USB 5V 2A Type-C با شارژر USB شناسه محصول: 9154 دسته: ماژول , ماژول پاوربانک , ماژول تغذیه، ولتاژ و جریان اشتراک گذاری: 106,000 تومان موجود - ماژول شارژر و بوستر باتری لیتیومی TYPE-C 2A عدد + افزودن به سبد خرید مقايسه افزودن به علاقه مندی 0 افرادی که اکنون این محصول را تماشا می کنند! توضیحات مشخصات فنی دانلود دیتاشیت پرسش و پاسخ نظرات (3) ماژول شارژر و بوستر باتری لیتیومی Type‑C 2A یک برد ترکیبی برای شارژ باتری لیتیوم‌یون/لیتیوم‌پلیمر تک‌سل و تبدیل ولتاژ باتری به خروجی 5 ولت است. این نوع ماژول‌ها برای ساخت پاوربانک، تغذیه مدارهای 5 ولتی، و پروژه‌های قابل حمل خیلی کاربردی‌اند و معمولاً با ورودی Type‑C شارژ می‌شوند. این ماژول معمولاً دو بخش اصلی دارد: شارژر باتری و بوستر 5 ولت. بخش شارژر باتری، ورودی 5 ولت را می‌گیرد و باتری 3.7 ولتی تک‌سل را با روش CC/CV شارژ می‌کند؛ یعنی ابتدا جریان ثابت و سپس ولتاژ ثابت تا باتری به 4.2 یا 4.35 ولت برسد. بخش بوستر هم ولتاژ باتری را به 5 ولت پایدار تبدیل می‌کند تا بتوان از آن برای تغذیه خروجی USB یا بارهای 5 ولتی استفاده کرد. در بعضی مدل‌ها، وقتی باتری ضعیف یا خالی است، چراغ قرمز وضعیت شارژ را نشان می‌دهد و بعد از تکمیل شارژ، چراغ آبی روشن می‌شود. اگر مدل شما از نوع پاوربانکی باشد، معمولاً امکان شارژ هم‌زمان و دشارژ هم‌زمان هم وجود دارد و برای خروجی 5V تا حدود 2 آمپر مناسب است. ویدیوی شارژر و بوستر باتری لیتیومی TYPE-C 2A https://dl.jamtronic.com/video/%D9%85%D8%A7%DA%98%D9%88%D9%84%20%D8%B4%D8%A7%D8%B1%DA%98%D8%B1%20%D9%88%20%D8%A8%D9%88%D8%B3%D8%AA%D8%B1%20TYPE-C.mp4 مشخصات فنی ماژول شارژر و تقویت کننده TYPE-C: نوع ماژول: شارژر و بوستر باتری لیتیومی تک‌سل. ورودی: 5 تا 5.5 ولت DC از طریق Type‑C. جریان شارژ: 2 آمپر ± 5% باتری قابل پشتیبانی: لیتیوم‌یون و لیتیوم‌پلیمر 3.6 / 3.7 / 4.2 ولت تک‌سل. ولتاژ شارژ کامل: حدود 4.2 ولت، و در بعضی نسخه‌ها 4.35 ولت. جریان شارژ: حدود 2 آمپر، در برخی مدل‌ها بسته به مدار تا 2.4 آمپر. خروجی بوستر: 5 ولت پایدار. جریان خروجی بوستر: تا 2 آمپر. بازدهی: حدود 92 تا 92.5 درصد. نشانگر LED: قرمز برای شارژ، آبی برای شارژ کامل. جریان استاتیک باتری: در بعضی مدل‌ها کمتر از 30 میکروآمپر. دانلود دیتاشیت ماژول شارژر و بوستر باتری لیتیومی TYPE-C 2A سؤالات متداول برای شارژر و ماژول تقویت کننده TYPE-C: 1. این ماژول چه کاری انجام می‌دهد؟ باتری لیتیومی تک‌سل را شارژ می‌کند و هم‌زمان ولتاژ آن را به 5 ولت برای خروجی تبدیل می‌کند. 2. برای چه باتری‌هایی مناسب است؟ برای باتری‌های لیتیوم‌یون و لیتیوم‌پلیمر تک‌سل 3.7 ولتی مناسب است. 3. آیا با Type‑C شارژ می‌شود؟ بله، ورودی شارژ آن از طریق پورت Type‑C و با 5 ولت تأمین می‌شود. 4. خروجی آن چند ولت است؟ خروجی بوستر معمولاً 5 ولت DC است. 5. جریان خروجی چقدر است؟ تا حدود 2 آمپر، بسته به نسخه و خنک‌کاری. 6. آیا برای پاوربانک مناسب است؟ بله، دقیقاً برای همین کار خیلی استفاده می‌شود. 7. چراغ‌های روی برد چه معنی دارند؟ معمولاً قرمز یعنی در حال شارژ و آبی یعنی شارژ کامل. 8. آیا محافظ باتری هم دارد؟ بعضی نسخه‌ها بخش محافظ دارند، اما همه مدل‌ها BMS کامل نیستند؛ باید مشخصات همان برد را بررسی کرد. 9. آیا می‌توان هم‌زمان شارژ و خروجی گرفت؟ در بعضی مدل‌های پاوربانکی بله. 10. از کجا برایش دیتاشیت یا مرجع بخوانم؟ صفحه‌های فروشگاه‌های معتبر بالا بهترین مرجع‌های فنی برای همین ماژول هستند. 3 دیدگاه برای ماژول شارژر و بوستر باتری لیتیومی TYPE-C 2A حامد – خرداد 28, 1403 - ژوئن 17, 2024 امتیاز 5 از 5 این ماژول همزمان برای دشارژ باتری هم قابل استفاده هست ؟ و اینکه باتری های لیتیوم پلیمر هم میشه باهاش شارژ کرد ؟ پشتیبان جم ترونیک – تیر 31, 1403 - ژوئیه 21, 2024 سلام فقط برای شارژه و برای باتری های لیتیومی مناسبه فرزاد – دی 25, 1403 - ژانویه 14, 2025 امتیاز 5 از 5 با سلام پورت یو اس بی نصب نیست روی برد ؟ کدوم مدل میتونه حداقل خروجی با ثباتی 1 امپر  و 5 ولتی داشته باشه که چراغ  یو اس بی روشن کنیم  باهاش ماژول  ارزان خروجی ثابتی ندارن و چراغ سو سو میزنه پشتیبان جم ترونیک – دی 29, 1403 - ژانویه 18, 2025 سلام بله سوکت جدا هست این سوسو زدن هم بخاطر خروجی محافظت شده ماژول هست کاریش نمیشه کرد. فرزاد – دی 25, 1403 - ژانویه 14, 2025 امتیاز 5 از 5 چنتا باتری 18650 میشه وصل کرد؟ پشتیبان جم ترونیک – دی 29, 1403 - ژانویه 18, 2025 سلام یک عدد دیدگاه شما پس از تایید نمایش داده می شود امتیاز 4 از 5 درود بر شما خروجی ۵ ولتش ۲  امپر است؟ دیدگاه خود را بنویسید لغو پاسخ برای فرستادن دیدگاه، باید وارد شده باشید. 106,000 تومان موجود - ماژول شارژر و بوستر باتری لیتیومی TYPE-C 2A عدد + افزودن به سبد خرید مقايسه افزودن به علاقه مندی 0 افرادی که اکنون این محصول را تماشا می کنند! محصولات مرتبط مقايسه نمایش سریع افزودن به علاقه مندی ترموستات دیجیتال دما روپنلی مدل XY-WT01 امتیاز 5.00 از 5 موجود 1,546,000 تومان افزودن به سبد خرید کد انحصاری محصول : 9688 مقايسه نمایش سریع افزودن به علاقه مندی شارژر باتری TP4056 سه چیپ با TYPE-C امتیاز 4.50 از 5 موجود 29,000 تومان افزودن به سبد خرید کد انحصاری محصول : 8445 مقايسه نمایش سریع افزودن به علاقه مندی ماژول LED RGB دارای چیپ درایور WS2812 موجود 43,000 تومان افزودن به سبد خرید کد انحصاری محصول : 10097 مقايسه نمایش سریع افزودن به علاقه مندی ماژول 9 محوره ژیروسکوپ-شتاب سنج-قطب نما GY-85 موجود 986,000 تومان افزودن به سبد خرید کد انحصاری محصول : 10140 حمل و نقل رایگان با پست سفارشات بالای 10 میلیون تومان بهترین قیمت بازار ضمانت اصالت کالا پشتیبانی فنی ماژول خرید ماژول ماژول آلتراسونیک و صوتی ماژول تغذیه، ولتاژ و جریان ماژول وایرلس ماژول بولوتوث قطعات الکترونیکی مقاومت خازن ترانزیستور سایر لینکهای سریع تماس با ما درباره ما شرایط و قوانین فروشگاه راهنمای خرید تماس با پشتیبانی 02191694828 تمام حقوق برای جم ترونیک محفوظ است. بستن منو دسته بندی ها ماژول ماژول صوتی و آلتراسونیک ماژول آمپلی فایر ماژول آلتراسونیک ماژول وایرلس ماژول های RFID ماژول rfid آنتن و تگ RFID ماژول بلوتوث ماژول و سوئیچ PIR ماژول rf ماژول wifi ماژول GPS-GSM-GPRS ماژول پزشکی ماژول ZigBee ماژول پرینتر، چاپگر ماژول تغذیه، ولتاژ و جریان سایر ماژول بخار سرد ماژول آداپتور ماژول کاهنده ولتاژ ماژول افزاینده ولتاژ ماژول پاوربانک ماژول حرکتی و شتاب ماژول شتاب سنج ماژول حرکت و لرزش ماژول نمایشگر و دوربین ماژول نمایشگر ماژول دوربین ماژول دما، رطوبت، فشار و گاز ماژول فشار سنج ماژول کنترل دما ماژول سنسور گاز ماژول اثر انگشت ماژول بخار سرد ولتمتر و آمپرمتر روپنلی ماژول تایمر ماژول درایور موتور ماژول مبدل و واسط ماژول رله ماژول LED سایر ماژول های کاربردی قطعات الکترونیکی مقاومت مقاومت 1/2 وات مقاومت شانه ای و Array مقاومت 1/4 وات مقاومت 1 وات مقاومت وات بالا و آجری پتانسیومتر مولتی ترن ولوم ترمیستور NTC و PTC سایر قطعات الکترونیک کانکتور کامپیوتری کانکتور فیش شبکه و تلفن جک اسپیکر و میکروفن فیش و جک آداپتور سرسیم و وایرشو ZIF سوکت تبدیل و کانکتور USB کانکتور FPC قطعات صوتی دیود سایر دیودها دیود زنر ZENER پل دیودها دیود شاتکی دیود سریع Fast خازن خازن مایلار خازن الکترولیتی خازن های الکترولیت 50V خازن های الکترولیت 35V خازن های الکترولیت 16V خازن های الکترولیت 25V خازن های الکترولیت بالای 50V خازن سرامیکی و عدسی خازن پلی استر خازن مولتی لایر خازن MKT خازن تانتال LED و تجهیزات مرتبط سایر تجهیزات مرتبط درایور POWER LED لنز Power LED LED رشد گیاه LED مات و خودرنگ LED اوال و کلاهی LED شیشه ای، هایبرایت و لیزری میکروکنترلر و پروسسور میکروکنترلر PIC AVR ARM سایر میکروکنترلرها آی سی درایور موتور مبدل های ولتاژ، جریان، فرکانس آی سی رگولاتور سوئیچینگ آی سی های ریموت کنترل Voltage Reference آی سی های حافظه آی سی مقایسه‌گر تراشه واسط اپتوکوپلر و اپتوکانتر مبدل ADC و DAC تراشه TTL تراشه CMOS تراشه OP-AMP صوت و آمپلی فایر تایمر و پالس سایر تراشه ها سوكت، کانکتور، فیش کانکتور مخابراتی و بین راهی کانکتور پاور سوکت IC معمولی سوکت IC نظامی باکس هدر و IDC ترمینال سایر ترانزیستور ترانزیستور ماسفت (MOSFET) ترانزیستور BJT فیوز فیوز گچی فیوز شیشه ای فیوز حرارتی جا فیوزی فیوز بشکه ای رله رله الکترومکانیکی کلید، سوئیچ، کیپد کلید کلنگی و کشویی دیپ سوئیچ کیپد و صفحه کلید تک سوئیچ کلید راکر شستی میکروسوئیچ سلکتور سگمنت و ماتریس سون سگمنت آنتن آنتن UHF و رادیویی آنتن GPS آنتن WIFI/GSM/GPRS کانکتور و اتصالات رگولاتور کریستال ترایاک و تریستور پین هدر لیزر پیچ و اسپیسر برد برد (Bread Board) وریستور فیبر، برد تبدیل، برد سوراخ دار فیبر مدارچاپی سلف سلف بشکه ای و دمبلی سلف مقاومتی هیت سینک و المان حرارتی پد عایق هیت سینک المان سرد/گرم کننده سنسور سنسور جریان سنسور وزن سنسور دما و رطوبت سنسور نور و IR سنسور گاز سایر سنسورها ابزارآلات و تجهیزات آچار انبردست و دم باریک ابزار سوراخ کاری و مته سشوار و چسب حرارتی گیره سوسماری ابزار مونتاژ، تعمیر و لحیم کاری خمیر و چسب سیلیکون فرچه، جامایع و الکل سایر ملزومات مونتاژ سیم لحیم، خمیر و ساچمه قلع قلع کش و انواع تمیزکننده ها اسید، روغن، فلاکس لحیم کاری اسید، رنگ و ملزومات مدارچاپی روغن و فلاکس لحیم کاری هویه، هیتر، وان قلع، نوک، سرهویه و المنت هویه، هیتر و وان قلع نوک، سرهویه و المنت پیچ گوشتی ابزار تعمیر موبایل منبع تغذیه پد نسوز اسیلوسکوپ سایر تجهیزات موبایل قاب بازکن و تاچ کش پیچ گوشتی موبایلی چسب چسب دوطرفه چسب حرارتی چسب ترانس چسب برق چسب مسی چسب آلومینیومی چسب، حلال و موادشیمیایی چسب نسوز و ساده تجهیزات اندازه گیری مولتی متر سیم چین، کف چین اسپری تمیز کننده پنس و کاتر وارنیش بست کمری سوهان جعبه ابزار و قطعات سایر ابزار الکترونیک آچار سوکت زن و پرسی میکروسکوپ و ذره بین پراب و کابل تست پروگرامر و بردهای آموزشی پروگرامر بردهای خانواده RASPBERRY بردهای خانواده آردوینو Arduino تجهیزات جانبی موتور موتور گیربكس موتور DC STEP موتور سروو موتور لامپ و چراغ قوه کیبورد و کیپد کابل و مبدل صوتی تصویری کابل، شارژر و مبدل USB انواع نمایشگر LCD/TFT/OLED نمایشگر LCD/GLCD نمایشگر HDMI/VGA نمایشگر OLED درایور LCD سیم و کابل مخابراتی و آیفونی و تلفنی فیلامنت سیم نسوز سیلیکونی سیم وایر رپ سیم لاکی کابل برق سیم باندی، اسپیکری کابل فلت سایر سیم و کابل ها شبکه سیم افشان محصولات کلکسیونی تولید داخل جاباتری چاپ و سفارش pcb برد مدار چاپی مجله جم ترونیک پروژه‌ها و ایده‌ها سوال‌های متداول ماژول ماژول صوتی و آلتراسونیک ماژول آمپلی فایر ماژول آلتراسونیک ماژول وایرلس ماژول های RFID ماژول rfid آنتن و تگ RFID ماژول بلوتوث ماژول و سوئیچ PIR ماژول rf ماژول wifi ماژول GPS-GSM-GPRS ماژول پزشکی ماژول ZigBee ماژول پرینتر، چاپگر ماژول تغذیه، ولتاژ و جریان سایر ماژول بخار سرد ماژول آداپتور ماژول کاهنده ولتاژ ماژول افزاینده ولتاژ ماژول پاوربانک ماژول حرکتی و شتاب ماژول شتاب سنج ماژول حرکت و لرزش ماژول نمایشگر و دوربین ماژول نمایشگر ماژول دوربین ماژول دما، رطوبت، فشار و گاز ماژول فشار سنج ماژول کنترل دما ماژول سنسور گاز ماژول اثر انگشت ماژول بخار سرد ولتمتر و آمپرمتر روپنلی ماژول تایمر ماژول درایور موتور ماژول مبدل و واسط ماژول رله ماژول LED سایر ماژول های کاربردی قطعات الکترونیکی مقاومت مقاومت 1/2 وات مقاومت شانه ای و Array مقاومت 1/4 وات مقاومت 1 وات مقاومت وات بالا و آجری پتانسیومتر مولتی ترن ولوم ترمیستور NTC و PTC سایر قطعات الکترونیک کانکتور کامپیوتری کانکتور فیش شبکه و تلفن جک اسپیکر و میکروفن فیش و جک آداپتور سرسیم و وایرشو ZIF سوکت تبدیل و کانکتور USB کانکتور FPC قطعات صوتی دیود سایر دیودها دیود زنر ZENER پل دیودها دیود شاتکی دیود سریع Fast خازن خازن مایلار خازن الکترولیتی خازن های الکترولیت 50V خازن های الکترولیت 35V خازن های الکترولیت 16V خازن های الکترولیت 25V خازن های الکترولیت بالای 50V خازن سرامیکی و عدسی خازن پلی استر خازن مولتی لایر خازن MKT خازن تانتال LED و تجهیزات مرتبط سایر تجهیزات مرتبط درایور POWER LED لنز Power LED LED رشد گیاه LED مات و خودرنگ LED اوال و کلاهی LED شیشه ای، هایبرایت و لیزری میکروکنترلر و پروسسور میکروکنترلر PIC AVR ARM سایر میکروکنترلرها آی سی درایور موتور مبدل های ولتاژ، جریان، فرکانس آی سی رگولاتور سوئیچینگ آی سی های ریموت کنترل Voltage Reference آی سی های حافظه آی سی مقایسه‌گر تراشه واسط اپتوکوپلر و اپتوکانتر مبدل ADC و DAC تراشه TTL تراشه CMOS تراشه OP-AMP صوت و آمپلی فایر تایمر و پالس سایر تراشه ها سوكت، کانکتور، فیش کانکتور مخابراتی و بین راهی کانکتور پاور سوکت IC معمولی سوکت IC نظامی باکس هدر و IDC ترمینال سایر ترانزیستور ترانزیستور ماسفت (MOSFET) ترانزیستور BJT فیوز فیوز گچی فیوز شیشه ای فیوز حرارتی جا فیوزی فیوز بشکه ای رله رله الکترومکانیکی کلید، سوئیچ، کیپد کلید کلنگی و کشویی دیپ سوئیچ کیپد و صفحه کلید تک سوئیچ کلید راکر شستی میکروسوئیچ سلکتور سگمنت و ماتریس سون سگمنت آنتن آنتن UHF و رادیویی آنتن GPS آنتن WIFI/GSM/GPRS کانکتور و اتصالات رگولاتور کریستال ترایاک و تریستور پین هدر لیزر پیچ و اسپیسر برد برد (Bread Board) وریستور فیبر، برد تبدیل، برد سوراخ دار فیبر مدارچاپی سلف سلف بشکه ای و دمبلی سلف مقاومتی هیت سینک و المان حرارتی پد عایق هیت سینک المان سرد/گرم کننده سنسور سنسور جریان سنسور وزن سنسور دما و رطوبت سنسور نور و IR سنسور گاز سایر سنسورها ابزارآلات و تجهیزات آچار انبردست و دم باریک ابزار سوراخ کاری و مته سشوار و چسب حرارتی گیره سوسماری ابزار مونتاژ، تعمیر و لحیم کاری خمیر و چسب سیلیکون فرچه، جامایع و الکل سایر ملزومات مونتاژ سیم لحیم، خمیر و ساچمه قلع قلع کش و انواع تمیزکننده ها اسید، روغن، فلاکس لحیم کاری اسید، رنگ و ملزومات مدارچاپی روغن و فلاکس لحیم کاری هویه، هیتر، وان قلع، نوک، سرهویه و المنت هویه، هیتر و وان قلع نوک، سرهویه و المنت پیچ گوشتی ابزار تعمیر موبایل منبع تغذیه پد نسوز اسیلوسکوپ سایر تجهیزات موبایل قاب بازکن و تاچ کش پیچ گوشتی موبایلی چسب چسب دوطرفه چسب حرارتی چسب ترانس چسب برق چسب مسی چسب آلومینیومی چسب، حلال و موادشیمیایی چسب نسوز و ساده تجهیزات اندازه گیری مولتی متر سیم چین، کف چین اسپری تمیز کننده پنس و کاتر وارنیش بست کمری سوهان جعبه ابزار و قطعات سایر ابزار الکترونیک آچار سوکت زن و پرسی میکروسکوپ و ذره بین پراب و کابل تست پروگرامر و بردهای آموزشی پروگرامر بردهای خانواده RASPBERRY بردهای خانواده آردوینو Arduino تجهیزات جانبی موتور موتور گیربكس موتور DC STEP موتور سروو موتور لامپ و چراغ قوه کیبورد و کیپد کابل و مبدل صوتی تصویری کابل، شارژر و مبدل USB انواع نمایشگر LCD/TFT/OLED نمایشگر LCD/GLCD نمایشگر HDMI/VGA نمایشگر OLED درایور LCD سیم و کابل مخابراتی و آیفونی و تلفنی فیلامنت سیم نسوز سیلیکونی سیم وایر رپ سیم لاکی کابل برق سیم باندی، اسپیکری کابل فلت سایر سیم و کابل ها شبکه سیم افشان محصولات کلکسیونی تولید داخل جاباتری چاپ و سفارش pcb برد مدار چاپی مجله جم ترونیک پروژه‌ها و ایده‌ها سوال‌های متداول سبد خرید بستن فروشگاه 0 لیست علاقه مندی ها 0 مورد سبد خرید حساب من</t>
+(به زودی) شبکه سیم و کابل فرمان، دیتا، سنسوری(AWG) سیم و کابل برق و پاور مخابراتی و آیفونی و تلفنی کابل فلت و FFC سیم باندی (اسپیکری) سایر سیم و کابل ها فیلامنت سیم لاکی سیم نسوز سیلیکونی سیم وایر رپ محصولات کلکسیونی تولید داخل انتخاب دسته بندی انتخاب دسته بندی ابزارآلات و تجهیزات آچار آچار سوکت زن و پرسی ابزار تعمیر موبایل اسیلوسکوپ پد نسوز پیچ گوشتی موبایلی سایر تجهیزات موبایل قاب بازکن و تاچ کش منبع تغذیه ابزار سوراخ کاری و مته ابزار مونتاژ، تعمیر و لحیم کاری اسید، روغن، فلاکس لحیم کاری اسید، رنگ و ملزومات مدارچاپی روغن و فلاکس لحیم کاری خمیر و چسب سیلیکون سایر ملزومات مونتاژ محلول سیم لحیم، خمیر و ساچمه قلع فرچه، جامایع و الکل قلع کش و انواع تمیزکننده ها هویه، هیتر، وان قلع، نوک، سرهویه و المنت نوک، سرهویه و المنت هویه، هیتر و وان قلع اسپری تمیز کننده انبردست و دم باریک بست کمری پنس و کاتر پیچ گوشتی تجهیزات اندازه گیری مولتی متر تجهیزات حفاظتی و کنترلی جامپر و سیم جامپر جعبه ابزار و قطعات چسب چسب آلومینیومی چسب برق چسب ترانس چسب حرارتی چسب دوطرفه چسب مسی چسب نسوز و ساده چسب، حلال و موادشیمیایی سایر ابزار الکترونیک پراب و کابل تست میکروسکوپ و ذره بین سشوار و چسب حرارتی سوهان سیم چین، کف چین گیره سوسماری وارنیش پروگرامر و بردهای آموزشی بردهای خانواده RASPBERRY بردهای خانواده آردوینو Arduino پروگرامر مینی کامپیوتر Mini PC سایر مینی کامپیوترها تجهیزات جانبی انواع نمایشگر LCD/TFT/OLED نمایشگر HDMI/VGA نمایشگر LCD/GLCD نمایشگر OLED درایور LCD کابل و مبدل صوتی تصویری کابل و مبدل کامپیوتری کابل، شارژر و مبدل USB کیبورد و کیپد لامپ و چراغ قوه محافظ تیراژه موتور STEP موتور سروو موتور موتور DC موتور گیربكس تولید داخل دوره های آموزشی ESP-32 سنسور سایر سنسورها سنسور القایی سنسور جریان سنسور دما و رطوبت سنسور گاز سنسور نور و IR سنسور و لنز PIR سنسور وزن سیم و کابل سایر سیم و کابل ها سیم افشان سیم باندی، اسپیکری سیم لاکی سیم نسوز سیلیکونی سیم وایر رپ شبکه فیلامنت کابل برق کابل فلت مخابراتی و آیفونی و تلفنی فروش عمده قطعات الکترونیکی کانکتور قطعات الکترونیکی LED و تجهیزات مرتبط LED اوال و کلاهی LED شیشه ای، هایبرایت و لیزری LED مات و خودرنگ درایور POWER LED سایر تجهیزات مرتبط لنز Power LED آنتن آنتن GPS آنتن UHF و رادیویی آنتن WIFI/GSM/GPRS آی سی Voltage Reference آی سی رگولاتور سوئیچینگ آی سی مقایسه‌گر آی سی های حافظه آی سی های ریموت کنترل اپتوکوپلر و اپتوکانتر تایمر و پالس تراشه CMOS تراشه OP-AMP تراشه TTL تراشه واسط درایور موتور سایر تراشه ها صوت و آمپلی فایر مبدل ADC و DAC مبدل های ولتاژ، جریان، فرکانس باتری برد برد (Bread Board) پیچ و اسپیسر پین هدر ترانزیستور ترانزیستور BJT ترانزیستور ماسفت (MOSFET) ترایاک و تریستور جاباتری خازن خازن MKT خازن الکترولیتی خازن های الکترولیت 16V خازن های الکترولیت 25V خازن های الکترولیت 35V خازن های الکترولیت 50V خازن های الکترولیت بالای 50V خازن پلی استر خازن تانتال خازن سرامیکی و عدسی خازن مایلار خازن مولتی لایر دیود پل دیودها دیود زنر ZENER دیود سریع Fast دیود شاتکی سایر دیودها رگولاتور رله رله الکترومکانیکی سایر قطعات الکترونیک ZIF سوکت تبدیل و کانکتور USB ترمینال و سوکت فونیکس جک اسپیکر و میکروفن سرسیم و وایرشو فیش و جک آداپتور قطعات صوتی کانکتور BNC و Coaxial کانکتور FPC کانکتور فیش شبکه و تلفن کانکتور کامپیوتری سگمنت و ماتریس سون سگمنت سلف سلف بشکه ای و دمبلی سلف مقاومتی سوكت، کانکتور، فیش باکس هدر و IDC ترمینال سوکت IC معمولی سوکت IC نظامی کانکتور XH کانکتور پاور کانکتور مخابراتی و بین راهی فن حلزونی فیبر، برد تبدیل، برد سوراخ دار برد تبدیل فیبر مدارچاپی فیوز جا فیوزی فیوز بشکه ای فیوز حرارتی فیوز شیشه ای فیوز گچی کریستال کلید، سوئیچ، کیپد تک سوئیچ دیپ سوئیچ سلکتور شستی کلید راکر کلید کلنگی و کشویی کیپد و صفحه کلید میکروسوئیچ کیس دستگاه لیزر مقاومت پتانسیومتر ترمیستور NTC و PTC مقاومت 1 وات مقاومت 1/2 وات مقاومت 1/4 وات مقاومت ntc مقاومت دیود مقاومت شانه ای و Array مولتی ترن ولوم میکروکنترلر و پروسسور ARM AVR سایر میکروکنترلرها میکروکنترلر PIC هیت سینک و المان حرارتی المان سرد/گرم کننده پد عایق هیت سینک وریستور ماژول سایر ماژول های کاربردی ماژول LED ماژول ZigBee ماژول اثر انگشت ماژول بخار سرد ماژول پرینتر، چاپگر ماژول پزشکی ماژول تایمر ماژول تغذیه، ولتاژ و جریان سایر ماژول آداپتور ماژول افزاینده ولتاژ ماژول پاوربانک ماژول کاهنده ولتاژ ماژول حرکتی و شتاب ماژول حرکت و لرزش ماژول شتاب سنج ماژول درایور موتور ماژول دما، رطوبت، فشار و گاز ماژول سنسور گاز ماژول فشار سنج ماژول کنترل دما ماژول رله ماژول صوتی و آلتراسونیک ماژول آلتراسونیک ماژول آمپلی فایر ماژول مبدل و واسط ماژول نمایشگر و دوربین ماژول دوربین ماژول نمایشگر ماژول وایرلس ماژول GPS-GSM-GPRS ماژول rf ماژول rfid آنتن و تگ RFID ماژول های RFID ماژول wifi ماژول بلوتوث ماژول و سوئیچ PIR ولتمتر و آمپرمتر روپنلی محصولات کاربردی محصولات کلکسیونی جستجو درخواست های محبوب ماژول ابزارآلات و تجهیزات تجهیزات جانبی سنسور 0 مورد / 0 تومان 0 0 ورود ایجاد یک حساب کاربری نام کاربری یا آدرس ایمیل * الزامی رمز عبور * الزامی ورود رمز عبور را فراموش کرده اید؟ مرا به خاطر بسپار جستجو ورود ایجاد یک حساب کاربری نام کاربری یا آدرس ایمیل * الزامی رمز عبور * الزامی ورود رمز عبور را فراموش کرده اید؟ مرا به خاطر بسپار خانه / ماژول / ماژول تغذیه، ولتاژ و جریان / ماژول پاوربانک / ماژول شارژر و بوستر باتری لیتیومی TYPE-C 2A ماژول سنسور ضربان قلب مناسب ARDUINO 358,000 تومان بازگشت به محصولات ای دی سی فلت خور 26 پین IDC 2*13 12,000 تومان برای بزرگنمایی کلیک کنید ماژول شارژر و بوستر باتری لیتیومی TYPE-C 2A امتیازدهی 5.00 از 5 در 3 امتیازدهی مشتری ( 3 بازخورد مشتری) شارژر و مبدل  افزاینده USB 5V 2A Type-C با شارژر USB شناسه محصول: 9154 دسته: ماژول , ماژول پاوربانک , ماژول تغذیه، ولتاژ و جریان اشتراک گذاری: 106,000 تومان موجود - ماژول شارژر و بوستر باتری لیتیومی TYPE-C 2A عدد + افزودن به سبد خرید مقايسه افزودن به علاقه مندی 0 افرادی که اکنون این محصول را تماشا می کنند! توضیحات مشخصات فنی دانلود دیتاشیت پرسش و پاسخ نظرات (3) ماژول شارژر و بوستر باتری لیتیومی Type‑C 2A یک برد ترکیبی برای شارژ باتری لیتیوم‌یون/لیتیوم‌پلیمر تک‌سل و تبدیل ولتاژ باتری به خروجی 5 ولت است. این نوع ماژول‌ها برای ساخت پاوربانک، تغذیه مدارهای 5 ولتی، و پروژه‌های قابل حمل خیلی کاربردی‌اند و معمولاً با ورودی Type‑C شارژ می‌شوند. این ماژول معمولاً دو بخش اصلی دارد: شارژر باتری و بوستر 5 ولت. بخش شارژر باتری، ورودی 5 ولت را می‌گیرد و باتری 3.7 ولتی تک‌سل را با روش CC/CV شارژ می‌کند؛ یعنی ابتدا جریان ثابت و سپس ولتاژ ثابت تا باتری به 4.2 یا 4.35 ولت برسد. بخش بوستر هم ولتاژ باتری را به 5 ولت پایدار تبدیل می‌کند تا بتوان از آن برای تغذیه خروجی USB یا بارهای 5 ولتی استفاده کرد. در بعضی مدل‌ها، وقتی باتری ضعیف یا خالی است، چراغ قرمز وضعیت شارژ را نشان می‌دهد و بعد از تکمیل شارژ، چراغ آبی روشن می‌شود. اگر مدل شما از نوع پاوربانکی باشد، معمولاً امکان شارژ هم‌زمان و دشارژ هم‌زمان هم وجود دارد و برای خروجی 5V تا حدود 2 آمپر مناسب است. ویدیوی شارژر و بوستر باتری لیتیومی TYPE-C 2A https://dl.jamtronic.com/video/%D9%85%D8%A7%DA%98%D9%88%D9%84%20%D8%B4%D8%A7%D8%B1%DA%98%D8%B1%20%D9%88%20%D8%A8%D9%88%D8%B3%D8%AA%D8%B1%20TYPE-C.mp4 مشخصات فنی ماژول شارژر و تقویت کننده TYPE-C: نوع ماژول: شارژر و بوستر باتری لیتیومی تک‌سل. ورودی: 5 تا 5.5 ولت DC از طریق Type‑C. جریان شارژ: 2 آمپر ± 5% باتری قابل پشتیبانی: لیتیوم‌یون و لیتیوم‌پلیمر 3.6 / 3.7 / 4.2 ولت تک‌سل. ولتاژ شارژ کامل: حدود 4.2 ولت، و در بعضی نسخه‌ها 4.35 ولت. جریان شارژ: حدود 2 آمپر، در برخی مدل‌ها بسته به مدار تا 2.4 آمپر. خروجی بوستر: 5 ولت پایدار. جریان خروجی بوستر: تا 2 آمپر. بازدهی: حدود 92 تا 92.5 درصد. نشانگر LED: قرمز برای شارژ، آبی برای شارژ کامل. جریان استاتیک باتری: در بعضی مدل‌ها کمتر از 30 میکروآمپر. دانلود دیتاشیت ماژول شارژر و بوستر باتری لیتیومی TYPE-C 2A سؤالات متداول برای شارژر و ماژول تقویت کننده TYPE-C: 1. این ماژول چه کاری انجام می‌دهد؟ باتری لیتیومی تک‌سل را شارژ می‌کند و هم‌زمان ولتاژ آن را به 5 ولت برای خروجی تبدیل می‌کند. 2. برای چه باتری‌هایی مناسب است؟ برای باتری‌های لیتیوم‌یون و لیتیوم‌پلیمر تک‌سل 3.7 ولتی مناسب است. 3. آیا با Type‑C شارژ می‌شود؟ بله، ورودی شارژ آن از طریق پورت Type‑C و با 5 ولت تأمین می‌شود. 4. خروجی آن چند ولت است؟ خروجی بوستر معمولاً 5 ولت DC است. 5. جریان خروجی چقدر است؟ تا حدود 2 آمپر، بسته به نسخه و خنک‌کاری. 6. آیا برای پاوربانک مناسب است؟ بله، دقیقاً برای همین کار خیلی استفاده می‌شود. 7. چراغ‌های روی برد چه معنی دارند؟ معمولاً قرمز یعنی در حال شارژ و آبی یعنی شارژ کامل. 8. آیا محافظ باتری هم دارد؟ بعضی نسخه‌ها بخش محافظ دارند، اما همه مدل‌ها BMS کامل نیستند؛ باید مشخصات همان برد را بررسی کرد. 9. آیا می‌توان هم‌زمان شارژ و خروجی گرفت؟ در بعضی مدل‌های پاوربانکی بله. 10. از کجا برایش دیتاشیت یا مرجع بخوانم؟ صفحه‌های فروشگاه‌های معتبر بالا بهترین مرجع‌های فنی برای همین ماژول هستند. 3 دیدگاه برای ماژول شارژر و بوستر باتری لیتیومی TYPE-C 2A حامد – خرداد 28, 1403 - ژوئن 17, 2024 امتیاز 5 از 5 این ماژول همزمان برای دشارژ باتری هم قابل استفاده هست ؟ و اینکه باتری های لیتیوم پلیمر هم میشه باهاش شارژ کرد ؟ پشتیبان جم ترونیک – تیر 31, 1403 - ژوئیه 21, 2024 سلام فقط برای شارژه و برای باتری های لیتیومی مناسبه فرزاد – دی 25, 1403 - ژانویه 14, 2025 امتیاز 5 از 5 با سلام پورت یو اس بی نصب نیست روی برد ؟ کدوم مدل میتونه حداقل خروجی با ثباتی 1 امپر  و 5 ولتی داشته باشه که چراغ  یو اس بی روشن کنیم  باهاش ماژول  ارزان خروجی ثابتی ندارن و چراغ سو سو میزنه پشتیبان جم ترونیک – دی 29, 1403 - ژانویه 18, 2025 سلام بله سوکت جدا هست این سوسو زدن هم بخاطر خروجی محافظت شده ماژول هست کاریش نمیشه کرد. فرزاد – دی 25, 1403 - ژانویه 14, 2025 امتیاز 5 از 5 چنتا باتری 18650 میشه وصل کرد؟ پشتیبان جم ترونیک – دی 29, 1403 - ژانویه 18, 2025 سلام یک عدد دیدگاه شما پس از تایید نمایش داده می شود امتیاز 4 از 5 درود بر شما خروجی ۵ ولتش ۲  امپر است؟ دیدگاه خود را بنویسید لغو پاسخ برای فرستادن دیدگاه، باید وارد شده باشید. 106,000 تومان موجود - ماژول شارژر و بوستر باتری لیتیومی TYPE-C 2A عدد + افزودن به سبد خرید مقايسه افزودن به علاقه مندی 0 افرادی که اکنون این محصول را تماشا می کنند! محصولات مرتبط مقايسه نمایش سریع افزودن به علاقه مندی ماژول رله 2 کانال WiFi-ESP8266 اتمام موجودی اطلاعات بیشتر کد انحصاری محصول : 9276 مقايسه نمایش سریع افزودن به علاقه مندی برد توسعه درایور استپر موتور 8825/A4988 موجود 165,000 تومان افزودن به سبد خرید کد انحصاری محصول : 10100 مقايسه نمایش سریع افزودن به علاقه مندی سنسور دما و رطوبت AM2301 موجود 470,000 تومان افزودن به سبد خرید کد انحصاری محصول : 8207 مقايسه نمایش سریع افزودن به علاقه مندی ماژول LED چراغ راهنمایی و رانندگی موجود 54,000 تومان افزودن به سبد خرید کد انحصاری محصول : 9082 حمل و نقل رایگان با پست سفارشات بالای 10 میلیون تومان بهترین قیمت بازار ضمانت اصالت کالا پشتیبانی فنی ماژول خرید ماژول ماژول آلتراسونیک و صوتی ماژول تغذیه، ولتاژ و جریان ماژول وایرلس ماژول بولوتوث قطعات الکترونیکی مقاومت خازن ترانزیستور سایر لینکهای سریع تماس با ما درباره ما شرایط و قوانین فروشگاه راهنمای خرید تماس با پشتیبانی 02191694828 تمام حقوق برای جم ترونیک محفوظ است. بستن منو دسته بندی ها ماژول ماژول صوتی و آلتراسونیک ماژول آمپلی فایر ماژول آلتراسونیک ماژول وایرلس ماژول های RFID ماژول rfid آنتن و تگ RFID ماژول بلوتوث ماژول و سوئیچ PIR ماژول rf ماژول wifi ماژول GPS-GSM-GPRS ماژول پزشکی ماژول ZigBee ماژول پرینتر، چاپگر ماژول تغذیه، ولتاژ و جریان سایر ماژول بخار سرد ماژول آداپتور ماژول کاهنده ولتاژ ماژول افزاینده ولتاژ ماژول پاوربانک ماژول حرکتی و شتاب ماژول شتاب سنج ماژول حرکت و لرزش ماژول نمایشگر و دوربین ماژول نمایشگر ماژول دوربین ماژول دما، رطوبت، فشار و گاز ماژول فشار سنج ماژول کنترل دما ماژول سنسور گاز ماژول اثر انگشت ماژول بخار سرد ولتمتر و آمپرمتر روپنلی ماژول تایمر ماژول درایور موتور ماژول مبدل و واسط ماژول رله ماژول LED سایر ماژول های کاربردی قطعات الکترونیکی مقاومت مقاومت 1/2 وات مقاومت شانه ای و Array مقاومت 1/4 وات مقاومت 1 وات مقاومت وات بالا و آجری پتانسیومتر مولتی ترن ولوم ترمیستور NTC و PTC سایر قطعات الکترونیک کانکتور کامپیوتری کانکتور فیش شبکه و تلفن جک اسپیکر و میکروفن فیش و جک آداپتور سرسیم و وایرشو ZIF سوکت تبدیل و کانکتور USB کانکتور FPC قطعات صوتی دیود سایر دیودها دیود زنر ZENER پل دیودها دیود شاتکی دیود سریع Fast خازن خازن مایلار خازن الکترولیتی خازن های الکترولیت 50V خازن های الکترولیت 35V خازن های الکترولیت 16V خازن های الکترولیت 25V خازن های الکترولیت بالای 50V خازن سرامیکی و عدسی خازن پلی استر خازن مولتی لایر خازن MKT خازن تانتال LED و تجهیزات مرتبط سایر تجهیزات مرتبط درایور POWER LED لنز Power LED LED رشد گیاه LED مات و خودرنگ LED اوال و کلاهی LED شیشه ای، هایبرایت و لیزری میکروکنترلر و پروسسور میکروکنترلر PIC AVR ARM سایر میکروکنترلرها آی سی درایور موتور مبدل های ولتاژ، جریان، فرکانس آی سی رگولاتور سوئیچینگ آی سی های ریموت کنترل Voltage Reference آی سی های حافظه آی سی مقایسه‌گر تراشه واسط اپتوکوپلر و اپتوکانتر مبدل ADC و DAC تراشه TTL تراشه CMOS تراشه OP-AMP صوت و آمپلی فایر تایمر و پالس سایر تراشه ها سوكت، کانکتور، فیش کانکتور مخابراتی و بین راهی کانکتور پاور سوکت IC معمولی سوکت IC نظامی باکس هدر و IDC ترمینال سایر ترانزیستور ترانزیستور ماسفت (MOSFET) ترانزیستور BJT فیوز فیوز گچی فیوز شیشه ای فیوز حرارتی جا فیوزی فیوز بشکه ای رله رله الکترومکانیکی کلید، سوئیچ، کیپد کلید کلنگی و کشویی دیپ سوئیچ کیپد و صفحه کلید تک سوئیچ کلید راکر شستی میکروسوئیچ سلکتور سگمنت و ماتریس سون سگمنت آنتن آنتن UHF و رادیویی آنتن GPS آنتن WIFI/GSM/GPRS کانکتور و اتصالات رگولاتور کریستال ترایاک و تریستور پین هدر لیزر پیچ و اسپیسر برد برد (Bread Board) وریستور فیبر، برد تبدیل، برد سوراخ دار فیبر مدارچاپی سلف سلف بشکه ای و دمبلی سلف مقاومتی هیت سینک و المان حرارتی پد عایق هیت سینک المان سرد/گرم کننده سنسور سنسور جریان سنسور وزن سنسور دما و رطوبت سنسور نور و IR سنسور گاز سایر سنسورها ابزارآلات و تجهیزات آچار انبردست و دم باریک ابزار سوراخ کاری و مته سشوار و چسب حرارتی گیره سوسماری ابزار مونتاژ، تعمیر و لحیم کاری خمیر و چسب سیلیکون فرچه، جامایع و الکل سایر ملزومات مونتاژ سیم لحیم، خمیر و ساچمه قلع قلع کش و انواع تمیزکننده ها اسید، روغن، فلاکس لحیم کاری اسید، رنگ و ملزومات مدارچاپی روغن و فلاکس لحیم کاری هویه، هیتر، وان قلع، نوک، سرهویه و المنت هویه، هیتر و وان قلع نوک، سرهویه و المنت پیچ گوشتی ابزار تعمیر موبایل منبع تغذیه پد نسوز اسیلوسکوپ سایر تجهیزات موبایل قاب بازکن و تاچ کش پیچ گوشتی موبایلی چسب چسب دوطرفه چسب حرارتی چسب ترانس چسب برق چسب مسی چسب آلومینیومی چسب، حلال و موادشیمیایی چسب نسوز و ساده تجهیزات اندازه گیری مولتی متر سیم چین، کف چین اسپری تمیز کننده پنس و کاتر وارنیش بست کمری سوهان جعبه ابزار و قطعات سایر ابزار الکترونیک آچار سوکت زن و پرسی میکروسکوپ و ذره بین پراب و کابل تست پروگرامر و بردهای آموزشی پروگرامر بردهای خانواده RASPBERRY بردهای خانواده آردوینو Arduino تجهیزات جانبی موتور موتور گیربكس موتور DC STEP موتور سروو موتور لامپ و چراغ قوه کیبورد و کیپد کابل و مبدل صوتی تصویری کابل، شارژر و مبدل USB انواع نمایشگر LCD/TFT/OLED نمایشگر LCD/GLCD نمایشگر HDMI/VGA نمایشگر OLED درایور LCD سیم و کابل مخابراتی و آیفونی و تلفنی فیلامنت سیم نسوز سیلیکونی سیم وایر رپ سیم لاکی کابل برق سیم باندی، اسپیکری کابل فلت سایر سیم و کابل ها شبکه سیم افشان محصولات کلکسیونی تولید داخل جاباتری چاپ و سفارش pcb برد مدار چاپی مجله جم ترونیک پروژه‌ها و ایده‌ها سوال‌های متداول ماژول ماژول صوتی و آلتراسونیک ماژول آمپلی فایر ماژول آلتراسونیک ماژول وایرلس ماژول های RFID ماژول rfid آنتن و تگ RFID ماژول بلوتوث ماژول و سوئیچ PIR ماژول rf ماژول wifi ماژول GPS-GSM-GPRS ماژول پزشکی ماژول ZigBee ماژول پرینتر، چاپگر ماژول تغذیه، ولتاژ و جریان سایر ماژول بخار سرد ماژول آداپتور ماژول کاهنده ولتاژ ماژول افزاینده ولتاژ ماژول پاوربانک ماژول حرکتی و شتاب ماژول شتاب سنج ماژول حرکت و لرزش ماژول نمایشگر و دوربین ماژول نمایشگر ماژول دوربین ماژول دما، رطوبت، فشار و گاز ماژول فشار سنج ماژول کنترل دما ماژول سنسور گاز ماژول اثر انگشت ماژول بخار سرد ولتمتر و آمپرمتر روپنلی ماژول تایمر ماژول درایور موتور ماژول مبدل و واسط ماژول رله ماژول LED سایر ماژول های کاربردی قطعات الکترونیکی مقاومت مقاومت 1/2 وات مقاومت شانه ای و Array مقاومت 1/4 وات مقاومت 1 وات مقاومت وات بالا و آجری پتانسیومتر مولتی ترن ولوم ترمیستور NTC و PTC سایر قطعات الکترونیک کانکتور کامپیوتری کانکتور فیش شبکه و تلفن جک اسپیکر و میکروفن فیش و جک آداپتور سرسیم و وایرشو ZIF سوکت تبدیل و کانکتور USB کانکتور FPC قطعات صوتی دیود سایر دیودها دیود زنر ZENER پل دیودها دیود شاتکی دیود سریع Fast خازن خازن مایلار خازن الکترولیتی خازن های الکترولیت 50V خازن های الکترولیت 35V خازن های الکترولیت 16V خازن های الکترولیت 25V خازن های الکترولیت بالای 50V خازن سرامیکی و عدسی خازن پلی استر خازن مولتی لایر خازن MKT خازن تانتال LED و تجهیزات مرتبط سایر تجهیزات مرتبط درایور POWER LED لنز Power LED LED رشد گیاه LED مات و خودرنگ LED اوال و کلاهی LED شیشه ای، هایبرایت و لیزری میکروکنترلر و پروسسور میکروکنترلر PIC AVR ARM سایر میکروکنترلرها آی سی درایور موتور مبدل های ولتاژ، جریان، فرکانس آی سی رگولاتور سوئیچینگ آی سی های ریموت کنترل Voltage Reference آی سی های حافظه آی سی مقایسه‌گر تراشه واسط اپتوکوپلر و اپتوکانتر مبدل ADC و DAC تراشه TTL تراشه CMOS تراشه OP-AMP صوت و آمپلی فایر تایمر و پالس سایر تراشه ها سوكت، کانکتور، فیش کانکتور مخابراتی و بین راهی کانکتور پاور سوکت IC معمولی سوکت IC نظامی باکس هدر و IDC ترمینال سایر ترانزیستور ترانزیستور ماسفت (MOSFET) ترانزیستور BJT فیوز فیوز گچی فیوز شیشه ای فیوز حرارتی جا فیوزی فیوز بشکه ای رله رله الکترومکانیکی کلید، سوئیچ، کیپد کلید کلنگی و کشویی دیپ سوئیچ کیپد و صفحه کلید تک سوئیچ کلید راکر شستی میکروسوئیچ سلکتور سگمنت و ماتریس سون سگمنت آنتن آنتن UHF و رادیویی آنتن GPS آنتن WIFI/GSM/GPRS کانکتور و اتصالات رگولاتور کریستال ترایاک و تریستور پین هدر لیزر پیچ و اسپیسر برد برد (Bread Board) وریستور فیبر، برد تبدیل، برد سوراخ دار فیبر مدارچاپی سلف سلف بشکه ای و دمبلی سلف مقاومتی هیت سینک و المان حرارتی پد عایق هیت سینک المان سرد/گرم کننده سنسور سنسور جریان سنسور وزن سنسور دما و رطوبت سنسور نور و IR سنسور گاز سایر سنسورها ابزارآلات و تجهیزات آچار انبردست و دم باریک ابزار سوراخ کاری و مته سشوار و چسب حرارتی گیره سوسماری ابزار مونتاژ، تعمیر و لحیم کاری خمیر و چسب سیلیکون فرچه، جامایع و الکل سایر ملزومات مونتاژ سیم لحیم، خمیر و ساچمه قلع قلع کش و انواع تمیزکننده ها اسید، روغن، فلاکس لحیم کاری اسید، رنگ و ملزومات مدارچاپی روغن و فلاکس لحیم کاری هویه، هیتر، وان قلع، نوک، سرهویه و المنت هویه، هیتر و وان قلع نوک، سرهویه و المنت پیچ گوشتی ابزار تعمیر موبایل منبع تغذیه پد نسوز اسیلوسکوپ سایر تجهیزات موبایل قاب بازکن و تاچ کش پیچ گوشتی موبایلی چسب چسب دوطرفه چسب حرارتی چسب ترانس چسب برق چسب مسی چسب آلومینیومی چسب، حلال و موادشیمیایی چسب نسوز و ساده تجهیزات اندازه گیری مولتی متر سیم چین، کف چین اسپری تمیز کننده پنس و کاتر وارنیش بست کمری سوهان جعبه ابزار و قطعات سایر ابزار الکترونیک آچار سوکت زن و پرسی میکروسکوپ و ذره بین پراب و کابل تست پروگرامر و بردهای آموزشی پروگرامر بردهای خانواده RASPBERRY بردهای خانواده آردوینو Arduino تجهیزات جانبی موتور موتور گیربكس موتور DC STEP موتور سروو موتور لامپ و چراغ قوه کیبورد و کیپد کابل و مبدل صوتی تصویری کابل، شارژر و مبدل USB انواع نمایشگر LCD/TFT/OLED نمایشگر LCD/GLCD نمایشگر HDMI/VGA نمایشگر OLED درایور LCD سیم و کابل مخابراتی و آیفونی و تلفنی فیلامنت سیم نسوز سیلیکونی سیم وایر رپ سیم لاکی کابل برق سیم باندی، اسپیکری کابل فلت سایر سیم و کابل ها شبکه سیم افشان محصولات کلکسیونی تولید داخل جاباتری چاپ و سفارش pcb برد مدار چاپی مجله جم ترونیک پروژه‌ها و ایده‌ها سوال‌های متداول سبد خرید بستن فروشگاه 0 لیست علاقه مندی ها 0 مورد سبد خرید حساب من</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1185,10 +1174,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="3" t="n">
         <v>1060000</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="3" t="n">
         <v>1060000</v>
       </c>
     </row>
@@ -1199,14 +1188,14 @@
       <c r="B22" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>https://landaelectronic.com/product/dc-gear-motor-zga12-fn20-6v_70rpm/</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) - لاندا الکترونیک Skip to navigation Skip to main content صفحه نخست فروشگاه وبلاگ درباره ما تماس با ما حریم خصوصی کاربر قوانین و مقررات با ثبت نام در لاندا الکترونیک , در هر بار خرید 2 درصد تخفیف بگیرید 021-88699 جستجو ورود | ثبت نام 0 0 0 مورد ۰ تومان منو 0 مورد ورود | ثبت نام موتورها موتورهای استپ استپ موتور گیربکس دار نما 17 نما 23 نما 34 موتورهای سروو درایورها پمپ ها منبع تغذیه ماژول ها رباتیک ابزارها پیشنهاد ویژه خانه موتورهای DC گیربکس دار موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) موتور دی سی گیربکس دار ZGA12-FN30 (6V 430RPM) ۶۵۰,۰۰۰ تومان بازگشت به محصولات موتور دی سی گیربکس دار 1.61.068 (12V 6RPM) ۱,۰۰۰,۰۰۰ تومان -27% برای بزرگنمایی کلیک کنید Landa موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) امتیاز 4.50 از 5 امتیاز 2 مشتری (دیدگاه کاربر 2 ) ۵۵۰,۰۰۰ تومان قیمت اصلی: ۵۵۰,۰۰۰ تومان بود. ۴۰۰,۰۰۰ تومان قیمت فعلی: ۴۰۰,۰۰۰ تومان. برند لاندا قطرشفت 3میلیمتر ولتاژ 6VDC جریان 0.5A سرعت 70 دور در دقیقه گشتاور 0.6 کیلوگرم بر سانتی متر 97 در انبار موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) عدد افزودن به سبد خرید مقايسه افزودن به علاقه مندی اشتراک گذاری: توضیحات توضیحات تکمیلی نظرات (2) توضیحات موتور دی سی گیربکس دار ZGA12-FN20 با ولتاژ 6 ولت و سرعت 70RPM موتور دی سی گیربکس دار ZGA12-FN20 با ولتاژ 6 ولت و سرعت 70RPM یا ZGA12-FN20 از ترکیب یک موتور الکتریکی به همراه یک گیربکس ساخته شده است. در این نوع موتورها انرژی الکتریکی توسط یک آهنربا به انرژی مکانیکی تبدیل میشود. در این نوع موتورها گیربکس دار، گیربکس وظیفه دارد تا دور و گشتاور را برای رسیدن به قدرت مطلوب تنظیم کند. علاوه بر اینها افزایش و کاهش قدرت چرخش و سرعت نیز بر عهده گیربکس است. هرچه نرخ کاهش سرعت در گیربکس بیشتر شود، قدرت آن بالاتر خواهد رفت. موتور گیربکس‌های ZGA12-FN20 دارای سرعت 70 دور بر دقیقه است و ولتاژ مصرفی این موتور 6ولت میباشد. در صورتی که ولتاژ کمتری به آن‌ها داده شود دور خروجی و توان و نهایتا گشتاور تولیدی موتور کاهش میابد. از طرفی با افزایش ولتاژ دور خروجی و توان و نهایتا گشتاور تولیدی موتور افزایش میابد ولی عمر مفید موتور کاهش میابد و سریع‌تر از بین می‌رود. کاربرد موتور دی سی گیربکس دار ZGA12-FN20 با ولتاژ 6 ولت و سرعت 70RPM موتور دی سی گیربکس دار ZGA12-FN20 ، موتوری قوی است که برای مصارف صنعتی، دستگاه های CNC، رباتیک و… مناسب است. وجود گیربکس باعث می‌شود به سرعت‌های متفاوت و گشتاور بیشتری نسبت به موتور بدون گیربکس رسید. چرخ‌دنده‌های گیربکس‌ این موتور فلزی هستند و در صورت نیاز می‌توان برای روان‌تر و بی‌صدا کار کردن آن آن‌ها را روغن کاری کرد. لاندا الکترونیک ، با سابقه ای درخشان در زمینه واردات قطعات الکترونیکی، مرجعی امن و شناخته شده برای خرید آسان و راحت شماست. شما می توانید برای خرید محصول مورد نظر خود، از تجربه 24 ساله متخصصان لاندا الکترونیک، بهره ببرید و پس از مشاوره انتخابی صحیح داشته باشید. لاندا الکترونیک، بزرگ ترین وارد کننده قطعات الکترونیکی در کشور؛ محصولات خود را با قیمت مناسب ارائه می دهد. همکاران ما بلافاصله پس از ثبت درخواست، سفارش شما را پیگیری کرده و در کوتاه ترین زمان ممکن برای شما ارسال خواهند کرد. (عزیزان ساکن تهران در همان روز و سایر شهرها ظرف مدت زمان حداکثر 72 ساعت کاری) توضیحات تکمیلی وزن 0.1 کیلوگرم ابعاد 1.2 × 1 × 3.3 سانتیمتر نام تجاری Landa قطرشفت(mm) 3 ولتاژ 6 جریان(A) 0.5 گشتاور(kg/cm) 0.6 سرعت بدون بار (RPM) 70 جهت چرخش CW/CCW نظرات (2) 2 دیدگاه برای موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) مشتری – آذر 8, 1402 نمره 5 از 5 اندازه بند انگشته ولی فوق العاده قوی هست مناسب پیچ بند هم هست منتحی یکم دورش پایینه جلال بتویی – بهمن 3, 1404 نمره 4 از 5 قیمت رو اشتباه زدید فک کنم دیدگاه خود را بنویسید لغو پاسخ برای ثبت نقد و بررسی وارد حساب کاربری خود شوید. محصولات مشابه مقايسه موتور دی سی 1.13.043.033 (20V 3100RPM) ۵۸۰,۰۰۰ تومان نمره 0 از 5 موتور دی سی 1.13.043.033 (20V 3100RPM) موتور دی سی 1.13.043.033 ساخت شرکت BUHLER آلمان است. این موتور با ولتاژ 20 افزودن به علاقه مندی افزودن به سبد خرید نمایش سریع فروخته شده مقايسه موتور دی سی ZGB37REE (12V 20RPM) تماس بگیرید نمره 0 از 5 موتور دی سی ZGB37REE موتور دی سی ZGB37REE ساخت کشور چین به سفارش شرکت لاندا الکترونیک ایران است. این موتور افزودن به علاقه مندی اطلاعات بیشتر نمایش سریع مقايسه موتور دی سی 1.13.046.422 (24V 3800RPM) ۱,۶۰۰,۰۰۰ تومان نمره 0 از 5 برند buhler قطر شفت 4 میلیمتر ولتاژ 24VDC جریان 3.4A سرعت 3800 دور در دقیقه افزودن به علاقه مندی افزودن به سبد خرید نمایش سریع فروخته شده مقايسه موتور دی سی گیربکس دار 1.61.065.327 (12V 9.5RPM) ۳۸۰,۰۰۰ تومان نمره 0 از 5 موتور دی سی گیربکس دار 1.61.065.327 با ولتاژ 12ولت و سرعت 9.5RPM موتور دی سی گیربکس دار 1.61.065.327 با ولتاژ افزودن به علاقه مندی اطلاعات بیشتر نمایش سریع فروخته شده مقايسه موتور دی سی Elv (12V 3000RPM) ۲۷۰,۰۰۰ تومان نمره 0 از 5 موتور دی سی Elv با ولتاژ 12 ولت و سرعت 3000RPM موتور دی سی Elv با ولتاژ 12 ولت و افزودن به علاقه مندی اطلاعات بیشتر نمایش سریع فروخته شده مقايسه موتور دی سی گیربکس دار 1.61.050.443 (12V 61.4RPM) ۲۲,۰۰۰,۰۰۰ تومان نمره 0 از 5 نمایش و دانلود کاتالوگ   موتور دی سی گیربکس دار 1.61.050.443 با ولتاژ 12 ولت و سرعت 61.4RPM موتور دی افزودن به علاقه مندی اطلاعات بیشتر نمایش سریع مقايسه موتور دی سی گیربکس دار 1.61.050.440 (12V 460RPM) ۲۲,۰۰۰,۰۰۰ تومان نمره 0 از 5 نمایش و دانلود کاتالوگ موتور دی سی گیربکس دار 1.61.050.440 با ولتاژ 12 ولت و سرعت 460RPM موتور دی سی افزودن به علاقه مندی افزودن به سبد خرید نمایش سریع مقايسه موتور دی سی گیربکس دار انکدر دار 1.61.113 BMW (12V 102RPM) ۳۹,۰۰۰,۰۰۰ تومان نمره 0 از 5 برند BUHLER ولتاژ(V) 12V DC سرعت بدون بار (RPM) 102 گشتاور (kg/cm) 155 جریان (A) 25 افزودن به علاقه مندی افزودن به سبد خرید نمایش سریع ارسال ارسال سریع پشتیبانی پشتیبانی آنلاین و تلفنی پرداخت آنلاین پرداخت آنلاین و امن آدرس دفتر مرکزی خیابان جمهوری، بین پل حافظ و سی تیر، ساختمان عباسیان طبقه زیرین پلاک ۴۸ شماره تماس : ۰۲۱۶۶۷۰۰۴۵۶ آدرس ایمیل : info@landaelectronic.com لاندا الکترونیک | بزرگترین مرکز تخصصی فروش و مشاوره قطعات الکترونیکی در ایران شنبه تا چهارشنبه ۹:۳۰ تا ۱۸:۰۰ و پنجشنبه ها ۹:۳۰ تا ۱۴:۰۰ انواع روش های پرداخت اعتماد شما، افتخار ماست ©2024 لاندا الکترونیک. کلیه حقوق محفوظ است ( قدرت گرفته با www.NikiSite.com ) جستجو منو دسته بندی ها موتورها موتورهای DC بدون گیربکس انکودر دار موتورهای خطی موتورهای ویبره موتورهای DC گیربکس دار موتورهای DC گیربکس دار – شفت مستقیم موتورهای DC گیربکس دار – گیربکس خورشیدی موتورهای DC گیربکس دار – گیربکس حلزونی موتورهای DC گیربکس دار – انکودر دار موتورهای AC موتور دستگاه های جوجه کشی موتورهای استپر استپ موتور گیربکس دار نما 17 نما 23 نما 34 موتورهای سروو موتورهای سرو AC صنعتی موتورهای سرو DC روباتیک منبع تغذیه درایورها درایور موتورهای DC درایور موتورهای استپ پمپ منبع تغذیه ماژول ها رباتیک قطعات الکترونیکی قطعات مکانیکی ابزارها پیشنهاد ویژه صفحه نخست فروشگاه وبلاگ درباره ما تماس با ما حریم خصوصی کاربر قوانین و مقررات سبد خرید بستن موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) نمره 4.50 از 5 ۵۵۰,۰۰۰ تومان قیمت اصلی: ۵۵۰,۰۰۰ تومان بود. ۴۰۰,۰۰۰ تومان قیمت فعلی: ۴۰۰,۰۰۰ تومان. 97 در انبار موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) عدد افزودن به سبد خرید مقايسه افزودن به علاقه مندی فروشگاه حساب من سبد خرید</t>
+          <t>موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) - لاندا الکترونیک Skip to navigation Skip to main content صفحه نخست فروشگاه وبلاگ درباره ما تماس با ما حریم خصوصی کاربر قوانین و مقررات با ثبت نام در لاندا الکترونیک , در هر بار خرید 2 درصد تخفیف بگیرید 021-88699 جستجو ورود | ثبت نام 0 0 0 مورد ۰ تومان منو 0 مورد ورود | ثبت نام موتورها موتورهای استپ استپ موتور گیربکس دار نما 17 نما 23 نما 34 موتورهای سروو درایورها پمپ ها منبع تغذیه ماژول ها رباتیک ابزارها پیشنهاد ویژه خانه موتورهای DC گیربکس دار موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) موتور دی سی گیربکس دار ZGA12-FN30 (6V 430RPM) ۶۵۰,۰۰۰ تومان بازگشت به محصولات موتور دی سی گیربکس دار 1.61.068 (12V 6RPM) ۱,۰۰۰,۰۰۰ تومان -27% برای بزرگنمایی کلیک کنید Landa موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) امتیاز 4.50 از 5 امتیاز 2 مشتری (دیدگاه کاربر 2 ) ۵۵۰,۰۰۰ تومان قیمت اصلی: ۵۵۰,۰۰۰ تومان بود. ۴۰۰,۰۰۰ تومان قیمت فعلی: ۴۰۰,۰۰۰ تومان. برند لاندا قطرشفت 3میلیمتر ولتاژ 6VDC جریان 0.5A سرعت 70 دور در دقیقه گشتاور 0.6 کیلوگرم بر سانتی متر 97 در انبار موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) عدد افزودن به سبد خرید مقايسه افزودن به علاقه مندی اشتراک گذاری: توضیحات توضیحات تکمیلی نظرات (2) توضیحات موتور دی سی گیربکس دار ZGA12-FN20 با ولتاژ 6 ولت و سرعت 70RPM موتور دی سی گیربکس دار ZGA12-FN20 با ولتاژ 6 ولت و سرعت 70RPM یا ZGA12-FN20 از ترکیب یک موتور الکتریکی به همراه یک گیربکس ساخته شده است. در این نوع موتورها انرژی الکتریکی توسط یک آهنربا به انرژی مکانیکی تبدیل میشود. در این نوع موتورها گیربکس دار، گیربکس وظیفه دارد تا دور و گشتاور را برای رسیدن به قدرت مطلوب تنظیم کند. علاوه بر اینها افزایش و کاهش قدرت چرخش و سرعت نیز بر عهده گیربکس است. هرچه نرخ کاهش سرعت در گیربکس بیشتر شود، قدرت آن بالاتر خواهد رفت. موتور گیربکس‌های ZGA12-FN20 دارای سرعت 70 دور بر دقیقه است و ولتاژ مصرفی این موتور 6ولت میباشد. در صورتی که ولتاژ کمتری به آن‌ها داده شود دور خروجی و توان و نهایتا گشتاور تولیدی موتور کاهش میابد. از طرفی با افزایش ولتاژ دور خروجی و توان و نهایتا گشتاور تولیدی موتور افزایش میابد ولی عمر مفید موتور کاهش میابد و سریع‌تر از بین می‌رود. کاربرد موتور دی سی گیربکس دار ZGA12-FN20 با ولتاژ 6 ولت و سرعت 70RPM موتور دی سی گیربکس دار ZGA12-FN20 ، موتوری قوی است که برای مصارف صنعتی، دستگاه های CNC، رباتیک و… مناسب است. وجود گیربکس باعث می‌شود به سرعت‌های متفاوت و گشتاور بیشتری نسبت به موتور بدون گیربکس رسید. چرخ‌دنده‌های گیربکس‌ این موتور فلزی هستند و در صورت نیاز می‌توان برای روان‌تر و بی‌صدا کار کردن آن آن‌ها را روغن کاری کرد. لاندا الکترونیک ، با سابقه ای درخشان در زمینه واردات قطعات الکترونیکی، مرجعی امن و شناخته شده برای خرید آسان و راحت شماست. شما می توانید برای خرید محصول مورد نظر خود، از تجربه 24 ساله متخصصان لاندا الکترونیک، بهره ببرید و پس از مشاوره انتخابی صحیح داشته باشید. لاندا الکترونیک، بزرگ ترین وارد کننده قطعات الکترونیکی در کشور؛ محصولات خود را با قیمت مناسب ارائه می دهد. همکاران ما بلافاصله پس از ثبت درخواست، سفارش شما را پیگیری کرده و در کوتاه ترین زمان ممکن برای شما ارسال خواهند کرد. (عزیزان ساکن تهران در همان روز و سایر شهرها ظرف مدت زمان حداکثر 72 ساعت کاری) توضیحات تکمیلی وزن 0.1 کیلوگرم ابعاد 1.2 × 1 × 3.3 سانتیمتر نام تجاری Landa قطرشفت(mm) 3 ولتاژ 6 جریان(A) 0.5 گشتاور(kg/cm) 0.6 سرعت بدون بار (RPM) 70 جهت چرخش CW/CCW نظرات (2) 2 دیدگاه برای موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) مشتری – آذر 8, 1402 نمره 5 از 5 اندازه بند انگشته ولی فوق العاده قوی هست مناسب پیچ بند هم هست منتحی یکم دورش پایینه جلال بتویی – بهمن 3, 1404 نمره 4 از 5 قیمت رو اشتباه زدید فک کنم دیدگاه خود را بنویسید لغو پاسخ برای ثبت نقد و بررسی وارد حساب کاربری خود شوید. محصولات مشابه مقايسه موتور دی سی 29014002 6/30v (24V 6000RPM) ۱,۲۰۰,۰۰۰ تومان نمره 0 از 5 موتور دی سی 29014002 6/30v موتور دی سی 29014002 6/30v ، محصول شرکتBUHLER آلمان است. در حال حاضر درصنایع گوناگون افزودن به علاقه مندی افزودن به سبد خرید نمایش سریع فروخته شده مقايسه موتور دی سی گیربکس دار Tsukasa (24V 350RPM) ۱۵۰,۰۰۰ تومان نمره 5.00 از 5 موتور دی سی گیربکس دار Tsukasa با ولتاژ 24 ولت و سرعت 350RPM موتور دی سی گیربکس دار Tsukasa با افزودن به علاقه مندی اطلاعات بیشتر نمایش سریع فروخته شده مقايسه موتور دی سی گیربکس دار ASMO(24V 24.5RPM) ۱۲۰,۰۰۰ تومان نمره 0 از 5 موتور دی سی گیربکس دار ASMO با ولتاژ 24 ولت و سرعت 24.5RPM موتور دی سی گیربکس دار ASMO با افزودن به علاقه مندی اطلاعات بیشتر نمایش سریع فروخته شده مقايسه موتور دی سی Elv (12V 3000RPM) ۲۷۰,۰۰۰ تومان نمره 0 از 5 موتور دی سی Elv با ولتاژ 12 ولت و سرعت 3000RPM موتور دی سی Elv با ولتاژ 12 ولت و افزودن به علاقه مندی اطلاعات بیشتر نمایش سریع فروخته شده مقايسه موتور دی سی 1.13.044.023.01 (24V 7100RPM) ۱,۱۰۰,۰۰۰ تومان نمره 0 از 5 نمایش و دانلود کاتالوگ موتور دی سی 1.13.044.023.01 با ولتاژ 24 ولت و سرعت 7100RPM موتور دی سی 1.13.044.023.01 با افزودن به علاقه مندی اطلاعات بیشتر نمایش سریع فروخته شده مقايسه موتور دی سی گیربکس دار 1.61.050.467 (24V 14RPM) ۲۲,۰۰۰,۰۰۰ تومان نمره 0 از 5 نمایش و دانلود کاتالوگ موتور دی سی گیربکس دار 1.61.050.467 با ولتاژ 24 ولت و سرعت 14RPM موتور دی سی افزودن به علاقه مندی اطلاعات بیشتر نمایش سریع مقايسه موتور دی سی گیربکس دار 1.61.050.466 (24V 23.5RPM) ۲۲,۰۰۰,۰۰۰ تومان نمره 0 از 5 نمایش و دانلود کاتالوگ   موتور دی سی گیربکس دار 1.61.050.466 با ولتاژ 24 ولت و سرعت 23.5RPM موتور دی افزودن به علاقه مندی افزودن به سبد خرید نمایش سریع مقايسه موتور دی سی 1.13.035.024 (24V 5800RPM) ۱,۸۰۰,۰۰۰ تومان نمره 0 از 5 موتور دی سی 1.13.035.024 با ولتاژ 24 ولت و سرعت 5800RPM موتور دی سی 1.13.035.024 با ولتاژ 24 ولت و افزودن به علاقه مندی افزودن به سبد خرید نمایش سریع ارسال ارسال سریع پشتیبانی پشتیبانی آنلاین و تلفنی پرداخت آنلاین پرداخت آنلاین و امن آدرس دفتر مرکزی خیابان جمهوری، بین پل حافظ و سی تیر، ساختمان عباسیان طبقه زیرین پلاک ۴۸ شماره تماس : ۰۲۱۶۶۷۰۰۴۵۶ آدرس ایمیل : info@landaelectronic.com لاندا الکترونیک | بزرگترین مرکز تخصصی فروش و مشاوره قطعات الکترونیکی در ایران شنبه تا چهارشنبه ۹:۳۰ تا ۱۸:۰۰ و پنجشنبه ها ۹:۳۰ تا ۱۴:۰۰ انواع روش های پرداخت اعتماد شما، افتخار ماست ©2024 لاندا الکترونیک. کلیه حقوق محفوظ است ( قدرت گرفته با www.NikiSite.com ) جستجو منو دسته بندی ها موتورها موتورهای DC بدون گیربکس انکودر دار موتورهای خطی موتورهای ویبره موتورهای DC گیربکس دار موتورهای DC گیربکس دار – شفت مستقیم موتورهای DC گیربکس دار – گیربکس خورشیدی موتورهای DC گیربکس دار – گیربکس حلزونی موتورهای DC گیربکس دار – انکودر دار موتورهای AC موتور دستگاه های جوجه کشی موتورهای استپر استپ موتور گیربکس دار نما 17 نما 23 نما 34 موتورهای سروو موتورهای سرو AC صنعتی موتورهای سرو DC روباتیک منبع تغذیه درایورها درایور موتورهای DC درایور موتورهای استپ پمپ منبع تغذیه ماژول ها رباتیک قطعات الکترونیکی قطعات مکانیکی ابزارها پیشنهاد ویژه صفحه نخست فروشگاه وبلاگ درباره ما تماس با ما حریم خصوصی کاربر قوانین و مقررات سبد خرید بستن موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) نمره 4.50 از 5 ۵۵۰,۰۰۰ تومان قیمت اصلی: ۵۵۰,۰۰۰ تومان بود. ۴۰۰,۰۰۰ تومان قیمت فعلی: ۴۰۰,۰۰۰ تومان. 97 در انبار موتور دی سی گیربکس دار ZGA12-FN20 (6V 70RPM) عدد افزودن به سبد خرید مقايسه افزودن به علاقه مندی فروشگاه حساب من سبد خرید</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1214,10 +1203,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="3" t="n">
         <v>4000000</v>
       </c>
     </row>
@@ -1228,14 +1217,14 @@
       <c r="B23" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>https://ariaebox.com/product/%d8%a7%d8%b3%d9%81%d9%86%d8%ac-%d9%86%d8%b3%d9%88%d8%b2-%d8%a2%d8%a8%db%8c-%d9%be%d8%a7%da%a9-%da%a9%d9%86%d9%86%d8%af%d9%87-%d9%86%d9%88%da%a9-%d9%87%d9%88%db%8c%d9%87-6060-%d9%85%db%8c%d9%84%db%8c/</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>اسفنج نسوز ضخیم آبی پاک کننده نوک هویه 60*60 میلی متر - آریا باکس پرش به ناوبری رفتن به محتوای اصلی سفارش و واردات انواع PCB، قطعات الکترونیکی (ماژول، آی سی، ال سی دی، سنسور، کانکتور و ...) از چین پذیرفته می شود. سفارش و واردات انواع PCB، قطعات الکترونیکی (ماژول، آی سی، ال سی دی، سنسور، کانکتور و ...) از چین پذیرفته می شود. جستجو 0 موارد 0 تومان ورود | ثبت‌نام منو 0 موارد ورود | ثبت‌نام مرور دسته بندی ها باکس جعبه های ریلی استاندارد عمودی ماژولار براکت ریل برد جعبه های دستی قابل حمل GPS بدون نمایشگر با نمایشگر جعبه های تجهیزات شبکه پاوربانک جعبه های رومیزی شیب دار ساده جعبه های ضد آب آلومینیومی رومیزی و دیواری تابلویی جعبه تقسیم جعبه های آلومینیومی پایه دار رومیزی جعبه های دیواری سایر محصولات دستگیره سر ولوم کیپد درایور باکس رسپبری جا باتری کیف تجهیزات کیف های ابزار کیف های ضدآب و ضدضربه جعبه های پنلی جعبه های کنترل تردد دیجیتال کارتخوان جعبه های هوشند سازی کلید هاب و روتر پریز و سوکت جعبه های نمایشگر ابزار ابزار و مونتاژ لحیم کاری هیتر ، هویه و وان قلع نوک هویه و المنت سیم لحیم و خمیر قلع روغن و فلاکس لحیم کاری قلع کش و انواع تمیز کننده خمیر و چسب سیلیکون ابزار تعمیرات موبایل سپراتور التراسونیک لوپ ، میکروسکوپ و ذره بین ست پیچ گوشتی قاب باز کن و تاچ کش شابلون آی سی پد نسوز مولتی متر منبع تغذیه پراپ و کابل تست پیچ گوشتی سیم چین، کف چین و لخت کن انبردست و دم باریک پنس و کاتر آچار سوکت زن و پرسی مته و ابزار سوراخ کاری سشوار و چسب حرارتی دماسنج و رطوبت سنج انواع اسپری و محلول جعبه ابزار و کشوی قطعات قطعات الکترونیکی ماژول ماژول جرقه زن ماژول تغذیه و شارژ ماژول بخار سرد سنسور سنسور دما و رطوبت آی سی باکس ابزار قطعات الکترونیکی همه محصولات ثبت سفارش از چین سفارش pcb قوانین و مقررات سوالات متداول درباره ما تماس با ما پیگیری سفارشات خانه / ابزار / ابزار تعمیرات موبایل / پد نسوز / اسفنج نسوز ضخیم آبی پاک کننده نوک هویه 60*60 میلی متر اسفنج نسوز ضخیم آبی پاک کننده نوک هویه 60*60 میلی متر جدید جدید برای بزرگنمایی کلیک کنید 35,000 تومان 1415 در انبار اسفنج نسوز ضخیم آبی پاک کننده نوک هویه 60*60 میلی متر عدد افزودن به سبد خرید براق و تمیز کردن نوک انواع هویه جلوگیری از خوردگی و سابیدگی نوک هویه وزن 2 گرم ابعاد 2 × 60 × 60 میلی‌متر رنگ آبی تضمین بهترین قیمت بازار مشاوره و پشتیبانی آنلاین تضمین اصالت و سلامت کالا ارسال سریع سفارشات 35,000 تومان 1415 در انبار اسفنج نسوز ضخیم آبی پاک کننده نوک هویه 60*60 میلی متر عدد افزودن به سبد خرید دسته بندی: پد نسوز برچسب: آریاباکس , ابر نسوز تمیزکننده هویه , اسفنج پاک کننده هویه , اسفنج نسوز , اسفنج نسوز پاک کننده نوک هویه , اسفنج هویه , پد پاک کننده هویه , پد نسوز , پد نسوز نوک هویه توضیحات توضیحات تکمیلی نظرات (0) توضیحات اسفنج نسوز وسیله ای بسیار کاربردی و ارزان قیمت برای تمیز کردن نوک هویه و زدودن قلع اضافی یا اکسید موجود در قسمت های فولادی نوک هویه می باشد. برای استفاده از اسفنج نسوز باید همیشه اسفنج را مرطوب نگه داشت و زمانی که نوک هویه داغ است نوک هویه را به اسفنج کشیده تا تمیز شود. با خرید اسفنج نسوز نوک هویه خود را همیشه تمیز نگه دارید. توجه کنید که زدن نوک هویه در روغن لحیم برای تمیز کردن نوک هویه اصلا توصیه نمی شود. چرا که این کار باعث خورده شدن و از بین رفتن نوک هویه در مدت کوتاهی خواهد شد. بعد از مدتی کار کردن و کثیف شدن اسفنج، با شستن آن، به حالت اول باز می گردد. توضیحات تکمیلی وزن 2 گرم ابعاد 2 × 60 × 60 میلی‌متر رنگ آبی نظرات (0) دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “اسفنج نسوز ضخیم آبی پاک کننده نوک هویه 60*60 میلی متر” لغو پاسخ نشانی ایمیل شما منتشر نخواهد شد. بخش‌های موردنیاز علامت‌گذاری شده‌اند * امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. محصولات مشابه فروخته شده جدید مقایسه مشاهده سریع افزودن به علاقه مندی ها اطلاعات بیشتر اسفنج نسوز پاک کننده نوک هویه 35*50 مدل 936 پد نسوز نمره 5.00 از 5 5,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید پد نسوز سیلیکونی و آهنربایی S-160 پد نسوز 950,000 تومان فروخته شده جدید مقایسه مشاهده سریع افزودن به علاقه مندی ها اطلاعات بیشتر پد نسوز سیلیکونی و آهنربایی اصلی سانشاین Sunshine S-160 پد نسوز 360,000 تومان ارسال سریع برای تهران و شهرستان ها امکان تست و تعویض 48 ساعت امکان تست و عودت باکس سفارش مستقیم قطعات سفارش مستقیم انواع قطعات الکترونیک خرید از واتساپ وتلگرام @ariaebox / 09333603323 دسترسی سریع سبد خرید پیگیری سفارشات حساب کاربری من لینک های مفید تماس با ما درباره آریا باکس قوانین و مقررات در آریا باکس دسته بندی پرفروش کیف تجهیزات جعبه های ریلی جعبه های هوشمندسازی با ما همراه باشید با آریا باکس در ارتباط باشید 02166704819 02166754554 02166738683 02166765997 02166740303 02166765916 ایمیل : ariaebox.shop@gmail.com ساعت کاری: شنبه تا چهارشنبه از ساعت 9 الی 18  پنجشنبه ها 9 الی 14 تمام حقوق این وب سایت متعلق به آریا باکس می باشد. جستجو منو همه دسته بندی ها باکس جعبه های ریلی استاندارد عمودی ماژولار براکت ریل برد پاوربانک جعبه های آلومینیومی پایه دار رومیزی جعبه های پنلی جعبه های تجهیزات شبکه جعبه های دستی قابل حمل GPS بدون نمایشگر با نمایشگر جعبه های دیواری جعبه های رومیزی شیب دار ساده جعبه های ضدآب تابلویی جعبه تقسیم آلومینیومی رومیزی و دیواری جعبه های کنترل تردد دیجیتال کارتخوان جعبه های نمایشگر جعبه های هوشمندسازی باکس پریز و سوکت باکس کلید باکس هاب و روتر سایر محصولات درایور باکس رسپبری جا باتری جعبه های آداپتور سر ولوم کیپد کیف تجهیزات ابزار قطعات الکترونیکی ماژول ماژول جرقه زن ماژول تغذیه و شارژ باکس ابزار قطعات الکترونیکی همه محصولات ثبت سفارش از چین سفارش pcb قوانین و مقررات سوالات متداول درباره ما تماس با ما لیست علاقه مندی ها مقایسه ورود / ثبت نام سبد خرید بستن</t>
+          <t>اسفنج نسوز ضخیم آبی پاک کننده نوک هویه 60*60 میلی متر - آریا باکس پرش به ناوبری رفتن به محتوای اصلی سفارش و واردات انواع PCB، قطعات الکترونیکی (ماژول، آی سی، ال سی دی، سنسور، کانکتور و ...) از چین پذیرفته می شود. سفارش و واردات انواع PCB، قطعات الکترونیکی (ماژول، آی سی، ال سی دی، سنسور، کانکتور و ...) از چین پذیرفته می شود. جستجو 0 موارد 0 تومان ورود | ثبت‌نام منو 0 موارد ورود | ثبت‌نام مرور دسته بندی ها باکس جعبه های ریلی استاندارد عمودی ماژولار براکت ریل برد جعبه های دستی قابل حمل GPS بدون نمایشگر با نمایشگر جعبه های تجهیزات شبکه پاوربانک جعبه های رومیزی شیب دار ساده جعبه های ضد آب آلومینیومی رومیزی و دیواری تابلویی جعبه تقسیم جعبه های آلومینیومی پایه دار رومیزی جعبه های دیواری سایر محصولات دستگیره سر ولوم کیپد درایور باکس رسپبری جا باتری کیف تجهیزات کیف های ابزار کیف های ضدآب و ضدضربه جعبه های پنلی جعبه های کنترل تردد دیجیتال کارتخوان جعبه های هوشند سازی کلید هاب و روتر پریز و سوکت جعبه های نمایشگر ابزار ابزار و مونتاژ لحیم کاری هیتر ، هویه و وان قلع نوک هویه و المنت سیم لحیم و خمیر قلع روغن و فلاکس لحیم کاری قلع کش و انواع تمیز کننده خمیر و چسب سیلیکون ابزار تعمیرات موبایل سپراتور التراسونیک لوپ ، میکروسکوپ و ذره بین ست پیچ گوشتی قاب باز کن و تاچ کش شابلون آی سی پد نسوز مولتی متر منبع تغذیه پراپ و کابل تست پیچ گوشتی سیم چین، کف چین و لخت کن انبردست و دم باریک پنس و کاتر آچار سوکت زن و پرسی مته و ابزار سوراخ کاری سشوار و چسب حرارتی دماسنج و رطوبت سنج انواع اسپری و محلول جعبه ابزار و کشوی قطعات قطعات الکترونیکی ماژول ماژول جرقه زن ماژول تغذیه و شارژ ماژول بخار سرد سنسور سنسور دما و رطوبت آی سی باکس ابزار قطعات الکترونیکی همه محصولات ثبت سفارش از چین سفارش pcb قوانین و مقررات سوالات متداول درباره ما تماس با ما پیگیری سفارشات خانه / ابزار / ابزار تعمیرات موبایل / پد نسوز / اسفنج نسوز ضخیم آبی پاک کننده نوک هویه 60*60 میلی متر اسفنج نسوز ضخیم آبی پاک کننده نوک هویه 60*60 میلی متر جدید جدید برای بزرگنمایی کلیک کنید 35,000 تومان 1412 در انبار اسفنج نسوز ضخیم آبی پاک کننده نوک هویه 60*60 میلی متر عدد افزودن به سبد خرید براق و تمیز کردن نوک انواع هویه جلوگیری از خوردگی و سابیدگی نوک هویه وزن 2 گرم ابعاد 2 × 60 × 60 میلی‌متر رنگ آبی تضمین بهترین قیمت بازار مشاوره و پشتیبانی آنلاین تضمین اصالت و سلامت کالا ارسال سریع سفارشات 35,000 تومان 1412 در انبار اسفنج نسوز ضخیم آبی پاک کننده نوک هویه 60*60 میلی متر عدد افزودن به سبد خرید دسته بندی: پد نسوز برچسب: آریاباکس , ابر نسوز تمیزکننده هویه , اسفنج پاک کننده هویه , اسفنج نسوز , اسفنج نسوز پاک کننده نوک هویه , اسفنج هویه , پد پاک کننده هویه , پد نسوز , پد نسوز نوک هویه توضیحات توضیحات تکمیلی نظرات (0) توضیحات اسفنج نسوز وسیله ای بسیار کاربردی و ارزان قیمت برای تمیز کردن نوک هویه و زدودن قلع اضافی یا اکسید موجود در قسمت های فولادی نوک هویه می باشد. برای استفاده از اسفنج نسوز باید همیشه اسفنج را مرطوب نگه داشت و زمانی که نوک هویه داغ است نوک هویه را به اسفنج کشیده تا تمیز شود. با خرید اسفنج نسوز نوک هویه خود را همیشه تمیز نگه دارید. توجه کنید که زدن نوک هویه در روغن لحیم برای تمیز کردن نوک هویه اصلا توصیه نمی شود. چرا که این کار باعث خورده شدن و از بین رفتن نوک هویه در مدت کوتاهی خواهد شد. بعد از مدتی کار کردن و کثیف شدن اسفنج، با شستن آن، به حالت اول باز می گردد. توضیحات تکمیلی وزن 2 گرم ابعاد 2 × 60 × 60 میلی‌متر رنگ آبی نظرات (0) دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “اسفنج نسوز ضخیم آبی پاک کننده نوک هویه 60*60 میلی متر” لغو پاسخ نشانی ایمیل شما منتشر نخواهد شد. بخش‌های موردنیاز علامت‌گذاری شده‌اند * امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. محصولات مشابه فروخته شده جدید مقایسه مشاهده سریع افزودن به علاقه مندی ها اطلاعات بیشتر اسفنج نسوز پاک کننده نوک هویه 35*50 مدل 936 پد نسوز نمره 5.00 از 5 5,000 تومان مقایسه مشاهده سریع افزودن به علاقه مندی ها افزودن به سبد خرید پد نسوز سیلیکونی و آهنربایی S-160 پد نسوز 950,000 تومان فروخته شده جدید مقایسه مشاهده سریع افزودن به علاقه مندی ها اطلاعات بیشتر پد نسوز سیلیکونی و آهنربایی اصلی سانشاین Sunshine S-160 پد نسوز 360,000 تومان ارسال سریع برای تهران و شهرستان ها امکان تست و تعویض 48 ساعت امکان تست و عودت باکس سفارش مستقیم قطعات سفارش مستقیم انواع قطعات الکترونیک خرید از واتساپ وتلگرام @ariaebox / 09333603323 دسترسی سریع سبد خرید پیگیری سفارشات حساب کاربری من لینک های مفید تماس با ما درباره آریا باکس قوانین و مقررات در آریا باکس دسته بندی پرفروش کیف تجهیزات جعبه های ریلی جعبه های هوشمندسازی با ما همراه باشید با آریا باکس در ارتباط باشید 02166704819 02166754554 02166738683 02166765997 02166740303 02166765916 ایمیل : ariaebox.shop@gmail.com ساعت کاری: شنبه تا چهارشنبه از ساعت 9 الی 18  پنجشنبه ها 9 الی 14 تمام حقوق این وب سایت متعلق به آریا باکس می باشد. جستجو منو همه دسته بندی ها باکس جعبه های ریلی استاندارد عمودی ماژولار براکت ریل برد پاوربانک جعبه های آلومینیومی پایه دار رومیزی جعبه های پنلی جعبه های تجهیزات شبکه جعبه های دستی قابل حمل GPS بدون نمایشگر با نمایشگر جعبه های دیواری جعبه های رومیزی شیب دار ساده جعبه های ضدآب تابلویی جعبه تقسیم آلومینیومی رومیزی و دیواری جعبه های کنترل تردد دیجیتال کارتخوان جعبه های نمایشگر جعبه های هوشمندسازی باکس پریز و سوکت باکس کلید باکس هاب و روتر سایر محصولات درایور باکس رسپبری جا باتری جعبه های آداپتور سر ولوم کیپد کیف تجهیزات ابزار قطعات الکترونیکی ماژول ماژول جرقه زن ماژول تغذیه و شارژ باکس ابزار قطعات الکترونیکی همه محصولات ثبت سفارش از چین سفارش pcb قوانین و مقررات سوالات متداول درباره ما تماس با ما لیست علاقه مندی ها مقایسه ورود / ثبت نام سبد خرید بستن</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1243,10 +1232,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="3" t="n">
         <v>350000</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="3" t="n">
         <v>350000</v>
       </c>
     </row>
@@ -1257,14 +1246,14 @@
       <c r="B24" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>https://nikushop.com/product/h21a1/</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>H21A1 – نیکوشاپ Skip to content جستجو برای: سبد خرید شما خالی است. بازگشت به فروشگاه سبد خرید سبد خرید شما خالی است. بازگشت به فروشگاه صفحه اصلی فروشگاه ورود/ثبت‌نام قوانین تماس با ما وب سایت قدیم جستجو برای: خانه / SENSORS/سنسورها / Infrared Sensor خانه › SENSORS/سنسورها › Infrared Sensor H21A1 شناسه کالا: ۲۸۱۰۰۲۶ سنسور مادون قرمز اپتوکانتر 3 میلی متری کلید نوری انتقال دهنده فتوترانزیستوری درباره این محصول Features Sensing Distance (Min) 3mm Collector Emitter Voltage (VCEO) 30V Output Type  Phototransistor DC Collector Curren  20mA Reverse Voltage (Vrrm)  6V Forward Voltage (Vf)  1.7V Mounting Style  Through Hole Minimum Operating Temperature  -55°C Maximum Operating Temperature  100°C Brand  Fairchild Semiconductor Package  Package U توضیحات تکمیلی + وزن 3 گرم نظرات (0) + اولین نفری باشید که دیدگاه می‌گذارد برای «H21A1» لغو پاسخ امتیاز شما * دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. من ربات نیستم دیدگاه‌ها هنوز دیدگاهی ثبت نشده است. ۶۶۰,۰۰۰ ریال تحویل: ۱ الی ۲ روز کاری ارسال به سراسر ایران موجود در انبار تعداد: H21A1 عدد افزودن به سبد خرید معامله امن فروشنده نیکوشاپ بازگشت طبق قوانین فروشگاه پشتیبانی تماس با پشتیبانی محصولات مشابه + مشاهده Infrared Sensor GP2S04-06 فتو سنسور 2,818,310 ریال Reflective photosensor مشابه با  ON2170 ,CNB1302 + مشاهده Infrared Sensor GP2Y0A21YK 9,050,800 ریال ماژول فاصله سنج شارپ + مشاهده Infrared Sensor IR TRANSMITTER 5mm 49,500 ریال دیود فرستنده 940nm مادون قرمز 5 میلی متری + مشاهده در انبار موجود نمی باشد Infrared Sensor H22A1 732,050 ریال سنسور مادون قرمز (اپتوکانتر) H22A1 + مشاهده Infrared Sensor IR RECIVER 5mm 59,840 ریال دیود گیرنده 940nm مادون قرمز 5 میلی متری + مشاهده Infrared Sensor TSOP1138 1,730,300 ریال سنسور گیرنده مادون قرمز TSOP1138 اورجینال برند VISHAY + مشاهده Infrared Sensor IR TRANSMITTER 8mm 665,500 ریال دیود فرستنده مادون قرمز 8 میلی متری + مشاهده Infrared Sensor HS0038A2D 1,011,560 ریال سنسور گیرنده مادون قرمز HS0038 همه حقوق برای نیکوشاپ محفوظ است. - جستجو برای: صفحه اصلی فروشگاه ورود/ثبت‌نام قوانین تماس با ما وب سایت قدیم Newsletter 0 × برای مشاهده نتایج زنده، شروع به تایپ کنید... × × ورود نام کاربری یا آدرس ایمیل * الزامی گذرواژه * الزامی من ربات نیستم مرا به خاطر بسپار ورود گذرواژه خود را فراموش کرده اید؟ عضویت آدرس ایمیل * الزامی گذرواژه * الزامی من ربات نیستم اطلاعات شخصی شما برای پردازش سفارش شما استفاده می‌شود، و پشتیبانی از تجربه شما در این وبسایت، و برای اهداف دیگری که در سیاست حفظ حریم خصوصی توضیح داده شده است. عضویت</t>
+          <t>H21A1 – نیکوشاپ Skip to content جستجو برای: سبد خرید شما خالی است. بازگشت به فروشگاه سبد خرید سبد خرید شما خالی است. بازگشت به فروشگاه صفحه اصلی فروشگاه ورود/ثبت‌نام قوانین تماس با ما وب سایت قدیم جستجو برای: خانه / SENSORS/سنسورها / Infrared Sensor خانه › SENSORS/سنسورها › Infrared Sensor H21A1 شناسه کالا: ۲۸۱۰۰۲۶ سنسور مادون قرمز اپتوکانتر 3 میلی متری کلید نوری انتقال دهنده فتوترانزیستوری درباره این محصول Features Sensing Distance (Min) 3mm Collector Emitter Voltage (VCEO) 30V Output Type  Phototransistor DC Collector Curren  20mA Reverse Voltage (Vrrm)  6V Forward Voltage (Vf)  1.7V Mounting Style  Through Hole Minimum Operating Temperature  -55°C Maximum Operating Temperature  100°C Brand  Fairchild Semiconductor Package  Package U توضیحات تکمیلی + وزن 3 گرم نظرات (0) + اولین نفری باشید که دیدگاه می‌گذارد برای «H21A1» لغو پاسخ امتیاز شما * دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. من ربات نیستم دیدگاه‌ها هنوز دیدگاهی ثبت نشده است. ۶۶۰,۰۰۰ ریال تحویل: ۱ الی ۲ روز کاری ارسال به سراسر ایران موجود در انبار تعداد: H21A1 عدد افزودن به سبد خرید معامله امن فروشنده نیکوشاپ بازگشت طبق قوانین فروشگاه پشتیبانی تماس با پشتیبانی محصولات مشابه + مشاهده Infrared Sensor CNY70 665,500 ریال REFLECTIVE OPTOSENSOR WITH TRAسنسور مادون قرمز + مشاهده Infrared Sensor TCRT5000-CHINA 286,110 ریال Reflective Optical Sensor with Transistor Outputسنسور مادون قرمز مدل چینی + مشاهده Infrared Sensor HY860F 1,181,510 ریال سنسور مادون قرمز (اپتوکانتر) HY860F + مشاهده Infrared Sensor IR TRANSMITTER 8mm 665,500 ریال دیود فرستنده مادون قرمز 8 میلی متری + مشاهده Infrared Sensor ماژول اپتوکانتر Q15 865,150 ریال این ماژول برای راه اندازی اپتوکانتر است.OPTO COUNTER MODULE + مشاهده Infrared Sensor HS0038BD 837,760 ریال سنسور گیرنده 38KHZ مادون قرمز HS0038B + مشاهده Infrared Sensor IR RECIVER 3mm 46,530 ریال دیود گیرنده مادون قرمز 3 میلی متری + مشاهده Infrared Sensor PD438C 532,400 ریال گیرنده فتودیود PD438C برند EVERLIGHT همه حقوق برای نیکوشاپ محفوظ است. - جستجو برای: صفحه اصلی فروشگاه ورود/ثبت‌نام قوانین تماس با ما وب سایت قدیم Newsletter 0 × برای مشاهده نتایج زنده، شروع به تایپ کنید... × × ورود نام کاربری یا آدرس ایمیل * الزامی گذرواژه * الزامی من ربات نیستم مرا به خاطر بسپار ورود گذرواژه خود را فراموش کرده اید؟ عضویت آدرس ایمیل * الزامی گذرواژه * الزامی من ربات نیستم اطلاعات شخصی شما برای پردازش سفارش شما استفاده می‌شود، و پشتیبانی از تجربه شما در این وبسایت، و برای اهداف دیگری که در سیاست حفظ حریم خصوصی توضیح داده شده است. عضویت</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1272,10 +1261,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="3" t="n">
         <v>660000</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="3" t="n">
         <v>660000</v>
       </c>
     </row>
@@ -1286,7 +1275,7 @@
       <c r="B25" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>https://www.denizetc.com/terminal-block-kf129r-2pin-5-0mm</t>
         </is>
@@ -1301,10 +1290,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="3" t="n">
         <v>144000</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="3" t="n">
         <v>144000</v>
       </c>
     </row>
@@ -1315,14 +1304,14 @@
       <c r="B26" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>https://www.iran-module.ir/product_info.php/products_id/2954/pname/%D8%AC%D8%B9%D8%A8%D9%87-(%DA%A9%D9%8A%D8%B3)-%D8%A2%D9%84%D9%88%D9%85%D9%8A%D9%86%D9%8A%D9%88%D9%85%D9%8A-%D8%A8%D8%B1%D8%AF-%D8%B1%D8%B3%D9%BE%D8%A8%D8%B1%D9%8A-%D9%BE%D8%A7%D9%8A-5-%D8%A8%D9%87-%D9%87%D9%85%D8%B1%D8%A7%D9%87-%D9%81%D9%86-%D8%AF%D9%88%D8%A8%D9%84</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>بردهای توسعه - Raspberry Pi - DEV-00383 - جعبه (کيس) آلومينيومي برد رسپبري پاي 5 به همراه فن دوبل - ايران ماژول الكترونيك انتخاب واحد پولی: دلار یورو ريال تومان سبد خرید: ( 0 ) مورد خوش آمدید, کاربر گرامی صفحه اصلی سفارشات خارجی جستجوی پیشرفته تماس با ما درباره ما ورود پشتیبانی آنلاین Start Live Help Chat شاخه ها حراج قطعات Arduino GPS آنتن ماژول گيرنده GSM/GPRS LCD Single Board Computer ابزار DAQ بخار سرد برد برد برد رله پمپ خنک کننده/گرم کننده دستگاه های اندازه گيری ديتالاگر شیر برقی قفل برقی و سلونوئید لیزر متفرقه بردهای توسعه Android ARM LPC SAM SAMSUNG AVR Banana Pi Beagle Cypress FPGA LattePanda Intel Micro:bit MSP NET. NanoPI Odroid بـــورد اصلی تجهیزات جانبی NVIDEA Orange Pi PIC Raspberry Pi RENESAS ST Teensy TI Wiznet بردهای Breakout پاور، تغذيه و باتری پرنده بدون سرنشين اتوپايلوت رادیو کنترل و تلمتری ربات پرنده سنسور موتور و بدنه پروگرمر ARM AVR PIC پرینتر پرینتر حرارتی پرینتر سه بعدی تبلت ها لوازم جانبی خانه هوشمند کنترلرهای بلوتوث كنترلرهای شبكه خودرو الکتریکی قطعات و تجهیزات جانبی کنترلر موتور درایورها راديويیRF و ارتباطات Bluetooth General Modem Nordic RFID WiFi ZigBee آنتن فرستنده و گیرنده تصویر فرستنده و گیرنده صوت قطعات مخابراتی کانکتور مخابراتی رباتيك درايور قطعات مكانيكی چرخ ربات غيره كيت ربات موتور ردیابی سلول های خورشیدی سنسور IMU/AHRS PIR التراسونيك بيومتری تاچ تشخیص سطح مایعات تشعشعات جریان/ولتاژ حسگر مجاورتی دما رطوبت زاويه سنج ژيروسكوپ 1 محوری 2 محوری 3 محوری شتاب سنج 1 محوری 2 محوری 3 محوری شعله آتش صوت فشار فلومتر گاز ليزر مادون قرمز مایکروویو مغناطيس و قطب نما نور/تصوير/رنگ نيرو/گشتاور/خمش/لرزش هواشناسی هويت ID صوت قطعات آی سی های SMD آی سی های عمومی اسيلاتور و نوسانگر پتانسیومتر خازن دیود و ترانزیستور رگولاتور سلف و القاگر سوپر خازن قطعات عمومی کانکتورها كليد/سوییچ ميكروكنترلرهای AVR ميكروكنترلرهای ARM ميكروكنترلرهای PIC كابل HDMI USB پارالل سریال شبكه فایر وایر فیبر نوری مبدل اينترفيس نور و LED 3mm 5mm 10mm RGB SMD پر توان سون سگمنت ماوراء بنفش اطلاعيه ها مرا از تغييرات محصول جعبه (کيس) آلومينيومي برد رسپبري پاي 5 به همراه فن دوبل آگاه كن. مقایسه محصولات محصولی برای مقایسه انتخاب نشده است! ورود به سيستم آدرس پست الكترونيك: كلمه عبور: کلمه عبورتان را فراموش کرده اید؟ هنوز ثبت نام نکرده اید؟ تگ محصولات ser2usb usb2232 rpi 4852232 op-amp 2322lan ttl2232 2sma rpic ser2lan ttl2usb hdmi2vga vga2hdmi opamp wifi2ser lan2232 2ufl lan2ser ser2wifi d2a ttl2lan زیگبی 4222232 CASE lan2ttl 2322422 usb2ttl kit usb2ser 2322usb 2322485 4852ttl USB2485 2smaf a2d waveshare 4852usb ttl2485 2322ttl av2hdmi مقالات مقالات جدید تمامی مقالات تمامی موضوعات مقالات متفرقه RSS مقالات فروشگاه » بردهای توسعه » Raspberry Pi » DEV-00383 جعبه (کيس) آلومينيومي برد رسپبري پاي 5 به همراه فن دوبل [ DEV-00383 ] کد کالا : DEV-00383 قیمت: 1,950,000تومان مشخصات فنی جعبه (کیس) آلومینیومی برد رزبری پای 5 به همراه فن دوبل مناسب برای: رزبری پای 5 مدل‌های 4GB و 8GB جنس بدنه: آلومینیوم رنگ بدنه: مشکی ابعاد کیس: 85x56x22 میلی‌متر ویژگی فن‌ها: فن‌های DC Brushless ابعاد فن‌ها: 30x30 میلی‌متر سیستم خنک‌کننده: فن دوبل با خنک‌سازی مؤثر ویژگی‌های جعبه (کیس) آلومینیومی برد رزبری پای 5 به همراه فن دوبل ساختار مقاوم و با دوام از جنس آلومینیوم طراحی مناسب برای دفع حرارت بهینه و جلوگیری از داغ شدن سیستم خنک‌کننده دوبل برای حفظ عملکرد پایدار دسترسی آسان به تمام پورت‌ها و اتصالات مناسب برای پروژه‌های حرفه‌ای و صنعتی اطلاعات تماس Iran Module Electronic 02166720648 با بیان پوزش در اغلب اوقات قادر به مشاوره تلفنی نخواهیم بود. 021 کالاهای ناموجود فاقد لینک افزودن به سبد خرید میباشند bel_elc@yahoo.com www.iran-module.ir 02166713123 09391963671 به دلیل محدودیتهای اعمال شده کرونایی امکان پذیرایی هنگام مراجعه وجود ندارد. آدرس تهران خ جمهوری بین پل حافظ و سی تیر پاساژ فرشته پلاک 267 [ [ [ تا بهبود شرایط بهداشتی جامعه خدمت رسانی ترجیحاً غیرحضوری خواهد بود ] ] ] ساعت شنبه تا چهارشنبه 22:00 ~ 10:00 ♢ ♡ با آرزوی سلامتی توجه کالاهای ناموجود فاقد لینک افزودن به سبد خرید می باشند پرفروشترین محصولات کابل micro USB برای رزبری پای 3 با سوییچ Power بورد رسپبری پای Raspberry Pi 3 Model B+ UK ساخت Element14 فن خنک کننده مخصوص رسپبری پای Raspberry Pi Fan بورد رسپبری پای 4  Raspberry Pi 4 2G Model B UK ساخت انگلستان بورد رسپبری پای 4  Raspberry Pi 4 4G Model B UK ساخت انگلستان آداپتور اورجینال رسپبری پای 4 خروجی 5 ولت 3 آمپر جعبه (کیس) آلومینیومی برد رسپبری پای 4 به همراه فن دوبل کیس پلاستیکی فن خور برای رزبری پای 4 کیس اریجینال رنگی Element14 برای رزبری پای 4 کابل تبدیل HDMI به VGA همراه با خروجی صدا DT-6404 دوربین 8 مگاپیکسل برای برد رسپبری اوریجینال محصول Element14 بورد رسپبری پای 4  Raspberry Pi 4 8G Model B UK ساخت انگلستان دوربین 8MP رسپبری پای  V2.1 NoIR محصول Element14 برد رزبری پای 5 رم 8 گیگ Raspberry Pi 5 8G Model B UK کابل مبدل میکرو USB به USB مناسب برای رزبری پای زیرو رفرنس بورد برای GPIO رسپبری پای برد رسپبری پای پیکو Raspberry Pi Pico دوربین 12.3 مگاپیکسل IMX477R رزبری پای مبدل Micro USB به TYPE C کوتاه مناسب برای رسپبری پای 4 برد رسپبری پای پیکو دبلیو  Raspberry Pi Pico W مبدل Micro USB به TYPE C بدنه فلزی مناسب برای رسپبری پای 4 نمایشگر 7 اینچ رسپبری تاچ خازنی اریجینال Element14 به علاوه قاب مخصوص رزبری 3 و 4 هت توسعه بورد رسپبری پای فیبر سوراخدار تماس با ما کپی‌رایت © 2026 ایران ماژول الکترونیک راه اندازی شده توسط فروشگاه ساز ویرچو</t>
+          <t>بردهای توسعه - Raspberry Pi - DEV-00383 - جعبه (کيس) آلومينيومي برد رسپبري پاي 5 به همراه فن دوبل - ايران ماژول الكترونيك انتخاب واحد پولی: دلار یورو ريال تومان سبد خرید: ( 0 ) مورد خوش آمدید, کاربر گرامی صفحه اصلی سفارشات خارجی جستجوی پیشرفته تماس با ما درباره ما ورود پشتیبانی آنلاین Start Live Help Chat شاخه ها حراج قطعات Arduino GPS آنتن ماژول گيرنده GSM/GPRS LCD Single Board Computer ابزار DAQ بخار سرد برد برد برد رله پمپ خنک کننده/گرم کننده دستگاه های اندازه گيری ديتالاگر شیر برقی قفل برقی و سلونوئید لیزر متفرقه بردهای توسعه Android ARM LPC SAM SAMSUNG AVR Banana Pi Beagle Cypress FPGA LattePanda Intel Micro:bit MSP NET. NanoPI Odroid بـــورد اصلی تجهیزات جانبی NVIDEA Orange Pi PIC Raspberry Pi RENESAS ST Teensy TI Wiznet بردهای Breakout پاور، تغذيه و باتری پرنده بدون سرنشين اتوپايلوت رادیو کنترل و تلمتری ربات پرنده سنسور موتور و بدنه پروگرمر ARM AVR PIC پرینتر پرینتر حرارتی پرینتر سه بعدی تبلت ها لوازم جانبی خانه هوشمند کنترلرهای بلوتوث كنترلرهای شبكه خودرو الکتریکی قطعات و تجهیزات جانبی کنترلر موتور درایورها راديويیRF و ارتباطات Bluetooth General Modem Nordic RFID WiFi ZigBee آنتن فرستنده و گیرنده تصویر فرستنده و گیرنده صوت قطعات مخابراتی کانکتور مخابراتی رباتيك درايور قطعات مكانيكی چرخ ربات غيره كيت ربات موتور ردیابی سلول های خورشیدی سنسور IMU/AHRS PIR التراسونيك بيومتری تاچ تشخیص سطح مایعات تشعشعات جریان/ولتاژ حسگر مجاورتی دما رطوبت زاويه سنج ژيروسكوپ 1 محوری 2 محوری 3 محوری شتاب سنج 1 محوری 2 محوری 3 محوری شعله آتش صوت فشار فلومتر گاز ليزر مادون قرمز مایکروویو مغناطيس و قطب نما نور/تصوير/رنگ نيرو/گشتاور/خمش/لرزش هواشناسی هويت ID صوت قطعات آی سی های SMD آی سی های عمومی اسيلاتور و نوسانگر پتانسیومتر خازن دیود و ترانزیستور رگولاتور سلف و القاگر سوپر خازن قطعات عمومی کانکتورها كليد/سوییچ ميكروكنترلرهای AVR ميكروكنترلرهای ARM ميكروكنترلرهای PIC كابل HDMI USB پارالل سریال شبكه فایر وایر فیبر نوری مبدل اينترفيس نور و LED 3mm 5mm 10mm RGB SMD پر توان سون سگمنت ماوراء بنفش اطلاعيه ها مرا از تغييرات محصول جعبه (کيس) آلومينيومي برد رسپبري پاي 5 به همراه فن دوبل آگاه كن. مقایسه محصولات محصولی برای مقایسه انتخاب نشده است! ورود به سيستم آدرس پست الكترونيك: كلمه عبور: کلمه عبورتان را فراموش کرده اید؟ هنوز ثبت نام نکرده اید؟ تگ محصولات usb2ser usb2ttl 2322422 2sma USB2485 op-amp usb2232 rpic ser2wifi av2hdmi rpi d2a ser2lan ttl2232 lan2232 4852ttl kit lan2ser wifi2ser CASE 4852232 2smaf 4852usb opamp ttl2485 زیگبی ttl2usb 2322usb 2322485 lan2ttl a2d 4222232 2322lan ttl2lan 2322ttl 2ufl waveshare vga2hdmi hdmi2vga ser2usb مقالات مقالات جدید تمامی مقالات تمامی موضوعات مقالات متفرقه RSS مقالات فروشگاه » بردهای توسعه » Raspberry Pi » DEV-00383 جعبه (کيس) آلومينيومي برد رسپبري پاي 5 به همراه فن دوبل [ DEV-00383 ] کد کالا : DEV-00383 قیمت: 1,950,000تومان مشخصات فنی جعبه (کیس) آلومینیومی برد رزبری پای 5 به همراه فن دوبل مناسب برای: رزبری پای 5 مدل‌های 4GB و 8GB جنس بدنه: آلومینیوم رنگ بدنه: مشکی ابعاد کیس: 85x56x22 میلی‌متر ویژگی فن‌ها: فن‌های DC Brushless ابعاد فن‌ها: 30x30 میلی‌متر سیستم خنک‌کننده: فن دوبل با خنک‌سازی مؤثر ویژگی‌های جعبه (کیس) آلومینیومی برد رزبری پای 5 به همراه فن دوبل ساختار مقاوم و با دوام از جنس آلومینیوم طراحی مناسب برای دفع حرارت بهینه و جلوگیری از داغ شدن سیستم خنک‌کننده دوبل برای حفظ عملکرد پایدار دسترسی آسان به تمام پورت‌ها و اتصالات مناسب برای پروژه‌های حرفه‌ای و صنعتی اطلاعات تماس Iran Module Electronic 02166720648 با بیان پوزش در اغلب اوقات قادر به مشاوره تلفنی نخواهیم بود. 021 کالاهای ناموجود فاقد لینک افزودن به سبد خرید میباشند bel_elc@yahoo.com www.iran-module.ir 02166713123 09391963671 به دلیل محدودیتهای اعمال شده کرونایی امکان پذیرایی هنگام مراجعه وجود ندارد. آدرس تهران خ جمهوری بین پل حافظ و سی تیر پاساژ فرشته پلاک 267 [ [ [ تا بهبود شرایط بهداشتی جامعه خدمت رسانی ترجیحاً غیرحضوری خواهد بود ] ] ] ساعت شنبه تا چهارشنبه 22:00 ~ 10:00 ♢ ♡ با آرزوی سلامتی توجه کالاهای ناموجود فاقد لینک افزودن به سبد خرید می باشند پرفروشترین محصولات کابل micro USB برای رزبری پای 3 با سوییچ Power بورد رسپبری پای Raspberry Pi 3 Model B+ UK ساخت Element14 فن خنک کننده مخصوص رسپبری پای Raspberry Pi Fan بورد رسپبری پای 4  Raspberry Pi 4 2G Model B UK ساخت انگلستان بورد رسپبری پای 4  Raspberry Pi 4 4G Model B UK ساخت انگلستان آداپتور اورجینال رسپبری پای 4 خروجی 5 ولت 3 آمپر جعبه (کیس) آلومینیومی برد رسپبری پای 4 به همراه فن دوبل کیس پلاستیکی فن خور برای رزبری پای 4 کیس اریجینال رنگی Element14 برای رزبری پای 4 کابل تبدیل HDMI به VGA همراه با خروجی صدا DT-6404 دوربین 8 مگاپیکسل برای برد رسپبری اوریجینال محصول Element14 بورد رسپبری پای 4  Raspberry Pi 4 8G Model B UK ساخت انگلستان دوربین 8MP رسپبری پای  V2.1 NoIR محصول Element14 برد رزبری پای 5 رم 8 گیگ Raspberry Pi 5 8G Model B UK کابل مبدل میکرو USB به USB مناسب برای رزبری پای زیرو رفرنس بورد برای GPIO رسپبری پای برد رسپبری پای پیکو Raspberry Pi Pico دوربین 12.3 مگاپیکسل IMX477R رزبری پای مبدل Micro USB به TYPE C کوتاه مناسب برای رسپبری پای 4 برد رسپبری پای پیکو دبلیو  Raspberry Pi Pico W مبدل Micro USB به TYPE C بدنه فلزی مناسب برای رسپبری پای 4 نمایشگر 7 اینچ رسپبری تاچ خازنی اریجینال Element14 به علاوه قاب مخصوص رزبری 3 و 4 هت توسعه بورد رسپبری پای فیبر سوراخدار تماس با ما کپی‌رایت © 2026 ایران ماژول الکترونیک راه اندازی شده توسط فروشگاه ساز ویرچو</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1330,10 +1319,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="3" t="n">
         <v>19500000</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="3" t="n">
         <v>19500000</v>
       </c>
     </row>
@@ -1344,14 +1333,14 @@
       <c r="B27" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>https://skytech.ir/product_details.aspx?ID_Parts=22724&amp;3MM-YELLOW-LED</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>فروشگاه قطعات الکترونیکی اسکای تکنولوژی کاربر عزیز خوش آمدید! صفحه اصلی سفارش خارجی سفارش PCB مرسوله وبلاگ درباره ما تماس با ما پیشنهادات ثبت نام شماره مرسوله Dev Boards Audio Modules Computing Data Conversion Modules Display Modules Energy Harvesting Modules Engineering Tools Ethernet &amp; Communication Modules Interface Modules Memory &amp; Data Storage Modules Accessories Other Modules Power Management Modules Sensor Modules Software Video Modules Wireless &amp; RF Modules Discrete Semiconductors Diodes &amp; Rectifiers Thyristors Transistors Discrete Semiconductor Modules MOSFETS Diac &amp; Triacs IGBTS Embedded Processors &amp; Controllers CPLD - Complex Programmable Logic Devices FPGA - Configuration Memory Processors - Application Specialized CPU - Central Processing Units FPGA - Field Programmable Gate Array RF System on a Chip - SoC Digital Signal Processors &amp; Controllers - DSP, DSC Microcontrollers - MCU SPLD - Simple Programmable Logic Devices EEPLD - Electronically Erasable Programmable Logic Devices Microprocessors - MPU Systems on a Chip - SoC Integrated Circuits - ICs Active Filter &amp; Isolators Digital Potentiometer ICs Multimedia ICs Amplifier ICs Driver ICs Optocouplers / Photocouplers Audio ICs Embedded Processors &amp; Controllers Power Management ICs Chipsets Equalizers &amp; Signal Generators Programmable Logic ICs Clock &amp; Timer ICs Interface ICs Security ICs / Authentication ICs Communication &amp; Networking ICs Logic ICs Switch ICs Counter ICs Memory ICs Wireless &amp; RF Integrated Circuits Data Converter ICs Memory ICs DRAM Managed NAND NAND Flash EEPROM Memory Controllers NOR Flash eMMC Memory IC Development Tools NVRAM EPROM Memory Modules &amp; Memory Cards SRAM FIFO Multichip Packages Storage F-RAM SD RAM Wireless &amp; RF Semiconductors PIN Diodes Transistors RF Wireless &amp; RF Integrated Circuits Sensors &amp; Modules Audio Sensors Flow Sensors Optical Sensors Biometric Sensors Force Sensors &amp; Load Cells Pressure Sensors Capacitive Touch Sensors Linear Displacement Sensors Proximity Sensors Current Sensors Liquid Level Sensors Sensor Development Tools Encoders Magnetic Sensors Sensor Hardware &amp; Accessories Environmental Sensors Motion &amp; Position Sensors Temperature Sensors Wireless Modules Ultrasonic Industrial Automation Connector Audio &amp; Video Connectors Headers &amp; Wire Housings Pin &amp; Socket Connectors Automotive Connectors I/O Connectors Power Connectors Backplane Connectors IC &amp; Component Sockets Power Line Filters Board to Board &amp; Mezzanine Connectors IEEE 1394 Connectors RF Interconnects Card Edge Connectors Junction Systems Solar Connectors / Photovoltaic Connectors Circular Connectors Lighting Connectors Terminal Blocks Data Bus Components Memory Connectors Terminals D-Sub Connectors MIL-Spec / MIL-Type Unspecified Connectors FFC / FPC Modular Connectors / Ethernet Connectors USB Connectors Fiber Optic Connectors Passive Componnent Antennas Ferrites Signal Conditioning Audio Transformers / Signal Transformers Frequency Control &amp; Timing Devices Thermistors - NTC Capacitors Inductors, Chokes &amp; Coils Thermistors - PTC EMI Filters / EMI Suppression Potentiometers, Trimmers &amp; Rheostats Varistors Encoders Resistors Filters Electromechanical Audio Devices I/O Modules Printers Circuit Breakers Industrial Automation Relays Encoders Knobs &amp; Dials Switches Hardware Fans &amp; Blowers Heat Sinks Termoelectric Coller Motors and Drivers Enclosures Enclosures, Boxes, &amp; Cases Racks &amp; Cabinets Standard Electrical LED Lighting &amp; Opto Electronic LED Bulbs &amp; Modules Displays Laser Drivers LED Emitters Optical Switches Fiber Optics LED Indication Optocouplers / Photocouplers Infrared Data Communications Camera Display LED LCD 7 Segment Character &amp; Monocolor LCD Touch Screen Power Supply Addappter Convertor Electric battery &amp; Cells Fuse &amp; Circuit protection Fuse &amp; Protection Thermal Switches Fuse Holders Circuit Breakers &amp; Accessories Resettable-Fuses-PPTC Thermistors Thyristors Varistors ESD Suppressors / TVS Diodes Tools &amp; Supplies Accessories Labels and Industrial Warning Signs Soldering Adhesive Tapes Liquid Dispensers &amp; Bottles Storage Boxes &amp; Cases Anti-Static Control Products Prototyping Products Tools Chemicals Programmer تخفیف ویژه فهرست تخفیفات ویژه سنجش رضایتمندی صفحه اصلی / LED Lighting &amp; Opto Electronic / LED Emitters / LED Emitters / 3MM YELLOW LED LED زرد رنگ 3MM YELLOW LED 3MM YELLOW LED (Light emitting diode) کیفیت: Bulk(فله ایی) پکیج: TH-2 قیمت تک فروشی 6,122 ریال قیمت عمده 5,916 ریال (10 به بالا) قیمت ویژه 5,834 ریال (100 به بالا) قیمت فوق العاده 5,793 ریال (1000 به بالا) قیمت تک فروشی 0.003 تتر با تخفیف 0.01 0.01 0.01 0.01 تعداد موجودی در انبار : 11684 عدد تعدادی از این کالا توسط مشتری رزرو شده است در صورت موجود شدن خبر بده افزودن به علاقه مندی ها تعداد درخواست: مشخصات کالا کالا های مشابه دانلود فایل توضیحات LED زرد 3mm يک ديود ساطع کننده نور (LED) است که نور زرد رنگ توليد مي کند و قطر آن 3 ميلي متر است. در اينجا توضيحات کاملي در مورد اين نوع LED ارائه مي شود: ويژگي هاي کليدي: نوع: ديود ساطع کننده نور (LED) رنگ نور: زرد قطر: 3 ميلي متر جنس: معمولاً از مواد نيمه هادي مانند گاليم آرسنيد فسفيد (GaAsP) ساخته مي شود. ولتاژ کاري: معمولاً بين 1.8 تا 2.2 ولت است. جريان کاري: معمولاً بين 10 تا 20 ميلي آمپر است. زاويه ديد: بسته به نوع LED، زاويه ديد مي تواند متفاوت باشد. نوع لنز: مي تواند شفاف يا مات باشد. کاربردها: نشانگرهاي وضعيت در دستگاه هاي الکترونيکي پنل هاي نمايشگر تزئينات و نورپردازي پروژه هاي الکترونيکي DIY تابلوهاي تبليغاتي مزايا: مصرف انرژي کم طول عمر بالا اندازه کوچک تنوع رنگي قيمت مناسب Description The 3mm Yellow LED is a light-emitting diode (LED) that produces yellow light and is 3 mm in diameter. Here is a complete description of this type of LED: Key Features: Type: Light-emitting diode (LED) Light color: Yellow Diameter: 3 mm Material: Usually made of semiconductor materials such as gallium arsenide phosphide (GaAsP). Working voltage: Usually between 1.8 and 2.2 V. Working current: Usually between 10 and 20 mA. Viewing angle: Depending on the type of LED, the viewing angle can vary. Lens type: Can be clear or opaque. Applications: Status indicators in electronic devices Display panels Decorations and lighting DIY electronic projects Advertising boards Advantages: Low power consumption Long lifespan Small size Color variety Affordable price HSMR-C191-S0000 تک فروشی: 2657610 ریال عمده: 2531610 ریال اضافه به سبد مشاهده کالا WS2812B تک فروشی: 198000 ریال عمده: 156000 ریال اضافه به سبد مشاهده کالا AEMD-CM1L-34B02 تک فروشی: 3098400 ریال عمده: 2951400 ریال اضافه به سبد مشاهده کالا SFH 2706 تک فروشی: 4860000 ریال عمده: 4629000 ریال اضافه به سبد مشاهده کالا Red Led 0805 تک فروشی: 88500 ریال عمده: 84300 ریال اضافه به سبد مشاهده کالا TSAL6200 تک فروشی: 279600 ریال عمده: 267000 ریال اضافه به سبد مشاهده کالا SML813BNTT86 تک فروشی: 2652900 ریال عمده: 2526900 ریال اضافه به سبد مشاهده کالا XPGDWT-U1-0000-00EDV تک فروشی: 5304000 ریال عمده: 5052000 ریال اضافه به سبد مشاهده کالا 5MM LED Dip Yellow تک فروشی: 41550 ریال عمده: 41550 ریال اضافه به سبد مشاهده کالا PT333-3B تک فروشی: 240000 ریال عمده: 198000 ریال اضافه به سبد مشاهده کالا CZ-408SUGC02-01 تک فروشی: 22800 ریال عمده: 21120 ریال اضافه به سبد مشاهده کالا S11153-01MT تک فروشی: 4440000 ریال عمده: 4230000 ریال اضافه به سبد مشاهده کالا اسناد و فایل های متنی مدار های چاپی برنامه ها و فایل ها سایت های و ارتباط ها گروه بازرگانی اسکایتک وارد كننده قطعات الکترونیک و نیمه هادی با بیش از پنج سال تجربه افتخار دارد با عرضه محصولات اصلی ، با كیفیت و استاندارد جهت ارج نهادن به سلیقه توزیع كنندگان متعهد در راستای حفاظت از منافع و مصالح مصرف كنندگان نهایی گام بردارد. فروشگاه اسکای تک با حمایت كم نظیر مشتریان خوش نام و فعال به عنوان گروهی پیشرو در ایران ، موفق به اخذ نمایندگی انحصاری و توزیع بسیاری از كمپانی های معتبر جهان  در یك مجموعه گردیده است . استقبال چشمگیر مشتریان صادق و مصرف كنندگان فهیم از خرید قطعات الکترونیک با كیفیت در مقابل قطعات نامرغوب و غیر استاندارد وارداتی، موجب گردآوری طیف وسیعی (بالغ بر 40000 قلم كالا)‌ از قطعات الکترونیک گوناگون دراین فروشگاه شده است. قوانین ارتباط با فروشگاه ارتباط با واحد فروش ارتباط با واحد پشتیبانی فنی انتقادات و پیشنهادات قوانین و شرایط سایت دسترسی های سایت نقشه سایت درباره ما سوالات متداول شماره حساب ها لینک های ما آپارات فروشگاه اسکایتک کلیه حقوق این سایت متعلق به فروشگاه Skytech می باشد</t>
+          <t>فروشگاه قطعات الکترونیکی اسکای تکنولوژی کاربر عزیز خوش آمدید! صفحه اصلی سفارش خارجی سفارش PCB مرسوله وبلاگ درباره ما تماس با ما پیشنهادات ثبت نام شماره مرسوله Dev Boards Audio Modules Computing Data Conversion Modules Display Modules Energy Harvesting Modules Engineering Tools Ethernet &amp; Communication Modules Interface Modules Memory &amp; Data Storage Modules Accessories Other Modules Power Management Modules Sensor Modules Software Video Modules Wireless &amp; RF Modules Discrete Semiconductors Diodes &amp; Rectifiers Thyristors Transistors Discrete Semiconductor Modules MOSFETS Diac &amp; Triacs IGBTS Embedded Processors &amp; Controllers CPLD - Complex Programmable Logic Devices FPGA - Configuration Memory Processors - Application Specialized CPU - Central Processing Units FPGA - Field Programmable Gate Array RF System on a Chip - SoC Digital Signal Processors &amp; Controllers - DSP, DSC Microcontrollers - MCU SPLD - Simple Programmable Logic Devices EEPLD - Electronically Erasable Programmable Logic Devices Microprocessors - MPU Systems on a Chip - SoC Integrated Circuits - ICs Active Filter &amp; Isolators Digital Potentiometer ICs Multimedia ICs Amplifier ICs Driver ICs Optocouplers / Photocouplers Audio ICs Embedded Processors &amp; Controllers Power Management ICs Chipsets Equalizers &amp; Signal Generators Programmable Logic ICs Clock &amp; Timer ICs Interface ICs Security ICs / Authentication ICs Communication &amp; Networking ICs Logic ICs Switch ICs Counter ICs Memory ICs Wireless &amp; RF Integrated Circuits Data Converter ICs Memory ICs DRAM Managed NAND NAND Flash EEPROM Memory Controllers NOR Flash eMMC Memory IC Development Tools NVRAM EPROM Memory Modules &amp; Memory Cards SRAM FIFO Multichip Packages Storage F-RAM SD RAM Wireless &amp; RF Semiconductors PIN Diodes Transistors RF Wireless &amp; RF Integrated Circuits Sensors &amp; Modules Audio Sensors Flow Sensors Optical Sensors Biometric Sensors Force Sensors &amp; Load Cells Pressure Sensors Capacitive Touch Sensors Linear Displacement Sensors Proximity Sensors Current Sensors Liquid Level Sensors Sensor Development Tools Encoders Magnetic Sensors Sensor Hardware &amp; Accessories Environmental Sensors Motion &amp; Position Sensors Temperature Sensors Wireless Modules Ultrasonic Industrial Automation Connector Audio &amp; Video Connectors Headers &amp; Wire Housings Pin &amp; Socket Connectors Automotive Connectors I/O Connectors Power Connectors Backplane Connectors IC &amp; Component Sockets Power Line Filters Board to Board &amp; Mezzanine Connectors IEEE 1394 Connectors RF Interconnects Card Edge Connectors Junction Systems Solar Connectors / Photovoltaic Connectors Circular Connectors Lighting Connectors Terminal Blocks Data Bus Components Memory Connectors Terminals D-Sub Connectors MIL-Spec / MIL-Type Unspecified Connectors FFC / FPC Modular Connectors / Ethernet Connectors USB Connectors Fiber Optic Connectors Passive Componnent Antennas Ferrites Signal Conditioning Audio Transformers / Signal Transformers Frequency Control &amp; Timing Devices Thermistors - NTC Capacitors Inductors, Chokes &amp; Coils Thermistors - PTC EMI Filters / EMI Suppression Potentiometers, Trimmers &amp; Rheostats Varistors Encoders Resistors Filters Electromechanical Audio Devices I/O Modules Printers Circuit Breakers Industrial Automation Relays Encoders Knobs &amp; Dials Switches Hardware Fans &amp; Blowers Heat Sinks Termoelectric Coller Motors and Drivers Enclosures Enclosures, Boxes, &amp; Cases Racks &amp; Cabinets Standard Electrical LED Lighting &amp; Opto Electronic LED Bulbs &amp; Modules Displays Laser Drivers LED Emitters Optical Switches Fiber Optics LED Indication Optocouplers / Photocouplers Infrared Data Communications Camera Display LED LCD 7 Segment Character &amp; Monocolor LCD Touch Screen Power Supply Addappter Convertor Electric battery &amp; Cells Fuse &amp; Circuit protection Fuse &amp; Protection Thermal Switches Fuse Holders Circuit Breakers &amp; Accessories Resettable-Fuses-PPTC Thermistors Thyristors Varistors ESD Suppressors / TVS Diodes Tools &amp; Supplies Accessories Labels and Industrial Warning Signs Soldering Adhesive Tapes Liquid Dispensers &amp; Bottles Storage Boxes &amp; Cases Anti-Static Control Products Prototyping Products Tools Chemicals Programmer تخفیف ویژه فهرست تخفیفات ویژه سنجش رضایتمندی صفحه اصلی / LED Lighting &amp; Opto Electronic / LED Emitters / LED Emitters / 3MM YELLOW LED LED زرد رنگ 3MM YELLOW LED 3MM YELLOW LED (Light emitting diode) کیفیت: Bulk(فله ایی) پکیج: TH-2 قیمت تک فروشی 6,122 ریال قیمت عمده 5,916 ریال (10 به بالا) قیمت ویژه 5,834 ریال (100 به بالا) قیمت فوق العاده 5,793 ریال (1000 به بالا) قیمت تک فروشی 0.003 تتر با تخفیف 0.01 0.01 0.01 0.01 تعداد موجودی در انبار : 11684 عدد تعدادی از این کالا توسط مشتری رزرو شده است در صورت موجود شدن خبر بده افزودن به علاقه مندی ها تعداد درخواست: مشخصات کالا کالا های مشابه دانلود فایل توضیحات LED زرد 3mm يک ديود ساطع کننده نور (LED) است که نور زرد رنگ توليد مي کند و قطر آن 3 ميلي متر است. در اينجا توضيحات کاملي در مورد اين نوع LED ارائه مي شود: ويژگي هاي کليدي: نوع: ديود ساطع کننده نور (LED) رنگ نور: زرد قطر: 3 ميلي متر جنس: معمولاً از مواد نيمه هادي مانند گاليم آرسنيد فسفيد (GaAsP) ساخته مي شود. ولتاژ کاري: معمولاً بين 1.8 تا 2.2 ولت است. جريان کاري: معمولاً بين 10 تا 20 ميلي آمپر است. زاويه ديد: بسته به نوع LED، زاويه ديد مي تواند متفاوت باشد. نوع لنز: مي تواند شفاف يا مات باشد. کاربردها: نشانگرهاي وضعيت در دستگاه هاي الکترونيکي پنل هاي نمايشگر تزئينات و نورپردازي پروژه هاي الکترونيکي DIY تابلوهاي تبليغاتي مزايا: مصرف انرژي کم طول عمر بالا اندازه کوچک تنوع رنگي قيمت مناسب Description The 3mm Yellow LED is a light-emitting diode (LED) that produces yellow light and is 3 mm in diameter. Here is a complete description of this type of LED: Key Features: Type: Light-emitting diode (LED) Light color: Yellow Diameter: 3 mm Material: Usually made of semiconductor materials such as gallium arsenide phosphide (GaAsP). Working voltage: Usually between 1.8 and 2.2 V. Working current: Usually between 10 and 20 mA. Viewing angle: Depending on the type of LED, the viewing angle can vary. Lens type: Can be clear or opaque. Applications: Status indicators in electronic devices Display panels Decorations and lighting DIY electronic projects Advertising boards Advantages: Low power consumption Long lifespan Small size Color variety Affordable price LED RGB PLCC 6PIN 3806 تک فروشی: 135000 ریال عمده: 118200 ریال اضافه به سبد مشاهده کالا WFGD-CM5R48S-BD تک فروشی: 22800 ریال عمده: 21120 ریال اضافه به سبد مشاهده کالا IN-S63ASR تک فروشی: 267600 ریال عمده: 255000 ریال اضافه به سبد مشاهده کالا SM0603UV-405 تک فروشی: 5305500 ریال عمده: 5053500 ریال اضافه به سبد مشاهده کالا 5MM RED LED تک فروشی: 40920 ریال عمده: 40500 ریال اضافه به سبد مشاهده کالا WS2812B تک فروشی: 198000 ریال عمده: 156000 ریال اضافه به سبد مشاهده کالا PT333-3B تک فروشی: 240000 ریال عمده: 198000 ریال اضافه به سبد مشاهده کالا GREEN LED 0805 تک فروشی: 220800 ریال عمده: 210300 ریال اضافه به سبد مشاهده کالا IR333C/H0/L10 CAT:R , 5MM تک فروشی: 309000 ریال عمده: 267000 ریال اضافه به سبد مشاهده کالا XPGDWT-U1-0000-00EDV تک فروشی: 5304000 ریال عمده: 5052000 ریال اضافه به سبد مشاهده کالا CZ-408SURC02-DXP تک فروشی: 22800 ریال عمده: 21120 ریال اضافه به سبد مشاهده کالا XPGDWT-U1-0000-00EE7 تک فروشی: 6627000 ریال عمده: 6312000 ریال اضافه به سبد مشاهده کالا اسناد و فایل های متنی مدار های چاپی برنامه ها و فایل ها سایت های و ارتباط ها گروه بازرگانی اسکایتک وارد كننده قطعات الکترونیک و نیمه هادی با بیش از پنج سال تجربه افتخار دارد با عرضه محصولات اصلی ، با كیفیت و استاندارد جهت ارج نهادن به سلیقه توزیع كنندگان متعهد در راستای حفاظت از منافع و مصالح مصرف كنندگان نهایی گام بردارد. فروشگاه اسکای تک با حمایت كم نظیر مشتریان خوش نام و فعال به عنوان گروهی پیشرو در ایران ، موفق به اخذ نمایندگی انحصاری و توزیع بسیاری از كمپانی های معتبر جهان  در یك مجموعه گردیده است . استقبال چشمگیر مشتریان صادق و مصرف كنندگان فهیم از خرید قطعات الکترونیک با كیفیت در مقابل قطعات نامرغوب و غیر استاندارد وارداتی، موجب گردآوری طیف وسیعی (بالغ بر 40000 قلم كالا)‌ از قطعات الکترونیک گوناگون دراین فروشگاه شده است. قوانین ارتباط با فروشگاه ارتباط با واحد فروش ارتباط با واحد پشتیبانی فنی انتقادات و پیشنهادات قوانین و شرایط سایت دسترسی های سایت نقشه سایت درباره ما سوالات متداول شماره حساب ها لینک های ما آپارات فروشگاه اسکایتک کلیه حقوق این سایت متعلق به فروشگاه Skytech می باشد</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1359,10 +1348,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="3" t="n">
         <v>6122</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" s="3" t="n">
         <v>6122</v>
       </c>
     </row>
@@ -1373,14 +1362,14 @@
       <c r="B28" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>https://bahar-enclosure.ir/product/bwp-10201-a2-%d8%ac%d8%b9%d8%a8%d9%87-%d8%b6%d8%af-%d8%a2%d8%a8-%d9%82%d8%a7%d8%a8%d9%84-%d9%86%d8%b5%d8%a8-%d8%b1%d9%88%d9%8a-%d8%af%d9%8a%d9%88%d8%a7%d8%b1-%d9%88-%d9%84%d9%88%d9%84%d9%87/</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>BWP 10201-A2 جعبه ضد آب قابل نصب روي ديوار و لوله - مجتمع بهار پرش به محتوا جستجوی پیشرفته قوانین و مقررات گالری تصاویر جستجوی پیشرفته قوانین و مقررات گالری تصاویر 13 مرداد 1405 18:03 ورود / ثبت نام جستجو ... فروشگاه BAD SERIES BAD – A BDA SERIES BDA – A BDA – B BDA – C BDA – D BDC SERIES BDC – 300 BDH SERIES BDH – 200 BEC SERIES BEC – BLUEBERRY BEC – WONDERFUL BMC SERIES BMC – A BMC – B BMC – C BMD SERIES BMD – A BMD – B BMD – C BMD – D BMW SERIES BMW – A BMW – B BMW – C BRT SERIES BRT – A BRT – B BRT – C BWA SERIES BWA BWP SERIES BWP – 100 BWP – 102 BWP – 103 BWP – 105 BWP – 106 BWP – 108 OTHERS GOODS ENCLOSURES HOLDER KNOBS PANEL بدون دسته‌ بندی پلاستیکی رومیزی پلاستیکی ضد آب جعبه های آلومینیوم با پانل پلاستیکی جعبه های آهنی با پانل آلومینیوم جعبه های آهنی با پانل پلاستیکی جعبه های تمام فلزی (آهنی) جعبه های دیواری جعبه های رک مونت استاندارد 19 اینچ جعبه های ریلی جعبه های قابل حمل کیس های قابل حمل محصولات محصولات فروش ویژه محصولات گوناگون ( متعلقات ) محصولات ویژه نتایج مشاهده همه نتایج صفحه اصلی درباره ما محصولات بستن محصولات باز کردن محصولات جعبه پلاستیکی رومیزی جعبه پلاستیکی ضد آب جعبه قابل نصب(دیواری) جعبه قابل حمل دستی جعبه صنعتی (ریلی) کیس قابل حمل(ضد ضربه) جعبه آهنی با پانل پلاستیکی جعبه تمام فلزی(آهنی) جعبه آهنی با پانل آلومینیوم جعبه آلومینیوم با پانل پلاستیکی جعبه رک مونت استاندارد 19اینچ محصولات گوناگون(متعلقات) BAD – A/B Series BRT – A / B / C Series BDH – A Series BDC – A Series BWA – A Series BEC A/B Series BWP – 100 / 102 / 105 / 106 / 108 Series BMW – A / B / C Series BMD – A / B / C Series BMC – A / B / C Series BDA – A / B / C / D Series Others – A / B / C / D Series خدمات دانلودها تماس با ما کاتالوگ دیجیتال Home / BWP SERIES / BWP - 102 / BWP 10201-A2 جعبه ضد آب قابل نصب روي ديوار و لوله      5/5 BWP 10201-A2 جعبه ضد آب قابل نصب روي ديوار و لوله نام کالا BWP 10201-A2 جعبه ضد آب قابل نصب روي ديوار و لوله کد کالا BWP 10201-A2 مواد تشکیل دهنده ABS وزن کالا 200 g کلاس حفاظتی IP68 ابعاد mm 47 x68x 86 :size تاییدیه بین المللی RoHS , IP68 , SGS , ABS 1,204,000 تومان 22 در انبار BWP 10201-A2 جعبه ضد آب قابل نصب روي ديوار و لوله عدد افزودن به سبد خرید دانلود فایل ها تضمین کیفیت تمامی محصولات ارائه شده توسط این مجتمع دارای بالاترین استانداردهای جهانی می باشد. در صورت هر گونه مشکل، با کمال میل پاسخگوی شما خواهیم بود . قیمت مناسب و رقابتی عرضه محصولات با کیفیت از این تنوع کالایی وسیع،هزینه های تولید شما به حداقل خواهد رساند وهمواره می کوشیم تا با پایین ترین هزینه،بالاترین خدمات را به شما عرضه کنیم . پشتیبانی بعد از خرید ما آماده پاسخگویی هرگونه نیاز شما در این مسیر می باشیم و کادر مجرب ما شما را تا به دست آوردن نتیجه مطلوب همراهی خواهد کرد . توضیحات تکمیلی محصول این گروه از جعبه های ضدآب جزو منحصر به فرد ترین تولیدات این مجموعه بوده که تا به حال حاضر تولید و خدمت شما تولید کنندگان عزیز عرضه گردیده . محصول ارائه شده ، نمایشی از قدرت فن آوری – دقت و ارزش ها می باشد که در وجه تمایز این مجموعه با رقبای کشورهایی نظیر آلمان . ژاپن . کره و تایوان بوده که با نام تجاری بهار تولید و خدمت شما دوستان عزیز عرضه می گردد . این سری از محصولات که به کوچک ترین نکات در تولید ، بسته بندی و عرضه آن توجه شده در دو سری 102 (طلایی – کامل ترین و حرفه ای ترین ) و سری 103 ( نقره ای – زیبایی به همراه قیمت اقتصادی ) تولید و عرضه می گردد . فرم کلی و سایز تمامی محصولات این دو گروه دقیقا یکی بوده و تغییرات زیر دلیل اختلاف قیمت در عرضه این محصولات می باشد . حذف مهره برنجی داخل جعبه باتوجه به هزینه این قطعه فلزی و زمان بر بودن نصب این قطعه در قالب هنگام تزریق در سری طلایی تزریق به صورت دستی توسط اپراتور دستگاه بوده درصورتی که در سری نقره ای تزریق رباتیک بدون دخالت اپراتور و کامل به صورت اتوماتیک انجام میگیرد که باعث کاهش هزینه تولید آن میشود . تفاوت در نوع پیچ جعبه ها سری طلایی پیچ ها به صورت دنده مهره ای بوده با سری مخصوص هزارخار ودر سری نقره ای پیچ خودکار سفارشی واشر ضد آب محصول در سری طلایی واشر ضدآب سیلیکونی تزریق قالبی و در سری نقره ای واشر ماکارونی جوش خورده می باشد . متعلقات همراه محصول سری طلایی کامل ترین گروه از این جعبه ها بوده در صورتی که در مدل نقره ای بعضی از موارد حذف گردیده . بسته بندی محصول سری طلایی با بسته بندی کارتن ارائه میشود و در مدل نقره ای با نایلون و بدون کارتن بسته بندی تفکیکی . تنوع رنگ بندی محصول سری طلایی در سینزده تنوع رنگی عرضه می گردد و در سری نقره ای تنها در دو رنگ سفید و مشکی عرضه میشود . صفحه مشبک پلاستیکی در سری طلایی داخل جعبه ها صفحه مشبکی قرار میگیرد که می توان قطعات گوناگون روی آن نصب کرد . روکش سلفنی ضدخش در سری طلایی تمامی طرف های بدنه با فویل سلفنی محافظت میشود در سری نقره ای فقط روی درب محصول. محل تزریق در کف جعبه در سری طلایی محل تزریق با دستگاه CNC برداشته میشود- در نسخه نقره ای به صورت دستی قیچی میشود . محصولات مرتبط محصولات دیگر در این دسته ITEM NO: BWP 10201-A85 جعبه ضد آب قابل نصب روي ديوار و لوله mm 15 x68x 86 :size :size ITEM NO: BWP 10201-A48 جعبه ضد آب قابل نصب روي ديوار و لوله mm 15 x68x 86 :size :size ITEM NO: BWP 10201-A27 جعبه ضد آب قابل نصب روي ديوار و لوله mm 47 x68x 86 :size :size ITEM NO: BWP 10201-A25 باکس بهار mm 47 x68x 86 :size :size ITEM NO: BWP 10201-A8 جعبه ضد آب قابل نصب روي ديوار و لوله mm 47 x68x 86 :size :size ITEM NO: BWP 10201-A7 جعبه ضد آب mm 47 x68x 86 :size :size ITEM NO: BWP 10201-A6 جعبه بهار mm 47 x68x 86 :size :size ITEM NO: BWP 10201-A5 جعبه ضد آب قابل نصب روي ديوار و لوله mm 47 x68x 86 :size :size دسترسی سریع صفحه اصلی محصولات خدمات دانلود ها گالری تصویر تماس با ما کاتالوگ دیجیتال صفحه اصلی محصولات خدمات دانلود ها گالری تصویر تماس با ما کاتالوگ دیجیتال حساب کاربری ورود يا ایجاد حساب کاربری پیگیری سفارش ثبت خطا در سایت ورود يا ایجاد حساب کاربری پیگیری سفارش ثبت خطا در سایت مجتمع بهار تولید کننده  انواع جعبه های پلاستیکی و فلزی ما توانسته ایم بخش عمده ای از نیاز های تولیدات شما را بر آورده کرده و هم اکنون بزرگترین عرضه کننده انواع جعبه های فلزی و پلاستیکی درزمینه های مختلفی همچون الکترونیک - برق - مخابرات و پزشکی و انواع پروژه های الکترونیکی در ایران و سایر کشور های پیشرفته جهان باشیم. ارسال پیام به پشتیبانی آنلاین واتساپ درخواست مشاوره کارشناسان در کوتاه ترین زمان با شما تماس خواهند گرفت " * " indicates required fields نام * شماره موبایل * نوع درخواست درود، لطفا با بنده تماس حاصل نمایید. درود، چگونه می توان با شما تماس حاصل نماییم؟ درود، لطفا اطلاعات ساعت کاری خود را اعلام فرمایید. درود، لطفا جهت سفارش آنلاین بنده را راهنمایی کنید. درود، برای سفارش پانچ کاری روی محصولات چگونه اقدام کنیم؟ توضیحات تمامی حقوق سایت برای مجتمع بهار محفوظ می باشد طراحی و توسعه توسط خانه کاتالوگ دیجیتال داچه صفحه اصلی قوانین و مقررات ورود / ثبت نام استفاده از شماره تلفن Use آدرس ایمیل ادامه تصویر امنیتی * تصویر امنیتی را وارد کنید: بازیابی رمز عبور استفاده از شماره تلفن Use آدرس ایمیل ادامه دسترسی آسان به سایت صفحه اصلی درباره ما محصولات خدمات دانلود ها تماس با ما کاتالوگ دیجیتال جستجوی پیشرفته در بین محصولات بخشی از اسم محصول یا اسم کامل محصول را وارد کنید.</t>
+          <t>BWP 10201-A2 جعبه ضد آب قابل نصب روي ديوار و لوله - مجتمع بهار پرش به محتوا جستجوی پیشرفته قوانین و مقررات گالری تصاویر جستجوی پیشرفته قوانین و مقررات گالری تصاویر 13 مرداد 1405 23:56 ورود / ثبت نام جستجو ... فروشگاه BAD SERIES BAD – A BDA SERIES BDA – A BDA – B BDA – C BDA – D BDC SERIES BDC – 300 BDH SERIES BDH – 200 BEC SERIES BEC – BLUEBERRY BEC – WONDERFUL BMC SERIES BMC – A BMC – B BMC – C BMD SERIES BMD – A BMD – B BMD – C BMD – D BMW SERIES BMW – A BMW – B BMW – C BRT SERIES BRT – A BRT – B BRT – C BWA SERIES BWA BWP SERIES BWP – 100 BWP – 102 BWP – 103 BWP – 105 BWP – 106 BWP – 108 OTHERS GOODS ENCLOSURES HOLDER KNOBS PANEL بدون دسته‌ بندی پلاستیکی رومیزی پلاستیکی ضد آب جعبه های آلومینیوم با پانل پلاستیکی جعبه های آهنی با پانل آلومینیوم جعبه های آهنی با پانل پلاستیکی جعبه های تمام فلزی (آهنی) جعبه های دیواری جعبه های رک مونت استاندارد 19 اینچ جعبه های ریلی جعبه های قابل حمل کیس های قابل حمل محصولات محصولات فروش ویژه محصولات گوناگون ( متعلقات ) محصولات ویژه نتایج مشاهده همه نتایج صفحه اصلی درباره ما محصولات بستن محصولات باز کردن محصولات جعبه پلاستیکی رومیزی جعبه پلاستیکی ضد آب جعبه قابل نصب(دیواری) جعبه قابل حمل دستی جعبه صنعتی (ریلی) کیس قابل حمل(ضد ضربه) جعبه آهنی با پانل پلاستیکی جعبه تمام فلزی(آهنی) جعبه آهنی با پانل آلومینیوم جعبه آلومینیوم با پانل پلاستیکی جعبه رک مونت استاندارد 19اینچ محصولات گوناگون(متعلقات) BAD – A/B Series BRT – A / B / C Series BDH – A Series BDC – A Series BWA – A Series BEC A/B Series BWP – 100 / 102 / 105 / 106 / 108 Series BMW – A / B / C Series BMD – A / B / C Series BMC – A / B / C Series BDA – A / B / C / D Series Others – A / B / C / D Series خدمات دانلودها تماس با ما کاتالوگ دیجیتال Home / BWP SERIES / BWP - 102 / BWP 10201-A2 جعبه ضد آب قابل نصب روي ديوار و لوله      5/5 BWP 10201-A2 جعبه ضد آب قابل نصب روي ديوار و لوله نام کالا BWP 10201-A2 جعبه ضد آب قابل نصب روي ديوار و لوله کد کالا BWP 10201-A2 مواد تشکیل دهنده ABS وزن کالا 200 g کلاس حفاظتی IP68 ابعاد mm 47 x68x 86 :size تاییدیه بین المللی RoHS , IP68 , SGS , ABS 1,204,000 تومان 22 در انبار BWP 10201-A2 جعبه ضد آب قابل نصب روي ديوار و لوله عدد افزودن به سبد خرید دانلود فایل ها تضمین کیفیت تمامی محصولات ارائه شده توسط این مجتمع دارای بالاترین استانداردهای جهانی می باشد. در صورت هر گونه مشکل، با کمال میل پاسخگوی شما خواهیم بود . قیمت مناسب و رقابتی عرضه محصولات با کیفیت از این تنوع کالایی وسیع،هزینه های تولید شما به حداقل خواهد رساند وهمواره می کوشیم تا با پایین ترین هزینه،بالاترین خدمات را به شما عرضه کنیم . پشتیبانی بعد از خرید ما آماده پاسخگویی هرگونه نیاز شما در این مسیر می باشیم و کادر مجرب ما شما را تا به دست آوردن نتیجه مطلوب همراهی خواهد کرد . توضیحات تکمیلی محصول این گروه از جعبه های ضدآب جزو منحصر به فرد ترین تولیدات این مجموعه بوده که تا به حال حاضر تولید و خدمت شما تولید کنندگان عزیز عرضه گردیده . محصول ارائه شده ، نمایشی از قدرت فن آوری – دقت و ارزش ها می باشد که در وجه تمایز این مجموعه با رقبای کشورهایی نظیر آلمان . ژاپن . کره و تایوان بوده که با نام تجاری بهار تولید و خدمت شما دوستان عزیز عرضه می گردد . این سری از محصولات که به کوچک ترین نکات در تولید ، بسته بندی و عرضه آن توجه شده در دو سری 102 (طلایی – کامل ترین و حرفه ای ترین ) و سری 103 ( نقره ای – زیبایی به همراه قیمت اقتصادی ) تولید و عرضه می گردد . فرم کلی و سایز تمامی محصولات این دو گروه دقیقا یکی بوده و تغییرات زیر دلیل اختلاف قیمت در عرضه این محصولات می باشد . حذف مهره برنجی داخل جعبه باتوجه به هزینه این قطعه فلزی و زمان بر بودن نصب این قطعه در قالب هنگام تزریق در سری طلایی تزریق به صورت دستی توسط اپراتور دستگاه بوده درصورتی که در سری نقره ای تزریق رباتیک بدون دخالت اپراتور و کامل به صورت اتوماتیک انجام میگیرد که باعث کاهش هزینه تولید آن میشود . تفاوت در نوع پیچ جعبه ها سری طلایی پیچ ها به صورت دنده مهره ای بوده با سری مخصوص هزارخار ودر سری نقره ای پیچ خودکار سفارشی واشر ضد آب محصول در سری طلایی واشر ضدآب سیلیکونی تزریق قالبی و در سری نقره ای واشر ماکارونی جوش خورده می باشد . متعلقات همراه محصول سری طلایی کامل ترین گروه از این جعبه ها بوده در صورتی که در مدل نقره ای بعضی از موارد حذف گردیده . بسته بندی محصول سری طلایی با بسته بندی کارتن ارائه میشود و در مدل نقره ای با نایلون و بدون کارتن بسته بندی تفکیکی . تنوع رنگ بندی محصول سری طلایی در سینزده تنوع رنگی عرضه می گردد و در سری نقره ای تنها در دو رنگ سفید و مشکی عرضه میشود . صفحه مشبک پلاستیکی در سری طلایی داخل جعبه ها صفحه مشبکی قرار میگیرد که می توان قطعات گوناگون روی آن نصب کرد . روکش سلفنی ضدخش در سری طلایی تمامی طرف های بدنه با فویل سلفنی محافظت میشود در سری نقره ای فقط روی درب محصول. محل تزریق در کف جعبه در سری طلایی محل تزریق با دستگاه CNC برداشته میشود- در نسخه نقره ای به صورت دستی قیچی میشود . محصولات مرتبط محصولات دیگر در این دسته ITEM NO: BWP 10201-A85 جعبه ضد آب قابل نصب روي ديوار و لوله mm 15 x68x 86 :size :size ITEM NO: BWP 10201-A48 جعبه ضد آب قابل نصب روي ديوار و لوله mm 15 x68x 86 :size :size ITEM NO: BWP 10201-A27 جعبه ضد آب قابل نصب روي ديوار و لوله mm 47 x68x 86 :size :size ITEM NO: BWP 10201-A25 باکس بهار mm 47 x68x 86 :size :size ITEM NO: BWP 10201-A8 جعبه ضد آب قابل نصب روي ديوار و لوله mm 47 x68x 86 :size :size ITEM NO: BWP 10201-A7 جعبه ضد آب mm 47 x68x 86 :size :size ITEM NO: BWP 10201-A6 جعبه بهار mm 47 x68x 86 :size :size ITEM NO: BWP 10201-A5 جعبه ضد آب قابل نصب روي ديوار و لوله mm 47 x68x 86 :size :size دسترسی سریع صفحه اصلی محصولات خدمات دانلود ها گالری تصویر تماس با ما کاتالوگ دیجیتال صفحه اصلی محصولات خدمات دانلود ها گالری تصویر تماس با ما کاتالوگ دیجیتال حساب کاربری ورود يا ایجاد حساب کاربری پیگیری سفارش ثبت خطا در سایت ورود يا ایجاد حساب کاربری پیگیری سفارش ثبت خطا در سایت مجتمع بهار تولید کننده  انواع جعبه های پلاستیکی و فلزی ما توانسته ایم بخش عمده ای از نیاز های تولیدات شما را بر آورده کرده و هم اکنون بزرگترین عرضه کننده انواع جعبه های فلزی و پلاستیکی درزمینه های مختلفی همچون الکترونیک - برق - مخابرات و پزشکی و انواع پروژه های الکترونیکی در ایران و سایر کشور های پیشرفته جهان باشیم. ارسال پیام به پشتیبانی آنلاین واتساپ درخواست مشاوره کارشناسان در کوتاه ترین زمان با شما تماس خواهند گرفت " * " indicates required fields نام * شماره موبایل * نوع درخواست درود، لطفا با بنده تماس حاصل نمایید. درود، چگونه می توان با شما تماس حاصل نماییم؟ درود، لطفا اطلاعات ساعت کاری خود را اعلام فرمایید. درود، لطفا جهت سفارش آنلاین بنده را راهنمایی کنید. درود، برای سفارش پانچ کاری روی محصولات چگونه اقدام کنیم؟ توضیحات تمامی حقوق سایت برای مجتمع بهار محفوظ می باشد طراحی و توسعه توسط خانه کاتالوگ دیجیتال داچه صفحه اصلی قوانین و مقررات ورود / ثبت نام استفاده از شماره تلفن Use آدرس ایمیل ادامه تصویر امنیتی * تصویر امنیتی را وارد کنید: بازیابی رمز عبور استفاده از شماره تلفن Use آدرس ایمیل ادامه دسترسی آسان به سایت صفحه اصلی درباره ما محصولات خدمات دانلود ها تماس با ما کاتالوگ دیجیتال جستجوی پیشرفته در بین محصولات بخشی از اسم محصول یا اسم کامل محصول را وارد کنید.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1388,10 +1377,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="3" t="n">
         <v>12040000</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" s="3" t="n">
         <v>12040000</v>
       </c>
     </row>
@@ -1417,10 +1406,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="3" t="n">
         <v>2535000</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" s="3" t="n">
         <v>2535000</v>
       </c>
     </row>
@@ -1431,7 +1420,7 @@
       <c r="B30" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>https://www.alphakit.ir/product/%d8%a7%d9%84-%d8%a7%db%8c-%d8%af%db%8c-50-%d9%88%d8%a7%d8%aa-12-24-%d9%88%d9%84%d8%aa-cob-%d9%85%d9%87%d8%aa%d8%a7%d8%a8%db%8c-%da%a9%d9%84%db%8c%d8%af%d8%af%d8%a7%d8%b1/</t>
         </is>
@@ -1440,7 +1429,7 @@
         <is>
           <t>ال ای دی پروژکتوری 50 وات 12-24 ولت COB سفید مهتابی کلیددار بدون نیاز به هیت سینک – آلفاکیت – فروشگاه تخصصی الکترونیک 0 سبد خرید شما در حال حاضر خالی است. بازگشت به فروشگاه ورود / ثبت نام دسته‌بندی کالاها ال ای دی و تجهیزات نورپردازی ال ای دی پروژکتور ال ای دی COB لامپ ال ای دی ال ای دی SMD پروژکتور ال ای دی ال ای دی رشد گیاه ال ای دی هدلایت ال ای دی هدلایت COB ال ای دی هدلایت CSP لامپ هدلایت درایور هدلایت آنتی هدلایت مزاحم گیر ال ای دی دیلایت ال ای دی خودرویی (12 ولت) چراغ قوه و چراغ شارژی چراغ قوه و چراغ شارژی چراغ پیشانی باتری لیتیوم یون ال ای دی براکتی ال ای دی پاور ال ای دی هالوژنی هیت سینک بدنه لامپ و پروژکتور ال ای دی نواری تابلو ال ای دی ال ای دی مات ال ای دی لیزری فلاشر ال ای دی درایور ال ای دی پاور لنز ال ای دی خمیر و چسب سیلیکون انواع سیم و کابل ماژول های کاربردی ماژول GPRS-GSM-GPS ماژول های نمایشگر ماژول دوربین ماژول تگ RFID آنتن و تگ RFID ماژول RFID ریموت و ماژول های RF ماژول ISM BAND ماژول های کاربردی ماژول درایور موتور ماژول آلتراسونیک ZIGBEE ماژول های شتاب سنج و ژیروسکوپ ماژول شبکه و WIFI مبدل و واسته ماژول فشار ماژول تغذیه، ولتاژ، جریان ماژول بلوتوث ماژول های صوتی ماژول بخار سرد ماژول اثر انگشت ماژول دما و رطوبت ماژول گاز ماژول های پزشکی ماژول حرکت و لرزش ماژول های رله ماژول های تایمر و پالس تجهیزات اندازه گیری و مونتاژ مونتاژ و لحیم کاری انواع هویه نوک هویه گیره مونتاژ و پایه هویه سیم لحیم قلع کش خمیر و چسب سیلیکون روغن و فلاکس لحیم کاری سایر لوازم مونتاژ لوازم اندازه گیری دما و رطوبت سنج ذره بین و میکروسکوپ مته و ابزار برش کاری اسپری ها کیس و جعبه جعبه قطعات و ابزار ابزار و لوازم الکترونیکی پیچگوشتی آچار سوکت زن و پرسی سشوار و چسپ حرارتی انبر دست ودم باریک پنس و کاتر سیم چین و کف چین انواع سوهان سایر ابزار الکترونیک قطعات الکترونیکی ترانزیستورها ماسفت سایر ترانزیستور ها IGBT رگولاتور ها رله ها انواع ترایاک و تریستور پین هدر ها انواع سوکت، کانکتور، فیش کانکتور مخابراتی کانکتور کامپیوتری کانکتور USB جک اسپیکر و میکروفن سوکت IC معمولی سوکت IC نظامی باکس هدر – IDC ZIF سوکت فیش و جک آداپتور ترمینال کانکتور فیش شبکه وتلفن سایر سوکت ها انواع سیم و کابل سیم و کابل فرمان کابل و گیره سوسماری وارنیش حرارتی انواع کلید، سوئیچ کلید کلنگی و کشویی تک سوئیچ دیپ سوئیچ کیپد و صفحه کلید میکروسوئیچ کلید راکر شستی انواع فیوزها فیوز شیشه ای بازر BUZZER انواع سوئیچینگ و آداپتور آداپتور ها پاور سوئیچینگ باتری و تجهیزات باتری قلمی و نیم قلمی باتری سکه ای باتری کتابی باتری خشک باتری لیتیوم یون باتری لیتیوم پلیمر جا باتری و سر باتری شارژر ها باتری ریموتی لیزر ها فیبر مدار چاپی انواع اسپیسر برد برد bread board انواع فن و هیت سینک فن هیت سینک المان سرد کننده ریموت کنترلرها سگمنت و ماتریس دات ماتریس سون سگمنت انواع سنسور سنسور دما و رطوبت سنسور IR سنسور گاز سنسور رنگ سنسور ولنز PIR سنسور جریان سنسور وزن ،نیرو،فشار سایر سنسور ها رباتیک اتصالات پلاستیکی بدنه ربات چرخ ربات انواع موتور موتور DC موتور براشلس موتور گیربکس استپ موتور سروو موتور ملخ ربات دسته کنترل فلایت کنترل ربات پیش ساخته دکوراتیو ساعت رومیزی برچسب‌های ویژه ال ای دی CREE ال ای دی هدلایت آنتی هدلایت مزاحم گیر ال ای دی 12 ولت ال ای دی 24 ولت ال ای دی 32 ولت پروژکتور ال ای دی چراغ پیشانی ریسه نئون فلکسی اینورتر خودرو مولتی متر دوربین (آندوسکوپ) سیم لحیم اکتیویتی سیم لحیم بهینکس فندک فروش عمده صفحه اصلی فروشگاه محصولات تخفیف‌‌دار راهنمای خرید مقالات درباره آلفاکیت تماس با آلفاکیت 0 سبد خرید شما در حال حاضر خالی است. بازگشت به فروشگاه پیگیری سفارشات ال ای دی پروژکتوری 50 وات 12-24 ولت COB سفید مهتابی کلیددار بدون نیاز به هیت سینک خانه ال ای دی و تجهیزات نورپردازی ال ای دی پروژکتور ال ای دی پروژکتوری 50 وات 12-24 ولت COB سفید مهتابی کلیددار بدون نیاز به هیت سینک 25% مقایسه محصول ال ای دی پروژکتوری 50 وات 12-24 ولت COB سفید مهتابی کلیددار بدون نیاز به هیت سینک 590,000 تومان قیمت اصلی: 590,000 تومان بود. 440,000 تومان قیمت فعلی: 440,000 تومان. تخفیف
                 : 150,000 تومان افزودن به سبد خرید (  آخرین بروزرسانی : 4 مرداد, 1405 ) ویژگی های کلیدی محصول توان: 50 وات ولتاژ ورودی: 12-24 ولت رنگ: سفید مهتابی ابعاد: 150x60 میلیمتر میزان روشنایی: 5000 لومن دسته بندی : ال ای دی COB , ال ای دی پروژکتور , محصولات تخفیف دار برچسب ها ال ای دی 12 ولت , ال ای دی 24 ولت بررسی اجمالی محصول چیپ ال ای دی پروژکتوری 50 وات 12-24 ولت COB سفید مهتابی کلیددار بدون نیاز به هیت سینک قابل نصب به باتری خودرو سواری، کامیون و تریلی بدون هیچ درایوری نقاط
-                قوت نقاط ضعف بدون نیاز به هیت سینک دارای کلید هزینه ارسال سفارش‌های کل سبد‌خرید: 165 هزار‌تومان با پست پیشتاز (بجز دسته “بدنه لامپ و پروژکتور”) توضیحات توضیحات تکمیلی نظرات (0) نقد و بررسی : ال ای دی پروژکتوری 50 وات 12-24 ولت COB سفید مهتابی کلیددار بدون نیاز به هیت سینک مشخصات: توان: 50 وات ولتاژ ورودی: 12-24 ولت جریان مصرفی: 3500 میلی آمپر رنگ: سفید مهتابی دمای رنگ: 6000 کلوین جنس پی سی بی: آلومینیوم ابعاد: 150×60 میلیمتر سایز فسفرک: 110×53 میلیمتر میزان روشنایی: 5000 لومن قابل استفاده برای ساخت پروژکتور کمپینگ – قابل استفاده با باتری خودرو – ساخت پروژکتور قابل نصب به سیستم‌های خورشیدی بدون نیاز به هیت سینک دارای کلید اقلام همراه محصول: چیپ ال ای دی، برچسب و پیچ های محصول نکته: این محصول هم با ولتاژ 12 ولت و هم با ولتاژ 24 ولت کار می‌کند. نکته: این LED بدون هیچ درایوری قابل نصب به باتری خودرو سواری، کامیون و تریلی می‌باشد. مشخصات فنی : توان 50 وات ولتاژ 12 ولت, 24 ولت رنگ سفید مهتابی دیدگاه دیدگاهی ثبت نشده. اولین نفری باشید که نظر می دهید برای “ال ای دی پروژکتوری 50 وات 12-24 ولت COB سفید مهتابی کلیددار بدون نیاز به هیت سینک” لغو پاسخ برای نوشتن دیدگاه باید وارد بشوید . محصولات مرتبط ال ای دی پاور 5 وات سفید مهتابی 8 ولت 700 میلی آمپر 180,000 تومان افزودن به سبد خرید LED COB مهتابی 100W 220V با درایور داخلی – LY.105X100 نمره 3.67 از 5 745,000 تومان افزودن به سبد خرید ال ای دی COB بلوکی 2.4 وات 12 ولت صورتی نمره 5.00 از 5 31,000 تومان افزودن به سبد خرید ال ای دی 50 وات 220 ولت COB سفید مهتابی مدل Groundwire نمره 3.50 از 5 330,000 تومان افزودن به سبد خرید ال ای دی پاور 50 وات سفید مهتابی 32 ولت 1500 میلی آمپر 85,000 تومان افزودن به سبد خرید 24% ال ای دی 3 وات 300 میلی آمپر سفید مهتابی مدل 2B3C 55,000 تومان قیمت اصلی: 55,000 تومان بود. 42,000 تومان قیمت فعلی: 42,000 تومان. افزودن به سبد خرید 28% ال ای دی 50 وات 220 ولت COB سفید مهتابی برند LY 265,000 تومان قیمت اصلی: 265,000 تومان بود. 190,000 تومان قیمت فعلی: 190,000 تومان. افزودن به سبد خرید ال ای دی COB نور طبیعی 50 وات 220 ولت با درایور داخلی 385,000 تومان افزودن به سبد خرید ال ای دی COB پنلی 30 وات 900 میلی آمپر سفید مهتابی مدل XY-2828 130,000 تومان افزودن به سبد خرید ال ای دی COB پنلی 30 وات 900 میلی آمپر سفید مهتابی مدل XF-1919 109,000 تومان افزودن به سبد خرید ال ای دی COB بلوکی 2.4 وات 12 ولت سبز 31,000 تومان افزودن به سبد خرید ال ای دی COB پنلی 30 وات 900 میلی آمپر سفید آفتابی مدل XF-1919 145,000 تومان افزودن به سبد خرید سبدخرید فروشگاه تماس با آلفاکیت پیگیری سفارشات ارتباط با ما 0914 9234219 041 35570539 alphakit alphakit.ir alphakit alphakit_ir خدمات مشتریان قوانین و مقررات شرایط بازگرداندن کالا حریم خصوصی راهنمای خرید کالا شماره حساب‌ها پیگیری سفارشات ثبت شکایات دسترسی سریع ثبت‌نام / ورود حساب کاربری محصولات تخفیف‌‌دار فروش عمده مقالات درباره آلفاکیت تماس با آلفاکیت آلفاکیت – فروشگاه تخصصی الکترونیک آلفاکیت مرجع تخصصی فروش چیپ لامپ و پروژکتور ال‌ای‌دی، هدلایت خودرو‌، تجهیزات نورپردازی، ماژول، ابزارآلات و تجهیزات الکترونیکی آدرس: آذربایجان شرقی، تبریز، خیابان محققی، روبروی پاساژ امت، به طرف باغ گلستان، جنب کوچه دکتر نوایی، جنب عطاری امام رضا، ساختمان پناهی، طبقه یک، سمت راست، واحد هفت تمامی حقوق این سایت متعلق به فروشگاه آلفاکیت است و تحت قوانین جمهوری اسلامی ایران فعالیت می‌کند. ورود با شماره موبایل با آدرس ایمیل ادامه دهید آیا هنوز عضو نشده‌اید؟ ثبت‌نام کنید ثبت‌نام نام کاربری * شماره تلفن رمزعبور * ادامه دهید قبلا عضو شده‌اید؟ ورود ارسال به ایمیل به من اطلاع بده با پر کردن فرم زیر هر زمان که این محصول موجود شد از طریق ایمیل یا ارسال پیامک به شما اطلاع رسانی خواهد شد. از طریق: ایمیل به بازگشت ثبت</t>
+                قوت نقاط ضعف بدون نیاز به هیت سینک دارای کلید هزینه ارسال سفارش‌های کل سبد‌خرید: 165 هزار‌تومان با پست پیشتاز (بجز دسته “بدنه لامپ و پروژکتور”) توضیحات توضیحات تکمیلی نظرات (0) نقد و بررسی : ال ای دی پروژکتوری 50 وات 12-24 ولت COB سفید مهتابی کلیددار بدون نیاز به هیت سینک مشخصات: توان: 50 وات ولتاژ ورودی: 12-24 ولت جریان مصرفی: 3500 میلی آمپر رنگ: سفید مهتابی دمای رنگ: 6000 کلوین جنس پی سی بی: آلومینیوم ابعاد: 150×60 میلیمتر سایز فسفرک: 110×53 میلیمتر میزان روشنایی: 5000 لومن قابل استفاده برای ساخت پروژکتور کمپینگ – قابل استفاده با باتری خودرو – ساخت پروژکتور قابل نصب به سیستم‌های خورشیدی بدون نیاز به هیت سینک دارای کلید اقلام همراه محصول: چیپ ال ای دی، برچسب و پیچ های محصول نکته: این محصول هم با ولتاژ 12 ولت و هم با ولتاژ 24 ولت کار می‌کند. نکته: این LED بدون هیچ درایوری قابل نصب به باتری خودرو سواری، کامیون و تریلی می‌باشد. مشخصات فنی : توان 50 وات ولتاژ 12 ولت, 24 ولت رنگ سفید مهتابی دیدگاه دیدگاهی ثبت نشده. اولین نفری باشید که نظر می دهید برای “ال ای دی پروژکتوری 50 وات 12-24 ولت COB سفید مهتابی کلیددار بدون نیاز به هیت سینک” لغو پاسخ برای نوشتن دیدگاه باید وارد بشوید . محصولات مرتبط ال ای دی پاور 50 وات سفید مهتابی 32 ولت 1500 میلی آمپر 85,000 تومان افزودن به سبد خرید ال ای دی 30 وات 220 ولت COB سفید مهتابی 74X63 میلیمتر 315,000 تومان افزودن به سبد خرید ال ای دی 50 وات 220 ولت COB سفید آفتابی برند LY 219,000 تومان افزودن به سبد خرید 28% ال ای دی 50 وات 220 ولت COB سفید مهتابی برند LY 265,000 تومان قیمت اصلی: 265,000 تومان بود. 190,000 تومان قیمت فعلی: 190,000 تومان. افزودن به سبد خرید ال ای دی COB پروژکتوری 50 وات 12 ولت سفید مهتابی نمره 5.00 از 5 285,000 تومان افزودن به سبد خرید LED COB مهتابی 50W 220V با درایور داخلی – 6147F نمره 5.00 از 5 265,000 تومان افزودن به سبد خرید ال ای دی COB بلوکی 2.4 وات 12 ولت صورتی نمره 5.00 از 5 31,000 تومان افزودن به سبد خرید ال ای دی COB پنلی 6 وات 300 میلی آمپر دو رنگ برند LY 49,000 تومان افزودن به سبد خرید LED COB گرد 5W آفتابی 110,000 تومان افزودن به سبد خرید ال ای دی 35 وات 220 ولت COB سفید مهتابی برند LY 179,000 تومان افزودن به سبد خرید ال ای دی COB پروژکتوری 50 وات 12 ولت سفید آفتابی مدل 4C30B نمره 3.33 از 5 300,000 تومان افزودن به سبد خرید ال ای دی COB آفتابی 30W 220V با درایور داخلی 74X63 میلیمتر 270,000 تومان افزودن به سبد خرید سبدخرید فروشگاه تماس با آلفاکیت پیگیری سفارشات ارتباط با ما 0914 9234219 041 35570539 alphakit alphakit.ir alphakit alphakit_ir خدمات مشتریان قوانین و مقررات شرایط بازگرداندن کالا حریم خصوصی راهنمای خرید کالا شماره حساب‌ها پیگیری سفارشات ثبت شکایات دسترسی سریع ثبت‌نام / ورود حساب کاربری محصولات تخفیف‌‌دار فروش عمده مقالات درباره آلفاکیت تماس با آلفاکیت آلفاکیت – فروشگاه تخصصی الکترونیک آلفاکیت مرجع تخصصی فروش چیپ لامپ و پروژکتور ال‌ای‌دی، هدلایت خودرو‌، تجهیزات نورپردازی، ماژول، ابزارآلات و تجهیزات الکترونیکی آدرس: آذربایجان شرقی، تبریز، خیابان محققی، روبروی پاساژ امت، به طرف باغ گلستان، جنب کوچه دکتر نوایی، جنب عطاری امام رضا، ساختمان پناهی، طبقه یک، سمت راست، واحد هفت تمامی حقوق این سایت متعلق به فروشگاه آلفاکیت است و تحت قوانین جمهوری اسلامی ایران فعالیت می‌کند. ورود با شماره موبایل با آدرس ایمیل ادامه دهید آیا هنوز عضو نشده‌اید؟ ثبت‌نام کنید ثبت‌نام نام کاربری * شماره تلفن رمزعبور * ادامه دهید قبلا عضو شده‌اید؟ ورود ارسال به ایمیل به من اطلاع بده با پر کردن فرم زیر هر زمان که این محصول موجود شد از طریق ایمیل یا ارسال پیامک به شما اطلاع رسانی خواهد شد. از طریق: ایمیل به بازگشت ثبت</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1448,10 +1437,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="3" t="n">
         <v>5900000</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" s="3" t="n">
         <v>5900000</v>
       </c>
     </row>
@@ -1462,27 +1451,23 @@
       <c r="B31" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>https://shop.ideaelec.com/product/esp8266-12e/</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ماژول وای فای ESP8266-12E اورجینال Ai-thinker | ایده الکترونیک قابل توجه کاربران محترم فروشگاه ایده الکترونیک؛ با توجه به اینکه فاکتور فیزیکی به همراه سفارش به صورت پیش فرض ارسال نخواهد شد در صورت نیاز به فاکتور لطفا در صفحه تسویه حساب گزینه ارسال فاکتور رو انتخاب کنید. از توجه شما سپاسگزاریم. رد کردن Skip to navigation Skip to main content جستجو ورود ایجاد یک حساب کاربری نام کاربری یا آدرس ایمیل * الزامی رمز عبور * الزامی ورود رمز عبور را فراموش کرده اید؟ مرا به خاطر بسپار ادامه دهید 0 مورد جستجو مرور دسته ها آی سی ها پروسسور و کنترلر میکروکنترلر AVR میکروکنترلر PIC میکروکنترلر ARM میکروپروسسور DSP FPGA CPLD منطقی شمارنده شیفت رجیستر لچ و فلیپ فلاپ گیت های منطقی دیکدر و مالتی پلکسر بافر، درایور، فرستنده و گیرنده مبدل کنترلر تاچ اسکرین پتانسیومتر دیجیتال مبدل آنالوگ به دیجیتال مبدل دیجیتال به آنالوگ تغذیه و درایور درایور گیت رفرنس ولتاژ درایور موتور کنترل باطری درایور ال ای دی رگولاتور ولتاژ- خطی رگولاتور ولتاژ – سوئیچینگ خطی ابزار دقیق مقایسه کننده آمپلی فایر صوتی آمپلی فایر – آپ امپ ، بافر حافظه رم فلش FIFO EEPROM ساعت و کلاک ساعت و زمان بافر کلاک و درایور تولید کننده کلاک و فرکانس شمارنده ها و نوسان سازها واسطه واسط USB واسط شبکه کد گذار و رمز گشا واسط های سریال راه انداز سنسور رادیویی آنتن رادیویی آمپلی فایر رادیویی فرستنده و گیرنده رادیویی نیمه هادی ها ترانزیستور BJT IGBT JFET MOSFET تریستور دیاک تریاک SCR دیود دیود زنر دیود شاتکی دیود یکسوکننده قطعات پسیو خازن خازن میکا خازن پلیمری خازن تانتالیوم خازن آرایه ای خازن سرامیکی خازن پلی استر خازن متغیر- تریمر خازن الکترولیت فلزی سلف سلف متغییر سلف ثابت مقاومت مقاومت سیم پیچ مقاومت متغیر مقاومت Through Hole ترمیستور مقاومت آرایه ای مقاومت SMD کریستال و اسیلاتور رزوناتور اسیلاتور کریستال فریت و چوک فریت بید چوک ترانسفورماتور ترانس کاهنده ولتاژ ترانس سوئیچینگ ترانس صوتی ترانس رادیویی ترانس فیلتر الکترومکانیک رله ها پایه رله رله های خودرویی رله تاخیر زمانی رله آی سی رله سیگنال رله قدرت صوتی اسپیکر میکروفون بازر حرارتی هیت سینک فن و دمنده کلید و کیپد کی پد سوئیچ روتاری سوئیچ راکر تک سوئیچ میکرو سوئیچ دیپ سوئیچ لوازم جانبی موتور و درایور استپر موتور درایور موتور موتورهای AC,DC,Servo سنسورها حرکتی سنسور شتاب سنسور ژیروسکوپ نوری فتو دیود فتوترانزیستور دیود های لیزری سنسور فتوالکتریک سنسور جریان سنسور اثر هال سنسور جریان دما و رطوبت رطوبت PTC-NTC سنسور دما دیجیتال سنسور دما آنالوگ متفرقه مغناطیسی سنسور فشار هوا پراکسی سنسور FLOW اپتوالکترونیک اپتوکوپلر اپتوکوپلر اپتوماسفت اپتوترایاک اپتوتریستور LED Through hole LED نوار LED SMD LED نمایشگرها LCD کاراکتری LCD گرافیکی LCD رنگی سون سگمنت دات ماتریس فیبر نوری لیزر لامپ کابل و کانکتور کانکتور دی کانکتور کانکتور بدنه صدا و تصویر ماژولار و شبکه سوکت آی سی و قطعات اسلات حافظه هدر و اتصال سیم فتوولتاییک و سولار رادیویی و کواکسیال اسلات کارت خودرویی ترمینال اتصال بین بردها فیبر نوری USB FFC/FPC IDC سیم و کابل صدا و تصویر کابل اترنت کابل فلت فیبر نوری کابل usb FPC/FFC محافظ و پلاک کابل رادیویی و کواکسیال تجهیزات آزمایشگاهی و اندازه گیری دماسنج مولتی متر منبع تغذیع اسیلوسکوپ پراب و کلیپس روشنایی و لوپ آنالایزر کولیس و میکرومتر فانکشن ژنراتور (مولد سیگنال) پروگرامر ابزار چکش تیغ و اره گیره و بست انبردست و پنس پالت، کشوی ابزار آچار و پیچ گوشتی هویه و ابزار لحیم کاری سوکت زن و سر سیم زن دریل و پیچ گوشتی برقی جعبه و اتصالات فنر واشر اسپیسر پیچ و مهره انکلوشر (جعبه و قاب) نمونه سازی و مواد مصرفی بردبورد مواد خام شیمیایی فیلامنت پرینتر سه بعدی تغذیه و محافظت منابع تغذیه سوئیچینگ آداپتور یو پی اس ماژول تغذیه محافظ تغذیه اینورتر DC به AC باطری و تجهیزات مدارهای محافظ و فیوزها ESD فیوز پایه فیوز وریستور دیود TVS قطع کننده مدار فیوز برگشت پذیر PTC ماژول و برد توسعه کامپیوترهای تک بردی رسپبری Beeglebone Friendly ARM کامپیوترهای صنعتی آردوینو برد آردوینو ماژول آردوینو شیلد آردوینو کیت آردوینو سایر وایرلس، شبکه و اینترنت اشیا فرستنده،گیرنده رادیویی (RF) GPS, GSM, GPRS بلوتوث وای فای Ethernet صدا و تصویر ماژول نمایشگر (LED,seven SEG,LCD) دوربین و پردازش تصویر ماژول صوتی Encoder ماژول های کاربردی استارتر کیت – هدر برد رابط ها و مبدل ها ماژول های رله ماژول های تغذیه، ولتاژ و جریان ساعت RTC ماژول RFID فاصله سنج اولتراسونیک سایر ماژول ها درایور و موتور سنسورهای ماژولار فتوسل،لیزر و مادون قرمز ماژول های دما و رطوبت ماژول های گاز ماژول های فشار ماژول های حرکتی PIR ماژول های وزن و ترازو ماژول اثرانگشت شتاب سنج، ژیروسکوپ، قطب نما ماژول تشخیص رنگ روباتیک و مکاترونیک شاسی و سازه پایه ها و براکت ها فریم آلومینیوم و فریم پلاستیک اتصالات و کانکتور چرخ دنده و گیربکس چرخ دنده فلزی و چرخ دنده پلاستیکی گیربکس آماده تسمه و پولی زنجیر و چرخ زنجیر زنجیر رباتیکی فلزی و پلیمری چرخ‌زنجیر ست زنجیر و چرخ‌زنجیر ملحقات زنجیر و چرخ‌زنجیر بازو و گیره رباتیک بازو های مکانیکی رباتیک گیره رباتیک قطعات پرینت سه بعدی مخصوص بازو و گیره چرخ و سیستم حرکتی چرخ های رباتیک چرخ آمنی-omni چرخ ساده چرخ گیربکسی چرخ مکانوم چرخ پلیمری-سیلیکونی چرخ تانکی-بزرگ صنعتی چرخ هرزگردمخصوص ترک-رولر ترک ها و سیستم خزنده ترک پلاستیکی-لاستیکی ترک های تانکی آماده ست ترک با چرخ و موتور ملحقات چرخ لوازم جانبی رباتیک کیت ربات برای دانش‌آموزان و مبتدی‌ها کیت آموزشی رباتیک متوسطه پیشرفته ربات‌های آماده مسابقه‌ای موتور های رباتیک تکنولوژی و سرگرمی کیت های آموزشی هواپیمای بدون سرنشین کوادکوپتر جمهوری، نبش سی تیر 02166751923 جمهوری، نبش سی تیر 02166751923 برای بزرگنمایی کلیک کنید خانه / ماژول و برد توسعه / وایرلس،شبکه و اینترنت اشیا / وای فای / ماژول وای فای ESP8266-12E اورجینال Ai-thinker نمایشگر  7 اینچ با تاچ خازنی Waveshare رسپبری 1024x600 ۱۴,۰۶۵,۸۲۶ تومان بازگشت به محصولات گیرنده بلوتوث VHM 314 با ریموت ۵۳۶,۷۹۸ تومان قیمت اصلی: ۵۳۶,۷۹۸ تومان بود. ۲۹۵,۴۰۶ تومان قیمت فعلی: ۲۹۵,۴۰۶ تومان. ماژول وای فای ESP8266-12E اورجینال Ai-thinker ۴۲۰,۰۸۴ تومان ماژول وای فای ESP8266-12E با پشتیبانی از ارتباط سریال uart و دستورات ATcommand بدون نیاز به نصب آنتن خارجی مناسب برای کاربردهای IOT مدل های دیگر این محصول PCBتبدیل ESP-0 7 ,ESP-0 8 ,ESP-12 برد wifi آردوینو WeMos D1 mini با هسته ESP8266 برد wifi آردوینو WeMos D1 mini با هسته ESP8266- برد توسعه وایفای ESPB266 و میکرو USB ماژول ESP-01 Downloader Adapter ماژول ESP-13 ماژول مبدل مدل ESP8266 ماژول وای فای ESP-01S با خروجی سریال ماژول وای فای ESP-07 ماژول وای فای ESP-07. ماژول وای فای ESP-12F ماژول وای فای ESP-12F تولید Ai Thinker ماژول وای فای ESP8266 01 همراه با آنتن داخلی ماژول وای فای ESP8266 01 همراه با آنتن داخلی Ai thinker ماژول وای فای ESP8266-12E ماژول وای فای ESP8266-12E اورجینال Ai-thinker ماژول وای فای با رله | ESP8266 موجود در انبار - ماژول وای فای ESP8266-12E اورجینال Ai-thinker عدد + افزودن به سبد خرید مقايسه افزودن به علاقه مندی به من از طریق پیامک اطلاع بده زمانیکه محصول حراج شد زمانیکه محصول توقف فروش شد زمانیکه نسخه جدید محصول منتشر شد ثبت شناسه محصول: B1607 دسته: وای فای , وایرلس،شبکه و اینترنت اشیا برچسب: 12E , esp8266 , ESP8266-12E , wifi , wifi module , ماژول بیسیم , ماژول وای فای , وای فای اشتراک گذاری: توضیحات توضیحات تکمیلی نظرات (0) توضیحات بر روی این ماژول ها از یک تقویت کننده استفاده شده که موجب افزایش برد و کارآیی دستگاه می شود همچنین از یک تقویت کنندLNA که برای تقویت امواج ظعیف بکار میرود استفاده شده که در کنار تقویت کننده PA کیفیت و برد مناسبی را در اختیار کاربر قرار می دهد . پروتکل ارتباطی از نوعUART بوده که براحتی و با ارسال دستورات ATcommand می توان به تنظیمات ماژول دسترسی پیدا کرد. مناسب برای کاربردهای اینترنت اشیا قابل برنامه نویسی در محیط اردینو دیتاشیت: https://wiki.ai-thinker.com/_media/esp8266/a014ps01.pdf توضیحات تکمیلی وزن 2 گرم نظرات (0) دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “ماژول وای فای ESP8266-12E اورجینال Ai-thinker” لغو پاسخ نشانی ایمیل شما منتشر نخواهد شد. بخش‌های موردنیاز علامت‌گذاری شده‌اند * امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف دیدگاه شما * نام * ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. شما باید وارد حساب خود شده باشید تا قادر به اضافه کردن تصاویر در نظرات باشید. محصولات مشابه فروخته شده افزودن به علاقه مندی مینی کی بورد بی سیم دارای تاچ پنل با بک لایت آبی 5.0 رسپبری , ماژول های کاربردی , سایر ماژول ها , وایرلس،شبکه و اینترنت اشیا ۹۴۵,۱۷۰ تومان کد انحصاری محصول : HQ0302 اطلاعات بیشتر مقايسه نمایش سریع -10% فروخته شده افزودن به علاقه مندی ماژول SIM800C 24MBit WITH BT وایرلس،شبکه و اینترنت اشیا , GPS, GSM, GPRS ۱,۰۵۸,۴۰۰ تومان قیمت اصلی: ۱,۰۵۸,۴۰۰ تومان بود. ۹۵۶,۹۷۰ تومان قیمت فعلی: ۹۵۶,۹۷۰ تومان. کد انحصاری محصول : IE2-01W04 اطلاعات بیشتر مقايسه نمایش سریع -25% افزودن به علاقه مندی ماژول انتقال بی سیم دیتا NRF24L01 دارای آنتن PCB وایرلس،شبکه و اینترنت اشیا , ماژول های رادیویی (RF) ۴۵۳,۰۴۸ تومان قیمت اصلی: ۴۵۳,۰۴۸ تومان بود. ۳۴۱,۶۰۳ تومان قیمت فعلی: ۳۴۱,۶۰۳ تومان. کد انحصاری محصول : D0404 افزودن به سبد خرید مقايسه نمایش سریع فروخته شده افزودن به علاقه مندی ماژول بلوتوث CJMCU 8223 NRF51822 + LIS3DH وایرلس،شبکه و اینترنت اشیا , بلوتوث ۳۵۸,۹۳۲ تومان کد انحصاری محصول : BQ0509 اطلاعات بیشتر مقايسه نمایش سریع فروخته شده افزودن به علاقه مندی ماژول بلوتوث نسخه 4 – NRF51822 وایرلس،شبکه و اینترنت اشیا , بلوتوث ۱۹۰,۴۱۸ تومان کد انحصاری محصول : E1186 اطلاعات بیشتر مقايسه نمایش سریع افزودن به علاقه مندی ماژول شبکه ENC28J60 وایرلس،شبکه و اینترنت اشیا , Ethernet ۵۹۱,۱۵۰ تومان کد انحصاری محصول : E0101 افزودن به سبد خرید مقايسه نمایش سریع فروخته شده افزودن به علاقه مندی ماژول وای فای ESP-12F تولید Ai Thinker وایرلس،شبکه و اینترنت اشیا , وای فای , ماژول و برد توسعه ۳۷۸,۸۰۹ تومان کد انحصاری محصول : IE2-03P06 اطلاعات بیشتر مقايسه نمایش سریع فروخته شده افزودن به علاقه مندی ماژول وای فای ESP8266 01 همراه با آنتن داخلی Ai thinker وایرلس،شبکه و اینترنت اشیا , وای فای ۴۱۴,۶۵۵ تومان کد انحصاری محصول : A0701 اطلاعات بیشتر مقايسه نمایش سریع پیام رسان ها و شبکه های اجتماعی اینستاگرام یوتیوب آپارات تلگرام تماس با ما شماره تماس: 02166751923 (18-10) واتساپ یا تلگرام: 09376324850 ایمیل: Info@ideaelec.com آدرس: تهران، خیابان جمهوری، نبش سی تیر، ساختمان فرقانی، طبقه اول، پلاک 10 خدمات مشتریان حساب کاربری پاسخ به پرسش های متداول رویه های بازگرداندن کالا خدمات پس از فروش راهنمای خرید از ایده الکترونیک شیوه های پرداخت روش های ارسال قوانین و مقررات فروشگاه اینترنتی ایده الکترونیک، تسهیل در خرید آنلاین با توجه به گسترش فناوری اطلاعات در زندگی روزمره و استقبال عمومی از خریدهای آنلاین تیم تخصصی ایده الکترونیک برای توسعه کسب وکار در زمینه الکترونیک اقدام به تاسیس فروشگاه آنلاین قطعات و بردهای الکترونیک با شرایط زیر نموده است فضایی مطمئن برای خرید قطعات و بردهای الکترونیک راهنمایی و مشاوره متخصصان الکترونیک برای انتخاب محصول مناسب ارسال سریع کالاها برای کاربران پس از ثبت سفارش تضمین قیمت مناسب و مطمئن برای کالاهای مورد نظر در نظر گرفتن تخفیف ویژه مشتریان فروشگاه اینترنتی ایده الکترونیک پشتیبانی کامل از محصولات خریداری شده توسط کاربران استفاده از مطالب فروشگاه اینترنتی ایده الکترونیک فقط برای مقاصد غیرتجاری و با ذکر منبع بلامانع است. کلیه حقوق این سایت متعلق به فروشگاه آنلاین ایده الکترونیک می‌باشد. جستجو آی سی ها پروسسور و کنترلر میکروکنترلر AVR میکروکنترلر PIC میکروکنترلر ARM میکروپروسسور DSP FPGA CPLD منطقی شمارنده شیفت رجیستر لچ و فلیپ فلاپ گیت های منطقی دیکدر و مالتی پلکسر بافر، درایور، فرستنده و گیرنده مبدل کنترلر تاچ اسکرین پتانسیومتر دیجیتال مبدل آنالوگ به دیجیتال مبدل دیجیتال به آنالوگ تغذیه و درایور درایور گیت رفرنس ولتاژ درایور موتور کنترل باطری درایور ال ای دی رگولاتور ولتاژ- خطی رگولاتور ولتاژ – سوئیچینگ خطی ابزار دقیق مقایسه کننده آمپلی فایر صوتی آمپلی فایر – آپ امپ ، بافر حافظه رم فلش FIFO EEPROM ساعت و کلاک ساعت و زمان بافر کلاک و درایور تولید کننده کلاک و فرکانس شمارنده ها و نوسان سازها واسطه واسط USB واسط شبکه کد گذار و رمز گشا واسط های سریال راه انداز سنسور رادیویی آنتن رادیویی آمپلی فایر رادیویی فرستنده و گیرنده رادیویی نیمه هادی ها ترانزیستور BJT IGBT JFET MOSFET تریستور دیاک تریاک SCR دیود دیود زنر دیود شاتکی دیود یکسوکننده قطعات پسیو خازن خازن میکا خازن پلیمری خازن تانتالیوم خازن آرایه ای خازن سرامیکی خازن پلی استر خازن متغیر- تریمر خازن الکترولیت فلزی سلف سلف متغییر سلف ثابت مقاومت مقاومت سیم پیچ مقاومت متغیر مقاومت Through Hole ترمیستور مقاومت آرایه ای مقاومت SMD کریستال و اسیلاتور رزوناتور اسیلاتور کریستال فریت و چوک فریت بید چوک ترانسفورماتور ترانس کاهنده ولتاژ ترانس سوئیچینگ ترانس صوتی ترانس رادیویی ترانس فیلتر الکترومکانیک رله ها پایه رله رله های خودرویی رله تاخیر زمانی رله آی سی رله سیگنال رله قدرت صوتی اسپیکر میکروفون بازر حرارتی هیت سینک فن و دمنده کلید و کیپد کی پد سوئیچ روتاری سوئیچ راکر تک سوئیچ میکرو سوئیچ دیپ سوئیچ لوازم جانبی موتور و درایور استپر موتور درایور موتور موتورهای AC,DC,Servo سنسورها حرکتی سنسور شتاب سنسور ژیروسکوپ نوری فتو دیود فتوترانزیستور دیود های لیزری سنسور فتوالکتریک سنسور جریان سنسور اثر هال سنسور جریان دما و رطوبت رطوبت PTC-NTC سنسور دما دیجیتال سنسور دما آنالوگ متفرقه مغناطیسی سنسور فشار هوا پراکسی سنسور FLOW اپتوالکترونیک اپتوکوپلر اپتوکوپلر اپتوماسفت اپتوترایاک اپتوتریستور LED Through hole LED نوار LED SMD LED نمایشگرها LCD کاراکتری LCD گرافیکی LCD رنگی سون سگمنت دات ماتریس فیبر نوری لیزر لامپ کابل و کانکتور کانکتور دی کانکتور کانکتور بدنه صدا و تصویر ماژولار و شبکه سوکت آی سی و قطعات اسلات حافظه هدر و اتصال سیم فتوولتاییک و سولار رادیویی و کواکسیال اسلات کارت خودرویی ترمینال اتصال بین بردها فیبر نوری USB FFC/FPC IDC سیم و کابل صدا و تصویر کابل اترنت کابل فلت فیبر نوری کابل usb FPC/FFC محافظ و پلاک کابل رادیویی و کواکسیال تجهیزات آزمایشگاهی و اندازه گیری دماسنج مولتی متر منبع تغذیع اسیلوسکوپ پراب و کلیپس روشنایی و لوپ آنالایزر کولیس و میکرومتر فانکشن ژنراتور (مولد سیگنال) پروگرامر ابزار چکش تیغ و اره گیره و بست انبردست و پنس پالت، کشوی ابزار آچار و پیچ گوشتی هویه و ابزار لحیم کاری سوکت زن و سر سیم زن دریل و پیچ گوشتی برقی جعبه و اتصالات فنر واشر اسپیسر پیچ و مهره انکلوشر (جعبه و قاب) نمونه سازی و مواد مصرفی بردبورد مواد خام شیمیایی فیلامنت پرینتر سه بعدی تغذیه و محافظت منابع تغذیه سوئیچینگ آداپتور یو پی اس ماژول تغذیه محافظ تغذیه اینورتر DC به AC باطری و تجهیزات مدارهای محافظ و فیوزها ESD فیوز پایه فیوز وریستور دیود TVS قطع کننده مدار فیوز برگشت پذیر PTC ماژول و برد توسعه کامپیوترهای تک بردی رسپبری Beeglebone Friendly ARM کامپیوترهای صنعتی آردوینو برد آردوینو ماژول آردوینو شیلد آردوینو کیت آردوینو سایر وایرلس، شبکه و اینترنت اشیا فرستنده،گیرنده رادیویی (RF) GPS, GSM, GPRS بلوتوث وای فای Ethernet صدا و تصویر ماژول نمایشگر (LED,seven SEG,LCD) دوربین و پردازش تصویر ماژول صوتی Encoder ماژول های کاربردی استارتر کیت – هدر برد رابط ها و مبدل ها ماژول های رله ماژول های تغذیه، ولتاژ و جریان ساعت RTC ماژول RFID فاصله سنج اولتراسونیک سایر ماژول ها درایور و موتور سنسورهای ماژولار فتوسل،لیزر و مادون قرمز ماژول های دما و رطوبت ماژول های گاز ماژول های فشار ماژول های حرکتی PIR ماژول های وزن و ترازو ماژول اثرانگشت شتاب سنج، ژیروسکوپ، قطب نما ماژول تشخیص رنگ روباتیک و مکاترونیک شاسی و سازه پایه ها و براکت ها فریم آلومینیوم و فریم پلاستیک اتصالات و کانکتور چرخ دنده و گیربکس چرخ دنده فلزی و چرخ دنده پلاستیکی گیربکس آماده تسمه و پولی زنجیر و چرخ زنجیر زنجیر رباتیکی فلزی و پلیمری چرخ‌زنجیر ست زنجیر و چرخ‌زنجیر ملحقات زنجیر و چرخ‌زنجیر بازو و گیره رباتیک بازو های مکانیکی رباتیک گیره رباتیک قطعات پرینت سه بعدی مخصوص بازو و گیره چرخ و سیستم حرکتی چرخ های رباتیک چرخ آمنی-omni چرخ ساده چرخ گیربکسی چرخ مکانوم چرخ پلیمری-سیلیکونی چرخ تانکی-بزرگ صنعتی چرخ هرزگردمخصوص ترک-رولر ترک ها و سیستم خزنده ترک پلاستیکی-لاستیکی ترک های تانکی آماده ست ترک با چرخ و موتور ملحقات چرخ لوازم جانبی رباتیک کیت ربات برای دانش‌آموزان و مبتدی‌ها کیت آموزشی رباتیک متوسطه پیشرفته ربات‌های آماده مسابقه‌ای موتور های رباتیک تکنولوژی و سرگرمی کیت های آموزشی هواپیمای بدون سرنشین کوادکوپتر منو 0 مورد سبد خرید حساب من فروشگاه ماژول وای فای ESP8266-12E اورجینال Ai-thinker ۴۲۰,۰۸۴ تومان موجود در انبار - ماژول وای فای ESP8266-12E اورجینال Ai-thinker عدد + افزودن به سبد خرید مقايسه افزودن به علاقه مندی ورود با شماره موبایل با آدرس ایمیل مرا به خاطر بسپار ادامه دهید آیا هنوز عضو نشده اید؟ اکنون ثبت نام کنید بازنشانی رمزعبور با شماره موبایل با آدرس ایمیل ادامه دهید ثبت نام رمزعبور ادامه دهید قبلا عضو شده اید؟ اکنون وارد شوید متوجه شدم ✕ | از «ایده الکترونیک» مثل دیجی‌کالا خرید کن! با وارد کردن شماره تلفنی که در دیجی‌کالا ثبت کردی، اطلاعات حسابت رو ببین، آدرست رو انتخاب کن و خریدت رو مثل دیجی‌کالا سریع، قسطی و امن انجام بده. تایید شده توسط دیجی‌کالا این سایت توسط دیجی‌کالا بررسی شده و مالکیت، اطلاعات تماس، کیفیت و نحوه ارائه خدمات آن تأیید شده‌است. متوجه شدم</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>140658260</v>
-      </c>
-      <c r="G31" t="n">
-        <v>140658260</v>
-      </c>
+          <t>ERROR: HTTPSConnectionPool(host='shop.ideaelec.com', port=443): Max retries exceeded with url: /product/esp8266-12e/ (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='shop.ideaelec.com', port=443) at 0x21cd97bbed0&gt;, 'Connection to shop.ideaelec.com timed out. (connect timeout=30)'))</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1491,14 +1476,14 @@
       <c r="B32" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>https://bazaarbargh.ir/product/%d9%85%d8%a7%da%98%d9%88%d9%84-%d8%a7%d9%84-%d8%a7%db%8c-%d8%af%db%8c-rgb-ws2812-%d9%85%d8%b1%d8%a8%d8%b9%db%8c-4x4/</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ماژول ال ای دی RGB WS2812 مربعی 4×4 رد کردن به ناوبری رد کردن به محتوای اصلی جستجو 0 محصول 0 تومان ورود / ثبت نام ورود / ثبت نام خانه قطعات الکترونیک ترانزیستور مقاومت خازن ال ای دی دیود فیوز منبع تغذیه سوئیچینگ تریستور/ ترایاک ریموت آی سی سلف کریستال میکروکنترلر رله کلید وریستور سنسور کانکتور ال سی دی و سون سگمنت موتور و گریبکس ابزار ترانس و آداپتور باتری سیم لحیم و قلع قطعات متفرقه قطعات ماینر فن و گارد ماژول ماژول تغذیه، مبدل ولتاژ و شارژ ماژول شارژ و مدیریت باتری ماژول تغذیه سوئیچینگ ماژول های مبدل ولتاژ ‒ مبدل کاهنده ولتاژ ‒ مبدل افزاینده ولتاژ ‒ مبدل افزاینده و کاهنده ولتاژ ماژول پاور بانک ‒ کیس پاور بانک ‒ باتری پاور بانک ماژول های ارتباطی، بی سیم، اینترنت اشیا ماژول بلوتوث ماژول وای فای ماژول GPS GSM GPRS ماژول RFID (تگ کارت) ماژول فرستنده و گیرنده ماژول مادون قرمز و لیزر ماژول شبکه ماژول های سنسور ماژول سنسور لمسی ماژول دما و رطوبت ماژول سنسور تشخیص حرکت و PIR سنسور ولتاژ و جریان ماژول گاز ماژول شتاب سنج و ژیروسکوپ ماژول قطب نما و زاویه سنج ماژول تشخیص رنگ و نور ماژول فشار ماژول آلتراسونیک سنسور متفرقه ماژول های کاربردی ماژول بخار سرد ماژول رله ماژول ساعت RTC ماژول دیمر ماژول نمایشگر ماژول ولت متر و آمپرمتر ماژول‌ های مبدل و اینترفیس دیباگر و پروگرامر سایر ماژول ها ماژول‌ ها و تجهیزات ال‌ ای‌ دی چیپ ال ای دی ال ای دی نواری ال ای دی خطی درایور ال ای دی ماژول صوتی و آمپلی فایر ماژول آمپلی فایر بلوتوث دار ماژول آمپلی فایر کلاس AB,D ماژول های پخش و ضبط و میکروفن ماژول بر اساس برند برد آردوینو برد رسپبری پای ماژول برد های STM ماژول مبدل SMD به DIP ماژول درایور و کنترل موتور خرید اینورتر مبدل برق 12 به 220 مبدل برق 12 به 24 مبدل برق 24 به 110 مبدل برق 24 به 12 مبدل برق 24 به 220 مبدل برق 12 به 110 جانبی رایانه دستگاه برش لیزر تجهیزات آزمایشگاهی مقالات جستجو 0 محصول 0 تومان بزرگنمایی تصویر ماژول ال ای دی RGB WS2812 مربعی 4×4 خانه / ماژول / ماژول‌ ها و تجهیزات ال‌ ای‌ دی / ال ای دی خطی / ماژول ال ای دی RGB WS2812 مربعی 4×4 شناسه : MOID-274 Categories ال ای دی خطی , ماژول , ماژول‌ ها و تجهیزات ال‌ ای‌ دی بازاربرق 4.90 (1,966 Reviews) هر قسط با ترب‌پی: 7,250 تومان ۴ قسط ماهانه. بدون سود، چک و ضامن. ۴ قسط ماهانه. بدون سود، چک و ضامن. دارای 16 عدد LED RGB فول کالر چیدمان LED ها به‌صورت ماتریس 4×4 مجهز به چیپ WS2812 مناسب برای پروژه‌های نورپردازی، آردوینو و رباتیک ابعاد 30×30 میلی‌متر با طراحی مربعی قابلیت ایجاد افکت‌ها و الگوهای نوری متنوع 29,000 تومان ارسال این محصول از: 3 روز کاری دیگر موجود در انبار (فعال برای پیش سفارش) ماژول ال ای دی RGB WS2812 مربعی 4×4 عدد افزودن به سبد خرید هر قسط با ترب‌پی: 7,250 تومان ۴ قسط ماهانه. بدون سود، چک و ضامن. ویژگی های محصول توضیحات تکمیلی وزن 5 گرم توضیحات محصول ماژول LED RGB WS2812 مربعی 4×4 ماژول ال ای دی LED RGB WS2812 مربعی یک برد نور پردازی مبتنی بر LED های RGB آدرس‌ پذیر است که از 16 عدد LED فول کالر در قالب یک ماتریس 4×4 تشکیل شده است. هر LED در این ماژول دارای مدار کنترل داخلی بوده و می‌توان رنگ و میزان روشنایی هر LED را به‌صورت مستقل کنترل کرد. برخلاف LED های RGB معمولی که برای کنترل هر رنگ نیاز به سیم‌کشی و پایه‌ های متعدد دارند، چیپ LED های WS2812 با استفاده از یک پروتکل ارتباطی دیجیتال سریال، اطلاعات رنگ را دریافت کرده و امکان کنترل تعداد زیادی LED را با تعداد پایه‌های کمتر فراهم می‌کنند. ویژگی‌های ماژول LED WS2812 دارای 16 عدد LED RGB فول کالر با قابلیت تولید رنگ‌های متنوع طراحی شده به‌صورت ماتریس مربعی 4×4 برای ایجاد الگوهای نوری مجهز به چیپ کنترل داخلی برای آدرس‌دهی مستقل هر LED قابلیت تنظیم جداگانه رنگ هر پیکسل LED ارتباط با میکروکنترلر از طریق پروتکل سریال دیجیتال ابعاد کوچک و مناسب برای استفاده در پروژه‌های محدود از نظر فضا قابل استفاده در پروژه‌های مبتنی بر آردوینو، میکروکنترلرها و سیستم‌های رباتیک کاربرد های ماژول RGB WS2812 مربعی نورپردازی هوشمند و تزئینی این ماژول به دلیل قابلیت نمایش رنگ‌های مختلف، برای ساخت چراغ‌های تزئینی، نورپردازی محیطی، تابلوهای نوری و پروژه‌های خلاقانه مورد استفاده قرار می‌گیرد. ساخت نمایشگرهای ماتریسی کوچک چیدمان 4×4 LED امکان نمایش الگوهای گرافیکی ساده، اعداد، حروف و علائم را فراهم می‌کند و می‌توان از آن در ساخت نمایشگرهای کوچک استفاده کرد. پروژه‌های هنری و تعاملی قابلیت کنترل مستقل هر LED باعث شده است این ماژول در ساخت نقاشی‌های نوری، آثار هنری دیجیتال و پروژه‌های تعاملی کاربرد داشته باشد. پروژه‌های رباتیک و الکترونیکی ماژول WS2812 به دلیل کنترل ساده و سازگاری با بسیاری از بردهای توسعه مانند آردوینو، گزینه‌ای مناسب برای نمایش وضعیت، ایجاد جلوه‌های نوری و افزایش قابلیت‌های بصری پروژه‌های رباتیکی است. محصولات مرتبط محصولات مشابه هر قسط 62,750 تومان ماژول آمپلی فایر PAM8403 با پتانسیومتر 251,000 تومان افزودن به سبد خرید هر قسط 293,750 تومان برد آردوینو Pro Mini دارای پردازنده مرکزی ATmega328 1,175,000 تومان افزودن به سبد خرید هر قسط 222,500 تومان ماژول شبکه ENC28J60 890,000 تومان افزودن به سبد خرید هر قسط 9,250 تومان ماژول کلید تاچ خازنی تک کانال با آی سی TTP223 نمره 4.50 از 5 37,000 تومان افزودن به سبد خرید هر قسط 16,150 تومان سنسور گیرنده آلتراسونیک 10 میلی متر | Ultrasonic R 64,600 تومان افزودن به سبد خرید هر قسط 122,500 تومان ماژول سگمنت 8 رقمی با درایور TM1638 490,000 تومان افزودن به سبد خرید 🔥 همین حالا با کد bazaarbargh ، از ۱۵٪ تخفیف خرید نقدی روی تمامی محصولات بهره‌مند شوید. × معرفی بازار برق تیم متخصصین بازاربرق با بیست سال سابقه واردات، تهیه و توزیع قطعات الکترونیک ، گرد هم آمده است تا از بزرگ ترین و متنوع ترین مرجع و فروشگاه قطعات الکترونیک ایران رونمایی کند. این سایت در نظر دارد تا ایجاد فرصتی مناسب برای رقابت سالم و پویا بین همکاران، تولیدکنندگان و واردکنندگان گرامی در سطح بین المللی، بهترین و جامع ترین خدمات را برای مشتریان نیز فراهم آورد. سلام دسترسی سریع خرید خازن الکترولیتی پیشنهادهای شگفت انگیز تماس با ما وبلاگ خرید خازن الکترولیتی پیشنهادهای شگفت انگیز تماس با ما وبلاگ ارتباط با ما اصفهان – چهارباغ – کوچه کازرونی – مجتمع صدف – واحد 302 ساعات 8 الی 14:30 03132247096 – 03132208367-09128408365 info@bazaarbargh.ir مجوز ها تمامی کالاها و خدمات بازار برق دارای مجوز‌های لازم از مراجع مربوطه می‌باشند و فعالیت های بازار برق تابع قوانین و مقررات جمهوری اسلامی ایران میباشد. جستجو خانه قطعات الکترونیک ترانزیستور مقاومت خازن ال ای دی دیود فیوز منبع تغذیه سوئیچینگ تریستور/ ترایاک ریموت آی سی سلف کریستال میکروکنترلر رله کلید وریستور سنسور کانکتور ال سی دی و سون سگمنت موتور و گریبکس ابزار ترانس و آداپتور باتری سیم لحیم و قلع قطعات متفرقه قطعات ماینر فن و گارد ماژول ماژول تغذیه، مبدل ولتاژ و شارژ ماژول شارژ و مدیریت باتری ماژول تغذیه سوئیچینگ ماژول های مبدل ولتاژ ‒ مبدل کاهنده ولتاژ ‒ مبدل افزاینده ولتاژ ‒ مبدل افزاینده و کاهنده ولتاژ ماژول پاور بانک ‒ کیس پاور بانک ‒ باتری پاور بانک ماژول های ارتباطی، بی سیم، اینترنت اشیا ماژول بلوتوث ماژول وای فای ماژول GPS GSM GPRS ماژول RFID (تگ کارت) ماژول فرستنده و گیرنده ماژول مادون قرمز و لیزر ماژول شبکه ماژول های سنسور ماژول سنسور لمسی ماژول دما و رطوبت ماژول سنسور تشخیص حرکت و PIR سنسور ولتاژ و جریان ماژول گاز ماژول شتاب سنج و ژیروسکوپ ماژول قطب نما و زاویه سنج ماژول تشخیص رنگ و نور ماژول فشار ماژول آلتراسونیک سنسور متفرقه ماژول های کاربردی ماژول بخار سرد ماژول رله ماژول ساعت RTC ماژول دیمر ماژول نمایشگر ماژول ولت متر و آمپرمتر ماژول‌ های مبدل و اینترفیس دیباگر و پروگرامر سایر ماژول ها ماژول‌ ها و تجهیزات ال‌ ای‌ دی چیپ ال ای دی ال ای دی نواری ال ای دی خطی درایور ال ای دی ماژول صوتی و آمپلی فایر ماژول آمپلی فایر بلوتوث دار ماژول آمپلی فایر کلاس AB,D ماژول های پخش و ضبط و میکروفن ماژول بر اساس برند برد آردوینو برد رسپبری پای ماژول برد های STM ماژول مبدل SMD به DIP ماژول درایور و کنترل موتور خرید اینورتر مبدل برق 12 به 220 مبدل برق 12 به 24 مبدل برق 24 به 110 مبدل برق 24 به 12 مبدل برق 24 به 220 مبدل برق 12 به 110 جانبی رایانه دستگاه برش لیزر تجهیزات آزمایشگاهی مقالات ورود / ثبت نام ورود بستن نام کاربری یا آدرس ایمیل * الزامی رمز عبور * الزامی ورود رمز عبور را فراموش کرده اید؟ مرا به خاطر بسپار هنوز حساب کاربری ندارید؟ ایجاد حساب کاربری حساب کاربری سبد خرید منو</t>
+          <t>ماژول ال ای دی RGB WS2812 مربعی 4×4 رد کردن به ناوبری رد کردن به محتوای اصلی جستجو 0 محصول 0 تومان ورود / ثبت نام ورود / ثبت نام خانه قطعات الکترونیک ترانزیستور مقاومت خازن ال ای دی دیود فیوز منبع تغذیه سوئیچینگ تریستور/ ترایاک ریموت آی سی سلف کریستال میکروکنترلر رله کلید وریستور سنسور کانکتور ال سی دی و سون سگمنت موتور و گریبکس ابزار ترانس و آداپتور باتری سیم لحیم و قلع قطعات متفرقه قطعات ماینر فن و گارد ماژول ماژول تغذیه، مبدل ولتاژ و شارژ ماژول شارژ و مدیریت باتری ماژول تغذیه سوئیچینگ ماژول های مبدل ولتاژ ‒ مبدل کاهنده ولتاژ ‒ مبدل افزاینده ولتاژ ‒ مبدل افزاینده و کاهنده ولتاژ ماژول پاور بانک ‒ کیس پاور بانک ‒ باتری پاور بانک ماژول های ارتباطی، بی سیم، اینترنت اشیا ماژول بلوتوث ماژول وای فای ماژول GPS GSM GPRS ماژول RFID (تگ کارت) ماژول فرستنده و گیرنده ماژول مادون قرمز و لیزر ماژول شبکه ماژول های سنسور ماژول سنسور لمسی ماژول دما و رطوبت ماژول سنسور تشخیص حرکت و PIR سنسور ولتاژ و جریان ماژول گاز ماژول شتاب سنج و ژیروسکوپ ماژول قطب نما و زاویه سنج ماژول تشخیص رنگ و نور ماژول فشار ماژول آلتراسونیک سنسور متفرقه ماژول های کاربردی ماژول بخار سرد ماژول رله ماژول ساعت RTC ماژول دیمر ماژول نمایشگر ماژول ولت متر و آمپرمتر ماژول‌ های مبدل و اینترفیس دیباگر و پروگرامر سایر ماژول ها ماژول‌ ها و تجهیزات ال‌ ای‌ دی چیپ ال ای دی ال ای دی نواری ال ای دی خطی درایور ال ای دی ماژول صوتی و آمپلی فایر ماژول آمپلی فایر بلوتوث دار ماژول آمپلی فایر کلاس AB,D ماژول های پخش و ضبط و میکروفن ماژول بر اساس برند برد آردوینو برد رسپبری پای ماژول برد های STM ماژول مبدل SMD به DIP ماژول درایور و کنترل موتور خرید اینورتر مبدل برق 12 به 220 مبدل برق 12 به 24 مبدل برق 24 به 110 مبدل برق 24 به 12 مبدل برق 24 به 220 مبدل برق 12 به 110 جانبی رایانه دستگاه برش لیزر تجهیزات آزمایشگاهی مقالات جستجو 0 محصول 0 تومان بزرگنمایی تصویر ماژول ال ای دی RGB WS2812 مربعی 4×4 خانه / ماژول / ماژول‌ ها و تجهیزات ال‌ ای‌ دی / ال ای دی خطی / ماژول ال ای دی RGB WS2812 مربعی 4×4 شناسه : MOID-274 Categories ال ای دی خطی , ماژول , ماژول‌ ها و تجهیزات ال‌ ای‌ دی بازاربرق 4.90 (1,966 Reviews) هر قسط با ترب‌پی: 7,250 تومان ۴ قسط ماهانه. بدون سود، چک و ضامن. ۴ قسط ماهانه. بدون سود، چک و ضامن. دارای 16 عدد LED RGB فول کالر چیدمان LED ها به‌صورت ماتریس 4×4 مجهز به چیپ WS2812 مناسب برای پروژه‌های نورپردازی، آردوینو و رباتیک ابعاد 30×30 میلی‌متر با طراحی مربعی قابلیت ایجاد افکت‌ها و الگوهای نوری متنوع 29,000 تومان ارسال این محصول از: 3 روز کاری دیگر موجود در انبار (فعال برای پیش سفارش) ماژول ال ای دی RGB WS2812 مربعی 4×4 عدد افزودن به سبد خرید هر قسط با ترب‌پی: 7,250 تومان ۴ قسط ماهانه. بدون سود، چک و ضامن. ویژگی های محصول توضیحات تکمیلی وزن 5 گرم توضیحات محصول ماژول LED RGB WS2812 مربعی 4×4 ماژول ال ای دی LED RGB WS2812 مربعی یک برد نور پردازی مبتنی بر LED های RGB آدرس‌ پذیر است که از 16 عدد LED فول کالر در قالب یک ماتریس 4×4 تشکیل شده است. هر LED در این ماژول دارای مدار کنترل داخلی بوده و می‌توان رنگ و میزان روشنایی هر LED را به‌صورت مستقل کنترل کرد. برخلاف LED های RGB معمولی که برای کنترل هر رنگ نیاز به سیم‌کشی و پایه‌ های متعدد دارند، چیپ LED های WS2812 با استفاده از یک پروتکل ارتباطی دیجیتال سریال، اطلاعات رنگ را دریافت کرده و امکان کنترل تعداد زیادی LED را با تعداد پایه‌های کمتر فراهم می‌کنند. ویژگی‌های ماژول LED WS2812 دارای 16 عدد LED RGB فول کالر با قابلیت تولید رنگ‌های متنوع طراحی شده به‌صورت ماتریس مربعی 4×4 برای ایجاد الگوهای نوری مجهز به چیپ کنترل داخلی برای آدرس‌دهی مستقل هر LED قابلیت تنظیم جداگانه رنگ هر پیکسل LED ارتباط با میکروکنترلر از طریق پروتکل سریال دیجیتال ابعاد کوچک و مناسب برای استفاده در پروژه‌های محدود از نظر فضا قابل استفاده در پروژه‌های مبتنی بر آردوینو، میکروکنترلرها و سیستم‌های رباتیک کاربرد های ماژول RGB WS2812 مربعی نورپردازی هوشمند و تزئینی این ماژول به دلیل قابلیت نمایش رنگ‌های مختلف، برای ساخت چراغ‌های تزئینی، نورپردازی محیطی، تابلوهای نوری و پروژه‌های خلاقانه مورد استفاده قرار می‌گیرد. ساخت نمایشگرهای ماتریسی کوچک چیدمان 4×4 LED امکان نمایش الگوهای گرافیکی ساده، اعداد، حروف و علائم را فراهم می‌کند و می‌توان از آن در ساخت نمایشگرهای کوچک استفاده کرد. پروژه‌های هنری و تعاملی قابلیت کنترل مستقل هر LED باعث شده است این ماژول در ساخت نقاشی‌های نوری، آثار هنری دیجیتال و پروژه‌های تعاملی کاربرد داشته باشد. پروژه‌های رباتیک و الکترونیکی ماژول WS2812 به دلیل کنترل ساده و سازگاری با بسیاری از بردهای توسعه مانند آردوینو، گزینه‌ای مناسب برای نمایش وضعیت، ایجاد جلوه‌های نوری و افزایش قابلیت‌های بصری پروژه‌های رباتیکی است. محصولات مرتبط محصولات مشابه هر قسط 58,750 تومان ماژول PIR سنسور تشخیص حرکت بدن نمره 5.00 از 5 235,000 تومان افزودن به سبد خرید هر قسط 467,325 تومان برد آردوینو Lilypad نمره 5.00 از 5 1,869,300 تومان افزودن به سبد خرید هر قسط 72,500 تومان ماژول آمپلی فایر تک کاناله 18 وات TDA2030A 290,000 تومان افزودن به سبد خرید هر قسط 104,150 تومان ماژول آمپلی فایر استریو 10 وات PAM8610 نمره 5.00 از 5 416,600 تومان افزودن به سبد خرید هر قسط 222,500 تومان ماژول شبکه ENC28J60 890,000 تومان افزودن به سبد خرید هر قسط 104,150 تومان ماژول آمپلی فایر بلوتوث استریو CT14 دارای پورت شارژ میکرو یو اس بی نمره 5.00 از 5 416,600 تومان افزودن به سبد خرید 🔥 همین حالا با کد bazaarbargh ، از ۱۵٪ تخفیف خرید نقدی روی تمامی محصولات بهره‌مند شوید. × معرفی بازار برق تیم متخصصین بازاربرق با بیست سال سابقه واردات، تهیه و توزیع قطعات الکترونیک ، گرد هم آمده است تا از بزرگ ترین و متنوع ترین مرجع و فروشگاه قطعات الکترونیک ایران رونمایی کند. این سایت در نظر دارد تا ایجاد فرصتی مناسب برای رقابت سالم و پویا بین همکاران، تولیدکنندگان و واردکنندگان گرامی در سطح بین المللی، بهترین و جامع ترین خدمات را برای مشتریان نیز فراهم آورد. سلام دسترسی سریع خرید خازن الکترولیتی پیشنهادهای شگفت انگیز تماس با ما وبلاگ خرید خازن الکترولیتی پیشنهادهای شگفت انگیز تماس با ما وبلاگ ارتباط با ما اصفهان – چهارباغ – کوچه کازرونی – مجتمع صدف – واحد 302 ساعات 8 الی 14:30 03132247096 – 03132208367-09128408365 info@bazaarbargh.ir مجوز ها تمامی کالاها و خدمات بازار برق دارای مجوز‌های لازم از مراجع مربوطه می‌باشند و فعالیت های بازار برق تابع قوانین و مقررات جمهوری اسلامی ایران میباشد. جستجو خانه قطعات الکترونیک ترانزیستور مقاومت خازن ال ای دی دیود فیوز منبع تغذیه سوئیچینگ تریستور/ ترایاک ریموت آی سی سلف کریستال میکروکنترلر رله کلید وریستور سنسور کانکتور ال سی دی و سون سگمنت موتور و گریبکس ابزار ترانس و آداپتور باتری سیم لحیم و قلع قطعات متفرقه قطعات ماینر فن و گارد ماژول ماژول تغذیه، مبدل ولتاژ و شارژ ماژول شارژ و مدیریت باتری ماژول تغذیه سوئیچینگ ماژول های مبدل ولتاژ ‒ مبدل کاهنده ولتاژ ‒ مبدل افزاینده ولتاژ ‒ مبدل افزاینده و کاهنده ولتاژ ماژول پاور بانک ‒ کیس پاور بانک ‒ باتری پاور بانک ماژول های ارتباطی، بی سیم، اینترنت اشیا ماژول بلوتوث ماژول وای فای ماژول GPS GSM GPRS ماژول RFID (تگ کارت) ماژول فرستنده و گیرنده ماژول مادون قرمز و لیزر ماژول شبکه ماژول های سنسور ماژول سنسور لمسی ماژول دما و رطوبت ماژول سنسور تشخیص حرکت و PIR سنسور ولتاژ و جریان ماژول گاز ماژول شتاب سنج و ژیروسکوپ ماژول قطب نما و زاویه سنج ماژول تشخیص رنگ و نور ماژول فشار ماژول آلتراسونیک سنسور متفرقه ماژول های کاربردی ماژول بخار سرد ماژول رله ماژول ساعت RTC ماژول دیمر ماژول نمایشگر ماژول ولت متر و آمپرمتر ماژول‌ های مبدل و اینترفیس دیباگر و پروگرامر سایر ماژول ها ماژول‌ ها و تجهیزات ال‌ ای‌ دی چیپ ال ای دی ال ای دی نواری ال ای دی خطی درایور ال ای دی ماژول صوتی و آمپلی فایر ماژول آمپلی فایر بلوتوث دار ماژول آمپلی فایر کلاس AB,D ماژول های پخش و ضبط و میکروفن ماژول بر اساس برند برد آردوینو برد رسپبری پای ماژول برد های STM ماژول مبدل SMD به DIP ماژول درایور و کنترل موتور خرید اینورتر مبدل برق 12 به 220 مبدل برق 12 به 24 مبدل برق 24 به 110 مبدل برق 24 به 12 مبدل برق 24 به 220 مبدل برق 12 به 110 جانبی رایانه دستگاه برش لیزر تجهیزات آزمایشگاهی مقالات ورود / ثبت نام ورود بستن نام کاربری یا آدرس ایمیل * الزامی رمز عبور * الزامی ورود رمز عبور را فراموش کرده اید؟ مرا به خاطر بسپار هنوز حساب کاربری ندارید؟ ایجاد حساب کاربری حساب کاربری سبد خرید منو</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1506,10 +1491,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
+      <c r="F32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1520,7 +1505,7 @@
       <c r="B33" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>https://www.merqc.com/item/3571/%D8%AF%D9%85_%DA%AF%D8%B1%D8%AF_%D9%BE%D8%B1%D9%88%D8%B3%DA%A9%DB%8C%D8%AA_1PK_5</t>
         </is>
@@ -1530,7 +1515,7 @@
           <t>دم گرد پروسکیت 1PK-501D ۰۳۱−۳۲۳۷۲۷۶۷ merqc.shop@gmail.com پیگیری سفارش پرداخت ورود ثبت‌نام ۰ آیتم - ۰ سبد خرید خالی می‌باشد مجموع هزینه 0 ریال سبد خرید منو Home IC آی سی other رگلاتور میکروکنترلر AVR CMOS TTL سوکت آی سی ادامه دسته‌بندی capacitor خازن الکترولیتی پلی استر عدسی خازن smd 805 خازن smd 1206 تانتالیومsmdسایزA ادامه دسته‌بندی مقاومت , پتانسیومتر , ولوم مقاومت 1/4w مقاومت 1w مقاومت 2w 5w آجری 10w آجری smd805 ادامه دسته‌بندی قطعات ربات پروازی فریم کواد کوپتر باتری Li-Po کواد کوپتر آماده موتور براشلس اسپید کنترل گیمبال ادامه دسته‌بندی diode دیود دیود زنر پل دیود دیود smd زنر smd پل دیود smd ادامه دسته‌بندی inductor سلف سلف مقاومتی بشکه ای/حلقوی سلفsmd 805 سلفsmd 1206 سلفsmd 1210 سلف حلقویsmd ادامه دسته‌بندی transistor ترانزیستور ترانزیستور mosfet ماسفت IGBT ترانزیستور smd ماسفت smd ترایاک ادامه دسته‌بندی سنسورها مادون قرمز,فتوسل اپتوکانتر سنسور دما سنسوردود و گاز رنگ/شدت نور سنسور رطوبت ادامه دسته‌بندی ماژول ها و بردهای برنامه پذیر هوشمند سازی ماژول فاصله ماژول بلوتوث ماژول GPS,GPRS ماژول قطب نما شتاب,ژیروسکوپ ادامه دسته‌بندی قطعات الکترونیکی دیگر کریستال کریستالsmd اسیلاتور اسیلاتورsmd رله رله smd ادامه دسته‌بندی ابزار الکترونیکی , پروگرامر , مبدل پروگرامر لحیم کاری مولتی متر ابزار دستی پروجکت برد اسپری ها پیچ گوشتی ادامه دسته‌بندی باتری,جا باتری,شارژر غیرشارژی,آلکالاین شارژی لیتیوم آیون باتری تلفنی باتری بک آپ باتری خشک ادامه دسته‌بندی LED , نمایشگرها , فلاشر , لیزر LCD تاچ LCD دات ماتریس بارگراف سون سگمنت LED خود رنگ ادامه دسته‌بندی موتور , پمپ , فن موتور DC استپ موتور سروو موتور مینی موتورگیربکس موتورگیربکسzga25 موتورگیربکسzga37 ادامه دسته‌بندی شاسی , کلید , کیــپد دیپ سوییچ دیپ سوییچ smd تک سوئیچ تک سوئیچ smd شاسی کلید ادامه دسته‌بندی بست , اسپیسر , گلند , پیچ اسپیسر فلزی اسپیسرپلاستیک بست کمربندی گِلند واشر دور سیم پیچ و مهره فلزی ادامه دسته‌بندی کانکتور , اتصالات , آنتن پین هدر پین هدر smd جک و فیش کانکتورمخابراتی کانکتورپاوری ATX,L6.2,SM,EL ادامه دسته‌بندی کابل,رابط سیمی,مبدل,وارنیش پراب PROBE سیم وایرپ سیم بِرِد برد کابل رابط های سیمی وارنیش ادامه دسته‌بندی لوازم تلویزیون LED و LCD چوک LCD لامپ فلورسنت برد تصویر بک لایت LED تستر بک لایت آداپتور,ترانس,منبع تغذیه,چوک آداپتور ترانس مبدل dc-dc منبع تغذیه چوک آداپتور صنعتی ادامه دسته‌بندی لوازم جانبی ,لوازم تلفنی , روشنایی ,آهنربا چراق قوه و اضطراری ترازو دیجیتال گجت لوازم تلفنی قطعات جانبی لامپ ادامه دسته‌بندی ریموت کنترل , محصول GSM وRF , بی سیم ریموت کنترل Wifi کنترل SMS کنترل بی سیم ریموت لوازم جانبی کامپیوتری موس صفحه کلید(کیبرد) وبکم(WebCam) اسپیکر(speaker) هاب(Hub) تبدیلات کامپیوتری ادامه دسته‌بندی تجهیزات Weller و Erem هویه قلمی weller هویه تفنگیweller هویه شارژیweller هویه گازی weller هویه رومیزیweller لوازم جانبیweller ادامه دسته‌بندی *****فروش ویــــــــــــژه***** انواع آی سی انواع دیود انواع ماسفت انواع LED انواع پل دیود انواع کریستال ادامه دسته‌بندی میکروفن , بلندگو , قطعات صوتی USB/FM player بلندگو بازر هدست/هندزفری موسیقی پلیر اسپیکر شارژی ادامه دسته‌بندی انواع چسب , خمیر , گریس , لاک , رنگ چسب دو طرفه چسب عایق چسب برزنت/پارچه چسب برق چسب آلومینیوم چسب مسی ادامه دسته‌بندی اجناس ویترینی اجناس ویـترینی پیشنهاد
                                     ویژه ابزار دستی دم گرد پروسکیت 1PK-501D (دم گرد proskit مدل 1PK-501D) دم گرد پروسکیت 1PK-501D جهت مشاهده گالری بر روی تصاویر کلیک نمایید. دسته‌بندی: ابزار دستی کد محصول: 7064 امتیاز محصول: 700 موجود درانبار: ناموجود ۹,۲۲۳,۲۳۲ ریال ۸,۶۱۹,۸۴۳ ریال تعداد + - ناموجود مقایسه محصول دیدگاه، نقد وارد نمایید نقد و بررسی خصوصیات دیدگاه‌ها / نقدها ثبت دیدگاه حساب کاربری جهت ثبت دیدگاه نیاز به ورود به حساب کاربری می‌باشد، قبلا
                                         ثبت‌نام کرده‌اید ؟ وارد شوید ثبت نام ورود به حساب کاربر گرامی، دیدگاه شما پس از تایید تیم مدیریت جهت دیگر کاربران
-                                نمایش داده خواهد شد. شاید مورد نیازتان شود متر لیزری پروسکیت PROSKIT NT-6350 ۶۳,۹۱۰,۰۰۰ ریال افزودن به سبد خرید آچار فرانسه 6 اینچی ۴,۲۶۸,۰۰۰ ریال افزودن به سبد خرید تستر شبکه معمولی مدل ST-468 ۴,۸۵۰,۰۰۰ ریال افزودن به سبد خرید دستگاه بست کمربندی کش ۲۵,۰۵۳,۸۹۰ ریال ناموجود ست انبر قفلی دو تایی کوچک ۱۵,۶۰۵,۶۱۶ ریال ناموجود پانچ مخابراتی ضربه ای پروسکیت CP-3152 ۶۲,۰۷۷,۵۶۳ ریال ناموجود کابل لخت کن کواکسیال پروسکیت cp-521 ۱۴,۳۰۰,۰۰۰ ریال افزودن به سبد خرید ست آچار بکس پروسکیت 8PK-SD016 ۴۴,۱۴۱,۵۶۷ ریال ناموجود سیم لخت کن پروسکیت 8pk-3162 ۱۵,۶۳۱,۹۴۸ ریال ناموجود ست آلن 7 تایی پروسکیت 8PK-022 ۷,۰۴۴,۸۲۵ ریال ناموجود پرفروش DMV32 ۸۵۸,۰۹۷ ریال سون سگمنت کاتد 100x140 میلی متر 0 ریال BUX98A ۱۱,۳۴۶,۰۲۷ ریال 22UF/25V smd TAN D ۴۰۶,۳۶۰ ریال مقاومت 1.5 مگا اهم پکیج 1206 SMD رول 5000 عددی ۲۶,۸۱۲,۵۰۰ ریال تخفیف‌های ویژه با عضویت در وبسایت از تخفیف‌های ویژه برخوردار خواهید شد، کدهای تخفیف تنها برای اعضا گرانقدر
+                                نمایش داده خواهد شد. شاید مورد نیازتان شود متر لیزری پروسکیت PROSKIT NT-6350 ۶۳,۹۱۰,۰۰۰ ریال افزودن به سبد خرید آچار فرانسه 6 اینچی ۴,۲۶۸,۰۰۰ ریال افزودن به سبد خرید تستر شبکه معمولی مدل ST-468 ۴,۸۵۰,۰۰۰ ریال افزودن به سبد خرید دستگاه بست کمربندی کش ۲۵,۰۵۳,۸۹۰ ریال ناموجود ست انبر قفلی دو تایی کوچک ۱۵,۶۰۵,۶۱۶ ریال ناموجود پانچ مخابراتی ضربه ای پروسکیت CP-3152 ۶۲,۰۷۷,۵۶۳ ریال ناموجود کابل لخت کن کواکسیال پروسکیت cp-521 ۱۴,۳۰۰,۰۰۰ ریال افزودن به سبد خرید ست آچار بکس پروسکیت 8PK-SD016 ۴۴,۱۴۱,۵۶۷ ریال ناموجود سیم لخت کن پروسکیت 8pk-3162 ۱۵,۶۳۱,۹۴۸ ریال ناموجود ست آلن 7 تایی پروسکیت 8PK-022 ۷,۰۴۴,۸۲۵ ریال ناموجود پرفروش DMV32 ۸۵۸,۰۹۷ ریال سون سگمنت کاتد 100x140 میلی متر 0 ریال BUX98A ۱۱,۳۴۶,۰۲۷ ریال 22UF/25V smd TAN D ۴۰۶,۳۶۰ ریال مقاومت 8.2 کیلو اهم پکیج 0805 SMD رول 5000 عددی ۱۷,۲۵۶,۲۵۰ ریال تخفیف‌های ویژه با عضویت در وبسایت از تخفیف‌های ویژه برخوردار خواهید شد، کدهای تخفیف تنها برای اعضا گرانقدر
                         وبسایت ارسال خواهد شد. دارای مجوز تمامی كالاها، دارای مجوزهای لازم از مراجع مربوطه مي‌باشند و فعایت فروشگاه تابع قوانين جمهوری
                         اسلامی ايران است. اطلاعات تماس اصفهان خیابان طالقانی پاساژ پوریای ولی طبقه همکف فروشگاه محمد الکترونیک ۰۳۱−۳۲۳۷۲۷۶۷ merqc.shop@gmail.com تماس با ما فروشگاه محمد الکترونیک نحوه ارسال حریم شخصی کاربران قوانین مختصری از MERQC فروشگاه محمد الکترونیک با حدود یک دهه سابقه در زمینه تهیه و توزیع  قطعات الکترونیک , رباتیک , ابزار دقیق , انواع باتری و ... به صورت عمده و خرده در بازار سنتی جهت رفاه هرچه بیشتر مشتریان و هم گام بودن با تکنولوژی تصمیم به راه اندازی فروشگاه اینترنتی با قابلیت خرید آنلاین و ارسال سفارشات نموده است. تمامی حقوق مادی و معنوی این وبسایت مربوط به فروشگاه قطعات الکترونیک محمد الکترونیک می‌باشد</t>
         </is>
@@ -1540,10 +1525,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1554,7 +1539,7 @@
       <c r="B34" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>https://shop.qom-elec.ir/product/%d8%b3%d9%88%da%a9%d8%aa-%d9%85%d8%a7%d8%af%da%af%db%8c-886-type-c-%d8%b1%d9%88-%d9%be%d9%86%d9%84%db%8c-%d9%81%d9%84%d8%b2%db%8c-4-%d9%be%db%8c%d9%86/</t>
         </is>
@@ -1571,6 +1556,8 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1579,7 +1566,7 @@
       <c r="B35" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>https://shop.qom-elec.ir/product/%da%86%d8%b1%d8%a7%d8%ba-%d8%a7%d8%b6%d8%b7%d8%b1%d8%a7%d8%b1%db%8c-%da%86%d9%86%d8%af%d9%85%d9%86%d8%b8%d9%88%d8%b1%d9%87-%d8%ac%d8%b9%d8%a8%d9%87%d8%a7%d8%a8%d8%b2%d8%a7%d8%b1-%d8%af%d8%a7/</t>
         </is>
@@ -1591,11 +1578,13 @@
 						سریع، تلاش می‌کنیم تا تجربه‌ای ساده، مطمئن و حرفه‌ای را برای مشتریان خود فراهم کنیم. تنوع محصولات الکترونیکی و رباتیک ارسال سریع به سراسر کشور پشتیبانی تخصصی و مشاوره خرید قطعات با کیفیت و قیمت مناسب © تمامی حقوق برای فروشگاه تخصصی قم الکترونیک محفوظ می‌باشد. ورود به سیستم × ایمیل / شماره موبایل رمزعبور کد تایید مرا به خاطر بسپار ورود رمز عبور را فراموش کرده اید؟ ورود با کد یکبارمصرف ارسال مجدد کد یکبار مصرف (00: 120 ) آیا حساب کاربری ندارید؟ ثبت نام ایمیل / شماره موبایل کد تایید رمزعبور تایید رمز عبور بازنشانی رمزعبور ارسال مجدد کد یکبار مصرف (00: 120 ) برگشت به صفحه ورود به سایت شماره موبایل رمزعبور شماره موبایل کد تایید * کد تایید ثبت نام با ارسال پیامک به شماره موبایل ارسال مجدد کد یکبار مصرف (00: 120 ) ثبت نام با رمزعبور برگشت به صفحه ورود به سایت (+98) Iran برای خرید تعداد (سفارش عمده) لطفا قبل از ثبت سفارش با فروشگاه هماهنگ فرمایید. در صورتی‌که بدون هماهنگی سفارش ثبت شود و موجودی کالا کافی نباشد، مبلغ پرداختی پس از کسر کارمزدهای بانکی و مالیاتی به حساب شما بازگشت داده خواهد شد. × فروش حضوری این محصول فقط به صورت حضوری قابل خرید است. متوجه شدم</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1604,7 +1593,7 @@
       <c r="B36" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>https://shop.rngo.ir/Arduino-boards/%D8%A8%D8%B1%D8%AF-%D8%A2%D8%B1%D8%AF%D9%88%DB%8C%D9%86%D9%88-mega2560-r3</t>
         </is>
@@ -1619,10 +1608,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="F36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1633,7 +1622,7 @@
       <c r="B37" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>https://iecshop.ir/QC-PASS-LABEL-HOLOGRAM-120PCS</t>
         </is>
@@ -1656,10 +1645,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1670,7 +1659,7 @@
       <c r="B38" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>https://sparkeyelec.ir/product/%d9%85%d8%a7%da%98%d9%88%d9%84-%d8%a8%d9%84%d9%88%d8%aa%d9%88%d8%ab-hc-05/</t>
         </is>
@@ -1689,10 +1678,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1703,14 +1692,14 @@
       <c r="B39" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>https://donya-ic.ir/shop/10uf-450v/</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10UF-450V | فروشگاه قطعات الکترونیک دنیا آی سی پرش به ناوبری پرش به محتوا به فروشگاه قطعات الکترونیکی دنیا آی سی خوش آمدید. شماره تماس  : 66755300-021, 66739752-021 واردات قطعات الکترونیک مدارات مجتمع ( آی سی ) ترانزیستور، دیود، تایریستور، پل دیود قطعات مایکرویووی فرکانس بالا قطعات پسیو (مقاومت، خازن، سلف …) نمایشگر، LED انواع کانکتور و پین هدر رله، کلید، سوییچ و کیپد دنیا آی سی واردات قطعات الکترونیک فروشگاه درباره ما تماس با ما واتساپ 09191775116 ایمیل: info@donya-ic.ir براساس دسته بندی ها جستجو برای: همه دسته بندی ها سایر محصولات مدارات مجتمع ( آی سی ) ترانزیستور، دیود، تایریستور، پل دیود قطعات مایکرویووی فرکانس بالا نمایشگر، LED قطعات پسیو (مقاومت، خازن، سلف …) رله ماسفت ماژول ای جی بی تی مشتری قبلی هستید؟ وارد شوید حساب کاربری ندارید؟ ثبت نام 0 ۰ تومان سبد خرید شما خالی است. واردات قطعات الکترونیک مدارات مجتمع ( آی سی ) ترانزیستور، دیود، تایریستور، پل دیود قطعات مایکرویووی فرکانس بالا قطعات پسیو (مقاومت، خازن، سلف …) نمایشگر، LED انواع کانکتور و پین هدر رله، کلید، سوییچ و کیپد جستجو جستجو برای: جستجو 0 خانه فروشگاه قطعات پسیو (مقاومت، خازن، سلف …) 10UF-450V این محصول نیاز به استعلام برای تایید قیمت دارد قطعات پسیو (مقاومت، خازن، سلف …) 10UF-450V موجودی: 50 در انبار خازن الکترولیت 10 میکرو فاراد 450 ولت از خانواده خازن الکترولیت dip می‌باشد. ۲۸,۰۰۰ تومان 50 در انبار تعداد افزودن به سبد خرید نقد و بررسی بر اساس 0 نقد و بررسی 0.0 در مجموع 0 0 0 0 0 اولین نفر در نقد و بررسی “10UF-450V” لغو پاسخ امتیاز شما امتیاز … عالی خوب متوسط بد نیست خیلی ضعیف نقد و بررسی شما نام * آدرس ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. هنوز هیچ نقدی وجود ندارد. محصولات مشابه قطعات پسیو (مقاومت، خازن، سلف …) 220UF_300v قطعات پسیو (مقاومت، خازن، سلف …) 220UF_300v 0 از 5 (0) کدمحصول: n/a ۵۵,۷۰۰ تومان اطلاعات بیشتر قطعات پسیو (مقاومت، خازن، سلف …) 15KR_603 قطعات پسیو (مقاومت، خازن، سلف …) 15KR_603 0 از 5 (0) مقاومت 15کیلو اهم سایز 603 تعداد سفارش 100عدد می باشد کدمحصول: n/a ۳۰ تومان افزودن به سبد خرید قطعات پسیو (مقاومت، خازن، سلف …) 470UF_35V قطعات پسیو (مقاومت، خازن، سلف …) 470UF_35V 0 از 5 (0) خازن الکترولیت 470میکرو فاراد 35ولت_دیپ کدمحصول: n/a ۱۹,۷۰۰ تومان افزودن به سبد خرید قطعات پسیو (مقاومت، خازن، سلف …) 470UF_25V قطعات پسیو (مقاومت، خازن، سلف …) 470UF_25V 0 از 5 (0) 470میکروفاراد 25ولت الکترولیت می باشد. کدمحصول: n/a ۱۰,۷۰۰ تومان افزودن به سبد خرید دسته‌های محصولات ترانزیستور، دیود، تایریستور، پل دیود رله سایر محصولات قطعات پسیو (مقاومت، خازن، سلف …) قطعات مایکرویووی فرکانس بالا ماژول ای جی بی تی ماژول ای حی بی تی ماسفت مدارات مجتمع ( آی سی ) نمایشگر، LED جستجو برای: جستجو محصولات شاخص WF24LTYAJDNN0 ۲۸۶,۰۰۰ تومان LHA-83W+ ۲۳۸,۰۰۰ تومان محصولات حراجی برد مدل 3386 ۵ تومان ۱۴,۹۷۰,۰۰۰ تومان IRFL110 ۲۰,۷۰۰ تومان ۲۲,۷۰۰ تومان 1K2102DW ۸۳,۵۰۰ تومان ۸۷,۵۰۰ تومان محصولات پر امتیاز HT46R23 نمره 5.00 از 5 ۷۹,۷۰۰ تومان TPA3251 نمره 5.00 از 5 ۴۱۷,۰۰۰ تومان STA540SA نمره 5.00 از 5 ۵۷,۰۰۰ تومان سوال دارید؟ با ما تماس بگیرید 7 روز هفته 24 ساعته! 021-66755300 , 021-66739752 , 09191775116 اطلاعات تماس دفتر تهران : خیابان جمهوری - نرسیده به پل حافظ - ساختمان آلمینیوم - طبقه 3 شمالی- واحد 302 فعالیت دنیا آی سی تیم دنیا آی سی متشکل از گروهی جوان و با انگیزه با هدف تهیه و تامین انواع قطعات الکترونیکی و مخابراتی و ارائه آن به مراکز صنعت الکترونیک و مخابرات کشور می باشد. این مجموعه با تعاملاتی که در سراسر دنیا از جمله چین ، آمریکا و اروپا دارد می تواند به سرعت تمامی قطعات الکترونیکی شما را از بازار خارج تهیه نماید. آشنایی با میکروکنترلرهای AVR و انواع آن تکنولوژی RFID چیست؟ تاریخچه ای از ساخت و پیدایش میکروکنترلرها دیود چیست؟ و چه کاربردی دارد؟ واردات قطعات الکترونیک ( آمریکا و چین ) فروش آی سی کمیاب © فروش قطعات الکترونیک دنیا آی سی فعالیت دنیا آی سی تیم دنیا آی سی متشکل از گروهی جوان و با انگیزه با هدف تهیه و تامین انواع قطعات الکترونیکی و مخابراتی و ارائه آن به مراکز صنعت الکترونیک و مخابرات کشور می باشد. این مجموعه با تعاملاتی که در سراسر دنیا از جمله چین ، آمریکا و اروپا دارد می تواند به سرعت تمامی قطعات الکترونیکی شما را از بازار خارج تهیه نماید. آدرس دفتر تهران دفتر تهران : خیابان جمهوری - نرسیده به پل حافظ - ساختمان آلمینیوم - طبقه 3 شمالی- واحد 302 سوال دارید؟ با ما تماس بگیرید 7 روز هفته 24 ساعته! 021-66755300 , 021-66739752 , 09191775116 قیمت محصولات فروشگاه به دلیل نوسانات ارزی متغیر می باشد. لطفا قبل از ثبت سفارش استعلام قیمت نمایید. رد کردن</t>
+          <t>10UF-450V | فروشگاه قطعات الکترونیک دنیا آی سی پرش به ناوبری پرش به محتوا به فروشگاه قطعات الکترونیکی دنیا آی سی خوش آمدید. شماره تماس  : 66755300-021, 66739752-021 واردات قطعات الکترونیک مدارات مجتمع ( آی سی ) ترانزیستور، دیود، تایریستور، پل دیود قطعات مایکرویووی فرکانس بالا قطعات پسیو (مقاومت، خازن، سلف …) نمایشگر، LED انواع کانکتور و پین هدر رله، کلید، سوییچ و کیپد دنیا آی سی واردات قطعات الکترونیک فروشگاه درباره ما تماس با ما واتساپ 09191775116 ایمیل: info@donya-ic.ir براساس دسته بندی ها جستجو برای: همه دسته بندی ها سایر محصولات مدارات مجتمع ( آی سی ) ترانزیستور، دیود، تایریستور، پل دیود قطعات مایکرویووی فرکانس بالا نمایشگر، LED قطعات پسیو (مقاومت، خازن، سلف …) رله ماسفت ماژول ای جی بی تی مشتری قبلی هستید؟ وارد شوید حساب کاربری ندارید؟ ثبت نام 0 ۰ تومان سبد خرید شما خالی است. واردات قطعات الکترونیک مدارات مجتمع ( آی سی ) ترانزیستور، دیود، تایریستور، پل دیود قطعات مایکرویووی فرکانس بالا قطعات پسیو (مقاومت، خازن، سلف …) نمایشگر، LED انواع کانکتور و پین هدر رله، کلید، سوییچ و کیپد جستجو جستجو برای: جستجو 0 خانه فروشگاه قطعات پسیو (مقاومت، خازن، سلف …) 10UF-450V این محصول نیاز به استعلام برای تایید قیمت دارد قطعات پسیو (مقاومت، خازن، سلف …) 10UF-450V موجودی: 50 در انبار خازن الکترولیت 10 میکرو فاراد 450 ولت از خانواده خازن الکترولیت dip می‌باشد. ۲۸,۰۰۰ تومان 50 در انبار تعداد افزودن به سبد خرید نقد و بررسی بر اساس 0 نقد و بررسی 0.0 در مجموع 0 0 0 0 0 اولین نفر در نقد و بررسی “10UF-450V” لغو پاسخ امتیاز شما امتیاز … عالی خوب متوسط بد نیست خیلی ضعیف نقد و بررسی شما نام * آدرس ایمیل * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. هنوز هیچ نقدی وجود ندارد. محصولات مشابه قطعات پسیو (مقاومت، خازن، سلف …) 47UH-3A قطعات پسیو (مقاومت، خازن، سلف …) 47UH-3A 0 از 5 (0) سلف47مبکرو هانری 3امپر کدمحصول: n/a ۵,۷۰۰ تومان افزودن به سبد خرید قطعات پسیو (مقاومت، خازن، سلف …) 1MR_1206 قطعات پسیو (مقاومت، خازن، سلف …) 1MR_1206 0 از 5 (0) کدمحصول: n/a ۶۴ تومان افزودن به سبد خرید قطعات پسیو (مقاومت، خازن، سلف …) 22UF 6.3V قطعات پسیو (مقاومت، خازن، سلف …) 22UF 6.3V 0 از 5 (0) 22UF  16V  Size D کدمحصول: n/a ۹,۷۰۰ تومان افزودن به سبد خرید قطعات پسیو (مقاومت، خازن، سلف …) R0 قطعات پسیو (مقاومت، خازن، سلف …) R0 0 از 5 (0) مقاومت 0 اهم smd کدمحصول: n/a ۶۰ تومان – ۱۰۰ تومان انتخاب گزینه ها این محصول دارای انواع مختلفی می باشد. گزینه ها ممکن است در صفحه محصول انتخاب شوند دسته‌های محصولات ترانزیستور، دیود، تایریستور، پل دیود رله سایر محصولات قطعات پسیو (مقاومت، خازن، سلف …) قطعات مایکرویووی فرکانس بالا ماژول ای جی بی تی ماژول ای حی بی تی ماسفت مدارات مجتمع ( آی سی ) نمایشگر، LED جستجو برای: جستجو محصولات شاخص WF24LTYAJDNN0 ۲۸۶,۰۰۰ تومان LHA-83W+ ۲۳۸,۰۰۰ تومان محصولات حراجی برد مدل 3386 ۵ تومان ۱۴,۹۷۰,۰۰۰ تومان IRFL110 ۲۰,۷۰۰ تومان ۲۲,۷۰۰ تومان 1K2102DW ۸۳,۵۰۰ تومان ۸۷,۵۰۰ تومان محصولات پر امتیاز STA540SA نمره 5.00 از 5 ۵۷,۰۰۰ تومان HT46R23 نمره 5.00 از 5 ۷۹,۷۰۰ تومان TPA3251 نمره 5.00 از 5 ۴۱۷,۰۰۰ تومان سوال دارید؟ با ما تماس بگیرید 7 روز هفته 24 ساعته! 021-66755300 , 021-66739752 , 09191775116 اطلاعات تماس دفتر تهران : خیابان جمهوری - نرسیده به پل حافظ - ساختمان آلمینیوم - طبقه 3 شمالی- واحد 302 فعالیت دنیا آی سی تیم دنیا آی سی متشکل از گروهی جوان و با انگیزه با هدف تهیه و تامین انواع قطعات الکترونیکی و مخابراتی و ارائه آن به مراکز صنعت الکترونیک و مخابرات کشور می باشد. این مجموعه با تعاملاتی که در سراسر دنیا از جمله چین ، آمریکا و اروپا دارد می تواند به سرعت تمامی قطعات الکترونیکی شما را از بازار خارج تهیه نماید. آشنایی با میکروکنترلرهای AVR و انواع آن تکنولوژی RFID چیست؟ تاریخچه ای از ساخت و پیدایش میکروکنترلرها دیود چیست؟ و چه کاربردی دارد؟ واردات قطعات الکترونیک ( آمریکا و چین ) فروش آی سی کمیاب © فروش قطعات الکترونیک دنیا آی سی فعالیت دنیا آی سی تیم دنیا آی سی متشکل از گروهی جوان و با انگیزه با هدف تهیه و تامین انواع قطعات الکترونیکی و مخابراتی و ارائه آن به مراکز صنعت الکترونیک و مخابرات کشور می باشد. این مجموعه با تعاملاتی که در سراسر دنیا از جمله چین ، آمریکا و اروپا دارد می تواند به سرعت تمامی قطعات الکترونیکی شما را از بازار خارج تهیه نماید. آدرس دفتر تهران دفتر تهران : خیابان جمهوری - نرسیده به پل حافظ - ساختمان آلمینیوم - طبقه 3 شمالی- واحد 302 سوال دارید؟ با ما تماس بگیرید 7 روز هفته 24 ساعته! 021-66755300 , 021-66739752 , 09191775116 قیمت محصولات فروشگاه به دلیل نوسانات ارزی متغیر می باشد. لطفا قبل از ثبت سفارش استعلام قیمت نمایید. رد کردن</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1718,10 +1707,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1732,7 +1721,7 @@
       <c r="B40" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>https://rizsmd.com/product/zener-2-4v-minimelf-smd/</t>
         </is>
@@ -1747,6 +1736,8 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1755,7 +1746,7 @@
       <c r="B41" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="15" t="inlineStr">
         <is>
           <t>https://kavirelectronic.ir/eshop/e-paper-2-66-inch/1202051-epd-e-paper-266-inch-152x296-pixel-ssd1680-black-white-red.html</t>
         </is>
@@ -1775,10 +1766,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="F41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1804,10 +1795,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
+      <c r="F42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1818,14 +1809,14 @@
       <c r="B43" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>https://shop.sisoog.com/product/eg800qeulc-lte-cat-1-bis-module/</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>خرید، قیمت و بررسی ماژول EG800QEULC LTE Cat 1 bis کویکتل | شاپ سیسوگ رفتن به محتوا بدون نتیجه خانه فروشگاه تماس با ما درباره ما فروشگاه سیسوگ فروشگاه سیسوگ خانه فروشگاه تماس با ما درباره ما سبد خرید 0 تومان 0 Search Login Search سبد خرید 0 تومان 0 Login Menu خانه » فروشگاه » ماژول EG800QEULC LTE Cat 1 bis کویکتل 🔍 ماژول EG800QEULC LTE Cat 1 bis کویکتل 1,305,000 تومان ماژول EG800QEULC LTE Cat 1 bis کوچک برای IoT با سرعت ۱۰/۵ مگابیت، DFOTA و Wi-Fi Scan موجود در انبار ماژول EG800QEULC LTE Cat 1 bis کویکتل عدد افزودن به سبد خرید شناسه محصول: AT1051 دسته: LTE CAT1 برند: Quectel توضیحات نظرات (0) معرفی ماژول EG800QEULC کویکتل ماژول Quectel EG800QEULC از سری EG800Q، یک ماژول LTE Cat 1 bis پیشرفته است که به‌طور خاص برای کاربردهای M2M و IoT بهینه‌سازی شده است. این ماژول بر پایه استاندارد 3GPP Rel-14 توسعه یافته و حداکثر سرعت ۱۰ مگابیت بر ثانیه در دانلود و ۵ مگابیت بر ثانیه در آپلود را ارائه می‌دهد. EG800QEULC با فرم‌فکتور LGA فشرده و یکپارچه طراحی شده و از آنتن تک و رابط‌های استاندارد صنعتی بهره می‌برد. این سری با حکاکی لیزری تولید می‌شود و ظاهر شیک، مقاومت مکانیکی بالا، دفع حرارت مناسب و برچسب‌گذاری بادوام دارد که آن را برای تولید انبوه مناسب می‌سازد. سری EG800Q شامل دو واریانت اصلی است: EG800Q-EU EG800Q-NA پشتیبانی از مجموعه گسترده‌ای از پروتکل‌های اینترنتی، رابط‌های صنعتی و درایورهای USB برای سیستم‌عامل‌های Windows 8.1/10/11، Linux و Android باعث شده این ماژول برای طیف وسیعی از کاربردها مناسب باشد. از جمله مهم‌ترین کاربردهای آن می‌توان به مدیریت دارایی‌ها، telematics تجاری، پرداخت‌های هوشمند، کنترل دسترسی از راه دور (RMAC)، ایمنی هوشمند، اتوماسیون، کنتورهای هوشمند و شبکه برق هوشمند اشاره کرد. مشخصات فنی ماژول EG800QEULC دسته‌بندی پارامتر توضیحات پارت نامبر EG800QEULC-N03-SNNSA – سیم‌کارت رابط USIM پشتیبانی از یک سیم‌کارت UART ۳ رابط (اصلی، دیباگ و کمکی) USB 2.0 یک پورت High Speed رابط‌ها Digital Audio (PCM) یک رابط (Optional) ADC ۲ عدد NET_STATUS یک پایه آنتن یک آنتن اصلی کنترل RESET_N یک پایه PWRKEY یک پایه USB_BOOT یک پایه ویژگی‌های پیشرفته DFOTA به‌روزرسانی از راه دور (پشتیبانی کامل) Wi-Fi Scan پشتیبانی تشخیص سیم‌کارت پشتیبانی I2C یک رابط Quectel Enhanced AT Commands پشتیبانی نرم‌افزار پروتکل‌ها TCP/UDP/PPP/HTTP/MQTT/HTTPS/FTPS/SSL/NTP و پروتکل‌های دیگر درایور RIL Android 4.x تا 13.x درایورهای USB USB RNDIS Windows 8.1/10/11 و Linux USB ECM Linux USB Serial Windows 8.1/10/11، Linux، Android ویژگی‌های الکتریکی ولتاژ تغذیه ۳.۳ تا ۴.۳ ولت (معمول ۳.۸ ولت) مصرف توان Sleep Mode: حدود ۰.۰۶ میلی‌آمپر Idle Mode (USB disconnected): حدود ۴.۵۰ میلی‌آمپر ابعاد و وزن ابعاد ۱۷.۷ × ۱۵.۸ × ۲.۴ میلی‌متر دما دمای عملیاتی -۳۵°C تا +۷۵°C (Extended: -۴۰°C تا +۸۵°C) دانلود Quectel EG800Q Series LTE Standard Specification دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “ماژول EG800QEULC LTE Cat 1 bis کویکتل” لغو پاسخ نشانی ایمیل شما منتشر نخواهد شد. بخش‌های موردنیاز علامت‌گذاری شده‌اند * امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف نام * ایمیل * دیدگاه شما * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. ثبت Δ محصولات مشابه ماژول EC200U-EU AA LTE 4G CAT1 GNSS BT Quectel کویکتل 2,004,000 تومان LTE CAT1 افزودن به سبد خرید ماژول EG915U-EU AB 4G+2G CAT1 Bluetooth Quectel کویکتل 1,935,000 تومان LTE CAT1 افزودن به سبد خرید موجودی به پایان رسید ماژول EC200U-EU MiniPCIe LTE / GPS کویکتل 2,766,000 تومان LTE CAT1 اطلاعات بیشتر ماژول EG810MEULA Cat1 bis VoLTE کویکتل 1,234,000 تومان LTE CAT1 افزودن به سبد خرید موجودی به پایان رسید ماژول EC21-E Mini PCIe Quectel کویکتل 8,170,000 تومان LTE CAT1 اطلاعات بیشتر ماژول SLM320E LTE CAT1 + GPS/BT – MeiG 1,929,000 تومان LTE CAT1 افزودن به سبد خرید ماژول EG810MEULC LTE Cat 1 bis کویکتل 1,157,100 تومان LTE CAT1 افزودن به سبد خرید ماژول EC200U AB LTE 4G CAT1 Quectel کویکتل 1,935,000 تومان LTE CAT1 افزودن به سبد خرید فروشگاه سیسوگ قوانین و مقررات استرداد وجه نحوه ارسال کالا نحوه پرداخت خدمات پس از فروش اطلاع رسانی : همراهان گرامی، فروشگاه فعال بوده و موجودی تمامی محصولات به روز می باشد. Got it! X</t>
+          <t>خرید، قیمت و بررسی ماژول EG800QEULC LTE Cat 1 bis کویکتل | شاپ سیسوگ رفتن به محتوا بدون نتیجه خانه فروشگاه تماس با ما درباره ما فروشگاه سیسوگ فروشگاه سیسوگ خانه فروشگاه تماس با ما درباره ما سبد خرید 0 تومان 0 Search Login Search سبد خرید 0 تومان 0 Login Menu خانه » فروشگاه » ماژول EG800QEULC LTE Cat 1 bis کویکتل 🔍 ماژول EG800QEULC LTE Cat 1 bis کویکتل 1,305,000 تومان ماژول EG800QEULC LTE Cat 1 bis کوچک برای IoT با سرعت ۱۰/۵ مگابیت، DFOTA و Wi-Fi Scan موجود در انبار ماژول EG800QEULC LTE Cat 1 bis کویکتل عدد افزودن به سبد خرید شناسه محصول: AT1051 دسته: LTE CAT1 برند: Quectel توضیحات نظرات (0) معرفی ماژول EG800QEULC کویکتل ماژول Quectel EG800QEULC از سری EG800Q، یک ماژول LTE Cat 1 bis پیشرفته است که به‌طور خاص برای کاربردهای M2M و IoT بهینه‌سازی شده است. این ماژول بر پایه استاندارد 3GPP Rel-14 توسعه یافته و حداکثر سرعت ۱۰ مگابیت بر ثانیه در دانلود و ۵ مگابیت بر ثانیه در آپلود را ارائه می‌دهد. EG800QEULC با فرم‌فکتور LGA فشرده و یکپارچه طراحی شده و از آنتن تک و رابط‌های استاندارد صنعتی بهره می‌برد. این سری با حکاکی لیزری تولید می‌شود و ظاهر شیک، مقاومت مکانیکی بالا، دفع حرارت مناسب و برچسب‌گذاری بادوام دارد که آن را برای تولید انبوه مناسب می‌سازد. سری EG800Q شامل دو واریانت اصلی است: EG800Q-EU EG800Q-NA پشتیبانی از مجموعه گسترده‌ای از پروتکل‌های اینترنتی، رابط‌های صنعتی و درایورهای USB برای سیستم‌عامل‌های Windows 8.1/10/11، Linux و Android باعث شده این ماژول برای طیف وسیعی از کاربردها مناسب باشد. از جمله مهم‌ترین کاربردهای آن می‌توان به مدیریت دارایی‌ها، telematics تجاری، پرداخت‌های هوشمند، کنترل دسترسی از راه دور (RMAC)، ایمنی هوشمند، اتوماسیون، کنتورهای هوشمند و شبکه برق هوشمند اشاره کرد. مشخصات فنی ماژول EG800QEULC دسته‌بندی پارامتر توضیحات پارت نامبر EG800QEULC-N03-SNNSA – سیم‌کارت رابط USIM پشتیبانی از یک سیم‌کارت UART ۳ رابط (اصلی، دیباگ و کمکی) USB 2.0 یک پورت High Speed رابط‌ها Digital Audio (PCM) یک رابط (Optional) ADC ۲ عدد NET_STATUS یک پایه آنتن یک آنتن اصلی کنترل RESET_N یک پایه PWRKEY یک پایه USB_BOOT یک پایه ویژگی‌های پیشرفته DFOTA به‌روزرسانی از راه دور (پشتیبانی کامل) Wi-Fi Scan پشتیبانی تشخیص سیم‌کارت پشتیبانی I2C یک رابط Quectel Enhanced AT Commands پشتیبانی نرم‌افزار پروتکل‌ها TCP/UDP/PPP/HTTP/MQTT/HTTPS/FTPS/SSL/NTP و پروتکل‌های دیگر درایور RIL Android 4.x تا 13.x درایورهای USB USB RNDIS Windows 8.1/10/11 و Linux USB ECM Linux USB Serial Windows 8.1/10/11، Linux، Android ویژگی‌های الکتریکی ولتاژ تغذیه ۳.۳ تا ۴.۳ ولت (معمول ۳.۸ ولت) مصرف توان Sleep Mode: حدود ۰.۰۶ میلی‌آمپر Idle Mode (USB disconnected): حدود ۴.۵۰ میلی‌آمپر ابعاد و وزن ابعاد ۱۷.۷ × ۱۵.۸ × ۲.۴ میلی‌متر دما دمای عملیاتی -۳۵°C تا +۷۵°C (Extended: -۴۰°C تا +۸۵°C) دانلود Quectel EG800Q Series LTE Standard Specification دیدگاهها هیچ دیدگاهی برای این محصول نوشته نشده است. اولین نفری باشید که دیدگاهی را ارسال می کنید برای “ماژول EG800QEULC LTE Cat 1 bis کویکتل” لغو پاسخ نشانی ایمیل شما منتشر نخواهد شد. بخش‌های موردنیاز علامت‌گذاری شده‌اند * امتیاز شما * امتیاز دهید… عالی خوب متوسط نه خیلی بد خیلی ضعیف نام * ایمیل * دیدگاه شما * ذخیره نام، ایمیل و وبسایت من در مرورگر برای زمانی که دوباره دیدگاهی می‌نویسم. ثبت Δ محصولات مشابه ماژول SLM320E LTE CAT1 – MeiG 1,726,000 تومان LTE CAT1 افزودن به سبد خرید ماژول SLM320E LTE CAT1 + GPS/BT – MeiG 1,929,000 تومان LTE CAT1 افزودن به سبد خرید ماژول EG915U-EU AB 4G+2G CAT1 Bluetooth Quectel کویکتل 1,935,000 تومان LTE CAT1 افزودن به سبد خرید موجودی به پایان رسید ماژول EG800AK-EULG 4G CAT1 only + GPS Quectel کویکتل 1,208,000 تومان LTE CAT1 اطلاعات بیشتر ماژول EC200U-EU AA LTE 4G CAT1 GNSS BT Quectel کویکتل 2,004,000 تومان LTE CAT1 افزودن به سبد خرید ماژول SLM336E LTE CAT1 برند MeiG 1,693,000 تومان LTE CAT1 افزودن به سبد خرید ماژول EG810MEULA Cat1 bis VoLTE کویکتل 1,234,000 تومان LTE CAT1 افزودن به سبد خرید موجودی به پایان رسید ماژول EC200U-EU MiniPCIe LTE / GPS کویکتل 2,766,000 تومان LTE CAT1 اطلاعات بیشتر فروشگاه سیسوگ قوانین و مقررات استرداد وجه نحوه ارسال کالا نحوه پرداخت خدمات پس از فروش اطلاع رسانی : همراهان گرامی، فروشگاه فعال بوده و موجودی تمامی محصولات به روز می باشد. Got it! X</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1833,10 +1824,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="F43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1847,7 +1838,7 @@
       <c r="B44" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>https://iran-micro.com/%D8%A2%D9%85%D9%BE%D8%B1-%D9%85%D8%AA%D8%B1-%D8%B9%D9%82%D8%B1%D8%A8%D9%87-%D8%A7%DB%8C-%D8%A2%D9%86%D8%A7%D9%84%D9%88%DA%AF-500-%D9%85%DB%8C%D9%84%DB%8C-%D8%A2%D9%85%D9%BE%D8%B1-500ma-dc</t>
         </is>
@@ -1865,10 +1856,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
+      <c r="F44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1879,14 +1870,14 @@
       <c r="B45" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>https://www.microele.com/power-connector/430251000p3mmmolex.html</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>430251000,P3mm,Molex در صورت هر گونه مشکل در روند ثبت سفارش با شماره 09134722518 تماس بگیرید ورود | ثبت نام منو تنظیمات جستجو برای محصولات بیشتر کلیک کنید. هیچ محصولی یافت نشد. 0 آیتم - 0 ریال سبد خرید شما خالی است. دسته‌بندی‌ها ماژول ها RF GSM/GPRS RFID 3G ISM ZIGBEE BLUETOOTH WIFI RF BOOSTER GPS/GLONASS FM Radio NB-IoT 4G Audio CAMERA CONVERTOR DC-DC INTERFACE AUDIO Amplifier Players/Recorder Clock &amp; Timer RTC TIMER Memories SD &amp; Micro SD Electromechanic Relay Measurement Distance Voltage GAS LOAD ANGEL Humid&amp;Temprature Bio-metric Finger Analog A2D Ultra Sonic Humidifier Motion PIR مخابراتی و آر اف ANTENNA GSM GPS WIFI UHF 3G Remote Controller Fixed Code Learning Reciver نیمه هادی ها IC microcontrollers FPGA Logic IC Analog IC Voltage Reference eprom Flash Regulators PMIC Interface Step-Down Converter leds-optoelectronics Led Block Led Strip led Led Leans Laser LED Series sensors-transducers Light temprature Encoders Image Sensors, Camera Magnetic Motion Sensors Humidity Vibration Sensor Diode Rectifier Schottky Zener Fast Transistor BJT RFBJT MOSFET ISOLATOR OPTO ISOLATOR TRIAC &amp; SCR Thyristor Signal Thyristor Thyristor TVS DIODS تغذیه و محافظ مدار Batterys Nickel-Cadmium (NiCd) Nikel-Metal (NiMH) Li-Polimer Li-Ion Alkaline Lithium Zinc-Carbon Battery Mangment Battery charger Circuit protection Battery protection Power supply Switching Power Supply POWER CONTROL Adapter USB Charger led Drivers Circuit Board الکترومکانیک Key Pad Flat Keypad Other KeyPad switchs Micro Switch Dip Switch AUDIO Speaker Buzzer Microphone Relay Power Relay کانکتور و سوکت ها IC socket ZIF Socket SMD Adaptor Coaxial connectors SMA UFL BNC MCX MMCX Ntype SMB UHF TS9 Headers &amp; Wire Housings PIN HEADER XH Connector Circuit connectors PTR DC JACK Push Connectors Terminals ATX Audio connectors phone jack Power connectors Battery FUSE Power pluggable-connectors sata PS2 usb connectors Type A Type B Memory Connectors MMC/SD/uSD SIMCARD SMART CARD سیم و کابل Shielded wire RG AC Power نمایشگرها LCD Character graphic TFT LCD نوسان سازها Crystals KHz MHz قطعات غیر فعال الکترونیکی Capacitors Electrolytic Tantalum Ceramic Polyester Supercaps Resistors Thick Film Inductors, Coils, Choks Fixed Inductors Thermal-management Heat-sinks Thermal-pads-sheets Circuite Protection Fuse بردهای توسعه Evaluation Boards GSM GPS Raspberry pi Raspberry Boards Raspberry accessory Orange Pi Orange Pi Boards Arduino Arduino Boards Arduino Shields Arduino Accessories STM جعبه ها Plastic Box Plastic profile Plastic Box Metal Box Aluminum Profile Spacer &amp; Screw ابزار Laboratory Instruments multimeters Bread Board Soldering Workshop tools BreadBoard Crimping tool bnc Crimping Network محصولات ماژول ها RF CAMERA CONVERTOR AUDIO Clock &amp; Timer Memories Electromechanic Measurement Bio-metric Analog Ultra Sonic Motion تغذیه و محافظ مدار Batterys Battery Mangment Circuit protection Power supply led Drivers مخابراتی و آر اف ANTENNA Remote Controller نیمه هادی ها IC leds-optoelectronics sensors-transducers Diode Transistor ISOLATOR TRIAC &amp; SCR Signal Thyristor TVS الکترومکانیک Key Pad switchs AUDIO Relay سیم و کابل Shielded wire کانکتور و سوکت ها IC socket Coaxial connectors Headers &amp; Wire Housings Circuit connectors Terminals Audio connectors Power connectors pluggable-connectors usb connectors Memory Connectors قطعات غیر فعال الکترونیکی Capacitors Resistors Inductors, Coils, Choks Thermal-management Circuite Protection نمایشگرها LCD بردهای توسعه Evaluation Boards Raspberry pi Orange Pi Arduino STM نوسان سازها Crystals جعبه ها Plastic Box Metal Box Spacer &amp; Screw ابزار Laboratory Instruments Workshop tools Crimping tool وبلاگ مونتاژ ماشینی بردهای الکترونیکی خانه &gt; کانکتور و سوکت ها &gt; Power connectors &gt; 430251000,P3mm,Molex جدید 430251000,P3mm,Molex کد محصول: 160501015 Connector Housings ATX,Molex ادامه مطلب نمایش کمتر 550,000 ریال بدون مالیات افزودن به سبد خرید اشتراک‌گذاری برای خرید عمده و دریافت قیمت ویژه این محصول، با ما تماس بگیرید: 03132373281 علاقه‌مندی 0 افزودن به لیست علاقه‌مندی‌ها افزودن به مقایسه 0 کد QR توضیحات جزئیات محصول نظرات توضیحات قطعه Molex 430251000 یک Micro-Fit 3.0 Receptacle Housing با فاصله پایه (Pitch) 3.00mm است. این کانکتور در رده‌ی Connector Housings قرار دارد و برای کاربردهای Wire-to-Board و Wire-to-Wire طراحی شده است ادامه مطلب نمایش کمتر جزئیات محصول مرجع 160501015 مشخصات پارت نامبر 430251000,P3mm,Molex رنگ مشکی نوع کاربرد Power, Wire-to-Board, Wire-to-Wire پکیج Receptacle Housing (سوکت مادگی) دمای کاری 40°C ~ 105°C- فاصله پین ها (mm) 3mm نظرات بدون نظر 14 محصولات مشابه در شاخه های مختلف: جک شارژ لپ تاپ SONY 47,000 ریال Jack charger,SONY,laptop افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی پین فیوز 35,400 ریال افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی جک آداپتوری DC 2.5mm 48,000 ریال قطر مغزی 2.5mm افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی ناموجود فیوز باکس 0 ریال مخصوص فیوز شیشه ای کوچک علاقه‌مندی مشاهده بیشتر علاقه‌مندی سوکت باطری سکه ای 2032 76,500 ریال سوکت باطری سکه ای افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی جک آداپتوری DC 2.1mm 48,900 ریال قطر مغزی 2.1mm افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی کانکتور بین راهی 2 پین SM 126,000 ریال 2Pin, 9cm,Femal, 22AWG افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی ناموجود ست کانکتور ضدآب 0.3*2 0 ریال 2PIN WATERPROOF CONNECTOR علاقه‌مندی مشاهده بیشتر علاقه‌مندی ناموجود ست کانکتور ضدآب 0.75*2 0 ریال 2PIN WATERPROOF CONNECTOR علاقه‌مندی مشاهده بیشتر علاقه‌مندی ناموجود جک شارژ لپ تاپ HP &amp; Acer 0 ریال Jack charger,HP,Acer,laptop علاقه‌مندی مشاهده بیشتر علاقه‌مندی جک شارژ لپ تاپ TOSHIBA 537,000 ریال Jack charger,TOSHIBA,laptop افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی جک آداپتوری روپانلی فلزی مدل DC-025M 304,000 ریال جک مخصوص آداپتور افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی ناموجود ست کانکتور ضدآب 0.5*4 0 ریال 4PIN WATERPROOF CONNECTOR علاقه‌مندی مشاهده بیشتر علاقه‌مندی جک آداپتوری روپانلی مدل DC-022 117,000 ریال جک مخصوص آداپتور افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی اطلاعات تماس با مایکروالکام آدرس اصفهان، خیابان طالقانی، نرسیده به چهارراه شمس آبادی، مجتمع الماس ،طبقه اول، واحد 103 تلفن 03132373281 آدرس ایمیل info[at]microele.com چرا مایکروالکام؟ پشتیبانی سریع و متنوع تنوع محصولات گارانتی بازگشت پرداخت امن کیفیت محصولات ثبت شکایت راهنمای کاربران چگونه خرید کنم؟ چگونه محصول را دریافت میکنم؟ رهگیری سفارش شماره حساب‌ها پرداخت آنلاین وجه دسترسی سریع وبلاگ مایکروالکام محصولات جدید محصولات پر فروش درباره مایکروالکام تماس با مایکروالکام مایکروالکام؛ تجربه‌ای بیش از یک دهه در تأمین قطعات الکترونیک از سال 1391، شرکت مایکروالکام با تمرکز بر تأمین قطعات الکترونیک برای صنایع تولیدی، همراه شما بوده است. با بهره‌گیری از تخصص تیمی حرفه‌ای و تعهد به ارائه بهترین خدمات، موفق به ساخت جایگاهی قابل‌اعتماد در این صنعت شده‌ایم. دفاتر ما در اصفهان و شنزن (چین)، به‌عنوان پل ارتباطی میان تولیدکنندگان ایرانی و تأمین‌کنندگان جهانی، همواره در تلاش برای تسهیل فرایند تأمین و تضمین کیفیت هستند. چه به‌دنبال بهترین قیمت باشید، چه به‌دنبال جدیدترین فناوری‌ها، ما اینجا هستیم تا شما را یاری کنیم. در مسیر رشد و توسعه، با چالش‌های متعددی روبرو بوده‌ایم، اما همیشه بهبود و ارائه راه‌حل‌های نوآورانه، هدف اصلی ما بوده است. با خدمات منحصربه‌فرد ما، می‌توانید قطعات مورد نیاز خود را بدون دغدغه تأمین کرده و بر رشد کسب‌وکار خود تمرکز کنید. مایکروالکام؛ پلی مطمئن میان تولیدکنندگان و بازارهای جهانی مایکروالکام 2012-2026 منو محصولات ماژول ها RF CAMERA CONVERTOR AUDIO Clock &amp; Timer Memories Electromechanic Measurement Bio-metric Analog Ultra Sonic Motion تغذیه و محافظ مدار Batterys Battery Mangment Circuit protection Power supply led Drivers مخابراتی و آر اف ANTENNA Remote Controller نیمه هادی ها IC leds-optoelectronics sensors-transducers Diode Transistor ISOLATOR TRIAC &amp; SCR Signal Thyristor TVS الکترومکانیک Key Pad switchs AUDIO Relay سیم و کابل Shielded wire کانکتور و سوکت ها IC socket Coaxial connectors Headers &amp; Wire Housings Circuit connectors Terminals Audio connectors Power connectors pluggable-connectors usb connectors Memory Connectors قطعات غیر فعال الکترونیکی Capacitors Resistors Inductors, Coils, Choks Thermal-management Circuite Protection نمایشگرها LCD بردهای توسعه Evaluation Boards Raspberry pi Orange Pi Arduino STM نوسان سازها Crystals جعبه ها Plastic Box Metal Box Spacer &amp; Screw ابزار Laboratory Instruments Workshop tools Crimping tool وبلاگ مونتاژ ماشینی بردهای الکترونیکی تنظیمات محصولات ماژول ها RF CAMERA CONVERTOR AUDIO Clock &amp; Timer Memories Electromechanic Measurement Bio-metric Analog Ultra Sonic Motion تغذیه و محافظ مدار Batterys Battery Mangment Circuit protection Power supply led Drivers مخابراتی و آر اف ANTENNA Remote Controller نیمه هادی ها IC leds-optoelectronics sensors-transducers Diode Transistor ISOLATOR TRIAC &amp; SCR Signal Thyristor TVS الکترومکانیک Key Pad switchs AUDIO Relay سیم و کابل Shielded wire کانکتور و سوکت ها IC socket Coaxial connectors Headers &amp; Wire Housings Circuit connectors Terminals Audio connectors Power connectors pluggable-connectors usb connectors Memory Connectors قطعات غیر فعال الکترونیکی Capacitors Resistors Inductors, Coils, Choks Thermal-management Circuite Protection نمایشگرها LCD بردهای توسعه Evaluation Boards Raspberry pi Orange Pi Arduino STM نوسان سازها Crystals جعبه ها Plastic Box Metal Box Spacer &amp; Screw ابزار Laboratory Instruments Workshop tools Crimping tool وبلاگ مونتاژ ماشینی بردهای الکترونیکی ورود | ثبت نام جستجو برای محصولات بیشتر کلیک کنید. هیچ محصولی یافت نشد. بازدیدهای اخیر 430251000,P3mm,Molex 550,000 ریال لیست دلخواه ذخیره در لیست علاقه‌مندی My wishlist ( 0 ) aria-hidden="true" ایجاد مورد علاقه بدون آیتم جستجو جستجو برای محصولات بیشتر کلیک کنید. هیچ محصولی یافت نشد. سبد خرید سبد خرید شما خالی است. کد QR اشتراک‌گذاری هم‌‌‌رسانی در واتساپ هم رسانی در اینستاگرام هم رسانی در ایتا هم‌رسانی در تلگرام هم‌‌‌رسانی در پینترست سبد خرید 0 جستجو بالا لطفا اول به حساب کاربری خود وارد شوید ورود به حساب کاربری برای ذخیره آیتم‌های مورد علاقه، یک حساب کاربری رایگان ایجاد کنید. ورود به حساب کاربری برای استفاده از لیست‌های علاقه‌مندی، یک حساب کاربری رایگان بسازید. ورود به حساب کاربری ×</t>
+          <t>430251000,P3mm,Molex در صورت هر گونه مشکل در روند ثبت سفارش با شماره 09134722518 تماس بگیرید ورود | ثبت نام منو تنظیمات جستجو برای محصولات بیشتر کلیک کنید. هیچ محصولی یافت نشد. 0 آیتم - 0 ریال سبد خرید شما خالی است. دسته‌بندی‌ها ماژول ها RF GSM/GPRS RFID 3G ISM ZIGBEE BLUETOOTH WIFI RF BOOSTER GPS/GLONASS FM Radio NB-IoT 4G Audio CAMERA CONVERTOR DC-DC INTERFACE AUDIO Amplifier Players/Recorder Clock &amp; Timer RTC TIMER Memories SD &amp; Micro SD Electromechanic Relay Measurement Distance Voltage GAS LOAD ANGEL Humid&amp;Temprature Bio-metric Finger Analog A2D Ultra Sonic Humidifier Motion PIR مخابراتی و آر اف ANTENNA GSM GPS WIFI UHF 3G Remote Controller Fixed Code Learning Reciver نیمه هادی ها IC microcontrollers FPGA Logic IC Analog IC Voltage Reference eprom Flash Regulators PMIC Interface Step-Down Converter leds-optoelectronics Led Block Led Strip led Led Leans Laser LED Series sensors-transducers Light temprature Encoders Image Sensors, Camera Magnetic Motion Sensors Humidity Vibration Sensor Diode Rectifier Schottky Zener Fast Transistor BJT RFBJT MOSFET ISOLATOR OPTO ISOLATOR TRIAC &amp; SCR Thyristor Signal Thyristor Thyristor TVS DIODS تغذیه و محافظ مدار Batterys Nickel-Cadmium (NiCd) Nikel-Metal (NiMH) Li-Polimer Li-Ion Alkaline Lithium Zinc-Carbon Battery Mangment Battery charger Circuit protection Battery protection Power supply Switching Power Supply POWER CONTROL Adapter USB Charger led Drivers Circuit Board الکترومکانیک Key Pad Flat Keypad Other KeyPad switchs Micro Switch Dip Switch AUDIO Speaker Buzzer Microphone Relay Power Relay کانکتور و سوکت ها IC socket ZIF Socket SMD Adaptor Coaxial connectors SMA UFL BNC MCX MMCX Ntype SMB UHF TS9 Headers &amp; Wire Housings PIN HEADER XH Connector Circuit connectors PTR DC JACK Push Connectors Terminals ATX Audio connectors phone jack Power connectors Battery FUSE Power pluggable-connectors sata PS2 usb connectors Type A Type B Memory Connectors MMC/SD/uSD SIMCARD SMART CARD سیم و کابل Shielded wire RG AC Power نمایشگرها LCD Character graphic TFT LCD نوسان سازها Crystals KHz MHz قطعات غیر فعال الکترونیکی Capacitors Electrolytic Tantalum Ceramic Polyester Supercaps Resistors Thick Film Inductors, Coils, Choks Fixed Inductors Thermal-management Heat-sinks Thermal-pads-sheets Circuite Protection Fuse بردهای توسعه Evaluation Boards GSM GPS Raspberry pi Raspberry Boards Raspberry accessory Orange Pi Orange Pi Boards Arduino Arduino Boards Arduino Shields Arduino Accessories STM جعبه ها Plastic Box Plastic profile Plastic Box Metal Box Aluminum Profile Spacer &amp; Screw ابزار Laboratory Instruments multimeters Bread Board Soldering Workshop tools BreadBoard Crimping tool bnc Crimping Network محصولات ماژول ها RF CAMERA CONVERTOR AUDIO Clock &amp; Timer Memories Electromechanic Measurement Bio-metric Analog Ultra Sonic Motion تغذیه و محافظ مدار Batterys Battery Mangment Circuit protection Power supply led Drivers مخابراتی و آر اف ANTENNA Remote Controller نیمه هادی ها IC leds-optoelectronics sensors-transducers Diode Transistor ISOLATOR TRIAC &amp; SCR Signal Thyristor TVS الکترومکانیک Key Pad switchs AUDIO Relay سیم و کابل Shielded wire کانکتور و سوکت ها IC socket Coaxial connectors Headers &amp; Wire Housings Circuit connectors Terminals Audio connectors Power connectors pluggable-connectors usb connectors Memory Connectors قطعات غیر فعال الکترونیکی Capacitors Resistors Inductors, Coils, Choks Thermal-management Circuite Protection نمایشگرها LCD بردهای توسعه Evaluation Boards Raspberry pi Orange Pi Arduino STM نوسان سازها Crystals جعبه ها Plastic Box Metal Box Spacer &amp; Screw ابزار Laboratory Instruments Workshop tools Crimping tool وبلاگ مونتاژ ماشینی بردهای الکترونیکی خانه &gt; کانکتور و سوکت ها &gt; Power connectors &gt; 430251000,P3mm,Molex جدید 430251000,P3mm,Molex کد محصول: 160501015 Connector Housings ATX,Molex ادامه مطلب نمایش کمتر 550,000 ریال بدون مالیات افزودن به سبد خرید اشتراک‌گذاری برای خرید عمده و دریافت قیمت ویژه این محصول، با ما تماس بگیرید: 03132373281 علاقه‌مندی 0 افزودن به لیست علاقه‌مندی‌ها افزودن به مقایسه 0 کد QR توضیحات جزئیات محصول نظرات توضیحات قطعه Molex 430251000 یک Micro-Fit 3.0 Receptacle Housing با فاصله پایه (Pitch) 3.00mm است. این کانکتور در رده‌ی Connector Housings قرار دارد و برای کاربردهای Wire-to-Board و Wire-to-Wire طراحی شده است ادامه مطلب نمایش کمتر جزئیات محصول مرجع 160501015 مشخصات پارت نامبر 430251000,P3mm,Molex رنگ مشکی نوع کاربرد Power, Wire-to-Board, Wire-to-Wire پکیج Receptacle Housing (سوکت مادگی) دمای کاری 40°C ~ 105°C- فاصله پین ها (mm) 3mm نظرات بدون نظر 14 محصولات مشابه در شاخه های مختلف: کانکتور بین راهی 2 پین SM 126,000 ریال 2Pin, 9cm,Femal, 22AWG افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی جک آداپتوری روپانلی فلزی مدل DC-025M 304,000 ریال جک مخصوص آداپتور افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی ناموجود ست کانکتور ضدآب 0.75*2 0 ریال 2PIN WATERPROOF CONNECTOR علاقه‌مندی مشاهده بیشتر علاقه‌مندی ناموجود فیوز باکس 0 ریال مخصوص فیوز شیشه ای کوچک علاقه‌مندی مشاهده بیشتر علاقه‌مندی ناموجود ست کانکتور ضدآب 0.3*2 0 ریال 2PIN WATERPROOF CONNECTOR علاقه‌مندی مشاهده بیشتر علاقه‌مندی ناموجود ست کانکتور ضدآب 0.5*4 0 ریال 4PIN WATERPROOF CONNECTOR علاقه‌مندی مشاهده بیشتر علاقه‌مندی جک آداپتوری DC 2.5mm 48,000 ریال قطر مغزی 2.5mm افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی ناموجود جک شارژ لپ تاپ HP &amp; Acer 0 ریال Jack charger,HP,Acer,laptop علاقه‌مندی مشاهده بیشتر علاقه‌مندی پین فیوز 35,400 ریال افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی جک آداپتوری DC 2.1mm 48,900 ریال قطر مغزی 2.1mm افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی جک شارژ لپ تاپ SONY 47,000 ریال Jack charger,SONY,laptop افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی سوکت باطری سکه ای 2032 76,500 ریال سوکت باطری سکه ای افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی جک آداپتوری روپانلی مدل DC-022 117,000 ریال جک مخصوص آداپتور افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی جک شارژ لپ تاپ TOSHIBA 537,000 ریال Jack charger,TOSHIBA,laptop افزودن به سبد خرید علاقه‌مندی مشاهده بیشتر علاقه‌مندی اطلاعات تماس با مایکروالکام آدرس اصفهان، خیابان طالقانی، نرسیده به چهارراه شمس آبادی، مجتمع الماس ،طبقه اول، واحد 103 تلفن 03132373281 آدرس ایمیل info[at]microele.com چرا مایکروالکام؟ پشتیبانی سریع و متنوع تنوع محصولات گارانتی بازگشت پرداخت امن کیفیت محصولات ثبت شکایت راهنمای کاربران چگونه خرید کنم؟ چگونه محصول را دریافت میکنم؟ رهگیری سفارش شماره حساب‌ها پرداخت آنلاین وجه دسترسی سریع وبلاگ مایکروالکام محصولات جدید محصولات پر فروش درباره مایکروالکام تماس با مایکروالکام مایکروالکام؛ تجربه‌ای بیش از یک دهه در تأمین قطعات الکترونیک از سال 1391، شرکت مایکروالکام با تمرکز بر تأمین قطعات الکترونیک برای صنایع تولیدی، همراه شما بوده است. با بهره‌گیری از تخصص تیمی حرفه‌ای و تعهد به ارائه بهترین خدمات، موفق به ساخت جایگاهی قابل‌اعتماد در این صنعت شده‌ایم. دفاتر ما در اصفهان و شنزن (چین)، به‌عنوان پل ارتباطی میان تولیدکنندگان ایرانی و تأمین‌کنندگان جهانی، همواره در تلاش برای تسهیل فرایند تأمین و تضمین کیفیت هستند. چه به‌دنبال بهترین قیمت باشید، چه به‌دنبال جدیدترین فناوری‌ها، ما اینجا هستیم تا شما را یاری کنیم. در مسیر رشد و توسعه، با چالش‌های متعددی روبرو بوده‌ایم، اما همیشه بهبود و ارائه راه‌حل‌های نوآورانه، هدف اصلی ما بوده است. با خدمات منحصربه‌فرد ما، می‌توانید قطعات مورد نیاز خود را بدون دغدغه تأمین کرده و بر رشد کسب‌وکار خود تمرکز کنید. مایکروالکام؛ پلی مطمئن میان تولیدکنندگان و بازارهای جهانی مایکروالکام 2012-2026 منو محصولات ماژول ها RF CAMERA CONVERTOR AUDIO Clock &amp; Timer Memories Electromechanic Measurement Bio-metric Analog Ultra Sonic Motion تغذیه و محافظ مدار Batterys Battery Mangment Circuit protection Power supply led Drivers مخابراتی و آر اف ANTENNA Remote Controller نیمه هادی ها IC leds-optoelectronics sensors-transducers Diode Transistor ISOLATOR TRIAC &amp; SCR Signal Thyristor TVS الکترومکانیک Key Pad switchs AUDIO Relay سیم و کابل Shielded wire کانکتور و سوکت ها IC socket Coaxial connectors Headers &amp; Wire Housings Circuit connectors Terminals Audio connectors Power connectors pluggable-connectors usb connectors Memory Connectors قطعات غیر فعال الکترونیکی Capacitors Resistors Inductors, Coils, Choks Thermal-management Circuite Protection نمایشگرها LCD بردهای توسعه Evaluation Boards Raspberry pi Orange Pi Arduino STM نوسان سازها Crystals جعبه ها Plastic Box Metal Box Spacer &amp; Screw ابزار Laboratory Instruments Workshop tools Crimping tool وبلاگ مونتاژ ماشینی بردهای الکترونیکی تنظیمات محصولات ماژول ها RF CAMERA CONVERTOR AUDIO Clock &amp; Timer Memories Electromechanic Measurement Bio-metric Analog Ultra Sonic Motion تغذیه و محافظ مدار Batterys Battery Mangment Circuit protection Power supply led Drivers مخابراتی و آر اف ANTENNA Remote Controller نیمه هادی ها IC leds-optoelectronics sensors-transducers Diode Transistor ISOLATOR TRIAC &amp; SCR Signal Thyristor TVS الکترومکانیک Key Pad switchs AUDIO Relay سیم و کابل Shielded wire کانکتور و سوکت ها IC socket Coaxial connectors Headers &amp; Wire Housings Circuit connectors Terminals Audio connectors Power connectors pluggable-connectors usb connectors Memory Connectors قطعات غیر فعال الکترونیکی Capacitors Resistors Inductors, Coils, Choks Thermal-management Circuite Protection نمایشگرها LCD بردهای توسعه Evaluation Boards Raspberry pi Orange Pi Arduino STM نوسان سازها Crystals جعبه ها Plastic Box Metal Box Spacer &amp; Screw ابزار Laboratory Instruments Workshop tools Crimping tool وبلاگ مونتاژ ماشینی بردهای الکترونیکی ورود | ثبت نام جستجو برای محصولات بیشتر کلیک کنید. هیچ محصولی یافت نشد. بازدیدهای اخیر 430251000,P3mm,Molex 550,000 ریال لیست دلخواه ذخیره در لیست علاقه‌مندی My wishlist ( 0 ) aria-hidden="true" ایجاد مورد علاقه بدون آیتم جستجو جستجو برای محصولات بیشتر کلیک کنید. هیچ محصولی یافت نشد. سبد خرید سبد خرید شما خالی است. کد QR اشتراک‌گذاری هم‌‌‌رسانی در واتساپ هم رسانی در اینستاگرام هم رسانی در ایتا هم‌رسانی در تلگرام هم‌‌‌رسانی در پینترست سبد خرید 0 جستجو بالا لطفا اول به حساب کاربری خود وارد شوید ورود به حساب کاربری برای ذخیره آیتم‌های مورد علاقه، یک حساب کاربری رایگان ایجاد کنید. ورود به حساب کاربری برای استفاده از لیست‌های علاقه‌مندی، یک حساب کاربری رایگان بسازید. ورود به حساب کاربری ×</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1894,21 +1885,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
+      <c r="F45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>308807650</v>
+      <c r="G46" s="3" t="n">
+        <v>158025390</v>
       </c>
     </row>
   </sheetData>
